--- a/Assets/StreamingAssets/Configurations/Cards.xlsx
+++ b/Assets/StreamingAssets/Configurations/Cards.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D55A90A4-454D-4EAC-B4DF-FF3F047F18B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="24750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -30,6 +24,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -930,26 +926,176 @@
     <t>当红温大于50层时</t>
   </si>
   <si>
+    <t>M卡用2次</t>
+  </si>
+  <si>
     <t>VCardTypeUsedCountCondition</t>
-  </si>
-  <si>
-    <t>M卡用2次</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -968,11 +1114,206 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFFF0000"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -987,17 +1328,250 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
       <right style="thin">
-        <color rgb="FFFF0000"/>
+        <color rgb="FF7F7F7F"/>
       </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
-      <bottom/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1005,34 +1579,78 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFFFFFFF"/>
-      <color rgb="FFAB0580"/>
-      <color rgb="FF00B050"/>
-      <color rgb="FFFFB200"/>
-      <color rgb="FF4B58FF"/>
-      <color rgb="FFFF2160"/>
+      <color rgb="00FFFFFF"/>
+      <color rgb="00AB0580"/>
+      <color rgb="0000B050"/>
+      <color rgb="00FFB200"/>
+      <color rgb="004B58FF"/>
+      <color rgb="00FF2160"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1290,43 +1908,42 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:AE61"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="3.425" customWidth="1"/>
+    <col min="2" max="2" width="12.7083333333333" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" style="4" customWidth="1"/>
-    <col min="8" max="8" width="7.140625" customWidth="1"/>
-    <col min="9" max="9" width="14" style="4" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" customWidth="1"/>
-    <col min="11" max="11" width="13.7109375" customWidth="1"/>
-    <col min="12" max="12" width="9.7109375" style="4" customWidth="1"/>
-    <col min="13" max="13" width="9.7109375" customWidth="1"/>
-    <col min="14" max="14" width="12.140625" customWidth="1"/>
-    <col min="15" max="15" width="17.7109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="10.425" customWidth="1"/>
+    <col min="5" max="5" width="13.425" customWidth="1"/>
+    <col min="6" max="6" width="10.5666666666667" customWidth="1"/>
+    <col min="7" max="7" width="9.70833333333333" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7.14166666666667" customWidth="1"/>
+    <col min="9" max="9" width="14" style="2" customWidth="1"/>
+    <col min="10" max="10" width="10.2833333333333" customWidth="1"/>
+    <col min="11" max="11" width="13.7083333333333" customWidth="1"/>
+    <col min="12" max="12" width="9.70833333333333" style="2" customWidth="1"/>
+    <col min="13" max="13" width="9.70833333333333" customWidth="1"/>
+    <col min="14" max="14" width="12.1416666666667" customWidth="1"/>
+    <col min="15" max="15" width="17.7083333333333" style="2" customWidth="1"/>
     <col min="16" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="12.28515625" customWidth="1"/>
-    <col min="18" max="18" width="17.140625" style="4" customWidth="1"/>
-    <col min="21" max="21" width="17.7109375" style="4" customWidth="1"/>
-    <col min="22" max="22" width="10.7109375" customWidth="1"/>
+    <col min="17" max="17" width="12.2833333333333" customWidth="1"/>
+    <col min="18" max="18" width="17.1416666666667" style="2" customWidth="1"/>
+    <col min="21" max="21" width="17.7083333333333" style="2" customWidth="1"/>
+    <col min="22" max="22" width="10.7083333333333" customWidth="1"/>
     <col min="23" max="23" width="11" customWidth="1"/>
-    <col min="24" max="24" width="17.7109375" style="4" customWidth="1"/>
-    <col min="25" max="25" width="12.42578125" customWidth="1"/>
-    <col min="26" max="26" width="12.42578125" style="4" customWidth="1"/>
-    <col min="27" max="27" width="12.28515625" customWidth="1"/>
-    <col min="28" max="28" width="9" style="4"/>
-    <col min="29" max="29" width="4.28515625" customWidth="1"/>
+    <col min="24" max="24" width="17.7083333333333" style="2" customWidth="1"/>
+    <col min="25" max="25" width="12.425" customWidth="1"/>
+    <col min="26" max="26" width="12.425" style="2" customWidth="1"/>
+    <col min="27" max="27" width="12.2833333333333" customWidth="1"/>
+    <col min="28" max="28" width="9" style="2"/>
+    <col min="29" max="29" width="4.28333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31">
@@ -1348,13 +1965,13 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
@@ -1363,55 +1980,55 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
       <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
       <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
       <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="3" t="s">
         <v>21</v>
       </c>
       <c r="W1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="Z1" s="2" t="s">
         <v>25</v>
       </c>
       <c r="AA1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AB1" s="2" t="s">
         <v>27</v>
       </c>
       <c r="AC1" t="s">
@@ -1421,7 +2038,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:31">
+    <row r="2" hidden="1" spans="1:31">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1441,10 +2058,10 @@
         <v>34</v>
       </c>
       <c r="G2"/>
-      <c r="H2" s="2">
+      <c r="H2" s="3">
         <v>4</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="2">
         <v>3</v>
       </c>
       <c r="J2">
@@ -1454,13 +2071,13 @@
         <v>0</v>
       </c>
       <c r="L2"/>
-      <c r="M2" s="2">
+      <c r="M2" s="3">
         <v>11</v>
       </c>
       <c r="N2">
         <v>7</v>
       </c>
-      <c r="O2" s="4">
+      <c r="O2" s="2">
         <v>7</v>
       </c>
       <c r="R2"/>
@@ -1473,7 +2090,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" hidden="1" spans="1:31">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1493,10 +2110,10 @@
         <v>34</v>
       </c>
       <c r="G3"/>
-      <c r="H3" s="2">
-        <v>0</v>
-      </c>
-      <c r="I3" s="4">
+      <c r="H3" s="3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
         <v>0</v>
       </c>
       <c r="J3">
@@ -1506,13 +2123,13 @@
         <v>0</v>
       </c>
       <c r="L3"/>
-      <c r="M3" s="2">
+      <c r="M3" s="3">
         <v>2</v>
       </c>
       <c r="N3">
         <v>4</v>
       </c>
-      <c r="O3" s="4">
+      <c r="O3" s="2">
         <v>4</v>
       </c>
       <c r="R3"/>
@@ -1547,7 +2164,7 @@
       <c r="H4">
         <v>5</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="2">
         <v>4</v>
       </c>
       <c r="J4">
@@ -1556,13 +2173,13 @@
       <c r="K4">
         <v>0</v>
       </c>
-      <c r="M4" s="2">
+      <c r="M4" s="3">
         <v>11</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
-      <c r="O4" s="4">
+      <c r="O4" s="2">
         <v>18</v>
       </c>
       <c r="P4">
@@ -1571,7 +2188,7 @@
       <c r="Q4">
         <v>9</v>
       </c>
-      <c r="R4" s="4">
+      <c r="R4" s="2">
         <v>12</v>
       </c>
       <c r="AC4" s="5"/>
@@ -1579,7 +2196,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" hidden="1" spans="1:31">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1599,10 +2216,10 @@
         <v>34</v>
       </c>
       <c r="G5"/>
-      <c r="H5" s="2">
-        <v>3</v>
-      </c>
-      <c r="I5" s="4">
+      <c r="H5" s="3">
+        <v>3</v>
+      </c>
+      <c r="I5" s="2">
         <v>3</v>
       </c>
       <c r="J5">
@@ -1612,22 +2229,22 @@
         <v>0</v>
       </c>
       <c r="L5"/>
-      <c r="M5" s="2">
+      <c r="M5" s="3">
         <v>11</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
-      <c r="O5" s="4">
+      <c r="O5" s="2">
         <v>5</v>
       </c>
-      <c r="P5" s="2">
+      <c r="P5" s="3">
         <v>2</v>
       </c>
       <c r="Q5">
         <v>2</v>
       </c>
-      <c r="R5" s="4">
+      <c r="R5" s="2">
         <v>2</v>
       </c>
       <c r="U5"/>
@@ -1658,13 +2275,13 @@
       <c r="F6" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="2">
         <v>3</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6" s="2">
         <v>1</v>
       </c>
       <c r="J6">
@@ -1673,7 +2290,7 @@
       <c r="K6">
         <v>1</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6" s="3">
         <v>0</v>
       </c>
       <c r="P6">
@@ -1682,7 +2299,7 @@
       <c r="Q6">
         <v>2</v>
       </c>
-      <c r="R6" s="4">
+      <c r="R6" s="2">
         <v>7</v>
       </c>
       <c r="S6">
@@ -1691,7 +2308,7 @@
       <c r="T6">
         <v>1</v>
       </c>
-      <c r="U6" s="4">
+      <c r="U6" s="2">
         <v>1</v>
       </c>
       <c r="AC6" s="5"/>
@@ -1699,7 +2316,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" hidden="1" spans="1:31">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1719,10 +2336,10 @@
         <v>34</v>
       </c>
       <c r="G7"/>
-      <c r="H7" s="2">
+      <c r="H7" s="3">
         <v>5</v>
       </c>
-      <c r="I7" s="4">
+      <c r="I7" s="2">
         <v>4</v>
       </c>
       <c r="J7">
@@ -1732,26 +2349,26 @@
         <v>1</v>
       </c>
       <c r="L7"/>
-      <c r="M7" s="2">
+      <c r="M7" s="3">
         <v>4</v>
       </c>
       <c r="O7"/>
-      <c r="P7" s="2">
+      <c r="P7" s="3">
         <v>21</v>
       </c>
       <c r="Q7">
         <v>2</v>
       </c>
-      <c r="R7" s="4">
-        <v>2</v>
-      </c>
-      <c r="S7" s="2">
+      <c r="R7" s="2">
+        <v>2</v>
+      </c>
+      <c r="S7" s="3">
         <v>14</v>
       </c>
       <c r="T7">
         <v>1</v>
       </c>
-      <c r="U7" s="4">
+      <c r="U7" s="2">
         <v>1</v>
       </c>
       <c r="X7"/>
@@ -1762,7 +2379,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:31">
+    <row r="8" hidden="1" spans="1:31">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1784,10 +2401,10 @@
       <c r="G8">
         <v>0</v>
       </c>
-      <c r="H8" s="2">
-        <v>1</v>
-      </c>
-      <c r="I8" s="4">
+      <c r="H8" s="3">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2">
         <v>1</v>
       </c>
       <c r="J8">
@@ -1797,31 +2414,31 @@
         <v>1</v>
       </c>
       <c r="L8"/>
-      <c r="M8" s="2">
+      <c r="M8" s="3">
         <v>2</v>
       </c>
       <c r="N8">
         <v>7</v>
       </c>
-      <c r="O8" s="4">
+      <c r="O8" s="2">
         <v>7</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P8" s="3">
         <v>3</v>
       </c>
       <c r="Q8">
         <v>1</v>
       </c>
-      <c r="R8" s="4">
-        <v>1</v>
-      </c>
-      <c r="S8" s="2">
+      <c r="R8" s="2">
+        <v>1</v>
+      </c>
+      <c r="S8" s="3">
         <v>14</v>
       </c>
       <c r="T8">
         <v>1</v>
       </c>
-      <c r="U8" s="4">
+      <c r="U8" s="2">
         <v>1</v>
       </c>
       <c r="X8"/>
@@ -1832,7 +2449,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:31">
+    <row r="9" hidden="1" spans="1:31">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1852,10 +2469,10 @@
         <v>34</v>
       </c>
       <c r="G9"/>
-      <c r="H9" s="2">
-        <v>2</v>
-      </c>
-      <c r="I9" s="4">
+      <c r="H9" s="3">
+        <v>2</v>
+      </c>
+      <c r="I9" s="2">
         <v>2</v>
       </c>
       <c r="J9">
@@ -1865,22 +2482,22 @@
         <v>0</v>
       </c>
       <c r="L9"/>
-      <c r="M9" s="2">
+      <c r="M9" s="3">
         <v>6</v>
       </c>
       <c r="N9">
         <v>3</v>
       </c>
-      <c r="O9" s="4">
+      <c r="O9" s="2">
         <v>4</v>
       </c>
-      <c r="P9" s="2">
+      <c r="P9" s="3">
         <v>2</v>
       </c>
       <c r="Q9">
         <v>3</v>
       </c>
-      <c r="R9" s="4">
+      <c r="R9" s="2">
         <v>4</v>
       </c>
       <c r="U9"/>
@@ -1892,7 +2509,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:31">
+    <row r="10" hidden="1" spans="1:31">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1912,10 +2529,10 @@
         <v>34</v>
       </c>
       <c r="G10"/>
-      <c r="H10" s="2">
-        <v>2</v>
-      </c>
-      <c r="I10" s="4">
+      <c r="H10" s="3">
+        <v>2</v>
+      </c>
+      <c r="I10" s="2">
         <v>2</v>
       </c>
       <c r="J10">
@@ -1925,22 +2542,22 @@
         <v>0</v>
       </c>
       <c r="L10"/>
-      <c r="M10" s="2">
+      <c r="M10" s="3">
         <v>7</v>
       </c>
       <c r="N10">
         <v>2</v>
       </c>
-      <c r="O10" s="4">
-        <v>3</v>
-      </c>
-      <c r="P10" s="2">
+      <c r="O10" s="2">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3">
         <v>2</v>
       </c>
       <c r="Q10">
         <v>2</v>
       </c>
-      <c r="R10" s="4">
+      <c r="R10" s="2">
         <v>3</v>
       </c>
       <c r="U10"/>
@@ -1974,7 +2591,7 @@
       <c r="H11">
         <v>2</v>
       </c>
-      <c r="I11" s="4">
+      <c r="I11" s="2">
         <v>2</v>
       </c>
       <c r="J11">
@@ -1983,22 +2600,22 @@
       <c r="K11">
         <v>0</v>
       </c>
-      <c r="M11" s="2">
+      <c r="M11" s="3">
         <v>15</v>
       </c>
       <c r="N11">
         <v>2</v>
       </c>
-      <c r="O11" s="4">
-        <v>3</v>
-      </c>
-      <c r="P11" s="2">
+      <c r="O11" s="2">
+        <v>3</v>
+      </c>
+      <c r="P11" s="3">
         <v>2</v>
       </c>
       <c r="Q11">
         <v>2</v>
       </c>
-      <c r="R11" s="4">
+      <c r="R11" s="2">
         <v>3</v>
       </c>
       <c r="AC11" s="5"/>
@@ -2006,7 +2623,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:31">
+    <row r="12" hidden="1" spans="1:31">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2026,10 +2643,10 @@
         <v>34</v>
       </c>
       <c r="G12"/>
-      <c r="H12" s="2">
+      <c r="H12" s="3">
         <v>6</v>
       </c>
-      <c r="I12" s="4">
+      <c r="I12" s="2">
         <v>6</v>
       </c>
       <c r="J12">
@@ -2039,22 +2656,22 @@
         <v>0</v>
       </c>
       <c r="L12"/>
-      <c r="M12" s="2">
+      <c r="M12" s="3">
         <v>11</v>
       </c>
       <c r="N12">
         <v>9</v>
       </c>
-      <c r="O12" s="4">
+      <c r="O12" s="2">
         <v>13</v>
       </c>
-      <c r="P12" s="2">
+      <c r="P12" s="3">
         <v>11</v>
       </c>
       <c r="Q12">
         <v>9</v>
       </c>
-      <c r="R12" s="4">
+      <c r="R12" s="2">
         <v>13</v>
       </c>
       <c r="U12"/>
@@ -2069,7 +2686,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:31">
+    <row r="13" hidden="1" spans="1:31">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2089,10 +2706,10 @@
         <v>34</v>
       </c>
       <c r="G13"/>
-      <c r="H13" s="2">
+      <c r="H13" s="3">
         <v>5</v>
       </c>
-      <c r="I13" s="4">
+      <c r="I13" s="2">
         <v>5</v>
       </c>
       <c r="J13">
@@ -2102,22 +2719,22 @@
         <v>0</v>
       </c>
       <c r="L13"/>
-      <c r="M13" s="2">
+      <c r="M13" s="3">
         <v>11</v>
       </c>
       <c r="N13">
         <v>11</v>
       </c>
-      <c r="O13" s="4">
+      <c r="O13" s="2">
         <v>15</v>
       </c>
-      <c r="P13" s="2">
+      <c r="P13" s="3">
         <v>2</v>
       </c>
       <c r="Q13">
         <v>7</v>
       </c>
-      <c r="R13" s="4">
+      <c r="R13" s="2">
         <v>9</v>
       </c>
       <c r="U13"/>
@@ -2129,7 +2746,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:31">
+    <row r="14" hidden="1" spans="1:31">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2149,10 +2766,10 @@
         <v>34</v>
       </c>
       <c r="G14"/>
-      <c r="H14" s="2">
+      <c r="H14" s="3">
         <v>5</v>
       </c>
-      <c r="I14" s="4">
+      <c r="I14" s="2">
         <v>4</v>
       </c>
       <c r="J14">
@@ -2162,13 +2779,13 @@
         <v>0</v>
       </c>
       <c r="L14"/>
-      <c r="M14" s="2">
+      <c r="M14" s="3">
         <v>6</v>
       </c>
       <c r="N14">
         <v>6</v>
       </c>
-      <c r="O14" s="4">
+      <c r="O14" s="2">
         <v>8</v>
       </c>
       <c r="R14"/>
@@ -2181,7 +2798,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:31">
+    <row r="15" hidden="1" spans="1:31">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2201,10 +2818,10 @@
         <v>34</v>
       </c>
       <c r="G15"/>
-      <c r="H15" s="2">
+      <c r="H15" s="3">
         <v>4</v>
       </c>
-      <c r="I15" s="4">
+      <c r="I15" s="2">
         <v>4</v>
       </c>
       <c r="J15">
@@ -2214,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="L15"/>
-      <c r="M15" s="2">
+      <c r="M15" s="3">
         <v>18</v>
       </c>
       <c r="N15">
         <v>1.4</v>
       </c>
-      <c r="O15" s="4">
+      <c r="O15" s="2">
         <v>1.8</v>
       </c>
       <c r="R15"/>
@@ -2233,7 +2850,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:31">
+    <row r="16" hidden="1" spans="1:31">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2253,10 +2870,10 @@
         <v>34</v>
       </c>
       <c r="G16"/>
-      <c r="H16" s="2">
+      <c r="H16" s="3">
         <v>6</v>
       </c>
-      <c r="I16" s="4">
+      <c r="I16" s="2">
         <v>5</v>
       </c>
       <c r="J16">
@@ -2266,23 +2883,23 @@
         <v>0</v>
       </c>
       <c r="L16"/>
-      <c r="M16" s="2">
+      <c r="M16" s="3">
         <v>6</v>
       </c>
       <c r="N16">
         <v>4</v>
       </c>
-      <c r="O16" s="4">
+      <c r="O16" s="2">
         <v>5</v>
       </c>
-      <c r="P16" s="2">
+      <c r="P16" s="3">
         <v>18</v>
       </c>
       <c r="Q16">
         <v>0.8</v>
       </c>
-      <c r="R16" s="4">
-        <v>1.1000000000000001</v>
+      <c r="R16" s="2">
+        <v>1.1</v>
       </c>
       <c r="U16"/>
       <c r="X16"/>
@@ -2293,7 +2910,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:31">
+    <row r="17" hidden="1" spans="1:31">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2313,10 +2930,10 @@
         <v>34</v>
       </c>
       <c r="G17"/>
-      <c r="H17" s="2">
-        <v>3</v>
-      </c>
-      <c r="I17" s="4">
+      <c r="H17" s="3">
+        <v>3</v>
+      </c>
+      <c r="I17" s="2">
         <v>3</v>
       </c>
       <c r="J17">
@@ -2326,31 +2943,31 @@
         <v>1</v>
       </c>
       <c r="L17"/>
-      <c r="M17" s="2">
+      <c r="M17" s="3">
         <v>19</v>
       </c>
       <c r="N17">
         <v>1</v>
       </c>
-      <c r="O17" s="4">
-        <v>1</v>
-      </c>
-      <c r="P17" s="2">
+      <c r="O17" s="2">
+        <v>1</v>
+      </c>
+      <c r="P17" s="3">
         <v>2</v>
       </c>
       <c r="Q17">
         <v>4</v>
       </c>
-      <c r="R17" s="4">
+      <c r="R17" s="2">
         <v>6</v>
       </c>
-      <c r="S17" s="2">
+      <c r="S17" s="3">
         <v>21</v>
       </c>
       <c r="T17">
         <v>2</v>
       </c>
-      <c r="U17" s="4">
+      <c r="U17" s="2">
         <v>3</v>
       </c>
       <c r="X17"/>
@@ -2383,7 +3000,7 @@
       <c r="H18">
         <v>4</v>
       </c>
-      <c r="I18" s="4">
+      <c r="I18" s="2">
         <v>3</v>
       </c>
       <c r="J18">
@@ -2392,19 +3009,19 @@
       <c r="K18">
         <v>0</v>
       </c>
-      <c r="M18" s="2">
+      <c r="M18" s="3">
         <v>15</v>
       </c>
       <c r="N18">
         <v>5</v>
       </c>
-      <c r="O18" s="4">
+      <c r="O18" s="2">
         <v>7</v>
       </c>
       <c r="Y18">
         <v>61</v>
       </c>
-      <c r="Z18" s="4">
+      <c r="Z18" s="2">
         <v>1.5</v>
       </c>
       <c r="AC18" s="5"/>
@@ -2412,7 +3029,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:31">
+    <row r="19" hidden="1" spans="1:31">
       <c r="A19">
         <v>19</v>
       </c>
@@ -2432,10 +3049,10 @@
         <v>34</v>
       </c>
       <c r="G19"/>
-      <c r="H19" s="2">
+      <c r="H19" s="3">
         <v>5</v>
       </c>
-      <c r="I19" s="4">
+      <c r="I19" s="2">
         <v>4</v>
       </c>
       <c r="J19">
@@ -2445,22 +3062,22 @@
         <v>1</v>
       </c>
       <c r="L19"/>
-      <c r="M19" s="2">
+      <c r="M19" s="3">
         <v>23</v>
       </c>
       <c r="N19">
         <v>1</v>
       </c>
-      <c r="O19" s="4">
-        <v>1</v>
-      </c>
-      <c r="P19" s="2">
+      <c r="O19" s="2">
+        <v>1</v>
+      </c>
+      <c r="P19" s="3">
         <v>7</v>
       </c>
       <c r="Q19">
         <v>1</v>
       </c>
-      <c r="R19" s="4">
+      <c r="R19" s="2">
         <v>2</v>
       </c>
       <c r="U19"/>
@@ -2494,7 +3111,7 @@
       <c r="H20">
         <v>6</v>
       </c>
-      <c r="I20" s="4">
+      <c r="I20" s="2">
         <v>6</v>
       </c>
       <c r="J20">
@@ -2503,22 +3120,22 @@
       <c r="K20">
         <v>0</v>
       </c>
-      <c r="L20" s="4">
-        <v>0</v>
-      </c>
-      <c r="M20" s="2">
+      <c r="L20" s="2">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>11</v>
       </c>
       <c r="N20">
         <v>24</v>
       </c>
-      <c r="O20" s="4">
+      <c r="O20" s="2">
         <v>30</v>
       </c>
       <c r="Y20">
         <v>62</v>
       </c>
-      <c r="Z20" s="4">
+      <c r="Z20" s="2">
         <v>7</v>
       </c>
       <c r="AC20" s="6"/>
@@ -2548,7 +3165,7 @@
       <c r="H21">
         <v>5</v>
       </c>
-      <c r="I21" s="4">
+      <c r="I21" s="2">
         <v>4</v>
       </c>
       <c r="J21">
@@ -2557,22 +3174,22 @@
       <c r="K21">
         <v>1</v>
       </c>
-      <c r="M21" s="2">
+      <c r="M21" s="3">
         <v>26</v>
       </c>
       <c r="N21">
         <v>2</v>
       </c>
-      <c r="O21" s="4">
-        <v>2</v>
-      </c>
-      <c r="P21" s="2">
+      <c r="O21" s="2">
+        <v>2</v>
+      </c>
+      <c r="P21" s="3">
         <v>11</v>
       </c>
       <c r="Q21">
         <v>30</v>
       </c>
-      <c r="R21" s="4">
+      <c r="R21" s="2">
         <v>42</v>
       </c>
       <c r="S21">
@@ -2581,7 +3198,7 @@
       <c r="T21">
         <v>5</v>
       </c>
-      <c r="U21" s="4">
+      <c r="U21" s="2">
         <v>7</v>
       </c>
       <c r="AC21" s="5"/>
@@ -2589,7 +3206,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:31">
+    <row r="22" hidden="1" spans="1:31">
       <c r="A22">
         <v>22</v>
       </c>
@@ -2609,10 +3226,10 @@
         <v>34</v>
       </c>
       <c r="G22"/>
-      <c r="H22" s="2">
+      <c r="H22" s="3">
         <v>4</v>
       </c>
-      <c r="I22" s="4">
+      <c r="I22" s="2">
         <v>4</v>
       </c>
       <c r="J22">
@@ -2622,22 +3239,22 @@
         <v>1</v>
       </c>
       <c r="L22"/>
-      <c r="M22" s="2">
+      <c r="M22" s="3">
         <v>6</v>
       </c>
       <c r="N22">
         <v>2</v>
       </c>
-      <c r="O22" s="4">
+      <c r="O22" s="2">
         <v>4</v>
       </c>
-      <c r="P22" s="2">
+      <c r="P22" s="3">
         <v>28</v>
       </c>
       <c r="Q22">
         <v>1</v>
       </c>
-      <c r="R22" s="4">
+      <c r="R22" s="2">
         <v>1</v>
       </c>
       <c r="U22"/>
@@ -2649,7 +3266,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:31">
+    <row r="23" hidden="1" spans="1:31">
       <c r="A23">
         <v>23</v>
       </c>
@@ -2669,10 +3286,10 @@
         <v>34</v>
       </c>
       <c r="G23"/>
-      <c r="H23" s="2">
-        <v>1</v>
-      </c>
-      <c r="I23" s="4">
+      <c r="H23" s="3">
+        <v>1</v>
+      </c>
+      <c r="I23" s="2">
         <v>1</v>
       </c>
       <c r="J23">
@@ -2682,22 +3299,22 @@
         <v>0</v>
       </c>
       <c r="L23"/>
-      <c r="M23" s="2">
+      <c r="M23" s="3">
         <v>6</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
-      <c r="O23" s="4">
+      <c r="O23" s="2">
         <v>7</v>
       </c>
-      <c r="P23" s="2">
+      <c r="P23" s="3">
         <v>2</v>
       </c>
       <c r="Q23">
         <v>1</v>
       </c>
-      <c r="R23" s="4">
+      <c r="R23" s="2">
         <v>1</v>
       </c>
       <c r="U23"/>
@@ -2731,7 +3348,7 @@
       <c r="H24">
         <v>4</v>
       </c>
-      <c r="I24" s="4">
+      <c r="I24" s="2">
         <v>4</v>
       </c>
       <c r="J24">
@@ -2740,28 +3357,28 @@
       <c r="K24">
         <v>0</v>
       </c>
-      <c r="M24" s="2">
+      <c r="M24" s="3">
         <v>15</v>
       </c>
       <c r="N24">
         <v>3</v>
       </c>
-      <c r="O24" s="4">
+      <c r="O24" s="2">
         <v>4</v>
       </c>
-      <c r="P24" s="2">
+      <c r="P24" s="3">
         <v>11</v>
       </c>
       <c r="Q24">
         <v>8</v>
       </c>
-      <c r="R24" s="4">
+      <c r="R24" s="2">
         <v>11</v>
       </c>
       <c r="Y24">
         <v>63</v>
       </c>
-      <c r="Z24" s="4">
+      <c r="Z24" s="2">
         <v>3</v>
       </c>
       <c r="AC24" s="5"/>
@@ -2769,7 +3386,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:31">
+    <row r="25" hidden="1" spans="1:31">
       <c r="A25">
         <v>25</v>
       </c>
@@ -2789,10 +3406,10 @@
         <v>34</v>
       </c>
       <c r="G25"/>
-      <c r="H25" s="2">
-        <v>3</v>
-      </c>
-      <c r="I25" s="4">
+      <c r="H25" s="3">
+        <v>3</v>
+      </c>
+      <c r="I25" s="2">
         <v>2</v>
       </c>
       <c r="J25">
@@ -2802,13 +3419,13 @@
         <v>0</v>
       </c>
       <c r="L25"/>
-      <c r="M25" s="2">
+      <c r="M25" s="3">
         <v>7</v>
       </c>
       <c r="N25">
         <v>3</v>
       </c>
-      <c r="O25" s="4">
+      <c r="O25" s="2">
         <v>5</v>
       </c>
       <c r="R25"/>
@@ -2821,7 +3438,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="26" spans="1:31">
+    <row r="26" hidden="1" spans="1:31">
       <c r="A26">
         <v>26</v>
       </c>
@@ -2841,10 +3458,10 @@
         <v>34</v>
       </c>
       <c r="G26"/>
-      <c r="H26" s="2">
-        <v>3</v>
-      </c>
-      <c r="I26" s="4">
+      <c r="H26" s="3">
+        <v>3</v>
+      </c>
+      <c r="I26" s="2">
         <v>2</v>
       </c>
       <c r="J26">
@@ -2854,22 +3471,22 @@
         <v>0</v>
       </c>
       <c r="L26"/>
-      <c r="M26" s="2">
+      <c r="M26" s="3">
         <v>7</v>
       </c>
       <c r="N26">
         <v>3</v>
       </c>
-      <c r="O26" s="4">
+      <c r="O26" s="2">
         <v>4</v>
       </c>
-      <c r="P26" s="2">
+      <c r="P26" s="3">
         <v>2</v>
       </c>
       <c r="Q26">
         <v>4</v>
       </c>
-      <c r="R26" s="4">
+      <c r="R26" s="2">
         <v>6</v>
       </c>
       <c r="U26"/>
@@ -2903,7 +3520,7 @@
       <c r="H27">
         <v>8</v>
       </c>
-      <c r="I27" s="4">
+      <c r="I27" s="2">
         <v>6</v>
       </c>
       <c r="J27">
@@ -2912,25 +3529,25 @@
       <c r="K27">
         <v>1</v>
       </c>
-      <c r="L27" s="4">
-        <v>0</v>
-      </c>
-      <c r="M27" s="2">
+      <c r="L27" s="2">
+        <v>0</v>
+      </c>
+      <c r="M27" s="3">
         <v>11</v>
       </c>
       <c r="N27">
         <v>12</v>
       </c>
-      <c r="O27" s="4">
+      <c r="O27" s="2">
         <v>18</v>
       </c>
-      <c r="P27" s="2">
+      <c r="P27" s="3">
         <v>56</v>
       </c>
       <c r="Q27">
         <v>24</v>
       </c>
-      <c r="R27" s="4">
+      <c r="R27" s="2">
         <v>30</v>
       </c>
       <c r="S27">
@@ -2939,7 +3556,7 @@
       <c r="T27">
         <v>36</v>
       </c>
-      <c r="U27" s="4">
+      <c r="U27" s="2">
         <v>44</v>
       </c>
       <c r="AC27" s="6"/>
@@ -2969,7 +3586,7 @@
       <c r="H28">
         <v>1</v>
       </c>
-      <c r="I28" s="4">
+      <c r="I28" s="2">
         <v>0</v>
       </c>
       <c r="J28">
@@ -2978,19 +3595,19 @@
       <c r="K28">
         <v>0</v>
       </c>
-      <c r="M28" s="2">
+      <c r="M28" s="3">
         <v>2</v>
       </c>
       <c r="N28">
         <v>6</v>
       </c>
-      <c r="O28" s="4">
+      <c r="O28" s="2">
         <v>8</v>
       </c>
       <c r="Y28">
         <v>21</v>
       </c>
-      <c r="Z28" s="4">
+      <c r="Z28" s="2">
         <v>12</v>
       </c>
       <c r="AC28" s="5"/>
@@ -2998,7 +3615,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:31">
+    <row r="29" hidden="1" spans="1:31">
       <c r="A29">
         <v>30</v>
       </c>
@@ -3018,10 +3635,10 @@
         <v>34</v>
       </c>
       <c r="G29"/>
-      <c r="H29" s="2">
+      <c r="H29" s="3">
         <v>5</v>
       </c>
-      <c r="I29" s="4">
+      <c r="I29" s="2">
         <v>5</v>
       </c>
       <c r="J29">
@@ -3031,31 +3648,31 @@
         <v>1</v>
       </c>
       <c r="L29"/>
-      <c r="M29" s="2">
+      <c r="M29" s="3">
         <v>32</v>
       </c>
       <c r="N29">
         <v>30</v>
       </c>
-      <c r="O29" s="4">
+      <c r="O29" s="2">
         <v>30</v>
       </c>
-      <c r="P29" s="2">
+      <c r="P29" s="3">
         <v>2</v>
       </c>
       <c r="Q29">
         <v>3</v>
       </c>
-      <c r="R29" s="4">
+      <c r="R29" s="2">
         <v>5</v>
       </c>
-      <c r="S29" s="2">
+      <c r="S29" s="3">
         <v>21</v>
       </c>
       <c r="T29">
         <v>2</v>
       </c>
-      <c r="U29" s="4">
+      <c r="U29" s="2">
         <v>3</v>
       </c>
       <c r="X29"/>
@@ -3066,7 +3683,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="1:31">
+    <row r="30" hidden="1" spans="1:31">
       <c r="A30">
         <v>31</v>
       </c>
@@ -3086,10 +3703,10 @@
         <v>34</v>
       </c>
       <c r="G30"/>
-      <c r="H30" s="2">
+      <c r="H30" s="3">
         <v>4</v>
       </c>
-      <c r="I30" s="4">
+      <c r="I30" s="2">
         <v>4</v>
       </c>
       <c r="J30">
@@ -3099,22 +3716,22 @@
         <v>1</v>
       </c>
       <c r="L30"/>
-      <c r="M30" s="2">
+      <c r="M30" s="3">
         <v>33</v>
       </c>
       <c r="N30">
         <v>50</v>
       </c>
-      <c r="O30" s="4">
+      <c r="O30" s="2">
         <v>70</v>
       </c>
-      <c r="P30" s="2">
+      <c r="P30" s="3">
         <v>2</v>
       </c>
       <c r="Q30">
         <v>2</v>
       </c>
-      <c r="R30" s="4">
+      <c r="R30" s="2">
         <v>4</v>
       </c>
       <c r="U30"/>
@@ -3126,7 +3743,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="1:31">
+    <row r="31" hidden="1" spans="1:31">
       <c r="A31">
         <v>32</v>
       </c>
@@ -3146,10 +3763,10 @@
         <v>34</v>
       </c>
       <c r="G31"/>
-      <c r="H31" s="2">
+      <c r="H31" s="3">
         <v>4</v>
       </c>
-      <c r="I31" s="4">
+      <c r="I31" s="2">
         <v>3</v>
       </c>
       <c r="J31">
@@ -3159,22 +3776,22 @@
         <v>1</v>
       </c>
       <c r="L31"/>
-      <c r="M31" s="2">
+      <c r="M31" s="3">
         <v>33</v>
       </c>
       <c r="N31">
         <v>20</v>
       </c>
-      <c r="O31" s="4">
+      <c r="O31" s="2">
         <v>30</v>
       </c>
-      <c r="P31" s="2">
+      <c r="P31" s="3">
         <v>35</v>
       </c>
       <c r="Q31">
         <v>1</v>
       </c>
-      <c r="R31" s="4">
+      <c r="R31" s="2">
         <v>1</v>
       </c>
       <c r="U31"/>
@@ -3186,7 +3803,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:31">
+    <row r="32" hidden="1" spans="1:31">
       <c r="A32">
         <v>33</v>
       </c>
@@ -3206,10 +3823,10 @@
         <v>34</v>
       </c>
       <c r="G32"/>
-      <c r="H32" s="2">
+      <c r="H32" s="3">
         <v>7</v>
       </c>
-      <c r="I32" s="4">
+      <c r="I32" s="2">
         <v>6</v>
       </c>
       <c r="J32">
@@ -3251,7 +3868,7 @@
       <c r="H33">
         <v>8</v>
       </c>
-      <c r="I33" s="4">
+      <c r="I33" s="2">
         <v>7</v>
       </c>
       <c r="J33">
@@ -3260,19 +3877,19 @@
       <c r="K33">
         <v>1</v>
       </c>
-      <c r="M33" s="2">
+      <c r="M33" s="3">
         <v>11</v>
       </c>
       <c r="N33">
         <v>38</v>
       </c>
-      <c r="O33" s="4">
+      <c r="O33" s="2">
         <v>52</v>
       </c>
       <c r="Y33">
         <v>64</v>
       </c>
-      <c r="Z33" s="4">
+      <c r="Z33" s="2">
         <v>1</v>
       </c>
       <c r="AE33" t="s">
@@ -3301,7 +3918,7 @@
       <c r="H34">
         <v>3</v>
       </c>
-      <c r="I34" s="4">
+      <c r="I34" s="2">
         <v>3</v>
       </c>
       <c r="J34">
@@ -3310,16 +3927,16 @@
       <c r="K34">
         <v>0</v>
       </c>
-      <c r="L34" s="4">
-        <v>0</v>
-      </c>
-      <c r="M34" s="2">
+      <c r="L34" s="2">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
         <v>15</v>
       </c>
       <c r="N34">
         <v>3</v>
       </c>
-      <c r="O34" s="4">
+      <c r="O34" s="2">
         <v>4</v>
       </c>
       <c r="AE34" t="s">
@@ -3348,7 +3965,7 @@
       <c r="H35">
         <v>3</v>
       </c>
-      <c r="I35" s="4">
+      <c r="I35" s="2">
         <v>3</v>
       </c>
       <c r="J35">
@@ -3357,13 +3974,13 @@
       <c r="K35">
         <v>0</v>
       </c>
-      <c r="M35" s="2">
+      <c r="M35" s="3">
         <v>11</v>
       </c>
       <c r="N35">
         <v>18</v>
       </c>
-      <c r="O35" s="4">
+      <c r="O35" s="2">
         <v>22</v>
       </c>
       <c r="AE35" t="s">
@@ -3374,7 +3991,7 @@
       <c r="A36">
         <v>37</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B36" s="4">
         <v>144</v>
       </c>
       <c r="C36" t="s">
@@ -3392,7 +4009,7 @@
       <c r="H36">
         <v>3</v>
       </c>
-      <c r="I36" s="4">
+      <c r="I36" s="2">
         <v>3</v>
       </c>
       <c r="J36">
@@ -3401,29 +4018,29 @@
       <c r="K36">
         <v>0</v>
       </c>
-      <c r="M36" s="2">
+      <c r="M36" s="3">
         <v>15</v>
       </c>
       <c r="N36">
         <v>3</v>
       </c>
-      <c r="O36" s="4">
+      <c r="O36" s="2">
         <v>4</v>
       </c>
-      <c r="P36" s="2">
+      <c r="P36" s="3">
         <v>2</v>
       </c>
       <c r="Q36">
         <v>6</v>
       </c>
-      <c r="R36" s="4">
+      <c r="R36" s="2">
         <v>8</v>
       </c>
       <c r="AE36" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="1:31">
+    <row r="37" hidden="1" spans="1:31">
       <c r="A37">
         <v>38</v>
       </c>
@@ -3443,10 +4060,10 @@
         <v>34</v>
       </c>
       <c r="G37"/>
-      <c r="H37" s="2">
-        <v>3</v>
-      </c>
-      <c r="I37" s="4">
+      <c r="H37" s="3">
+        <v>3</v>
+      </c>
+      <c r="I37" s="2">
         <v>3</v>
       </c>
       <c r="J37">
@@ -3456,22 +4073,22 @@
         <v>0</v>
       </c>
       <c r="L37"/>
-      <c r="M37" s="2">
+      <c r="M37" s="3">
         <v>7</v>
       </c>
       <c r="N37">
         <v>3</v>
       </c>
-      <c r="O37" s="4">
+      <c r="O37" s="2">
         <v>4</v>
       </c>
-      <c r="P37" s="2">
+      <c r="P37" s="3">
         <v>2</v>
       </c>
       <c r="Q37">
         <v>6</v>
       </c>
-      <c r="R37" s="4">
+      <c r="R37" s="2">
         <v>8</v>
       </c>
       <c r="U37"/>
@@ -3482,7 +4099,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="38" spans="1:31">
+    <row r="38" hidden="1" spans="1:31">
       <c r="A38">
         <v>39</v>
       </c>
@@ -3502,10 +4119,10 @@
         <v>34</v>
       </c>
       <c r="G38"/>
-      <c r="H38" s="2">
-        <v>1</v>
-      </c>
-      <c r="I38" s="4">
+      <c r="H38" s="3">
+        <v>1</v>
+      </c>
+      <c r="I38" s="2">
         <v>1</v>
       </c>
       <c r="J38">
@@ -3515,22 +4132,22 @@
         <v>1</v>
       </c>
       <c r="L38"/>
-      <c r="M38" s="2">
+      <c r="M38" s="3">
         <v>21</v>
       </c>
       <c r="N38">
         <v>4</v>
       </c>
-      <c r="O38" s="4">
+      <c r="O38" s="2">
         <v>5</v>
       </c>
-      <c r="P38" s="2">
+      <c r="P38" s="3">
         <v>2</v>
       </c>
       <c r="Q38">
         <v>3</v>
       </c>
-      <c r="R38" s="4">
+      <c r="R38" s="2">
         <v>5</v>
       </c>
       <c r="U38"/>
@@ -3541,7 +4158,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:31">
+    <row r="39" hidden="1" spans="1:31">
       <c r="A39">
         <v>40</v>
       </c>
@@ -3561,10 +4178,10 @@
         <v>34</v>
       </c>
       <c r="G39"/>
-      <c r="H39" s="2">
-        <v>1</v>
-      </c>
-      <c r="I39" s="4">
+      <c r="H39" s="3">
+        <v>1</v>
+      </c>
+      <c r="I39" s="2">
         <v>1</v>
       </c>
       <c r="J39">
@@ -3574,22 +4191,22 @@
         <v>1</v>
       </c>
       <c r="L39"/>
-      <c r="M39" s="2">
+      <c r="M39" s="3">
         <v>5</v>
       </c>
       <c r="N39">
         <v>1</v>
       </c>
-      <c r="O39" s="4">
-        <v>2</v>
-      </c>
-      <c r="P39" s="2">
+      <c r="O39" s="2">
+        <v>2</v>
+      </c>
+      <c r="P39" s="3">
         <v>2</v>
       </c>
       <c r="Q39">
         <v>6</v>
       </c>
-      <c r="R39" s="4">
+      <c r="R39" s="2">
         <v>7</v>
       </c>
       <c r="U39"/>
@@ -3600,7 +4217,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="1:31">
+    <row r="40" hidden="1" spans="1:31">
       <c r="A40">
         <v>41</v>
       </c>
@@ -3620,10 +4237,10 @@
         <v>34</v>
       </c>
       <c r="G40"/>
-      <c r="H40" s="2">
+      <c r="H40" s="3">
         <v>4</v>
       </c>
-      <c r="I40" s="4">
+      <c r="I40" s="2">
         <v>3</v>
       </c>
       <c r="J40">
@@ -3633,22 +4250,22 @@
         <v>1</v>
       </c>
       <c r="L40"/>
-      <c r="M40" s="2">
+      <c r="M40" s="3">
         <v>7</v>
       </c>
       <c r="N40">
         <v>4</v>
       </c>
-      <c r="O40" s="4">
+      <c r="O40" s="2">
         <v>5</v>
       </c>
-      <c r="P40" s="2">
+      <c r="P40" s="3">
         <v>38</v>
       </c>
       <c r="Q40">
         <v>4</v>
       </c>
-      <c r="R40" s="4">
+      <c r="R40" s="2">
         <v>5</v>
       </c>
       <c r="U40"/>
@@ -3659,7 +4276,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="41" spans="1:31">
+    <row r="41" hidden="1" spans="1:31">
       <c r="A41">
         <v>42</v>
       </c>
@@ -3679,10 +4296,10 @@
         <v>34</v>
       </c>
       <c r="G41"/>
-      <c r="H41" s="2">
-        <v>2</v>
-      </c>
-      <c r="I41" s="4">
+      <c r="H41" s="3">
+        <v>2</v>
+      </c>
+      <c r="I41" s="2">
         <v>2</v>
       </c>
       <c r="J41">
@@ -3692,22 +4309,22 @@
         <v>0</v>
       </c>
       <c r="L41"/>
-      <c r="M41" s="2">
+      <c r="M41" s="3">
         <v>6</v>
       </c>
       <c r="N41">
         <v>3</v>
       </c>
-      <c r="O41" s="4">
-        <v>3</v>
-      </c>
-      <c r="P41" s="2">
+      <c r="O41" s="2">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3">
         <v>39</v>
       </c>
       <c r="Q41">
         <v>2</v>
       </c>
-      <c r="R41" s="4">
+      <c r="R41" s="2">
         <v>3</v>
       </c>
       <c r="U41"/>
@@ -3718,7 +4335,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="42" spans="1:31">
+    <row r="42" hidden="1" spans="1:31">
       <c r="A42">
         <v>43</v>
       </c>
@@ -3738,10 +4355,10 @@
         <v>34</v>
       </c>
       <c r="G42"/>
-      <c r="H42" s="2">
+      <c r="H42" s="3">
         <v>4</v>
       </c>
-      <c r="I42" s="4">
+      <c r="I42" s="2">
         <v>3</v>
       </c>
       <c r="J42">
@@ -3751,22 +4368,22 @@
         <v>1</v>
       </c>
       <c r="L42"/>
-      <c r="M42" s="2">
+      <c r="M42" s="3">
         <v>7</v>
       </c>
       <c r="N42">
         <v>1</v>
       </c>
-      <c r="O42" s="4">
-        <v>3</v>
-      </c>
-      <c r="P42" s="2">
+      <c r="O42" s="2">
+        <v>3</v>
+      </c>
+      <c r="P42" s="3">
         <v>41</v>
       </c>
       <c r="Q42">
         <v>1</v>
       </c>
-      <c r="R42" s="4">
+      <c r="R42" s="2">
         <v>1</v>
       </c>
       <c r="U42"/>
@@ -3777,7 +4394,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="43" spans="1:31">
+    <row r="43" hidden="1" spans="1:31">
       <c r="A43">
         <v>44</v>
       </c>
@@ -3797,10 +4414,10 @@
         <v>34</v>
       </c>
       <c r="G43"/>
-      <c r="H43" s="2">
+      <c r="H43" s="3">
         <v>7</v>
       </c>
-      <c r="I43" s="4">
+      <c r="I43" s="2">
         <v>4</v>
       </c>
       <c r="J43">
@@ -3810,31 +4427,31 @@
         <v>1</v>
       </c>
       <c r="L43"/>
-      <c r="M43" s="2">
+      <c r="M43" s="3">
         <v>6</v>
       </c>
       <c r="N43">
         <v>5</v>
       </c>
-      <c r="O43" s="4">
+      <c r="O43" s="2">
         <v>5</v>
       </c>
-      <c r="P43" s="2">
+      <c r="P43" s="3">
         <v>14</v>
       </c>
       <c r="Q43">
         <v>1</v>
       </c>
-      <c r="R43" s="4">
-        <v>1</v>
-      </c>
-      <c r="S43" s="2">
+      <c r="R43" s="2">
+        <v>1</v>
+      </c>
+      <c r="S43" s="3">
         <v>18</v>
       </c>
       <c r="T43">
         <v>0.9</v>
       </c>
-      <c r="U43" s="4">
+      <c r="U43" s="2">
         <v>1.2</v>
       </c>
       <c r="X43"/>
@@ -3866,7 +4483,7 @@
       <c r="H44">
         <v>6</v>
       </c>
-      <c r="I44" s="4">
+      <c r="I44" s="2">
         <v>4</v>
       </c>
       <c r="J44">
@@ -3875,29 +4492,29 @@
       <c r="K44">
         <v>1</v>
       </c>
-      <c r="M44" s="2">
+      <c r="M44" s="3">
         <v>15</v>
       </c>
       <c r="N44">
         <v>2</v>
       </c>
-      <c r="O44" s="4">
-        <v>2</v>
-      </c>
-      <c r="P44" s="2">
+      <c r="O44" s="2">
+        <v>2</v>
+      </c>
+      <c r="P44" s="3">
         <v>42</v>
       </c>
       <c r="Q44">
         <v>8</v>
       </c>
-      <c r="R44" s="4">
+      <c r="R44" s="2">
         <v>12</v>
       </c>
       <c r="AE44" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="45" spans="1:31">
+    <row r="45" hidden="1" spans="1:31">
       <c r="A45">
         <v>46</v>
       </c>
@@ -3917,10 +4534,10 @@
         <v>34</v>
       </c>
       <c r="G45"/>
-      <c r="H45" s="2">
+      <c r="H45" s="3">
         <v>5</v>
       </c>
-      <c r="I45" s="4">
+      <c r="I45" s="2">
         <v>4</v>
       </c>
       <c r="J45">
@@ -3930,31 +4547,31 @@
         <v>1</v>
       </c>
       <c r="L45"/>
-      <c r="M45" s="2">
+      <c r="M45" s="3">
         <v>7</v>
       </c>
       <c r="N45">
         <v>7</v>
       </c>
-      <c r="O45" s="4">
+      <c r="O45" s="2">
         <v>9</v>
       </c>
-      <c r="P45" s="2">
+      <c r="P45" s="3">
         <v>26</v>
       </c>
       <c r="Q45">
         <v>2</v>
       </c>
-      <c r="R45" s="4">
-        <v>2</v>
-      </c>
-      <c r="S45" s="2">
+      <c r="R45" s="2">
+        <v>2</v>
+      </c>
+      <c r="S45" s="3">
         <v>2</v>
       </c>
       <c r="T45">
         <v>7</v>
       </c>
-      <c r="U45" s="4">
+      <c r="U45" s="2">
         <v>8</v>
       </c>
       <c r="X45"/>
@@ -3964,7 +4581,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="46" spans="1:31">
+    <row r="46" hidden="1" spans="1:31">
       <c r="A46">
         <v>47</v>
       </c>
@@ -3984,10 +4601,10 @@
         <v>34</v>
       </c>
       <c r="G46"/>
-      <c r="H46" s="2">
+      <c r="H46" s="3">
         <v>10</v>
       </c>
-      <c r="I46" s="4">
+      <c r="I46" s="2">
         <v>6</v>
       </c>
       <c r="J46">
@@ -3997,31 +4614,31 @@
         <v>1</v>
       </c>
       <c r="L46"/>
-      <c r="M46" s="2">
+      <c r="M46" s="3">
         <v>32</v>
       </c>
       <c r="N46">
         <v>40</v>
       </c>
-      <c r="O46" s="4">
+      <c r="O46" s="2">
         <v>40</v>
       </c>
-      <c r="P46" s="2">
+      <c r="P46" s="3">
         <v>33</v>
       </c>
       <c r="Q46">
         <v>30</v>
       </c>
-      <c r="R46" s="4">
+      <c r="R46" s="2">
         <v>30</v>
       </c>
-      <c r="S46" s="2">
+      <c r="S46" s="3">
         <v>19</v>
       </c>
       <c r="T46">
         <v>1</v>
       </c>
-      <c r="U46" s="4">
+      <c r="U46" s="2">
         <v>1</v>
       </c>
       <c r="X46"/>
@@ -4031,7 +4648,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="1:31">
+    <row r="47" hidden="1" spans="1:31">
       <c r="A47">
         <v>48</v>
       </c>
@@ -4051,10 +4668,10 @@
         <v>34</v>
       </c>
       <c r="G47"/>
-      <c r="H47" s="2">
-        <v>2</v>
-      </c>
-      <c r="I47" s="4">
+      <c r="H47" s="3">
+        <v>2</v>
+      </c>
+      <c r="I47" s="2">
         <v>1</v>
       </c>
       <c r="J47">
@@ -4064,13 +4681,13 @@
         <v>0</v>
       </c>
       <c r="L47"/>
-      <c r="M47" s="2">
+      <c r="M47" s="3">
         <v>11</v>
       </c>
       <c r="N47">
         <v>10</v>
       </c>
-      <c r="O47" s="4">
+      <c r="O47" s="2">
         <v>14</v>
       </c>
       <c r="R47"/>
@@ -4082,7 +4699,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="48" spans="1:31">
+    <row r="48" hidden="1" spans="1:31">
       <c r="A48">
         <v>49</v>
       </c>
@@ -4102,10 +4719,10 @@
         <v>34</v>
       </c>
       <c r="G48"/>
-      <c r="H48" s="2">
+      <c r="H48" s="3">
         <v>4</v>
       </c>
-      <c r="I48" s="4">
+      <c r="I48" s="2">
         <v>3</v>
       </c>
       <c r="J48">
@@ -4115,22 +4732,22 @@
         <v>0</v>
       </c>
       <c r="L48"/>
-      <c r="M48" s="2">
+      <c r="M48" s="3">
         <v>11</v>
       </c>
       <c r="N48">
         <v>8</v>
       </c>
-      <c r="O48" s="4">
+      <c r="O48" s="2">
         <v>11</v>
       </c>
-      <c r="P48" s="2">
+      <c r="P48" s="3">
         <v>6</v>
       </c>
       <c r="Q48">
         <v>3</v>
       </c>
-      <c r="R48" s="4">
+      <c r="R48" s="2">
         <v>3</v>
       </c>
       <c r="U48"/>
@@ -4163,7 +4780,7 @@
       <c r="H49">
         <v>4</v>
       </c>
-      <c r="I49" s="4">
+      <c r="I49" s="2">
         <v>3</v>
       </c>
       <c r="J49">
@@ -4172,29 +4789,29 @@
       <c r="K49">
         <v>0</v>
       </c>
-      <c r="M49" s="2">
+      <c r="M49" s="3">
         <v>11</v>
       </c>
       <c r="N49">
         <v>7</v>
       </c>
-      <c r="O49" s="4">
+      <c r="O49" s="2">
         <v>11</v>
       </c>
-      <c r="P49" s="2">
+      <c r="P49" s="3">
         <v>45</v>
       </c>
       <c r="Q49">
         <v>2</v>
       </c>
-      <c r="R49" s="4">
+      <c r="R49" s="2">
         <v>3</v>
       </c>
       <c r="AE49" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="1:31">
+    <row r="50" hidden="1" spans="1:31">
       <c r="A50">
         <v>51</v>
       </c>
@@ -4214,10 +4831,10 @@
         <v>34</v>
       </c>
       <c r="G50"/>
-      <c r="H50" s="2">
+      <c r="H50" s="3">
         <v>5</v>
       </c>
-      <c r="I50" s="4">
+      <c r="I50" s="2">
         <v>4</v>
       </c>
       <c r="J50">
@@ -4227,22 +4844,22 @@
         <v>1</v>
       </c>
       <c r="L50"/>
-      <c r="M50" s="2">
+      <c r="M50" s="3">
         <v>6</v>
       </c>
       <c r="N50">
         <v>5</v>
       </c>
-      <c r="O50" s="4">
+      <c r="O50" s="2">
         <v>7</v>
       </c>
-      <c r="P50" s="2">
+      <c r="P50" s="3">
         <v>18</v>
       </c>
       <c r="Q50">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="R50" s="4">
+        <v>1.1</v>
+      </c>
+      <c r="R50" s="2">
         <v>1.7</v>
       </c>
       <c r="U50"/>
@@ -4253,7 +4870,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="51" spans="1:31">
+    <row r="51" hidden="1" spans="1:31">
       <c r="A51">
         <v>52</v>
       </c>
@@ -4273,10 +4890,10 @@
         <v>34</v>
       </c>
       <c r="G51"/>
-      <c r="H51" s="2">
+      <c r="H51" s="3">
         <v>9</v>
       </c>
-      <c r="I51" s="4">
+      <c r="I51" s="2">
         <v>6</v>
       </c>
       <c r="J51">
@@ -4286,22 +4903,22 @@
         <v>1</v>
       </c>
       <c r="L51"/>
-      <c r="M51" s="2">
+      <c r="M51" s="3">
         <v>6</v>
       </c>
       <c r="N51">
         <v>1</v>
       </c>
-      <c r="O51" s="4">
-        <v>3</v>
-      </c>
-      <c r="P51" s="2">
+      <c r="O51" s="2">
+        <v>3</v>
+      </c>
+      <c r="P51" s="3">
         <v>49</v>
       </c>
       <c r="Q51">
         <v>1</v>
       </c>
-      <c r="R51" s="4">
+      <c r="R51" s="2">
         <v>1</v>
       </c>
       <c r="U51"/>
@@ -4312,7 +4929,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="52" spans="1:31">
+    <row r="52" hidden="1" spans="1:31">
       <c r="A52">
         <v>53</v>
       </c>
@@ -4332,10 +4949,10 @@
         <v>34</v>
       </c>
       <c r="G52"/>
-      <c r="H52" s="2">
-        <v>1</v>
-      </c>
-      <c r="I52" s="4">
+      <c r="H52" s="3">
+        <v>1</v>
+      </c>
+      <c r="I52" s="2">
         <v>0</v>
       </c>
       <c r="J52">
@@ -4345,22 +4962,22 @@
         <v>1</v>
       </c>
       <c r="L52"/>
-      <c r="M52" s="2">
+      <c r="M52" s="3">
         <v>9</v>
       </c>
       <c r="N52">
         <v>2</v>
       </c>
-      <c r="O52" s="4">
-        <v>2</v>
-      </c>
-      <c r="P52" s="2">
+      <c r="O52" s="2">
+        <v>2</v>
+      </c>
+      <c r="P52" s="3">
         <v>21</v>
       </c>
       <c r="Q52">
         <v>2</v>
       </c>
-      <c r="R52" s="4">
+      <c r="R52" s="2">
         <v>2</v>
       </c>
       <c r="U52"/>
@@ -4393,7 +5010,7 @@
       <c r="H53">
         <v>5</v>
       </c>
-      <c r="I53" s="4">
+      <c r="I53" s="2">
         <v>5</v>
       </c>
       <c r="J53">
@@ -4402,7 +5019,7 @@
       <c r="K53">
         <v>1</v>
       </c>
-      <c r="L53" s="4">
+      <c r="L53" s="2">
         <v>6</v>
       </c>
       <c r="M53">
@@ -4411,7 +5028,7 @@
       <c r="N53">
         <v>3</v>
       </c>
-      <c r="O53" s="4">
+      <c r="O53" s="2">
         <v>4</v>
       </c>
       <c r="P53">
@@ -4420,7 +5037,7 @@
       <c r="Q53">
         <v>-0.5</v>
       </c>
-      <c r="R53" s="4">
+      <c r="R53" s="2">
         <v>-0.5</v>
       </c>
       <c r="AE53" t="s">
@@ -4446,13 +5063,13 @@
       <c r="F54" t="s">
         <v>47</v>
       </c>
-      <c r="G54" s="4">
+      <c r="G54" s="2">
         <v>14</v>
       </c>
       <c r="H54">
         <v>2</v>
       </c>
-      <c r="I54" s="4">
+      <c r="I54" s="2">
         <v>1</v>
       </c>
       <c r="J54">
@@ -4467,7 +5084,7 @@
       <c r="N54">
         <v>3</v>
       </c>
-      <c r="O54" s="4">
+      <c r="O54" s="2">
         <v>4</v>
       </c>
       <c r="P54">
@@ -4476,7 +5093,7 @@
       <c r="Q54">
         <v>1</v>
       </c>
-      <c r="R54" s="4">
+      <c r="R54" s="2">
         <v>1</v>
       </c>
       <c r="S54">
@@ -4485,7 +5102,7 @@
       <c r="T54">
         <v>3</v>
       </c>
-      <c r="U54" s="4">
+      <c r="U54" s="2">
         <v>5</v>
       </c>
       <c r="AE54" t="s">
@@ -4514,7 +5131,7 @@
       <c r="H55">
         <v>4</v>
       </c>
-      <c r="I55" s="4">
+      <c r="I55" s="2">
         <v>3</v>
       </c>
       <c r="J55">
@@ -4529,7 +5146,7 @@
       <c r="N55">
         <v>1</v>
       </c>
-      <c r="O55" s="4">
+      <c r="O55" s="2">
         <v>3</v>
       </c>
       <c r="P55">
@@ -4538,10 +5155,10 @@
       <c r="Q55">
         <v>1</v>
       </c>
-      <c r="R55" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA55" s="4"/>
+      <c r="R55" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA55" s="2"/>
       <c r="AE55" t="s">
         <v>41</v>
       </c>
@@ -4565,13 +5182,13 @@
       <c r="F56" t="s">
         <v>47</v>
       </c>
-      <c r="G56" s="4">
+      <c r="G56" s="2">
         <v>3</v>
       </c>
       <c r="H56">
         <v>2</v>
       </c>
-      <c r="I56" s="4">
+      <c r="I56" s="2">
         <v>1</v>
       </c>
       <c r="J56">
@@ -4586,7 +5203,7 @@
       <c r="N56">
         <v>3</v>
       </c>
-      <c r="O56" s="4">
+      <c r="O56" s="2">
         <v>4</v>
       </c>
       <c r="P56">
@@ -4595,7 +5212,7 @@
       <c r="Q56">
         <v>12</v>
       </c>
-      <c r="R56" s="4">
+      <c r="R56" s="2">
         <v>18</v>
       </c>
       <c r="S56">
@@ -4604,10 +5221,10 @@
       <c r="T56">
         <v>1</v>
       </c>
-      <c r="U56" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA56" s="4"/>
+      <c r="U56" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA56" s="2"/>
       <c r="AE56" t="s">
         <v>41</v>
       </c>
@@ -4631,13 +5248,13 @@
       <c r="F57" t="s">
         <v>47</v>
       </c>
-      <c r="G57" s="4">
+      <c r="G57" s="2">
         <v>3</v>
       </c>
       <c r="H57">
         <v>2</v>
       </c>
-      <c r="I57" s="4">
+      <c r="I57" s="2">
         <v>1</v>
       </c>
       <c r="J57">
@@ -4652,7 +5269,7 @@
       <c r="N57">
         <v>5</v>
       </c>
-      <c r="O57" s="4">
+      <c r="O57" s="2">
         <v>6</v>
       </c>
       <c r="P57">
@@ -4661,7 +5278,7 @@
       <c r="Q57">
         <v>5</v>
       </c>
-      <c r="R57" s="4">
+      <c r="R57" s="2">
         <v>6</v>
       </c>
       <c r="AE57" t="s">
@@ -4690,7 +5307,7 @@
       <c r="H58">
         <v>3</v>
       </c>
-      <c r="I58" s="4">
+      <c r="I58" s="2">
         <v>2</v>
       </c>
       <c r="J58">
@@ -4725,7 +5342,7 @@
       <c r="H59">
         <v>4</v>
       </c>
-      <c r="I59" s="4">
+      <c r="I59" s="2">
         <v>3</v>
       </c>
       <c r="J59">
@@ -4740,7 +5357,7 @@
       <c r="N59">
         <v>7</v>
       </c>
-      <c r="O59" s="4">
+      <c r="O59" s="2">
         <v>9</v>
       </c>
       <c r="AE59" t="s">
@@ -4769,7 +5386,7 @@
       <c r="H60">
         <v>2</v>
       </c>
-      <c r="I60" s="4">
+      <c r="I60" s="2">
         <v>2</v>
       </c>
       <c r="J60">
@@ -4782,7 +5399,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="61" spans="1:31">
+    <row r="61" hidden="1" spans="1:11">
       <c r="A61">
         <v>62</v>
       </c>
@@ -4801,13 +5418,13 @@
       <c r="F61" t="s">
         <v>47</v>
       </c>
-      <c r="G61" s="4">
+      <c r="G61" s="2">
         <v>14</v>
       </c>
       <c r="H61">
         <v>3</v>
       </c>
-      <c r="I61" s="4">
+      <c r="I61" s="2">
         <v>2</v>
       </c>
       <c r="J61">
@@ -4818,32 +5435,34 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AE61" xr:uid="{00000000-0009-0000-0000-000000000000}">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AE61" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="30">
       <filters>
         <filter val="C"/>
-        <filter val="F"/>
       </filters>
     </filterColumn>
+    <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I62"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.42578125" customWidth="1"/>
+    <col min="1" max="1" width="3.425" customWidth="1"/>
+    <col min="2" max="2" width="27.425" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
     <col min="4" max="4" width="33" customWidth="1"/>
-    <col min="5" max="5" width="19.28515625" customWidth="1"/>
-    <col min="6" max="6" width="18.85546875" customWidth="1"/>
-    <col min="7" max="8" width="10.28515625" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" customWidth="1"/>
+    <col min="5" max="5" width="19.2833333333333" customWidth="1"/>
+    <col min="6" max="6" width="18.8583333333333" customWidth="1"/>
+    <col min="7" max="8" width="10.2833333333333" customWidth="1"/>
+    <col min="9" max="9" width="15.1416666666667" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6167,24 +6786,26 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:O22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.42578125" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" customWidth="1"/>
-    <col min="4" max="5" width="16.140625" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" customWidth="1"/>
+    <col min="1" max="1" width="9.425" customWidth="1"/>
+    <col min="2" max="2" width="27.425" customWidth="1"/>
+    <col min="3" max="3" width="14.425" customWidth="1"/>
+    <col min="4" max="5" width="16.1416666666667" customWidth="1"/>
+    <col min="6" max="6" width="12.425" customWidth="1"/>
+    <col min="7" max="7" width="14.425" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="10.140625" customWidth="1"/>
+    <col min="10" max="10" width="10.1416666666667" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6235,7 +6856,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:9">
       <c r="A2">
         <v>0</v>
       </c>
@@ -6264,7 +6885,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
@@ -6287,7 +6908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>2</v>
       </c>
@@ -6304,7 +6925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>3</v>
       </c>
@@ -6339,7 +6960,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>4</v>
       </c>
@@ -6362,7 +6983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>5</v>
       </c>
@@ -6385,7 +7006,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>6</v>
       </c>
@@ -6408,7 +7029,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>7</v>
       </c>
@@ -6431,7 +7052,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>8</v>
       </c>
@@ -6454,7 +7075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:9">
       <c r="A11">
         <v>9</v>
       </c>
@@ -6483,7 +7104,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:9">
       <c r="A12">
         <v>10</v>
       </c>
@@ -6512,7 +7133,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>11</v>
       </c>
@@ -6535,7 +7156,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>12</v>
       </c>
@@ -6558,7 +7179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>13</v>
       </c>
@@ -6581,7 +7202,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>14</v>
       </c>
@@ -6650,7 +7271,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>17</v>
       </c>
@@ -6667,7 +7288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>18</v>
       </c>
@@ -6684,7 +7305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>19</v>
       </c>
@@ -6726,22 +7347,24 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.85833333333333" customWidth="1"/>
+    <col min="2" max="2" width="22.7083333333333" customWidth="1"/>
+    <col min="3" max="3" width="28.5666666666667" customWidth="1"/>
+    <col min="4" max="4" width="15.5666666666667" customWidth="1"/>
+    <col min="5" max="5" width="16.1416666666667" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" customWidth="1"/>
+    <col min="7" max="7" width="11.1416666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -6767,7 +7390,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>0</v>
       </c>
@@ -6787,7 +7410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="12.95" customHeight="1">
+    <row r="3" ht="12.95" customHeight="1" spans="1:6">
       <c r="A3">
         <v>1</v>
       </c>
@@ -6804,7 +7427,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="12.95" customHeight="1">
+    <row r="4" ht="12.95" customHeight="1" spans="1:6">
       <c r="A4">
         <v>2</v>
       </c>
@@ -6821,7 +7444,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>3</v>
       </c>
@@ -6841,7 +7464,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>4</v>
       </c>
@@ -6861,7 +7484,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>5</v>
       </c>
@@ -6881,7 +7504,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>6</v>
       </c>
@@ -6901,7 +7524,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>7</v>
       </c>
@@ -6921,7 +7544,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>8</v>
       </c>
@@ -6941,15 +7564,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
+        <v>297</v>
+      </c>
+      <c r="C11" t="s">
         <v>298</v>
-      </c>
-      <c r="C11" t="s">
-        <v>297</v>
       </c>
       <c r="D11" t="s">
         <v>287</v>
@@ -6963,6 +7586,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Cards.xlsx
+++ b/Assets/StreamingAssets/Configurations/Cards.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{688C71BD-0AE5-418B-B638-597A12AAA34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -24,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -935,167 +939,17 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1114,194 +968,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1327,251 +995,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1586,71 +1012,27 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="00FFFFFF"/>
-      <color rgb="00AB0580"/>
-      <color rgb="0000B050"/>
-      <color rgb="00FFB200"/>
-      <color rgb="004B58FF"/>
-      <color rgb="00FF2160"/>
+      <color rgb="FFFFFFFF"/>
+      <color rgb="FFAB0580"/>
+      <color rgb="FF00B050"/>
+      <color rgb="FFFFB200"/>
+      <color rgb="FF4B58FF"/>
+      <color rgb="FFFF2160"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1908,42 +1290,43 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:AE61"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.425" customWidth="1"/>
-    <col min="2" max="2" width="12.7083333333333" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
-    <col min="4" max="4" width="10.425" customWidth="1"/>
-    <col min="5" max="5" width="13.425" customWidth="1"/>
-    <col min="6" max="6" width="10.5666666666667" customWidth="1"/>
-    <col min="7" max="7" width="9.70833333333333" style="2" customWidth="1"/>
-    <col min="8" max="8" width="7.14166666666667" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7.140625" customWidth="1"/>
     <col min="9" max="9" width="14" style="2" customWidth="1"/>
-    <col min="10" max="10" width="10.2833333333333" customWidth="1"/>
-    <col min="11" max="11" width="13.7083333333333" customWidth="1"/>
-    <col min="12" max="12" width="9.70833333333333" style="2" customWidth="1"/>
-    <col min="13" max="13" width="9.70833333333333" customWidth="1"/>
-    <col min="14" max="14" width="12.1416666666667" customWidth="1"/>
-    <col min="15" max="15" width="17.7083333333333" style="2" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" customWidth="1"/>
+    <col min="11" max="11" width="13.7109375" customWidth="1"/>
+    <col min="12" max="12" width="9.7109375" style="2" customWidth="1"/>
+    <col min="13" max="13" width="9.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.140625" customWidth="1"/>
+    <col min="15" max="15" width="17.7109375" style="2" customWidth="1"/>
     <col min="16" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="12.2833333333333" customWidth="1"/>
-    <col min="18" max="18" width="17.1416666666667" style="2" customWidth="1"/>
-    <col min="21" max="21" width="17.7083333333333" style="2" customWidth="1"/>
-    <col min="22" max="22" width="10.7083333333333" customWidth="1"/>
+    <col min="17" max="17" width="12.28515625" customWidth="1"/>
+    <col min="18" max="18" width="17.140625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="17.7109375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="11" customWidth="1"/>
-    <col min="24" max="24" width="17.7083333333333" style="2" customWidth="1"/>
-    <col min="25" max="25" width="12.425" customWidth="1"/>
-    <col min="26" max="26" width="12.425" style="2" customWidth="1"/>
-    <col min="27" max="27" width="12.2833333333333" customWidth="1"/>
+    <col min="24" max="24" width="17.7109375" style="2" customWidth="1"/>
+    <col min="25" max="25" width="12.42578125" customWidth="1"/>
+    <col min="26" max="26" width="12.42578125" style="2" customWidth="1"/>
+    <col min="27" max="27" width="12.28515625" customWidth="1"/>
     <col min="28" max="28" width="9" style="2"/>
-    <col min="29" max="29" width="4.28333333333333" customWidth="1"/>
+    <col min="29" max="29" width="4.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31">
@@ -2038,7 +1421,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" hidden="1" spans="1:31">
+    <row r="2" spans="1:31" hidden="1">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2090,7 +1473,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" hidden="1" spans="1:31">
+    <row r="3" spans="1:31" hidden="1">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2196,7 +1579,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" hidden="1" spans="1:31">
+    <row r="5" spans="1:31" hidden="1">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2316,7 +1699,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" hidden="1" spans="1:31">
+    <row r="7" spans="1:31" hidden="1">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2379,7 +1762,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" hidden="1" spans="1:31">
+    <row r="8" spans="1:31" hidden="1">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2449,7 +1832,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" hidden="1" spans="1:31">
+    <row r="9" spans="1:31" hidden="1">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2509,7 +1892,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" hidden="1" spans="1:31">
+    <row r="10" spans="1:31" hidden="1">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2623,7 +2006,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" hidden="1" spans="1:31">
+    <row r="12" spans="1:31" hidden="1">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2686,7 +2069,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" hidden="1" spans="1:31">
+    <row r="13" spans="1:31" hidden="1">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2746,7 +2129,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" hidden="1" spans="1:31">
+    <row r="14" spans="1:31" hidden="1">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2798,7 +2181,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" hidden="1" spans="1:31">
+    <row r="15" spans="1:31" hidden="1">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2850,7 +2233,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" hidden="1" spans="1:31">
+    <row r="16" spans="1:31" hidden="1">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2899,7 +2282,7 @@
         <v>0.8</v>
       </c>
       <c r="R16" s="2">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="U16"/>
       <c r="X16"/>
@@ -2910,7 +2293,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" hidden="1" spans="1:31">
+    <row r="17" spans="1:31" hidden="1">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3029,7 +2412,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" hidden="1" spans="1:31">
+    <row r="19" spans="1:31" hidden="1">
       <c r="A19">
         <v>19</v>
       </c>
@@ -3206,7 +2589,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" hidden="1" spans="1:31">
+    <row r="22" spans="1:31" hidden="1">
       <c r="A22">
         <v>22</v>
       </c>
@@ -3266,7 +2649,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" hidden="1" spans="1:31">
+    <row r="23" spans="1:31" hidden="1">
       <c r="A23">
         <v>23</v>
       </c>
@@ -3386,7 +2769,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" hidden="1" spans="1:31">
+    <row r="25" spans="1:31" hidden="1">
       <c r="A25">
         <v>25</v>
       </c>
@@ -3438,7 +2821,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="26" hidden="1" spans="1:31">
+    <row r="26" spans="1:31" hidden="1">
       <c r="A26">
         <v>26</v>
       </c>
@@ -3615,7 +2998,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="29" hidden="1" spans="1:31">
+    <row r="29" spans="1:31" hidden="1">
       <c r="A29">
         <v>30</v>
       </c>
@@ -3683,7 +3066,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="30" hidden="1" spans="1:31">
+    <row r="30" spans="1:31" hidden="1">
       <c r="A30">
         <v>31</v>
       </c>
@@ -3743,7 +3126,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" hidden="1" spans="1:31">
+    <row r="31" spans="1:31" hidden="1">
       <c r="A31">
         <v>32</v>
       </c>
@@ -3803,7 +3186,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" hidden="1" spans="1:31">
+    <row r="32" spans="1:31" hidden="1">
       <c r="A32">
         <v>33</v>
       </c>
@@ -4040,7 +3423,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="37" hidden="1" spans="1:31">
+    <row r="37" spans="1:31" hidden="1">
       <c r="A37">
         <v>38</v>
       </c>
@@ -4099,7 +3482,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="38" hidden="1" spans="1:31">
+    <row r="38" spans="1:31" hidden="1">
       <c r="A38">
         <v>39</v>
       </c>
@@ -4158,7 +3541,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" hidden="1" spans="1:31">
+    <row r="39" spans="1:31" hidden="1">
       <c r="A39">
         <v>40</v>
       </c>
@@ -4217,7 +3600,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="40" hidden="1" spans="1:31">
+    <row r="40" spans="1:31" hidden="1">
       <c r="A40">
         <v>41</v>
       </c>
@@ -4276,7 +3659,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="41" hidden="1" spans="1:31">
+    <row r="41" spans="1:31" hidden="1">
       <c r="A41">
         <v>42</v>
       </c>
@@ -4335,7 +3718,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="42" hidden="1" spans="1:31">
+    <row r="42" spans="1:31" hidden="1">
       <c r="A42">
         <v>43</v>
       </c>
@@ -4394,7 +3777,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="43" hidden="1" spans="1:31">
+    <row r="43" spans="1:31" hidden="1">
       <c r="A43">
         <v>44</v>
       </c>
@@ -4514,7 +3897,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="45" hidden="1" spans="1:31">
+    <row r="45" spans="1:31" hidden="1">
       <c r="A45">
         <v>46</v>
       </c>
@@ -4581,7 +3964,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="46" hidden="1" spans="1:31">
+    <row r="46" spans="1:31" hidden="1">
       <c r="A46">
         <v>47</v>
       </c>
@@ -4648,7 +4031,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="47" hidden="1" spans="1:31">
+    <row r="47" spans="1:31" hidden="1">
       <c r="A47">
         <v>48</v>
       </c>
@@ -4699,7 +4082,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="48" hidden="1" spans="1:31">
+    <row r="48" spans="1:31" hidden="1">
       <c r="A48">
         <v>49</v>
       </c>
@@ -4811,7 +4194,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" hidden="1" spans="1:31">
+    <row r="50" spans="1:31" hidden="1">
       <c r="A50">
         <v>51</v>
       </c>
@@ -4857,7 +4240,7 @@
         <v>18</v>
       </c>
       <c r="Q50">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="R50" s="2">
         <v>1.7</v>
@@ -4870,7 +4253,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="51" hidden="1" spans="1:31">
+    <row r="51" spans="1:31" hidden="1">
       <c r="A51">
         <v>52</v>
       </c>
@@ -4929,7 +4312,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="52" hidden="1" spans="1:31">
+    <row r="52" spans="1:31" hidden="1">
       <c r="A52">
         <v>53</v>
       </c>
@@ -5399,7 +4782,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="61" hidden="1" spans="1:11">
+    <row r="61" spans="1:31" hidden="1">
       <c r="A61">
         <v>62</v>
       </c>
@@ -5435,34 +4818,31 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AE61" etc:filterBottomFollowUsedRange="0">
+  <autoFilter ref="A1:AE61" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="30">
       <filters>
         <filter val="C"/>
       </filters>
     </filterColumn>
-    <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I62"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.425" customWidth="1"/>
-    <col min="2" max="2" width="27.425" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
     <col min="4" max="4" width="33" customWidth="1"/>
-    <col min="5" max="5" width="19.2833333333333" customWidth="1"/>
-    <col min="6" max="6" width="18.8583333333333" customWidth="1"/>
-    <col min="7" max="8" width="10.2833333333333" customWidth="1"/>
-    <col min="9" max="9" width="15.1416666666667" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" customWidth="1"/>
+    <col min="7" max="8" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6786,26 +6166,24 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.425" customWidth="1"/>
-    <col min="2" max="2" width="27.425" customWidth="1"/>
-    <col min="3" max="3" width="14.425" customWidth="1"/>
-    <col min="4" max="5" width="16.1416666666667" customWidth="1"/>
-    <col min="6" max="6" width="12.425" customWidth="1"/>
-    <col min="7" max="7" width="14.425" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
+    <col min="4" max="5" width="16.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="10.1416666666667" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6856,7 +6234,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>0</v>
       </c>
@@ -6885,7 +6263,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>1</v>
       </c>
@@ -6908,7 +6286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>2</v>
       </c>
@@ -6925,7 +6303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:15">
       <c r="A5">
         <v>3</v>
       </c>
@@ -6960,7 +6338,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:15">
       <c r="A6">
         <v>4</v>
       </c>
@@ -6983,7 +6361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:15">
       <c r="A7">
         <v>5</v>
       </c>
@@ -7006,7 +6384,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:15">
       <c r="A8">
         <v>6</v>
       </c>
@@ -7029,7 +6407,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:15">
       <c r="A9">
         <v>7</v>
       </c>
@@ -7052,7 +6430,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:15">
       <c r="A10">
         <v>8</v>
       </c>
@@ -7075,7 +6453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:15">
       <c r="A11">
         <v>9</v>
       </c>
@@ -7104,7 +6482,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:15">
       <c r="A12">
         <v>10</v>
       </c>
@@ -7133,7 +6511,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:15">
       <c r="A13">
         <v>11</v>
       </c>
@@ -7156,7 +6534,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:15">
       <c r="A14">
         <v>12</v>
       </c>
@@ -7179,7 +6557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:15">
       <c r="A15">
         <v>13</v>
       </c>
@@ -7202,7 +6580,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:15">
       <c r="A16">
         <v>14</v>
       </c>
@@ -7271,7 +6649,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>17</v>
       </c>
@@ -7288,7 +6666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>18</v>
       </c>
@@ -7305,7 +6683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>19</v>
       </c>
@@ -7347,24 +6725,22 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85833333333333" customWidth="1"/>
-    <col min="2" max="2" width="22.7083333333333" customWidth="1"/>
-    <col min="3" max="3" width="28.5666666666667" customWidth="1"/>
-    <col min="4" max="4" width="15.5666666666667" customWidth="1"/>
-    <col min="5" max="5" width="16.1416666666667" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="11.1416666666667" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -7390,7 +6766,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -7410,7 +6786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="12.95" customHeight="1" spans="1:6">
+    <row r="3" spans="1:7" ht="12.95" customHeight="1">
       <c r="A3">
         <v>1</v>
       </c>
@@ -7427,7 +6803,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" ht="12.95" customHeight="1" spans="1:6">
+    <row r="4" spans="1:7" ht="12.95" customHeight="1">
       <c r="A4">
         <v>2</v>
       </c>
@@ -7444,7 +6820,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>3</v>
       </c>
@@ -7464,7 +6840,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>4</v>
       </c>
@@ -7484,7 +6860,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>5</v>
       </c>
@@ -7504,7 +6880,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>6</v>
       </c>
@@ -7524,7 +6900,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>7</v>
       </c>
@@ -7544,7 +6920,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>8</v>
       </c>
@@ -7564,7 +6940,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>9</v>
       </c>
@@ -7586,7 +6962,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Cards.xlsx
+++ b/Assets/StreamingAssets/Configurations/Cards.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Conditions" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cards!$A$1:$AE$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cards!$A$1:$AG$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="301">
   <si>
     <t>ID</t>
   </si>
@@ -50,6 +50,15 @@
     <t>Type</t>
   </si>
   <si>
+    <t>LiveType</t>
+  </si>
+  <si>
+    <t>TAG1</t>
+  </si>
+  <si>
+    <t>TAG2</t>
+  </si>
+  <si>
     <t>CostType</t>
   </si>
   <si>
@@ -122,9 +131,6 @@
     <t>功能是否正常</t>
   </si>
   <si>
-    <t>TAG</t>
-  </si>
-  <si>
     <t>互动</t>
   </si>
   <si>
@@ -137,10 +143,10 @@
     <t>A</t>
   </si>
   <si>
+    <t>F</t>
+  </si>
+  <si>
     <t>Stamina</t>
-  </si>
-  <si>
-    <t>F</t>
   </si>
   <si>
     <t>喝水</t>
@@ -1095,7 +1101,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1278,12 +1284,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1310,19 +1310,19 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
+      <left style="thin">
         <color rgb="FFFF0000"/>
-      </right>
+      </left>
+      <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left/>
+      <right style="thin">
         <color rgb="FFFF0000"/>
-      </left>
-      <right/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -1560,29 +1560,31 @@
     <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
@@ -1913,40 +1915,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:AE61"/>
+  <sheetPr/>
+  <dimension ref="A1:AG61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
     <col min="2" max="2" width="12.7083333333333" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
-    <col min="4" max="4" width="10.425" customWidth="1"/>
-    <col min="5" max="5" width="13.425" customWidth="1"/>
-    <col min="6" max="6" width="10.5666666666667" customWidth="1"/>
-    <col min="7" max="7" width="9.70833333333333" style="2" customWidth="1"/>
-    <col min="8" max="8" width="7.14166666666667" customWidth="1"/>
-    <col min="9" max="9" width="14" style="2" customWidth="1"/>
-    <col min="10" max="10" width="10.2833333333333" customWidth="1"/>
-    <col min="11" max="11" width="13.7083333333333" customWidth="1"/>
-    <col min="12" max="12" width="9.70833333333333" style="2" customWidth="1"/>
-    <col min="13" max="13" width="9.70833333333333" customWidth="1"/>
-    <col min="14" max="14" width="12.1416666666667" customWidth="1"/>
-    <col min="15" max="15" width="17.7083333333333" style="2" customWidth="1"/>
-    <col min="16" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="12.2833333333333" customWidth="1"/>
-    <col min="18" max="18" width="17.1416666666667" style="2" customWidth="1"/>
-    <col min="21" max="21" width="17.7083333333333" style="2" customWidth="1"/>
-    <col min="22" max="22" width="10.7083333333333" customWidth="1"/>
-    <col min="23" max="23" width="11" customWidth="1"/>
-    <col min="24" max="24" width="17.7083333333333" style="2" customWidth="1"/>
-    <col min="25" max="25" width="12.425" customWidth="1"/>
-    <col min="26" max="26" width="12.425" style="2" customWidth="1"/>
-    <col min="27" max="27" width="12.2833333333333" customWidth="1"/>
-    <col min="28" max="28" width="9" style="2"/>
-    <col min="29" max="29" width="4.28333333333333" customWidth="1"/>
+    <col min="4" max="4" width="10.425" style="2" customWidth="1"/>
+    <col min="5" max="5" width="4.85" customWidth="1"/>
+    <col min="6" max="6" width="7.89166666666667" customWidth="1"/>
+    <col min="7" max="7" width="5.06666666666667" customWidth="1"/>
+    <col min="8" max="8" width="5.50833333333333" style="3" customWidth="1"/>
+    <col min="9" max="9" width="10.5666666666667" customWidth="1"/>
+    <col min="10" max="10" width="9.70833333333333" style="4" customWidth="1"/>
+    <col min="11" max="11" width="7.14166666666667" customWidth="1"/>
+    <col min="12" max="12" width="14" style="4" customWidth="1"/>
+    <col min="13" max="13" width="10.2833333333333" customWidth="1"/>
+    <col min="14" max="14" width="13.7083333333333" customWidth="1"/>
+    <col min="15" max="15" width="9.70833333333333" style="4" customWidth="1"/>
+    <col min="16" max="16" width="9.70833333333333" customWidth="1"/>
+    <col min="17" max="17" width="12.1416666666667" customWidth="1"/>
+    <col min="18" max="18" width="17.7083333333333" style="4" customWidth="1"/>
+    <col min="19" max="19" width="11" customWidth="1"/>
+    <col min="20" max="20" width="12.2833333333333" customWidth="1"/>
+    <col min="21" max="21" width="17.1416666666667" style="4" customWidth="1"/>
+    <col min="24" max="24" width="17.7083333333333" style="4" customWidth="1"/>
+    <col min="25" max="25" width="10.7083333333333" customWidth="1"/>
+    <col min="26" max="26" width="11" customWidth="1"/>
+    <col min="27" max="27" width="17.7083333333333" style="4" customWidth="1"/>
+    <col min="28" max="28" width="12.425" customWidth="1"/>
+    <col min="29" max="29" width="12.425" style="4" customWidth="1"/>
+    <col min="30" max="30" width="12.2833333333333" customWidth="1"/>
+    <col min="31" max="31" width="9" style="4"/>
+    <col min="32" max="32" width="4.28333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:32">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1956,7 +1961,7 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
@@ -1965,2741 +1970,2747 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
       <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="6" t="s">
         <v>15</v>
       </c>
       <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="6" t="s">
         <v>18</v>
       </c>
       <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" s="6" t="s">
         <v>21</v>
       </c>
       <c r="W1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Y1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AD1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" hidden="1" spans="1:31">
+      <c r="AE1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2"/>
-      <c r="H2" s="3">
+        <v>36</v>
+      </c>
+      <c r="I2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2"/>
+      <c r="K2" s="6">
         <v>4</v>
       </c>
-      <c r="I2" s="2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2"/>
-      <c r="M2" s="3">
+      <c r="L2" s="4">
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2"/>
+      <c r="P2" s="6">
         <v>11</v>
       </c>
-      <c r="N2">
+      <c r="Q2">
         <v>7</v>
       </c>
-      <c r="O2" s="2">
+      <c r="R2" s="4">
         <v>7</v>
       </c>
-      <c r="R2"/>
       <c r="U2"/>
       <c r="X2"/>
-      <c r="Z2"/>
-      <c r="AB2"/>
-      <c r="AC2" s="5"/>
-      <c r="AE2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" hidden="1" spans="1:31">
+      <c r="AA2"/>
+      <c r="AC2"/>
+      <c r="AE2"/>
+      <c r="AF2" s="7"/>
+    </row>
+    <row r="3" spans="1:32">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" t="s">
         <v>36</v>
       </c>
-      <c r="C3" t="s">
+      <c r="I3" t="s">
         <v>37</v>
       </c>
-      <c r="D3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3"/>
-      <c r="H3" s="3">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3"/>
-      <c r="M3" s="3">
-        <v>2</v>
+      <c r="J3"/>
+      <c r="K3" s="6">
+        <v>0</v>
+      </c>
+      <c r="L3" s="4">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
       </c>
       <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3"/>
+      <c r="P3" s="6">
+        <v>2</v>
+      </c>
+      <c r="Q3">
         <v>4</v>
       </c>
-      <c r="O3" s="2">
+      <c r="R3" s="4">
         <v>4</v>
       </c>
-      <c r="R3"/>
       <c r="U3"/>
       <c r="X3"/>
-      <c r="Z3"/>
-      <c r="AB3"/>
-      <c r="AC3" s="5"/>
-      <c r="AE3" t="s">
+      <c r="AA3"/>
+      <c r="AC3"/>
+      <c r="AE3"/>
+      <c r="AF3" s="7"/>
+    </row>
+    <row r="4" spans="1:32">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="4" spans="1:31">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" t="s">
-        <v>33</v>
-      </c>
       <c r="F4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4">
+        <v>5</v>
+      </c>
+      <c r="L4" s="4">
+        <v>4</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="P4" s="6">
+        <v>11</v>
+      </c>
+      <c r="Q4">
+        <v>15</v>
+      </c>
+      <c r="R4" s="4">
+        <v>18</v>
+      </c>
+      <c r="S4">
+        <v>56</v>
+      </c>
+      <c r="T4">
+        <v>9</v>
+      </c>
+      <c r="U4" s="4">
+        <v>12</v>
+      </c>
+      <c r="AF4" s="7"/>
+    </row>
+    <row r="5" spans="1:32">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="H4">
+      <c r="E5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5"/>
+      <c r="K5" s="6">
+        <v>3</v>
+      </c>
+      <c r="L5" s="4">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5"/>
+      <c r="P5" s="6">
+        <v>11</v>
+      </c>
+      <c r="Q5">
         <v>5</v>
       </c>
-      <c r="I4" s="2">
-        <v>4</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="M4" s="3">
-        <v>11</v>
-      </c>
-      <c r="N4">
-        <v>15</v>
-      </c>
-      <c r="O4" s="2">
-        <v>18</v>
-      </c>
-      <c r="P4">
-        <v>56</v>
-      </c>
-      <c r="Q4">
-        <v>9</v>
-      </c>
-      <c r="R4" s="2">
-        <v>12</v>
-      </c>
-      <c r="AC4" s="5"/>
-      <c r="AE4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" hidden="1" spans="1:31">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5"/>
-      <c r="H5" s="3">
-        <v>3</v>
-      </c>
-      <c r="I5" s="2">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5"/>
-      <c r="M5" s="3">
-        <v>11</v>
-      </c>
-      <c r="N5">
+      <c r="R5" s="4">
         <v>5</v>
       </c>
-      <c r="O5" s="2">
-        <v>5</v>
-      </c>
-      <c r="P5" s="3">
-        <v>2</v>
-      </c>
-      <c r="Q5">
-        <v>2</v>
-      </c>
-      <c r="R5" s="2">
-        <v>2</v>
-      </c>
-      <c r="U5"/>
+      <c r="S5" s="6">
+        <v>2</v>
+      </c>
+      <c r="T5">
+        <v>2</v>
+      </c>
+      <c r="U5" s="4">
+        <v>2</v>
+      </c>
       <c r="X5"/>
-      <c r="Z5"/>
-      <c r="AB5"/>
-      <c r="AC5" s="5"/>
-      <c r="AE5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31">
+      <c r="AA5"/>
+      <c r="AC5"/>
+      <c r="AE5"/>
+      <c r="AF5" s="7"/>
+    </row>
+    <row r="6" spans="1:32">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F6" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6" s="2">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6" s="2">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
+        <v>43</v>
+      </c>
+      <c r="I6" t="s">
+        <v>49</v>
+      </c>
+      <c r="J6" s="4">
+        <v>3</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
-      <c r="M6" s="3">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>2</v>
-      </c>
-      <c r="Q6">
-        <v>2</v>
-      </c>
-      <c r="R6" s="2">
+      <c r="L6" s="4">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="P6" s="6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>2</v>
+      </c>
+      <c r="T6">
+        <v>2</v>
+      </c>
+      <c r="U6" s="4">
         <v>7</v>
       </c>
-      <c r="S6">
+      <c r="V6">
         <v>9</v>
       </c>
-      <c r="T6">
-        <v>1</v>
-      </c>
-      <c r="U6" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC6" s="5"/>
-      <c r="AE6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" hidden="1" spans="1:31">
+      <c r="W6">
+        <v>1</v>
+      </c>
+      <c r="X6" s="4">
+        <v>1</v>
+      </c>
+      <c r="AF6" s="7"/>
+    </row>
+    <row r="7" spans="1:32">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D7" t="s">
-        <v>46</v>
-      </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7"/>
-      <c r="H7" s="3">
+        <v>36</v>
+      </c>
+      <c r="I7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7"/>
+      <c r="K7" s="6">
         <v>5</v>
       </c>
-      <c r="I7" s="2">
+      <c r="L7" s="4">
         <v>4</v>
       </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7"/>
-      <c r="M7" s="3">
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7"/>
+      <c r="P7" s="6">
         <v>4</v>
       </c>
-      <c r="O7"/>
-      <c r="P7" s="3">
+      <c r="R7"/>
+      <c r="S7" s="6">
         <v>21</v>
       </c>
-      <c r="Q7">
-        <v>2</v>
-      </c>
-      <c r="R7" s="2">
-        <v>2</v>
-      </c>
-      <c r="S7" s="3">
+      <c r="T7">
+        <v>2</v>
+      </c>
+      <c r="U7" s="4">
+        <v>2</v>
+      </c>
+      <c r="V7" s="6">
         <v>14</v>
       </c>
-      <c r="T7">
-        <v>1</v>
-      </c>
-      <c r="U7" s="2">
-        <v>1</v>
-      </c>
-      <c r="X7"/>
-      <c r="Z7"/>
-      <c r="AB7"/>
-      <c r="AC7" s="5"/>
-      <c r="AE7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" hidden="1" spans="1:31">
+      <c r="W7">
+        <v>1</v>
+      </c>
+      <c r="X7" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA7"/>
+      <c r="AC7"/>
+      <c r="AE7"/>
+      <c r="AF7" s="7"/>
+    </row>
+    <row r="8" spans="1:32">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" t="s">
-        <v>46</v>
+        <v>53</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F8" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>1</v>
-      </c>
-      <c r="I8" s="2">
-        <v>1</v>
+        <v>54</v>
+      </c>
+      <c r="I8" t="s">
+        <v>49</v>
       </c>
       <c r="J8">
-        <v>1</v>
-      </c>
-      <c r="K8">
-        <v>1</v>
-      </c>
-      <c r="L8"/>
-      <c r="M8" s="3">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="K8" s="6">
+        <v>1</v>
+      </c>
+      <c r="L8" s="4">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
       </c>
       <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8"/>
+      <c r="P8" s="6">
+        <v>2</v>
+      </c>
+      <c r="Q8">
         <v>7</v>
       </c>
-      <c r="O8" s="2">
+      <c r="R8" s="4">
         <v>7</v>
       </c>
-      <c r="P8" s="3">
-        <v>3</v>
-      </c>
-      <c r="Q8">
-        <v>1</v>
-      </c>
-      <c r="R8" s="2">
-        <v>1</v>
-      </c>
-      <c r="S8" s="3">
+      <c r="S8" s="6">
+        <v>3</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8" s="4">
+        <v>1</v>
+      </c>
+      <c r="V8" s="6">
         <v>14</v>
       </c>
-      <c r="T8">
-        <v>1</v>
-      </c>
-      <c r="U8" s="2">
-        <v>1</v>
-      </c>
-      <c r="X8"/>
-      <c r="Z8"/>
-      <c r="AB8"/>
-      <c r="AC8" s="5"/>
-      <c r="AE8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" hidden="1" spans="1:31">
+      <c r="W8">
+        <v>1</v>
+      </c>
+      <c r="X8" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA8"/>
+      <c r="AC8"/>
+      <c r="AE8"/>
+      <c r="AF8" s="7"/>
+    </row>
+    <row r="9" spans="1:32">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" t="s">
-        <v>32</v>
+        <v>56</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9"/>
-      <c r="H9" s="3">
-        <v>2</v>
-      </c>
-      <c r="I9" s="2">
-        <v>2</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9"/>
-      <c r="M9" s="3">
+        <v>35</v>
+      </c>
+      <c r="I9" t="s">
+        <v>37</v>
+      </c>
+      <c r="J9"/>
+      <c r="K9" s="6">
+        <v>2</v>
+      </c>
+      <c r="L9" s="4">
+        <v>2</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9"/>
+      <c r="P9" s="6">
         <v>6</v>
       </c>
-      <c r="N9">
-        <v>3</v>
-      </c>
-      <c r="O9" s="2">
+      <c r="Q9">
+        <v>3</v>
+      </c>
+      <c r="R9" s="4">
         <v>4</v>
       </c>
-      <c r="P9" s="3">
-        <v>2</v>
-      </c>
-      <c r="Q9">
-        <v>3</v>
-      </c>
-      <c r="R9" s="2">
+      <c r="S9" s="6">
+        <v>2</v>
+      </c>
+      <c r="T9">
+        <v>3</v>
+      </c>
+      <c r="U9" s="4">
         <v>4</v>
       </c>
-      <c r="U9"/>
       <c r="X9"/>
-      <c r="Z9"/>
-      <c r="AB9"/>
-      <c r="AC9" s="5"/>
-      <c r="AE9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" hidden="1" spans="1:31">
+      <c r="AA9"/>
+      <c r="AC9"/>
+      <c r="AE9"/>
+      <c r="AF9" s="7"/>
+    </row>
+    <row r="10" spans="1:32">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
-      </c>
-      <c r="D10" t="s">
-        <v>32</v>
+        <v>58</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F10" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10"/>
-      <c r="H10" s="3">
-        <v>2</v>
-      </c>
-      <c r="I10" s="2">
-        <v>2</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10"/>
-      <c r="M10" s="3">
+        <v>54</v>
+      </c>
+      <c r="I10" t="s">
+        <v>37</v>
+      </c>
+      <c r="J10"/>
+      <c r="K10" s="6">
+        <v>2</v>
+      </c>
+      <c r="L10" s="4">
+        <v>2</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10"/>
+      <c r="P10" s="6">
         <v>7</v>
       </c>
-      <c r="N10">
-        <v>2</v>
-      </c>
-      <c r="O10" s="2">
-        <v>3</v>
-      </c>
-      <c r="P10" s="3">
-        <v>2</v>
-      </c>
       <c r="Q10">
         <v>2</v>
       </c>
-      <c r="R10" s="2">
-        <v>3</v>
-      </c>
-      <c r="U10"/>
+      <c r="R10" s="4">
+        <v>3</v>
+      </c>
+      <c r="S10" s="6">
+        <v>2</v>
+      </c>
+      <c r="T10">
+        <v>2</v>
+      </c>
+      <c r="U10" s="4">
+        <v>3</v>
+      </c>
       <c r="X10"/>
-      <c r="Z10"/>
-      <c r="AB10"/>
-      <c r="AC10" s="5"/>
-      <c r="AE10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31">
+      <c r="AA10"/>
+      <c r="AC10"/>
+      <c r="AE10"/>
+      <c r="AF10" s="7"/>
+    </row>
+    <row r="11" spans="1:32">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" t="s">
-        <v>32</v>
+        <v>60</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F11" t="s">
-        <v>34</v>
-      </c>
-      <c r="H11">
-        <v>2</v>
-      </c>
-      <c r="I11" s="2">
-        <v>2</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="I11" t="s">
+        <v>37</v>
       </c>
       <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="M11" s="3">
+        <v>2</v>
+      </c>
+      <c r="L11" s="4">
+        <v>2</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="P11" s="6">
         <v>15</v>
       </c>
-      <c r="N11">
-        <v>2</v>
-      </c>
-      <c r="O11" s="2">
-        <v>3</v>
-      </c>
-      <c r="P11" s="3">
-        <v>2</v>
-      </c>
       <c r="Q11">
         <v>2</v>
       </c>
-      <c r="R11" s="2">
-        <v>3</v>
-      </c>
-      <c r="AC11" s="5"/>
-      <c r="AE11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" hidden="1" spans="1:31">
+      <c r="R11" s="4">
+        <v>3</v>
+      </c>
+      <c r="S11" s="6">
+        <v>2</v>
+      </c>
+      <c r="T11">
+        <v>2</v>
+      </c>
+      <c r="U11" s="4">
+        <v>3</v>
+      </c>
+      <c r="AF11" s="7"/>
+    </row>
+    <row r="12" spans="1:33">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" t="s">
-        <v>32</v>
+        <v>62</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12"/>
-      <c r="H12" s="3">
+        <v>54</v>
+      </c>
+      <c r="I12" t="s">
+        <v>37</v>
+      </c>
+      <c r="J12"/>
+      <c r="K12" s="6">
         <v>6</v>
       </c>
-      <c r="I12" s="2">
+      <c r="L12" s="4">
         <v>6</v>
       </c>
-      <c r="J12">
-        <v>1</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12"/>
-      <c r="M12" s="3">
-        <v>11</v>
+      <c r="M12">
+        <v>1</v>
       </c>
       <c r="N12">
-        <v>9</v>
-      </c>
-      <c r="O12" s="2">
-        <v>13</v>
-      </c>
-      <c r="P12" s="3">
+        <v>0</v>
+      </c>
+      <c r="O12"/>
+      <c r="P12" s="6">
         <v>11</v>
       </c>
       <c r="Q12">
         <v>9</v>
       </c>
-      <c r="R12" s="2">
+      <c r="R12" s="4">
         <v>13</v>
       </c>
-      <c r="U12"/>
+      <c r="S12" s="6">
+        <v>11</v>
+      </c>
+      <c r="T12">
+        <v>9</v>
+      </c>
+      <c r="U12" s="4">
+        <v>13</v>
+      </c>
       <c r="X12"/>
-      <c r="Z12"/>
-      <c r="AB12"/>
-      <c r="AC12" s="5"/>
-      <c r="AD12" t="s">
-        <v>61</v>
-      </c>
-      <c r="AE12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" hidden="1" spans="1:31">
+      <c r="AA12"/>
+      <c r="AC12"/>
+      <c r="AE12"/>
+      <c r="AF12" s="7"/>
+      <c r="AG12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
-      </c>
-      <c r="D13" t="s">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="E13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F13" t="s">
-        <v>34</v>
-      </c>
-      <c r="G13"/>
-      <c r="H13" s="3">
+        <v>36</v>
+      </c>
+      <c r="I13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J13"/>
+      <c r="K13" s="6">
         <v>5</v>
       </c>
-      <c r="I13" s="2">
+      <c r="L13" s="4">
         <v>5</v>
       </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13"/>
-      <c r="M13" s="3">
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13"/>
+      <c r="P13" s="6">
         <v>11</v>
       </c>
-      <c r="N13">
+      <c r="Q13">
         <v>11</v>
       </c>
-      <c r="O13" s="2">
+      <c r="R13" s="4">
         <v>15</v>
       </c>
-      <c r="P13" s="3">
-        <v>2</v>
-      </c>
-      <c r="Q13">
+      <c r="S13" s="6">
+        <v>2</v>
+      </c>
+      <c r="T13">
         <v>7</v>
       </c>
-      <c r="R13" s="2">
+      <c r="U13" s="4">
         <v>9</v>
       </c>
-      <c r="U13"/>
       <c r="X13"/>
-      <c r="Z13"/>
-      <c r="AB13"/>
-      <c r="AC13" s="5"/>
-      <c r="AE13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" hidden="1" spans="1:31">
+      <c r="AA13"/>
+      <c r="AC13"/>
+      <c r="AE13"/>
+      <c r="AF13" s="7"/>
+    </row>
+    <row r="14" spans="1:32">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
-      </c>
-      <c r="D14" t="s">
-        <v>32</v>
+        <v>68</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F14" t="s">
-        <v>34</v>
-      </c>
-      <c r="G14"/>
-      <c r="H14" s="3">
+        <v>35</v>
+      </c>
+      <c r="I14" t="s">
+        <v>37</v>
+      </c>
+      <c r="J14"/>
+      <c r="K14" s="6">
         <v>5</v>
       </c>
-      <c r="I14" s="2">
+      <c r="L14" s="4">
         <v>4</v>
       </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14"/>
-      <c r="M14" s="3">
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14"/>
+      <c r="P14" s="6">
         <v>6</v>
       </c>
-      <c r="N14">
+      <c r="Q14">
         <v>6</v>
       </c>
-      <c r="O14" s="2">
+      <c r="R14" s="4">
         <v>8</v>
       </c>
-      <c r="R14"/>
       <c r="U14"/>
       <c r="X14"/>
-      <c r="Z14"/>
-      <c r="AB14"/>
-      <c r="AC14" s="5"/>
-      <c r="AE14" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" hidden="1" spans="1:31">
+      <c r="AA14"/>
+      <c r="AC14"/>
+      <c r="AE14"/>
+      <c r="AF14" s="7"/>
+    </row>
+    <row r="15" spans="1:32">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D15" t="s">
-        <v>64</v>
+        <v>70</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="E15" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F15" t="s">
-        <v>34</v>
-      </c>
-      <c r="G15"/>
-      <c r="H15" s="3">
+        <v>35</v>
+      </c>
+      <c r="I15" t="s">
+        <v>37</v>
+      </c>
+      <c r="J15"/>
+      <c r="K15" s="6">
         <v>4</v>
       </c>
-      <c r="I15" s="2">
+      <c r="L15" s="4">
         <v>4</v>
       </c>
-      <c r="J15">
-        <v>1</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15"/>
-      <c r="M15" s="3">
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15"/>
+      <c r="P15" s="6">
         <v>18</v>
       </c>
-      <c r="N15">
+      <c r="Q15">
         <v>1.4</v>
       </c>
-      <c r="O15" s="2">
+      <c r="R15" s="4">
         <v>1.8</v>
       </c>
-      <c r="R15"/>
       <c r="U15"/>
       <c r="X15"/>
-      <c r="Z15"/>
-      <c r="AB15"/>
-      <c r="AC15" s="5"/>
-      <c r="AE15" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" hidden="1" spans="1:31">
+      <c r="AA15"/>
+      <c r="AC15"/>
+      <c r="AE15"/>
+      <c r="AF15" s="7"/>
+    </row>
+    <row r="16" spans="1:32">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
-      </c>
-      <c r="D16" t="s">
-        <v>64</v>
+        <v>72</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="E16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F16" t="s">
-        <v>34</v>
-      </c>
-      <c r="G16"/>
-      <c r="H16" s="3">
+        <v>35</v>
+      </c>
+      <c r="I16" t="s">
+        <v>37</v>
+      </c>
+      <c r="J16"/>
+      <c r="K16" s="6">
         <v>6</v>
       </c>
-      <c r="I16" s="2">
+      <c r="L16" s="4">
         <v>5</v>
       </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16"/>
-      <c r="M16" s="3">
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16"/>
+      <c r="P16" s="6">
         <v>6</v>
       </c>
-      <c r="N16">
+      <c r="Q16">
         <v>4</v>
       </c>
-      <c r="O16" s="2">
+      <c r="R16" s="4">
         <v>5</v>
       </c>
-      <c r="P16" s="3">
+      <c r="S16" s="6">
         <v>18</v>
       </c>
-      <c r="Q16">
+      <c r="T16">
         <v>0.8</v>
       </c>
-      <c r="R16" s="2">
+      <c r="U16" s="4">
         <v>1.1</v>
       </c>
-      <c r="U16"/>
       <c r="X16"/>
-      <c r="Z16"/>
-      <c r="AB16"/>
-      <c r="AC16" s="5"/>
-      <c r="AE16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" hidden="1" spans="1:31">
+      <c r="AA16"/>
+      <c r="AC16"/>
+      <c r="AE16"/>
+      <c r="AF16" s="7"/>
+    </row>
+    <row r="17" spans="1:32">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>72</v>
-      </c>
-      <c r="D17" t="s">
-        <v>64</v>
+        <v>74</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="E17" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F17" t="s">
-        <v>34</v>
-      </c>
-      <c r="G17"/>
-      <c r="H17" s="3">
-        <v>3</v>
-      </c>
-      <c r="I17" s="2">
-        <v>3</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>1</v>
-      </c>
-      <c r="L17"/>
-      <c r="M17" s="3">
+        <v>36</v>
+      </c>
+      <c r="I17" t="s">
+        <v>37</v>
+      </c>
+      <c r="J17"/>
+      <c r="K17" s="6">
+        <v>3</v>
+      </c>
+      <c r="L17" s="4">
+        <v>3</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17"/>
+      <c r="P17" s="6">
         <v>19</v>
       </c>
-      <c r="N17">
-        <v>1</v>
-      </c>
-      <c r="O17" s="2">
-        <v>1</v>
-      </c>
-      <c r="P17" s="3">
-        <v>2</v>
-      </c>
       <c r="Q17">
+        <v>1</v>
+      </c>
+      <c r="R17" s="4">
+        <v>1</v>
+      </c>
+      <c r="S17" s="6">
+        <v>2</v>
+      </c>
+      <c r="T17">
         <v>4</v>
       </c>
-      <c r="R17" s="2">
+      <c r="U17" s="4">
         <v>6</v>
       </c>
-      <c r="S17" s="3">
+      <c r="V17" s="6">
         <v>21</v>
       </c>
-      <c r="T17">
-        <v>2</v>
-      </c>
-      <c r="U17" s="2">
-        <v>3</v>
-      </c>
-      <c r="X17"/>
-      <c r="Z17"/>
-      <c r="AB17"/>
-      <c r="AC17" s="6"/>
-      <c r="AE17" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:31">
+      <c r="W17">
+        <v>2</v>
+      </c>
+      <c r="X17" s="4">
+        <v>3</v>
+      </c>
+      <c r="AA17"/>
+      <c r="AC17"/>
+      <c r="AE17"/>
+      <c r="AF17" s="8"/>
+    </row>
+    <row r="18" spans="1:32">
       <c r="A18">
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
-      </c>
-      <c r="D18" t="s">
-        <v>64</v>
+        <v>76</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="E18" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F18" t="s">
-        <v>34</v>
-      </c>
-      <c r="H18">
+        <v>43</v>
+      </c>
+      <c r="I18" t="s">
+        <v>37</v>
+      </c>
+      <c r="K18">
         <v>4</v>
       </c>
-      <c r="I18" s="2">
-        <v>3</v>
-      </c>
-      <c r="J18">
-        <v>1</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="L18" s="4">
+        <v>3</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="P18" s="6">
         <v>15</v>
       </c>
-      <c r="N18">
+      <c r="Q18">
         <v>5</v>
       </c>
-      <c r="O18" s="2">
+      <c r="R18" s="4">
         <v>7</v>
       </c>
-      <c r="Y18">
+      <c r="AB18">
         <v>61</v>
       </c>
-      <c r="Z18" s="2">
+      <c r="AC18" s="4">
         <v>1.5</v>
       </c>
-      <c r="AC18" s="5"/>
-      <c r="AE18" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" hidden="1" spans="1:31">
+      <c r="AF18" s="7"/>
+    </row>
+    <row r="19" spans="1:32">
       <c r="A19">
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
-      </c>
-      <c r="D19" t="s">
-        <v>46</v>
+        <v>78</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="E19" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F19" t="s">
-        <v>34</v>
-      </c>
-      <c r="G19"/>
-      <c r="H19" s="3">
+        <v>54</v>
+      </c>
+      <c r="I19" t="s">
+        <v>37</v>
+      </c>
+      <c r="J19"/>
+      <c r="K19" s="6">
         <v>5</v>
       </c>
-      <c r="I19" s="2">
+      <c r="L19" s="4">
         <v>4</v>
       </c>
-      <c r="J19">
-        <v>1</v>
-      </c>
-      <c r="K19">
-        <v>1</v>
-      </c>
-      <c r="L19"/>
-      <c r="M19" s="3">
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19"/>
+      <c r="P19" s="6">
         <v>23</v>
       </c>
-      <c r="N19">
-        <v>1</v>
-      </c>
-      <c r="O19" s="2">
-        <v>1</v>
-      </c>
-      <c r="P19" s="3">
+      <c r="Q19">
+        <v>1</v>
+      </c>
+      <c r="R19" s="4">
+        <v>1</v>
+      </c>
+      <c r="S19" s="6">
         <v>7</v>
       </c>
-      <c r="Q19">
-        <v>1</v>
-      </c>
-      <c r="R19" s="2">
-        <v>2</v>
-      </c>
-      <c r="U19"/>
+      <c r="T19">
+        <v>1</v>
+      </c>
+      <c r="U19" s="4">
+        <v>2</v>
+      </c>
       <c r="X19"/>
-      <c r="Z19"/>
-      <c r="AB19"/>
-      <c r="AC19" s="5"/>
-      <c r="AE19" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="20" spans="1:31">
+      <c r="AA19"/>
+      <c r="AC19"/>
+      <c r="AE19"/>
+      <c r="AF19" s="7"/>
+    </row>
+    <row r="20" spans="1:32">
       <c r="A20">
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" t="s">
-        <v>32</v>
+        <v>80</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="E20" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F20" t="s">
-        <v>34</v>
-      </c>
-      <c r="H20">
+        <v>43</v>
+      </c>
+      <c r="I20" t="s">
+        <v>37</v>
+      </c>
+      <c r="K20">
         <v>6</v>
       </c>
-      <c r="I20" s="2">
+      <c r="L20" s="4">
         <v>6</v>
       </c>
-      <c r="J20">
-        <v>1</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20" s="2">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20" s="4">
+        <v>0</v>
+      </c>
+      <c r="P20" s="6">
         <v>11</v>
       </c>
-      <c r="N20">
+      <c r="Q20">
         <v>24</v>
       </c>
-      <c r="O20" s="2">
+      <c r="R20" s="4">
         <v>30</v>
       </c>
-      <c r="Y20">
+      <c r="AB20">
         <v>62</v>
       </c>
-      <c r="Z20" s="2">
+      <c r="AC20" s="4">
         <v>7</v>
       </c>
-      <c r="AC20" s="6"/>
-      <c r="AE20" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:31">
+      <c r="AF20" s="8"/>
+    </row>
+    <row r="21" spans="1:32">
       <c r="A21">
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s">
-        <v>80</v>
-      </c>
-      <c r="D21" t="s">
-        <v>64</v>
+        <v>82</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="E21" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F21" t="s">
-        <v>34</v>
-      </c>
-      <c r="H21">
+        <v>43</v>
+      </c>
+      <c r="I21" t="s">
+        <v>37</v>
+      </c>
+      <c r="K21">
         <v>5</v>
       </c>
-      <c r="I21" s="2">
+      <c r="L21" s="4">
         <v>4</v>
       </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>1</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="P21" s="6">
         <v>26</v>
       </c>
-      <c r="N21">
-        <v>2</v>
-      </c>
-      <c r="O21" s="2">
-        <v>2</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="Q21">
+        <v>2</v>
+      </c>
+      <c r="R21" s="4">
+        <v>2</v>
+      </c>
+      <c r="S21" s="6">
         <v>11</v>
       </c>
-      <c r="Q21">
+      <c r="T21">
         <v>30</v>
       </c>
-      <c r="R21" s="2">
+      <c r="U21" s="4">
         <v>42</v>
       </c>
-      <c r="S21">
-        <v>2</v>
-      </c>
-      <c r="T21">
+      <c r="V21">
+        <v>2</v>
+      </c>
+      <c r="W21">
         <v>5</v>
       </c>
-      <c r="U21" s="2">
+      <c r="X21" s="4">
         <v>7</v>
       </c>
-      <c r="AC21" s="5"/>
-      <c r="AE21" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" hidden="1" spans="1:31">
+      <c r="AF21" s="7"/>
+    </row>
+    <row r="22" spans="1:32">
       <c r="A22">
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s">
-        <v>82</v>
-      </c>
-      <c r="D22" t="s">
-        <v>64</v>
+        <v>84</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="E22" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G22"/>
-      <c r="H22" s="3">
+        <v>35</v>
+      </c>
+      <c r="I22" t="s">
+        <v>37</v>
+      </c>
+      <c r="J22"/>
+      <c r="K22" s="6">
         <v>4</v>
       </c>
-      <c r="I22" s="2">
+      <c r="L22" s="4">
         <v>4</v>
       </c>
-      <c r="J22">
-        <v>1</v>
-      </c>
-      <c r="K22">
-        <v>1</v>
-      </c>
-      <c r="L22"/>
-      <c r="M22" s="3">
+      <c r="M22">
+        <v>1</v>
+      </c>
+      <c r="N22">
+        <v>1</v>
+      </c>
+      <c r="O22"/>
+      <c r="P22" s="6">
         <v>6</v>
       </c>
-      <c r="N22">
-        <v>2</v>
-      </c>
-      <c r="O22" s="2">
+      <c r="Q22">
+        <v>2</v>
+      </c>
+      <c r="R22" s="4">
         <v>4</v>
       </c>
-      <c r="P22" s="3">
+      <c r="S22" s="6">
         <v>28</v>
       </c>
-      <c r="Q22">
-        <v>1</v>
-      </c>
-      <c r="R22" s="2">
-        <v>1</v>
-      </c>
-      <c r="U22"/>
+      <c r="T22">
+        <v>1</v>
+      </c>
+      <c r="U22" s="4">
+        <v>1</v>
+      </c>
       <c r="X22"/>
-      <c r="Z22"/>
-      <c r="AB22"/>
-      <c r="AC22" s="5"/>
-      <c r="AE22" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" hidden="1" spans="1:31">
+      <c r="AA22"/>
+      <c r="AC22"/>
+      <c r="AE22"/>
+      <c r="AF22" s="7"/>
+    </row>
+    <row r="23" spans="1:32">
       <c r="A23">
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>84</v>
-      </c>
-      <c r="D23" t="s">
-        <v>64</v>
+        <v>86</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="E23" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F23" t="s">
-        <v>34</v>
-      </c>
-      <c r="G23"/>
-      <c r="H23" s="3">
-        <v>1</v>
-      </c>
-      <c r="I23" s="2">
-        <v>1</v>
-      </c>
-      <c r="J23">
-        <v>1</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="L23"/>
-      <c r="M23" s="3">
+        <v>35</v>
+      </c>
+      <c r="I23" t="s">
+        <v>37</v>
+      </c>
+      <c r="J23"/>
+      <c r="K23" s="6">
+        <v>1</v>
+      </c>
+      <c r="L23" s="4">
+        <v>1</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23"/>
+      <c r="P23" s="6">
         <v>6</v>
       </c>
-      <c r="N23">
+      <c r="Q23">
         <v>5</v>
       </c>
-      <c r="O23" s="2">
+      <c r="R23" s="4">
         <v>7</v>
       </c>
-      <c r="P23" s="3">
-        <v>2</v>
-      </c>
-      <c r="Q23">
-        <v>1</v>
-      </c>
-      <c r="R23" s="2">
-        <v>1</v>
-      </c>
-      <c r="U23"/>
+      <c r="S23" s="6">
+        <v>2</v>
+      </c>
+      <c r="T23">
+        <v>1</v>
+      </c>
+      <c r="U23" s="4">
+        <v>1</v>
+      </c>
       <c r="X23"/>
-      <c r="Z23"/>
-      <c r="AB23"/>
-      <c r="AC23" s="5"/>
-      <c r="AE23" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:31">
+      <c r="AA23"/>
+      <c r="AC23"/>
+      <c r="AE23"/>
+      <c r="AF23" s="7"/>
+    </row>
+    <row r="24" spans="1:32">
       <c r="A24">
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
-        <v>86</v>
-      </c>
-      <c r="D24" t="s">
-        <v>32</v>
+        <v>88</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="E24" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F24" t="s">
-        <v>34</v>
-      </c>
-      <c r="H24">
+        <v>43</v>
+      </c>
+      <c r="I24" t="s">
+        <v>37</v>
+      </c>
+      <c r="K24">
         <v>4</v>
       </c>
-      <c r="I24" s="2">
+      <c r="L24" s="4">
         <v>4</v>
       </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3">
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="P24" s="6">
         <v>15</v>
       </c>
-      <c r="N24">
-        <v>3</v>
-      </c>
-      <c r="O24" s="2">
+      <c r="Q24">
+        <v>3</v>
+      </c>
+      <c r="R24" s="4">
         <v>4</v>
       </c>
-      <c r="P24" s="3">
+      <c r="S24" s="6">
         <v>11</v>
       </c>
-      <c r="Q24">
+      <c r="T24">
         <v>8</v>
       </c>
-      <c r="R24" s="2">
+      <c r="U24" s="4">
         <v>11</v>
       </c>
-      <c r="Y24">
+      <c r="AB24">
         <v>63</v>
       </c>
-      <c r="Z24" s="2">
-        <v>3</v>
-      </c>
-      <c r="AC24" s="5"/>
-      <c r="AE24" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" hidden="1" spans="1:31">
+      <c r="AC24" s="4">
+        <v>3</v>
+      </c>
+      <c r="AF24" s="7"/>
+    </row>
+    <row r="25" spans="1:32">
       <c r="A25">
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D25" t="s">
-        <v>32</v>
+        <v>90</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="E25" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F25" t="s">
-        <v>34</v>
-      </c>
-      <c r="G25"/>
-      <c r="H25" s="3">
-        <v>3</v>
-      </c>
-      <c r="I25" s="2">
-        <v>2</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25"/>
-      <c r="M25" s="3">
+        <v>54</v>
+      </c>
+      <c r="I25" t="s">
+        <v>37</v>
+      </c>
+      <c r="J25"/>
+      <c r="K25" s="6">
+        <v>3</v>
+      </c>
+      <c r="L25" s="4">
+        <v>2</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25"/>
+      <c r="P25" s="6">
         <v>7</v>
       </c>
-      <c r="N25">
-        <v>3</v>
-      </c>
-      <c r="O25" s="2">
+      <c r="Q25">
+        <v>3</v>
+      </c>
+      <c r="R25" s="4">
         <v>5</v>
       </c>
-      <c r="R25"/>
       <c r="U25"/>
       <c r="X25"/>
-      <c r="Z25"/>
-      <c r="AB25"/>
-      <c r="AC25" s="5"/>
-      <c r="AE25" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" hidden="1" spans="1:31">
+      <c r="AA25"/>
+      <c r="AC25"/>
+      <c r="AE25"/>
+      <c r="AF25" s="7"/>
+    </row>
+    <row r="26" spans="1:32">
       <c r="A26">
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
-        <v>90</v>
-      </c>
-      <c r="D26" t="s">
-        <v>32</v>
+        <v>92</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="E26" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F26" t="s">
-        <v>34</v>
-      </c>
-      <c r="G26"/>
-      <c r="H26" s="3">
-        <v>3</v>
-      </c>
-      <c r="I26" s="2">
-        <v>2</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26"/>
-      <c r="M26" s="3">
+        <v>54</v>
+      </c>
+      <c r="I26" t="s">
+        <v>37</v>
+      </c>
+      <c r="J26"/>
+      <c r="K26" s="6">
+        <v>3</v>
+      </c>
+      <c r="L26" s="4">
+        <v>2</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26"/>
+      <c r="P26" s="6">
         <v>7</v>
       </c>
-      <c r="N26">
-        <v>3</v>
-      </c>
-      <c r="O26" s="2">
+      <c r="Q26">
+        <v>3</v>
+      </c>
+      <c r="R26" s="4">
         <v>4</v>
       </c>
-      <c r="P26" s="3">
-        <v>2</v>
-      </c>
-      <c r="Q26">
+      <c r="S26" s="6">
+        <v>2</v>
+      </c>
+      <c r="T26">
         <v>4</v>
       </c>
-      <c r="R26" s="2">
+      <c r="U26" s="4">
         <v>6</v>
       </c>
-      <c r="U26"/>
       <c r="X26"/>
-      <c r="Z26"/>
-      <c r="AB26"/>
-      <c r="AC26" s="5"/>
-      <c r="AE26" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:31">
+      <c r="AA26"/>
+      <c r="AC26"/>
+      <c r="AE26"/>
+      <c r="AF26" s="7"/>
+    </row>
+    <row r="27" spans="1:32">
       <c r="A27">
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
-      </c>
-      <c r="D27" t="s">
-        <v>46</v>
+        <v>94</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="E27" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F27" t="s">
-        <v>34</v>
-      </c>
-      <c r="H27">
+        <v>43</v>
+      </c>
+      <c r="I27" t="s">
+        <v>37</v>
+      </c>
+      <c r="K27">
         <v>8</v>
       </c>
-      <c r="I27" s="2">
+      <c r="L27" s="4">
         <v>6</v>
       </c>
-      <c r="J27">
-        <v>1</v>
-      </c>
-      <c r="K27">
-        <v>1</v>
-      </c>
-      <c r="L27" s="2">
-        <v>0</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="M27">
+        <v>1</v>
+      </c>
+      <c r="N27">
+        <v>1</v>
+      </c>
+      <c r="O27" s="4">
+        <v>0</v>
+      </c>
+      <c r="P27" s="6">
         <v>11</v>
       </c>
-      <c r="N27">
+      <c r="Q27">
         <v>12</v>
       </c>
-      <c r="O27" s="2">
+      <c r="R27" s="4">
         <v>18</v>
       </c>
-      <c r="P27" s="3">
+      <c r="S27" s="6">
         <v>56</v>
       </c>
-      <c r="Q27">
+      <c r="T27">
         <v>24</v>
       </c>
-      <c r="R27" s="2">
+      <c r="U27" s="4">
         <v>30</v>
       </c>
-      <c r="S27">
+      <c r="V27">
         <v>57</v>
       </c>
-      <c r="T27">
+      <c r="W27">
         <v>36</v>
       </c>
-      <c r="U27" s="2">
+      <c r="X27" s="4">
         <v>44</v>
       </c>
-      <c r="AC27" s="6"/>
-      <c r="AE27" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28" spans="1:31">
+      <c r="AF27" s="8"/>
+    </row>
+    <row r="28" spans="1:32">
       <c r="A28">
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s">
-        <v>94</v>
-      </c>
-      <c r="D28" t="s">
-        <v>32</v>
+        <v>96</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="E28" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F28" t="s">
-        <v>34</v>
-      </c>
-      <c r="H28">
-        <v>1</v>
-      </c>
-      <c r="I28" s="2">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>1</v>
+        <v>43</v>
+      </c>
+      <c r="I28" t="s">
+        <v>37</v>
       </c>
       <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="M28" s="3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="L28" s="4">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>1</v>
       </c>
       <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="P28" s="6">
+        <v>2</v>
+      </c>
+      <c r="Q28">
         <v>6</v>
       </c>
-      <c r="O28" s="2">
+      <c r="R28" s="4">
         <v>8</v>
       </c>
-      <c r="Y28">
+      <c r="AB28">
         <v>21</v>
       </c>
-      <c r="Z28" s="2">
+      <c r="AC28" s="4">
         <v>12</v>
       </c>
-      <c r="AC28" s="5"/>
-      <c r="AE28" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="29" hidden="1" spans="1:31">
+      <c r="AF28" s="7"/>
+    </row>
+    <row r="29" spans="1:32">
       <c r="A29">
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
-      </c>
-      <c r="D29" t="s">
-        <v>64</v>
+        <v>98</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="E29" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F29" t="s">
-        <v>34</v>
-      </c>
-      <c r="G29"/>
-      <c r="H29" s="3">
+        <v>36</v>
+      </c>
+      <c r="I29" t="s">
+        <v>37</v>
+      </c>
+      <c r="J29"/>
+      <c r="K29" s="6">
         <v>5</v>
       </c>
-      <c r="I29" s="2">
+      <c r="L29" s="4">
         <v>5</v>
       </c>
-      <c r="J29">
-        <v>1</v>
-      </c>
-      <c r="K29">
-        <v>1</v>
-      </c>
-      <c r="L29"/>
-      <c r="M29" s="3">
+      <c r="M29">
+        <v>1</v>
+      </c>
+      <c r="N29">
+        <v>1</v>
+      </c>
+      <c r="O29"/>
+      <c r="P29" s="6">
         <v>32</v>
       </c>
-      <c r="N29">
+      <c r="Q29">
         <v>30</v>
       </c>
-      <c r="O29" s="2">
+      <c r="R29" s="4">
         <v>30</v>
       </c>
-      <c r="P29" s="3">
-        <v>2</v>
-      </c>
-      <c r="Q29">
-        <v>3</v>
-      </c>
-      <c r="R29" s="2">
+      <c r="S29" s="6">
+        <v>2</v>
+      </c>
+      <c r="T29">
+        <v>3</v>
+      </c>
+      <c r="U29" s="4">
         <v>5</v>
       </c>
-      <c r="S29" s="3">
+      <c r="V29" s="6">
         <v>21</v>
       </c>
-      <c r="T29">
-        <v>2</v>
-      </c>
-      <c r="U29" s="2">
-        <v>3</v>
-      </c>
-      <c r="X29"/>
-      <c r="Z29"/>
-      <c r="AB29"/>
-      <c r="AC29" s="5"/>
-      <c r="AE29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="30" hidden="1" spans="1:31">
+      <c r="W29">
+        <v>2</v>
+      </c>
+      <c r="X29" s="4">
+        <v>3</v>
+      </c>
+      <c r="AA29"/>
+      <c r="AC29"/>
+      <c r="AE29"/>
+      <c r="AF29" s="7"/>
+    </row>
+    <row r="30" spans="1:32">
       <c r="A30">
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C30" t="s">
-        <v>98</v>
-      </c>
-      <c r="D30" t="s">
-        <v>64</v>
+        <v>100</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="E30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F30" t="s">
-        <v>34</v>
-      </c>
-      <c r="G30"/>
-      <c r="H30" s="3">
+        <v>36</v>
+      </c>
+      <c r="I30" t="s">
+        <v>37</v>
+      </c>
+      <c r="J30"/>
+      <c r="K30" s="6">
         <v>4</v>
       </c>
-      <c r="I30" s="2">
+      <c r="L30" s="4">
         <v>4</v>
       </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>1</v>
-      </c>
-      <c r="L30"/>
-      <c r="M30" s="3">
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>1</v>
+      </c>
+      <c r="O30"/>
+      <c r="P30" s="6">
         <v>33</v>
       </c>
-      <c r="N30">
+      <c r="Q30">
         <v>50</v>
       </c>
-      <c r="O30" s="2">
+      <c r="R30" s="4">
         <v>70</v>
       </c>
-      <c r="P30" s="3">
-        <v>2</v>
-      </c>
-      <c r="Q30">
-        <v>2</v>
-      </c>
-      <c r="R30" s="2">
+      <c r="S30" s="6">
+        <v>2</v>
+      </c>
+      <c r="T30">
+        <v>2</v>
+      </c>
+      <c r="U30" s="4">
         <v>4</v>
       </c>
-      <c r="U30"/>
       <c r="X30"/>
-      <c r="Z30"/>
-      <c r="AB30"/>
-      <c r="AC30" s="6"/>
-      <c r="AE30" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" hidden="1" spans="1:31">
+      <c r="AA30"/>
+      <c r="AC30"/>
+      <c r="AE30"/>
+      <c r="AF30" s="8"/>
+    </row>
+    <row r="31" spans="1:32">
       <c r="A31">
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C31" t="s">
-        <v>100</v>
-      </c>
-      <c r="D31" t="s">
-        <v>46</v>
+        <v>102</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="E31" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F31" t="s">
-        <v>34</v>
-      </c>
-      <c r="G31"/>
-      <c r="H31" s="3">
+        <v>36</v>
+      </c>
+      <c r="I31" t="s">
+        <v>37</v>
+      </c>
+      <c r="J31"/>
+      <c r="K31" s="6">
         <v>4</v>
       </c>
-      <c r="I31" s="2">
-        <v>3</v>
-      </c>
-      <c r="J31">
-        <v>1</v>
-      </c>
-      <c r="K31">
-        <v>1</v>
-      </c>
-      <c r="L31"/>
-      <c r="M31" s="3">
+      <c r="L31" s="4">
+        <v>3</v>
+      </c>
+      <c r="M31">
+        <v>1</v>
+      </c>
+      <c r="N31">
+        <v>1</v>
+      </c>
+      <c r="O31"/>
+      <c r="P31" s="6">
         <v>33</v>
       </c>
-      <c r="N31">
+      <c r="Q31">
         <v>20</v>
       </c>
-      <c r="O31" s="2">
+      <c r="R31" s="4">
         <v>30</v>
       </c>
-      <c r="P31" s="3">
+      <c r="S31" s="6">
         <v>35</v>
       </c>
-      <c r="Q31">
-        <v>1</v>
-      </c>
-      <c r="R31" s="2">
-        <v>1</v>
-      </c>
-      <c r="U31"/>
+      <c r="T31">
+        <v>1</v>
+      </c>
+      <c r="U31" s="4">
+        <v>1</v>
+      </c>
       <c r="X31"/>
-      <c r="Z31"/>
-      <c r="AB31"/>
-      <c r="AC31" s="6"/>
-      <c r="AE31" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="32" hidden="1" spans="1:31">
+      <c r="AA31"/>
+      <c r="AC31"/>
+      <c r="AE31"/>
+      <c r="AF31" s="8"/>
+    </row>
+    <row r="32" spans="1:31">
       <c r="A32">
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C32" t="s">
-        <v>102</v>
-      </c>
-      <c r="D32" t="s">
-        <v>46</v>
+        <v>104</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="E32" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F32" t="s">
-        <v>34</v>
-      </c>
-      <c r="G32"/>
-      <c r="H32" s="3">
+        <v>36</v>
+      </c>
+      <c r="I32" t="s">
+        <v>37</v>
+      </c>
+      <c r="J32"/>
+      <c r="K32" s="6">
         <v>7</v>
       </c>
-      <c r="I32" s="2">
+      <c r="L32" s="4">
         <v>6</v>
       </c>
-      <c r="J32">
-        <v>1</v>
-      </c>
-      <c r="K32">
-        <v>1</v>
-      </c>
-      <c r="L32"/>
+      <c r="M32">
+        <v>1</v>
+      </c>
+      <c r="N32">
+        <v>1</v>
+      </c>
       <c r="O32"/>
       <c r="R32"/>
       <c r="U32"/>
       <c r="X32"/>
-      <c r="Z32"/>
-      <c r="AB32"/>
-      <c r="AE32" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="33" spans="1:31">
+      <c r="AA32"/>
+      <c r="AC32"/>
+      <c r="AE32"/>
+    </row>
+    <row r="33" spans="1:29">
       <c r="A33">
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C33" t="s">
-        <v>104</v>
-      </c>
-      <c r="D33" t="s">
-        <v>46</v>
+        <v>106</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="E33" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F33" t="s">
-        <v>34</v>
-      </c>
-      <c r="H33">
+        <v>43</v>
+      </c>
+      <c r="I33" t="s">
+        <v>37</v>
+      </c>
+      <c r="K33">
         <v>8</v>
       </c>
-      <c r="I33" s="2">
+      <c r="L33" s="4">
         <v>7</v>
       </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
-      <c r="K33">
-        <v>1</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>1</v>
+      </c>
+      <c r="P33" s="6">
         <v>11</v>
       </c>
-      <c r="N33">
+      <c r="Q33">
         <v>38</v>
       </c>
-      <c r="O33" s="2">
+      <c r="R33" s="4">
         <v>52</v>
       </c>
-      <c r="Y33">
+      <c r="AB33">
         <v>64</v>
       </c>
-      <c r="Z33" s="2">
-        <v>1</v>
-      </c>
-      <c r="AE33" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="34" spans="1:31">
+      <c r="AC33" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18">
       <c r="A34">
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C34" t="s">
-        <v>106</v>
-      </c>
-      <c r="D34" t="s">
-        <v>64</v>
+        <v>108</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="E34" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F34" t="s">
-        <v>34</v>
-      </c>
-      <c r="H34">
-        <v>3</v>
-      </c>
-      <c r="I34" s="2">
-        <v>3</v>
-      </c>
-      <c r="J34">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="I34" t="s">
+        <v>37</v>
       </c>
       <c r="K34">
-        <v>0</v>
-      </c>
-      <c r="L34" s="2">
-        <v>0</v>
-      </c>
-      <c r="M34" s="3">
+        <v>3</v>
+      </c>
+      <c r="L34" s="4">
+        <v>3</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34" s="4">
+        <v>0</v>
+      </c>
+      <c r="P34" s="6">
         <v>15</v>
       </c>
-      <c r="N34">
-        <v>3</v>
-      </c>
-      <c r="O34" s="2">
+      <c r="Q34">
+        <v>3</v>
+      </c>
+      <c r="R34" s="4">
         <v>4</v>
       </c>
-      <c r="AE34" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="35" spans="1:31">
+    </row>
+    <row r="35" spans="1:18">
       <c r="A35">
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C35" t="s">
-        <v>108</v>
-      </c>
-      <c r="D35" t="s">
-        <v>64</v>
+        <v>110</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="E35" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F35" t="s">
-        <v>34</v>
-      </c>
-      <c r="H35">
-        <v>3</v>
-      </c>
-      <c r="I35" s="2">
-        <v>3</v>
-      </c>
-      <c r="J35">
-        <v>1</v>
+        <v>43</v>
+      </c>
+      <c r="I35" t="s">
+        <v>37</v>
       </c>
       <c r="K35">
-        <v>0</v>
-      </c>
-      <c r="M35" s="3">
+        <v>3</v>
+      </c>
+      <c r="L35" s="4">
+        <v>3</v>
+      </c>
+      <c r="M35">
+        <v>1</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="P35" s="6">
         <v>11</v>
       </c>
-      <c r="N35">
+      <c r="Q35">
         <v>18</v>
       </c>
-      <c r="O35" s="2">
+      <c r="R35" s="4">
         <v>22</v>
       </c>
-      <c r="AE35" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="36" spans="1:31">
+    </row>
+    <row r="36" spans="1:21">
       <c r="A36">
         <v>37</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B36" s="5">
         <v>144</v>
       </c>
       <c r="C36" t="s">
-        <v>109</v>
-      </c>
-      <c r="D36" t="s">
-        <v>64</v>
+        <v>111</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="E36" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F36" t="s">
-        <v>34</v>
-      </c>
-      <c r="H36">
-        <v>3</v>
-      </c>
-      <c r="I36" s="2">
-        <v>3</v>
-      </c>
-      <c r="J36">
-        <v>1</v>
+        <v>43</v>
+      </c>
+      <c r="I36" t="s">
+        <v>37</v>
       </c>
       <c r="K36">
-        <v>0</v>
-      </c>
-      <c r="M36" s="3">
+        <v>3</v>
+      </c>
+      <c r="L36" s="4">
+        <v>3</v>
+      </c>
+      <c r="M36">
+        <v>1</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="P36" s="6">
         <v>15</v>
       </c>
-      <c r="N36">
-        <v>3</v>
-      </c>
-      <c r="O36" s="2">
+      <c r="Q36">
+        <v>3</v>
+      </c>
+      <c r="R36" s="4">
         <v>4</v>
       </c>
-      <c r="P36" s="3">
-        <v>2</v>
-      </c>
-      <c r="Q36">
+      <c r="S36" s="6">
+        <v>2</v>
+      </c>
+      <c r="T36">
         <v>6</v>
       </c>
-      <c r="R36" s="2">
+      <c r="U36" s="4">
         <v>8</v>
       </c>
-      <c r="AE36" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="37" hidden="1" spans="1:31">
+    </row>
+    <row r="37" spans="1:31">
       <c r="A37">
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C37" t="s">
-        <v>111</v>
-      </c>
-      <c r="D37" t="s">
-        <v>64</v>
+        <v>113</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="E37" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F37" t="s">
-        <v>34</v>
-      </c>
-      <c r="G37"/>
-      <c r="H37" s="3">
-        <v>3</v>
-      </c>
-      <c r="I37" s="2">
-        <v>3</v>
-      </c>
-      <c r="J37">
-        <v>1</v>
-      </c>
-      <c r="K37">
-        <v>0</v>
-      </c>
-      <c r="L37"/>
-      <c r="M37" s="3">
+        <v>54</v>
+      </c>
+      <c r="I37" t="s">
+        <v>37</v>
+      </c>
+      <c r="J37"/>
+      <c r="K37" s="6">
+        <v>3</v>
+      </c>
+      <c r="L37" s="4">
+        <v>3</v>
+      </c>
+      <c r="M37">
+        <v>1</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37"/>
+      <c r="P37" s="6">
         <v>7</v>
       </c>
-      <c r="N37">
-        <v>3</v>
-      </c>
-      <c r="O37" s="2">
+      <c r="Q37">
+        <v>3</v>
+      </c>
+      <c r="R37" s="4">
         <v>4</v>
       </c>
-      <c r="P37" s="3">
-        <v>2</v>
-      </c>
-      <c r="Q37">
+      <c r="S37" s="6">
+        <v>2</v>
+      </c>
+      <c r="T37">
         <v>6</v>
       </c>
-      <c r="R37" s="2">
+      <c r="U37" s="4">
         <v>8</v>
       </c>
-      <c r="U37"/>
       <c r="X37"/>
-      <c r="Z37"/>
-      <c r="AB37"/>
-      <c r="AE37" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="38" hidden="1" spans="1:31">
+      <c r="AA37"/>
+      <c r="AC37"/>
+      <c r="AE37"/>
+    </row>
+    <row r="38" spans="1:31">
       <c r="A38">
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C38" t="s">
-        <v>113</v>
-      </c>
-      <c r="D38" t="s">
-        <v>46</v>
+        <v>115</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="E38" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F38" t="s">
-        <v>34</v>
-      </c>
-      <c r="G38"/>
-      <c r="H38" s="3">
-        <v>1</v>
-      </c>
-      <c r="I38" s="2">
-        <v>1</v>
-      </c>
-      <c r="J38">
-        <v>1</v>
-      </c>
-      <c r="K38">
-        <v>1</v>
-      </c>
-      <c r="L38"/>
-      <c r="M38" s="3">
+        <v>36</v>
+      </c>
+      <c r="I38" t="s">
+        <v>37</v>
+      </c>
+      <c r="J38"/>
+      <c r="K38" s="6">
+        <v>1</v>
+      </c>
+      <c r="L38" s="4">
+        <v>1</v>
+      </c>
+      <c r="M38">
+        <v>1</v>
+      </c>
+      <c r="N38">
+        <v>1</v>
+      </c>
+      <c r="O38"/>
+      <c r="P38" s="6">
         <v>21</v>
       </c>
-      <c r="N38">
+      <c r="Q38">
         <v>4</v>
       </c>
-      <c r="O38" s="2">
+      <c r="R38" s="4">
         <v>5</v>
       </c>
-      <c r="P38" s="3">
-        <v>2</v>
-      </c>
-      <c r="Q38">
-        <v>3</v>
-      </c>
-      <c r="R38" s="2">
+      <c r="S38" s="6">
+        <v>2</v>
+      </c>
+      <c r="T38">
+        <v>3</v>
+      </c>
+      <c r="U38" s="4">
         <v>5</v>
       </c>
-      <c r="U38"/>
       <c r="X38"/>
-      <c r="Z38"/>
-      <c r="AB38"/>
-      <c r="AE38" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="39" hidden="1" spans="1:31">
+      <c r="AA38"/>
+      <c r="AC38"/>
+      <c r="AE38"/>
+    </row>
+    <row r="39" spans="1:31">
       <c r="A39">
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C39" t="s">
-        <v>115</v>
-      </c>
-      <c r="D39" t="s">
-        <v>46</v>
+        <v>117</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="E39" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F39" t="s">
-        <v>34</v>
-      </c>
-      <c r="G39"/>
-      <c r="H39" s="3">
-        <v>1</v>
-      </c>
-      <c r="I39" s="2">
-        <v>1</v>
-      </c>
-      <c r="J39">
-        <v>1</v>
-      </c>
-      <c r="K39">
-        <v>1</v>
-      </c>
-      <c r="L39"/>
-      <c r="M39" s="3">
+        <v>36</v>
+      </c>
+      <c r="I39" t="s">
+        <v>37</v>
+      </c>
+      <c r="J39"/>
+      <c r="K39" s="6">
+        <v>1</v>
+      </c>
+      <c r="L39" s="4">
+        <v>1</v>
+      </c>
+      <c r="M39">
+        <v>1</v>
+      </c>
+      <c r="N39">
+        <v>1</v>
+      </c>
+      <c r="O39"/>
+      <c r="P39" s="6">
         <v>5</v>
       </c>
-      <c r="N39">
-        <v>1</v>
-      </c>
-      <c r="O39" s="2">
-        <v>2</v>
-      </c>
-      <c r="P39" s="3">
-        <v>2</v>
-      </c>
       <c r="Q39">
+        <v>1</v>
+      </c>
+      <c r="R39" s="4">
+        <v>2</v>
+      </c>
+      <c r="S39" s="6">
+        <v>2</v>
+      </c>
+      <c r="T39">
         <v>6</v>
       </c>
-      <c r="R39" s="2">
+      <c r="U39" s="4">
         <v>7</v>
       </c>
-      <c r="U39"/>
       <c r="X39"/>
-      <c r="Z39"/>
-      <c r="AB39"/>
-      <c r="AE39" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="40" hidden="1" spans="1:31">
+      <c r="AA39"/>
+      <c r="AC39"/>
+      <c r="AE39"/>
+    </row>
+    <row r="40" spans="1:31">
       <c r="A40">
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C40" t="s">
-        <v>117</v>
-      </c>
-      <c r="D40" t="s">
-        <v>46</v>
+        <v>119</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="E40" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F40" t="s">
-        <v>34</v>
-      </c>
-      <c r="G40"/>
-      <c r="H40" s="3">
+        <v>54</v>
+      </c>
+      <c r="I40" t="s">
+        <v>37</v>
+      </c>
+      <c r="J40"/>
+      <c r="K40" s="6">
         <v>4</v>
       </c>
-      <c r="I40" s="2">
-        <v>3</v>
-      </c>
-      <c r="J40">
-        <v>1</v>
-      </c>
-      <c r="K40">
-        <v>1</v>
-      </c>
-      <c r="L40"/>
-      <c r="M40" s="3">
+      <c r="L40" s="4">
+        <v>3</v>
+      </c>
+      <c r="M40">
+        <v>1</v>
+      </c>
+      <c r="N40">
+        <v>1</v>
+      </c>
+      <c r="O40"/>
+      <c r="P40" s="6">
         <v>7</v>
-      </c>
-      <c r="N40">
-        <v>4</v>
-      </c>
-      <c r="O40" s="2">
-        <v>5</v>
-      </c>
-      <c r="P40" s="3">
-        <v>38</v>
       </c>
       <c r="Q40">
         <v>4</v>
       </c>
-      <c r="R40" s="2">
+      <c r="R40" s="4">
         <v>5</v>
       </c>
-      <c r="U40"/>
+      <c r="S40" s="6">
+        <v>38</v>
+      </c>
+      <c r="T40">
+        <v>4</v>
+      </c>
+      <c r="U40" s="4">
+        <v>5</v>
+      </c>
       <c r="X40"/>
-      <c r="Z40"/>
-      <c r="AB40"/>
-      <c r="AE40" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="41" hidden="1" spans="1:31">
+      <c r="AA40"/>
+      <c r="AC40"/>
+      <c r="AE40"/>
+    </row>
+    <row r="41" spans="1:31">
       <c r="A41">
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C41" t="s">
-        <v>119</v>
-      </c>
-      <c r="D41" t="s">
-        <v>32</v>
+        <v>121</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="E41" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F41" t="s">
-        <v>34</v>
-      </c>
-      <c r="G41"/>
-      <c r="H41" s="3">
-        <v>2</v>
-      </c>
-      <c r="I41" s="2">
-        <v>2</v>
-      </c>
-      <c r="J41">
-        <v>0</v>
-      </c>
-      <c r="K41">
-        <v>0</v>
-      </c>
-      <c r="L41"/>
-      <c r="M41" s="3">
+        <v>35</v>
+      </c>
+      <c r="I41" t="s">
+        <v>37</v>
+      </c>
+      <c r="J41"/>
+      <c r="K41" s="6">
+        <v>2</v>
+      </c>
+      <c r="L41" s="4">
+        <v>2</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41"/>
+      <c r="P41" s="6">
         <v>6</v>
       </c>
-      <c r="N41">
-        <v>3</v>
-      </c>
-      <c r="O41" s="2">
-        <v>3</v>
-      </c>
-      <c r="P41" s="3">
+      <c r="Q41">
+        <v>3</v>
+      </c>
+      <c r="R41" s="4">
+        <v>3</v>
+      </c>
+      <c r="S41" s="6">
         <v>39</v>
       </c>
-      <c r="Q41">
-        <v>2</v>
-      </c>
-      <c r="R41" s="2">
-        <v>3</v>
-      </c>
-      <c r="U41"/>
+      <c r="T41">
+        <v>2</v>
+      </c>
+      <c r="U41" s="4">
+        <v>3</v>
+      </c>
       <c r="X41"/>
-      <c r="Z41"/>
-      <c r="AB41"/>
-      <c r="AE41" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="42" hidden="1" spans="1:31">
+      <c r="AA41"/>
+      <c r="AC41"/>
+      <c r="AE41"/>
+    </row>
+    <row r="42" spans="1:31">
       <c r="A42">
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C42" t="s">
-        <v>121</v>
-      </c>
-      <c r="D42" t="s">
-        <v>64</v>
+        <v>123</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="E42" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F42" t="s">
-        <v>34</v>
-      </c>
-      <c r="G42"/>
-      <c r="H42" s="3">
+        <v>54</v>
+      </c>
+      <c r="I42" t="s">
+        <v>37</v>
+      </c>
+      <c r="J42"/>
+      <c r="K42" s="6">
         <v>4</v>
       </c>
-      <c r="I42" s="2">
-        <v>3</v>
-      </c>
-      <c r="J42">
-        <v>1</v>
-      </c>
-      <c r="K42">
-        <v>1</v>
-      </c>
-      <c r="L42"/>
-      <c r="M42" s="3">
+      <c r="L42" s="4">
+        <v>3</v>
+      </c>
+      <c r="M42">
+        <v>1</v>
+      </c>
+      <c r="N42">
+        <v>1</v>
+      </c>
+      <c r="O42"/>
+      <c r="P42" s="6">
         <v>7</v>
       </c>
-      <c r="N42">
-        <v>1</v>
-      </c>
-      <c r="O42" s="2">
-        <v>3</v>
-      </c>
-      <c r="P42" s="3">
+      <c r="Q42">
+        <v>1</v>
+      </c>
+      <c r="R42" s="4">
+        <v>3</v>
+      </c>
+      <c r="S42" s="6">
         <v>41</v>
       </c>
-      <c r="Q42">
-        <v>1</v>
-      </c>
-      <c r="R42" s="2">
-        <v>1</v>
-      </c>
-      <c r="U42"/>
+      <c r="T42">
+        <v>1</v>
+      </c>
+      <c r="U42" s="4">
+        <v>1</v>
+      </c>
       <c r="X42"/>
-      <c r="Z42"/>
-      <c r="AB42"/>
-      <c r="AE42" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="43" hidden="1" spans="1:31">
+      <c r="AA42"/>
+      <c r="AC42"/>
+      <c r="AE42"/>
+    </row>
+    <row r="43" spans="1:31">
       <c r="A43">
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C43" t="s">
-        <v>123</v>
-      </c>
-      <c r="D43" t="s">
-        <v>64</v>
+        <v>125</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="E43" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F43" t="s">
-        <v>34</v>
-      </c>
-      <c r="G43"/>
-      <c r="H43" s="3">
+        <v>35</v>
+      </c>
+      <c r="I43" t="s">
+        <v>37</v>
+      </c>
+      <c r="J43"/>
+      <c r="K43" s="6">
         <v>7</v>
       </c>
-      <c r="I43" s="2">
+      <c r="L43" s="4">
         <v>4</v>
       </c>
-      <c r="J43">
-        <v>0</v>
-      </c>
-      <c r="K43">
-        <v>1</v>
-      </c>
-      <c r="L43"/>
-      <c r="M43" s="3">
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>1</v>
+      </c>
+      <c r="O43"/>
+      <c r="P43" s="6">
         <v>6</v>
       </c>
-      <c r="N43">
+      <c r="Q43">
         <v>5</v>
       </c>
-      <c r="O43" s="2">
+      <c r="R43" s="4">
         <v>5</v>
       </c>
-      <c r="P43" s="3">
+      <c r="S43" s="6">
         <v>14</v>
       </c>
-      <c r="Q43">
-        <v>1</v>
-      </c>
-      <c r="R43" s="2">
-        <v>1</v>
-      </c>
-      <c r="S43" s="3">
+      <c r="T43">
+        <v>1</v>
+      </c>
+      <c r="U43" s="4">
+        <v>1</v>
+      </c>
+      <c r="V43" s="6">
         <v>18</v>
       </c>
-      <c r="T43">
+      <c r="W43">
         <v>0.9</v>
       </c>
-      <c r="U43" s="2">
+      <c r="X43" s="4">
         <v>1.2</v>
       </c>
-      <c r="X43"/>
-      <c r="Z43"/>
-      <c r="AB43"/>
-      <c r="AE43" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="44" spans="1:31">
+      <c r="AA43"/>
+      <c r="AC43"/>
+      <c r="AE43"/>
+    </row>
+    <row r="44" spans="1:21">
       <c r="A44">
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C44" t="s">
-        <v>125</v>
-      </c>
-      <c r="D44" t="s">
-        <v>64</v>
+        <v>127</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="E44" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F44" t="s">
-        <v>34</v>
-      </c>
-      <c r="H44">
+        <v>43</v>
+      </c>
+      <c r="I44" t="s">
+        <v>37</v>
+      </c>
+      <c r="K44">
         <v>6</v>
       </c>
-      <c r="I44" s="2">
+      <c r="L44" s="4">
         <v>4</v>
       </c>
-      <c r="J44">
-        <v>1</v>
-      </c>
-      <c r="K44">
-        <v>1</v>
-      </c>
-      <c r="M44" s="3">
+      <c r="M44">
+        <v>1</v>
+      </c>
+      <c r="N44">
+        <v>1</v>
+      </c>
+      <c r="P44" s="6">
         <v>15</v>
       </c>
-      <c r="N44">
-        <v>2</v>
-      </c>
-      <c r="O44" s="2">
-        <v>2</v>
-      </c>
-      <c r="P44" s="3">
+      <c r="Q44">
+        <v>2</v>
+      </c>
+      <c r="R44" s="4">
+        <v>2</v>
+      </c>
+      <c r="S44" s="6">
         <v>42</v>
       </c>
-      <c r="Q44">
+      <c r="T44">
         <v>8</v>
       </c>
-      <c r="R44" s="2">
+      <c r="U44" s="4">
         <v>12</v>
       </c>
-      <c r="AE44" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="45" hidden="1" spans="1:31">
+    </row>
+    <row r="45" spans="1:31">
       <c r="A45">
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C45" t="s">
-        <v>127</v>
-      </c>
-      <c r="D45" t="s">
-        <v>64</v>
+        <v>129</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="E45" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F45" t="s">
-        <v>34</v>
-      </c>
-      <c r="G45"/>
-      <c r="H45" s="3">
+        <v>54</v>
+      </c>
+      <c r="I45" t="s">
+        <v>37</v>
+      </c>
+      <c r="J45"/>
+      <c r="K45" s="6">
         <v>5</v>
       </c>
-      <c r="I45" s="2">
+      <c r="L45" s="4">
         <v>4</v>
       </c>
-      <c r="J45">
-        <v>0</v>
-      </c>
-      <c r="K45">
-        <v>1</v>
-      </c>
-      <c r="L45"/>
-      <c r="M45" s="3">
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>1</v>
+      </c>
+      <c r="O45"/>
+      <c r="P45" s="6">
         <v>7</v>
       </c>
-      <c r="N45">
+      <c r="Q45">
         <v>7</v>
       </c>
-      <c r="O45" s="2">
+      <c r="R45" s="4">
         <v>9</v>
       </c>
-      <c r="P45" s="3">
+      <c r="S45" s="6">
         <v>26</v>
       </c>
-      <c r="Q45">
-        <v>2</v>
-      </c>
-      <c r="R45" s="2">
-        <v>2</v>
-      </c>
-      <c r="S45" s="3">
-        <v>2</v>
-      </c>
       <c r="T45">
+        <v>2</v>
+      </c>
+      <c r="U45" s="4">
+        <v>2</v>
+      </c>
+      <c r="V45" s="6">
+        <v>2</v>
+      </c>
+      <c r="W45">
         <v>7</v>
       </c>
-      <c r="U45" s="2">
+      <c r="X45" s="4">
         <v>8</v>
       </c>
-      <c r="X45"/>
-      <c r="Z45"/>
-      <c r="AB45"/>
-      <c r="AE45" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="46" hidden="1" spans="1:31">
+      <c r="AA45"/>
+      <c r="AC45"/>
+      <c r="AE45"/>
+    </row>
+    <row r="46" spans="1:31">
       <c r="A46">
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C46" t="s">
-        <v>129</v>
-      </c>
-      <c r="D46" t="s">
-        <v>46</v>
+        <v>131</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="E46" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F46" t="s">
-        <v>34</v>
-      </c>
-      <c r="G46"/>
-      <c r="H46" s="3">
+        <v>36</v>
+      </c>
+      <c r="I46" t="s">
+        <v>37</v>
+      </c>
+      <c r="J46"/>
+      <c r="K46" s="6">
         <v>10</v>
       </c>
-      <c r="I46" s="2">
+      <c r="L46" s="4">
         <v>6</v>
       </c>
-      <c r="J46">
-        <v>1</v>
-      </c>
-      <c r="K46">
-        <v>1</v>
-      </c>
-      <c r="L46"/>
-      <c r="M46" s="3">
+      <c r="M46">
+        <v>1</v>
+      </c>
+      <c r="N46">
+        <v>1</v>
+      </c>
+      <c r="O46"/>
+      <c r="P46" s="6">
         <v>32</v>
       </c>
-      <c r="N46">
+      <c r="Q46">
         <v>40</v>
       </c>
-      <c r="O46" s="2">
+      <c r="R46" s="4">
         <v>40</v>
       </c>
-      <c r="P46" s="3">
+      <c r="S46" s="6">
         <v>33</v>
       </c>
-      <c r="Q46">
+      <c r="T46">
         <v>30</v>
       </c>
-      <c r="R46" s="2">
+      <c r="U46" s="4">
         <v>30</v>
       </c>
-      <c r="S46" s="3">
+      <c r="V46" s="6">
         <v>19</v>
       </c>
-      <c r="T46">
-        <v>1</v>
-      </c>
-      <c r="U46" s="2">
-        <v>1</v>
-      </c>
-      <c r="X46"/>
-      <c r="Z46"/>
-      <c r="AB46"/>
-      <c r="AE46" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="47" hidden="1" spans="1:31">
+      <c r="W46">
+        <v>1</v>
+      </c>
+      <c r="X46" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA46"/>
+      <c r="AC46"/>
+      <c r="AE46"/>
+    </row>
+    <row r="47" spans="1:31">
       <c r="A47">
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C47" t="s">
-        <v>131</v>
-      </c>
-      <c r="D47" t="s">
-        <v>32</v>
+        <v>133</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="E47" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F47" t="s">
-        <v>34</v>
-      </c>
-      <c r="G47"/>
-      <c r="H47" s="3">
-        <v>2</v>
-      </c>
-      <c r="I47" s="2">
-        <v>1</v>
-      </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47">
-        <v>0</v>
-      </c>
-      <c r="L47"/>
-      <c r="M47" s="3">
+        <v>54</v>
+      </c>
+      <c r="I47" t="s">
+        <v>37</v>
+      </c>
+      <c r="J47"/>
+      <c r="K47" s="6">
+        <v>2</v>
+      </c>
+      <c r="L47" s="4">
+        <v>1</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47"/>
+      <c r="P47" s="6">
         <v>11</v>
       </c>
-      <c r="N47">
+      <c r="Q47">
         <v>10</v>
       </c>
-      <c r="O47" s="2">
+      <c r="R47" s="4">
         <v>14</v>
       </c>
-      <c r="R47"/>
       <c r="U47"/>
       <c r="X47"/>
-      <c r="Z47"/>
-      <c r="AB47"/>
-      <c r="AE47" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="48" hidden="1" spans="1:31">
+      <c r="AA47"/>
+      <c r="AC47"/>
+      <c r="AE47"/>
+    </row>
+    <row r="48" spans="1:31">
       <c r="A48">
         <v>49</v>
       </c>
@@ -4707,570 +4718,564 @@
         <v>123</v>
       </c>
       <c r="C48" t="s">
-        <v>132</v>
-      </c>
-      <c r="D48" t="s">
-        <v>32</v>
+        <v>134</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="E48" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F48" t="s">
-        <v>34</v>
-      </c>
-      <c r="G48"/>
-      <c r="H48" s="3">
+        <v>35</v>
+      </c>
+      <c r="I48" t="s">
+        <v>37</v>
+      </c>
+      <c r="J48"/>
+      <c r="K48" s="6">
         <v>4</v>
       </c>
-      <c r="I48" s="2">
-        <v>3</v>
-      </c>
-      <c r="J48">
-        <v>0</v>
-      </c>
-      <c r="K48">
-        <v>0</v>
-      </c>
-      <c r="L48"/>
-      <c r="M48" s="3">
+      <c r="L48" s="4">
+        <v>3</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48"/>
+      <c r="P48" s="6">
         <v>11</v>
       </c>
-      <c r="N48">
+      <c r="Q48">
         <v>8</v>
       </c>
-      <c r="O48" s="2">
+      <c r="R48" s="4">
         <v>11</v>
       </c>
-      <c r="P48" s="3">
+      <c r="S48" s="6">
         <v>6</v>
       </c>
-      <c r="Q48">
-        <v>3</v>
-      </c>
-      <c r="R48" s="2">
-        <v>3</v>
-      </c>
-      <c r="U48"/>
+      <c r="T48">
+        <v>3</v>
+      </c>
+      <c r="U48" s="4">
+        <v>3</v>
+      </c>
       <c r="X48"/>
-      <c r="Z48"/>
-      <c r="AB48"/>
-      <c r="AE48" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="49" spans="1:31">
+      <c r="AA48"/>
+      <c r="AC48"/>
+      <c r="AE48"/>
+    </row>
+    <row r="49" spans="1:21">
       <c r="A49">
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C49" t="s">
-        <v>134</v>
-      </c>
-      <c r="D49" t="s">
-        <v>32</v>
+        <v>136</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="E49" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F49" t="s">
-        <v>34</v>
-      </c>
-      <c r="H49">
+        <v>43</v>
+      </c>
+      <c r="I49" t="s">
+        <v>37</v>
+      </c>
+      <c r="K49">
         <v>4</v>
       </c>
-      <c r="I49" s="2">
-        <v>3</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>0</v>
-      </c>
-      <c r="M49" s="3">
+      <c r="L49" s="4">
+        <v>3</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="P49" s="6">
         <v>11</v>
       </c>
-      <c r="N49">
+      <c r="Q49">
         <v>7</v>
       </c>
-      <c r="O49" s="2">
+      <c r="R49" s="4">
         <v>11</v>
       </c>
-      <c r="P49" s="3">
+      <c r="S49" s="6">
         <v>45</v>
       </c>
-      <c r="Q49">
-        <v>2</v>
-      </c>
-      <c r="R49" s="2">
-        <v>3</v>
-      </c>
-      <c r="AE49" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="50" hidden="1" spans="1:31">
+      <c r="T49">
+        <v>2</v>
+      </c>
+      <c r="U49" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:31">
       <c r="A50">
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C50" t="s">
-        <v>136</v>
-      </c>
-      <c r="D50" t="s">
-        <v>46</v>
+        <v>138</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="E50" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F50" t="s">
-        <v>34</v>
-      </c>
-      <c r="G50"/>
-      <c r="H50" s="3">
+        <v>35</v>
+      </c>
+      <c r="I50" t="s">
+        <v>37</v>
+      </c>
+      <c r="J50"/>
+      <c r="K50" s="6">
         <v>5</v>
       </c>
-      <c r="I50" s="2">
+      <c r="L50" s="4">
         <v>4</v>
       </c>
-      <c r="J50">
-        <v>1</v>
-      </c>
-      <c r="K50">
-        <v>1</v>
-      </c>
-      <c r="L50"/>
-      <c r="M50" s="3">
+      <c r="M50">
+        <v>1</v>
+      </c>
+      <c r="N50">
+        <v>1</v>
+      </c>
+      <c r="O50"/>
+      <c r="P50" s="6">
         <v>6</v>
       </c>
-      <c r="N50">
+      <c r="Q50">
         <v>5</v>
       </c>
-      <c r="O50" s="2">
+      <c r="R50" s="4">
         <v>7</v>
       </c>
-      <c r="P50" s="3">
+      <c r="S50" s="6">
         <v>18</v>
       </c>
-      <c r="Q50">
+      <c r="T50">
         <v>1.1</v>
       </c>
-      <c r="R50" s="2">
+      <c r="U50" s="4">
         <v>1.7</v>
       </c>
-      <c r="U50"/>
       <c r="X50"/>
-      <c r="Z50"/>
-      <c r="AB50"/>
-      <c r="AE50" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="51" hidden="1" spans="1:31">
+      <c r="AA50"/>
+      <c r="AC50"/>
+      <c r="AE50"/>
+    </row>
+    <row r="51" spans="1:31">
       <c r="A51">
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C51" t="s">
-        <v>138</v>
-      </c>
-      <c r="D51" t="s">
-        <v>46</v>
+        <v>140</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="E51" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F51" t="s">
-        <v>34</v>
-      </c>
-      <c r="G51"/>
-      <c r="H51" s="3">
+        <v>35</v>
+      </c>
+      <c r="I51" t="s">
+        <v>37</v>
+      </c>
+      <c r="J51"/>
+      <c r="K51" s="6">
         <v>9</v>
       </c>
-      <c r="I51" s="2">
+      <c r="L51" s="4">
         <v>6</v>
       </c>
-      <c r="J51">
-        <v>1</v>
-      </c>
-      <c r="K51">
-        <v>1</v>
-      </c>
-      <c r="L51"/>
-      <c r="M51" s="3">
+      <c r="M51">
+        <v>1</v>
+      </c>
+      <c r="N51">
+        <v>1</v>
+      </c>
+      <c r="O51"/>
+      <c r="P51" s="6">
         <v>6</v>
       </c>
-      <c r="N51">
-        <v>1</v>
-      </c>
-      <c r="O51" s="2">
-        <v>3</v>
-      </c>
-      <c r="P51" s="3">
+      <c r="Q51">
+        <v>1</v>
+      </c>
+      <c r="R51" s="4">
+        <v>3</v>
+      </c>
+      <c r="S51" s="6">
         <v>49</v>
       </c>
-      <c r="Q51">
-        <v>1</v>
-      </c>
-      <c r="R51" s="2">
-        <v>1</v>
-      </c>
-      <c r="U51"/>
+      <c r="T51">
+        <v>1</v>
+      </c>
+      <c r="U51" s="4">
+        <v>1</v>
+      </c>
       <c r="X51"/>
-      <c r="Z51"/>
-      <c r="AB51"/>
-      <c r="AE51" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="52" hidden="1" spans="1:31">
+      <c r="AA51"/>
+      <c r="AC51"/>
+      <c r="AE51"/>
+    </row>
+    <row r="52" spans="1:31">
       <c r="A52">
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C52" t="s">
-        <v>140</v>
-      </c>
-      <c r="D52" t="s">
-        <v>64</v>
+        <v>142</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="E52" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F52" t="s">
-        <v>34</v>
-      </c>
-      <c r="G52"/>
-      <c r="H52" s="3">
-        <v>1</v>
-      </c>
-      <c r="I52" s="2">
-        <v>0</v>
-      </c>
-      <c r="J52">
-        <v>1</v>
-      </c>
-      <c r="K52">
-        <v>1</v>
-      </c>
-      <c r="L52"/>
-      <c r="M52" s="3">
+        <v>36</v>
+      </c>
+      <c r="I52" t="s">
+        <v>37</v>
+      </c>
+      <c r="J52"/>
+      <c r="K52" s="6">
+        <v>1</v>
+      </c>
+      <c r="L52" s="4">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>1</v>
+      </c>
+      <c r="N52">
+        <v>1</v>
+      </c>
+      <c r="O52"/>
+      <c r="P52" s="6">
         <v>9</v>
       </c>
-      <c r="N52">
-        <v>2</v>
-      </c>
-      <c r="O52" s="2">
-        <v>2</v>
-      </c>
-      <c r="P52" s="3">
+      <c r="Q52">
+        <v>2</v>
+      </c>
+      <c r="R52" s="4">
+        <v>2</v>
+      </c>
+      <c r="S52" s="6">
         <v>21</v>
       </c>
-      <c r="Q52">
-        <v>2</v>
-      </c>
-      <c r="R52" s="2">
-        <v>2</v>
-      </c>
-      <c r="U52"/>
+      <c r="T52">
+        <v>2</v>
+      </c>
+      <c r="U52" s="4">
+        <v>2</v>
+      </c>
       <c r="X52"/>
-      <c r="Z52"/>
-      <c r="AB52"/>
-      <c r="AE52" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="53" spans="1:31">
+      <c r="AA52"/>
+      <c r="AC52"/>
+      <c r="AE52"/>
+    </row>
+    <row r="53" spans="1:21">
       <c r="A53">
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C53" t="s">
-        <v>142</v>
-      </c>
-      <c r="D53" t="s">
-        <v>46</v>
+        <v>144</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="E53" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F53" t="s">
-        <v>34</v>
-      </c>
-      <c r="H53">
+        <v>43</v>
+      </c>
+      <c r="I53" t="s">
+        <v>37</v>
+      </c>
+      <c r="K53">
         <v>5</v>
       </c>
-      <c r="I53" s="2">
+      <c r="L53" s="4">
         <v>5</v>
       </c>
-      <c r="J53">
-        <v>0</v>
-      </c>
-      <c r="K53">
-        <v>1</v>
-      </c>
-      <c r="L53" s="2">
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <v>1</v>
+      </c>
+      <c r="O53" s="4">
         <v>6</v>
       </c>
-      <c r="M53">
+      <c r="P53">
         <v>50</v>
       </c>
-      <c r="N53">
-        <v>3</v>
-      </c>
-      <c r="O53" s="2">
+      <c r="Q53">
+        <v>3</v>
+      </c>
+      <c r="R53" s="4">
         <v>4</v>
       </c>
-      <c r="P53">
+      <c r="S53">
         <v>51</v>
       </c>
-      <c r="Q53">
+      <c r="T53">
         <v>-0.5</v>
       </c>
-      <c r="R53" s="2">
+      <c r="U53" s="4">
         <v>-0.5</v>
       </c>
-      <c r="AE53" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="54" spans="1:31">
+    </row>
+    <row r="54" spans="1:24">
       <c r="A54">
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C54" t="s">
-        <v>144</v>
-      </c>
-      <c r="D54" t="s">
-        <v>64</v>
+        <v>146</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="E54" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F54" t="s">
-        <v>47</v>
-      </c>
-      <c r="G54" s="2">
+        <v>43</v>
+      </c>
+      <c r="I54" t="s">
+        <v>49</v>
+      </c>
+      <c r="J54" s="4">
         <v>14</v>
       </c>
-      <c r="H54">
-        <v>2</v>
-      </c>
-      <c r="I54" s="2">
-        <v>1</v>
-      </c>
-      <c r="J54">
-        <v>0</v>
-      </c>
       <c r="K54">
+        <v>2</v>
+      </c>
+      <c r="L54" s="4">
         <v>1</v>
       </c>
       <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <v>1</v>
+      </c>
+      <c r="P54">
         <v>15</v>
       </c>
-      <c r="N54">
-        <v>3</v>
-      </c>
-      <c r="O54" s="2">
+      <c r="Q54">
+        <v>3</v>
+      </c>
+      <c r="R54" s="4">
         <v>4</v>
       </c>
-      <c r="P54">
+      <c r="S54">
         <v>14</v>
       </c>
-      <c r="Q54">
-        <v>1</v>
-      </c>
-      <c r="R54" s="2">
-        <v>1</v>
-      </c>
-      <c r="S54">
+      <c r="T54">
+        <v>1</v>
+      </c>
+      <c r="U54" s="4">
+        <v>1</v>
+      </c>
+      <c r="V54">
         <v>52</v>
       </c>
-      <c r="T54">
-        <v>3</v>
-      </c>
-      <c r="U54" s="2">
+      <c r="W54">
+        <v>3</v>
+      </c>
+      <c r="X54" s="4">
         <v>5</v>
       </c>
-      <c r="AE54" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="55" spans="1:31">
+    </row>
+    <row r="55" spans="1:30">
       <c r="A55">
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C55" t="s">
-        <v>146</v>
-      </c>
-      <c r="D55" t="s">
-        <v>64</v>
+        <v>148</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="E55" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F55" t="s">
-        <v>34</v>
-      </c>
-      <c r="H55">
+        <v>43</v>
+      </c>
+      <c r="I55" t="s">
+        <v>37</v>
+      </c>
+      <c r="K55">
         <v>4</v>
       </c>
-      <c r="I55" s="2">
-        <v>3</v>
-      </c>
-      <c r="J55">
-        <v>1</v>
-      </c>
-      <c r="K55">
-        <v>1</v>
+      <c r="L55" s="4">
+        <v>3</v>
       </c>
       <c r="M55">
+        <v>1</v>
+      </c>
+      <c r="N55">
+        <v>1</v>
+      </c>
+      <c r="P55">
         <v>15</v>
       </c>
-      <c r="N55">
-        <v>1</v>
-      </c>
-      <c r="O55" s="2">
-        <v>3</v>
-      </c>
-      <c r="P55">
+      <c r="Q55">
+        <v>1</v>
+      </c>
+      <c r="R55" s="4">
+        <v>3</v>
+      </c>
+      <c r="S55">
         <v>60</v>
       </c>
-      <c r="Q55">
-        <v>1</v>
-      </c>
-      <c r="R55" s="2">
-        <v>1</v>
-      </c>
-      <c r="AA55" s="2"/>
-      <c r="AE55" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="56" spans="1:31">
+      <c r="T55">
+        <v>1</v>
+      </c>
+      <c r="U55" s="4">
+        <v>1</v>
+      </c>
+      <c r="AD55" s="4"/>
+    </row>
+    <row r="56" spans="1:30">
       <c r="A56">
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C56" t="s">
-        <v>148</v>
-      </c>
-      <c r="D56" t="s">
-        <v>64</v>
+        <v>150</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="E56" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F56" t="s">
-        <v>47</v>
-      </c>
-      <c r="G56" s="2">
-        <v>3</v>
-      </c>
-      <c r="H56">
-        <v>2</v>
-      </c>
-      <c r="I56" s="2">
-        <v>1</v>
-      </c>
-      <c r="J56">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="I56" t="s">
+        <v>49</v>
+      </c>
+      <c r="J56" s="4">
+        <v>3</v>
       </c>
       <c r="K56">
+        <v>2</v>
+      </c>
+      <c r="L56" s="4">
         <v>1</v>
       </c>
       <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>1</v>
+      </c>
+      <c r="P56">
         <v>45</v>
       </c>
-      <c r="N56">
-        <v>3</v>
-      </c>
-      <c r="O56" s="2">
+      <c r="Q56">
+        <v>3</v>
+      </c>
+      <c r="R56" s="4">
         <v>4</v>
       </c>
-      <c r="P56">
+      <c r="S56">
         <v>11</v>
       </c>
-      <c r="Q56">
+      <c r="T56">
         <v>12</v>
       </c>
-      <c r="R56" s="2">
+      <c r="U56" s="4">
         <v>18</v>
       </c>
-      <c r="S56">
+      <c r="V56">
         <v>14</v>
       </c>
-      <c r="T56">
-        <v>1</v>
-      </c>
-      <c r="U56" s="2">
-        <v>1</v>
-      </c>
-      <c r="AA56" s="2"/>
-      <c r="AE56" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="57" spans="1:31">
+      <c r="W56">
+        <v>1</v>
+      </c>
+      <c r="X56" s="4">
+        <v>1</v>
+      </c>
+      <c r="AD56" s="4"/>
+    </row>
+    <row r="57" spans="1:21">
       <c r="A57">
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C57" t="s">
-        <v>150</v>
-      </c>
-      <c r="D57" t="s">
-        <v>46</v>
+        <v>152</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="E57" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F57" t="s">
-        <v>47</v>
-      </c>
-      <c r="G57" s="2">
-        <v>3</v>
-      </c>
-      <c r="H57">
-        <v>2</v>
-      </c>
-      <c r="I57" s="2">
-        <v>1</v>
-      </c>
-      <c r="J57">
-        <v>1</v>
+        <v>43</v>
+      </c>
+      <c r="I57" t="s">
+        <v>49</v>
+      </c>
+      <c r="J57" s="4">
+        <v>3</v>
       </c>
       <c r="K57">
+        <v>2</v>
+      </c>
+      <c r="L57" s="4">
         <v>1</v>
       </c>
       <c r="M57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N57">
-        <v>5</v>
-      </c>
-      <c r="O57" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P57">
         <v>2</v>
@@ -5278,171 +5283,169 @@
       <c r="Q57">
         <v>5</v>
       </c>
-      <c r="R57" s="2">
+      <c r="R57" s="4">
         <v>6</v>
       </c>
-      <c r="AE57" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="58" spans="1:31">
+      <c r="S57">
+        <v>2</v>
+      </c>
+      <c r="T57">
+        <v>5</v>
+      </c>
+      <c r="U57" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
       <c r="A58">
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C58" t="s">
-        <v>152</v>
-      </c>
-      <c r="D58" t="s">
-        <v>32</v>
+        <v>154</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="E58" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F58" t="s">
-        <v>34</v>
-      </c>
-      <c r="H58">
-        <v>3</v>
-      </c>
-      <c r="I58" s="2">
-        <v>2</v>
-      </c>
-      <c r="J58">
-        <v>1</v>
+        <v>43</v>
+      </c>
+      <c r="I58" t="s">
+        <v>37</v>
       </c>
       <c r="K58">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="59" spans="1:31">
+        <v>3</v>
+      </c>
+      <c r="L58" s="4">
+        <v>2</v>
+      </c>
+      <c r="M58">
+        <v>1</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18">
       <c r="A59">
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C59" t="s">
-        <v>154</v>
-      </c>
-      <c r="D59" t="s">
-        <v>64</v>
+        <v>156</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="E59" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F59" t="s">
-        <v>34</v>
-      </c>
-      <c r="H59">
+        <v>43</v>
+      </c>
+      <c r="I59" t="s">
+        <v>37</v>
+      </c>
+      <c r="K59">
         <v>4</v>
       </c>
-      <c r="I59" s="2">
-        <v>3</v>
-      </c>
-      <c r="J59">
-        <v>1</v>
-      </c>
-      <c r="K59">
-        <v>0</v>
+      <c r="L59" s="4">
+        <v>3</v>
       </c>
       <c r="M59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>2</v>
+      </c>
+      <c r="Q59">
         <v>7</v>
       </c>
-      <c r="O59" s="2">
+      <c r="R59" s="4">
         <v>9</v>
       </c>
-      <c r="AE59" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="60" spans="1:31">
+    </row>
+    <row r="60" spans="1:14">
       <c r="A60">
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C60" t="s">
-        <v>156</v>
-      </c>
-      <c r="D60" t="s">
-        <v>46</v>
+        <v>158</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="E60" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F60" t="s">
-        <v>34</v>
-      </c>
-      <c r="H60">
-        <v>2</v>
-      </c>
-      <c r="I60" s="2">
-        <v>2</v>
-      </c>
-      <c r="J60">
-        <v>1</v>
+        <v>43</v>
+      </c>
+      <c r="I60" t="s">
+        <v>37</v>
       </c>
       <c r="K60">
-        <v>1</v>
-      </c>
-      <c r="AE60" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="61" hidden="1" spans="1:11">
+        <v>2</v>
+      </c>
+      <c r="L60" s="4">
+        <v>2</v>
+      </c>
+      <c r="M60">
+        <v>1</v>
+      </c>
+      <c r="N60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
       <c r="A61">
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C61" t="s">
-        <v>158</v>
-      </c>
-      <c r="D61" t="s">
-        <v>64</v>
+        <v>160</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="E61" t="s">
-        <v>33</v>
-      </c>
-      <c r="F61" t="s">
-        <v>47</v>
-      </c>
-      <c r="G61" s="2">
+        <v>35</v>
+      </c>
+      <c r="I61" t="s">
+        <v>49</v>
+      </c>
+      <c r="J61" s="4">
         <v>14</v>
       </c>
-      <c r="H61">
-        <v>3</v>
-      </c>
-      <c r="I61" s="2">
-        <v>2</v>
-      </c>
-      <c r="J61">
-        <v>0</v>
-      </c>
       <c r="K61">
+        <v>3</v>
+      </c>
+      <c r="L61" s="4">
+        <v>2</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AE61" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="30">
-      <filters>
-        <filter val="C"/>
-      </filters>
-    </filterColumn>
-    <extLst/>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
@@ -5480,19 +5483,19 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5500,13 +5503,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I2">
         <v>-1</v>
@@ -5517,19 +5520,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -5540,16 +5543,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -5560,16 +5563,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -5580,13 +5583,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -5597,16 +5600,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C7" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D7" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E7" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -5617,13 +5620,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C8" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D8" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -5637,13 +5640,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C9" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -5657,13 +5660,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>188</v>
+      </c>
+      <c r="C10" t="s">
+        <v>188</v>
+      </c>
+      <c r="D10" t="s">
         <v>186</v>
-      </c>
-      <c r="C10" t="s">
-        <v>186</v>
-      </c>
-      <c r="D10" t="s">
-        <v>184</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -5677,13 +5680,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C11" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -5694,16 +5697,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C12" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D12" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E12" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -5714,16 +5717,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C13" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D13" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E13" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -5734,19 +5737,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C14" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D14" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -5757,16 +5760,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C15" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D15" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E15" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -5777,16 +5780,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C16" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D16" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E16" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -5797,13 +5800,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C17" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D17" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -5817,16 +5820,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C18" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D18" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E18" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -5837,13 +5840,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C19" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D19" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -5857,13 +5860,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C20" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D20" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -5877,16 +5880,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C21" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D21" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E21" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -5897,16 +5900,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C22" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D22" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E22" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -5917,13 +5920,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C23" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D23" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E23">
         <v>5</v>
@@ -5937,19 +5940,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C24" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D24" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -5960,13 +5963,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C25" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D25" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -5980,16 +5983,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C26" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D26" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E26" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -6003,16 +6006,16 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C27" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D27" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E27" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -6023,13 +6026,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C28" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D28" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -6043,19 +6046,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C29" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D29" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -6069,13 +6072,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C30" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D30" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -6089,19 +6092,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C31" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D31" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E31" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F31" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -6112,19 +6115,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C32" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D32" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E32">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -6135,19 +6138,19 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C33" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D33" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E33">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -6158,16 +6161,16 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C34" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D34" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E34" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -6178,16 +6181,16 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C35" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D35" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E35" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -6198,19 +6201,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C36" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D36" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E36" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F36" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -6224,13 +6227,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C37" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D37" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E37">
         <v>11</v>
@@ -6244,16 +6247,16 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C38" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D38" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E38" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -6264,13 +6267,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C39" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D39" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -6287,16 +6290,16 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C40" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D40" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E40" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -6307,13 +6310,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C41" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D41" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -6330,19 +6333,19 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C42" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D42" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -6356,13 +6359,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C43" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D43" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E43">
         <v>12</v>
@@ -6376,13 +6379,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C44" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D44" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E44">
         <v>13</v>
@@ -6396,19 +6399,19 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C45" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D45" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E45" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F45" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I45">
         <v>-1</v>
@@ -6419,16 +6422,16 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C46" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D46" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E46" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I46">
         <v>1</v>
@@ -6439,13 +6442,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C47" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D47" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E47">
         <v>14</v>
@@ -6459,19 +6462,19 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C48" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D48" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I48">
         <v>-1</v>
@@ -6482,13 +6485,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C49" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D49" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E49">
         <v>15</v>
@@ -6502,19 +6505,19 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C50" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D50" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I50">
         <v>-1</v>
@@ -6525,13 +6528,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C51" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D51" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E51">
         <v>16</v>
@@ -6545,13 +6548,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C52" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D52" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -6565,13 +6568,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C53" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D53" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E53">
         <v>3</v>
@@ -6585,13 +6588,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C54" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D54" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E54">
         <v>3</v>
@@ -6608,16 +6611,16 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C55" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D55" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E55" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G55">
         <v>6</v>
@@ -6631,16 +6634,16 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C56" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D56" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E56" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G56">
         <v>7</v>
@@ -6654,16 +6657,16 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C57" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D57" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E57" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G57">
         <v>8</v>
@@ -6677,16 +6680,16 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C58" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D58" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E58" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G58">
         <v>6</v>
@@ -6700,16 +6703,16 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C59" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D59" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E59" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G59">
         <v>7</v>
@@ -6723,16 +6726,16 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
+        <v>259</v>
+      </c>
+      <c r="C60" t="s">
         <v>257</v>
       </c>
-      <c r="C60" t="s">
-        <v>255</v>
-      </c>
       <c r="D60" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E60" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G60">
         <v>8</v>
@@ -6746,19 +6749,19 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C61" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D61" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E61">
         <v>3</v>
       </c>
       <c r="F61" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I61">
         <v>-1</v>
@@ -6769,13 +6772,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C62" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D62" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E62">
         <v>20</v>
@@ -6817,43 +6820,43 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="O1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6861,10 +6864,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -6890,10 +6893,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -6913,10 +6916,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>270</v>
+      </c>
+      <c r="C4" t="s">
         <v>268</v>
-      </c>
-      <c r="C4" t="s">
-        <v>266</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -6930,10 +6933,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -6965,10 +6968,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -6988,10 +6991,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>274</v>
+      </c>
+      <c r="C7" t="s">
         <v>272</v>
-      </c>
-      <c r="C7" t="s">
-        <v>270</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -7011,10 +7014,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C8" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -7034,10 +7037,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -7057,10 +7060,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C10" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -7080,10 +7083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C11" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -7109,10 +7112,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C12" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -7138,10 +7141,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C13" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -7161,10 +7164,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C14" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -7184,10 +7187,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C15" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -7207,10 +7210,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C16" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -7230,10 +7233,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C17" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -7253,10 +7256,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C18" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -7276,10 +7279,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C19" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -7293,10 +7296,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C20" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -7310,10 +7313,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C21" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -7327,10 +7330,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C22" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -7378,16 +7381,16 @@
         <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -7395,13 +7398,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -7415,16 +7418,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C3" t="s">
+        <v>291</v>
+      </c>
+      <c r="D3" t="s">
         <v>289</v>
       </c>
-      <c r="D3" t="s">
-        <v>287</v>
-      </c>
       <c r="F3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" ht="12.95" customHeight="1" spans="1:6">
@@ -7432,16 +7435,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C4" t="s">
+        <v>291</v>
+      </c>
+      <c r="D4" t="s">
         <v>289</v>
       </c>
-      <c r="D4" t="s">
-        <v>287</v>
-      </c>
       <c r="F4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -7449,13 +7452,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C5" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -7469,13 +7472,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -7489,13 +7492,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C7" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D7" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -7509,13 +7512,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C8" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D8" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -7529,13 +7532,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D9" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -7549,13 +7552,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C10" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D10" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -7569,16 +7572,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C11" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D11" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F11">
         <v>2</v>

--- a/Assets/StreamingAssets/Configurations/Cards.xlsx
+++ b/Assets/StreamingAssets/Configurations/Cards.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{402544E3-79F5-492A-BE22-4EEB323B6A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView xWindow="0" yWindow="540" windowWidth="38730" windowHeight="20850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -24,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -941,167 +945,17 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1120,188 +974,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1327,332 +1001,44 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="00FFFFFF"/>
-      <color rgb="00AB0580"/>
-      <color rgb="0000B050"/>
-      <color rgb="00FFB200"/>
-      <color rgb="004B58FF"/>
-      <color rgb="00FF2160"/>
+      <color rgb="FFFFFFFF"/>
+      <color rgb="FFAB0580"/>
+      <color rgb="FF00B050"/>
+      <color rgb="FFFFB200"/>
+      <color rgb="FF4B58FF"/>
+      <color rgb="FFFF2160"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1910,48 +1296,48 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AG61"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.425" customWidth="1"/>
-    <col min="2" max="2" width="12.7083333333333" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
-    <col min="4" max="4" width="10.425" style="2" customWidth="1"/>
-    <col min="5" max="5" width="4.85" customWidth="1"/>
-    <col min="6" max="6" width="7.89166666666667" customWidth="1"/>
-    <col min="7" max="7" width="5.06666666666667" customWidth="1"/>
-    <col min="8" max="8" width="5.50833333333333" style="3" customWidth="1"/>
-    <col min="9" max="9" width="10.5666666666667" customWidth="1"/>
-    <col min="10" max="10" width="9.70833333333333" style="4" customWidth="1"/>
-    <col min="11" max="11" width="7.14166666666667" customWidth="1"/>
-    <col min="12" max="12" width="14" style="4" customWidth="1"/>
-    <col min="13" max="13" width="10.2833333333333" customWidth="1"/>
-    <col min="14" max="14" width="13.7083333333333" customWidth="1"/>
-    <col min="15" max="15" width="9.70833333333333" style="4" customWidth="1"/>
-    <col min="16" max="16" width="9.70833333333333" customWidth="1"/>
-    <col min="17" max="17" width="12.1416666666667" customWidth="1"/>
-    <col min="18" max="18" width="17.7083333333333" style="4" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="4.85546875" customWidth="1"/>
+    <col min="6" max="6" width="7.85546875" customWidth="1"/>
+    <col min="7" max="7" width="5" customWidth="1"/>
+    <col min="8" max="8" width="5.5703125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" style="3" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" customWidth="1"/>
+    <col min="12" max="12" width="14" style="3" customWidth="1"/>
+    <col min="13" max="13" width="10.28515625" customWidth="1"/>
+    <col min="14" max="14" width="13.7109375" customWidth="1"/>
+    <col min="15" max="15" width="9.7109375" style="3" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="17" width="12.140625" customWidth="1"/>
+    <col min="18" max="18" width="17.7109375" style="3" customWidth="1"/>
     <col min="19" max="19" width="11" customWidth="1"/>
-    <col min="20" max="20" width="12.2833333333333" customWidth="1"/>
-    <col min="21" max="21" width="17.1416666666667" style="4" customWidth="1"/>
-    <col min="24" max="24" width="17.7083333333333" style="4" customWidth="1"/>
-    <col min="25" max="25" width="10.7083333333333" customWidth="1"/>
+    <col min="20" max="20" width="12.28515625" customWidth="1"/>
+    <col min="21" max="21" width="17.140625" style="3" customWidth="1"/>
+    <col min="24" max="24" width="17.7109375" style="3" customWidth="1"/>
+    <col min="25" max="25" width="10.7109375" customWidth="1"/>
     <col min="26" max="26" width="11" customWidth="1"/>
-    <col min="27" max="27" width="17.7083333333333" style="4" customWidth="1"/>
-    <col min="28" max="28" width="12.425" customWidth="1"/>
-    <col min="29" max="29" width="12.425" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12.2833333333333" customWidth="1"/>
-    <col min="31" max="31" width="9" style="4"/>
-    <col min="32" max="32" width="4.28333333333333" customWidth="1"/>
+    <col min="27" max="27" width="17.7109375" style="3" customWidth="1"/>
+    <col min="28" max="28" width="12.42578125" customWidth="1"/>
+    <col min="29" max="29" width="12.42578125" style="3" customWidth="1"/>
+    <col min="30" max="30" width="12.28515625" customWidth="1"/>
+    <col min="31" max="31" width="9" style="3"/>
+    <col min="32" max="32" width="4.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32">
+    <row r="1" spans="1:33">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1979,13 +1365,13 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
       <c r="M1" t="s">
@@ -1994,62 +1380,62 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
       <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
       <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
       <c r="W1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="X1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
       <c r="Z1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AA1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AB1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="4" t="s">
+      <c r="AC1" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AD1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AE1" s="3" t="s">
         <v>30</v>
       </c>
       <c r="AF1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:32">
+    <row r="2" spans="1:33">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2072,10 +1458,10 @@
         <v>37</v>
       </c>
       <c r="J2"/>
-      <c r="K2" s="6">
+      <c r="K2" s="2">
         <v>4</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="3">
         <v>3</v>
       </c>
       <c r="M2">
@@ -2085,13 +1471,13 @@
         <v>0</v>
       </c>
       <c r="O2"/>
-      <c r="P2" s="6">
+      <c r="P2" s="2">
         <v>11</v>
       </c>
       <c r="Q2">
         <v>7</v>
       </c>
-      <c r="R2" s="4">
+      <c r="R2" s="3">
         <v>7</v>
       </c>
       <c r="U2"/>
@@ -2099,9 +1485,9 @@
       <c r="AA2"/>
       <c r="AC2"/>
       <c r="AE2"/>
-      <c r="AF2" s="7"/>
-    </row>
-    <row r="3" spans="1:32">
+      <c r="AF2" s="5"/>
+    </row>
+    <row r="3" spans="1:33">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2124,10 +1510,10 @@
         <v>37</v>
       </c>
       <c r="J3"/>
-      <c r="K3" s="6">
-        <v>0</v>
-      </c>
-      <c r="L3" s="4">
+      <c r="K3" s="2">
+        <v>0</v>
+      </c>
+      <c r="L3" s="3">
         <v>0</v>
       </c>
       <c r="M3">
@@ -2137,13 +1523,13 @@
         <v>0</v>
       </c>
       <c r="O3"/>
-      <c r="P3" s="6">
+      <c r="P3" s="2">
         <v>2</v>
       </c>
       <c r="Q3">
         <v>4</v>
       </c>
-      <c r="R3" s="4">
+      <c r="R3" s="3">
         <v>4</v>
       </c>
       <c r="U3"/>
@@ -2151,9 +1537,9 @@
       <c r="AA3"/>
       <c r="AC3"/>
       <c r="AE3"/>
-      <c r="AF3" s="7"/>
-    </row>
-    <row r="4" spans="1:32">
+      <c r="AF3" s="5"/>
+    </row>
+    <row r="4" spans="1:33">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2178,7 +1564,7 @@
       <c r="K4">
         <v>5</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="3">
         <v>4</v>
       </c>
       <c r="M4">
@@ -2187,13 +1573,13 @@
       <c r="N4">
         <v>0</v>
       </c>
-      <c r="P4" s="6">
+      <c r="P4" s="2">
         <v>11</v>
       </c>
       <c r="Q4">
         <v>15</v>
       </c>
-      <c r="R4" s="4">
+      <c r="R4" s="3">
         <v>18</v>
       </c>
       <c r="S4">
@@ -2202,12 +1588,12 @@
       <c r="T4">
         <v>9</v>
       </c>
-      <c r="U4" s="4">
+      <c r="U4" s="3">
         <v>12</v>
       </c>
-      <c r="AF4" s="7"/>
-    </row>
-    <row r="5" spans="1:32">
+      <c r="AF4" s="5"/>
+    </row>
+    <row r="5" spans="1:33">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2230,10 +1616,10 @@
         <v>37</v>
       </c>
       <c r="J5"/>
-      <c r="K5" s="6">
-        <v>3</v>
-      </c>
-      <c r="L5" s="4">
+      <c r="K5" s="2">
+        <v>3</v>
+      </c>
+      <c r="L5" s="3">
         <v>3</v>
       </c>
       <c r="M5">
@@ -2243,31 +1629,31 @@
         <v>0</v>
       </c>
       <c r="O5"/>
-      <c r="P5" s="6">
+      <c r="P5" s="2">
         <v>11</v>
       </c>
       <c r="Q5">
         <v>5</v>
       </c>
-      <c r="R5" s="4">
+      <c r="R5" s="3">
         <v>5</v>
       </c>
-      <c r="S5" s="6">
+      <c r="S5" s="2">
         <v>2</v>
       </c>
       <c r="T5">
         <v>2</v>
       </c>
-      <c r="U5" s="4">
+      <c r="U5" s="3">
         <v>2</v>
       </c>
       <c r="X5"/>
       <c r="AA5"/>
       <c r="AC5"/>
       <c r="AE5"/>
-      <c r="AF5" s="7"/>
-    </row>
-    <row r="6" spans="1:32">
+      <c r="AF5" s="5"/>
+    </row>
+    <row r="6" spans="1:33">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2289,13 +1675,13 @@
       <c r="I6" t="s">
         <v>49</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="3">
         <v>3</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
-      <c r="L6" s="4">
+      <c r="L6" s="3">
         <v>1</v>
       </c>
       <c r="M6">
@@ -2304,7 +1690,7 @@
       <c r="N6">
         <v>1</v>
       </c>
-      <c r="P6" s="6">
+      <c r="P6" s="2">
         <v>0</v>
       </c>
       <c r="S6">
@@ -2313,7 +1699,7 @@
       <c r="T6">
         <v>2</v>
       </c>
-      <c r="U6" s="4">
+      <c r="U6" s="3">
         <v>7</v>
       </c>
       <c r="V6">
@@ -2322,12 +1708,12 @@
       <c r="W6">
         <v>1</v>
       </c>
-      <c r="X6" s="4">
-        <v>1</v>
-      </c>
-      <c r="AF6" s="7"/>
-    </row>
-    <row r="7" spans="1:32">
+      <c r="X6" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF6" s="5"/>
+    </row>
+    <row r="7" spans="1:33">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2350,10 +1736,10 @@
         <v>37</v>
       </c>
       <c r="J7"/>
-      <c r="K7" s="6">
+      <c r="K7" s="2">
         <v>5</v>
       </c>
-      <c r="L7" s="4">
+      <c r="L7" s="3">
         <v>4</v>
       </c>
       <c r="M7">
@@ -2363,34 +1749,34 @@
         <v>1</v>
       </c>
       <c r="O7"/>
-      <c r="P7" s="6">
+      <c r="P7" s="2">
         <v>4</v>
       </c>
       <c r="R7"/>
-      <c r="S7" s="6">
+      <c r="S7" s="2">
         <v>21</v>
       </c>
       <c r="T7">
         <v>2</v>
       </c>
-      <c r="U7" s="4">
-        <v>2</v>
-      </c>
-      <c r="V7" s="6">
+      <c r="U7" s="3">
+        <v>2</v>
+      </c>
+      <c r="V7" s="2">
         <v>14</v>
       </c>
       <c r="W7">
         <v>1</v>
       </c>
-      <c r="X7" s="4">
+      <c r="X7" s="3">
         <v>1</v>
       </c>
       <c r="AA7"/>
       <c r="AC7"/>
       <c r="AE7"/>
-      <c r="AF7" s="7"/>
-    </row>
-    <row r="8" spans="1:32">
+      <c r="AF7" s="5"/>
+    </row>
+    <row r="8" spans="1:33">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2415,10 +1801,10 @@
       <c r="J8">
         <v>0</v>
       </c>
-      <c r="K8" s="6">
-        <v>1</v>
-      </c>
-      <c r="L8" s="4">
+      <c r="K8" s="2">
+        <v>1</v>
+      </c>
+      <c r="L8" s="3">
         <v>1</v>
       </c>
       <c r="M8">
@@ -2428,39 +1814,39 @@
         <v>1</v>
       </c>
       <c r="O8"/>
-      <c r="P8" s="6">
+      <c r="P8" s="2">
         <v>2</v>
       </c>
       <c r="Q8">
         <v>7</v>
       </c>
-      <c r="R8" s="4">
+      <c r="R8" s="3">
         <v>7</v>
       </c>
-      <c r="S8" s="6">
+      <c r="S8" s="2">
         <v>3</v>
       </c>
       <c r="T8">
         <v>1</v>
       </c>
-      <c r="U8" s="4">
-        <v>1</v>
-      </c>
-      <c r="V8" s="6">
+      <c r="U8" s="3">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2">
         <v>14</v>
       </c>
       <c r="W8">
         <v>1</v>
       </c>
-      <c r="X8" s="4">
+      <c r="X8" s="3">
         <v>1</v>
       </c>
       <c r="AA8"/>
       <c r="AC8"/>
       <c r="AE8"/>
-      <c r="AF8" s="7"/>
-    </row>
-    <row r="9" spans="1:32">
+      <c r="AF8" s="5"/>
+    </row>
+    <row r="9" spans="1:33">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2483,10 +1869,10 @@
         <v>37</v>
       </c>
       <c r="J9"/>
-      <c r="K9" s="6">
-        <v>2</v>
-      </c>
-      <c r="L9" s="4">
+      <c r="K9" s="2">
+        <v>2</v>
+      </c>
+      <c r="L9" s="3">
         <v>2</v>
       </c>
       <c r="M9">
@@ -2496,31 +1882,31 @@
         <v>0</v>
       </c>
       <c r="O9"/>
-      <c r="P9" s="6">
+      <c r="P9" s="2">
         <v>6</v>
       </c>
       <c r="Q9">
         <v>3</v>
       </c>
-      <c r="R9" s="4">
+      <c r="R9" s="3">
         <v>4</v>
       </c>
-      <c r="S9" s="6">
+      <c r="S9" s="2">
         <v>2</v>
       </c>
       <c r="T9">
         <v>3</v>
       </c>
-      <c r="U9" s="4">
+      <c r="U9" s="3">
         <v>4</v>
       </c>
       <c r="X9"/>
       <c r="AA9"/>
       <c r="AC9"/>
       <c r="AE9"/>
-      <c r="AF9" s="7"/>
-    </row>
-    <row r="10" spans="1:32">
+      <c r="AF9" s="5"/>
+    </row>
+    <row r="10" spans="1:33">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2543,10 +1929,10 @@
         <v>37</v>
       </c>
       <c r="J10"/>
-      <c r="K10" s="6">
-        <v>2</v>
-      </c>
-      <c r="L10" s="4">
+      <c r="K10" s="2">
+        <v>2</v>
+      </c>
+      <c r="L10" s="3">
         <v>2</v>
       </c>
       <c r="M10">
@@ -2556,31 +1942,31 @@
         <v>0</v>
       </c>
       <c r="O10"/>
-      <c r="P10" s="6">
+      <c r="P10" s="2">
         <v>7</v>
       </c>
       <c r="Q10">
         <v>2</v>
       </c>
-      <c r="R10" s="4">
-        <v>3</v>
-      </c>
-      <c r="S10" s="6">
+      <c r="R10" s="3">
+        <v>3</v>
+      </c>
+      <c r="S10" s="2">
         <v>2</v>
       </c>
       <c r="T10">
         <v>2</v>
       </c>
-      <c r="U10" s="4">
+      <c r="U10" s="3">
         <v>3</v>
       </c>
       <c r="X10"/>
       <c r="AA10"/>
       <c r="AC10"/>
       <c r="AE10"/>
-      <c r="AF10" s="7"/>
-    </row>
-    <row r="11" spans="1:32">
+      <c r="AF10" s="5"/>
+    </row>
+    <row r="11" spans="1:33">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2605,7 +1991,7 @@
       <c r="K11">
         <v>2</v>
       </c>
-      <c r="L11" s="4">
+      <c r="L11" s="3">
         <v>2</v>
       </c>
       <c r="M11">
@@ -2614,25 +2000,25 @@
       <c r="N11">
         <v>0</v>
       </c>
-      <c r="P11" s="6">
+      <c r="P11" s="2">
         <v>15</v>
       </c>
       <c r="Q11">
         <v>2</v>
       </c>
-      <c r="R11" s="4">
-        <v>3</v>
-      </c>
-      <c r="S11" s="6">
+      <c r="R11" s="3">
+        <v>3</v>
+      </c>
+      <c r="S11" s="2">
         <v>2</v>
       </c>
       <c r="T11">
         <v>2</v>
       </c>
-      <c r="U11" s="4">
-        <v>3</v>
-      </c>
-      <c r="AF11" s="7"/>
+      <c r="U11" s="3">
+        <v>3</v>
+      </c>
+      <c r="AF11" s="5"/>
     </row>
     <row r="12" spans="1:33">
       <c r="A12">
@@ -2657,10 +2043,10 @@
         <v>37</v>
       </c>
       <c r="J12"/>
-      <c r="K12" s="6">
+      <c r="K12" s="2">
         <v>6</v>
       </c>
-      <c r="L12" s="4">
+      <c r="L12" s="3">
         <v>6</v>
       </c>
       <c r="M12">
@@ -2670,34 +2056,34 @@
         <v>0</v>
       </c>
       <c r="O12"/>
-      <c r="P12" s="6">
+      <c r="P12" s="2">
         <v>11</v>
       </c>
       <c r="Q12">
         <v>9</v>
       </c>
-      <c r="R12" s="4">
+      <c r="R12" s="3">
         <v>13</v>
       </c>
-      <c r="S12" s="6">
+      <c r="S12" s="2">
         <v>11</v>
       </c>
       <c r="T12">
         <v>9</v>
       </c>
-      <c r="U12" s="4">
+      <c r="U12" s="3">
         <v>13</v>
       </c>
       <c r="X12"/>
       <c r="AA12"/>
       <c r="AC12"/>
       <c r="AE12"/>
-      <c r="AF12" s="7"/>
+      <c r="AF12" s="5"/>
       <c r="AG12" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:32">
+    <row r="13" spans="1:33">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2720,10 +2106,10 @@
         <v>37</v>
       </c>
       <c r="J13"/>
-      <c r="K13" s="6">
+      <c r="K13" s="2">
         <v>5</v>
       </c>
-      <c r="L13" s="4">
+      <c r="L13" s="3">
         <v>5</v>
       </c>
       <c r="M13">
@@ -2733,31 +2119,31 @@
         <v>0</v>
       </c>
       <c r="O13"/>
-      <c r="P13" s="6">
+      <c r="P13" s="2">
         <v>11</v>
       </c>
       <c r="Q13">
         <v>11</v>
       </c>
-      <c r="R13" s="4">
+      <c r="R13" s="3">
         <v>15</v>
       </c>
-      <c r="S13" s="6">
+      <c r="S13" s="2">
         <v>2</v>
       </c>
       <c r="T13">
         <v>7</v>
       </c>
-      <c r="U13" s="4">
+      <c r="U13" s="3">
         <v>9</v>
       </c>
       <c r="X13"/>
       <c r="AA13"/>
       <c r="AC13"/>
       <c r="AE13"/>
-      <c r="AF13" s="7"/>
-    </row>
-    <row r="14" spans="1:32">
+      <c r="AF13" s="5"/>
+    </row>
+    <row r="14" spans="1:33">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2780,10 +2166,10 @@
         <v>37</v>
       </c>
       <c r="J14"/>
-      <c r="K14" s="6">
+      <c r="K14" s="2">
         <v>5</v>
       </c>
-      <c r="L14" s="4">
+      <c r="L14" s="3">
         <v>4</v>
       </c>
       <c r="M14">
@@ -2793,13 +2179,13 @@
         <v>0</v>
       </c>
       <c r="O14"/>
-      <c r="P14" s="6">
+      <c r="P14" s="2">
         <v>6</v>
       </c>
       <c r="Q14">
         <v>6</v>
       </c>
-      <c r="R14" s="4">
+      <c r="R14" s="3">
         <v>8</v>
       </c>
       <c r="U14"/>
@@ -2807,9 +2193,9 @@
       <c r="AA14"/>
       <c r="AC14"/>
       <c r="AE14"/>
-      <c r="AF14" s="7"/>
-    </row>
-    <row r="15" spans="1:32">
+      <c r="AF14" s="5"/>
+    </row>
+    <row r="15" spans="1:33">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2832,10 +2218,10 @@
         <v>37</v>
       </c>
       <c r="J15"/>
-      <c r="K15" s="6">
+      <c r="K15" s="2">
         <v>4</v>
       </c>
-      <c r="L15" s="4">
+      <c r="L15" s="3">
         <v>4</v>
       </c>
       <c r="M15">
@@ -2845,13 +2231,13 @@
         <v>0</v>
       </c>
       <c r="O15"/>
-      <c r="P15" s="6">
+      <c r="P15" s="2">
         <v>18</v>
       </c>
       <c r="Q15">
         <v>1.4</v>
       </c>
-      <c r="R15" s="4">
+      <c r="R15" s="3">
         <v>1.8</v>
       </c>
       <c r="U15"/>
@@ -2859,9 +2245,9 @@
       <c r="AA15"/>
       <c r="AC15"/>
       <c r="AE15"/>
-      <c r="AF15" s="7"/>
-    </row>
-    <row r="16" spans="1:32">
+      <c r="AF15" s="5"/>
+    </row>
+    <row r="16" spans="1:33">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2884,10 +2270,10 @@
         <v>37</v>
       </c>
       <c r="J16"/>
-      <c r="K16" s="6">
+      <c r="K16" s="2">
         <v>6</v>
       </c>
-      <c r="L16" s="4">
+      <c r="L16" s="3">
         <v>5</v>
       </c>
       <c r="M16">
@@ -2897,29 +2283,29 @@
         <v>0</v>
       </c>
       <c r="O16"/>
-      <c r="P16" s="6">
+      <c r="P16" s="2">
         <v>6</v>
       </c>
       <c r="Q16">
         <v>4</v>
       </c>
-      <c r="R16" s="4">
+      <c r="R16" s="3">
         <v>5</v>
       </c>
-      <c r="S16" s="6">
+      <c r="S16" s="2">
         <v>18</v>
       </c>
       <c r="T16">
         <v>0.8</v>
       </c>
-      <c r="U16" s="4">
-        <v>1.1</v>
+      <c r="U16" s="3">
+        <v>1.1000000000000001</v>
       </c>
       <c r="X16"/>
       <c r="AA16"/>
       <c r="AC16"/>
       <c r="AE16"/>
-      <c r="AF16" s="7"/>
+      <c r="AF16" s="5"/>
     </row>
     <row r="17" spans="1:32">
       <c r="A17">
@@ -2944,10 +2330,10 @@
         <v>37</v>
       </c>
       <c r="J17"/>
-      <c r="K17" s="6">
-        <v>3</v>
-      </c>
-      <c r="L17" s="4">
+      <c r="K17" s="2">
+        <v>3</v>
+      </c>
+      <c r="L17" s="3">
         <v>3</v>
       </c>
       <c r="M17">
@@ -2957,37 +2343,37 @@
         <v>1</v>
       </c>
       <c r="O17"/>
-      <c r="P17" s="6">
+      <c r="P17" s="2">
         <v>19</v>
       </c>
       <c r="Q17">
         <v>1</v>
       </c>
-      <c r="R17" s="4">
-        <v>1</v>
-      </c>
-      <c r="S17" s="6">
+      <c r="R17" s="3">
+        <v>1</v>
+      </c>
+      <c r="S17" s="2">
         <v>2</v>
       </c>
       <c r="T17">
         <v>4</v>
       </c>
-      <c r="U17" s="4">
+      <c r="U17" s="3">
         <v>6</v>
       </c>
-      <c r="V17" s="6">
+      <c r="V17" s="2">
         <v>21</v>
       </c>
       <c r="W17">
         <v>2</v>
       </c>
-      <c r="X17" s="4">
+      <c r="X17" s="3">
         <v>3</v>
       </c>
       <c r="AA17"/>
       <c r="AC17"/>
       <c r="AE17"/>
-      <c r="AF17" s="8"/>
+      <c r="AF17" s="6"/>
     </row>
     <row r="18" spans="1:32">
       <c r="A18">
@@ -3014,7 +2400,7 @@
       <c r="K18">
         <v>4</v>
       </c>
-      <c r="L18" s="4">
+      <c r="L18" s="3">
         <v>3</v>
       </c>
       <c r="M18">
@@ -3023,22 +2409,22 @@
       <c r="N18">
         <v>0</v>
       </c>
-      <c r="P18" s="6">
+      <c r="P18" s="2">
         <v>15</v>
       </c>
       <c r="Q18">
         <v>5</v>
       </c>
-      <c r="R18" s="4">
+      <c r="R18" s="3">
         <v>7</v>
       </c>
       <c r="AB18">
         <v>61</v>
       </c>
-      <c r="AC18" s="4">
+      <c r="AC18" s="3">
         <v>1.5</v>
       </c>
-      <c r="AF18" s="7"/>
+      <c r="AF18" s="5"/>
     </row>
     <row r="19" spans="1:32">
       <c r="A19">
@@ -3063,10 +2449,10 @@
         <v>37</v>
       </c>
       <c r="J19"/>
-      <c r="K19" s="6">
+      <c r="K19" s="2">
         <v>5</v>
       </c>
-      <c r="L19" s="4">
+      <c r="L19" s="3">
         <v>4</v>
       </c>
       <c r="M19">
@@ -3076,29 +2462,29 @@
         <v>1</v>
       </c>
       <c r="O19"/>
-      <c r="P19" s="6">
+      <c r="P19" s="2">
         <v>23</v>
       </c>
       <c r="Q19">
         <v>1</v>
       </c>
-      <c r="R19" s="4">
-        <v>1</v>
-      </c>
-      <c r="S19" s="6">
+      <c r="R19" s="3">
+        <v>1</v>
+      </c>
+      <c r="S19" s="2">
         <v>7</v>
       </c>
       <c r="T19">
         <v>1</v>
       </c>
-      <c r="U19" s="4">
+      <c r="U19" s="3">
         <v>2</v>
       </c>
       <c r="X19"/>
       <c r="AA19"/>
       <c r="AC19"/>
       <c r="AE19"/>
-      <c r="AF19" s="7"/>
+      <c r="AF19" s="5"/>
     </row>
     <row r="20" spans="1:32">
       <c r="A20">
@@ -3125,7 +2511,7 @@
       <c r="K20">
         <v>6</v>
       </c>
-      <c r="L20" s="4">
+      <c r="L20" s="3">
         <v>6</v>
       </c>
       <c r="M20">
@@ -3134,25 +2520,25 @@
       <c r="N20">
         <v>0</v>
       </c>
-      <c r="O20" s="4">
-        <v>0</v>
-      </c>
-      <c r="P20" s="6">
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="2">
         <v>11</v>
       </c>
       <c r="Q20">
         <v>24</v>
       </c>
-      <c r="R20" s="4">
+      <c r="R20" s="3">
         <v>30</v>
       </c>
       <c r="AB20">
         <v>62</v>
       </c>
-      <c r="AC20" s="4">
+      <c r="AC20" s="3">
         <v>7</v>
       </c>
-      <c r="AF20" s="8"/>
+      <c r="AF20" s="6"/>
     </row>
     <row r="21" spans="1:32">
       <c r="A21">
@@ -3179,7 +2565,7 @@
       <c r="K21">
         <v>5</v>
       </c>
-      <c r="L21" s="4">
+      <c r="L21" s="3">
         <v>4</v>
       </c>
       <c r="M21">
@@ -3188,22 +2574,22 @@
       <c r="N21">
         <v>1</v>
       </c>
-      <c r="P21" s="6">
+      <c r="P21" s="2">
         <v>26</v>
       </c>
       <c r="Q21">
         <v>2</v>
       </c>
-      <c r="R21" s="4">
-        <v>2</v>
-      </c>
-      <c r="S21" s="6">
+      <c r="R21" s="3">
+        <v>2</v>
+      </c>
+      <c r="S21" s="2">
         <v>11</v>
       </c>
       <c r="T21">
         <v>30</v>
       </c>
-      <c r="U21" s="4">
+      <c r="U21" s="3">
         <v>42</v>
       </c>
       <c r="V21">
@@ -3212,10 +2598,10 @@
       <c r="W21">
         <v>5</v>
       </c>
-      <c r="X21" s="4">
+      <c r="X21" s="3">
         <v>7</v>
       </c>
-      <c r="AF21" s="7"/>
+      <c r="AF21" s="5"/>
     </row>
     <row r="22" spans="1:32">
       <c r="A22">
@@ -3240,10 +2626,10 @@
         <v>37</v>
       </c>
       <c r="J22"/>
-      <c r="K22" s="6">
+      <c r="K22" s="2">
         <v>4</v>
       </c>
-      <c r="L22" s="4">
+      <c r="L22" s="3">
         <v>4</v>
       </c>
       <c r="M22">
@@ -3253,29 +2639,29 @@
         <v>1</v>
       </c>
       <c r="O22"/>
-      <c r="P22" s="6">
+      <c r="P22" s="2">
         <v>6</v>
       </c>
       <c r="Q22">
         <v>2</v>
       </c>
-      <c r="R22" s="4">
+      <c r="R22" s="3">
         <v>4</v>
       </c>
-      <c r="S22" s="6">
+      <c r="S22" s="2">
         <v>28</v>
       </c>
       <c r="T22">
         <v>1</v>
       </c>
-      <c r="U22" s="4">
+      <c r="U22" s="3">
         <v>1</v>
       </c>
       <c r="X22"/>
       <c r="AA22"/>
       <c r="AC22"/>
       <c r="AE22"/>
-      <c r="AF22" s="7"/>
+      <c r="AF22" s="5"/>
     </row>
     <row r="23" spans="1:32">
       <c r="A23">
@@ -3300,10 +2686,10 @@
         <v>37</v>
       </c>
       <c r="J23"/>
-      <c r="K23" s="6">
-        <v>1</v>
-      </c>
-      <c r="L23" s="4">
+      <c r="K23" s="2">
+        <v>1</v>
+      </c>
+      <c r="L23" s="3">
         <v>1</v>
       </c>
       <c r="M23">
@@ -3313,29 +2699,29 @@
         <v>0</v>
       </c>
       <c r="O23"/>
-      <c r="P23" s="6">
+      <c r="P23" s="2">
         <v>6</v>
       </c>
       <c r="Q23">
         <v>5</v>
       </c>
-      <c r="R23" s="4">
+      <c r="R23" s="3">
         <v>7</v>
       </c>
-      <c r="S23" s="6">
+      <c r="S23" s="2">
         <v>2</v>
       </c>
       <c r="T23">
         <v>1</v>
       </c>
-      <c r="U23" s="4">
+      <c r="U23" s="3">
         <v>1</v>
       </c>
       <c r="X23"/>
       <c r="AA23"/>
       <c r="AC23"/>
       <c r="AE23"/>
-      <c r="AF23" s="7"/>
+      <c r="AF23" s="5"/>
     </row>
     <row r="24" spans="1:32">
       <c r="A24">
@@ -3362,7 +2748,7 @@
       <c r="K24">
         <v>4</v>
       </c>
-      <c r="L24" s="4">
+      <c r="L24" s="3">
         <v>4</v>
       </c>
       <c r="M24">
@@ -3371,31 +2757,31 @@
       <c r="N24">
         <v>0</v>
       </c>
-      <c r="P24" s="6">
+      <c r="P24" s="2">
         <v>15</v>
       </c>
       <c r="Q24">
         <v>3</v>
       </c>
-      <c r="R24" s="4">
+      <c r="R24" s="3">
         <v>4</v>
       </c>
-      <c r="S24" s="6">
+      <c r="S24" s="2">
         <v>11</v>
       </c>
       <c r="T24">
         <v>8</v>
       </c>
-      <c r="U24" s="4">
+      <c r="U24" s="3">
         <v>11</v>
       </c>
       <c r="AB24">
         <v>63</v>
       </c>
-      <c r="AC24" s="4">
-        <v>3</v>
-      </c>
-      <c r="AF24" s="7"/>
+      <c r="AC24" s="3">
+        <v>3</v>
+      </c>
+      <c r="AF24" s="5"/>
     </row>
     <row r="25" spans="1:32">
       <c r="A25">
@@ -3420,10 +2806,10 @@
         <v>37</v>
       </c>
       <c r="J25"/>
-      <c r="K25" s="6">
-        <v>3</v>
-      </c>
-      <c r="L25" s="4">
+      <c r="K25" s="2">
+        <v>3</v>
+      </c>
+      <c r="L25" s="3">
         <v>2</v>
       </c>
       <c r="M25">
@@ -3433,13 +2819,13 @@
         <v>0</v>
       </c>
       <c r="O25"/>
-      <c r="P25" s="6">
+      <c r="P25" s="2">
         <v>7</v>
       </c>
       <c r="Q25">
         <v>3</v>
       </c>
-      <c r="R25" s="4">
+      <c r="R25" s="3">
         <v>5</v>
       </c>
       <c r="U25"/>
@@ -3447,7 +2833,7 @@
       <c r="AA25"/>
       <c r="AC25"/>
       <c r="AE25"/>
-      <c r="AF25" s="7"/>
+      <c r="AF25" s="5"/>
     </row>
     <row r="26" spans="1:32">
       <c r="A26">
@@ -3472,10 +2858,10 @@
         <v>37</v>
       </c>
       <c r="J26"/>
-      <c r="K26" s="6">
-        <v>3</v>
-      </c>
-      <c r="L26" s="4">
+      <c r="K26" s="2">
+        <v>3</v>
+      </c>
+      <c r="L26" s="3">
         <v>2</v>
       </c>
       <c r="M26">
@@ -3485,29 +2871,29 @@
         <v>0</v>
       </c>
       <c r="O26"/>
-      <c r="P26" s="6">
+      <c r="P26" s="2">
         <v>7</v>
       </c>
       <c r="Q26">
         <v>3</v>
       </c>
-      <c r="R26" s="4">
+      <c r="R26" s="3">
         <v>4</v>
       </c>
-      <c r="S26" s="6">
+      <c r="S26" s="2">
         <v>2</v>
       </c>
       <c r="T26">
         <v>4</v>
       </c>
-      <c r="U26" s="4">
+      <c r="U26" s="3">
         <v>6</v>
       </c>
       <c r="X26"/>
       <c r="AA26"/>
       <c r="AC26"/>
       <c r="AE26"/>
-      <c r="AF26" s="7"/>
+      <c r="AF26" s="5"/>
     </row>
     <row r="27" spans="1:32">
       <c r="A27">
@@ -3534,7 +2920,7 @@
       <c r="K27">
         <v>8</v>
       </c>
-      <c r="L27" s="4">
+      <c r="L27" s="3">
         <v>6</v>
       </c>
       <c r="M27">
@@ -3543,25 +2929,25 @@
       <c r="N27">
         <v>1</v>
       </c>
-      <c r="O27" s="4">
-        <v>0</v>
-      </c>
-      <c r="P27" s="6">
+      <c r="O27" s="3">
+        <v>0</v>
+      </c>
+      <c r="P27" s="2">
         <v>11</v>
       </c>
       <c r="Q27">
         <v>12</v>
       </c>
-      <c r="R27" s="4">
+      <c r="R27" s="3">
         <v>18</v>
       </c>
-      <c r="S27" s="6">
+      <c r="S27" s="2">
         <v>56</v>
       </c>
       <c r="T27">
         <v>24</v>
       </c>
-      <c r="U27" s="4">
+      <c r="U27" s="3">
         <v>30</v>
       </c>
       <c r="V27">
@@ -3570,10 +2956,10 @@
       <c r="W27">
         <v>36</v>
       </c>
-      <c r="X27" s="4">
+      <c r="X27" s="3">
         <v>44</v>
       </c>
-      <c r="AF27" s="8"/>
+      <c r="AF27" s="6"/>
     </row>
     <row r="28" spans="1:32">
       <c r="A28">
@@ -3600,7 +2986,7 @@
       <c r="K28">
         <v>1</v>
       </c>
-      <c r="L28" s="4">
+      <c r="L28" s="3">
         <v>0</v>
       </c>
       <c r="M28">
@@ -3609,22 +2995,22 @@
       <c r="N28">
         <v>0</v>
       </c>
-      <c r="P28" s="6">
+      <c r="P28" s="2">
         <v>2</v>
       </c>
       <c r="Q28">
         <v>6</v>
       </c>
-      <c r="R28" s="4">
+      <c r="R28" s="3">
         <v>8</v>
       </c>
       <c r="AB28">
         <v>21</v>
       </c>
-      <c r="AC28" s="4">
+      <c r="AC28" s="3">
         <v>12</v>
       </c>
-      <c r="AF28" s="7"/>
+      <c r="AF28" s="5"/>
     </row>
     <row r="29" spans="1:32">
       <c r="A29">
@@ -3649,10 +3035,10 @@
         <v>37</v>
       </c>
       <c r="J29"/>
-      <c r="K29" s="6">
+      <c r="K29" s="2">
         <v>5</v>
       </c>
-      <c r="L29" s="4">
+      <c r="L29" s="3">
         <v>5</v>
       </c>
       <c r="M29">
@@ -3662,37 +3048,37 @@
         <v>1</v>
       </c>
       <c r="O29"/>
-      <c r="P29" s="6">
+      <c r="P29" s="2">
         <v>32</v>
       </c>
       <c r="Q29">
         <v>30</v>
       </c>
-      <c r="R29" s="4">
+      <c r="R29" s="3">
         <v>30</v>
       </c>
-      <c r="S29" s="6">
+      <c r="S29" s="2">
         <v>2</v>
       </c>
       <c r="T29">
         <v>3</v>
       </c>
-      <c r="U29" s="4">
+      <c r="U29" s="3">
         <v>5</v>
       </c>
-      <c r="V29" s="6">
+      <c r="V29" s="2">
         <v>21</v>
       </c>
       <c r="W29">
         <v>2</v>
       </c>
-      <c r="X29" s="4">
+      <c r="X29" s="3">
         <v>3</v>
       </c>
       <c r="AA29"/>
       <c r="AC29"/>
       <c r="AE29"/>
-      <c r="AF29" s="7"/>
+      <c r="AF29" s="5"/>
     </row>
     <row r="30" spans="1:32">
       <c r="A30">
@@ -3717,10 +3103,10 @@
         <v>37</v>
       </c>
       <c r="J30"/>
-      <c r="K30" s="6">
+      <c r="K30" s="2">
         <v>4</v>
       </c>
-      <c r="L30" s="4">
+      <c r="L30" s="3">
         <v>4</v>
       </c>
       <c r="M30">
@@ -3730,29 +3116,29 @@
         <v>1</v>
       </c>
       <c r="O30"/>
-      <c r="P30" s="6">
+      <c r="P30" s="2">
         <v>33</v>
       </c>
       <c r="Q30">
         <v>50</v>
       </c>
-      <c r="R30" s="4">
+      <c r="R30" s="3">
         <v>70</v>
       </c>
-      <c r="S30" s="6">
+      <c r="S30" s="2">
         <v>2</v>
       </c>
       <c r="T30">
         <v>2</v>
       </c>
-      <c r="U30" s="4">
+      <c r="U30" s="3">
         <v>4</v>
       </c>
       <c r="X30"/>
       <c r="AA30"/>
       <c r="AC30"/>
       <c r="AE30"/>
-      <c r="AF30" s="8"/>
+      <c r="AF30" s="6"/>
     </row>
     <row r="31" spans="1:32">
       <c r="A31">
@@ -3777,10 +3163,10 @@
         <v>37</v>
       </c>
       <c r="J31"/>
-      <c r="K31" s="6">
+      <c r="K31" s="2">
         <v>4</v>
       </c>
-      <c r="L31" s="4">
+      <c r="L31" s="3">
         <v>3</v>
       </c>
       <c r="M31">
@@ -3790,31 +3176,31 @@
         <v>1</v>
       </c>
       <c r="O31"/>
-      <c r="P31" s="6">
+      <c r="P31" s="2">
         <v>33</v>
       </c>
       <c r="Q31">
         <v>20</v>
       </c>
-      <c r="R31" s="4">
+      <c r="R31" s="3">
         <v>30</v>
       </c>
-      <c r="S31" s="6">
+      <c r="S31" s="2">
         <v>35</v>
       </c>
       <c r="T31">
         <v>1</v>
       </c>
-      <c r="U31" s="4">
+      <c r="U31" s="3">
         <v>1</v>
       </c>
       <c r="X31"/>
       <c r="AA31"/>
       <c r="AC31"/>
       <c r="AE31"/>
-      <c r="AF31" s="8"/>
-    </row>
-    <row r="32" spans="1:31">
+      <c r="AF31" s="6"/>
+    </row>
+    <row r="32" spans="1:32">
       <c r="A32">
         <v>33</v>
       </c>
@@ -3837,10 +3223,10 @@
         <v>37</v>
       </c>
       <c r="J32"/>
-      <c r="K32" s="6">
+      <c r="K32" s="2">
         <v>7</v>
       </c>
-      <c r="L32" s="4">
+      <c r="L32" s="3">
         <v>6</v>
       </c>
       <c r="M32">
@@ -3857,7 +3243,7 @@
       <c r="AC32"/>
       <c r="AE32"/>
     </row>
-    <row r="33" spans="1:29">
+    <row r="33" spans="1:31">
       <c r="A33">
         <v>34</v>
       </c>
@@ -3882,7 +3268,7 @@
       <c r="K33">
         <v>8</v>
       </c>
-      <c r="L33" s="4">
+      <c r="L33" s="3">
         <v>7</v>
       </c>
       <c r="M33">
@@ -3891,23 +3277,23 @@
       <c r="N33">
         <v>1</v>
       </c>
-      <c r="P33" s="6">
+      <c r="P33" s="2">
         <v>11</v>
       </c>
       <c r="Q33">
         <v>38</v>
       </c>
-      <c r="R33" s="4">
+      <c r="R33" s="3">
         <v>52</v>
       </c>
       <c r="AB33">
         <v>64</v>
       </c>
-      <c r="AC33" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18">
+      <c r="AC33" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:31">
       <c r="A34">
         <v>35</v>
       </c>
@@ -3932,7 +3318,7 @@
       <c r="K34">
         <v>3</v>
       </c>
-      <c r="L34" s="4">
+      <c r="L34" s="3">
         <v>3</v>
       </c>
       <c r="M34">
@@ -3941,20 +3327,20 @@
       <c r="N34">
         <v>0</v>
       </c>
-      <c r="O34" s="4">
-        <v>0</v>
-      </c>
-      <c r="P34" s="6">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="2">
         <v>15</v>
       </c>
       <c r="Q34">
         <v>3</v>
       </c>
-      <c r="R34" s="4">
+      <c r="R34" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:18">
+    <row r="35" spans="1:31">
       <c r="A35">
         <v>36</v>
       </c>
@@ -3979,7 +3365,7 @@
       <c r="K35">
         <v>3</v>
       </c>
-      <c r="L35" s="4">
+      <c r="L35" s="3">
         <v>3</v>
       </c>
       <c r="M35">
@@ -3988,21 +3374,21 @@
       <c r="N35">
         <v>0</v>
       </c>
-      <c r="P35" s="6">
+      <c r="P35" s="2">
         <v>11</v>
       </c>
       <c r="Q35">
         <v>18</v>
       </c>
-      <c r="R35" s="4">
+      <c r="R35" s="3">
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:21">
+    <row r="36" spans="1:31">
       <c r="A36">
         <v>37</v>
       </c>
-      <c r="B36" s="5">
+      <c r="B36" s="4">
         <v>144</v>
       </c>
       <c r="C36" t="s">
@@ -4023,7 +3409,7 @@
       <c r="K36">
         <v>3</v>
       </c>
-      <c r="L36" s="4">
+      <c r="L36" s="3">
         <v>3</v>
       </c>
       <c r="M36">
@@ -4032,22 +3418,22 @@
       <c r="N36">
         <v>0</v>
       </c>
-      <c r="P36" s="6">
+      <c r="P36" s="2">
         <v>15</v>
       </c>
       <c r="Q36">
         <v>3</v>
       </c>
-      <c r="R36" s="4">
+      <c r="R36" s="3">
         <v>4</v>
       </c>
-      <c r="S36" s="6">
+      <c r="S36" s="2">
         <v>2</v>
       </c>
       <c r="T36">
         <v>6</v>
       </c>
-      <c r="U36" s="4">
+      <c r="U36" s="3">
         <v>8</v>
       </c>
     </row>
@@ -4074,10 +3460,10 @@
         <v>37</v>
       </c>
       <c r="J37"/>
-      <c r="K37" s="6">
-        <v>3</v>
-      </c>
-      <c r="L37" s="4">
+      <c r="K37" s="2">
+        <v>3</v>
+      </c>
+      <c r="L37" s="3">
         <v>3</v>
       </c>
       <c r="M37">
@@ -4087,22 +3473,22 @@
         <v>0</v>
       </c>
       <c r="O37"/>
-      <c r="P37" s="6">
+      <c r="P37" s="2">
         <v>7</v>
       </c>
       <c r="Q37">
         <v>3</v>
       </c>
-      <c r="R37" s="4">
+      <c r="R37" s="3">
         <v>4</v>
       </c>
-      <c r="S37" s="6">
+      <c r="S37" s="2">
         <v>2</v>
       </c>
       <c r="T37">
         <v>6</v>
       </c>
-      <c r="U37" s="4">
+      <c r="U37" s="3">
         <v>8</v>
       </c>
       <c r="X37"/>
@@ -4133,10 +3519,10 @@
         <v>37</v>
       </c>
       <c r="J38"/>
-      <c r="K38" s="6">
-        <v>1</v>
-      </c>
-      <c r="L38" s="4">
+      <c r="K38" s="2">
+        <v>1</v>
+      </c>
+      <c r="L38" s="3">
         <v>1</v>
       </c>
       <c r="M38">
@@ -4146,22 +3532,22 @@
         <v>1</v>
       </c>
       <c r="O38"/>
-      <c r="P38" s="6">
+      <c r="P38" s="2">
         <v>21</v>
       </c>
       <c r="Q38">
         <v>4</v>
       </c>
-      <c r="R38" s="4">
+      <c r="R38" s="3">
         <v>5</v>
       </c>
-      <c r="S38" s="6">
+      <c r="S38" s="2">
         <v>2</v>
       </c>
       <c r="T38">
         <v>3</v>
       </c>
-      <c r="U38" s="4">
+      <c r="U38" s="3">
         <v>5</v>
       </c>
       <c r="X38"/>
@@ -4192,10 +3578,10 @@
         <v>37</v>
       </c>
       <c r="J39"/>
-      <c r="K39" s="6">
-        <v>1</v>
-      </c>
-      <c r="L39" s="4">
+      <c r="K39" s="2">
+        <v>1</v>
+      </c>
+      <c r="L39" s="3">
         <v>1</v>
       </c>
       <c r="M39">
@@ -4205,22 +3591,22 @@
         <v>1</v>
       </c>
       <c r="O39"/>
-      <c r="P39" s="6">
+      <c r="P39" s="2">
         <v>5</v>
       </c>
       <c r="Q39">
         <v>1</v>
       </c>
-      <c r="R39" s="4">
-        <v>2</v>
-      </c>
-      <c r="S39" s="6">
+      <c r="R39" s="3">
+        <v>2</v>
+      </c>
+      <c r="S39" s="2">
         <v>2</v>
       </c>
       <c r="T39">
         <v>6</v>
       </c>
-      <c r="U39" s="4">
+      <c r="U39" s="3">
         <v>7</v>
       </c>
       <c r="X39"/>
@@ -4251,10 +3637,10 @@
         <v>37</v>
       </c>
       <c r="J40"/>
-      <c r="K40" s="6">
+      <c r="K40" s="2">
         <v>4</v>
       </c>
-      <c r="L40" s="4">
+      <c r="L40" s="3">
         <v>3</v>
       </c>
       <c r="M40">
@@ -4264,22 +3650,22 @@
         <v>1</v>
       </c>
       <c r="O40"/>
-      <c r="P40" s="6">
+      <c r="P40" s="2">
         <v>7</v>
       </c>
       <c r="Q40">
         <v>4</v>
       </c>
-      <c r="R40" s="4">
+      <c r="R40" s="3">
         <v>5</v>
       </c>
-      <c r="S40" s="6">
+      <c r="S40" s="2">
         <v>38</v>
       </c>
       <c r="T40">
         <v>4</v>
       </c>
-      <c r="U40" s="4">
+      <c r="U40" s="3">
         <v>5</v>
       </c>
       <c r="X40"/>
@@ -4310,10 +3696,10 @@
         <v>37</v>
       </c>
       <c r="J41"/>
-      <c r="K41" s="6">
-        <v>2</v>
-      </c>
-      <c r="L41" s="4">
+      <c r="K41" s="2">
+        <v>2</v>
+      </c>
+      <c r="L41" s="3">
         <v>2</v>
       </c>
       <c r="M41">
@@ -4323,22 +3709,22 @@
         <v>0</v>
       </c>
       <c r="O41"/>
-      <c r="P41" s="6">
+      <c r="P41" s="2">
         <v>6</v>
       </c>
       <c r="Q41">
         <v>3</v>
       </c>
-      <c r="R41" s="4">
-        <v>3</v>
-      </c>
-      <c r="S41" s="6">
+      <c r="R41" s="3">
+        <v>3</v>
+      </c>
+      <c r="S41" s="2">
         <v>39</v>
       </c>
       <c r="T41">
         <v>2</v>
       </c>
-      <c r="U41" s="4">
+      <c r="U41" s="3">
         <v>3</v>
       </c>
       <c r="X41"/>
@@ -4369,10 +3755,10 @@
         <v>37</v>
       </c>
       <c r="J42"/>
-      <c r="K42" s="6">
+      <c r="K42" s="2">
         <v>4</v>
       </c>
-      <c r="L42" s="4">
+      <c r="L42" s="3">
         <v>3</v>
       </c>
       <c r="M42">
@@ -4382,22 +3768,22 @@
         <v>1</v>
       </c>
       <c r="O42"/>
-      <c r="P42" s="6">
+      <c r="P42" s="2">
         <v>7</v>
       </c>
       <c r="Q42">
         <v>1</v>
       </c>
-      <c r="R42" s="4">
-        <v>3</v>
-      </c>
-      <c r="S42" s="6">
+      <c r="R42" s="3">
+        <v>3</v>
+      </c>
+      <c r="S42" s="2">
         <v>41</v>
       </c>
       <c r="T42">
         <v>1</v>
       </c>
-      <c r="U42" s="4">
+      <c r="U42" s="3">
         <v>1</v>
       </c>
       <c r="X42"/>
@@ -4428,10 +3814,10 @@
         <v>37</v>
       </c>
       <c r="J43"/>
-      <c r="K43" s="6">
+      <c r="K43" s="2">
         <v>7</v>
       </c>
-      <c r="L43" s="4">
+      <c r="L43" s="3">
         <v>4</v>
       </c>
       <c r="M43">
@@ -4441,38 +3827,38 @@
         <v>1</v>
       </c>
       <c r="O43"/>
-      <c r="P43" s="6">
+      <c r="P43" s="2">
         <v>6</v>
       </c>
       <c r="Q43">
         <v>5</v>
       </c>
-      <c r="R43" s="4">
+      <c r="R43" s="3">
         <v>5</v>
       </c>
-      <c r="S43" s="6">
+      <c r="S43" s="2">
         <v>14</v>
       </c>
       <c r="T43">
         <v>1</v>
       </c>
-      <c r="U43" s="4">
-        <v>1</v>
-      </c>
-      <c r="V43" s="6">
+      <c r="U43" s="3">
+        <v>1</v>
+      </c>
+      <c r="V43" s="2">
         <v>18</v>
       </c>
       <c r="W43">
         <v>0.9</v>
       </c>
-      <c r="X43" s="4">
+      <c r="X43" s="3">
         <v>1.2</v>
       </c>
       <c r="AA43"/>
       <c r="AC43"/>
       <c r="AE43"/>
     </row>
-    <row r="44" spans="1:21">
+    <row r="44" spans="1:31">
       <c r="A44">
         <v>45</v>
       </c>
@@ -4497,7 +3883,7 @@
       <c r="K44">
         <v>6</v>
       </c>
-      <c r="L44" s="4">
+      <c r="L44" s="3">
         <v>4</v>
       </c>
       <c r="M44">
@@ -4506,22 +3892,22 @@
       <c r="N44">
         <v>1</v>
       </c>
-      <c r="P44" s="6">
+      <c r="P44" s="2">
         <v>15</v>
       </c>
       <c r="Q44">
         <v>2</v>
       </c>
-      <c r="R44" s="4">
-        <v>2</v>
-      </c>
-      <c r="S44" s="6">
+      <c r="R44" s="3">
+        <v>2</v>
+      </c>
+      <c r="S44" s="2">
         <v>42</v>
       </c>
       <c r="T44">
         <v>8</v>
       </c>
-      <c r="U44" s="4">
+      <c r="U44" s="3">
         <v>12</v>
       </c>
     </row>
@@ -4548,10 +3934,10 @@
         <v>37</v>
       </c>
       <c r="J45"/>
-      <c r="K45" s="6">
+      <c r="K45" s="2">
         <v>5</v>
       </c>
-      <c r="L45" s="4">
+      <c r="L45" s="3">
         <v>4</v>
       </c>
       <c r="M45">
@@ -4561,31 +3947,31 @@
         <v>1</v>
       </c>
       <c r="O45"/>
-      <c r="P45" s="6">
+      <c r="P45" s="2">
         <v>7</v>
       </c>
       <c r="Q45">
         <v>7</v>
       </c>
-      <c r="R45" s="4">
+      <c r="R45" s="3">
         <v>9</v>
       </c>
-      <c r="S45" s="6">
+      <c r="S45" s="2">
         <v>26</v>
       </c>
       <c r="T45">
         <v>2</v>
       </c>
-      <c r="U45" s="4">
-        <v>2</v>
-      </c>
-      <c r="V45" s="6">
+      <c r="U45" s="3">
+        <v>2</v>
+      </c>
+      <c r="V45" s="2">
         <v>2</v>
       </c>
       <c r="W45">
         <v>7</v>
       </c>
-      <c r="X45" s="4">
+      <c r="X45" s="3">
         <v>8</v>
       </c>
       <c r="AA45"/>
@@ -4615,10 +4001,10 @@
         <v>37</v>
       </c>
       <c r="J46"/>
-      <c r="K46" s="6">
+      <c r="K46" s="2">
         <v>10</v>
       </c>
-      <c r="L46" s="4">
+      <c r="L46" s="3">
         <v>6</v>
       </c>
       <c r="M46">
@@ -4628,31 +4014,31 @@
         <v>1</v>
       </c>
       <c r="O46"/>
-      <c r="P46" s="6">
+      <c r="P46" s="2">
         <v>32</v>
       </c>
       <c r="Q46">
         <v>40</v>
       </c>
-      <c r="R46" s="4">
+      <c r="R46" s="3">
         <v>40</v>
       </c>
-      <c r="S46" s="6">
+      <c r="S46" s="2">
         <v>33</v>
       </c>
       <c r="T46">
         <v>30</v>
       </c>
-      <c r="U46" s="4">
+      <c r="U46" s="3">
         <v>30</v>
       </c>
-      <c r="V46" s="6">
+      <c r="V46" s="2">
         <v>19</v>
       </c>
       <c r="W46">
         <v>1</v>
       </c>
-      <c r="X46" s="4">
+      <c r="X46" s="3">
         <v>1</v>
       </c>
       <c r="AA46"/>
@@ -4682,10 +4068,10 @@
         <v>37</v>
       </c>
       <c r="J47"/>
-      <c r="K47" s="6">
-        <v>2</v>
-      </c>
-      <c r="L47" s="4">
+      <c r="K47" s="2">
+        <v>2</v>
+      </c>
+      <c r="L47" s="3">
         <v>1</v>
       </c>
       <c r="M47">
@@ -4695,13 +4081,13 @@
         <v>0</v>
       </c>
       <c r="O47"/>
-      <c r="P47" s="6">
+      <c r="P47" s="2">
         <v>11</v>
       </c>
       <c r="Q47">
         <v>10</v>
       </c>
-      <c r="R47" s="4">
+      <c r="R47" s="3">
         <v>14</v>
       </c>
       <c r="U47"/>
@@ -4733,10 +4119,10 @@
         <v>37</v>
       </c>
       <c r="J48"/>
-      <c r="K48" s="6">
+      <c r="K48" s="2">
         <v>4</v>
       </c>
-      <c r="L48" s="4">
+      <c r="L48" s="3">
         <v>3</v>
       </c>
       <c r="M48">
@@ -4746,22 +4132,22 @@
         <v>0</v>
       </c>
       <c r="O48"/>
-      <c r="P48" s="6">
+      <c r="P48" s="2">
         <v>11</v>
       </c>
       <c r="Q48">
         <v>8</v>
       </c>
-      <c r="R48" s="4">
+      <c r="R48" s="3">
         <v>11</v>
       </c>
-      <c r="S48" s="6">
+      <c r="S48" s="2">
         <v>6</v>
       </c>
       <c r="T48">
         <v>3</v>
       </c>
-      <c r="U48" s="4">
+      <c r="U48" s="3">
         <v>3</v>
       </c>
       <c r="X48"/>
@@ -4769,7 +4155,7 @@
       <c r="AC48"/>
       <c r="AE48"/>
     </row>
-    <row r="49" spans="1:21">
+    <row r="49" spans="1:31">
       <c r="A49">
         <v>50</v>
       </c>
@@ -4794,7 +4180,7 @@
       <c r="K49">
         <v>4</v>
       </c>
-      <c r="L49" s="4">
+      <c r="L49" s="3">
         <v>3</v>
       </c>
       <c r="M49">
@@ -4803,22 +4189,22 @@
       <c r="N49">
         <v>0</v>
       </c>
-      <c r="P49" s="6">
+      <c r="P49" s="2">
         <v>11</v>
       </c>
       <c r="Q49">
         <v>7</v>
       </c>
-      <c r="R49" s="4">
+      <c r="R49" s="3">
         <v>11</v>
       </c>
-      <c r="S49" s="6">
+      <c r="S49" s="2">
         <v>45</v>
       </c>
       <c r="T49">
         <v>2</v>
       </c>
-      <c r="U49" s="4">
+      <c r="U49" s="3">
         <v>3</v>
       </c>
     </row>
@@ -4845,10 +4231,10 @@
         <v>37</v>
       </c>
       <c r="J50"/>
-      <c r="K50" s="6">
+      <c r="K50" s="2">
         <v>5</v>
       </c>
-      <c r="L50" s="4">
+      <c r="L50" s="3">
         <v>4</v>
       </c>
       <c r="M50">
@@ -4858,22 +4244,22 @@
         <v>1</v>
       </c>
       <c r="O50"/>
-      <c r="P50" s="6">
+      <c r="P50" s="2">
         <v>6</v>
       </c>
       <c r="Q50">
         <v>5</v>
       </c>
-      <c r="R50" s="4">
+      <c r="R50" s="3">
         <v>7</v>
       </c>
-      <c r="S50" s="6">
+      <c r="S50" s="2">
         <v>18</v>
       </c>
       <c r="T50">
-        <v>1.1</v>
-      </c>
-      <c r="U50" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U50" s="3">
         <v>1.7</v>
       </c>
       <c r="X50"/>
@@ -4904,10 +4290,10 @@
         <v>37</v>
       </c>
       <c r="J51"/>
-      <c r="K51" s="6">
+      <c r="K51" s="2">
         <v>9</v>
       </c>
-      <c r="L51" s="4">
+      <c r="L51" s="3">
         <v>6</v>
       </c>
       <c r="M51">
@@ -4917,22 +4303,22 @@
         <v>1</v>
       </c>
       <c r="O51"/>
-      <c r="P51" s="6">
+      <c r="P51" s="2">
         <v>6</v>
       </c>
       <c r="Q51">
         <v>1</v>
       </c>
-      <c r="R51" s="4">
-        <v>3</v>
-      </c>
-      <c r="S51" s="6">
+      <c r="R51" s="3">
+        <v>3</v>
+      </c>
+      <c r="S51" s="2">
         <v>49</v>
       </c>
       <c r="T51">
         <v>1</v>
       </c>
-      <c r="U51" s="4">
+      <c r="U51" s="3">
         <v>1</v>
       </c>
       <c r="X51"/>
@@ -4963,10 +4349,10 @@
         <v>37</v>
       </c>
       <c r="J52"/>
-      <c r="K52" s="6">
-        <v>1</v>
-      </c>
-      <c r="L52" s="4">
+      <c r="K52" s="2">
+        <v>1</v>
+      </c>
+      <c r="L52" s="3">
         <v>0</v>
       </c>
       <c r="M52">
@@ -4976,22 +4362,22 @@
         <v>1</v>
       </c>
       <c r="O52"/>
-      <c r="P52" s="6">
+      <c r="P52" s="2">
         <v>9</v>
       </c>
       <c r="Q52">
         <v>2</v>
       </c>
-      <c r="R52" s="4">
-        <v>2</v>
-      </c>
-      <c r="S52" s="6">
+      <c r="R52" s="3">
+        <v>2</v>
+      </c>
+      <c r="S52" s="2">
         <v>21</v>
       </c>
       <c r="T52">
         <v>2</v>
       </c>
-      <c r="U52" s="4">
+      <c r="U52" s="3">
         <v>2</v>
       </c>
       <c r="X52"/>
@@ -4999,7 +4385,7 @@
       <c r="AC52"/>
       <c r="AE52"/>
     </row>
-    <row r="53" spans="1:21">
+    <row r="53" spans="1:31">
       <c r="A53">
         <v>54</v>
       </c>
@@ -5024,7 +4410,7 @@
       <c r="K53">
         <v>5</v>
       </c>
-      <c r="L53" s="4">
+      <c r="L53" s="3">
         <v>5</v>
       </c>
       <c r="M53">
@@ -5033,7 +4419,7 @@
       <c r="N53">
         <v>1</v>
       </c>
-      <c r="O53" s="4">
+      <c r="O53" s="3">
         <v>6</v>
       </c>
       <c r="P53">
@@ -5042,7 +4428,7 @@
       <c r="Q53">
         <v>3</v>
       </c>
-      <c r="R53" s="4">
+      <c r="R53" s="3">
         <v>4</v>
       </c>
       <c r="S53">
@@ -5051,11 +4437,11 @@
       <c r="T53">
         <v>-0.5</v>
       </c>
-      <c r="U53" s="4">
+      <c r="U53" s="3">
         <v>-0.5</v>
       </c>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:31">
       <c r="A54">
         <v>55</v>
       </c>
@@ -5077,13 +4463,13 @@
       <c r="I54" t="s">
         <v>49</v>
       </c>
-      <c r="J54" s="4">
+      <c r="J54" s="3">
         <v>14</v>
       </c>
       <c r="K54">
         <v>2</v>
       </c>
-      <c r="L54" s="4">
+      <c r="L54" s="3">
         <v>1</v>
       </c>
       <c r="M54">
@@ -5098,7 +4484,7 @@
       <c r="Q54">
         <v>3</v>
       </c>
-      <c r="R54" s="4">
+      <c r="R54" s="3">
         <v>4</v>
       </c>
       <c r="S54">
@@ -5107,7 +4493,7 @@
       <c r="T54">
         <v>1</v>
       </c>
-      <c r="U54" s="4">
+      <c r="U54" s="3">
         <v>1</v>
       </c>
       <c r="V54">
@@ -5116,11 +4502,11 @@
       <c r="W54">
         <v>3</v>
       </c>
-      <c r="X54" s="4">
+      <c r="X54" s="3">
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:30">
+    <row r="55" spans="1:31">
       <c r="A55">
         <v>56</v>
       </c>
@@ -5145,7 +4531,7 @@
       <c r="K55">
         <v>4</v>
       </c>
-      <c r="L55" s="4">
+      <c r="L55" s="3">
         <v>3</v>
       </c>
       <c r="M55">
@@ -5160,7 +4546,7 @@
       <c r="Q55">
         <v>1</v>
       </c>
-      <c r="R55" s="4">
+      <c r="R55" s="3">
         <v>3</v>
       </c>
       <c r="S55">
@@ -5169,12 +4555,12 @@
       <c r="T55">
         <v>1</v>
       </c>
-      <c r="U55" s="4">
-        <v>1</v>
-      </c>
-      <c r="AD55" s="4"/>
-    </row>
-    <row r="56" spans="1:30">
+      <c r="U55" s="3">
+        <v>1</v>
+      </c>
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="1:31">
       <c r="A56">
         <v>57</v>
       </c>
@@ -5196,13 +4582,13 @@
       <c r="I56" t="s">
         <v>49</v>
       </c>
-      <c r="J56" s="4">
+      <c r="J56" s="3">
         <v>3</v>
       </c>
       <c r="K56">
         <v>2</v>
       </c>
-      <c r="L56" s="4">
+      <c r="L56" s="3">
         <v>1</v>
       </c>
       <c r="M56">
@@ -5217,7 +4603,7 @@
       <c r="Q56">
         <v>3</v>
       </c>
-      <c r="R56" s="4">
+      <c r="R56" s="3">
         <v>4</v>
       </c>
       <c r="S56">
@@ -5226,7 +4612,7 @@
       <c r="T56">
         <v>12</v>
       </c>
-      <c r="U56" s="4">
+      <c r="U56" s="3">
         <v>18</v>
       </c>
       <c r="V56">
@@ -5235,12 +4621,12 @@
       <c r="W56">
         <v>1</v>
       </c>
-      <c r="X56" s="4">
-        <v>1</v>
-      </c>
-      <c r="AD56" s="4"/>
-    </row>
-    <row r="57" spans="1:21">
+      <c r="X56" s="3">
+        <v>1</v>
+      </c>
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="1:31">
       <c r="A57">
         <v>58</v>
       </c>
@@ -5262,13 +4648,13 @@
       <c r="I57" t="s">
         <v>49</v>
       </c>
-      <c r="J57" s="4">
+      <c r="J57" s="3">
         <v>3</v>
       </c>
       <c r="K57">
         <v>2</v>
       </c>
-      <c r="L57" s="4">
+      <c r="L57" s="3">
         <v>1</v>
       </c>
       <c r="M57">
@@ -5283,7 +4669,7 @@
       <c r="Q57">
         <v>5</v>
       </c>
-      <c r="R57" s="4">
+      <c r="R57" s="3">
         <v>6</v>
       </c>
       <c r="S57">
@@ -5292,11 +4678,11 @@
       <c r="T57">
         <v>5</v>
       </c>
-      <c r="U57" s="4">
+      <c r="U57" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:14">
+    <row r="58" spans="1:31">
       <c r="A58">
         <v>59</v>
       </c>
@@ -5321,7 +4707,7 @@
       <c r="K58">
         <v>3</v>
       </c>
-      <c r="L58" s="4">
+      <c r="L58" s="3">
         <v>2</v>
       </c>
       <c r="M58">
@@ -5331,7 +4717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:18">
+    <row r="59" spans="1:31">
       <c r="A59">
         <v>60</v>
       </c>
@@ -5356,7 +4742,7 @@
       <c r="K59">
         <v>4</v>
       </c>
-      <c r="L59" s="4">
+      <c r="L59" s="3">
         <v>3</v>
       </c>
       <c r="M59">
@@ -5371,11 +4757,11 @@
       <c r="Q59">
         <v>7</v>
       </c>
-      <c r="R59" s="4">
+      <c r="R59" s="3">
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:14">
+    <row r="60" spans="1:31">
       <c r="A60">
         <v>61</v>
       </c>
@@ -5400,7 +4786,7 @@
       <c r="K60">
         <v>2</v>
       </c>
-      <c r="L60" s="4">
+      <c r="L60" s="3">
         <v>2</v>
       </c>
       <c r="M60">
@@ -5410,7 +4796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:14">
+    <row r="61" spans="1:31">
       <c r="A61">
         <v>62</v>
       </c>
@@ -5429,13 +4815,13 @@
       <c r="I61" t="s">
         <v>49</v>
       </c>
-      <c r="J61" s="4">
+      <c r="J61" s="3">
         <v>14</v>
       </c>
       <c r="K61">
         <v>3</v>
       </c>
-      <c r="L61" s="4">
+      <c r="L61" s="3">
         <v>2</v>
       </c>
       <c r="M61">
@@ -5447,25 +4833,23 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I62"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.425" customWidth="1"/>
-    <col min="2" max="2" width="27.425" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
     <col min="4" max="4" width="33" customWidth="1"/>
-    <col min="5" max="5" width="19.2833333333333" customWidth="1"/>
-    <col min="6" max="6" width="18.8583333333333" customWidth="1"/>
-    <col min="7" max="8" width="10.2833333333333" customWidth="1"/>
-    <col min="9" max="9" width="15.1416666666667" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" customWidth="1"/>
+    <col min="7" max="8" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6789,26 +6173,24 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.425" customWidth="1"/>
-    <col min="2" max="2" width="27.425" customWidth="1"/>
-    <col min="3" max="3" width="14.425" customWidth="1"/>
-    <col min="4" max="5" width="16.1416666666667" customWidth="1"/>
-    <col min="6" max="6" width="12.425" customWidth="1"/>
-    <col min="7" max="7" width="14.425" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
+    <col min="4" max="5" width="16.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="10.1416666666667" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6859,7 +6241,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>0</v>
       </c>
@@ -6888,7 +6270,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>1</v>
       </c>
@@ -6911,7 +6293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>2</v>
       </c>
@@ -6928,7 +6310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:15">
       <c r="A5">
         <v>3</v>
       </c>
@@ -6963,7 +6345,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:15">
       <c r="A6">
         <v>4</v>
       </c>
@@ -6986,7 +6368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:15">
       <c r="A7">
         <v>5</v>
       </c>
@@ -7009,7 +6391,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:15">
       <c r="A8">
         <v>6</v>
       </c>
@@ -7032,7 +6414,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:15">
       <c r="A9">
         <v>7</v>
       </c>
@@ -7055,7 +6437,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:15">
       <c r="A10">
         <v>8</v>
       </c>
@@ -7078,7 +6460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:15">
       <c r="A11">
         <v>9</v>
       </c>
@@ -7107,7 +6489,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:15">
       <c r="A12">
         <v>10</v>
       </c>
@@ -7136,7 +6518,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:15">
       <c r="A13">
         <v>11</v>
       </c>
@@ -7159,7 +6541,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:15">
       <c r="A14">
         <v>12</v>
       </c>
@@ -7182,7 +6564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:15">
       <c r="A15">
         <v>13</v>
       </c>
@@ -7205,7 +6587,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:15">
       <c r="A16">
         <v>14</v>
       </c>
@@ -7274,7 +6656,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>17</v>
       </c>
@@ -7291,7 +6673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>18</v>
       </c>
@@ -7308,7 +6690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>19</v>
       </c>
@@ -7350,24 +6732,22 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85833333333333" customWidth="1"/>
-    <col min="2" max="2" width="22.7083333333333" customWidth="1"/>
-    <col min="3" max="3" width="28.5666666666667" customWidth="1"/>
-    <col min="4" max="4" width="15.5666666666667" customWidth="1"/>
-    <col min="5" max="5" width="16.1416666666667" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="11.1416666666667" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -7393,7 +6773,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -7413,7 +6793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="12.95" customHeight="1" spans="1:6">
+    <row r="3" spans="1:7" ht="12.95" customHeight="1">
       <c r="A3">
         <v>1</v>
       </c>
@@ -7430,7 +6810,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" ht="12.95" customHeight="1" spans="1:6">
+    <row r="4" spans="1:7" ht="12.95" customHeight="1">
       <c r="A4">
         <v>2</v>
       </c>
@@ -7447,7 +6827,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>3</v>
       </c>
@@ -7467,7 +6847,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>4</v>
       </c>
@@ -7487,7 +6867,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>5</v>
       </c>
@@ -7507,7 +6887,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>6</v>
       </c>
@@ -7527,7 +6907,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>7</v>
       </c>
@@ -7547,7 +6927,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>8</v>
       </c>
@@ -7567,7 +6947,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>9</v>
       </c>
@@ -7589,7 +6969,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Cards.xlsx
+++ b/Assets/StreamingAssets/Configurations/Cards.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{402544E3-79F5-492A-BE22-4EEB323B6A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="540" windowWidth="38730" windowHeight="20850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="24750" windowHeight="10480" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -30,6 +24,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -945,17 +941,167 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -974,8 +1120,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1001,9 +1333,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1018,27 +1592,71 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFFFFFFF"/>
-      <color rgb="FFAB0580"/>
-      <color rgb="FF00B050"/>
-      <color rgb="FFFFB200"/>
-      <color rgb="FF4B58FF"/>
-      <color rgb="FFFF2160"/>
+      <color rgb="00FFFFFF"/>
+      <color rgb="00AB0580"/>
+      <color rgb="0000B050"/>
+      <color rgb="00FFB200"/>
+      <color rgb="004B58FF"/>
+      <color rgb="00FF2160"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1296,48 +1914,48 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AG61"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="3.425" customWidth="1"/>
+    <col min="2" max="2" width="12.7083333333333" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="4.85546875" customWidth="1"/>
-    <col min="6" max="6" width="7.85546875" customWidth="1"/>
+    <col min="4" max="4" width="10.425" style="2" customWidth="1"/>
+    <col min="5" max="5" width="4.85833333333333" customWidth="1"/>
+    <col min="6" max="6" width="7.85833333333333" customWidth="1"/>
     <col min="7" max="7" width="5" customWidth="1"/>
-    <col min="8" max="8" width="5.5703125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="10.5703125" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" style="3" customWidth="1"/>
-    <col min="11" max="11" width="7.140625" customWidth="1"/>
+    <col min="8" max="8" width="5.56666666666667" style="3" customWidth="1"/>
+    <col min="9" max="9" width="10.5666666666667" customWidth="1"/>
+    <col min="10" max="10" width="9.70833333333333" style="3" customWidth="1"/>
+    <col min="11" max="11" width="7.14166666666667" customWidth="1"/>
     <col min="12" max="12" width="14" style="3" customWidth="1"/>
-    <col min="13" max="13" width="10.28515625" customWidth="1"/>
-    <col min="14" max="14" width="13.7109375" customWidth="1"/>
-    <col min="15" max="15" width="9.7109375" style="3" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="17" width="12.140625" customWidth="1"/>
-    <col min="18" max="18" width="17.7109375" style="3" customWidth="1"/>
+    <col min="13" max="13" width="10.2833333333333" customWidth="1"/>
+    <col min="14" max="14" width="13.7083333333333" customWidth="1"/>
+    <col min="15" max="15" width="9.70833333333333" style="3" customWidth="1"/>
+    <col min="16" max="16" width="9.70833333333333" customWidth="1"/>
+    <col min="17" max="17" width="12.1416666666667" customWidth="1"/>
+    <col min="18" max="18" width="17.7083333333333" style="3" customWidth="1"/>
     <col min="19" max="19" width="11" customWidth="1"/>
-    <col min="20" max="20" width="12.28515625" customWidth="1"/>
-    <col min="21" max="21" width="17.140625" style="3" customWidth="1"/>
-    <col min="24" max="24" width="17.7109375" style="3" customWidth="1"/>
-    <col min="25" max="25" width="10.7109375" customWidth="1"/>
+    <col min="20" max="20" width="12.2833333333333" customWidth="1"/>
+    <col min="21" max="21" width="17.1416666666667" style="3" customWidth="1"/>
+    <col min="24" max="24" width="17.7083333333333" style="3" customWidth="1"/>
+    <col min="25" max="25" width="10.7083333333333" customWidth="1"/>
     <col min="26" max="26" width="11" customWidth="1"/>
-    <col min="27" max="27" width="17.7109375" style="3" customWidth="1"/>
-    <col min="28" max="28" width="12.42578125" customWidth="1"/>
-    <col min="29" max="29" width="12.42578125" style="3" customWidth="1"/>
-    <col min="30" max="30" width="12.28515625" customWidth="1"/>
+    <col min="27" max="27" width="17.7083333333333" style="3" customWidth="1"/>
+    <col min="28" max="28" width="12.425" customWidth="1"/>
+    <col min="29" max="29" width="12.425" style="3" customWidth="1"/>
+    <col min="30" max="30" width="12.2833333333333" customWidth="1"/>
     <col min="31" max="31" width="9" style="3"/>
-    <col min="32" max="32" width="4.28515625" customWidth="1"/>
+    <col min="32" max="32" width="4.28333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33">
+    <row r="1" spans="1:32">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1435,7 +2053,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:33">
+    <row r="2" hidden="1" spans="1:32">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1487,7 +2105,7 @@
       <c r="AE2"/>
       <c r="AF2" s="5"/>
     </row>
-    <row r="3" spans="1:33">
+    <row r="3" hidden="1" spans="1:32">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1539,7 +2157,7 @@
       <c r="AE3"/>
       <c r="AF3" s="5"/>
     </row>
-    <row r="4" spans="1:33">
+    <row r="4" spans="1:32">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1593,7 +2211,7 @@
       </c>
       <c r="AF4" s="5"/>
     </row>
-    <row r="5" spans="1:33">
+    <row r="5" hidden="1" spans="1:32">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1653,7 +2271,7 @@
       <c r="AE5"/>
       <c r="AF5" s="5"/>
     </row>
-    <row r="6" spans="1:33">
+    <row r="6" spans="1:32">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1713,7 +2331,7 @@
       </c>
       <c r="AF6" s="5"/>
     </row>
-    <row r="7" spans="1:33">
+    <row r="7" hidden="1" spans="1:32">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1776,7 +2394,7 @@
       <c r="AE7"/>
       <c r="AF7" s="5"/>
     </row>
-    <row r="8" spans="1:33">
+    <row r="8" hidden="1" spans="1:32">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1846,7 +2464,7 @@
       <c r="AE8"/>
       <c r="AF8" s="5"/>
     </row>
-    <row r="9" spans="1:33">
+    <row r="9" hidden="1" spans="1:32">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1906,7 +2524,7 @@
       <c r="AE9"/>
       <c r="AF9" s="5"/>
     </row>
-    <row r="10" spans="1:33">
+    <row r="10" hidden="1" spans="1:32">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1966,7 +2584,7 @@
       <c r="AE10"/>
       <c r="AF10" s="5"/>
     </row>
-    <row r="11" spans="1:33">
+    <row r="11" spans="1:32">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2020,7 +2638,7 @@
       </c>
       <c r="AF11" s="5"/>
     </row>
-    <row r="12" spans="1:33">
+    <row r="12" hidden="1" spans="1:33">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2083,7 +2701,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:33">
+    <row r="13" hidden="1" spans="1:32">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2143,7 +2761,7 @@
       <c r="AE13"/>
       <c r="AF13" s="5"/>
     </row>
-    <row r="14" spans="1:33">
+    <row r="14" hidden="1" spans="1:32">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2195,7 +2813,7 @@
       <c r="AE14"/>
       <c r="AF14" s="5"/>
     </row>
-    <row r="15" spans="1:33">
+    <row r="15" hidden="1" spans="1:32">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2247,7 +2865,7 @@
       <c r="AE15"/>
       <c r="AF15" s="5"/>
     </row>
-    <row r="16" spans="1:33">
+    <row r="16" hidden="1" spans="1:32">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2299,7 +2917,7 @@
         <v>0.8</v>
       </c>
       <c r="U16" s="3">
-        <v>1.1000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="X16"/>
       <c r="AA16"/>
@@ -2307,7 +2925,7 @@
       <c r="AE16"/>
       <c r="AF16" s="5"/>
     </row>
-    <row r="17" spans="1:32">
+    <row r="17" hidden="1" spans="1:32">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2426,7 +3044,7 @@
       </c>
       <c r="AF18" s="5"/>
     </row>
-    <row r="19" spans="1:32">
+    <row r="19" hidden="1" spans="1:32">
       <c r="A19">
         <v>19</v>
       </c>
@@ -2603,7 +3221,7 @@
       </c>
       <c r="AF21" s="5"/>
     </row>
-    <row r="22" spans="1:32">
+    <row r="22" hidden="1" spans="1:32">
       <c r="A22">
         <v>22</v>
       </c>
@@ -2663,7 +3281,7 @@
       <c r="AE22"/>
       <c r="AF22" s="5"/>
     </row>
-    <row r="23" spans="1:32">
+    <row r="23" hidden="1" spans="1:32">
       <c r="A23">
         <v>23</v>
       </c>
@@ -2783,7 +3401,7 @@
       </c>
       <c r="AF24" s="5"/>
     </row>
-    <row r="25" spans="1:32">
+    <row r="25" hidden="1" spans="1:32">
       <c r="A25">
         <v>25</v>
       </c>
@@ -2835,7 +3453,7 @@
       <c r="AE25"/>
       <c r="AF25" s="5"/>
     </row>
-    <row r="26" spans="1:32">
+    <row r="26" hidden="1" spans="1:32">
       <c r="A26">
         <v>26</v>
       </c>
@@ -3012,7 +3630,7 @@
       </c>
       <c r="AF28" s="5"/>
     </row>
-    <row r="29" spans="1:32">
+    <row r="29" hidden="1" spans="1:32">
       <c r="A29">
         <v>30</v>
       </c>
@@ -3080,7 +3698,7 @@
       <c r="AE29"/>
       <c r="AF29" s="5"/>
     </row>
-    <row r="30" spans="1:32">
+    <row r="30" hidden="1" spans="1:32">
       <c r="A30">
         <v>31</v>
       </c>
@@ -3140,7 +3758,7 @@
       <c r="AE30"/>
       <c r="AF30" s="6"/>
     </row>
-    <row r="31" spans="1:32">
+    <row r="31" hidden="1" spans="1:32">
       <c r="A31">
         <v>32</v>
       </c>
@@ -3200,7 +3818,7 @@
       <c r="AE31"/>
       <c r="AF31" s="6"/>
     </row>
-    <row r="32" spans="1:32">
+    <row r="32" hidden="1" spans="1:31">
       <c r="A32">
         <v>33</v>
       </c>
@@ -3243,7 +3861,7 @@
       <c r="AC32"/>
       <c r="AE32"/>
     </row>
-    <row r="33" spans="1:31">
+    <row r="33" spans="1:29">
       <c r="A33">
         <v>34</v>
       </c>
@@ -3293,7 +3911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:31">
+    <row r="34" spans="1:18">
       <c r="A34">
         <v>35</v>
       </c>
@@ -3340,7 +3958,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:31">
+    <row r="35" spans="1:18">
       <c r="A35">
         <v>36</v>
       </c>
@@ -3384,7 +4002,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:31">
+    <row r="36" spans="1:21">
       <c r="A36">
         <v>37</v>
       </c>
@@ -3437,7 +4055,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:31">
+    <row r="37" hidden="1" spans="1:31">
       <c r="A37">
         <v>38</v>
       </c>
@@ -3496,7 +4114,7 @@
       <c r="AC37"/>
       <c r="AE37"/>
     </row>
-    <row r="38" spans="1:31">
+    <row r="38" hidden="1" spans="1:31">
       <c r="A38">
         <v>39</v>
       </c>
@@ -3555,7 +4173,7 @@
       <c r="AC38"/>
       <c r="AE38"/>
     </row>
-    <row r="39" spans="1:31">
+    <row r="39" hidden="1" spans="1:31">
       <c r="A39">
         <v>40</v>
       </c>
@@ -3614,7 +4232,7 @@
       <c r="AC39"/>
       <c r="AE39"/>
     </row>
-    <row r="40" spans="1:31">
+    <row r="40" hidden="1" spans="1:31">
       <c r="A40">
         <v>41</v>
       </c>
@@ -3673,7 +4291,7 @@
       <c r="AC40"/>
       <c r="AE40"/>
     </row>
-    <row r="41" spans="1:31">
+    <row r="41" hidden="1" spans="1:31">
       <c r="A41">
         <v>42</v>
       </c>
@@ -3732,7 +4350,7 @@
       <c r="AC41"/>
       <c r="AE41"/>
     </row>
-    <row r="42" spans="1:31">
+    <row r="42" hidden="1" spans="1:31">
       <c r="A42">
         <v>43</v>
       </c>
@@ -3791,7 +4409,7 @@
       <c r="AC42"/>
       <c r="AE42"/>
     </row>
-    <row r="43" spans="1:31">
+    <row r="43" hidden="1" spans="1:31">
       <c r="A43">
         <v>44</v>
       </c>
@@ -3858,7 +4476,7 @@
       <c r="AC43"/>
       <c r="AE43"/>
     </row>
-    <row r="44" spans="1:31">
+    <row r="44" spans="1:21">
       <c r="A44">
         <v>45</v>
       </c>
@@ -3911,7 +4529,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:31">
+    <row r="45" hidden="1" spans="1:31">
       <c r="A45">
         <v>46</v>
       </c>
@@ -3978,7 +4596,7 @@
       <c r="AC45"/>
       <c r="AE45"/>
     </row>
-    <row r="46" spans="1:31">
+    <row r="46" hidden="1" spans="1:31">
       <c r="A46">
         <v>47</v>
       </c>
@@ -4045,7 +4663,7 @@
       <c r="AC46"/>
       <c r="AE46"/>
     </row>
-    <row r="47" spans="1:31">
+    <row r="47" hidden="1" spans="1:31">
       <c r="A47">
         <v>48</v>
       </c>
@@ -4096,7 +4714,7 @@
       <c r="AC47"/>
       <c r="AE47"/>
     </row>
-    <row r="48" spans="1:31">
+    <row r="48" hidden="1" spans="1:31">
       <c r="A48">
         <v>49</v>
       </c>
@@ -4155,7 +4773,7 @@
       <c r="AC48"/>
       <c r="AE48"/>
     </row>
-    <row r="49" spans="1:31">
+    <row r="49" spans="1:21">
       <c r="A49">
         <v>50</v>
       </c>
@@ -4208,7 +4826,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:31">
+    <row r="50" hidden="1" spans="1:31">
       <c r="A50">
         <v>51</v>
       </c>
@@ -4257,7 +4875,7 @@
         <v>18</v>
       </c>
       <c r="T50">
-        <v>1.1000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="U50" s="3">
         <v>1.7</v>
@@ -4267,7 +4885,7 @@
       <c r="AC50"/>
       <c r="AE50"/>
     </row>
-    <row r="51" spans="1:31">
+    <row r="51" hidden="1" spans="1:31">
       <c r="A51">
         <v>52</v>
       </c>
@@ -4326,7 +4944,7 @@
       <c r="AC51"/>
       <c r="AE51"/>
     </row>
-    <row r="52" spans="1:31">
+    <row r="52" hidden="1" spans="1:31">
       <c r="A52">
         <v>53</v>
       </c>
@@ -4385,7 +5003,7 @@
       <c r="AC52"/>
       <c r="AE52"/>
     </row>
-    <row r="53" spans="1:31">
+    <row r="53" spans="1:21">
       <c r="A53">
         <v>54</v>
       </c>
@@ -4441,7 +5059,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="54" spans="1:31">
+    <row r="54" spans="1:24">
       <c r="A54">
         <v>55</v>
       </c>
@@ -4506,7 +5124,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:31">
+    <row r="55" spans="1:30">
       <c r="A55">
         <v>56</v>
       </c>
@@ -4560,7 +5178,7 @@
       </c>
       <c r="AD55" s="3"/>
     </row>
-    <row r="56" spans="1:31">
+    <row r="56" spans="1:30">
       <c r="A56">
         <v>57</v>
       </c>
@@ -4626,7 +5244,7 @@
       </c>
       <c r="AD56" s="3"/>
     </row>
-    <row r="57" spans="1:31">
+    <row r="57" spans="1:21">
       <c r="A57">
         <v>58</v>
       </c>
@@ -4682,7 +5300,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:31">
+    <row r="58" spans="1:14">
       <c r="A58">
         <v>59</v>
       </c>
@@ -4717,7 +5335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:31">
+    <row r="59" spans="1:18">
       <c r="A59">
         <v>60</v>
       </c>
@@ -4761,7 +5379,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:31">
+    <row r="60" spans="1:14">
       <c r="A60">
         <v>61</v>
       </c>
@@ -4796,7 +5414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:31">
+    <row r="61" hidden="1" spans="1:14">
       <c r="A61">
         <v>62</v>
       </c>
@@ -4832,24 +5450,34 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AG61" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="C"/>
+      </filters>
+    </filterColumn>
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I62"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.42578125" customWidth="1"/>
+    <col min="1" max="1" width="3.425" customWidth="1"/>
+    <col min="2" max="2" width="27.425" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
     <col min="4" max="4" width="33" customWidth="1"/>
-    <col min="5" max="5" width="19.28515625" customWidth="1"/>
-    <col min="6" max="6" width="18.85546875" customWidth="1"/>
-    <col min="7" max="8" width="10.28515625" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" customWidth="1"/>
+    <col min="5" max="5" width="19.2833333333333" customWidth="1"/>
+    <col min="6" max="6" width="18.8583333333333" customWidth="1"/>
+    <col min="7" max="8" width="10.2833333333333" customWidth="1"/>
+    <col min="9" max="9" width="15.1416666666667" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6173,24 +6801,26 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:O22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.42578125" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" customWidth="1"/>
-    <col min="4" max="5" width="16.140625" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" customWidth="1"/>
+    <col min="1" max="1" width="9.425" customWidth="1"/>
+    <col min="2" max="2" width="27.425" customWidth="1"/>
+    <col min="3" max="3" width="14.425" customWidth="1"/>
+    <col min="4" max="5" width="16.1416666666667" customWidth="1"/>
+    <col min="6" max="6" width="12.425" customWidth="1"/>
+    <col min="7" max="7" width="14.425" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="10.140625" customWidth="1"/>
+    <col min="10" max="10" width="10.1416666666667" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6241,7 +6871,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:9">
       <c r="A2">
         <v>0</v>
       </c>
@@ -6270,7 +6900,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
@@ -6293,7 +6923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>2</v>
       </c>
@@ -6310,7 +6940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>3</v>
       </c>
@@ -6345,7 +6975,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>4</v>
       </c>
@@ -6368,7 +6998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>5</v>
       </c>
@@ -6391,7 +7021,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>6</v>
       </c>
@@ -6414,7 +7044,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>7</v>
       </c>
@@ -6437,7 +7067,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>8</v>
       </c>
@@ -6460,7 +7090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:9">
       <c r="A11">
         <v>9</v>
       </c>
@@ -6489,7 +7119,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:9">
       <c r="A12">
         <v>10</v>
       </c>
@@ -6518,7 +7148,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>11</v>
       </c>
@@ -6541,7 +7171,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>12</v>
       </c>
@@ -6564,7 +7194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>13</v>
       </c>
@@ -6587,7 +7217,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>14</v>
       </c>
@@ -6656,7 +7286,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>17</v>
       </c>
@@ -6673,7 +7303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>18</v>
       </c>
@@ -6690,7 +7320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>19</v>
       </c>
@@ -6732,22 +7362,24 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.85833333333333" customWidth="1"/>
+    <col min="2" max="2" width="22.7083333333333" customWidth="1"/>
+    <col min="3" max="3" width="28.5666666666667" customWidth="1"/>
+    <col min="4" max="4" width="15.5666666666667" customWidth="1"/>
+    <col min="5" max="5" width="16.1416666666667" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" customWidth="1"/>
+    <col min="7" max="7" width="11.1416666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -6773,7 +7405,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>0</v>
       </c>
@@ -6793,7 +7425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="12.95" customHeight="1">
+    <row r="3" ht="12.95" customHeight="1" spans="1:6">
       <c r="A3">
         <v>1</v>
       </c>
@@ -6810,7 +7442,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="12.95" customHeight="1">
+    <row r="4" ht="12.95" customHeight="1" spans="1:6">
       <c r="A4">
         <v>2</v>
       </c>
@@ -6827,7 +7459,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>3</v>
       </c>
@@ -6847,7 +7479,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>4</v>
       </c>
@@ -6867,7 +7499,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>5</v>
       </c>
@@ -6887,7 +7519,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>6</v>
       </c>
@@ -6907,7 +7539,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>7</v>
       </c>
@@ -6927,7 +7559,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>8</v>
       </c>
@@ -6947,7 +7579,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>9</v>
       </c>
@@ -6969,6 +7601,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Cards.xlsx
+++ b/Assets/StreamingAssets/Configurations/Cards.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" activeTab="1"/>
+    <workbookView windowWidth="24750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,7 @@
     <sheet name="Conditions" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cards!$A$1:$AG$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cards!$A$1:$AH$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="318">
   <si>
     <t>ID</t>
   </si>
@@ -44,6 +44,9 @@
     <t>Description</t>
   </si>
   <si>
+    <t>DescriptionInGame</t>
+  </si>
+  <si>
     <t>Rarity</t>
   </si>
   <si>
@@ -137,6 +140,9 @@
     <t>参数+7</t>
   </si>
   <si>
+    <t>参数+X1$1212</t>
+  </si>
+  <si>
     <t>Common</t>
   </si>
   <si>
@@ -155,6 +161,9 @@
     <t>神采+4</t>
   </si>
   <si>
+    <t>神采+X1</t>
+  </si>
+  <si>
     <t>M</t>
   </si>
   <si>
@@ -164,6 +173,9 @@
     <t>参数+15，红温大于10层时，参数+9</t>
   </si>
   <si>
+    <t>参数+X1，红温大于10层时，参数+X2</t>
+  </si>
+  <si>
     <t>C</t>
   </si>
   <si>
@@ -173,12 +185,18 @@
     <t>参数+5，神采+4</t>
   </si>
   <si>
+    <t>参数+X1，神采+X2</t>
+  </si>
+  <si>
     <t>kale</t>
   </si>
   <si>
     <t>下一张使用的牌会使用两次，抽一张卡,神采+2</t>
   </si>
   <si>
+    <t>下一张使用的牌会使用两次，抽X3张卡,神采+X2</t>
+  </si>
+  <si>
     <t>Epic</t>
   </si>
   <si>
@@ -191,12 +209,18 @@
     <t>重抽其他手牌，卡牌使用次数+1，体力消耗减少50%+2回合</t>
   </si>
   <si>
+    <t>重抽其他手牌，卡牌使用次数+X3，体力消耗减少50%+X2回合</t>
+  </si>
+  <si>
     <t>才八点</t>
   </si>
   <si>
     <t>获得一个额外回合，神采+7，出牌次数+1</t>
   </si>
   <si>
+    <t>获得一个额外回合，神采+X1，出牌次数+X2</t>
+  </si>
+  <si>
     <t>I</t>
   </si>
   <si>
@@ -206,24 +230,36 @@
     <t>亲和力+3，神采+2</t>
   </si>
   <si>
+    <t>亲和力+X1，神采+X2</t>
+  </si>
+  <si>
     <t>集中</t>
   </si>
   <si>
     <t>专注+2，神采+2</t>
   </si>
   <si>
+    <t>专注+X1，神采+X2</t>
+  </si>
+  <si>
     <t>生气</t>
   </si>
   <si>
     <t>红温+2，神采+2</t>
   </si>
   <si>
+    <t>红温+X1，神采+X2</t>
+  </si>
+  <si>
     <t>二次推流</t>
   </si>
   <si>
     <t>参数+9/2次</t>
   </si>
   <si>
+    <t>参数+X1/2次</t>
+  </si>
+  <si>
     <t>加分动画显示需改进</t>
   </si>
   <si>
@@ -242,22 +278,37 @@
     <t>亲和力+6</t>
   </si>
   <si>
+    <t>亲和力+X1</t>
+  </si>
+  <si>
     <t>饭撒</t>
   </si>
   <si>
     <t>获得亲和力140%的参数</t>
   </si>
   <si>
+    <t>获得亲和力X1的参数</t>
+  </si>
+  <si>
     <t>desuwa</t>
   </si>
   <si>
     <t>亲和力+4，获得亲和力层数80%的参数</t>
   </si>
   <si>
+    <t>亲和力+X1，获得亲和力层数X2的参数</t>
+  </si>
+  <si>
     <t>欢迎上舰</t>
   </si>
   <si>
     <t>舰长+1，神采+4，体力消耗减少+2回合</t>
+  </si>
+  <si>
+    <t>舰长+X1，神采+X2，体力消耗减少+X3回合</t>
+  </si>
+  <si>
+    <t>W</t>
   </si>
   <si>
     <t>攻击弹幕</t>
@@ -1101,7 +1152,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1279,12 +1330,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1566,16 +1611,16 @@
     <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1919,43 +1964,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:AG61"/>
+  <sheetPr/>
+  <dimension ref="A1:AH61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
     <col min="2" max="2" width="12.7083333333333" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
-    <col min="4" max="4" width="10.425" style="2" customWidth="1"/>
-    <col min="5" max="5" width="4.85833333333333" customWidth="1"/>
-    <col min="6" max="6" width="7.85833333333333" customWidth="1"/>
-    <col min="7" max="7" width="5" customWidth="1"/>
-    <col min="8" max="8" width="5.56666666666667" style="3" customWidth="1"/>
-    <col min="9" max="9" width="10.5666666666667" customWidth="1"/>
-    <col min="10" max="10" width="9.70833333333333" style="3" customWidth="1"/>
-    <col min="11" max="11" width="7.14166666666667" customWidth="1"/>
-    <col min="12" max="12" width="14" style="3" customWidth="1"/>
-    <col min="13" max="13" width="10.2833333333333" customWidth="1"/>
-    <col min="14" max="14" width="13.7083333333333" customWidth="1"/>
-    <col min="15" max="15" width="9.70833333333333" style="3" customWidth="1"/>
-    <col min="16" max="16" width="9.70833333333333" customWidth="1"/>
-    <col min="17" max="17" width="12.1416666666667" customWidth="1"/>
-    <col min="18" max="18" width="17.7083333333333" style="3" customWidth="1"/>
-    <col min="19" max="19" width="11" customWidth="1"/>
-    <col min="20" max="20" width="12.2833333333333" customWidth="1"/>
-    <col min="21" max="21" width="17.1416666666667" style="3" customWidth="1"/>
-    <col min="24" max="24" width="17.7083333333333" style="3" customWidth="1"/>
-    <col min="25" max="25" width="10.7083333333333" customWidth="1"/>
-    <col min="26" max="26" width="11" customWidth="1"/>
-    <col min="27" max="27" width="17.7083333333333" style="3" customWidth="1"/>
-    <col min="28" max="28" width="12.425" customWidth="1"/>
-    <col min="29" max="29" width="12.425" style="3" customWidth="1"/>
-    <col min="30" max="30" width="12.2833333333333" customWidth="1"/>
-    <col min="31" max="31" width="9" style="3"/>
-    <col min="32" max="32" width="4.28333333333333" customWidth="1"/>
+    <col min="4" max="4" width="57.7083333333333" customWidth="1"/>
+    <col min="5" max="5" width="10.425" style="2" customWidth="1"/>
+    <col min="6" max="6" width="4.85833333333333" customWidth="1"/>
+    <col min="7" max="7" width="7.85833333333333" customWidth="1"/>
+    <col min="8" max="8" width="5" customWidth="1"/>
+    <col min="9" max="9" width="5.56666666666667" style="3" customWidth="1"/>
+    <col min="10" max="10" width="10.5666666666667" customWidth="1"/>
+    <col min="11" max="11" width="9.70833333333333" style="3" customWidth="1"/>
+    <col min="12" max="12" width="7.14166666666667" customWidth="1"/>
+    <col min="13" max="13" width="14" style="3" customWidth="1"/>
+    <col min="14" max="14" width="10.2833333333333" customWidth="1"/>
+    <col min="15" max="15" width="13.7083333333333" customWidth="1"/>
+    <col min="16" max="16" width="9.70833333333333" style="3" customWidth="1"/>
+    <col min="17" max="17" width="9.70833333333333" customWidth="1"/>
+    <col min="18" max="18" width="12.1416666666667" customWidth="1"/>
+    <col min="19" max="19" width="17.7083333333333" style="3" customWidth="1"/>
+    <col min="20" max="20" width="11" customWidth="1"/>
+    <col min="21" max="21" width="12.2833333333333" customWidth="1"/>
+    <col min="22" max="22" width="17.1416666666667" style="3" customWidth="1"/>
+    <col min="25" max="25" width="17.7083333333333" style="3" customWidth="1"/>
+    <col min="26" max="26" width="10.7083333333333" customWidth="1"/>
+    <col min="27" max="27" width="11" customWidth="1"/>
+    <col min="28" max="28" width="17.7083333333333" style="3" customWidth="1"/>
+    <col min="29" max="29" width="12.425" customWidth="1"/>
+    <col min="30" max="30" width="12.425" style="3" customWidth="1"/>
+    <col min="31" max="31" width="12.2833333333333" customWidth="1"/>
+    <col min="32" max="32" width="9" style="3"/>
+    <col min="33" max="33" width="4.28333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32">
+    <row r="1" spans="1:33">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1965,10 +2011,10 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -1977,2032 +2023,2140 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
       <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="X1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AA1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AC1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AD1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AE1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AF1" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" hidden="1" spans="1:32">
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D2" t="s">
         <v>35</v>
       </c>
+      <c r="E2" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="F2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2"/>
+      <c r="L2" s="2">
+        <v>4</v>
+      </c>
+      <c r="M2" s="3">
+        <v>3</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2"/>
+      <c r="Q2" s="2">
+        <v>11</v>
+      </c>
+      <c r="R2">
+        <v>7</v>
+      </c>
+      <c r="S2" s="3">
+        <v>7</v>
+      </c>
+      <c r="V2"/>
+      <c r="Y2"/>
+      <c r="AB2"/>
+      <c r="AD2"/>
+      <c r="AF2"/>
+      <c r="AG2" s="5"/>
+    </row>
+    <row r="3" spans="1:33">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="I2" t="s">
+      <c r="F3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K3"/>
+      <c r="L3" s="2">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3"/>
+      <c r="Q3" s="2">
+        <v>2</v>
+      </c>
+      <c r="R3">
+        <v>4</v>
+      </c>
+      <c r="S3" s="3">
+        <v>4</v>
+      </c>
+      <c r="V3"/>
+      <c r="Y3"/>
+      <c r="AB3"/>
+      <c r="AD3"/>
+      <c r="AF3"/>
+      <c r="AG3" s="5"/>
+    </row>
+    <row r="4" spans="1:33">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" t="s">
         <v>37</v>
       </c>
-      <c r="J2"/>
-      <c r="K2" s="2">
+      <c r="G4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L4">
+        <v>5</v>
+      </c>
+      <c r="M4" s="3">
         <v>4</v>
       </c>
-      <c r="L2" s="3">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2"/>
-      <c r="P2" s="2">
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2">
         <v>11</v>
       </c>
-      <c r="Q2">
-        <v>7</v>
-      </c>
-      <c r="R2" s="3">
-        <v>7</v>
-      </c>
-      <c r="U2"/>
-      <c r="X2"/>
-      <c r="AA2"/>
-      <c r="AC2"/>
-      <c r="AE2"/>
-      <c r="AF2" s="5"/>
-    </row>
-    <row r="3" hidden="1" spans="1:32">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J3"/>
-      <c r="K3" s="2">
-        <v>0</v>
-      </c>
-      <c r="L3" s="3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3"/>
-      <c r="P3" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q3">
-        <v>4</v>
-      </c>
-      <c r="R3" s="3">
-        <v>4</v>
-      </c>
-      <c r="U3"/>
-      <c r="X3"/>
-      <c r="AA3"/>
-      <c r="AC3"/>
-      <c r="AE3"/>
-      <c r="AF3" s="5"/>
-    </row>
-    <row r="4" spans="1:32">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" t="s">
-        <v>43</v>
-      </c>
-      <c r="I4" t="s">
-        <v>37</v>
-      </c>
-      <c r="K4">
-        <v>5</v>
-      </c>
-      <c r="L4" s="3">
-        <v>4</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="P4" s="2">
-        <v>11</v>
-      </c>
-      <c r="Q4">
+      <c r="R4">
         <v>15</v>
       </c>
-      <c r="R4" s="3">
+      <c r="S4" s="3">
         <v>18</v>
       </c>
-      <c r="S4">
+      <c r="T4">
         <v>56</v>
       </c>
-      <c r="T4">
+      <c r="U4">
         <v>9</v>
       </c>
-      <c r="U4" s="3">
+      <c r="V4" s="3">
         <v>12</v>
       </c>
-      <c r="AF4" s="5"/>
-    </row>
-    <row r="5" hidden="1" spans="1:32">
+      <c r="AG4" s="5"/>
+    </row>
+    <row r="5" spans="1:33">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" t="s">
-        <v>35</v>
+        <v>49</v>
+      </c>
+      <c r="D5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5" t="s">
         <v>37</v>
       </c>
-      <c r="J5"/>
-      <c r="K5" s="2">
+      <c r="G5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5"/>
+      <c r="L5" s="2">
         <v>3</v>
       </c>
-      <c r="L5" s="3">
+      <c r="M5" s="3">
         <v>3</v>
       </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
       <c r="N5">
         <v>0</v>
       </c>
-      <c r="O5"/>
-      <c r="P5" s="2">
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5"/>
+      <c r="Q5" s="2">
         <v>11</v>
       </c>
-      <c r="Q5">
+      <c r="R5">
         <v>5</v>
       </c>
-      <c r="R5" s="3">
+      <c r="S5" s="3">
         <v>5</v>
       </c>
-      <c r="S5" s="2">
-        <v>2</v>
-      </c>
-      <c r="T5">
-        <v>2</v>
-      </c>
-      <c r="U5" s="3">
-        <v>2</v>
-      </c>
-      <c r="X5"/>
-      <c r="AA5"/>
-      <c r="AC5"/>
-      <c r="AE5"/>
-      <c r="AF5" s="5"/>
-    </row>
-    <row r="6" spans="1:32">
+      <c r="T5" s="2">
+        <v>2</v>
+      </c>
+      <c r="U5">
+        <v>2</v>
+      </c>
+      <c r="V5" s="3">
+        <v>2</v>
+      </c>
+      <c r="Y5"/>
+      <c r="AB5"/>
+      <c r="AD5"/>
+      <c r="AF5"/>
+      <c r="AG5" s="5"/>
+    </row>
+    <row r="6" spans="1:33">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" t="s">
-        <v>40</v>
+        <v>52</v>
+      </c>
+      <c r="D6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="F6" t="s">
         <v>43</v>
       </c>
-      <c r="I6" t="s">
-        <v>49</v>
-      </c>
-      <c r="J6" s="3">
+      <c r="G6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J6" t="s">
+        <v>55</v>
+      </c>
+      <c r="K6" s="3">
         <v>3</v>
       </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6" s="3">
-        <v>1</v>
-      </c>
-      <c r="M6">
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6" s="3">
         <v>1</v>
       </c>
       <c r="N6">
         <v>1</v>
       </c>
-      <c r="P6" s="2">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>2</v>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>0</v>
       </c>
       <c r="T6">
         <v>2</v>
       </c>
-      <c r="U6" s="3">
+      <c r="U6">
+        <v>2</v>
+      </c>
+      <c r="V6" s="3">
         <v>7</v>
       </c>
-      <c r="V6">
+      <c r="W6">
         <v>9</v>
       </c>
-      <c r="W6">
-        <v>1</v>
-      </c>
-      <c r="X6" s="3">
-        <v>1</v>
-      </c>
-      <c r="AF6" s="5"/>
-    </row>
-    <row r="7" hidden="1" spans="1:32">
+      <c r="X6">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG6" s="5"/>
+    </row>
+    <row r="7" spans="1:33">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" t="s">
-        <v>40</v>
+        <v>57</v>
+      </c>
+      <c r="D7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
-      </c>
-      <c r="I7" t="s">
-        <v>37</v>
-      </c>
-      <c r="J7"/>
-      <c r="K7" s="2">
+        <v>43</v>
+      </c>
+      <c r="G7" t="s">
+        <v>38</v>
+      </c>
+      <c r="J7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K7"/>
+      <c r="L7" s="2">
         <v>5</v>
       </c>
-      <c r="L7" s="3">
+      <c r="M7" s="3">
         <v>4</v>
       </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
       <c r="N7">
         <v>1</v>
       </c>
-      <c r="O7"/>
-      <c r="P7" s="2">
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7"/>
+      <c r="Q7" s="2">
         <v>4</v>
       </c>
-      <c r="R7"/>
-      <c r="S7" s="2">
+      <c r="S7"/>
+      <c r="T7" s="2">
         <v>21</v>
       </c>
-      <c r="T7">
-        <v>2</v>
-      </c>
-      <c r="U7" s="3">
-        <v>2</v>
-      </c>
-      <c r="V7" s="2">
+      <c r="U7">
+        <v>2</v>
+      </c>
+      <c r="V7" s="3">
+        <v>2</v>
+      </c>
+      <c r="W7" s="2">
         <v>14</v>
       </c>
-      <c r="W7">
-        <v>1</v>
-      </c>
-      <c r="X7" s="3">
-        <v>1</v>
-      </c>
-      <c r="AA7"/>
-      <c r="AC7"/>
-      <c r="AE7"/>
-      <c r="AF7" s="5"/>
-    </row>
-    <row r="8" hidden="1" spans="1:32">
+      <c r="X7">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB7"/>
+      <c r="AD7"/>
+      <c r="AF7"/>
+      <c r="AG7" s="5"/>
+    </row>
+    <row r="8" spans="1:33">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" t="s">
-        <v>40</v>
+        <v>60</v>
+      </c>
+      <c r="D8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
-      </c>
-      <c r="I8" t="s">
-        <v>49</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8" s="2">
-        <v>1</v>
-      </c>
-      <c r="L8" s="3">
-        <v>1</v>
-      </c>
-      <c r="M8">
+        <v>43</v>
+      </c>
+      <c r="G8" t="s">
+        <v>62</v>
+      </c>
+      <c r="J8" t="s">
+        <v>55</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2">
+        <v>1</v>
+      </c>
+      <c r="M8" s="3">
         <v>1</v>
       </c>
       <c r="N8">
         <v>1</v>
       </c>
-      <c r="O8"/>
-      <c r="P8" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q8">
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8"/>
+      <c r="Q8" s="2">
+        <v>2</v>
+      </c>
+      <c r="R8">
         <v>7</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7</v>
       </c>
-      <c r="S8" s="2">
+      <c r="T8" s="2">
         <v>3</v>
       </c>
-      <c r="T8">
-        <v>1</v>
-      </c>
-      <c r="U8" s="3">
-        <v>1</v>
-      </c>
-      <c r="V8" s="2">
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8" s="3">
+        <v>1</v>
+      </c>
+      <c r="W8" s="2">
         <v>14</v>
       </c>
-      <c r="W8">
-        <v>1</v>
-      </c>
-      <c r="X8" s="3">
-        <v>1</v>
-      </c>
-      <c r="AA8"/>
-      <c r="AC8"/>
-      <c r="AE8"/>
-      <c r="AF8" s="5"/>
-    </row>
-    <row r="9" hidden="1" spans="1:32">
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB8"/>
+      <c r="AD8"/>
+      <c r="AF8"/>
+      <c r="AG8" s="5"/>
+    </row>
+    <row r="9" spans="1:33">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" t="s">
-        <v>40</v>
+        <v>64</v>
+      </c>
+      <c r="D9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>35</v>
-      </c>
-      <c r="I9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" t="s">
         <v>37</v>
       </c>
-      <c r="J9"/>
-      <c r="K9" s="2">
-        <v>2</v>
-      </c>
-      <c r="L9" s="3">
-        <v>2</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
+      <c r="J9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K9"/>
+      <c r="L9" s="2">
+        <v>2</v>
+      </c>
+      <c r="M9" s="3">
+        <v>2</v>
       </c>
       <c r="N9">
         <v>0</v>
       </c>
-      <c r="O9"/>
-      <c r="P9" s="2">
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9"/>
+      <c r="Q9" s="2">
         <v>6</v>
       </c>
-      <c r="Q9">
+      <c r="R9">
         <v>3</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4</v>
       </c>
-      <c r="S9" s="2">
-        <v>2</v>
-      </c>
-      <c r="T9">
+      <c r="T9" s="2">
+        <v>2</v>
+      </c>
+      <c r="U9">
         <v>3</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4</v>
       </c>
-      <c r="X9"/>
-      <c r="AA9"/>
-      <c r="AC9"/>
-      <c r="AE9"/>
-      <c r="AF9" s="5"/>
-    </row>
-    <row r="10" hidden="1" spans="1:32">
+      <c r="Y9"/>
+      <c r="AB9"/>
+      <c r="AD9"/>
+      <c r="AF9"/>
+      <c r="AG9" s="5"/>
+    </row>
+    <row r="10" spans="1:33">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" t="s">
-        <v>40</v>
+        <v>67</v>
+      </c>
+      <c r="D10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
-      </c>
-      <c r="I10" t="s">
-        <v>37</v>
-      </c>
-      <c r="J10"/>
-      <c r="K10" s="2">
-        <v>2</v>
-      </c>
-      <c r="L10" s="3">
-        <v>2</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="G10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J10" t="s">
+        <v>39</v>
+      </c>
+      <c r="K10"/>
+      <c r="L10" s="2">
+        <v>2</v>
+      </c>
+      <c r="M10" s="3">
+        <v>2</v>
       </c>
       <c r="N10">
         <v>0</v>
       </c>
-      <c r="O10"/>
-      <c r="P10" s="2">
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10"/>
+      <c r="Q10" s="2">
         <v>7</v>
       </c>
-      <c r="Q10">
-        <v>2</v>
-      </c>
-      <c r="R10" s="3">
+      <c r="R10">
+        <v>2</v>
+      </c>
+      <c r="S10" s="3">
         <v>3</v>
       </c>
-      <c r="S10" s="2">
-        <v>2</v>
-      </c>
-      <c r="T10">
-        <v>2</v>
-      </c>
-      <c r="U10" s="3">
+      <c r="T10" s="2">
+        <v>2</v>
+      </c>
+      <c r="U10">
+        <v>2</v>
+      </c>
+      <c r="V10" s="3">
         <v>3</v>
       </c>
-      <c r="X10"/>
-      <c r="AA10"/>
-      <c r="AC10"/>
-      <c r="AE10"/>
-      <c r="AF10" s="5"/>
-    </row>
-    <row r="11" spans="1:32">
+      <c r="Y10"/>
+      <c r="AB10"/>
+      <c r="AD10"/>
+      <c r="AF10"/>
+      <c r="AG10" s="5"/>
+    </row>
+    <row r="11" spans="1:33">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" t="s">
-        <v>40</v>
+        <v>70</v>
+      </c>
+      <c r="D11" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="F11" t="s">
         <v>43</v>
       </c>
-      <c r="I11" t="s">
-        <v>37</v>
-      </c>
-      <c r="K11">
-        <v>2</v>
-      </c>
-      <c r="L11" s="3">
-        <v>2</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
+      <c r="G11" t="s">
+        <v>47</v>
+      </c>
+      <c r="J11" t="s">
+        <v>39</v>
+      </c>
+      <c r="L11">
+        <v>2</v>
+      </c>
+      <c r="M11" s="3">
+        <v>2</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
-      <c r="P11" s="2">
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="2">
         <v>15</v>
       </c>
-      <c r="Q11">
-        <v>2</v>
-      </c>
-      <c r="R11" s="3">
+      <c r="R11">
+        <v>2</v>
+      </c>
+      <c r="S11" s="3">
         <v>3</v>
       </c>
-      <c r="S11" s="2">
-        <v>2</v>
-      </c>
-      <c r="T11">
-        <v>2</v>
-      </c>
-      <c r="U11" s="3">
+      <c r="T11" s="2">
+        <v>2</v>
+      </c>
+      <c r="U11">
+        <v>2</v>
+      </c>
+      <c r="V11" s="3">
         <v>3</v>
       </c>
-      <c r="AF11" s="5"/>
-    </row>
-    <row r="12" hidden="1" spans="1:33">
+      <c r="AG11" s="5"/>
+    </row>
+    <row r="12" spans="1:34">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" t="s">
         <v>62</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" t="s">
-        <v>35</v>
-      </c>
-      <c r="F12" t="s">
-        <v>54</v>
-      </c>
-      <c r="I12" t="s">
-        <v>37</v>
-      </c>
-      <c r="J12"/>
-      <c r="K12" s="2">
+      <c r="J12" t="s">
+        <v>39</v>
+      </c>
+      <c r="K12"/>
+      <c r="L12" s="2">
         <v>6</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>6</v>
       </c>
-      <c r="M12">
-        <v>1</v>
-      </c>
       <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12"/>
-      <c r="P12" s="2">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12"/>
+      <c r="Q12" s="2">
         <v>11</v>
       </c>
-      <c r="Q12">
+      <c r="R12">
         <v>9</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>13</v>
       </c>
-      <c r="S12" s="2">
+      <c r="T12" s="2">
         <v>11</v>
       </c>
-      <c r="T12">
+      <c r="U12">
         <v>9</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>13</v>
       </c>
-      <c r="X12"/>
-      <c r="AA12"/>
-      <c r="AC12"/>
-      <c r="AE12"/>
-      <c r="AF12" s="5"/>
-      <c r="AG12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" hidden="1" spans="1:32">
+      <c r="Y12"/>
+      <c r="AB12"/>
+      <c r="AD12"/>
+      <c r="AF12"/>
+      <c r="AG12" s="5"/>
+      <c r="AH12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E13" t="s">
-        <v>35</v>
+        <v>77</v>
+      </c>
+      <c r="D13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="F13" t="s">
-        <v>36</v>
-      </c>
-      <c r="I13" t="s">
         <v>37</v>
       </c>
-      <c r="J13"/>
-      <c r="K13" s="2">
+      <c r="G13" t="s">
+        <v>38</v>
+      </c>
+      <c r="J13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K13"/>
+      <c r="L13" s="2">
         <v>5</v>
       </c>
-      <c r="L13" s="3">
+      <c r="M13" s="3">
         <v>5</v>
       </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
       <c r="N13">
         <v>0</v>
       </c>
-      <c r="O13"/>
-      <c r="P13" s="2">
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13"/>
+      <c r="Q13" s="2">
         <v>11</v>
       </c>
-      <c r="Q13">
+      <c r="R13">
         <v>11</v>
       </c>
-      <c r="R13" s="3">
+      <c r="S13" s="3">
         <v>15</v>
       </c>
-      <c r="S13" s="2">
-        <v>2</v>
-      </c>
-      <c r="T13">
+      <c r="T13" s="2">
+        <v>2</v>
+      </c>
+      <c r="U13">
         <v>7</v>
       </c>
-      <c r="U13" s="3">
+      <c r="V13" s="3">
         <v>9</v>
       </c>
-      <c r="X13"/>
-      <c r="AA13"/>
-      <c r="AC13"/>
-      <c r="AE13"/>
-      <c r="AF13" s="5"/>
-    </row>
-    <row r="14" hidden="1" spans="1:32">
+      <c r="Y13"/>
+      <c r="AB13"/>
+      <c r="AD13"/>
+      <c r="AF13"/>
+      <c r="AG13" s="5"/>
+    </row>
+    <row r="14" spans="1:33">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" t="s">
-        <v>40</v>
+        <v>80</v>
+      </c>
+      <c r="D14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="F14" t="s">
-        <v>35</v>
-      </c>
-      <c r="I14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G14" t="s">
         <v>37</v>
       </c>
-      <c r="J14"/>
-      <c r="K14" s="2">
+      <c r="J14" t="s">
+        <v>39</v>
+      </c>
+      <c r="K14"/>
+      <c r="L14" s="2">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>4</v>
       </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
       <c r="N14">
         <v>0</v>
       </c>
-      <c r="O14"/>
-      <c r="P14" s="2">
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14"/>
+      <c r="Q14" s="2">
         <v>6</v>
       </c>
-      <c r="Q14">
+      <c r="R14">
         <v>6</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>8</v>
       </c>
-      <c r="U14"/>
-      <c r="X14"/>
-      <c r="AA14"/>
-      <c r="AC14"/>
-      <c r="AE14"/>
-      <c r="AF14" s="5"/>
-    </row>
-    <row r="15" hidden="1" spans="1:32">
+      <c r="V14"/>
+      <c r="Y14"/>
+      <c r="AB14"/>
+      <c r="AD14"/>
+      <c r="AF14"/>
+      <c r="AG14" s="5"/>
+    </row>
+    <row r="15" spans="1:33">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E15" t="s">
-        <v>35</v>
+        <v>83</v>
+      </c>
+      <c r="D15" t="s">
+        <v>84</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="F15" t="s">
-        <v>35</v>
-      </c>
-      <c r="I15" t="s">
         <v>37</v>
       </c>
-      <c r="J15"/>
-      <c r="K15" s="2">
+      <c r="G15" t="s">
+        <v>37</v>
+      </c>
+      <c r="J15" t="s">
+        <v>39</v>
+      </c>
+      <c r="K15"/>
+      <c r="L15" s="2">
         <v>4</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4</v>
       </c>
-      <c r="M15">
-        <v>1</v>
-      </c>
       <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15"/>
-      <c r="P15" s="2">
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15"/>
+      <c r="Q15" s="2">
         <v>18</v>
       </c>
-      <c r="Q15">
+      <c r="R15">
         <v>1.4</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1.8</v>
       </c>
-      <c r="U15"/>
-      <c r="X15"/>
-      <c r="AA15"/>
-      <c r="AC15"/>
-      <c r="AE15"/>
-      <c r="AF15" s="5"/>
-    </row>
-    <row r="16" hidden="1" spans="1:32">
+      <c r="V15"/>
+      <c r="Y15"/>
+      <c r="AB15"/>
+      <c r="AD15"/>
+      <c r="AF15"/>
+      <c r="AG15" s="5"/>
+    </row>
+    <row r="16" spans="1:33">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E16" t="s">
-        <v>35</v>
+        <v>86</v>
+      </c>
+      <c r="D16" t="s">
+        <v>87</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="F16" t="s">
-        <v>35</v>
-      </c>
-      <c r="I16" t="s">
         <v>37</v>
       </c>
-      <c r="J16"/>
-      <c r="K16" s="2">
+      <c r="G16" t="s">
+        <v>37</v>
+      </c>
+      <c r="J16" t="s">
+        <v>39</v>
+      </c>
+      <c r="K16"/>
+      <c r="L16" s="2">
         <v>6</v>
       </c>
-      <c r="L16" s="3">
+      <c r="M16" s="3">
         <v>5</v>
       </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
       <c r="N16">
         <v>0</v>
       </c>
-      <c r="O16"/>
-      <c r="P16" s="2">
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16"/>
+      <c r="Q16" s="2">
         <v>6</v>
       </c>
-      <c r="Q16">
+      <c r="R16">
         <v>4</v>
       </c>
-      <c r="R16" s="3">
+      <c r="S16" s="3">
         <v>5</v>
       </c>
-      <c r="S16" s="2">
+      <c r="T16" s="2">
         <v>18</v>
       </c>
-      <c r="T16">
+      <c r="U16">
         <v>0.8</v>
       </c>
-      <c r="U16" s="3">
+      <c r="V16" s="3">
         <v>1.1</v>
       </c>
-      <c r="X16"/>
-      <c r="AA16"/>
-      <c r="AC16"/>
-      <c r="AE16"/>
-      <c r="AF16" s="5"/>
-    </row>
-    <row r="17" hidden="1" spans="1:32">
+      <c r="Y16"/>
+      <c r="AB16"/>
+      <c r="AD16"/>
+      <c r="AF16"/>
+      <c r="AG16" s="5"/>
+    </row>
+    <row r="17" spans="1:33">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>74</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E17" t="s">
-        <v>40</v>
+        <v>89</v>
+      </c>
+      <c r="D17" t="s">
+        <v>90</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="F17" t="s">
-        <v>36</v>
-      </c>
-      <c r="I17" t="s">
-        <v>37</v>
-      </c>
-      <c r="J17"/>
-      <c r="K17" s="2">
+        <v>43</v>
+      </c>
+      <c r="G17" t="s">
+        <v>38</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J17" t="s">
+        <v>39</v>
+      </c>
+      <c r="K17"/>
+      <c r="L17" s="2">
         <v>3</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3</v>
       </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
       <c r="N17">
-        <v>1</v>
-      </c>
-      <c r="O17"/>
-      <c r="P17" s="2">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>1</v>
+      </c>
+      <c r="P17"/>
+      <c r="Q17" s="2">
         <v>19</v>
       </c>
-      <c r="Q17">
-        <v>1</v>
-      </c>
-      <c r="R17" s="3">
-        <v>1</v>
-      </c>
-      <c r="S17" s="2">
-        <v>2</v>
-      </c>
-      <c r="T17">
+      <c r="R17">
+        <v>1</v>
+      </c>
+      <c r="S17" s="3">
+        <v>1</v>
+      </c>
+      <c r="T17" s="2">
+        <v>2</v>
+      </c>
+      <c r="U17">
         <v>4</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6</v>
       </c>
-      <c r="V17" s="2">
+      <c r="W17" s="2">
         <v>21</v>
       </c>
-      <c r="W17">
-        <v>2</v>
-      </c>
-      <c r="X17" s="3">
+      <c r="X17">
+        <v>2</v>
+      </c>
+      <c r="Y17" s="3">
         <v>3</v>
       </c>
-      <c r="AA17"/>
-      <c r="AC17"/>
-      <c r="AE17"/>
-      <c r="AF17" s="6"/>
-    </row>
-    <row r="18" spans="1:32">
+      <c r="AB17"/>
+      <c r="AD17"/>
+      <c r="AF17"/>
+      <c r="AG17" s="6"/>
+    </row>
+    <row r="18" spans="1:33">
       <c r="A18">
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E18" t="s">
-        <v>40</v>
+        <v>93</v>
+      </c>
+      <c r="D18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="F18" t="s">
         <v>43</v>
       </c>
-      <c r="I18" t="s">
-        <v>37</v>
-      </c>
-      <c r="K18">
+      <c r="G18" t="s">
+        <v>47</v>
+      </c>
+      <c r="J18" t="s">
+        <v>39</v>
+      </c>
+      <c r="L18">
         <v>4</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3</v>
       </c>
-      <c r="M18">
-        <v>1</v>
-      </c>
       <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="P18" s="2">
+        <v>1</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="2">
         <v>15</v>
       </c>
-      <c r="Q18">
+      <c r="R18">
         <v>5</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>7</v>
       </c>
-      <c r="AB18">
+      <c r="AC18">
         <v>61</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1.5</v>
       </c>
-      <c r="AF18" s="5"/>
-    </row>
-    <row r="19" hidden="1" spans="1:32">
+      <c r="AG18" s="5"/>
+    </row>
+    <row r="19" spans="1:33">
       <c r="A19">
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="C19" t="s">
-        <v>78</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E19" t="s">
-        <v>40</v>
+        <v>95</v>
+      </c>
+      <c r="D19" t="s">
+        <v>95</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="F19" t="s">
-        <v>54</v>
-      </c>
-      <c r="I19" t="s">
-        <v>37</v>
-      </c>
-      <c r="J19"/>
-      <c r="K19" s="2">
+        <v>43</v>
+      </c>
+      <c r="G19" t="s">
+        <v>62</v>
+      </c>
+      <c r="J19" t="s">
+        <v>39</v>
+      </c>
+      <c r="K19"/>
+      <c r="L19" s="2">
         <v>5</v>
       </c>
-      <c r="L19" s="3">
+      <c r="M19" s="3">
         <v>4</v>
       </c>
-      <c r="M19">
-        <v>1</v>
-      </c>
       <c r="N19">
         <v>1</v>
       </c>
-      <c r="O19"/>
-      <c r="P19" s="2">
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19"/>
+      <c r="Q19" s="2">
         <v>23</v>
       </c>
-      <c r="Q19">
-        <v>1</v>
-      </c>
-      <c r="R19" s="3">
-        <v>1</v>
-      </c>
-      <c r="S19" s="2">
+      <c r="R19">
+        <v>1</v>
+      </c>
+      <c r="S19" s="3">
+        <v>1</v>
+      </c>
+      <c r="T19" s="2">
         <v>7</v>
       </c>
-      <c r="T19">
-        <v>1</v>
-      </c>
-      <c r="U19" s="3">
-        <v>2</v>
-      </c>
-      <c r="X19"/>
-      <c r="AA19"/>
-      <c r="AC19"/>
-      <c r="AE19"/>
-      <c r="AF19" s="5"/>
-    </row>
-    <row r="20" spans="1:32">
+      <c r="U19">
+        <v>1</v>
+      </c>
+      <c r="V19" s="3">
+        <v>2</v>
+      </c>
+      <c r="Y19"/>
+      <c r="AB19"/>
+      <c r="AD19"/>
+      <c r="AF19"/>
+      <c r="AG19" s="5"/>
+    </row>
+    <row r="20" spans="1:33">
       <c r="A20">
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="C20" t="s">
-        <v>80</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E20" t="s">
-        <v>35</v>
+        <v>97</v>
+      </c>
+      <c r="D20" t="s">
+        <v>97</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="F20" t="s">
-        <v>43</v>
-      </c>
-      <c r="I20" t="s">
         <v>37</v>
       </c>
-      <c r="K20">
+      <c r="G20" t="s">
+        <v>47</v>
+      </c>
+      <c r="J20" t="s">
+        <v>39</v>
+      </c>
+      <c r="L20">
         <v>6</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>6</v>
       </c>
-      <c r="M20">
-        <v>1</v>
-      </c>
       <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="2">
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="2">
         <v>11</v>
       </c>
-      <c r="Q20">
+      <c r="R20">
         <v>24</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>30</v>
       </c>
-      <c r="AB20">
+      <c r="AC20">
         <v>62</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>7</v>
       </c>
-      <c r="AF20" s="6"/>
-    </row>
-    <row r="21" spans="1:32">
+      <c r="AG20" s="6"/>
+    </row>
+    <row r="21" spans="1:33">
       <c r="A21">
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="C21" t="s">
-        <v>82</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E21" t="s">
-        <v>35</v>
+        <v>99</v>
+      </c>
+      <c r="D21" t="s">
+        <v>99</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="F21" t="s">
-        <v>43</v>
-      </c>
-      <c r="I21" t="s">
         <v>37</v>
       </c>
-      <c r="K21">
+      <c r="G21" t="s">
+        <v>47</v>
+      </c>
+      <c r="J21" t="s">
+        <v>39</v>
+      </c>
+      <c r="L21">
         <v>5</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4</v>
       </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
       <c r="N21">
-        <v>1</v>
-      </c>
-      <c r="P21" s="2">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="2">
         <v>26</v>
       </c>
-      <c r="Q21">
-        <v>2</v>
-      </c>
-      <c r="R21" s="3">
-        <v>2</v>
-      </c>
-      <c r="S21" s="2">
+      <c r="R21">
+        <v>2</v>
+      </c>
+      <c r="S21" s="3">
+        <v>2</v>
+      </c>
+      <c r="T21" s="2">
         <v>11</v>
       </c>
-      <c r="T21">
+      <c r="U21">
         <v>30</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>42</v>
       </c>
-      <c r="V21">
-        <v>2</v>
-      </c>
       <c r="W21">
+        <v>2</v>
+      </c>
+      <c r="X21">
         <v>5</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>7</v>
       </c>
-      <c r="AF21" s="5"/>
-    </row>
-    <row r="22" hidden="1" spans="1:32">
+      <c r="AG21" s="5"/>
+    </row>
+    <row r="22" spans="1:33">
       <c r="A22">
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="C22" t="s">
-        <v>84</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E22" t="s">
-        <v>40</v>
+        <v>101</v>
+      </c>
+      <c r="D22" t="s">
+        <v>101</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="F22" t="s">
-        <v>35</v>
-      </c>
-      <c r="I22" t="s">
+        <v>43</v>
+      </c>
+      <c r="G22" t="s">
         <v>37</v>
       </c>
-      <c r="J22"/>
-      <c r="K22" s="2">
+      <c r="J22" t="s">
+        <v>39</v>
+      </c>
+      <c r="K22"/>
+      <c r="L22" s="2">
         <v>4</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>4</v>
       </c>
-      <c r="M22">
-        <v>1</v>
-      </c>
       <c r="N22">
         <v>1</v>
       </c>
-      <c r="O22"/>
-      <c r="P22" s="2">
+      <c r="O22">
+        <v>1</v>
+      </c>
+      <c r="P22"/>
+      <c r="Q22" s="2">
         <v>6</v>
       </c>
-      <c r="Q22">
-        <v>2</v>
-      </c>
-      <c r="R22" s="3">
+      <c r="R22">
+        <v>2</v>
+      </c>
+      <c r="S22" s="3">
         <v>4</v>
       </c>
-      <c r="S22" s="2">
+      <c r="T22" s="2">
         <v>28</v>
       </c>
-      <c r="T22">
-        <v>1</v>
-      </c>
-      <c r="U22" s="3">
-        <v>1</v>
-      </c>
-      <c r="X22"/>
-      <c r="AA22"/>
-      <c r="AC22"/>
-      <c r="AE22"/>
-      <c r="AF22" s="5"/>
-    </row>
-    <row r="23" hidden="1" spans="1:32">
+      <c r="U22">
+        <v>1</v>
+      </c>
+      <c r="V22" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y22"/>
+      <c r="AB22"/>
+      <c r="AD22"/>
+      <c r="AF22"/>
+      <c r="AG22" s="5"/>
+    </row>
+    <row r="23" spans="1:33">
       <c r="A23">
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="C23" t="s">
-        <v>86</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E23" t="s">
-        <v>40</v>
+        <v>103</v>
+      </c>
+      <c r="D23" t="s">
+        <v>103</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="F23" t="s">
-        <v>35</v>
-      </c>
-      <c r="I23" t="s">
+        <v>43</v>
+      </c>
+      <c r="G23" t="s">
         <v>37</v>
       </c>
-      <c r="J23"/>
-      <c r="K23" s="2">
-        <v>1</v>
-      </c>
-      <c r="L23" s="3">
-        <v>1</v>
-      </c>
-      <c r="M23">
+      <c r="J23" t="s">
+        <v>39</v>
+      </c>
+      <c r="K23"/>
+      <c r="L23" s="2">
+        <v>1</v>
+      </c>
+      <c r="M23" s="3">
         <v>1</v>
       </c>
       <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23"/>
-      <c r="P23" s="2">
+        <v>1</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23"/>
+      <c r="Q23" s="2">
         <v>6</v>
       </c>
-      <c r="Q23">
+      <c r="R23">
         <v>5</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>7</v>
       </c>
-      <c r="S23" s="2">
-        <v>2</v>
-      </c>
-      <c r="T23">
-        <v>1</v>
-      </c>
-      <c r="U23" s="3">
-        <v>1</v>
-      </c>
-      <c r="X23"/>
-      <c r="AA23"/>
-      <c r="AC23"/>
-      <c r="AE23"/>
-      <c r="AF23" s="5"/>
-    </row>
-    <row r="24" spans="1:32">
+      <c r="T23" s="2">
+        <v>2</v>
+      </c>
+      <c r="U23">
+        <v>1</v>
+      </c>
+      <c r="V23" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y23"/>
+      <c r="AB23"/>
+      <c r="AD23"/>
+      <c r="AF23"/>
+      <c r="AG23" s="5"/>
+    </row>
+    <row r="24" spans="1:33">
       <c r="A24">
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="C24" t="s">
-        <v>88</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E24" t="s">
-        <v>35</v>
+        <v>105</v>
+      </c>
+      <c r="D24" t="s">
+        <v>105</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="F24" t="s">
-        <v>43</v>
-      </c>
-      <c r="I24" t="s">
         <v>37</v>
       </c>
-      <c r="K24">
+      <c r="G24" t="s">
+        <v>47</v>
+      </c>
+      <c r="J24" t="s">
+        <v>39</v>
+      </c>
+      <c r="L24">
         <v>4</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4</v>
       </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
       <c r="N24">
         <v>0</v>
       </c>
-      <c r="P24" s="2">
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="2">
         <v>15</v>
       </c>
-      <c r="Q24">
+      <c r="R24">
         <v>3</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>4</v>
       </c>
-      <c r="S24" s="2">
+      <c r="T24" s="2">
         <v>11</v>
       </c>
-      <c r="T24">
+      <c r="U24">
         <v>8</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>11</v>
       </c>
-      <c r="AB24">
+      <c r="AC24">
         <v>63</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>3</v>
       </c>
-      <c r="AF24" s="5"/>
-    </row>
-    <row r="25" hidden="1" spans="1:32">
+      <c r="AG24" s="5"/>
+    </row>
+    <row r="25" spans="1:33">
       <c r="A25">
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="C25" t="s">
-        <v>90</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E25" t="s">
-        <v>40</v>
+        <v>107</v>
+      </c>
+      <c r="D25" t="s">
+        <v>107</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="F25" t="s">
-        <v>54</v>
-      </c>
-      <c r="I25" t="s">
-        <v>37</v>
-      </c>
-      <c r="J25"/>
-      <c r="K25" s="2">
+        <v>43</v>
+      </c>
+      <c r="G25" t="s">
+        <v>62</v>
+      </c>
+      <c r="J25" t="s">
+        <v>39</v>
+      </c>
+      <c r="K25"/>
+      <c r="L25" s="2">
         <v>3</v>
       </c>
-      <c r="L25" s="3">
-        <v>2</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
+      <c r="M25" s="3">
+        <v>2</v>
       </c>
       <c r="N25">
         <v>0</v>
       </c>
-      <c r="O25"/>
-      <c r="P25" s="2">
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25"/>
+      <c r="Q25" s="2">
         <v>7</v>
       </c>
-      <c r="Q25">
+      <c r="R25">
         <v>3</v>
       </c>
-      <c r="R25" s="3">
+      <c r="S25" s="3">
         <v>5</v>
       </c>
-      <c r="U25"/>
-      <c r="X25"/>
-      <c r="AA25"/>
-      <c r="AC25"/>
-      <c r="AE25"/>
-      <c r="AF25" s="5"/>
-    </row>
-    <row r="26" hidden="1" spans="1:32">
+      <c r="V25"/>
+      <c r="Y25"/>
+      <c r="AB25"/>
+      <c r="AD25"/>
+      <c r="AF25"/>
+      <c r="AG25" s="5"/>
+    </row>
+    <row r="26" spans="1:33">
       <c r="A26">
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="C26" t="s">
-        <v>92</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E26" t="s">
-        <v>40</v>
+        <v>109</v>
+      </c>
+      <c r="D26" t="s">
+        <v>109</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="F26" t="s">
-        <v>54</v>
-      </c>
-      <c r="I26" t="s">
-        <v>37</v>
-      </c>
-      <c r="J26"/>
-      <c r="K26" s="2">
+        <v>43</v>
+      </c>
+      <c r="G26" t="s">
+        <v>62</v>
+      </c>
+      <c r="J26" t="s">
+        <v>39</v>
+      </c>
+      <c r="K26"/>
+      <c r="L26" s="2">
         <v>3</v>
       </c>
-      <c r="L26" s="3">
-        <v>2</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
+      <c r="M26" s="3">
+        <v>2</v>
       </c>
       <c r="N26">
         <v>0</v>
       </c>
-      <c r="O26"/>
-      <c r="P26" s="2">
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26"/>
+      <c r="Q26" s="2">
         <v>7</v>
       </c>
-      <c r="Q26">
+      <c r="R26">
         <v>3</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4</v>
       </c>
-      <c r="S26" s="2">
-        <v>2</v>
-      </c>
-      <c r="T26">
+      <c r="T26" s="2">
+        <v>2</v>
+      </c>
+      <c r="U26">
         <v>4</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>6</v>
       </c>
-      <c r="X26"/>
-      <c r="AA26"/>
-      <c r="AC26"/>
-      <c r="AE26"/>
-      <c r="AF26" s="5"/>
-    </row>
-    <row r="27" spans="1:32">
+      <c r="Y26"/>
+      <c r="AB26"/>
+      <c r="AD26"/>
+      <c r="AF26"/>
+      <c r="AG26" s="5"/>
+    </row>
+    <row r="27" spans="1:33">
       <c r="A27">
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="C27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E27" t="s">
-        <v>35</v>
+        <v>111</v>
+      </c>
+      <c r="D27" t="s">
+        <v>111</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="F27" t="s">
-        <v>43</v>
-      </c>
-      <c r="I27" t="s">
         <v>37</v>
       </c>
-      <c r="K27">
+      <c r="G27" t="s">
+        <v>47</v>
+      </c>
+      <c r="J27" t="s">
+        <v>39</v>
+      </c>
+      <c r="L27">
         <v>8</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6</v>
       </c>
-      <c r="M27">
-        <v>1</v>
-      </c>
       <c r="N27">
         <v>1</v>
       </c>
-      <c r="O27" s="3">
-        <v>0</v>
-      </c>
-      <c r="P27" s="2">
+      <c r="O27">
+        <v>1</v>
+      </c>
+      <c r="P27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="2">
         <v>11</v>
       </c>
-      <c r="Q27">
+      <c r="R27">
         <v>12</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>18</v>
       </c>
-      <c r="S27" s="2">
+      <c r="T27" s="2">
         <v>56</v>
       </c>
-      <c r="T27">
+      <c r="U27">
         <v>24</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>30</v>
       </c>
-      <c r="V27">
+      <c r="W27">
         <v>57</v>
       </c>
-      <c r="W27">
+      <c r="X27">
         <v>36</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>44</v>
       </c>
-      <c r="AF27" s="6"/>
-    </row>
-    <row r="28" spans="1:32">
+      <c r="AG27" s="6"/>
+    </row>
+    <row r="28" spans="1:33">
       <c r="A28">
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="C28" t="s">
-        <v>96</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E28" t="s">
-        <v>40</v>
+        <v>113</v>
+      </c>
+      <c r="D28" t="s">
+        <v>113</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="F28" t="s">
         <v>43</v>
       </c>
-      <c r="I28" t="s">
-        <v>37</v>
-      </c>
-      <c r="K28">
-        <v>1</v>
-      </c>
-      <c r="L28" s="3">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>1</v>
+      <c r="G28" t="s">
+        <v>47</v>
+      </c>
+      <c r="J28" t="s">
+        <v>39</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
       </c>
       <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="P28" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q28">
+        <v>1</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="2">
+        <v>2</v>
+      </c>
+      <c r="R28">
         <v>6</v>
       </c>
-      <c r="R28" s="3">
+      <c r="S28" s="3">
         <v>8</v>
       </c>
-      <c r="AB28">
+      <c r="AC28">
         <v>21</v>
       </c>
-      <c r="AC28" s="3">
+      <c r="AD28" s="3">
         <v>12</v>
       </c>
-      <c r="AF28" s="5"/>
-    </row>
-    <row r="29" hidden="1" spans="1:32">
+      <c r="AG28" s="5"/>
+    </row>
+    <row r="29" spans="1:33">
       <c r="A29">
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="C29" t="s">
-        <v>98</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E29" t="s">
-        <v>40</v>
+        <v>115</v>
+      </c>
+      <c r="D29" t="s">
+        <v>115</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="F29" t="s">
-        <v>36</v>
-      </c>
-      <c r="I29" t="s">
-        <v>37</v>
-      </c>
-      <c r="J29"/>
-      <c r="K29" s="2">
+        <v>43</v>
+      </c>
+      <c r="G29" t="s">
+        <v>38</v>
+      </c>
+      <c r="J29" t="s">
+        <v>39</v>
+      </c>
+      <c r="K29"/>
+      <c r="L29" s="2">
         <v>5</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>5</v>
       </c>
-      <c r="M29">
-        <v>1</v>
-      </c>
       <c r="N29">
         <v>1</v>
       </c>
-      <c r="O29"/>
-      <c r="P29" s="2">
+      <c r="O29">
+        <v>1</v>
+      </c>
+      <c r="P29"/>
+      <c r="Q29" s="2">
         <v>32</v>
       </c>
-      <c r="Q29">
+      <c r="R29">
         <v>30</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>30</v>
       </c>
-      <c r="S29" s="2">
-        <v>2</v>
-      </c>
-      <c r="T29">
+      <c r="T29" s="2">
+        <v>2</v>
+      </c>
+      <c r="U29">
         <v>3</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>5</v>
       </c>
-      <c r="V29" s="2">
+      <c r="W29" s="2">
         <v>21</v>
       </c>
-      <c r="W29">
-        <v>2</v>
-      </c>
-      <c r="X29" s="3">
+      <c r="X29">
+        <v>2</v>
+      </c>
+      <c r="Y29" s="3">
         <v>3</v>
       </c>
-      <c r="AA29"/>
-      <c r="AC29"/>
-      <c r="AE29"/>
-      <c r="AF29" s="5"/>
-    </row>
-    <row r="30" hidden="1" spans="1:32">
+      <c r="AB29"/>
+      <c r="AD29"/>
+      <c r="AF29"/>
+      <c r="AG29" s="5"/>
+    </row>
+    <row r="30" spans="1:33">
       <c r="A30">
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="C30" t="s">
-        <v>100</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E30" t="s">
-        <v>40</v>
+        <v>117</v>
+      </c>
+      <c r="D30" t="s">
+        <v>117</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="F30" t="s">
-        <v>36</v>
-      </c>
-      <c r="I30" t="s">
-        <v>37</v>
-      </c>
-      <c r="J30"/>
-      <c r="K30" s="2">
+        <v>43</v>
+      </c>
+      <c r="G30" t="s">
+        <v>38</v>
+      </c>
+      <c r="J30" t="s">
+        <v>39</v>
+      </c>
+      <c r="K30"/>
+      <c r="L30" s="2">
         <v>4</v>
       </c>
-      <c r="L30" s="3">
+      <c r="M30" s="3">
         <v>4</v>
       </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
       <c r="N30">
-        <v>1</v>
-      </c>
-      <c r="O30"/>
-      <c r="P30" s="2">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>1</v>
+      </c>
+      <c r="P30"/>
+      <c r="Q30" s="2">
         <v>33</v>
       </c>
-      <c r="Q30">
+      <c r="R30">
         <v>50</v>
       </c>
-      <c r="R30" s="3">
+      <c r="S30" s="3">
         <v>70</v>
       </c>
-      <c r="S30" s="2">
-        <v>2</v>
-      </c>
-      <c r="T30">
-        <v>2</v>
-      </c>
-      <c r="U30" s="3">
+      <c r="T30" s="2">
+        <v>2</v>
+      </c>
+      <c r="U30">
+        <v>2</v>
+      </c>
+      <c r="V30" s="3">
         <v>4</v>
       </c>
-      <c r="X30"/>
-      <c r="AA30"/>
-      <c r="AC30"/>
-      <c r="AE30"/>
-      <c r="AF30" s="6"/>
-    </row>
-    <row r="31" hidden="1" spans="1:32">
+      <c r="Y30"/>
+      <c r="AB30"/>
+      <c r="AD30"/>
+      <c r="AF30"/>
+      <c r="AG30" s="6"/>
+    </row>
+    <row r="31" spans="1:33">
       <c r="A31">
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="C31" t="s">
-        <v>102</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E31" t="s">
-        <v>40</v>
+        <v>119</v>
+      </c>
+      <c r="D31" t="s">
+        <v>119</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="F31" t="s">
-        <v>36</v>
-      </c>
-      <c r="I31" t="s">
-        <v>37</v>
-      </c>
-      <c r="J31"/>
-      <c r="K31" s="2">
+        <v>43</v>
+      </c>
+      <c r="G31" t="s">
+        <v>38</v>
+      </c>
+      <c r="J31" t="s">
+        <v>39</v>
+      </c>
+      <c r="K31"/>
+      <c r="L31" s="2">
         <v>4</v>
       </c>
-      <c r="L31" s="3">
+      <c r="M31" s="3">
         <v>3</v>
       </c>
-      <c r="M31">
-        <v>1</v>
-      </c>
       <c r="N31">
         <v>1</v>
       </c>
-      <c r="O31"/>
-      <c r="P31" s="2">
+      <c r="O31">
+        <v>1</v>
+      </c>
+      <c r="P31"/>
+      <c r="Q31" s="2">
         <v>33</v>
       </c>
-      <c r="Q31">
+      <c r="R31">
         <v>20</v>
       </c>
-      <c r="R31" s="3">
+      <c r="S31" s="3">
         <v>30</v>
       </c>
-      <c r="S31" s="2">
+      <c r="T31" s="2">
         <v>35</v>
       </c>
-      <c r="T31">
-        <v>1</v>
-      </c>
-      <c r="U31" s="3">
-        <v>1</v>
-      </c>
-      <c r="X31"/>
-      <c r="AA31"/>
-      <c r="AC31"/>
-      <c r="AE31"/>
-      <c r="AF31" s="6"/>
-    </row>
-    <row r="32" hidden="1" spans="1:31">
+      <c r="U31">
+        <v>1</v>
+      </c>
+      <c r="V31" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y31"/>
+      <c r="AB31"/>
+      <c r="AD31"/>
+      <c r="AF31"/>
+      <c r="AG31" s="6"/>
+    </row>
+    <row r="32" spans="1:32">
       <c r="A32">
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="C32" t="s">
-        <v>104</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E32" t="s">
-        <v>40</v>
+        <v>121</v>
+      </c>
+      <c r="D32" t="s">
+        <v>121</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="F32" t="s">
-        <v>36</v>
-      </c>
-      <c r="I32" t="s">
-        <v>37</v>
-      </c>
-      <c r="J32"/>
-      <c r="K32" s="2">
+        <v>43</v>
+      </c>
+      <c r="G32" t="s">
+        <v>38</v>
+      </c>
+      <c r="J32" t="s">
+        <v>39</v>
+      </c>
+      <c r="K32"/>
+      <c r="L32" s="2">
         <v>7</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>6</v>
       </c>
-      <c r="M32">
-        <v>1</v>
-      </c>
       <c r="N32">
         <v>1</v>
       </c>
-      <c r="O32"/>
-      <c r="R32"/>
-      <c r="U32"/>
-      <c r="X32"/>
-      <c r="AA32"/>
-      <c r="AC32"/>
-      <c r="AE32"/>
-    </row>
-    <row r="33" spans="1:29">
+      <c r="O32">
+        <v>1</v>
+      </c>
+      <c r="P32"/>
+      <c r="S32"/>
+      <c r="V32"/>
+      <c r="Y32"/>
+      <c r="AB32"/>
+      <c r="AD32"/>
+      <c r="AF32"/>
+    </row>
+    <row r="33" spans="1:30">
       <c r="A33">
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="C33" t="s">
-        <v>106</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E33" t="s">
-        <v>35</v>
+        <v>123</v>
+      </c>
+      <c r="D33" t="s">
+        <v>123</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="F33" t="s">
-        <v>43</v>
-      </c>
-      <c r="I33" t="s">
         <v>37</v>
       </c>
-      <c r="K33">
+      <c r="G33" t="s">
+        <v>47</v>
+      </c>
+      <c r="J33" t="s">
+        <v>39</v>
+      </c>
+      <c r="L33">
         <v>8</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7</v>
       </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
       <c r="N33">
-        <v>1</v>
-      </c>
-      <c r="P33" s="2">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="2">
         <v>11</v>
       </c>
-      <c r="Q33">
+      <c r="R33">
         <v>38</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>52</v>
       </c>
-      <c r="AB33">
+      <c r="AC33">
         <v>64</v>
       </c>
-      <c r="AC33" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18">
+      <c r="AD33" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19">
       <c r="A34">
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="C34" t="s">
-        <v>108</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E34" t="s">
-        <v>40</v>
+        <v>125</v>
+      </c>
+      <c r="D34" t="s">
+        <v>125</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="F34" t="s">
         <v>43</v>
       </c>
-      <c r="I34" t="s">
-        <v>37</v>
-      </c>
-      <c r="K34">
+      <c r="G34" t="s">
+        <v>47</v>
+      </c>
+      <c r="J34" t="s">
+        <v>39</v>
+      </c>
+      <c r="L34">
         <v>3</v>
       </c>
-      <c r="L34" s="3">
+      <c r="M34" s="3">
         <v>3</v>
       </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
       <c r="N34">
         <v>0</v>
       </c>
-      <c r="O34" s="3">
-        <v>0</v>
-      </c>
-      <c r="P34" s="2">
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="2">
         <v>15</v>
       </c>
-      <c r="Q34">
+      <c r="R34">
         <v>3</v>
       </c>
-      <c r="R34" s="3">
+      <c r="S34" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:18">
+    <row r="35" spans="1:19">
       <c r="A35">
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="C35" t="s">
-        <v>110</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E35" t="s">
-        <v>35</v>
+        <v>127</v>
+      </c>
+      <c r="D35" t="s">
+        <v>127</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="F35" t="s">
-        <v>43</v>
-      </c>
-      <c r="I35" t="s">
         <v>37</v>
       </c>
-      <c r="K35">
+      <c r="G35" t="s">
+        <v>47</v>
+      </c>
+      <c r="J35" t="s">
+        <v>39</v>
+      </c>
+      <c r="L35">
         <v>3</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3</v>
       </c>
-      <c r="M35">
-        <v>1</v>
-      </c>
       <c r="N35">
-        <v>0</v>
-      </c>
-      <c r="P35" s="2">
+        <v>1</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="2">
         <v>11</v>
       </c>
-      <c r="Q35">
+      <c r="R35">
         <v>18</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:21">
+    <row r="36" spans="1:22">
       <c r="A36">
         <v>37</v>
       </c>
@@ -4010,711 +4164,747 @@
         <v>144</v>
       </c>
       <c r="C36" t="s">
-        <v>111</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E36" t="s">
-        <v>40</v>
+        <v>128</v>
+      </c>
+      <c r="D36" t="s">
+        <v>128</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="F36" t="s">
         <v>43</v>
       </c>
-      <c r="I36" t="s">
-        <v>37</v>
-      </c>
-      <c r="K36">
+      <c r="G36" t="s">
+        <v>47</v>
+      </c>
+      <c r="J36" t="s">
+        <v>39</v>
+      </c>
+      <c r="L36">
         <v>3</v>
       </c>
-      <c r="L36" s="3">
+      <c r="M36" s="3">
         <v>3</v>
       </c>
-      <c r="M36">
-        <v>1</v>
-      </c>
       <c r="N36">
-        <v>0</v>
-      </c>
-      <c r="P36" s="2">
+        <v>1</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="2">
         <v>15</v>
       </c>
-      <c r="Q36">
+      <c r="R36">
         <v>3</v>
       </c>
-      <c r="R36" s="3">
+      <c r="S36" s="3">
         <v>4</v>
       </c>
-      <c r="S36" s="2">
-        <v>2</v>
-      </c>
-      <c r="T36">
+      <c r="T36" s="2">
+        <v>2</v>
+      </c>
+      <c r="U36">
         <v>6</v>
       </c>
-      <c r="U36" s="3">
+      <c r="V36" s="3">
         <v>8</v>
       </c>
     </row>
-    <row r="37" hidden="1" spans="1:31">
+    <row r="37" spans="1:32">
       <c r="A37">
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="C37" t="s">
-        <v>113</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E37" t="s">
-        <v>40</v>
+        <v>130</v>
+      </c>
+      <c r="D37" t="s">
+        <v>130</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="F37" t="s">
-        <v>54</v>
-      </c>
-      <c r="I37" t="s">
-        <v>37</v>
-      </c>
-      <c r="J37"/>
-      <c r="K37" s="2">
+        <v>43</v>
+      </c>
+      <c r="G37" t="s">
+        <v>62</v>
+      </c>
+      <c r="J37" t="s">
+        <v>39</v>
+      </c>
+      <c r="K37"/>
+      <c r="L37" s="2">
         <v>3</v>
       </c>
-      <c r="L37" s="3">
+      <c r="M37" s="3">
         <v>3</v>
       </c>
-      <c r="M37">
-        <v>1</v>
-      </c>
       <c r="N37">
-        <v>0</v>
-      </c>
-      <c r="O37"/>
-      <c r="P37" s="2">
+        <v>1</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37"/>
+      <c r="Q37" s="2">
         <v>7</v>
       </c>
-      <c r="Q37">
+      <c r="R37">
         <v>3</v>
       </c>
-      <c r="R37" s="3">
+      <c r="S37" s="3">
         <v>4</v>
       </c>
-      <c r="S37" s="2">
-        <v>2</v>
-      </c>
-      <c r="T37">
+      <c r="T37" s="2">
+        <v>2</v>
+      </c>
+      <c r="U37">
         <v>6</v>
       </c>
-      <c r="U37" s="3">
+      <c r="V37" s="3">
         <v>8</v>
       </c>
-      <c r="X37"/>
-      <c r="AA37"/>
-      <c r="AC37"/>
-      <c r="AE37"/>
-    </row>
-    <row r="38" hidden="1" spans="1:31">
+      <c r="Y37"/>
+      <c r="AB37"/>
+      <c r="AD37"/>
+      <c r="AF37"/>
+    </row>
+    <row r="38" spans="1:32">
       <c r="A38">
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C38" t="s">
-        <v>115</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E38" t="s">
-        <v>40</v>
+        <v>132</v>
+      </c>
+      <c r="D38" t="s">
+        <v>132</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="F38" t="s">
-        <v>36</v>
-      </c>
-      <c r="I38" t="s">
-        <v>37</v>
-      </c>
-      <c r="J38"/>
-      <c r="K38" s="2">
-        <v>1</v>
-      </c>
-      <c r="L38" s="3">
-        <v>1</v>
-      </c>
-      <c r="M38">
+        <v>43</v>
+      </c>
+      <c r="G38" t="s">
+        <v>38</v>
+      </c>
+      <c r="J38" t="s">
+        <v>39</v>
+      </c>
+      <c r="K38"/>
+      <c r="L38" s="2">
+        <v>1</v>
+      </c>
+      <c r="M38" s="3">
         <v>1</v>
       </c>
       <c r="N38">
         <v>1</v>
       </c>
-      <c r="O38"/>
-      <c r="P38" s="2">
+      <c r="O38">
+        <v>1</v>
+      </c>
+      <c r="P38"/>
+      <c r="Q38" s="2">
         <v>21</v>
       </c>
-      <c r="Q38">
+      <c r="R38">
         <v>4</v>
       </c>
-      <c r="R38" s="3">
+      <c r="S38" s="3">
         <v>5</v>
       </c>
-      <c r="S38" s="2">
-        <v>2</v>
-      </c>
-      <c r="T38">
+      <c r="T38" s="2">
+        <v>2</v>
+      </c>
+      <c r="U38">
         <v>3</v>
       </c>
-      <c r="U38" s="3">
+      <c r="V38" s="3">
         <v>5</v>
       </c>
-      <c r="X38"/>
-      <c r="AA38"/>
-      <c r="AC38"/>
-      <c r="AE38"/>
-    </row>
-    <row r="39" hidden="1" spans="1:31">
+      <c r="Y38"/>
+      <c r="AB38"/>
+      <c r="AD38"/>
+      <c r="AF38"/>
+    </row>
+    <row r="39" spans="1:32">
       <c r="A39">
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="C39" t="s">
-        <v>117</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E39" t="s">
-        <v>40</v>
+        <v>134</v>
+      </c>
+      <c r="D39" t="s">
+        <v>134</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="F39" t="s">
-        <v>36</v>
-      </c>
-      <c r="I39" t="s">
-        <v>37</v>
-      </c>
-      <c r="J39"/>
-      <c r="K39" s="2">
-        <v>1</v>
-      </c>
-      <c r="L39" s="3">
-        <v>1</v>
-      </c>
-      <c r="M39">
+        <v>43</v>
+      </c>
+      <c r="G39" t="s">
+        <v>38</v>
+      </c>
+      <c r="J39" t="s">
+        <v>39</v>
+      </c>
+      <c r="K39"/>
+      <c r="L39" s="2">
+        <v>1</v>
+      </c>
+      <c r="M39" s="3">
         <v>1</v>
       </c>
       <c r="N39">
         <v>1</v>
       </c>
-      <c r="O39"/>
-      <c r="P39" s="2">
+      <c r="O39">
+        <v>1</v>
+      </c>
+      <c r="P39"/>
+      <c r="Q39" s="2">
         <v>5</v>
       </c>
-      <c r="Q39">
-        <v>1</v>
-      </c>
-      <c r="R39" s="3">
-        <v>2</v>
-      </c>
-      <c r="S39" s="2">
-        <v>2</v>
-      </c>
-      <c r="T39">
+      <c r="R39">
+        <v>1</v>
+      </c>
+      <c r="S39" s="3">
+        <v>2</v>
+      </c>
+      <c r="T39" s="2">
+        <v>2</v>
+      </c>
+      <c r="U39">
         <v>6</v>
       </c>
-      <c r="U39" s="3">
+      <c r="V39" s="3">
         <v>7</v>
       </c>
-      <c r="X39"/>
-      <c r="AA39"/>
-      <c r="AC39"/>
-      <c r="AE39"/>
-    </row>
-    <row r="40" hidden="1" spans="1:31">
+      <c r="Y39"/>
+      <c r="AB39"/>
+      <c r="AD39"/>
+      <c r="AF39"/>
+    </row>
+    <row r="40" spans="1:32">
       <c r="A40">
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="C40" t="s">
-        <v>119</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E40" t="s">
-        <v>40</v>
+        <v>136</v>
+      </c>
+      <c r="D40" t="s">
+        <v>136</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="F40" t="s">
-        <v>54</v>
-      </c>
-      <c r="I40" t="s">
-        <v>37</v>
-      </c>
-      <c r="J40"/>
-      <c r="K40" s="2">
+        <v>43</v>
+      </c>
+      <c r="G40" t="s">
+        <v>62</v>
+      </c>
+      <c r="J40" t="s">
+        <v>39</v>
+      </c>
+      <c r="K40"/>
+      <c r="L40" s="2">
         <v>4</v>
       </c>
-      <c r="L40" s="3">
+      <c r="M40" s="3">
         <v>3</v>
       </c>
-      <c r="M40">
-        <v>1</v>
-      </c>
       <c r="N40">
         <v>1</v>
       </c>
-      <c r="O40"/>
-      <c r="P40" s="2">
+      <c r="O40">
+        <v>1</v>
+      </c>
+      <c r="P40"/>
+      <c r="Q40" s="2">
         <v>7</v>
       </c>
-      <c r="Q40">
+      <c r="R40">
         <v>4</v>
       </c>
-      <c r="R40" s="3">
+      <c r="S40" s="3">
         <v>5</v>
       </c>
-      <c r="S40" s="2">
+      <c r="T40" s="2">
         <v>38</v>
       </c>
-      <c r="T40">
+      <c r="U40">
         <v>4</v>
       </c>
-      <c r="U40" s="3">
+      <c r="V40" s="3">
         <v>5</v>
       </c>
-      <c r="X40"/>
-      <c r="AA40"/>
-      <c r="AC40"/>
-      <c r="AE40"/>
-    </row>
-    <row r="41" hidden="1" spans="1:31">
+      <c r="Y40"/>
+      <c r="AB40"/>
+      <c r="AD40"/>
+      <c r="AF40"/>
+    </row>
+    <row r="41" spans="1:32">
       <c r="A41">
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="C41" t="s">
-        <v>121</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E41" t="s">
-        <v>40</v>
+        <v>138</v>
+      </c>
+      <c r="D41" t="s">
+        <v>138</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="F41" t="s">
-        <v>35</v>
-      </c>
-      <c r="I41" t="s">
+        <v>43</v>
+      </c>
+      <c r="G41" t="s">
         <v>37</v>
       </c>
-      <c r="J41"/>
-      <c r="K41" s="2">
-        <v>2</v>
-      </c>
-      <c r="L41" s="3">
-        <v>2</v>
-      </c>
-      <c r="M41">
-        <v>0</v>
+      <c r="J41" t="s">
+        <v>39</v>
+      </c>
+      <c r="K41"/>
+      <c r="L41" s="2">
+        <v>2</v>
+      </c>
+      <c r="M41" s="3">
+        <v>2</v>
       </c>
       <c r="N41">
         <v>0</v>
       </c>
-      <c r="O41"/>
-      <c r="P41" s="2">
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41"/>
+      <c r="Q41" s="2">
         <v>6</v>
       </c>
-      <c r="Q41">
+      <c r="R41">
         <v>3</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3</v>
       </c>
-      <c r="S41" s="2">
+      <c r="T41" s="2">
         <v>39</v>
       </c>
-      <c r="T41">
-        <v>2</v>
-      </c>
-      <c r="U41" s="3">
+      <c r="U41">
+        <v>2</v>
+      </c>
+      <c r="V41" s="3">
         <v>3</v>
       </c>
-      <c r="X41"/>
-      <c r="AA41"/>
-      <c r="AC41"/>
-      <c r="AE41"/>
-    </row>
-    <row r="42" hidden="1" spans="1:31">
+      <c r="Y41"/>
+      <c r="AB41"/>
+      <c r="AD41"/>
+      <c r="AF41"/>
+    </row>
+    <row r="42" spans="1:32">
       <c r="A42">
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="C42" t="s">
-        <v>123</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E42" t="s">
-        <v>40</v>
+        <v>140</v>
+      </c>
+      <c r="D42" t="s">
+        <v>140</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="F42" t="s">
-        <v>54</v>
-      </c>
-      <c r="I42" t="s">
-        <v>37</v>
-      </c>
-      <c r="J42"/>
-      <c r="K42" s="2">
+        <v>43</v>
+      </c>
+      <c r="G42" t="s">
+        <v>62</v>
+      </c>
+      <c r="J42" t="s">
+        <v>39</v>
+      </c>
+      <c r="K42"/>
+      <c r="L42" s="2">
         <v>4</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>3</v>
       </c>
-      <c r="M42">
-        <v>1</v>
-      </c>
       <c r="N42">
         <v>1</v>
       </c>
-      <c r="O42"/>
-      <c r="P42" s="2">
+      <c r="O42">
+        <v>1</v>
+      </c>
+      <c r="P42"/>
+      <c r="Q42" s="2">
         <v>7</v>
       </c>
-      <c r="Q42">
-        <v>1</v>
-      </c>
-      <c r="R42" s="3">
+      <c r="R42">
+        <v>1</v>
+      </c>
+      <c r="S42" s="3">
         <v>3</v>
       </c>
-      <c r="S42" s="2">
+      <c r="T42" s="2">
         <v>41</v>
       </c>
-      <c r="T42">
-        <v>1</v>
-      </c>
-      <c r="U42" s="3">
-        <v>1</v>
-      </c>
-      <c r="X42"/>
-      <c r="AA42"/>
-      <c r="AC42"/>
-      <c r="AE42"/>
-    </row>
-    <row r="43" hidden="1" spans="1:31">
+      <c r="U42">
+        <v>1</v>
+      </c>
+      <c r="V42" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y42"/>
+      <c r="AB42"/>
+      <c r="AD42"/>
+      <c r="AF42"/>
+    </row>
+    <row r="43" spans="1:32">
       <c r="A43">
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="C43" t="s">
-        <v>125</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E43" t="s">
-        <v>35</v>
+        <v>142</v>
+      </c>
+      <c r="D43" t="s">
+        <v>142</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="F43" t="s">
-        <v>35</v>
-      </c>
-      <c r="I43" t="s">
         <v>37</v>
       </c>
-      <c r="J43"/>
-      <c r="K43" s="2">
+      <c r="G43" t="s">
+        <v>37</v>
+      </c>
+      <c r="J43" t="s">
+        <v>39</v>
+      </c>
+      <c r="K43"/>
+      <c r="L43" s="2">
         <v>7</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4</v>
       </c>
-      <c r="M43">
-        <v>0</v>
-      </c>
       <c r="N43">
-        <v>1</v>
-      </c>
-      <c r="O43"/>
-      <c r="P43" s="2">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>1</v>
+      </c>
+      <c r="P43"/>
+      <c r="Q43" s="2">
         <v>6</v>
       </c>
-      <c r="Q43">
+      <c r="R43">
         <v>5</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5</v>
       </c>
-      <c r="S43" s="2">
+      <c r="T43" s="2">
         <v>14</v>
       </c>
-      <c r="T43">
-        <v>1</v>
-      </c>
-      <c r="U43" s="3">
-        <v>1</v>
-      </c>
-      <c r="V43" s="2">
+      <c r="U43">
+        <v>1</v>
+      </c>
+      <c r="V43" s="3">
+        <v>1</v>
+      </c>
+      <c r="W43" s="2">
         <v>18</v>
       </c>
-      <c r="W43">
+      <c r="X43">
         <v>0.9</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1.2</v>
       </c>
-      <c r="AA43"/>
-      <c r="AC43"/>
-      <c r="AE43"/>
-    </row>
-    <row r="44" spans="1:21">
+      <c r="AB43"/>
+      <c r="AD43"/>
+      <c r="AF43"/>
+    </row>
+    <row r="44" spans="1:22">
       <c r="A44">
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="C44" t="s">
-        <v>127</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E44" t="s">
-        <v>35</v>
+        <v>144</v>
+      </c>
+      <c r="D44" t="s">
+        <v>144</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="F44" t="s">
-        <v>43</v>
-      </c>
-      <c r="I44" t="s">
         <v>37</v>
       </c>
-      <c r="K44">
+      <c r="G44" t="s">
+        <v>47</v>
+      </c>
+      <c r="J44" t="s">
+        <v>39</v>
+      </c>
+      <c r="L44">
         <v>6</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4</v>
       </c>
-      <c r="M44">
-        <v>1</v>
-      </c>
       <c r="N44">
         <v>1</v>
       </c>
-      <c r="P44" s="2">
+      <c r="O44">
+        <v>1</v>
+      </c>
+      <c r="Q44" s="2">
         <v>15</v>
       </c>
-      <c r="Q44">
-        <v>2</v>
-      </c>
-      <c r="R44" s="3">
-        <v>2</v>
-      </c>
-      <c r="S44" s="2">
+      <c r="R44">
+        <v>2</v>
+      </c>
+      <c r="S44" s="3">
+        <v>2</v>
+      </c>
+      <c r="T44" s="2">
         <v>42</v>
       </c>
-      <c r="T44">
+      <c r="U44">
         <v>8</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>12</v>
       </c>
     </row>
-    <row r="45" hidden="1" spans="1:31">
+    <row r="45" spans="1:32">
       <c r="A45">
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="C45" t="s">
-        <v>129</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E45" t="s">
-        <v>40</v>
+        <v>146</v>
+      </c>
+      <c r="D45" t="s">
+        <v>146</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="F45" t="s">
-        <v>54</v>
-      </c>
-      <c r="I45" t="s">
-        <v>37</v>
-      </c>
-      <c r="J45"/>
-      <c r="K45" s="2">
+        <v>43</v>
+      </c>
+      <c r="G45" t="s">
+        <v>62</v>
+      </c>
+      <c r="J45" t="s">
+        <v>39</v>
+      </c>
+      <c r="K45"/>
+      <c r="L45" s="2">
         <v>5</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4</v>
       </c>
-      <c r="M45">
-        <v>0</v>
-      </c>
       <c r="N45">
-        <v>1</v>
-      </c>
-      <c r="O45"/>
-      <c r="P45" s="2">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>1</v>
+      </c>
+      <c r="P45"/>
+      <c r="Q45" s="2">
         <v>7</v>
       </c>
-      <c r="Q45">
+      <c r="R45">
         <v>7</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>9</v>
       </c>
-      <c r="S45" s="2">
+      <c r="T45" s="2">
         <v>26</v>
       </c>
-      <c r="T45">
-        <v>2</v>
-      </c>
-      <c r="U45" s="3">
-        <v>2</v>
-      </c>
-      <c r="V45" s="2">
-        <v>2</v>
-      </c>
-      <c r="W45">
+      <c r="U45">
+        <v>2</v>
+      </c>
+      <c r="V45" s="3">
+        <v>2</v>
+      </c>
+      <c r="W45" s="2">
+        <v>2</v>
+      </c>
+      <c r="X45">
         <v>7</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>8</v>
       </c>
-      <c r="AA45"/>
-      <c r="AC45"/>
-      <c r="AE45"/>
-    </row>
-    <row r="46" hidden="1" spans="1:31">
+      <c r="AB45"/>
+      <c r="AD45"/>
+      <c r="AF45"/>
+    </row>
+    <row r="46" spans="1:32">
       <c r="A46">
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="C46" t="s">
-        <v>131</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E46" t="s">
+        <v>148</v>
+      </c>
+      <c r="D46" t="s">
+        <v>148</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F46" t="s">
+        <v>43</v>
+      </c>
+      <c r="G46" t="s">
+        <v>38</v>
+      </c>
+      <c r="J46" t="s">
+        <v>39</v>
+      </c>
+      <c r="K46"/>
+      <c r="L46" s="2">
+        <v>10</v>
+      </c>
+      <c r="M46" s="3">
+        <v>6</v>
+      </c>
+      <c r="N46">
+        <v>1</v>
+      </c>
+      <c r="O46">
+        <v>1</v>
+      </c>
+      <c r="P46"/>
+      <c r="Q46" s="2">
+        <v>32</v>
+      </c>
+      <c r="R46">
         <v>40</v>
       </c>
-      <c r="F46" t="s">
-        <v>36</v>
-      </c>
-      <c r="I46" t="s">
-        <v>37</v>
-      </c>
-      <c r="J46"/>
-      <c r="K46" s="2">
-        <v>10</v>
-      </c>
-      <c r="L46" s="3">
-        <v>6</v>
-      </c>
-      <c r="M46">
-        <v>1</v>
-      </c>
-      <c r="N46">
-        <v>1</v>
-      </c>
-      <c r="O46"/>
-      <c r="P46" s="2">
-        <v>32</v>
-      </c>
-      <c r="Q46">
+      <c r="S46" s="3">
         <v>40</v>
       </c>
-      <c r="R46" s="3">
-        <v>40</v>
-      </c>
-      <c r="S46" s="2">
+      <c r="T46" s="2">
         <v>33</v>
       </c>
-      <c r="T46">
+      <c r="U46">
         <v>30</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>30</v>
       </c>
-      <c r="V46" s="2">
+      <c r="W46" s="2">
         <v>19</v>
       </c>
-      <c r="W46">
-        <v>1</v>
-      </c>
-      <c r="X46" s="3">
-        <v>1</v>
-      </c>
-      <c r="AA46"/>
-      <c r="AC46"/>
-      <c r="AE46"/>
-    </row>
-    <row r="47" hidden="1" spans="1:31">
+      <c r="X46">
+        <v>1</v>
+      </c>
+      <c r="Y46" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB46"/>
+      <c r="AD46"/>
+      <c r="AF46"/>
+    </row>
+    <row r="47" spans="1:32">
       <c r="A47">
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="C47" t="s">
-        <v>133</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E47" t="s">
-        <v>35</v>
+        <v>150</v>
+      </c>
+      <c r="D47" t="s">
+        <v>150</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="F47" t="s">
-        <v>54</v>
-      </c>
-      <c r="I47" t="s">
         <v>37</v>
       </c>
-      <c r="J47"/>
-      <c r="K47" s="2">
-        <v>2</v>
-      </c>
-      <c r="L47" s="3">
-        <v>1</v>
-      </c>
-      <c r="M47">
-        <v>0</v>
+      <c r="G47" t="s">
+        <v>62</v>
+      </c>
+      <c r="J47" t="s">
+        <v>39</v>
+      </c>
+      <c r="K47"/>
+      <c r="L47" s="2">
+        <v>2</v>
+      </c>
+      <c r="M47" s="3">
+        <v>1</v>
       </c>
       <c r="N47">
         <v>0</v>
       </c>
-      <c r="O47"/>
-      <c r="P47" s="2">
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47"/>
+      <c r="Q47" s="2">
         <v>11</v>
       </c>
-      <c r="Q47">
+      <c r="R47">
         <v>10</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>14</v>
       </c>
-      <c r="U47"/>
-      <c r="X47"/>
-      <c r="AA47"/>
-      <c r="AC47"/>
-      <c r="AE47"/>
-    </row>
-    <row r="48" hidden="1" spans="1:31">
+      <c r="V47"/>
+      <c r="Y47"/>
+      <c r="AB47"/>
+      <c r="AD47"/>
+      <c r="AF47"/>
+    </row>
+    <row r="48" spans="1:32">
       <c r="A48">
         <v>49</v>
       </c>
@@ -4722,742 +4912,776 @@
         <v>123</v>
       </c>
       <c r="C48" t="s">
-        <v>134</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E48" t="s">
-        <v>35</v>
+        <v>151</v>
+      </c>
+      <c r="D48" t="s">
+        <v>151</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="F48" t="s">
-        <v>35</v>
-      </c>
-      <c r="I48" t="s">
         <v>37</v>
       </c>
-      <c r="J48"/>
-      <c r="K48" s="2">
+      <c r="G48" t="s">
+        <v>37</v>
+      </c>
+      <c r="J48" t="s">
+        <v>39</v>
+      </c>
+      <c r="K48"/>
+      <c r="L48" s="2">
         <v>4</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3</v>
       </c>
-      <c r="M48">
-        <v>0</v>
-      </c>
       <c r="N48">
         <v>0</v>
       </c>
-      <c r="O48"/>
-      <c r="P48" s="2">
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48"/>
+      <c r="Q48" s="2">
         <v>11</v>
       </c>
-      <c r="Q48">
+      <c r="R48">
         <v>8</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>11</v>
       </c>
-      <c r="S48" s="2">
+      <c r="T48" s="2">
         <v>6</v>
       </c>
-      <c r="T48">
+      <c r="U48">
         <v>3</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3</v>
       </c>
-      <c r="X48"/>
-      <c r="AA48"/>
-      <c r="AC48"/>
-      <c r="AE48"/>
-    </row>
-    <row r="49" spans="1:21">
+      <c r="Y48"/>
+      <c r="AB48"/>
+      <c r="AD48"/>
+      <c r="AF48"/>
+    </row>
+    <row r="49" spans="1:22">
       <c r="A49">
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="C49" t="s">
-        <v>136</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E49" t="s">
-        <v>35</v>
+        <v>153</v>
+      </c>
+      <c r="D49" t="s">
+        <v>153</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="F49" t="s">
-        <v>43</v>
-      </c>
-      <c r="I49" t="s">
         <v>37</v>
       </c>
-      <c r="K49">
+      <c r="G49" t="s">
+        <v>47</v>
+      </c>
+      <c r="J49" t="s">
+        <v>39</v>
+      </c>
+      <c r="L49">
         <v>4</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3</v>
       </c>
-      <c r="M49">
-        <v>0</v>
-      </c>
       <c r="N49">
         <v>0</v>
       </c>
-      <c r="P49" s="2">
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="2">
         <v>11</v>
       </c>
-      <c r="Q49">
+      <c r="R49">
         <v>7</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>11</v>
       </c>
-      <c r="S49" s="2">
+      <c r="T49" s="2">
         <v>45</v>
       </c>
-      <c r="T49">
-        <v>2</v>
-      </c>
-      <c r="U49" s="3">
+      <c r="U49">
+        <v>2</v>
+      </c>
+      <c r="V49" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="50" hidden="1" spans="1:31">
+    <row r="50" spans="1:32">
       <c r="A50">
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="C50" t="s">
-        <v>138</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E50" t="s">
-        <v>35</v>
+        <v>155</v>
+      </c>
+      <c r="D50" t="s">
+        <v>155</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="F50" t="s">
-        <v>35</v>
-      </c>
-      <c r="I50" t="s">
         <v>37</v>
       </c>
-      <c r="J50"/>
-      <c r="K50" s="2">
+      <c r="G50" t="s">
+        <v>37</v>
+      </c>
+      <c r="J50" t="s">
+        <v>39</v>
+      </c>
+      <c r="K50"/>
+      <c r="L50" s="2">
         <v>5</v>
       </c>
-      <c r="L50" s="3">
+      <c r="M50" s="3">
         <v>4</v>
       </c>
-      <c r="M50">
-        <v>1</v>
-      </c>
       <c r="N50">
         <v>1</v>
       </c>
-      <c r="O50"/>
-      <c r="P50" s="2">
+      <c r="O50">
+        <v>1</v>
+      </c>
+      <c r="P50"/>
+      <c r="Q50" s="2">
         <v>6</v>
       </c>
-      <c r="Q50">
+      <c r="R50">
         <v>5</v>
       </c>
-      <c r="R50" s="3">
+      <c r="S50" s="3">
         <v>7</v>
       </c>
-      <c r="S50" s="2">
+      <c r="T50" s="2">
         <v>18</v>
       </c>
-      <c r="T50">
+      <c r="U50">
         <v>1.1</v>
       </c>
-      <c r="U50" s="3">
+      <c r="V50" s="3">
         <v>1.7</v>
       </c>
-      <c r="X50"/>
-      <c r="AA50"/>
-      <c r="AC50"/>
-      <c r="AE50"/>
-    </row>
-    <row r="51" hidden="1" spans="1:31">
+      <c r="Y50"/>
+      <c r="AB50"/>
+      <c r="AD50"/>
+      <c r="AF50"/>
+    </row>
+    <row r="51" spans="1:32">
       <c r="A51">
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="C51" t="s">
-        <v>140</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E51" t="s">
-        <v>40</v>
+        <v>157</v>
+      </c>
+      <c r="D51" t="s">
+        <v>157</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="F51" t="s">
-        <v>35</v>
-      </c>
-      <c r="I51" t="s">
+        <v>43</v>
+      </c>
+      <c r="G51" t="s">
         <v>37</v>
       </c>
-      <c r="J51"/>
-      <c r="K51" s="2">
+      <c r="J51" t="s">
+        <v>39</v>
+      </c>
+      <c r="K51"/>
+      <c r="L51" s="2">
         <v>9</v>
       </c>
-      <c r="L51" s="3">
+      <c r="M51" s="3">
         <v>6</v>
       </c>
-      <c r="M51">
-        <v>1</v>
-      </c>
       <c r="N51">
         <v>1</v>
       </c>
-      <c r="O51"/>
-      <c r="P51" s="2">
+      <c r="O51">
+        <v>1</v>
+      </c>
+      <c r="P51"/>
+      <c r="Q51" s="2">
         <v>6</v>
       </c>
-      <c r="Q51">
-        <v>1</v>
-      </c>
-      <c r="R51" s="3">
+      <c r="R51">
+        <v>1</v>
+      </c>
+      <c r="S51" s="3">
         <v>3</v>
       </c>
-      <c r="S51" s="2">
+      <c r="T51" s="2">
         <v>49</v>
       </c>
-      <c r="T51">
-        <v>1</v>
-      </c>
-      <c r="U51" s="3">
-        <v>1</v>
-      </c>
-      <c r="X51"/>
-      <c r="AA51"/>
-      <c r="AC51"/>
-      <c r="AE51"/>
-    </row>
-    <row r="52" hidden="1" spans="1:31">
+      <c r="U51">
+        <v>1</v>
+      </c>
+      <c r="V51" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y51"/>
+      <c r="AB51"/>
+      <c r="AD51"/>
+      <c r="AF51"/>
+    </row>
+    <row r="52" spans="1:32">
       <c r="A52">
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="C52" t="s">
-        <v>142</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E52" t="s">
-        <v>40</v>
+        <v>159</v>
+      </c>
+      <c r="D52" t="s">
+        <v>159</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="F52" t="s">
-        <v>36</v>
-      </c>
-      <c r="I52" t="s">
-        <v>37</v>
-      </c>
-      <c r="J52"/>
-      <c r="K52" s="2">
-        <v>1</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
-      <c r="M52">
-        <v>1</v>
+        <v>43</v>
+      </c>
+      <c r="G52" t="s">
+        <v>38</v>
+      </c>
+      <c r="J52" t="s">
+        <v>39</v>
+      </c>
+      <c r="K52"/>
+      <c r="L52" s="2">
+        <v>1</v>
+      </c>
+      <c r="M52" s="3">
+        <v>0</v>
       </c>
       <c r="N52">
         <v>1</v>
       </c>
-      <c r="O52"/>
-      <c r="P52" s="2">
+      <c r="O52">
+        <v>1</v>
+      </c>
+      <c r="P52"/>
+      <c r="Q52" s="2">
         <v>9</v>
       </c>
-      <c r="Q52">
-        <v>2</v>
-      </c>
-      <c r="R52" s="3">
-        <v>2</v>
-      </c>
-      <c r="S52" s="2">
+      <c r="R52">
+        <v>2</v>
+      </c>
+      <c r="S52" s="3">
+        <v>2</v>
+      </c>
+      <c r="T52" s="2">
         <v>21</v>
       </c>
-      <c r="T52">
-        <v>2</v>
-      </c>
-      <c r="U52" s="3">
-        <v>2</v>
-      </c>
-      <c r="X52"/>
-      <c r="AA52"/>
-      <c r="AC52"/>
-      <c r="AE52"/>
-    </row>
-    <row r="53" spans="1:21">
+      <c r="U52">
+        <v>2</v>
+      </c>
+      <c r="V52" s="3">
+        <v>2</v>
+      </c>
+      <c r="Y52"/>
+      <c r="AB52"/>
+      <c r="AD52"/>
+      <c r="AF52"/>
+    </row>
+    <row r="53" spans="1:22">
       <c r="A53">
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="C53" t="s">
-        <v>144</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E53" t="s">
-        <v>35</v>
+        <v>161</v>
+      </c>
+      <c r="D53" t="s">
+        <v>161</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="F53" t="s">
-        <v>43</v>
-      </c>
-      <c r="I53" t="s">
         <v>37</v>
       </c>
-      <c r="K53">
+      <c r="G53" t="s">
+        <v>47</v>
+      </c>
+      <c r="J53" t="s">
+        <v>39</v>
+      </c>
+      <c r="L53">
         <v>5</v>
       </c>
-      <c r="L53" s="3">
+      <c r="M53" s="3">
         <v>5</v>
       </c>
-      <c r="M53">
-        <v>0</v>
-      </c>
       <c r="N53">
-        <v>1</v>
-      </c>
-      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>1</v>
+      </c>
+      <c r="P53" s="3">
         <v>6</v>
       </c>
-      <c r="P53">
+      <c r="Q53">
         <v>50</v>
       </c>
-      <c r="Q53">
+      <c r="R53">
         <v>3</v>
       </c>
-      <c r="R53" s="3">
+      <c r="S53" s="3">
         <v>4</v>
       </c>
-      <c r="S53">
+      <c r="T53">
         <v>51</v>
       </c>
-      <c r="T53">
+      <c r="U53">
         <v>-0.5</v>
       </c>
-      <c r="U53" s="3">
+      <c r="V53" s="3">
         <v>-0.5</v>
       </c>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:25">
       <c r="A54">
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="C54" t="s">
-        <v>146</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E54" t="s">
-        <v>40</v>
+        <v>163</v>
+      </c>
+      <c r="D54" t="s">
+        <v>163</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="F54" t="s">
         <v>43</v>
       </c>
-      <c r="I54" t="s">
-        <v>49</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="G54" t="s">
+        <v>47</v>
+      </c>
+      <c r="J54" t="s">
+        <v>55</v>
+      </c>
+      <c r="K54" s="3">
         <v>14</v>
       </c>
-      <c r="K54">
-        <v>2</v>
-      </c>
-      <c r="L54" s="3">
-        <v>1</v>
-      </c>
-      <c r="M54">
-        <v>0</v>
+      <c r="L54">
+        <v>2</v>
+      </c>
+      <c r="M54" s="3">
+        <v>1</v>
       </c>
       <c r="N54">
-        <v>1</v>
-      </c>
-      <c r="P54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>1</v>
+      </c>
+      <c r="Q54">
         <v>15</v>
       </c>
-      <c r="Q54">
+      <c r="R54">
         <v>3</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4</v>
       </c>
-      <c r="S54">
+      <c r="T54">
         <v>14</v>
       </c>
-      <c r="T54">
-        <v>1</v>
-      </c>
-      <c r="U54" s="3">
-        <v>1</v>
-      </c>
-      <c r="V54">
+      <c r="U54">
+        <v>1</v>
+      </c>
+      <c r="V54" s="3">
+        <v>1</v>
+      </c>
+      <c r="W54">
         <v>52</v>
       </c>
-      <c r="W54">
+      <c r="X54">
         <v>3</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:30">
+    <row r="55" spans="1:31">
       <c r="A55">
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="C55" t="s">
-        <v>148</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E55" t="s">
-        <v>40</v>
+        <v>165</v>
+      </c>
+      <c r="D55" t="s">
+        <v>165</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="F55" t="s">
         <v>43</v>
       </c>
-      <c r="I55" t="s">
-        <v>37</v>
-      </c>
-      <c r="K55">
+      <c r="G55" t="s">
+        <v>47</v>
+      </c>
+      <c r="J55" t="s">
+        <v>39</v>
+      </c>
+      <c r="L55">
         <v>4</v>
       </c>
-      <c r="L55" s="3">
+      <c r="M55" s="3">
         <v>3</v>
       </c>
-      <c r="M55">
-        <v>1</v>
-      </c>
       <c r="N55">
         <v>1</v>
       </c>
-      <c r="P55">
+      <c r="O55">
+        <v>1</v>
+      </c>
+      <c r="Q55">
         <v>15</v>
       </c>
-      <c r="Q55">
-        <v>1</v>
-      </c>
-      <c r="R55" s="3">
+      <c r="R55">
+        <v>1</v>
+      </c>
+      <c r="S55" s="3">
         <v>3</v>
       </c>
-      <c r="S55">
+      <c r="T55">
         <v>60</v>
       </c>
-      <c r="T55">
-        <v>1</v>
-      </c>
-      <c r="U55" s="3">
-        <v>1</v>
-      </c>
-      <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="1:30">
+      <c r="U55">
+        <v>1</v>
+      </c>
+      <c r="V55" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="1:31">
       <c r="A56">
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="C56" t="s">
-        <v>150</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E56" t="s">
-        <v>35</v>
+        <v>167</v>
+      </c>
+      <c r="D56" t="s">
+        <v>167</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="F56" t="s">
-        <v>43</v>
-      </c>
-      <c r="I56" t="s">
-        <v>49</v>
-      </c>
-      <c r="J56" s="3">
+        <v>37</v>
+      </c>
+      <c r="G56" t="s">
+        <v>47</v>
+      </c>
+      <c r="J56" t="s">
+        <v>55</v>
+      </c>
+      <c r="K56" s="3">
         <v>3</v>
       </c>
-      <c r="K56">
-        <v>2</v>
-      </c>
-      <c r="L56" s="3">
-        <v>1</v>
-      </c>
-      <c r="M56">
-        <v>0</v>
+      <c r="L56">
+        <v>2</v>
+      </c>
+      <c r="M56" s="3">
+        <v>1</v>
       </c>
       <c r="N56">
-        <v>1</v>
-      </c>
-      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>1</v>
+      </c>
+      <c r="Q56">
         <v>45</v>
       </c>
-      <c r="Q56">
+      <c r="R56">
         <v>3</v>
       </c>
-      <c r="R56" s="3">
+      <c r="S56" s="3">
         <v>4</v>
       </c>
-      <c r="S56">
+      <c r="T56">
         <v>11</v>
       </c>
-      <c r="T56">
+      <c r="U56">
         <v>12</v>
       </c>
-      <c r="U56" s="3">
+      <c r="V56" s="3">
         <v>18</v>
       </c>
-      <c r="V56">
+      <c r="W56">
         <v>14</v>
       </c>
-      <c r="W56">
-        <v>1</v>
-      </c>
-      <c r="X56" s="3">
-        <v>1</v>
-      </c>
-      <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="1:21">
+      <c r="X56">
+        <v>1</v>
+      </c>
+      <c r="Y56" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="1:22">
       <c r="A57">
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="C57" t="s">
-        <v>152</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E57" t="s">
-        <v>35</v>
+        <v>169</v>
+      </c>
+      <c r="D57" t="s">
+        <v>169</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="F57" t="s">
-        <v>43</v>
-      </c>
-      <c r="I57" t="s">
-        <v>49</v>
-      </c>
-      <c r="J57" s="3">
+        <v>37</v>
+      </c>
+      <c r="G57" t="s">
+        <v>47</v>
+      </c>
+      <c r="J57" t="s">
+        <v>55</v>
+      </c>
+      <c r="K57" s="3">
         <v>3</v>
       </c>
-      <c r="K57">
-        <v>2</v>
-      </c>
-      <c r="L57" s="3">
-        <v>1</v>
-      </c>
-      <c r="M57">
+      <c r="L57">
+        <v>2</v>
+      </c>
+      <c r="M57" s="3">
         <v>1</v>
       </c>
       <c r="N57">
         <v>1</v>
       </c>
-      <c r="P57">
-        <v>2</v>
+      <c r="O57">
+        <v>1</v>
       </c>
       <c r="Q57">
+        <v>2</v>
+      </c>
+      <c r="R57">
         <v>5</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6</v>
       </c>
-      <c r="S57">
-        <v>2</v>
-      </c>
       <c r="T57">
+        <v>2</v>
+      </c>
+      <c r="U57">
         <v>5</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:14">
+    <row r="58" spans="1:15">
       <c r="A58">
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="C58" t="s">
-        <v>154</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E58" t="s">
-        <v>35</v>
+        <v>171</v>
+      </c>
+      <c r="D58" t="s">
+        <v>171</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="F58" t="s">
-        <v>43</v>
-      </c>
-      <c r="I58" t="s">
         <v>37</v>
       </c>
-      <c r="K58">
+      <c r="G58" t="s">
+        <v>47</v>
+      </c>
+      <c r="J58" t="s">
+        <v>39</v>
+      </c>
+      <c r="L58">
         <v>3</v>
       </c>
-      <c r="L58" s="3">
-        <v>2</v>
-      </c>
-      <c r="M58">
-        <v>1</v>
+      <c r="M58" s="3">
+        <v>2</v>
       </c>
       <c r="N58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:18">
+        <v>1</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19">
       <c r="A59">
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="C59" t="s">
-        <v>156</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E59" t="s">
-        <v>35</v>
+        <v>173</v>
+      </c>
+      <c r="D59" t="s">
+        <v>173</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="F59" t="s">
-        <v>43</v>
-      </c>
-      <c r="I59" t="s">
         <v>37</v>
       </c>
-      <c r="K59">
+      <c r="G59" t="s">
+        <v>47</v>
+      </c>
+      <c r="J59" t="s">
+        <v>39</v>
+      </c>
+      <c r="L59">
         <v>4</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3</v>
       </c>
-      <c r="M59">
-        <v>1</v>
-      </c>
       <c r="N59">
-        <v>0</v>
-      </c>
-      <c r="P59">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
       </c>
       <c r="Q59">
+        <v>2</v>
+      </c>
+      <c r="R59">
         <v>7</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:14">
+    <row r="60" spans="1:15">
       <c r="A60">
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="C60" t="s">
-        <v>158</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E60" t="s">
-        <v>35</v>
+        <v>175</v>
+      </c>
+      <c r="D60" t="s">
+        <v>175</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="F60" t="s">
-        <v>43</v>
-      </c>
-      <c r="I60" t="s">
         <v>37</v>
       </c>
-      <c r="K60">
-        <v>2</v>
-      </c>
-      <c r="L60" s="3">
-        <v>2</v>
-      </c>
-      <c r="M60">
-        <v>1</v>
+      <c r="G60" t="s">
+        <v>47</v>
+      </c>
+      <c r="J60" t="s">
+        <v>39</v>
+      </c>
+      <c r="L60">
+        <v>2</v>
+      </c>
+      <c r="M60" s="3">
+        <v>2</v>
       </c>
       <c r="N60">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" hidden="1" spans="1:14">
+      <c r="O60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15">
       <c r="A61">
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="C61" t="s">
-        <v>160</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E61" t="s">
-        <v>35</v>
-      </c>
-      <c r="I61" t="s">
-        <v>49</v>
-      </c>
-      <c r="J61" s="3">
+        <v>177</v>
+      </c>
+      <c r="D61" t="s">
+        <v>177</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F61" t="s">
+        <v>37</v>
+      </c>
+      <c r="J61" t="s">
+        <v>55</v>
+      </c>
+      <c r="K61" s="3">
         <v>14</v>
       </c>
-      <c r="K61">
+      <c r="L61">
         <v>3</v>
       </c>
-      <c r="L61" s="3">
-        <v>2</v>
-      </c>
-      <c r="M61">
-        <v>0</v>
+      <c r="M61" s="3">
+        <v>2</v>
       </c>
       <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AG61" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="C"/>
-      </filters>
-    </filterColumn>
-    <extLst/>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
@@ -5492,22 +5716,22 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E1" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="G1" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="H1" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="I1" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5515,13 +5739,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="C2" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="D2" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="I2">
         <v>-1</v>
@@ -5532,19 +5756,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="C3" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="D3" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="E3" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="F3" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -5555,16 +5779,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="C4" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="D4" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="E4" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -5575,16 +5799,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="C5" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="D5" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="E5" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -5595,13 +5819,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="C6" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="D6" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -5612,16 +5836,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="C7" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="D7" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="E7" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -5632,13 +5856,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="C8" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="D8" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -5652,13 +5876,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="C9" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="D9" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -5672,13 +5896,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="C10" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="D10" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -5692,13 +5916,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="C11" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="D11" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -5709,16 +5933,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="C12" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="D12" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="E12" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -5729,16 +5953,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="C13" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="D13" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="E13" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -5749,19 +5973,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="C14" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="D14" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -5772,16 +5996,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="C15" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="D15" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="E15" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -5792,16 +6016,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="C16" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="D16" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="E16" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -5812,13 +6036,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="C17" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="D17" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -5832,16 +6056,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="C18" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="D18" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="E18" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -5852,13 +6076,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="C19" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="D19" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -5872,13 +6096,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="C20" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="D20" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -5892,16 +6116,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="C21" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="D21" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="E21" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -5912,16 +6136,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="C22" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="D22" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="E22" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -5932,13 +6156,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="C23" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="D23" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="E23">
         <v>5</v>
@@ -5952,19 +6176,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="C24" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="D24" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -5975,13 +6199,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="C25" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="D25" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -5995,16 +6219,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="C26" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="D26" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="E26" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -6018,16 +6242,16 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="C27" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="D27" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="E27" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -6038,13 +6262,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="C28" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="D28" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -6058,19 +6282,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="C29" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="D29" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -6084,13 +6308,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="C30" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="D30" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -6104,19 +6328,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="C31" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="D31" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="E31" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="F31" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -6127,19 +6351,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="C32" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="D32" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="E32">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -6150,19 +6374,19 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="C33" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="D33" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="E33">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -6173,16 +6397,16 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="C34" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="D34" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="E34" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -6193,16 +6417,16 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="C35" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="D35" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="E35" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -6213,19 +6437,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C36" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="D36" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="E36" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="F36" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -6239,13 +6463,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="C37" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="D37" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="E37">
         <v>11</v>
@@ -6259,16 +6483,16 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="C38" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="D38" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="E38" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -6279,13 +6503,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="C39" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="D39" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -6302,16 +6526,16 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="C40" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="D40" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="E40" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -6322,13 +6546,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="C41" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="D41" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -6345,19 +6569,19 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="C42" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="D42" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -6371,13 +6595,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="C43" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="D43" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="E43">
         <v>12</v>
@@ -6391,13 +6615,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="C44" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="D44" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="E44">
         <v>13</v>
@@ -6411,19 +6635,19 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="C45" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="D45" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="E45" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="F45" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="I45">
         <v>-1</v>
@@ -6434,16 +6658,16 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="D46" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="E46" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="I46">
         <v>1</v>
@@ -6454,13 +6678,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="C47" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="D47" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="E47">
         <v>14</v>
@@ -6474,19 +6698,19 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="C48" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="D48" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="I48">
         <v>-1</v>
@@ -6497,13 +6721,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="C49" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="D49" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="E49">
         <v>15</v>
@@ -6517,19 +6741,19 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="C50" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="D50" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="I50">
         <v>-1</v>
@@ -6540,13 +6764,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="C51" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="D51" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="E51">
         <v>16</v>
@@ -6560,13 +6784,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="C52" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="D52" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -6580,13 +6804,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="C53" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="D53" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="E53">
         <v>3</v>
@@ -6600,13 +6824,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="C54" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="D54" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="E54">
         <v>3</v>
@@ -6623,16 +6847,16 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="C55" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="D55" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="E55" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="G55">
         <v>6</v>
@@ -6646,16 +6870,16 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="C56" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="D56" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="E56" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="G56">
         <v>7</v>
@@ -6669,16 +6893,16 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="C57" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="D57" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="E57" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="G57">
         <v>8</v>
@@ -6692,16 +6916,16 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="C58" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D58" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="E58" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="G58">
         <v>6</v>
@@ -6715,16 +6939,16 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="C59" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D59" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="E59" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="G59">
         <v>7</v>
@@ -6738,16 +6962,16 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="C60" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D60" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="E60" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="G60">
         <v>8</v>
@@ -6761,19 +6985,19 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="C61" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="D61" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="E61">
         <v>3</v>
       </c>
       <c r="F61" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="I61">
         <v>-1</v>
@@ -6784,13 +7008,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="C62" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="D62" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="E62">
         <v>20</v>
@@ -6832,43 +7056,43 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="D1" t="s">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="F1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N1" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="O1" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6876,10 +7100,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="C2" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -6905,10 +7129,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="C3" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -6928,10 +7152,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="C4" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -6945,10 +7169,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="C5" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -6980,10 +7204,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="C6" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -7003,10 +7227,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>274</v>
+        <v>291</v>
       </c>
       <c r="C7" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -7026,10 +7250,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="C8" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -7049,10 +7273,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="C9" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -7072,10 +7296,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="C10" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -7095,10 +7319,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="C11" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -7124,10 +7348,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="C12" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -7153,10 +7377,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="C13" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -7176,10 +7400,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="C14" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -7199,10 +7423,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="C15" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -7222,10 +7446,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="C16" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -7245,10 +7469,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="C17" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -7268,10 +7492,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="C18" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -7291,10 +7515,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="C19" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -7308,10 +7532,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="C20" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -7325,10 +7549,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="C21" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -7342,10 +7566,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C22" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -7390,19 +7614,19 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="E1" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="F1" t="s">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="G1" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -7410,13 +7634,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="C2" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="D2" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -7430,16 +7654,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>290</v>
+        <v>307</v>
       </c>
       <c r="C3" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="D3" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" ht="12.95" customHeight="1" spans="1:6">
@@ -7447,16 +7671,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="C4" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="D4" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="F4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -7464,13 +7688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="C5" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="D5" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -7484,13 +7708,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="C6" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="D6" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -7504,13 +7728,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>295</v>
+        <v>312</v>
       </c>
       <c r="C7" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="D7" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -7524,13 +7748,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="C8" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="D8" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -7544,13 +7768,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="C9" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="D9" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -7564,13 +7788,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="C10" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="D10" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -7584,16 +7808,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="C11" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="D11" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="E11" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F11">
         <v>2</v>

--- a/Assets/StreamingAssets/Configurations/Cards.xlsx
+++ b/Assets/StreamingAssets/Configurations/Cards.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView windowWidth="24750" windowHeight="10480" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="327">
   <si>
     <t>ID</t>
   </si>
@@ -179,6 +179,9 @@
     <t>C</t>
   </si>
   <si>
+    <t>angry</t>
+  </si>
+  <si>
     <t>战术喝水</t>
   </si>
   <si>
@@ -377,6 +380,9 @@
     <t>神采+6</t>
   </si>
   <si>
+    <t>fun</t>
+  </si>
+  <si>
     <t>SC</t>
   </si>
   <si>
@@ -791,6 +797,9 @@
     <t>有红温时，专注+X</t>
   </si>
   <si>
+    <t>体力+X</t>
+  </si>
+  <si>
     <t>体力回复X点</t>
   </si>
   <si>
@@ -872,6 +881,21 @@
     <t>每当使用A卡，红温+1</t>
   </si>
   <si>
+    <t>回合开始时，抽X张卡牌</t>
+  </si>
+  <si>
+    <t>回合开始时，抽1张卡牌</t>
+  </si>
+  <si>
+    <t>红温变成X倍</t>
+  </si>
+  <si>
+    <t>回合结束时，幽默+X</t>
+  </si>
+  <si>
+    <t>回合结束时，幽默+1</t>
+  </si>
+  <si>
     <t>BuffType</t>
   </si>
   <si>
@@ -933,6 +957,9 @@
   </si>
   <si>
     <t>每当使用A卡时，红温+1</t>
+  </si>
+  <si>
+    <t>回合开始时，抽一张卡</t>
   </si>
   <si>
     <t>OperatorType</t>
@@ -1964,7 +1991,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AH61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
@@ -2102,7 +2129,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:33">
+    <row r="2" hidden="1" spans="1:33">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2157,7 +2184,7 @@
       <c r="AF2"/>
       <c r="AG2" s="5"/>
     </row>
-    <row r="3" spans="1:33">
+    <row r="3" hidden="1" spans="1:33">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2234,6 +2261,9 @@
       <c r="G4" t="s">
         <v>47</v>
       </c>
+      <c r="H4" t="s">
+        <v>48</v>
+      </c>
       <c r="J4" t="s">
         <v>39</v>
       </c>
@@ -2269,18 +2299,18 @@
       </c>
       <c r="AG4" s="5"/>
     </row>
-    <row r="5" spans="1:33">
+    <row r="5" hidden="1" spans="1:33">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>36</v>
@@ -2337,16 +2367,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F6" t="s">
         <v>43</v>
@@ -2354,8 +2384,11 @@
       <c r="G6" t="s">
         <v>47</v>
       </c>
+      <c r="H6" t="s">
+        <v>48</v>
+      </c>
       <c r="J6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K6" s="3">
         <v>3</v>
@@ -2395,21 +2428,21 @@
       </c>
       <c r="AG6" s="5"/>
     </row>
-    <row r="7" spans="1:33">
+    <row r="7" hidden="1" spans="1:33">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F7" t="s">
         <v>43</v>
@@ -2461,30 +2494,30 @@
       <c r="AF7"/>
       <c r="AG7" s="5"/>
     </row>
-    <row r="8" spans="1:33">
+    <row r="8" hidden="1" spans="1:33">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F8" t="s">
         <v>43</v>
       </c>
       <c r="G8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -2534,18 +2567,18 @@
       <c r="AF8"/>
       <c r="AG8" s="5"/>
     </row>
-    <row r="9" spans="1:33">
+    <row r="9" hidden="1" spans="1:33">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>36</v>
@@ -2597,18 +2630,18 @@
       <c r="AF9"/>
       <c r="AG9" s="5"/>
     </row>
-    <row r="10" spans="1:33">
+    <row r="10" hidden="1" spans="1:33">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>36</v>
@@ -2617,7 +2650,7 @@
         <v>43</v>
       </c>
       <c r="G10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J10" t="s">
         <v>39</v>
@@ -2665,13 +2698,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>36</v>
@@ -2682,6 +2715,9 @@
       <c r="G11" t="s">
         <v>47</v>
       </c>
+      <c r="H11" t="s">
+        <v>48</v>
+      </c>
       <c r="J11" t="s">
         <v>39</v>
       </c>
@@ -2717,18 +2753,18 @@
       </c>
       <c r="AG11" s="5"/>
     </row>
-    <row r="12" spans="1:34">
+    <row r="12" hidden="1" spans="1:34">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>36</v>
@@ -2737,7 +2773,7 @@
         <v>37</v>
       </c>
       <c r="G12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J12" t="s">
         <v>39</v>
@@ -2780,24 +2816,24 @@
       <c r="AF12"/>
       <c r="AG12" s="5"/>
       <c r="AH12" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:33">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" hidden="1" spans="1:33">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F13" t="s">
         <v>37</v>
@@ -2846,18 +2882,18 @@
       <c r="AF13"/>
       <c r="AG13" s="5"/>
     </row>
-    <row r="14" spans="1:33">
+    <row r="14" hidden="1" spans="1:33">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>36</v>
@@ -2901,21 +2937,21 @@
       <c r="AF14"/>
       <c r="AG14" s="5"/>
     </row>
-    <row r="15" spans="1:33">
+    <row r="15" hidden="1" spans="1:33">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F15" t="s">
         <v>37</v>
@@ -2956,21 +2992,21 @@
       <c r="AF15"/>
       <c r="AG15" s="5"/>
     </row>
-    <row r="16" spans="1:33">
+    <row r="16" hidden="1" spans="1:33">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F16" t="s">
         <v>37</v>
@@ -3019,21 +3055,21 @@
       <c r="AF16"/>
       <c r="AG16" s="5"/>
     </row>
-    <row r="17" spans="1:33">
+    <row r="17" hidden="1" spans="1:33">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F17" t="s">
         <v>43</v>
@@ -3042,7 +3078,7 @@
         <v>38</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J17" t="s">
         <v>39</v>
@@ -3098,16 +3134,16 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F18" t="s">
         <v>43</v>
@@ -3115,6 +3151,9 @@
       <c r="G18" t="s">
         <v>47</v>
       </c>
+      <c r="H18" t="s">
+        <v>48</v>
+      </c>
       <c r="J18" t="s">
         <v>39</v>
       </c>
@@ -3147,27 +3186,27 @@
       </c>
       <c r="AG18" s="5"/>
     </row>
-    <row r="19" spans="1:33">
+    <row r="19" hidden="1" spans="1:33">
       <c r="A19">
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F19" t="s">
         <v>43</v>
       </c>
       <c r="G19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J19" t="s">
         <v>39</v>
@@ -3215,13 +3254,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D20" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>36</v>
@@ -3231,6 +3270,9 @@
       </c>
       <c r="G20" t="s">
         <v>47</v>
+      </c>
+      <c r="H20" t="s">
+        <v>48</v>
       </c>
       <c r="J20" t="s">
         <v>39</v>
@@ -3272,16 +3314,16 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F21" t="s">
         <v>37</v>
@@ -3289,6 +3331,9 @@
       <c r="G21" t="s">
         <v>47</v>
       </c>
+      <c r="H21" t="s">
+        <v>48</v>
+      </c>
       <c r="J21" t="s">
         <v>39</v>
       </c>
@@ -3333,21 +3378,21 @@
       </c>
       <c r="AG21" s="5"/>
     </row>
-    <row r="22" spans="1:33">
+    <row r="22" hidden="1" spans="1:33">
       <c r="A22">
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C22" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D22" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F22" t="s">
         <v>43</v>
@@ -3396,21 +3441,21 @@
       <c r="AF22"/>
       <c r="AG22" s="5"/>
     </row>
-    <row r="23" spans="1:33">
+    <row r="23" hidden="1" spans="1:33">
       <c r="A23">
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F23" t="s">
         <v>43</v>
@@ -3464,13 +3509,13 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>36</v>
@@ -3481,6 +3526,9 @@
       <c r="G24" t="s">
         <v>47</v>
       </c>
+      <c r="H24" t="s">
+        <v>48</v>
+      </c>
       <c r="J24" t="s">
         <v>39</v>
       </c>
@@ -3522,18 +3570,18 @@
       </c>
       <c r="AG24" s="5"/>
     </row>
-    <row r="25" spans="1:33">
+    <row r="25" hidden="1" spans="1:33">
       <c r="A25">
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D25" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>36</v>
@@ -3542,7 +3590,7 @@
         <v>43</v>
       </c>
       <c r="G25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J25" t="s">
         <v>39</v>
@@ -3577,18 +3625,18 @@
       <c r="AF25"/>
       <c r="AG25" s="5"/>
     </row>
-    <row r="26" spans="1:33">
+    <row r="26" hidden="1" spans="1:33">
       <c r="A26">
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C26" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D26" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>36</v>
@@ -3597,7 +3645,7 @@
         <v>43</v>
       </c>
       <c r="G26" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J26" t="s">
         <v>39</v>
@@ -3645,22 +3693,25 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C27" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D27" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F27" t="s">
         <v>37</v>
       </c>
       <c r="G27" t="s">
         <v>47</v>
+      </c>
+      <c r="H27" t="s">
+        <v>48</v>
       </c>
       <c r="J27" t="s">
         <v>39</v>
@@ -3714,13 +3765,13 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C28" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D28" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>36</v>
@@ -3731,6 +3782,9 @@
       <c r="G28" t="s">
         <v>47</v>
       </c>
+      <c r="H28" t="s">
+        <v>115</v>
+      </c>
       <c r="J28" t="s">
         <v>39</v>
       </c>
@@ -3763,21 +3817,21 @@
       </c>
       <c r="AG28" s="5"/>
     </row>
-    <row r="29" spans="1:33">
+    <row r="29" hidden="1" spans="1:33">
       <c r="A29">
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C29" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D29" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F29" t="s">
         <v>43</v>
@@ -3834,21 +3888,21 @@
       <c r="AF29"/>
       <c r="AG29" s="5"/>
     </row>
-    <row r="30" spans="1:33">
+    <row r="30" hidden="1" spans="1:33">
       <c r="A30">
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C30" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D30" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F30" t="s">
         <v>43</v>
@@ -3897,21 +3951,21 @@
       <c r="AF30"/>
       <c r="AG30" s="6"/>
     </row>
-    <row r="31" spans="1:33">
+    <row r="31" hidden="1" spans="1:33">
       <c r="A31">
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C31" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D31" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F31" t="s">
         <v>43</v>
@@ -3960,21 +4014,21 @@
       <c r="AF31"/>
       <c r="AG31" s="6"/>
     </row>
-    <row r="32" spans="1:32">
+    <row r="32" hidden="1" spans="1:32">
       <c r="A32">
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C32" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D32" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F32" t="s">
         <v>43</v>
@@ -4011,22 +4065,25 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F33" t="s">
         <v>37</v>
       </c>
       <c r="G33" t="s">
         <v>47</v>
+      </c>
+      <c r="H33" t="s">
+        <v>48</v>
       </c>
       <c r="J33" t="s">
         <v>39</v>
@@ -4064,22 +4121,25 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C34" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D34" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F34" t="s">
         <v>43</v>
       </c>
       <c r="G34" t="s">
         <v>47</v>
+      </c>
+      <c r="H34" t="s">
+        <v>48</v>
       </c>
       <c r="J34" t="s">
         <v>39</v>
@@ -4114,22 +4174,25 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C35" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D35" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F35" t="s">
         <v>37</v>
       </c>
       <c r="G35" t="s">
         <v>47</v>
+      </c>
+      <c r="H35" t="s">
+        <v>115</v>
       </c>
       <c r="J35" t="s">
         <v>39</v>
@@ -4164,13 +4227,13 @@
         <v>144</v>
       </c>
       <c r="C36" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D36" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F36" t="s">
         <v>43</v>
@@ -4178,6 +4241,9 @@
       <c r="G36" t="s">
         <v>47</v>
       </c>
+      <c r="H36" t="s">
+        <v>48</v>
+      </c>
       <c r="J36" t="s">
         <v>39</v>
       </c>
@@ -4212,27 +4278,27 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:32">
+    <row r="37" hidden="1" spans="1:32">
       <c r="A37">
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C37" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D37" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F37" t="s">
         <v>43</v>
       </c>
       <c r="G37" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J37" t="s">
         <v>39</v>
@@ -4274,21 +4340,21 @@
       <c r="AD37"/>
       <c r="AF37"/>
     </row>
-    <row r="38" spans="1:32">
+    <row r="38" hidden="1" spans="1:32">
       <c r="A38">
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C38" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D38" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F38" t="s">
         <v>43</v>
@@ -4336,21 +4402,21 @@
       <c r="AD38"/>
       <c r="AF38"/>
     </row>
-    <row r="39" spans="1:32">
+    <row r="39" hidden="1" spans="1:32">
       <c r="A39">
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C39" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D39" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F39" t="s">
         <v>43</v>
@@ -4398,27 +4464,27 @@
       <c r="AD39"/>
       <c r="AF39"/>
     </row>
-    <row r="40" spans="1:32">
+    <row r="40" hidden="1" spans="1:32">
       <c r="A40">
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C40" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D40" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F40" t="s">
         <v>43</v>
       </c>
       <c r="G40" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J40" t="s">
         <v>39</v>
@@ -4460,18 +4526,18 @@
       <c r="AD40"/>
       <c r="AF40"/>
     </row>
-    <row r="41" spans="1:32">
+    <row r="41" hidden="1" spans="1:32">
       <c r="A41">
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C41" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D41" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>36</v>
@@ -4522,27 +4588,27 @@
       <c r="AD41"/>
       <c r="AF41"/>
     </row>
-    <row r="42" spans="1:32">
+    <row r="42" hidden="1" spans="1:32">
       <c r="A42">
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C42" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D42" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F42" t="s">
         <v>43</v>
       </c>
       <c r="G42" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J42" t="s">
         <v>39</v>
@@ -4584,21 +4650,21 @@
       <c r="AD42"/>
       <c r="AF42"/>
     </row>
-    <row r="43" spans="1:32">
+    <row r="43" hidden="1" spans="1:32">
       <c r="A43">
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C43" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D43" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F43" t="s">
         <v>37</v>
@@ -4659,16 +4725,16 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C44" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D44" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F44" t="s">
         <v>37</v>
@@ -4676,6 +4742,9 @@
       <c r="G44" t="s">
         <v>47</v>
       </c>
+      <c r="H44" t="s">
+        <v>48</v>
+      </c>
       <c r="J44" t="s">
         <v>39</v>
       </c>
@@ -4710,27 +4779,27 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:32">
+    <row r="45" hidden="1" spans="1:32">
       <c r="A45">
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C45" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D45" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F45" t="s">
         <v>43</v>
       </c>
       <c r="G45" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J45" t="s">
         <v>39</v>
@@ -4780,21 +4849,21 @@
       <c r="AD45"/>
       <c r="AF45"/>
     </row>
-    <row r="46" spans="1:32">
+    <row r="46" hidden="1" spans="1:32">
       <c r="A46">
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C46" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D46" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F46" t="s">
         <v>43</v>
@@ -4850,18 +4919,18 @@
       <c r="AD46"/>
       <c r="AF46"/>
     </row>
-    <row r="47" spans="1:32">
+    <row r="47" hidden="1" spans="1:32">
       <c r="A47">
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C47" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D47" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>36</v>
@@ -4870,7 +4939,7 @@
         <v>37</v>
       </c>
       <c r="G47" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J47" t="s">
         <v>39</v>
@@ -4904,7 +4973,7 @@
       <c r="AD47"/>
       <c r="AF47"/>
     </row>
-    <row r="48" spans="1:32">
+    <row r="48" hidden="1" spans="1:32">
       <c r="A48">
         <v>49</v>
       </c>
@@ -4912,10 +4981,10 @@
         <v>123</v>
       </c>
       <c r="C48" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D48" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>36</v>
@@ -4971,13 +5040,13 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C49" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D49" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>36</v>
@@ -4988,6 +5057,9 @@
       <c r="G49" t="s">
         <v>47</v>
       </c>
+      <c r="H49" t="s">
+        <v>115</v>
+      </c>
       <c r="J49" t="s">
         <v>39</v>
       </c>
@@ -5022,21 +5094,21 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:32">
+    <row r="50" hidden="1" spans="1:32">
       <c r="A50">
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C50" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D50" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F50" t="s">
         <v>37</v>
@@ -5084,21 +5156,21 @@
       <c r="AD50"/>
       <c r="AF50"/>
     </row>
-    <row r="51" spans="1:32">
+    <row r="51" hidden="1" spans="1:32">
       <c r="A51">
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C51" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D51" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F51" t="s">
         <v>43</v>
@@ -5146,21 +5218,21 @@
       <c r="AD51"/>
       <c r="AF51"/>
     </row>
-    <row r="52" spans="1:32">
+    <row r="52" hidden="1" spans="1:32">
       <c r="A52">
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C52" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D52" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F52" t="s">
         <v>43</v>
@@ -5213,22 +5285,25 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C53" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D53" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F53" t="s">
         <v>37</v>
       </c>
       <c r="G53" t="s">
         <v>47</v>
+      </c>
+      <c r="H53" t="s">
+        <v>48</v>
       </c>
       <c r="J53" t="s">
         <v>39</v>
@@ -5272,16 +5347,16 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C54" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D54" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F54" t="s">
         <v>43</v>
@@ -5289,8 +5364,11 @@
       <c r="G54" t="s">
         <v>47</v>
       </c>
+      <c r="H54" t="s">
+        <v>48</v>
+      </c>
       <c r="J54" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K54" s="3">
         <v>14</v>
@@ -5340,22 +5418,25 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C55" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D55" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F55" t="s">
         <v>43</v>
       </c>
       <c r="G55" t="s">
         <v>47</v>
+      </c>
+      <c r="H55" t="s">
+        <v>48</v>
       </c>
       <c r="J55" t="s">
         <v>39</v>
@@ -5397,16 +5478,16 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C56" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D56" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F56" t="s">
         <v>37</v>
@@ -5414,8 +5495,11 @@
       <c r="G56" t="s">
         <v>47</v>
       </c>
+      <c r="H56" t="s">
+        <v>115</v>
+      </c>
       <c r="J56" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K56" s="3">
         <v>3</v>
@@ -5466,16 +5550,16 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C57" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D57" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F57" t="s">
         <v>37</v>
@@ -5483,8 +5567,11 @@
       <c r="G57" t="s">
         <v>47</v>
       </c>
+      <c r="H57" t="s">
+        <v>115</v>
+      </c>
       <c r="J57" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K57" s="3">
         <v>3</v>
@@ -5525,13 +5612,13 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C58" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D58" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>36</v>
@@ -5541,6 +5628,9 @@
       </c>
       <c r="G58" t="s">
         <v>47</v>
+      </c>
+      <c r="H58" t="s">
+        <v>115</v>
       </c>
       <c r="J58" t="s">
         <v>39</v>
@@ -5563,22 +5653,25 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C59" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D59" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F59" t="s">
         <v>37</v>
       </c>
       <c r="G59" t="s">
         <v>47</v>
+      </c>
+      <c r="H59" t="s">
+        <v>115</v>
       </c>
       <c r="J59" t="s">
         <v>39</v>
@@ -5610,16 +5703,16 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C60" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D60" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F60" t="s">
         <v>37</v>
@@ -5627,6 +5720,9 @@
       <c r="G60" t="s">
         <v>47</v>
       </c>
+      <c r="H60" t="s">
+        <v>115</v>
+      </c>
       <c r="J60" t="s">
         <v>39</v>
       </c>
@@ -5643,27 +5739,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:15">
+    <row r="61" hidden="1" spans="1:15">
       <c r="A61">
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C61" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D61" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F61" t="s">
         <v>37</v>
       </c>
       <c r="J61" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K61" s="3">
         <v>14</v>
@@ -5682,6 +5778,14 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AH61" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="C"/>
+      </filters>
+    </filterColumn>
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
@@ -5691,7 +5795,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
@@ -5719,19 +5823,19 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5739,13 +5843,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I2">
         <v>-1</v>
@@ -5756,19 +5860,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -5779,16 +5883,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -5799,16 +5903,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -5819,13 +5923,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -5836,16 +5940,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C7" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D7" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E7" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -5856,13 +5960,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C8" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D8" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -5876,13 +5980,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C9" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D9" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -5896,13 +6000,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>207</v>
+      </c>
+      <c r="C10" t="s">
+        <v>207</v>
+      </c>
+      <c r="D10" t="s">
         <v>205</v>
-      </c>
-      <c r="C10" t="s">
-        <v>205</v>
-      </c>
-      <c r="D10" t="s">
-        <v>203</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -5916,13 +6020,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C11" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D11" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -5933,16 +6037,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C12" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D12" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E12" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -5953,16 +6057,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C13" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D13" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E13" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -5973,19 +6077,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C14" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D14" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -5996,16 +6100,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C15" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D15" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E15" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -6016,16 +6120,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C16" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D16" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E16" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -6036,13 +6140,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C17" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D17" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -6056,16 +6160,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C18" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D18" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E18" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -6076,13 +6180,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C19" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D19" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -6096,13 +6200,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C20" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D20" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -6116,16 +6220,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C21" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D21" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E21" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -6136,16 +6240,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C22" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D22" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E22" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -6156,13 +6260,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C23" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D23" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E23">
         <v>5</v>
@@ -6176,19 +6280,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C24" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D24" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -6199,13 +6303,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C25" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D25" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -6219,16 +6323,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C26" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D26" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E26" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -6242,16 +6346,16 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C27" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D27" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E27" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -6262,13 +6366,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C28" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D28" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -6282,19 +6386,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C29" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D29" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -6308,13 +6412,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C30" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D30" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -6328,19 +6432,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C31" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D31" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E31" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F31" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -6351,19 +6455,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C32" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D32" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E32">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -6374,19 +6478,19 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C33" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D33" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E33">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -6397,16 +6501,16 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C34" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D34" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E34" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -6417,16 +6521,16 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C35" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D35" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E35" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -6437,19 +6541,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C36" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D36" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E36" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F36" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -6463,13 +6567,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C37" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D37" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E37">
         <v>11</v>
@@ -6483,16 +6587,16 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C38" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D38" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E38" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -6503,13 +6607,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C39" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D39" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -6526,16 +6630,16 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C40" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D40" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E40" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -6546,13 +6650,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C41" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D41" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -6569,19 +6673,19 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C42" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D42" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -6595,13 +6699,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C43" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D43" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E43">
         <v>12</v>
@@ -6615,13 +6719,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C44" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D44" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E44">
         <v>13</v>
@@ -6635,19 +6739,19 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D45" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E45" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F45" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I45">
         <v>-1</v>
@@ -6658,16 +6762,16 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E46" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="I46">
         <v>1</v>
@@ -6678,13 +6782,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C47" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D47" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E47">
         <v>14</v>
@@ -6698,19 +6802,19 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C48" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D48" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I48">
         <v>-1</v>
@@ -6721,13 +6825,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C49" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D49" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E49">
         <v>15</v>
@@ -6741,19 +6845,19 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C50" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D50" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I50">
         <v>-1</v>
@@ -6764,13 +6868,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C51" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D51" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E51">
         <v>16</v>
@@ -6784,13 +6888,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C52" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D52" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -6804,13 +6908,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C53" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D53" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E53">
         <v>3</v>
@@ -6824,13 +6928,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C54" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D54" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E54">
         <v>3</v>
@@ -6847,16 +6951,16 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C55" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D55" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E55" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G55">
         <v>6</v>
@@ -6870,16 +6974,16 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C56" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D56" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E56" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G56">
         <v>7</v>
@@ -6893,16 +6997,16 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C57" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D57" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E57" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G57">
         <v>8</v>
@@ -6916,16 +7020,16 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C58" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D58" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E58" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G58">
         <v>6</v>
@@ -6939,16 +7043,16 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C59" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D59" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E59" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G59">
         <v>7</v>
@@ -6962,16 +7066,16 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C60" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D60" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E60" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G60">
         <v>8</v>
@@ -6985,19 +7089,19 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C61" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D61" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E61">
         <v>3</v>
       </c>
       <c r="F61" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I61">
         <v>-1</v>
@@ -7008,18 +7112,121 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C62" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D62" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E62">
         <v>20</v>
       </c>
       <c r="I62">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="63" customFormat="1" spans="1:9">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="B63" t="s">
+        <v>282</v>
+      </c>
+      <c r="C63" t="s">
+        <v>282</v>
+      </c>
+      <c r="D63" t="s">
+        <v>209</v>
+      </c>
+      <c r="F63" t="s">
+        <v>242</v>
+      </c>
+      <c r="I63">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64">
+        <v>62</v>
+      </c>
+      <c r="B64" t="s">
+        <v>283</v>
+      </c>
+      <c r="C64" t="s">
+        <v>283</v>
+      </c>
+      <c r="D64" t="s">
+        <v>205</v>
+      </c>
+      <c r="E64">
+        <v>21</v>
+      </c>
+      <c r="I64">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65">
+        <v>63</v>
+      </c>
+      <c r="B65" t="s">
+        <v>284</v>
+      </c>
+      <c r="C65" t="s">
+        <v>284</v>
+      </c>
+      <c r="D65" t="s">
+        <v>265</v>
+      </c>
+      <c r="E65">
+        <v>3</v>
+      </c>
+      <c r="I65">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="66" customFormat="1" spans="1:9">
+      <c r="A66">
+        <v>64</v>
+      </c>
+      <c r="B66" t="s">
+        <v>285</v>
+      </c>
+      <c r="C66" t="s">
+        <v>285</v>
+      </c>
+      <c r="D66" t="s">
+        <v>205</v>
+      </c>
+      <c r="E66">
+        <v>14</v>
+      </c>
+      <c r="F66" t="s">
+        <v>191</v>
+      </c>
+      <c r="I66">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67">
+        <v>65</v>
+      </c>
+      <c r="B67" t="s">
+        <v>286</v>
+      </c>
+      <c r="C67" t="s">
+        <v>286</v>
+      </c>
+      <c r="D67" t="s">
+        <v>205</v>
+      </c>
+      <c r="E67">
+        <v>22</v>
+      </c>
+      <c r="I67">
         <v>-1</v>
       </c>
     </row>
@@ -7033,7 +7240,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9.425" customWidth="1"/>
@@ -7056,13 +7263,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="D1" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="F1" t="s">
         <v>16</v>
@@ -7089,10 +7296,10 @@
         <v>26</v>
       </c>
       <c r="N1" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="O1" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -7100,10 +7307,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="C2" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -7129,10 +7336,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="C3" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -7152,10 +7359,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="C4" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -7169,10 +7376,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="C5" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -7204,10 +7411,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="C6" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -7227,10 +7434,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="C7" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -7250,10 +7457,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="C8" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -7273,10 +7480,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="C9" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -7296,10 +7503,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C10" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -7319,10 +7526,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C11" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -7348,10 +7555,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C12" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -7377,10 +7584,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C13" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -7400,10 +7607,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -7423,10 +7630,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="C15" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -7446,10 +7653,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="C16" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -7469,10 +7676,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C17" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -7492,10 +7699,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C18" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -7515,10 +7722,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="C19" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -7532,10 +7739,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
+        <v>305</v>
+      </c>
+      <c r="C20" t="s">
         <v>297</v>
-      </c>
-      <c r="C20" t="s">
-        <v>289</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -7549,10 +7756,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="C21" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -7566,10 +7773,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="C22" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -7581,6 +7788,52 @@
         <v>59</v>
       </c>
       <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>308</v>
+      </c>
+      <c r="C23" t="s">
+        <v>297</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>61</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>286</v>
+      </c>
+      <c r="C24" t="s">
+        <v>293</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>64</v>
+      </c>
+      <c r="G24">
         <v>1</v>
       </c>
     </row>
@@ -7617,16 +7870,16 @@
         <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="E1" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="F1" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="G1" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -7634,13 +7887,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="C2" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="D2" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -7654,13 +7907,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="C3" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="D3" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="F3" t="s">
         <v>43</v>
@@ -7671,13 +7924,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="C4" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="D4" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="F4" t="s">
         <v>37</v>
@@ -7688,13 +7941,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="C5" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="D5" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -7708,13 +7961,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="C6" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="D6" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -7728,13 +7981,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="C7" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="D7" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -7748,13 +8001,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="C8" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="D8" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -7768,13 +8021,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>323</v>
+      </c>
+      <c r="C9" t="s">
         <v>314</v>
       </c>
-      <c r="C9" t="s">
-        <v>305</v>
-      </c>
       <c r="D9" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -7788,13 +8041,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C10" t="s">
+        <v>314</v>
+      </c>
+      <c r="D10" t="s">
         <v>315</v>
-      </c>
-      <c r="C10" t="s">
-        <v>305</v>
-      </c>
-      <c r="D10" t="s">
-        <v>306</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -7808,13 +8061,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="C11" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="D11" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="E11" t="s">
         <v>43</v>

--- a/Assets/StreamingAssets/Configurations/Cards.xlsx
+++ b/Assets/StreamingAssets/Configurations/Cards.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA9C686B-D039-42AD-93AF-A2A11D8274B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" activeTab="1"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -24,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1019,167 +1023,17 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1198,188 +1052,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1405,251 +1079,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1664,71 +1096,27 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="00FFFFFF"/>
-      <color rgb="00AB0580"/>
-      <color rgb="0000B050"/>
-      <color rgb="00FFB200"/>
-      <color rgb="004B58FF"/>
-      <color rgb="00FF2160"/>
+      <color rgb="FFFFFFFF"/>
+      <color rgb="FFAB0580"/>
+      <color rgb="FF00B050"/>
+      <color rgb="FFFFB200"/>
+      <color rgb="FF4B58FF"/>
+      <color rgb="FFFF2160"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1986,49 +1374,49 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AH61"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.425" customWidth="1"/>
-    <col min="2" max="2" width="12.7083333333333" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
-    <col min="4" max="4" width="57.7083333333333" customWidth="1"/>
-    <col min="5" max="5" width="10.425" style="2" customWidth="1"/>
-    <col min="6" max="6" width="4.85833333333333" customWidth="1"/>
-    <col min="7" max="7" width="7.85833333333333" customWidth="1"/>
+    <col min="4" max="4" width="57.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="4.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.85546875" customWidth="1"/>
     <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="9" max="9" width="5.56666666666667" style="3" customWidth="1"/>
-    <col min="10" max="10" width="10.5666666666667" customWidth="1"/>
-    <col min="11" max="11" width="9.70833333333333" style="3" customWidth="1"/>
-    <col min="12" max="12" width="7.14166666666667" customWidth="1"/>
+    <col min="9" max="9" width="5.5703125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" style="3" customWidth="1"/>
+    <col min="12" max="12" width="7.140625" customWidth="1"/>
     <col min="13" max="13" width="14" style="3" customWidth="1"/>
-    <col min="14" max="14" width="10.2833333333333" customWidth="1"/>
-    <col min="15" max="15" width="13.7083333333333" customWidth="1"/>
-    <col min="16" max="16" width="9.70833333333333" style="3" customWidth="1"/>
-    <col min="17" max="17" width="9.70833333333333" customWidth="1"/>
-    <col min="18" max="18" width="12.1416666666667" customWidth="1"/>
-    <col min="19" max="19" width="17.7083333333333" style="3" customWidth="1"/>
+    <col min="14" max="14" width="10.28515625" customWidth="1"/>
+    <col min="15" max="15" width="13.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" style="3" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="18" width="12.140625" customWidth="1"/>
+    <col min="19" max="19" width="17.7109375" style="3" customWidth="1"/>
     <col min="20" max="20" width="11" customWidth="1"/>
-    <col min="21" max="21" width="12.2833333333333" customWidth="1"/>
-    <col min="22" max="22" width="17.1416666666667" style="3" customWidth="1"/>
-    <col min="25" max="25" width="17.7083333333333" style="3" customWidth="1"/>
-    <col min="26" max="26" width="10.7083333333333" customWidth="1"/>
+    <col min="21" max="21" width="12.28515625" customWidth="1"/>
+    <col min="22" max="22" width="17.140625" style="3" customWidth="1"/>
+    <col min="25" max="25" width="17.7109375" style="3" customWidth="1"/>
+    <col min="26" max="26" width="10.7109375" customWidth="1"/>
     <col min="27" max="27" width="11" customWidth="1"/>
-    <col min="28" max="28" width="17.7083333333333" style="3" customWidth="1"/>
-    <col min="29" max="29" width="12.425" customWidth="1"/>
-    <col min="30" max="30" width="12.425" style="3" customWidth="1"/>
-    <col min="31" max="31" width="12.2833333333333" customWidth="1"/>
+    <col min="28" max="28" width="17.7109375" style="3" customWidth="1"/>
+    <col min="29" max="29" width="12.42578125" customWidth="1"/>
+    <col min="30" max="30" width="12.42578125" style="3" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" customWidth="1"/>
     <col min="32" max="32" width="9" style="3"/>
-    <col min="33" max="33" width="4.28333333333333" customWidth="1"/>
+    <col min="33" max="33" width="4.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33">
+    <row r="1" spans="1:34">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2129,7 +1517,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" hidden="1" spans="1:33">
+    <row r="2" spans="1:34">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2184,7 +1572,7 @@
       <c r="AF2"/>
       <c r="AG2" s="5"/>
     </row>
-    <row r="3" hidden="1" spans="1:33">
+    <row r="3" spans="1:34">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2239,7 +1627,7 @@
       <c r="AF3"/>
       <c r="AG3" s="5"/>
     </row>
-    <row r="4" spans="1:33">
+    <row r="4" spans="1:34">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2299,7 +1687,7 @@
       </c>
       <c r="AG4" s="5"/>
     </row>
-    <row r="5" hidden="1" spans="1:33">
+    <row r="5" spans="1:34">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2362,7 +1750,7 @@
       <c r="AF5"/>
       <c r="AG5" s="5"/>
     </row>
-    <row r="6" spans="1:33">
+    <row r="6" spans="1:34">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2428,7 +1816,7 @@
       </c>
       <c r="AG6" s="5"/>
     </row>
-    <row r="7" hidden="1" spans="1:33">
+    <row r="7" spans="1:34">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2494,7 +1882,7 @@
       <c r="AF7"/>
       <c r="AG7" s="5"/>
     </row>
-    <row r="8" hidden="1" spans="1:33">
+    <row r="8" spans="1:34">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2567,7 +1955,7 @@
       <c r="AF8"/>
       <c r="AG8" s="5"/>
     </row>
-    <row r="9" hidden="1" spans="1:33">
+    <row r="9" spans="1:34">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2630,7 +2018,7 @@
       <c r="AF9"/>
       <c r="AG9" s="5"/>
     </row>
-    <row r="10" hidden="1" spans="1:33">
+    <row r="10" spans="1:34">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2693,7 +2081,7 @@
       <c r="AF10"/>
       <c r="AG10" s="5"/>
     </row>
-    <row r="11" spans="1:33">
+    <row r="11" spans="1:34">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2753,7 +2141,7 @@
       </c>
       <c r="AG11" s="5"/>
     </row>
-    <row r="12" hidden="1" spans="1:34">
+    <row r="12" spans="1:34">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2819,7 +2207,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="13" hidden="1" spans="1:33">
+    <row r="13" spans="1:34">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2882,7 +2270,7 @@
       <c r="AF13"/>
       <c r="AG13" s="5"/>
     </row>
-    <row r="14" hidden="1" spans="1:33">
+    <row r="14" spans="1:34">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2937,7 +2325,7 @@
       <c r="AF14"/>
       <c r="AG14" s="5"/>
     </row>
-    <row r="15" hidden="1" spans="1:33">
+    <row r="15" spans="1:34">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2992,7 +2380,7 @@
       <c r="AF15"/>
       <c r="AG15" s="5"/>
     </row>
-    <row r="16" hidden="1" spans="1:33">
+    <row r="16" spans="1:34">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3047,7 +2435,7 @@
         <v>0.8</v>
       </c>
       <c r="V16" s="3">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="Y16"/>
       <c r="AB16"/>
@@ -3055,7 +2443,7 @@
       <c r="AF16"/>
       <c r="AG16" s="5"/>
     </row>
-    <row r="17" hidden="1" spans="1:33">
+    <row r="17" spans="1:33">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3179,14 +2567,14 @@
         <v>7</v>
       </c>
       <c r="AC18">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="AD18" s="3">
         <v>1.5</v>
       </c>
       <c r="AG18" s="5"/>
     </row>
-    <row r="19" hidden="1" spans="1:33">
+    <row r="19" spans="1:33">
       <c r="A19">
         <v>19</v>
       </c>
@@ -3378,7 +2766,7 @@
       </c>
       <c r="AG21" s="5"/>
     </row>
-    <row r="22" hidden="1" spans="1:33">
+    <row r="22" spans="1:33">
       <c r="A22">
         <v>22</v>
       </c>
@@ -3441,7 +2829,7 @@
       <c r="AF22"/>
       <c r="AG22" s="5"/>
     </row>
-    <row r="23" hidden="1" spans="1:33">
+    <row r="23" spans="1:33">
       <c r="A23">
         <v>23</v>
       </c>
@@ -3562,15 +2950,9 @@
       <c r="V24" s="3">
         <v>11</v>
       </c>
-      <c r="AC24">
-        <v>63</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>3</v>
-      </c>
       <c r="AG24" s="5"/>
     </row>
-    <row r="25" hidden="1" spans="1:33">
+    <row r="25" spans="1:33">
       <c r="A25">
         <v>25</v>
       </c>
@@ -3625,7 +3007,7 @@
       <c r="AF25"/>
       <c r="AG25" s="5"/>
     </row>
-    <row r="26" hidden="1" spans="1:33">
+    <row r="26" spans="1:33">
       <c r="A26">
         <v>26</v>
       </c>
@@ -3817,7 +3199,7 @@
       </c>
       <c r="AG28" s="5"/>
     </row>
-    <row r="29" hidden="1" spans="1:33">
+    <row r="29" spans="1:33">
       <c r="A29">
         <v>30</v>
       </c>
@@ -3888,7 +3270,7 @@
       <c r="AF29"/>
       <c r="AG29" s="5"/>
     </row>
-    <row r="30" hidden="1" spans="1:33">
+    <row r="30" spans="1:33">
       <c r="A30">
         <v>31</v>
       </c>
@@ -3951,7 +3333,7 @@
       <c r="AF30"/>
       <c r="AG30" s="6"/>
     </row>
-    <row r="31" hidden="1" spans="1:33">
+    <row r="31" spans="1:33">
       <c r="A31">
         <v>32</v>
       </c>
@@ -4014,7 +3396,7 @@
       <c r="AF31"/>
       <c r="AG31" s="6"/>
     </row>
-    <row r="32" hidden="1" spans="1:32">
+    <row r="32" spans="1:33">
       <c r="A32">
         <v>33</v>
       </c>
@@ -4060,7 +3442,7 @@
       <c r="AD32"/>
       <c r="AF32"/>
     </row>
-    <row r="33" spans="1:30">
+    <row r="33" spans="1:32">
       <c r="A33">
         <v>34</v>
       </c>
@@ -4116,7 +3498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:19">
+    <row r="34" spans="1:32">
       <c r="A34">
         <v>35</v>
       </c>
@@ -4169,7 +3551,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:19">
+    <row r="35" spans="1:32">
       <c r="A35">
         <v>36</v>
       </c>
@@ -4219,7 +3601,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:22">
+    <row r="36" spans="1:32">
       <c r="A36">
         <v>37</v>
       </c>
@@ -4278,7 +3660,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" hidden="1" spans="1:32">
+    <row r="37" spans="1:32">
       <c r="A37">
         <v>38</v>
       </c>
@@ -4340,7 +3722,7 @@
       <c r="AD37"/>
       <c r="AF37"/>
     </row>
-    <row r="38" hidden="1" spans="1:32">
+    <row r="38" spans="1:32">
       <c r="A38">
         <v>39</v>
       </c>
@@ -4402,7 +3784,7 @@
       <c r="AD38"/>
       <c r="AF38"/>
     </row>
-    <row r="39" hidden="1" spans="1:32">
+    <row r="39" spans="1:32">
       <c r="A39">
         <v>40</v>
       </c>
@@ -4464,7 +3846,7 @@
       <c r="AD39"/>
       <c r="AF39"/>
     </row>
-    <row r="40" hidden="1" spans="1:32">
+    <row r="40" spans="1:32">
       <c r="A40">
         <v>41</v>
       </c>
@@ -4526,7 +3908,7 @@
       <c r="AD40"/>
       <c r="AF40"/>
     </row>
-    <row r="41" hidden="1" spans="1:32">
+    <row r="41" spans="1:32">
       <c r="A41">
         <v>42</v>
       </c>
@@ -4588,7 +3970,7 @@
       <c r="AD41"/>
       <c r="AF41"/>
     </row>
-    <row r="42" hidden="1" spans="1:32">
+    <row r="42" spans="1:32">
       <c r="A42">
         <v>43</v>
       </c>
@@ -4650,7 +4032,7 @@
       <c r="AD42"/>
       <c r="AF42"/>
     </row>
-    <row r="43" hidden="1" spans="1:32">
+    <row r="43" spans="1:32">
       <c r="A43">
         <v>44</v>
       </c>
@@ -4720,7 +4102,7 @@
       <c r="AD43"/>
       <c r="AF43"/>
     </row>
-    <row r="44" spans="1:22">
+    <row r="44" spans="1:32">
       <c r="A44">
         <v>45</v>
       </c>
@@ -4779,7 +4161,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" hidden="1" spans="1:32">
+    <row r="45" spans="1:32">
       <c r="A45">
         <v>46</v>
       </c>
@@ -4849,7 +4231,7 @@
       <c r="AD45"/>
       <c r="AF45"/>
     </row>
-    <row r="46" hidden="1" spans="1:32">
+    <row r="46" spans="1:32">
       <c r="A46">
         <v>47</v>
       </c>
@@ -4919,7 +4301,7 @@
       <c r="AD46"/>
       <c r="AF46"/>
     </row>
-    <row r="47" hidden="1" spans="1:32">
+    <row r="47" spans="1:32">
       <c r="A47">
         <v>48</v>
       </c>
@@ -4973,7 +4355,7 @@
       <c r="AD47"/>
       <c r="AF47"/>
     </row>
-    <row r="48" hidden="1" spans="1:32">
+    <row r="48" spans="1:32">
       <c r="A48">
         <v>49</v>
       </c>
@@ -5035,7 +4417,7 @@
       <c r="AD48"/>
       <c r="AF48"/>
     </row>
-    <row r="49" spans="1:22">
+    <row r="49" spans="1:32">
       <c r="A49">
         <v>50</v>
       </c>
@@ -5094,7 +4476,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" hidden="1" spans="1:32">
+    <row r="50" spans="1:32">
       <c r="A50">
         <v>51</v>
       </c>
@@ -5146,7 +4528,7 @@
         <v>18</v>
       </c>
       <c r="U50">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="V50" s="3">
         <v>1.7</v>
@@ -5156,7 +4538,7 @@
       <c r="AD50"/>
       <c r="AF50"/>
     </row>
-    <row r="51" hidden="1" spans="1:32">
+    <row r="51" spans="1:32">
       <c r="A51">
         <v>52</v>
       </c>
@@ -5218,7 +4600,7 @@
       <c r="AD51"/>
       <c r="AF51"/>
     </row>
-    <row r="52" hidden="1" spans="1:32">
+    <row r="52" spans="1:32">
       <c r="A52">
         <v>53</v>
       </c>
@@ -5280,7 +4662,7 @@
       <c r="AD52"/>
       <c r="AF52"/>
     </row>
-    <row r="53" spans="1:22">
+    <row r="53" spans="1:32">
       <c r="A53">
         <v>54</v>
       </c>
@@ -5342,7 +4724,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="54" spans="1:25">
+    <row r="54" spans="1:32">
       <c r="A54">
         <v>55</v>
       </c>
@@ -5413,7 +4795,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:31">
+    <row r="55" spans="1:32">
       <c r="A55">
         <v>56</v>
       </c>
@@ -5473,7 +4855,7 @@
       </c>
       <c r="AE55" s="3"/>
     </row>
-    <row r="56" spans="1:31">
+    <row r="56" spans="1:32">
       <c r="A56">
         <v>57</v>
       </c>
@@ -5545,7 +4927,7 @@
       </c>
       <c r="AE56" s="3"/>
     </row>
-    <row r="57" spans="1:22">
+    <row r="57" spans="1:32">
       <c r="A57">
         <v>58</v>
       </c>
@@ -5607,7 +4989,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:15">
+    <row r="58" spans="1:32">
       <c r="A58">
         <v>59</v>
       </c>
@@ -5648,7 +5030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:19">
+    <row r="59" spans="1:32">
       <c r="A59">
         <v>60</v>
       </c>
@@ -5698,7 +5080,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:15">
+    <row r="60" spans="1:32">
       <c r="A60">
         <v>61</v>
       </c>
@@ -5739,7 +5121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" hidden="1" spans="1:15">
+    <row r="61" spans="1:32">
       <c r="A61">
         <v>62</v>
       </c>
@@ -5778,34 +5160,25 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AH61" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="C"/>
-      </filters>
-    </filterColumn>
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:AH61" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I67"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.425" customWidth="1"/>
-    <col min="2" max="2" width="27.425" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
     <col min="4" max="4" width="33" customWidth="1"/>
-    <col min="5" max="5" width="19.2833333333333" customWidth="1"/>
-    <col min="6" max="6" width="18.8583333333333" customWidth="1"/>
-    <col min="7" max="8" width="10.2833333333333" customWidth="1"/>
-    <col min="9" max="9" width="15.1416666666667" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" customWidth="1"/>
+    <col min="7" max="8" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7127,7 +6500,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="63" customFormat="1" spans="1:9">
+    <row r="63" spans="1:9">
       <c r="A63">
         <v>61</v>
       </c>
@@ -7187,7 +6560,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="66" customFormat="1" spans="1:9">
+    <row r="66" spans="1:9">
       <c r="A66">
         <v>64</v>
       </c>
@@ -7232,26 +6605,24 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.425" customWidth="1"/>
-    <col min="2" max="2" width="27.425" customWidth="1"/>
-    <col min="3" max="3" width="14.425" customWidth="1"/>
-    <col min="4" max="5" width="16.1416666666667" customWidth="1"/>
-    <col min="6" max="6" width="12.425" customWidth="1"/>
-    <col min="7" max="7" width="14.425" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
+    <col min="4" max="5" width="16.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="10.1416666666667" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7302,7 +6673,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>0</v>
       </c>
@@ -7331,7 +6702,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>1</v>
       </c>
@@ -7354,7 +6725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>2</v>
       </c>
@@ -7371,7 +6742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:15">
       <c r="A5">
         <v>3</v>
       </c>
@@ -7406,7 +6777,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:15">
       <c r="A6">
         <v>4</v>
       </c>
@@ -7429,7 +6800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:15">
       <c r="A7">
         <v>5</v>
       </c>
@@ -7452,7 +6823,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:15">
       <c r="A8">
         <v>6</v>
       </c>
@@ -7475,7 +6846,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:15">
       <c r="A9">
         <v>7</v>
       </c>
@@ -7498,7 +6869,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:15">
       <c r="A10">
         <v>8</v>
       </c>
@@ -7521,7 +6892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:15">
       <c r="A11">
         <v>9</v>
       </c>
@@ -7550,7 +6921,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:15">
       <c r="A12">
         <v>10</v>
       </c>
@@ -7579,7 +6950,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:15">
       <c r="A13">
         <v>11</v>
       </c>
@@ -7602,7 +6973,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:15">
       <c r="A14">
         <v>12</v>
       </c>
@@ -7625,7 +6996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:15">
       <c r="A15">
         <v>13</v>
       </c>
@@ -7648,7 +7019,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:15">
       <c r="A16">
         <v>14</v>
       </c>
@@ -7717,7 +7088,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>17</v>
       </c>
@@ -7734,7 +7105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>18</v>
       </c>
@@ -7751,7 +7122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>19</v>
       </c>
@@ -7839,24 +7210,22 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85833333333333" customWidth="1"/>
-    <col min="2" max="2" width="22.7083333333333" customWidth="1"/>
-    <col min="3" max="3" width="28.5666666666667" customWidth="1"/>
-    <col min="4" max="4" width="15.5666666666667" customWidth="1"/>
-    <col min="5" max="5" width="16.1416666666667" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="11.1416666666667" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -7882,7 +7251,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -7902,7 +7271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="12.95" customHeight="1" spans="1:6">
+    <row r="3" spans="1:7" ht="12.95" customHeight="1">
       <c r="A3">
         <v>1</v>
       </c>
@@ -7919,7 +7288,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" ht="12.95" customHeight="1" spans="1:6">
+    <row r="4" spans="1:7" ht="12.95" customHeight="1">
       <c r="A4">
         <v>2</v>
       </c>
@@ -7936,7 +7305,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>3</v>
       </c>
@@ -7956,7 +7325,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>4</v>
       </c>
@@ -7976,7 +7345,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>5</v>
       </c>
@@ -7996,7 +7365,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>6</v>
       </c>
@@ -8016,7 +7385,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>7</v>
       </c>
@@ -8036,7 +7405,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>8</v>
       </c>
@@ -8056,7 +7425,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>9</v>
       </c>
@@ -8078,7 +7447,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Cards.xlsx
+++ b/Assets/StreamingAssets/Configurations/Cards.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" activeTab="1"/>
+    <workbookView windowWidth="24750" windowHeight="10480" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -1991,7 +1991,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
+  <sheetPr/>
   <dimension ref="A1:AH61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
@@ -2129,7 +2129,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" hidden="1" spans="1:33">
+    <row r="2" spans="1:33">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2184,7 +2184,7 @@
       <c r="AF2"/>
       <c r="AG2" s="5"/>
     </row>
-    <row r="3" hidden="1" spans="1:33">
+    <row r="3" spans="1:33">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="AG4" s="5"/>
     </row>
-    <row r="5" hidden="1" spans="1:33">
+    <row r="5" spans="1:33">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="AG6" s="5"/>
     </row>
-    <row r="7" hidden="1" spans="1:33">
+    <row r="7" spans="1:33">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2494,7 +2494,7 @@
       <c r="AF7"/>
       <c r="AG7" s="5"/>
     </row>
-    <row r="8" hidden="1" spans="1:33">
+    <row r="8" spans="1:33">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2567,7 +2567,7 @@
       <c r="AF8"/>
       <c r="AG8" s="5"/>
     </row>
-    <row r="9" hidden="1" spans="1:33">
+    <row r="9" spans="1:33">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2630,7 +2630,7 @@
       <c r="AF9"/>
       <c r="AG9" s="5"/>
     </row>
-    <row r="10" hidden="1" spans="1:33">
+    <row r="10" spans="1:33">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="AG11" s="5"/>
     </row>
-    <row r="12" hidden="1" spans="1:34">
+    <row r="12" spans="1:34">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2819,7 +2819,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="13" hidden="1" spans="1:33">
+    <row r="13" spans="1:33">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2882,7 +2882,7 @@
       <c r="AF13"/>
       <c r="AG13" s="5"/>
     </row>
-    <row r="14" hidden="1" spans="1:33">
+    <row r="14" spans="1:33">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2937,7 +2937,7 @@
       <c r="AF14"/>
       <c r="AG14" s="5"/>
     </row>
-    <row r="15" hidden="1" spans="1:33">
+    <row r="15" spans="1:33">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2992,7 +2992,7 @@
       <c r="AF15"/>
       <c r="AG15" s="5"/>
     </row>
-    <row r="16" hidden="1" spans="1:33">
+    <row r="16" spans="1:33">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3055,7 +3055,7 @@
       <c r="AF16"/>
       <c r="AG16" s="5"/>
     </row>
-    <row r="17" hidden="1" spans="1:33">
+    <row r="17" spans="1:33">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="AG18" s="5"/>
     </row>
-    <row r="19" hidden="1" spans="1:33">
+    <row r="19" spans="1:33">
       <c r="A19">
         <v>19</v>
       </c>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="AG21" s="5"/>
     </row>
-    <row r="22" hidden="1" spans="1:33">
+    <row r="22" spans="1:33">
       <c r="A22">
         <v>22</v>
       </c>
@@ -3441,7 +3441,7 @@
       <c r="AF22"/>
       <c r="AG22" s="5"/>
     </row>
-    <row r="23" hidden="1" spans="1:33">
+    <row r="23" spans="1:33">
       <c r="A23">
         <v>23</v>
       </c>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="AG24" s="5"/>
     </row>
-    <row r="25" hidden="1" spans="1:33">
+    <row r="25" spans="1:33">
       <c r="A25">
         <v>25</v>
       </c>
@@ -3625,7 +3625,7 @@
       <c r="AF25"/>
       <c r="AG25" s="5"/>
     </row>
-    <row r="26" hidden="1" spans="1:33">
+    <row r="26" spans="1:33">
       <c r="A26">
         <v>26</v>
       </c>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="AG28" s="5"/>
     </row>
-    <row r="29" hidden="1" spans="1:33">
+    <row r="29" spans="1:33">
       <c r="A29">
         <v>30</v>
       </c>
@@ -3888,7 +3888,7 @@
       <c r="AF29"/>
       <c r="AG29" s="5"/>
     </row>
-    <row r="30" hidden="1" spans="1:33">
+    <row r="30" spans="1:33">
       <c r="A30">
         <v>31</v>
       </c>
@@ -3951,7 +3951,7 @@
       <c r="AF30"/>
       <c r="AG30" s="6"/>
     </row>
-    <row r="31" hidden="1" spans="1:33">
+    <row r="31" spans="1:33">
       <c r="A31">
         <v>32</v>
       </c>
@@ -4014,7 +4014,7 @@
       <c r="AF31"/>
       <c r="AG31" s="6"/>
     </row>
-    <row r="32" hidden="1" spans="1:32">
+    <row r="32" spans="1:32">
       <c r="A32">
         <v>33</v>
       </c>
@@ -4278,7 +4278,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" hidden="1" spans="1:32">
+    <row r="37" spans="1:32">
       <c r="A37">
         <v>38</v>
       </c>
@@ -4340,7 +4340,7 @@
       <c r="AD37"/>
       <c r="AF37"/>
     </row>
-    <row r="38" hidden="1" spans="1:32">
+    <row r="38" spans="1:32">
       <c r="A38">
         <v>39</v>
       </c>
@@ -4402,7 +4402,7 @@
       <c r="AD38"/>
       <c r="AF38"/>
     </row>
-    <row r="39" hidden="1" spans="1:32">
+    <row r="39" spans="1:32">
       <c r="A39">
         <v>40</v>
       </c>
@@ -4464,7 +4464,7 @@
       <c r="AD39"/>
       <c r="AF39"/>
     </row>
-    <row r="40" hidden="1" spans="1:32">
+    <row r="40" spans="1:32">
       <c r="A40">
         <v>41</v>
       </c>
@@ -4526,7 +4526,7 @@
       <c r="AD40"/>
       <c r="AF40"/>
     </row>
-    <row r="41" hidden="1" spans="1:32">
+    <row r="41" spans="1:32">
       <c r="A41">
         <v>42</v>
       </c>
@@ -4588,7 +4588,7 @@
       <c r="AD41"/>
       <c r="AF41"/>
     </row>
-    <row r="42" hidden="1" spans="1:32">
+    <row r="42" spans="1:32">
       <c r="A42">
         <v>43</v>
       </c>
@@ -4650,7 +4650,7 @@
       <c r="AD42"/>
       <c r="AF42"/>
     </row>
-    <row r="43" hidden="1" spans="1:32">
+    <row r="43" spans="1:32">
       <c r="A43">
         <v>44</v>
       </c>
@@ -4779,7 +4779,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" hidden="1" spans="1:32">
+    <row r="45" spans="1:32">
       <c r="A45">
         <v>46</v>
       </c>
@@ -4849,7 +4849,7 @@
       <c r="AD45"/>
       <c r="AF45"/>
     </row>
-    <row r="46" hidden="1" spans="1:32">
+    <row r="46" spans="1:32">
       <c r="A46">
         <v>47</v>
       </c>
@@ -4919,7 +4919,7 @@
       <c r="AD46"/>
       <c r="AF46"/>
     </row>
-    <row r="47" hidden="1" spans="1:32">
+    <row r="47" spans="1:32">
       <c r="A47">
         <v>48</v>
       </c>
@@ -4973,7 +4973,7 @@
       <c r="AD47"/>
       <c r="AF47"/>
     </row>
-    <row r="48" hidden="1" spans="1:32">
+    <row r="48" spans="1:32">
       <c r="A48">
         <v>49</v>
       </c>
@@ -5094,7 +5094,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" hidden="1" spans="1:32">
+    <row r="50" spans="1:32">
       <c r="A50">
         <v>51</v>
       </c>
@@ -5156,7 +5156,7 @@
       <c r="AD50"/>
       <c r="AF50"/>
     </row>
-    <row r="51" hidden="1" spans="1:32">
+    <row r="51" spans="1:32">
       <c r="A51">
         <v>52</v>
       </c>
@@ -5218,7 +5218,7 @@
       <c r="AD51"/>
       <c r="AF51"/>
     </row>
-    <row r="52" hidden="1" spans="1:32">
+    <row r="52" spans="1:32">
       <c r="A52">
         <v>53</v>
       </c>
@@ -5739,7 +5739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" hidden="1" spans="1:15">
+    <row r="61" spans="1:15">
       <c r="A61">
         <v>62</v>
       </c>
@@ -5778,14 +5778,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AH61" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="C"/>
-      </filters>
-    </filterColumn>
-    <extLst/>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>

--- a/Assets/StreamingAssets/Configurations/Cards.xlsx
+++ b/Assets/StreamingAssets/Configurations/Cards.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" activeTab="3"/>
+    <workbookView windowWidth="24750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="338">
   <si>
     <t>ID</t>
   </si>
@@ -140,7 +140,7 @@
     <t>参数+7</t>
   </si>
   <si>
-    <t>参数+X1$1212</t>
+    <t>参数+X1</t>
   </si>
   <si>
     <t>Common</t>
@@ -320,6 +320,9 @@
     <t>红温+5</t>
   </si>
   <si>
+    <t>红温+X1$红温变为1.5倍</t>
+  </si>
+  <si>
     <t>神降临</t>
   </si>
   <si>
@@ -960,6 +963,36 @@
   </si>
   <si>
     <t>回合开始时，抽一张卡</t>
+  </si>
+  <si>
+    <t>舰长BUFF1</t>
+  </si>
+  <si>
+    <t>舰长BUFF2</t>
+  </si>
+  <si>
+    <t>舰长BUFF3</t>
+  </si>
+  <si>
+    <t>舰长BUFF4</t>
+  </si>
+  <si>
+    <t>舰长BUFF5</t>
+  </si>
+  <si>
+    <t>舰长BUFF6</t>
+  </si>
+  <si>
+    <t>舰长BUFF7</t>
+  </si>
+  <si>
+    <t>舰长BUFF8</t>
+  </si>
+  <si>
+    <t>舰长BUFF9</t>
+  </si>
+  <si>
+    <t>舰长BUFF10</t>
   </si>
   <si>
     <t>OperatorType</t>
@@ -3140,7 +3173,7 @@
         <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>79</v>
@@ -3179,7 +3212,7 @@
         <v>7</v>
       </c>
       <c r="AC18">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="AD18" s="3">
         <v>1.5</v>
@@ -3191,13 +3224,13 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D19" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>55</v>
@@ -3254,13 +3287,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C20" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D20" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>36</v>
@@ -3314,13 +3347,13 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>79</v>
@@ -3383,13 +3416,13 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C22" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>79</v>
@@ -3446,13 +3479,13 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>79</v>
@@ -3509,13 +3542,13 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D24" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>36</v>
@@ -3575,13 +3608,13 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>36</v>
@@ -3630,13 +3663,13 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>36</v>
@@ -3693,13 +3726,13 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C27" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D27" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>55</v>
@@ -3765,13 +3798,13 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C28" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D28" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>36</v>
@@ -3783,7 +3816,7 @@
         <v>47</v>
       </c>
       <c r="H28" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J28" t="s">
         <v>39</v>
@@ -3822,13 +3855,13 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C29" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D29" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>79</v>
@@ -3893,13 +3926,13 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C30" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D30" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>79</v>
@@ -3956,13 +3989,13 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C31" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D31" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>55</v>
@@ -4019,13 +4052,13 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C32" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D32" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>55</v>
@@ -4065,13 +4098,13 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C33" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D33" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>55</v>
@@ -4121,13 +4154,13 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C34" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D34" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>79</v>
@@ -4174,13 +4207,13 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C35" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D35" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>79</v>
@@ -4192,7 +4225,7 @@
         <v>47</v>
       </c>
       <c r="H35" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J35" t="s">
         <v>39</v>
@@ -4227,10 +4260,10 @@
         <v>144</v>
       </c>
       <c r="C36" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D36" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>79</v>
@@ -4283,13 +4316,13 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C37" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D37" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>79</v>
@@ -4345,13 +4378,13 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C38" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D38" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>55</v>
@@ -4407,13 +4440,13 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C39" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D39" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>55</v>
@@ -4469,13 +4502,13 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C40" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D40" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>55</v>
@@ -4531,13 +4564,13 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C41" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D41" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>36</v>
@@ -4593,13 +4626,13 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C42" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D42" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>79</v>
@@ -4655,13 +4688,13 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C43" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D43" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>79</v>
@@ -4725,13 +4758,13 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C44" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D44" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>79</v>
@@ -4784,13 +4817,13 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C45" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D45" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>79</v>
@@ -4854,13 +4887,13 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C46" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D46" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>55</v>
@@ -4924,13 +4957,13 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C47" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D47" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>36</v>
@@ -4981,10 +5014,10 @@
         <v>123</v>
       </c>
       <c r="C48" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D48" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>36</v>
@@ -5040,13 +5073,13 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C49" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D49" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>36</v>
@@ -5058,7 +5091,7 @@
         <v>47</v>
       </c>
       <c r="H49" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J49" t="s">
         <v>39</v>
@@ -5099,13 +5132,13 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C50" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D50" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>55</v>
@@ -5161,13 +5194,13 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C51" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D51" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>55</v>
@@ -5223,13 +5256,13 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C52" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D52" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>79</v>
@@ -5285,13 +5318,13 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C53" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D53" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>55</v>
@@ -5347,13 +5380,13 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C54" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D54" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>79</v>
@@ -5418,13 +5451,13 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C55" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D55" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>79</v>
@@ -5478,13 +5511,13 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C56" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D56" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>79</v>
@@ -5496,7 +5529,7 @@
         <v>47</v>
       </c>
       <c r="H56" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J56" t="s">
         <v>56</v>
@@ -5550,13 +5583,13 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C57" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D57" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>55</v>
@@ -5568,7 +5601,7 @@
         <v>47</v>
       </c>
       <c r="H57" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J57" t="s">
         <v>56</v>
@@ -5612,13 +5645,13 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C58" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D58" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>36</v>
@@ -5630,7 +5663,7 @@
         <v>47</v>
       </c>
       <c r="H58" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J58" t="s">
         <v>39</v>
@@ -5653,13 +5686,13 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C59" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D59" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>79</v>
@@ -5671,7 +5704,7 @@
         <v>47</v>
       </c>
       <c r="H59" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J59" t="s">
         <v>39</v>
@@ -5703,13 +5736,13 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C60" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D60" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>55</v>
@@ -5721,7 +5754,7 @@
         <v>47</v>
       </c>
       <c r="H60" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J60" t="s">
         <v>39</v>
@@ -5744,19 +5777,25 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C61" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D61" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>79</v>
       </c>
       <c r="F61" t="s">
         <v>37</v>
+      </c>
+      <c r="G61" t="s">
+        <v>47</v>
+      </c>
+      <c r="H61" t="s">
+        <v>116</v>
       </c>
       <c r="J61" t="s">
         <v>56</v>
@@ -5815,19 +5854,19 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5835,13 +5874,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I2">
         <v>-1</v>
@@ -5852,19 +5891,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -5875,16 +5914,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -5895,16 +5934,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -5915,13 +5954,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -5932,16 +5971,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -5952,13 +5991,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -5972,13 +6011,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>207</v>
+      </c>
+      <c r="C9" t="s">
+        <v>207</v>
+      </c>
+      <c r="D9" t="s">
         <v>206</v>
-      </c>
-      <c r="C9" t="s">
-        <v>206</v>
-      </c>
-      <c r="D9" t="s">
-        <v>205</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -5992,13 +6031,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -6012,13 +6051,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -6029,16 +6068,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E12" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -6049,16 +6088,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D13" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E13" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -6069,19 +6108,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C14" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D14" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -6092,16 +6131,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E15" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -6112,16 +6151,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C16" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D16" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E16" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -6132,13 +6171,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C17" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D17" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -6152,16 +6191,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C18" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D18" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E18" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -6172,13 +6211,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C19" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D19" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -6192,13 +6231,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C20" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D20" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -6212,16 +6251,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C21" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D21" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E21" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -6232,16 +6271,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C22" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D22" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E22" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -6252,13 +6291,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C23" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D23" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E23">
         <v>5</v>
@@ -6272,19 +6311,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C24" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D24" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -6295,13 +6334,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C25" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D25" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -6315,16 +6354,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C26" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D26" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E26" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -6338,16 +6377,16 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C27" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D27" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E27" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -6358,13 +6397,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C28" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D28" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -6378,19 +6417,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C29" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D29" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -6404,13 +6443,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C30" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D30" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -6424,19 +6463,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C31" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D31" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E31" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F31" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -6447,19 +6486,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C32" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D32" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E32">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -6470,19 +6509,19 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C33" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D33" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E33">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -6493,16 +6532,16 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C34" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D34" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E34" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -6513,16 +6552,16 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C35" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D35" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E35" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -6533,19 +6572,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
+        <v>250</v>
+      </c>
+      <c r="C36" t="s">
+        <v>250</v>
+      </c>
+      <c r="D36" t="s">
+        <v>190</v>
+      </c>
+      <c r="E36" t="s">
         <v>249</v>
       </c>
-      <c r="C36" t="s">
-        <v>249</v>
-      </c>
-      <c r="D36" t="s">
-        <v>189</v>
-      </c>
-      <c r="E36" t="s">
-        <v>248</v>
-      </c>
       <c r="F36" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -6559,13 +6598,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C37" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D37" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E37">
         <v>11</v>
@@ -6579,16 +6618,16 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C38" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D38" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E38" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -6599,13 +6638,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C39" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D39" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -6622,16 +6661,16 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C40" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D40" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E40" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -6642,13 +6681,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C41" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D41" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -6665,19 +6704,19 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C42" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D42" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -6691,13 +6730,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D43" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E43">
         <v>12</v>
@@ -6711,13 +6750,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C44" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D44" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E44">
         <v>13</v>
@@ -6731,19 +6770,19 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C45" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E45" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F45" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I45">
         <v>-1</v>
@@ -6754,16 +6793,16 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C46" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D46" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E46" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I46">
         <v>1</v>
@@ -6774,13 +6813,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C47" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D47" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E47">
         <v>14</v>
@@ -6794,19 +6833,19 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C48" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D48" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I48">
         <v>-1</v>
@@ -6817,13 +6856,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C49" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D49" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E49">
         <v>15</v>
@@ -6837,19 +6876,19 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C50" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D50" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I50">
         <v>-1</v>
@@ -6860,13 +6899,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C51" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D51" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E51">
         <v>16</v>
@@ -6880,13 +6919,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C52" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D52" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -6900,13 +6939,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C53" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D53" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E53">
         <v>3</v>
@@ -6920,13 +6959,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C54" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D54" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E54">
         <v>3</v>
@@ -6943,16 +6982,16 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C55" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D55" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E55" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G55">
         <v>6</v>
@@ -6966,16 +7005,16 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C56" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D56" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E56" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G56">
         <v>7</v>
@@ -6989,16 +7028,16 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C57" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D57" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E57" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G57">
         <v>8</v>
@@ -7012,16 +7051,16 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C58" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D58" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E58" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G58">
         <v>6</v>
@@ -7035,16 +7074,16 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
+        <v>279</v>
+      </c>
+      <c r="C59" t="s">
         <v>278</v>
       </c>
-      <c r="C59" t="s">
-        <v>277</v>
-      </c>
       <c r="D59" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E59" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G59">
         <v>7</v>
@@ -7058,16 +7097,16 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C60" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D60" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E60" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G60">
         <v>8</v>
@@ -7081,19 +7120,19 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C61" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E61">
         <v>3</v>
       </c>
       <c r="F61" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I61">
         <v>-1</v>
@@ -7104,13 +7143,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C62" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D62" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E62">
         <v>20</v>
@@ -7124,16 +7163,16 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C63" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D63" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F63" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I63">
         <v>-1</v>
@@ -7144,13 +7183,13 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C64" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D64" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E64">
         <v>21</v>
@@ -7164,13 +7203,13 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C65" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D65" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E65">
         <v>3</v>
@@ -7184,19 +7223,19 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C66" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D66" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E66">
         <v>14</v>
       </c>
       <c r="F66" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I66">
         <v>-1</v>
@@ -7207,13 +7246,13 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C67" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D67" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E67">
         <v>22</v>
@@ -7232,7 +7271,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9.425" customWidth="1"/>
@@ -7255,13 +7294,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F1" t="s">
         <v>16</v>
@@ -7288,10 +7327,10 @@
         <v>26</v>
       </c>
       <c r="N1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -7299,10 +7338,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -7328,10 +7367,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C3" t="s">
         <v>294</v>
-      </c>
-      <c r="C3" t="s">
-        <v>293</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -7351,10 +7390,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -7368,10 +7407,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -7403,10 +7442,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -7426,10 +7465,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -7449,10 +7488,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -7472,10 +7511,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -7495,10 +7534,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -7518,10 +7557,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -7547,10 +7586,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C12" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -7576,10 +7615,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C13" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -7599,10 +7638,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C14" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -7622,10 +7661,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C15" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -7645,10 +7684,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C16" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -7668,10 +7707,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C17" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -7691,10 +7730,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C18" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -7714,10 +7753,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C19" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -7731,10 +7770,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C20" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -7748,10 +7787,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C21" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -7765,10 +7804,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C22" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -7788,10 +7827,10 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C23" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -7811,10 +7850,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C24" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -7827,6 +7866,176 @@
       </c>
       <c r="G24">
         <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>310</v>
+      </c>
+      <c r="C25" t="s">
+        <v>294</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C26" t="s">
+        <v>294</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>312</v>
+      </c>
+      <c r="C27" t="s">
+        <v>294</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>313</v>
+      </c>
+      <c r="C28" t="s">
+        <v>294</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>314</v>
+      </c>
+      <c r="C29" t="s">
+        <v>294</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>315</v>
+      </c>
+      <c r="C30" t="s">
+        <v>294</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>316</v>
+      </c>
+      <c r="C31" t="s">
+        <v>294</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>317</v>
+      </c>
+      <c r="C32" t="s">
+        <v>294</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s">
+        <v>318</v>
+      </c>
+      <c r="C33" t="s">
+        <v>294</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s">
+        <v>319</v>
+      </c>
+      <c r="C34" t="s">
+        <v>294</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7862,16 +8071,16 @@
         <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="E1" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="F1" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="G1" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -7879,13 +8088,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="C2" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="D2" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -7899,13 +8108,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="C3" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="D3" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="F3" t="s">
         <v>43</v>
@@ -7916,13 +8125,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="C4" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="D4" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="F4" t="s">
         <v>37</v>
@@ -7933,13 +8142,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="C5" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="D5" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -7953,13 +8162,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="C6" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="D6" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -7973,13 +8182,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="C7" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="D7" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -7993,13 +8202,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="C8" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="D8" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -8013,13 +8222,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="C9" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="D9" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -8033,13 +8242,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="C10" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="D10" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -8053,13 +8262,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="C11" t="s">
+        <v>337</v>
+      </c>
+      <c r="D11" t="s">
         <v>326</v>
-      </c>
-      <c r="D11" t="s">
-        <v>315</v>
       </c>
       <c r="E11" t="s">
         <v>43</v>

--- a/Assets/StreamingAssets/Configurations/Cards.xlsx
+++ b/Assets/StreamingAssets/Configurations/Cards.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F47183-F6A7-4E70-A44F-2E8DAA5F15B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView xWindow="0" yWindow="540" windowWidth="38730" windowHeight="20850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -13,7 +19,7 @@
     <sheet name="Conditions" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cards!$A$1:$AH$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cards!$A$1:$AI$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -24,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -33,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="339">
   <si>
     <t>ID</t>
   </si>
@@ -1047,172 +1051,32 @@
   </si>
   <si>
     <t>VCardTypeUsedCountCondition</t>
+  </si>
+  <si>
+    <t>Priority</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1231,188 +1095,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1438,253 +1122,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1696,72 +1138,29 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="00FFFFFF"/>
-      <color rgb="00AB0580"/>
-      <color rgb="0000B050"/>
-      <color rgb="00FFB200"/>
-      <color rgb="004B58FF"/>
-      <color rgb="00FF2160"/>
+      <color rgb="FFFFFFFF"/>
+      <color rgb="FFAB0580"/>
+      <color rgb="FF00B050"/>
+      <color rgb="FFFFB200"/>
+      <color rgb="FF4B58FF"/>
+      <color rgb="FFFF2160"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2019,49 +1418,49 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:AH61"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AI61"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.425" customWidth="1"/>
-    <col min="2" max="2" width="12.7083333333333" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
-    <col min="4" max="4" width="57.7083333333333" customWidth="1"/>
-    <col min="5" max="5" width="10.425" style="2" customWidth="1"/>
-    <col min="6" max="6" width="4.85833333333333" customWidth="1"/>
-    <col min="7" max="7" width="7.85833333333333" customWidth="1"/>
+    <col min="4" max="4" width="57.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="4.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.85546875" customWidth="1"/>
     <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="9" max="9" width="5.56666666666667" style="3" customWidth="1"/>
-    <col min="10" max="10" width="10.5666666666667" customWidth="1"/>
-    <col min="11" max="11" width="9.70833333333333" style="3" customWidth="1"/>
-    <col min="12" max="12" width="7.14166666666667" customWidth="1"/>
+    <col min="9" max="9" width="5.5703125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" style="3" customWidth="1"/>
+    <col min="12" max="12" width="7.140625" customWidth="1"/>
     <col min="13" max="13" width="14" style="3" customWidth="1"/>
-    <col min="14" max="14" width="10.2833333333333" customWidth="1"/>
-    <col min="15" max="15" width="13.7083333333333" customWidth="1"/>
-    <col min="16" max="16" width="9.70833333333333" style="3" customWidth="1"/>
-    <col min="17" max="17" width="9.70833333333333" customWidth="1"/>
-    <col min="18" max="18" width="12.1416666666667" customWidth="1"/>
-    <col min="19" max="19" width="17.7083333333333" style="3" customWidth="1"/>
-    <col min="20" max="20" width="11" customWidth="1"/>
-    <col min="21" max="21" width="12.2833333333333" customWidth="1"/>
-    <col min="22" max="22" width="17.1416666666667" style="3" customWidth="1"/>
-    <col min="25" max="25" width="17.7083333333333" style="3" customWidth="1"/>
-    <col min="26" max="26" width="10.7083333333333" customWidth="1"/>
-    <col min="27" max="27" width="11" customWidth="1"/>
-    <col min="28" max="28" width="17.7083333333333" style="3" customWidth="1"/>
-    <col min="29" max="29" width="12.425" customWidth="1"/>
-    <col min="30" max="30" width="12.425" style="3" customWidth="1"/>
-    <col min="31" max="31" width="12.2833333333333" customWidth="1"/>
-    <col min="32" max="32" width="9" style="3"/>
-    <col min="33" max="33" width="4.28333333333333" customWidth="1"/>
+    <col min="14" max="14" width="10.28515625" customWidth="1"/>
+    <col min="15" max="16" width="13.7109375" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="3" customWidth="1"/>
+    <col min="18" max="18" width="9.7109375" customWidth="1"/>
+    <col min="19" max="19" width="12.140625" customWidth="1"/>
+    <col min="20" max="20" width="17.7109375" style="3" customWidth="1"/>
+    <col min="21" max="21" width="11" customWidth="1"/>
+    <col min="22" max="22" width="12.28515625" customWidth="1"/>
+    <col min="23" max="23" width="17.140625" style="3" customWidth="1"/>
+    <col min="26" max="26" width="17.7109375" style="3" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" customWidth="1"/>
+    <col min="28" max="28" width="11" customWidth="1"/>
+    <col min="29" max="29" width="17.7109375" style="3" customWidth="1"/>
+    <col min="30" max="30" width="12.42578125" customWidth="1"/>
+    <col min="31" max="31" width="12.42578125" style="3" customWidth="1"/>
+    <col min="32" max="32" width="12.28515625" customWidth="1"/>
+    <col min="33" max="33" width="9" style="3"/>
+    <col min="34" max="34" width="4.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33">
+    <row r="1" spans="1:35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2107,62 +1506,65 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AA1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AD1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:33">
+    <row r="2" spans="1:35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2175,7 +1577,7 @@
       <c r="D2" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="7" t="s">
         <v>36</v>
       </c>
       <c r="F2" t="s">
@@ -2200,24 +1602,27 @@
       <c r="O2">
         <v>0</v>
       </c>
-      <c r="P2"/>
-      <c r="Q2" s="2">
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2"/>
+      <c r="R2" s="2">
         <v>11</v>
       </c>
-      <c r="R2">
+      <c r="S2">
         <v>7</v>
       </c>
-      <c r="S2" s="3">
+      <c r="T2" s="3">
         <v>7</v>
       </c>
-      <c r="V2"/>
-      <c r="Y2"/>
-      <c r="AB2"/>
-      <c r="AD2"/>
-      <c r="AF2"/>
-      <c r="AG2" s="5"/>
-    </row>
-    <row r="3" spans="1:33">
+      <c r="W2"/>
+      <c r="Z2"/>
+      <c r="AC2"/>
+      <c r="AE2"/>
+      <c r="AG2"/>
+      <c r="AH2" s="5"/>
+    </row>
+    <row r="3" spans="1:35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2255,24 +1660,27 @@
       <c r="O3">
         <v>0</v>
       </c>
-      <c r="P3"/>
-      <c r="Q3" s="2">
-        <v>2</v>
-      </c>
-      <c r="R3">
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3"/>
+      <c r="R3" s="2">
+        <v>2</v>
+      </c>
+      <c r="S3">
         <v>4</v>
       </c>
-      <c r="S3" s="3">
+      <c r="T3" s="3">
         <v>4</v>
       </c>
-      <c r="V3"/>
-      <c r="Y3"/>
-      <c r="AB3"/>
-      <c r="AD3"/>
-      <c r="AF3"/>
-      <c r="AG3" s="5"/>
-    </row>
-    <row r="4" spans="1:33">
+      <c r="W3"/>
+      <c r="Z3"/>
+      <c r="AC3"/>
+      <c r="AE3"/>
+      <c r="AG3"/>
+      <c r="AH3" s="5"/>
+    </row>
+    <row r="4" spans="1:35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2312,27 +1720,30 @@
       <c r="O4">
         <v>0</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="R4" s="2">
         <v>11</v>
       </c>
-      <c r="R4">
+      <c r="S4">
         <v>15</v>
       </c>
-      <c r="S4" s="3">
+      <c r="T4" s="3">
         <v>18</v>
       </c>
-      <c r="T4">
+      <c r="U4">
         <v>56</v>
       </c>
-      <c r="U4">
+      <c r="V4">
         <v>9</v>
       </c>
-      <c r="V4" s="3">
+      <c r="W4" s="3">
         <v>12</v>
       </c>
-      <c r="AG4" s="5"/>
-    </row>
-    <row r="5" spans="1:33">
+      <c r="AH4" s="5"/>
+    </row>
+    <row r="5" spans="1:35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2370,32 +1781,32 @@
       <c r="O5">
         <v>0</v>
       </c>
-      <c r="P5"/>
-      <c r="Q5" s="2">
+      <c r="Q5"/>
+      <c r="R5" s="2">
         <v>11</v>
       </c>
-      <c r="R5">
+      <c r="S5">
         <v>5</v>
       </c>
-      <c r="S5" s="3">
+      <c r="T5" s="3">
         <v>5</v>
       </c>
-      <c r="T5" s="2">
-        <v>2</v>
-      </c>
-      <c r="U5">
-        <v>2</v>
-      </c>
-      <c r="V5" s="3">
-        <v>2</v>
-      </c>
-      <c r="Y5"/>
-      <c r="AB5"/>
-      <c r="AD5"/>
-      <c r="AF5"/>
-      <c r="AG5" s="5"/>
-    </row>
-    <row r="6" spans="1:33">
+      <c r="U5" s="2">
+        <v>2</v>
+      </c>
+      <c r="V5">
+        <v>2</v>
+      </c>
+      <c r="W5" s="3">
+        <v>2</v>
+      </c>
+      <c r="Z5"/>
+      <c r="AC5"/>
+      <c r="AE5"/>
+      <c r="AG5"/>
+      <c r="AH5" s="5"/>
+    </row>
+    <row r="6" spans="1:35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2438,30 +1849,30 @@
       <c r="O6">
         <v>1</v>
       </c>
-      <c r="Q6" s="2">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>2</v>
+      <c r="R6" s="2">
+        <v>0</v>
       </c>
       <c r="U6">
         <v>2</v>
       </c>
-      <c r="V6" s="3">
+      <c r="V6">
+        <v>2</v>
+      </c>
+      <c r="W6" s="3">
         <v>7</v>
       </c>
-      <c r="W6">
+      <c r="X6">
         <v>9</v>
       </c>
-      <c r="X6">
-        <v>1</v>
-      </c>
-      <c r="Y6" s="3">
-        <v>1</v>
-      </c>
-      <c r="AG6" s="5"/>
-    </row>
-    <row r="7" spans="1:33">
+      <c r="Y6">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="3">
+        <v>1</v>
+      </c>
+      <c r="AH6" s="5"/>
+    </row>
+    <row r="7" spans="1:35">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2499,35 +1910,35 @@
       <c r="O7">
         <v>1</v>
       </c>
-      <c r="P7"/>
-      <c r="Q7" s="2">
+      <c r="Q7"/>
+      <c r="R7" s="2">
         <v>4</v>
       </c>
-      <c r="S7"/>
-      <c r="T7" s="2">
+      <c r="T7"/>
+      <c r="U7" s="2">
         <v>21</v>
       </c>
-      <c r="U7">
-        <v>2</v>
-      </c>
-      <c r="V7" s="3">
-        <v>2</v>
-      </c>
-      <c r="W7" s="2">
+      <c r="V7">
+        <v>2</v>
+      </c>
+      <c r="W7" s="3">
+        <v>2</v>
+      </c>
+      <c r="X7" s="2">
         <v>14</v>
       </c>
-      <c r="X7">
-        <v>1</v>
-      </c>
-      <c r="Y7" s="3">
-        <v>1</v>
-      </c>
-      <c r="AB7"/>
-      <c r="AD7"/>
-      <c r="AF7"/>
-      <c r="AG7" s="5"/>
-    </row>
-    <row r="8" spans="1:33">
+      <c r="Y7">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC7"/>
+      <c r="AE7"/>
+      <c r="AG7"/>
+      <c r="AH7" s="5"/>
+    </row>
+    <row r="8" spans="1:35">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2567,40 +1978,40 @@
       <c r="O8">
         <v>1</v>
       </c>
-      <c r="P8"/>
-      <c r="Q8" s="2">
-        <v>2</v>
-      </c>
-      <c r="R8">
+      <c r="Q8"/>
+      <c r="R8" s="2">
+        <v>2</v>
+      </c>
+      <c r="S8">
         <v>7</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7</v>
       </c>
-      <c r="T8" s="2">
-        <v>3</v>
-      </c>
-      <c r="U8">
-        <v>1</v>
-      </c>
-      <c r="V8" s="3">
-        <v>1</v>
-      </c>
-      <c r="W8" s="2">
+      <c r="U8" s="2">
+        <v>3</v>
+      </c>
+      <c r="V8">
+        <v>1</v>
+      </c>
+      <c r="W8" s="3">
+        <v>1</v>
+      </c>
+      <c r="X8" s="2">
         <v>14</v>
       </c>
-      <c r="X8">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>1</v>
-      </c>
-      <c r="AB8"/>
-      <c r="AD8"/>
-      <c r="AF8"/>
-      <c r="AG8" s="5"/>
-    </row>
-    <row r="9" spans="1:33">
+      <c r="Y8">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC8"/>
+      <c r="AE8"/>
+      <c r="AG8"/>
+      <c r="AH8" s="5"/>
+    </row>
+    <row r="9" spans="1:35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2638,32 +2049,32 @@
       <c r="O9">
         <v>0</v>
       </c>
-      <c r="P9"/>
-      <c r="Q9" s="2">
+      <c r="Q9"/>
+      <c r="R9" s="2">
         <v>6</v>
       </c>
-      <c r="R9">
-        <v>3</v>
-      </c>
-      <c r="S9" s="3">
+      <c r="S9">
+        <v>3</v>
+      </c>
+      <c r="T9" s="3">
         <v>4</v>
       </c>
-      <c r="T9" s="2">
-        <v>2</v>
-      </c>
-      <c r="U9">
-        <v>3</v>
-      </c>
-      <c r="V9" s="3">
+      <c r="U9" s="2">
+        <v>2</v>
+      </c>
+      <c r="V9">
+        <v>3</v>
+      </c>
+      <c r="W9" s="3">
         <v>4</v>
       </c>
-      <c r="Y9"/>
-      <c r="AB9"/>
-      <c r="AD9"/>
-      <c r="AF9"/>
-      <c r="AG9" s="5"/>
-    </row>
-    <row r="10" spans="1:33">
+      <c r="Z9"/>
+      <c r="AC9"/>
+      <c r="AE9"/>
+      <c r="AG9"/>
+      <c r="AH9" s="5"/>
+    </row>
+    <row r="10" spans="1:35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2701,32 +2112,32 @@
       <c r="O10">
         <v>0</v>
       </c>
-      <c r="P10"/>
-      <c r="Q10" s="2">
+      <c r="Q10"/>
+      <c r="R10" s="2">
         <v>7</v>
       </c>
-      <c r="R10">
-        <v>2</v>
-      </c>
-      <c r="S10" s="3">
-        <v>3</v>
-      </c>
-      <c r="T10" s="2">
-        <v>2</v>
-      </c>
-      <c r="U10">
-        <v>2</v>
-      </c>
-      <c r="V10" s="3">
-        <v>3</v>
-      </c>
-      <c r="Y10"/>
-      <c r="AB10"/>
-      <c r="AD10"/>
-      <c r="AF10"/>
-      <c r="AG10" s="5"/>
-    </row>
-    <row r="11" spans="1:33">
+      <c r="S10">
+        <v>2</v>
+      </c>
+      <c r="T10" s="3">
+        <v>3</v>
+      </c>
+      <c r="U10" s="2">
+        <v>2</v>
+      </c>
+      <c r="V10">
+        <v>2</v>
+      </c>
+      <c r="W10" s="3">
+        <v>3</v>
+      </c>
+      <c r="Z10"/>
+      <c r="AC10"/>
+      <c r="AE10"/>
+      <c r="AG10"/>
+      <c r="AH10" s="5"/>
+    </row>
+    <row r="11" spans="1:35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2766,27 +2177,27 @@
       <c r="O11">
         <v>0</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="R11" s="2">
         <v>15</v>
       </c>
-      <c r="R11">
-        <v>2</v>
-      </c>
-      <c r="S11" s="3">
-        <v>3</v>
-      </c>
-      <c r="T11" s="2">
-        <v>2</v>
-      </c>
-      <c r="U11">
-        <v>2</v>
-      </c>
-      <c r="V11" s="3">
-        <v>3</v>
-      </c>
-      <c r="AG11" s="5"/>
-    </row>
-    <row r="12" spans="1:34">
+      <c r="S11">
+        <v>2</v>
+      </c>
+      <c r="T11" s="3">
+        <v>3</v>
+      </c>
+      <c r="U11" s="2">
+        <v>2</v>
+      </c>
+      <c r="V11">
+        <v>2</v>
+      </c>
+      <c r="W11" s="3">
+        <v>3</v>
+      </c>
+      <c r="AH11" s="5"/>
+    </row>
+    <row r="12" spans="1:35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2824,35 +2235,35 @@
       <c r="O12">
         <v>0</v>
       </c>
-      <c r="P12"/>
-      <c r="Q12" s="2">
+      <c r="Q12"/>
+      <c r="R12" s="2">
         <v>11</v>
       </c>
-      <c r="R12">
+      <c r="S12">
         <v>9</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>13</v>
       </c>
-      <c r="T12" s="2">
+      <c r="U12" s="2">
         <v>11</v>
       </c>
-      <c r="U12">
+      <c r="V12">
         <v>9</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>13</v>
       </c>
-      <c r="Y12"/>
-      <c r="AB12"/>
-      <c r="AD12"/>
-      <c r="AF12"/>
-      <c r="AG12" s="5"/>
-      <c r="AH12" t="s">
+      <c r="Z12"/>
+      <c r="AC12"/>
+      <c r="AE12"/>
+      <c r="AG12"/>
+      <c r="AH12" s="5"/>
+      <c r="AI12" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="13" spans="1:33">
+    <row r="13" spans="1:35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2890,32 +2301,32 @@
       <c r="O13">
         <v>0</v>
       </c>
-      <c r="P13"/>
-      <c r="Q13" s="2">
+      <c r="Q13"/>
+      <c r="R13" s="2">
         <v>11</v>
       </c>
-      <c r="R13">
+      <c r="S13">
         <v>11</v>
       </c>
-      <c r="S13" s="3">
+      <c r="T13" s="3">
         <v>15</v>
       </c>
-      <c r="T13" s="2">
-        <v>2</v>
-      </c>
-      <c r="U13">
+      <c r="U13" s="2">
+        <v>2</v>
+      </c>
+      <c r="V13">
         <v>7</v>
       </c>
-      <c r="V13" s="3">
+      <c r="W13" s="3">
         <v>9</v>
       </c>
-      <c r="Y13"/>
-      <c r="AB13"/>
-      <c r="AD13"/>
-      <c r="AF13"/>
-      <c r="AG13" s="5"/>
-    </row>
-    <row r="14" spans="1:33">
+      <c r="Z13"/>
+      <c r="AC13"/>
+      <c r="AE13"/>
+      <c r="AG13"/>
+      <c r="AH13" s="5"/>
+    </row>
+    <row r="14" spans="1:35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2953,24 +2364,24 @@
       <c r="O14">
         <v>0</v>
       </c>
-      <c r="P14"/>
-      <c r="Q14" s="2">
+      <c r="Q14"/>
+      <c r="R14" s="2">
         <v>6</v>
       </c>
-      <c r="R14">
+      <c r="S14">
         <v>6</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>8</v>
       </c>
-      <c r="V14"/>
-      <c r="Y14"/>
-      <c r="AB14"/>
-      <c r="AD14"/>
-      <c r="AF14"/>
-      <c r="AG14" s="5"/>
-    </row>
-    <row r="15" spans="1:33">
+      <c r="W14"/>
+      <c r="Z14"/>
+      <c r="AC14"/>
+      <c r="AE14"/>
+      <c r="AG14"/>
+      <c r="AH14" s="5"/>
+    </row>
+    <row r="15" spans="1:35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3008,24 +2419,24 @@
       <c r="O15">
         <v>0</v>
       </c>
-      <c r="P15"/>
-      <c r="Q15" s="2">
+      <c r="Q15"/>
+      <c r="R15" s="2">
         <v>18</v>
       </c>
-      <c r="R15">
+      <c r="S15">
         <v>1.4</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1.8</v>
       </c>
-      <c r="V15"/>
-      <c r="Y15"/>
-      <c r="AB15"/>
-      <c r="AD15"/>
-      <c r="AF15"/>
-      <c r="AG15" s="5"/>
-    </row>
-    <row r="16" spans="1:33">
+      <c r="W15"/>
+      <c r="Z15"/>
+      <c r="AC15"/>
+      <c r="AE15"/>
+      <c r="AG15"/>
+      <c r="AH15" s="5"/>
+    </row>
+    <row r="16" spans="1:35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3063,32 +2474,32 @@
       <c r="O16">
         <v>0</v>
       </c>
-      <c r="P16"/>
-      <c r="Q16" s="2">
+      <c r="Q16"/>
+      <c r="R16" s="2">
         <v>6</v>
       </c>
-      <c r="R16">
+      <c r="S16">
         <v>4</v>
       </c>
-      <c r="S16" s="3">
+      <c r="T16" s="3">
         <v>5</v>
       </c>
-      <c r="T16" s="2">
+      <c r="U16" s="2">
         <v>18</v>
       </c>
-      <c r="U16">
+      <c r="V16">
         <v>0.8</v>
       </c>
-      <c r="V16" s="3">
-        <v>1.1</v>
-      </c>
-      <c r="Y16"/>
-      <c r="AB16"/>
-      <c r="AD16"/>
-      <c r="AF16"/>
-      <c r="AG16" s="5"/>
-    </row>
-    <row r="17" spans="1:33">
+      <c r="W16" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="Z16"/>
+      <c r="AC16"/>
+      <c r="AE16"/>
+      <c r="AG16"/>
+      <c r="AH16" s="5"/>
+    </row>
+    <row r="17" spans="1:34">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3129,40 +2540,40 @@
       <c r="O17">
         <v>1</v>
       </c>
-      <c r="P17"/>
-      <c r="Q17" s="2">
+      <c r="Q17"/>
+      <c r="R17" s="2">
         <v>19</v>
       </c>
-      <c r="R17">
-        <v>1</v>
-      </c>
-      <c r="S17" s="3">
-        <v>1</v>
-      </c>
-      <c r="T17" s="2">
-        <v>2</v>
-      </c>
-      <c r="U17">
+      <c r="S17">
+        <v>1</v>
+      </c>
+      <c r="T17" s="3">
+        <v>1</v>
+      </c>
+      <c r="U17" s="2">
+        <v>2</v>
+      </c>
+      <c r="V17">
         <v>4</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6</v>
       </c>
-      <c r="W17" s="2">
+      <c r="X17" s="2">
         <v>21</v>
       </c>
-      <c r="X17">
-        <v>2</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>3</v>
-      </c>
-      <c r="AB17"/>
-      <c r="AD17"/>
-      <c r="AF17"/>
-      <c r="AG17" s="6"/>
-    </row>
-    <row r="18" spans="1:33">
+      <c r="Y17">
+        <v>2</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>3</v>
+      </c>
+      <c r="AC17"/>
+      <c r="AE17"/>
+      <c r="AG17"/>
+      <c r="AH17" s="6"/>
+    </row>
+    <row r="18" spans="1:34">
       <c r="A18">
         <v>18</v>
       </c>
@@ -3202,24 +2613,24 @@
       <c r="O18">
         <v>0</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="R18" s="2">
         <v>15</v>
       </c>
-      <c r="R18">
+      <c r="S18">
         <v>5</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>7</v>
       </c>
-      <c r="AC18">
+      <c r="AD18">
         <v>63</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1.5</v>
       </c>
-      <c r="AG18" s="5"/>
-    </row>
-    <row r="19" spans="1:33">
+      <c r="AH18" s="5"/>
+    </row>
+    <row r="19" spans="1:34">
       <c r="A19">
         <v>19</v>
       </c>
@@ -3257,32 +2668,32 @@
       <c r="O19">
         <v>1</v>
       </c>
-      <c r="P19"/>
-      <c r="Q19" s="2">
+      <c r="Q19"/>
+      <c r="R19" s="2">
         <v>23</v>
       </c>
-      <c r="R19">
-        <v>1</v>
-      </c>
-      <c r="S19" s="3">
-        <v>1</v>
-      </c>
-      <c r="T19" s="2">
+      <c r="S19">
+        <v>1</v>
+      </c>
+      <c r="T19" s="3">
+        <v>1</v>
+      </c>
+      <c r="U19" s="2">
         <v>7</v>
       </c>
-      <c r="U19">
-        <v>1</v>
-      </c>
-      <c r="V19" s="3">
-        <v>2</v>
-      </c>
-      <c r="Y19"/>
-      <c r="AB19"/>
-      <c r="AD19"/>
-      <c r="AF19"/>
-      <c r="AG19" s="5"/>
-    </row>
-    <row r="20" spans="1:33">
+      <c r="V19">
+        <v>1</v>
+      </c>
+      <c r="W19" s="3">
+        <v>2</v>
+      </c>
+      <c r="Z19"/>
+      <c r="AC19"/>
+      <c r="AE19"/>
+      <c r="AG19"/>
+      <c r="AH19" s="5"/>
+    </row>
+    <row r="20" spans="1:34">
       <c r="A20">
         <v>20</v>
       </c>
@@ -3322,27 +2733,27 @@
       <c r="O20">
         <v>0</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="2">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="2">
         <v>11</v>
       </c>
-      <c r="R20">
+      <c r="S20">
         <v>24</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>30</v>
       </c>
-      <c r="AC20">
+      <c r="AD20">
         <v>62</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>7</v>
       </c>
-      <c r="AG20" s="6"/>
-    </row>
-    <row r="21" spans="1:33">
+      <c r="AH20" s="6"/>
+    </row>
+    <row r="21" spans="1:34">
       <c r="A21">
         <v>21</v>
       </c>
@@ -3382,36 +2793,36 @@
       <c r="O21">
         <v>1</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="R21" s="2">
         <v>26</v>
       </c>
-      <c r="R21">
-        <v>2</v>
-      </c>
-      <c r="S21" s="3">
-        <v>2</v>
-      </c>
-      <c r="T21" s="2">
+      <c r="S21">
+        <v>2</v>
+      </c>
+      <c r="T21" s="3">
+        <v>2</v>
+      </c>
+      <c r="U21" s="2">
         <v>11</v>
       </c>
-      <c r="U21">
+      <c r="V21">
         <v>30</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>42</v>
       </c>
-      <c r="W21">
-        <v>2</v>
-      </c>
       <c r="X21">
+        <v>2</v>
+      </c>
+      <c r="Y21">
         <v>5</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>7</v>
       </c>
-      <c r="AG21" s="5"/>
-    </row>
-    <row r="22" spans="1:33">
+      <c r="AH21" s="5"/>
+    </row>
+    <row r="22" spans="1:34">
       <c r="A22">
         <v>22</v>
       </c>
@@ -3449,32 +2860,32 @@
       <c r="O22">
         <v>1</v>
       </c>
-      <c r="P22"/>
-      <c r="Q22" s="2">
+      <c r="Q22"/>
+      <c r="R22" s="2">
         <v>6</v>
       </c>
-      <c r="R22">
-        <v>2</v>
-      </c>
-      <c r="S22" s="3">
+      <c r="S22">
+        <v>2</v>
+      </c>
+      <c r="T22" s="3">
         <v>4</v>
       </c>
-      <c r="T22" s="2">
+      <c r="U22" s="2">
         <v>28</v>
       </c>
-      <c r="U22">
-        <v>1</v>
-      </c>
-      <c r="V22" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y22"/>
-      <c r="AB22"/>
-      <c r="AD22"/>
-      <c r="AF22"/>
-      <c r="AG22" s="5"/>
-    </row>
-    <row r="23" spans="1:33">
+      <c r="V22">
+        <v>1</v>
+      </c>
+      <c r="W22" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z22"/>
+      <c r="AC22"/>
+      <c r="AE22"/>
+      <c r="AG22"/>
+      <c r="AH22" s="5"/>
+    </row>
+    <row r="23" spans="1:34">
       <c r="A23">
         <v>23</v>
       </c>
@@ -3512,32 +2923,32 @@
       <c r="O23">
         <v>0</v>
       </c>
-      <c r="P23"/>
-      <c r="Q23" s="2">
+      <c r="Q23"/>
+      <c r="R23" s="2">
         <v>6</v>
       </c>
-      <c r="R23">
+      <c r="S23">
         <v>5</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>7</v>
       </c>
-      <c r="T23" s="2">
-        <v>2</v>
-      </c>
-      <c r="U23">
-        <v>1</v>
-      </c>
-      <c r="V23" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y23"/>
-      <c r="AB23"/>
-      <c r="AD23"/>
-      <c r="AF23"/>
-      <c r="AG23" s="5"/>
-    </row>
-    <row r="24" spans="1:33">
+      <c r="U23" s="2">
+        <v>2</v>
+      </c>
+      <c r="V23">
+        <v>1</v>
+      </c>
+      <c r="W23" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z23"/>
+      <c r="AC23"/>
+      <c r="AE23"/>
+      <c r="AG23"/>
+      <c r="AH23" s="5"/>
+    </row>
+    <row r="24" spans="1:34">
       <c r="A24">
         <v>24</v>
       </c>
@@ -3577,33 +2988,33 @@
       <c r="O24">
         <v>0</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="R24" s="2">
         <v>15</v>
       </c>
-      <c r="R24">
-        <v>3</v>
-      </c>
-      <c r="S24" s="3">
+      <c r="S24">
+        <v>3</v>
+      </c>
+      <c r="T24" s="3">
         <v>4</v>
       </c>
-      <c r="T24" s="2">
+      <c r="U24" s="2">
         <v>11</v>
       </c>
-      <c r="U24">
+      <c r="V24">
         <v>8</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>11</v>
       </c>
-      <c r="AC24">
+      <c r="AD24">
         <v>63</v>
       </c>
-      <c r="AD24" s="3">
-        <v>3</v>
-      </c>
-      <c r="AG24" s="5"/>
-    </row>
-    <row r="25" spans="1:33">
+      <c r="AE24" s="3">
+        <v>3</v>
+      </c>
+      <c r="AH24" s="5"/>
+    </row>
+    <row r="25" spans="1:34">
       <c r="A25">
         <v>25</v>
       </c>
@@ -3641,24 +3052,24 @@
       <c r="O25">
         <v>0</v>
       </c>
-      <c r="P25"/>
-      <c r="Q25" s="2">
+      <c r="Q25"/>
+      <c r="R25" s="2">
         <v>7</v>
       </c>
-      <c r="R25">
-        <v>3</v>
-      </c>
-      <c r="S25" s="3">
+      <c r="S25">
+        <v>3</v>
+      </c>
+      <c r="T25" s="3">
         <v>5</v>
       </c>
-      <c r="V25"/>
-      <c r="Y25"/>
-      <c r="AB25"/>
-      <c r="AD25"/>
-      <c r="AF25"/>
-      <c r="AG25" s="5"/>
-    </row>
-    <row r="26" spans="1:33">
+      <c r="W25"/>
+      <c r="Z25"/>
+      <c r="AC25"/>
+      <c r="AE25"/>
+      <c r="AG25"/>
+      <c r="AH25" s="5"/>
+    </row>
+    <row r="26" spans="1:34">
       <c r="A26">
         <v>26</v>
       </c>
@@ -3696,32 +3107,32 @@
       <c r="O26">
         <v>0</v>
       </c>
-      <c r="P26"/>
-      <c r="Q26" s="2">
+      <c r="Q26"/>
+      <c r="R26" s="2">
         <v>7</v>
       </c>
-      <c r="R26">
-        <v>3</v>
-      </c>
-      <c r="S26" s="3">
+      <c r="S26">
+        <v>3</v>
+      </c>
+      <c r="T26" s="3">
         <v>4</v>
       </c>
-      <c r="T26" s="2">
-        <v>2</v>
-      </c>
-      <c r="U26">
+      <c r="U26" s="2">
+        <v>2</v>
+      </c>
+      <c r="V26">
         <v>4</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>6</v>
       </c>
-      <c r="Y26"/>
-      <c r="AB26"/>
-      <c r="AD26"/>
-      <c r="AF26"/>
-      <c r="AG26" s="5"/>
-    </row>
-    <row r="27" spans="1:33">
+      <c r="Z26"/>
+      <c r="AC26"/>
+      <c r="AE26"/>
+      <c r="AG26"/>
+      <c r="AH26" s="5"/>
+    </row>
+    <row r="27" spans="1:34">
       <c r="A27">
         <v>27</v>
       </c>
@@ -3761,39 +3172,39 @@
       <c r="O27">
         <v>1</v>
       </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="2">
+      <c r="Q27" s="3">
+        <v>0</v>
+      </c>
+      <c r="R27" s="2">
         <v>11</v>
       </c>
-      <c r="R27">
+      <c r="S27">
         <v>12</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>18</v>
       </c>
-      <c r="T27" s="2">
+      <c r="U27" s="2">
         <v>56</v>
       </c>
-      <c r="U27">
+      <c r="V27">
         <v>24</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>30</v>
       </c>
-      <c r="W27">
+      <c r="X27">
         <v>57</v>
       </c>
-      <c r="X27">
+      <c r="Y27">
         <v>36</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>44</v>
       </c>
-      <c r="AG27" s="6"/>
-    </row>
-    <row r="28" spans="1:33">
+      <c r="AH27" s="6"/>
+    </row>
+    <row r="28" spans="1:34">
       <c r="A28">
         <v>28</v>
       </c>
@@ -3833,24 +3244,24 @@
       <c r="O28">
         <v>0</v>
       </c>
-      <c r="Q28" s="2">
-        <v>2</v>
-      </c>
-      <c r="R28">
+      <c r="R28" s="2">
+        <v>2</v>
+      </c>
+      <c r="S28">
         <v>6</v>
       </c>
-      <c r="S28" s="3">
+      <c r="T28" s="3">
         <v>8</v>
       </c>
-      <c r="AC28">
+      <c r="AD28">
         <v>21</v>
       </c>
-      <c r="AD28" s="3">
+      <c r="AE28" s="3">
         <v>12</v>
       </c>
-      <c r="AG28" s="5"/>
-    </row>
-    <row r="29" spans="1:33">
+      <c r="AH28" s="5"/>
+    </row>
+    <row r="29" spans="1:34">
       <c r="A29">
         <v>30</v>
       </c>
@@ -3888,40 +3299,40 @@
       <c r="O29">
         <v>1</v>
       </c>
-      <c r="P29"/>
-      <c r="Q29" s="2">
+      <c r="Q29"/>
+      <c r="R29" s="2">
         <v>32</v>
       </c>
-      <c r="R29">
+      <c r="S29">
         <v>30</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>30</v>
       </c>
-      <c r="T29" s="2">
-        <v>2</v>
-      </c>
-      <c r="U29">
-        <v>3</v>
-      </c>
-      <c r="V29" s="3">
+      <c r="U29" s="2">
+        <v>2</v>
+      </c>
+      <c r="V29">
+        <v>3</v>
+      </c>
+      <c r="W29" s="3">
         <v>5</v>
       </c>
-      <c r="W29" s="2">
+      <c r="X29" s="2">
         <v>21</v>
       </c>
-      <c r="X29">
-        <v>2</v>
-      </c>
-      <c r="Y29" s="3">
-        <v>3</v>
-      </c>
-      <c r="AB29"/>
-      <c r="AD29"/>
-      <c r="AF29"/>
-      <c r="AG29" s="5"/>
-    </row>
-    <row r="30" spans="1:33">
+      <c r="Y29">
+        <v>2</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>3</v>
+      </c>
+      <c r="AC29"/>
+      <c r="AE29"/>
+      <c r="AG29"/>
+      <c r="AH29" s="5"/>
+    </row>
+    <row r="30" spans="1:34">
       <c r="A30">
         <v>31</v>
       </c>
@@ -3959,32 +3370,32 @@
       <c r="O30">
         <v>1</v>
       </c>
-      <c r="P30"/>
-      <c r="Q30" s="2">
+      <c r="Q30"/>
+      <c r="R30" s="2">
         <v>33</v>
       </c>
-      <c r="R30">
+      <c r="S30">
         <v>50</v>
       </c>
-      <c r="S30" s="3">
+      <c r="T30" s="3">
         <v>70</v>
       </c>
-      <c r="T30" s="2">
-        <v>2</v>
-      </c>
-      <c r="U30">
-        <v>2</v>
-      </c>
-      <c r="V30" s="3">
+      <c r="U30" s="2">
+        <v>2</v>
+      </c>
+      <c r="V30">
+        <v>2</v>
+      </c>
+      <c r="W30" s="3">
         <v>4</v>
       </c>
-      <c r="Y30"/>
-      <c r="AB30"/>
-      <c r="AD30"/>
-      <c r="AF30"/>
-      <c r="AG30" s="6"/>
-    </row>
-    <row r="31" spans="1:33">
+      <c r="Z30"/>
+      <c r="AC30"/>
+      <c r="AE30"/>
+      <c r="AG30"/>
+      <c r="AH30" s="6"/>
+    </row>
+    <row r="31" spans="1:34">
       <c r="A31">
         <v>32</v>
       </c>
@@ -4022,32 +3433,32 @@
       <c r="O31">
         <v>1</v>
       </c>
-      <c r="P31"/>
-      <c r="Q31" s="2">
+      <c r="Q31"/>
+      <c r="R31" s="2">
         <v>33</v>
       </c>
-      <c r="R31">
+      <c r="S31">
         <v>20</v>
       </c>
-      <c r="S31" s="3">
+      <c r="T31" s="3">
         <v>30</v>
       </c>
-      <c r="T31" s="2">
+      <c r="U31" s="2">
         <v>35</v>
       </c>
-      <c r="U31">
-        <v>1</v>
-      </c>
-      <c r="V31" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y31"/>
-      <c r="AB31"/>
-      <c r="AD31"/>
-      <c r="AF31"/>
-      <c r="AG31" s="6"/>
-    </row>
-    <row r="32" spans="1:32">
+      <c r="V31">
+        <v>1</v>
+      </c>
+      <c r="W31" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z31"/>
+      <c r="AC31"/>
+      <c r="AE31"/>
+      <c r="AG31"/>
+      <c r="AH31" s="6"/>
+    </row>
+    <row r="32" spans="1:34">
       <c r="A32">
         <v>33</v>
       </c>
@@ -4085,15 +3496,15 @@
       <c r="O32">
         <v>1</v>
       </c>
-      <c r="P32"/>
-      <c r="S32"/>
-      <c r="V32"/>
-      <c r="Y32"/>
-      <c r="AB32"/>
-      <c r="AD32"/>
-      <c r="AF32"/>
-    </row>
-    <row r="33" spans="1:30">
+      <c r="Q32"/>
+      <c r="T32"/>
+      <c r="W32"/>
+      <c r="Z32"/>
+      <c r="AC32"/>
+      <c r="AE32"/>
+      <c r="AG32"/>
+    </row>
+    <row r="33" spans="1:33">
       <c r="A33">
         <v>34</v>
       </c>
@@ -4133,23 +3544,23 @@
       <c r="O33">
         <v>1</v>
       </c>
-      <c r="Q33" s="2">
+      <c r="R33" s="2">
         <v>11</v>
       </c>
-      <c r="R33">
+      <c r="S33">
         <v>38</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>52</v>
       </c>
-      <c r="AC33">
+      <c r="AD33">
         <v>64</v>
       </c>
-      <c r="AD33" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19">
+      <c r="AE33" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:33">
       <c r="A34">
         <v>35</v>
       </c>
@@ -4189,20 +3600,20 @@
       <c r="O34">
         <v>0</v>
       </c>
-      <c r="P34" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="2">
         <v>15</v>
       </c>
-      <c r="R34">
-        <v>3</v>
-      </c>
-      <c r="S34" s="3">
+      <c r="S34">
+        <v>3</v>
+      </c>
+      <c r="T34" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:19">
+    <row r="35" spans="1:33">
       <c r="A35">
         <v>36</v>
       </c>
@@ -4242,17 +3653,17 @@
       <c r="O35">
         <v>0</v>
       </c>
-      <c r="Q35" s="2">
+      <c r="R35" s="2">
         <v>11</v>
       </c>
-      <c r="R35">
+      <c r="S35">
         <v>18</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:22">
+    <row r="36" spans="1:33">
       <c r="A36">
         <v>37</v>
       </c>
@@ -4292,26 +3703,26 @@
       <c r="O36">
         <v>0</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="R36" s="2">
         <v>15</v>
       </c>
-      <c r="R36">
-        <v>3</v>
-      </c>
-      <c r="S36" s="3">
+      <c r="S36">
+        <v>3</v>
+      </c>
+      <c r="T36" s="3">
         <v>4</v>
       </c>
-      <c r="T36" s="2">
-        <v>2</v>
-      </c>
-      <c r="U36">
+      <c r="U36" s="2">
+        <v>2</v>
+      </c>
+      <c r="V36">
         <v>6</v>
       </c>
-      <c r="V36" s="3">
+      <c r="W36" s="3">
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:32">
+    <row r="37" spans="1:33">
       <c r="A37">
         <v>38</v>
       </c>
@@ -4349,31 +3760,31 @@
       <c r="O37">
         <v>0</v>
       </c>
-      <c r="P37"/>
-      <c r="Q37" s="2">
+      <c r="Q37"/>
+      <c r="R37" s="2">
         <v>7</v>
       </c>
-      <c r="R37">
-        <v>3</v>
-      </c>
-      <c r="S37" s="3">
+      <c r="S37">
+        <v>3</v>
+      </c>
+      <c r="T37" s="3">
         <v>4</v>
       </c>
-      <c r="T37" s="2">
-        <v>2</v>
-      </c>
-      <c r="U37">
+      <c r="U37" s="2">
+        <v>2</v>
+      </c>
+      <c r="V37">
         <v>6</v>
       </c>
-      <c r="V37" s="3">
+      <c r="W37" s="3">
         <v>8</v>
       </c>
-      <c r="Y37"/>
-      <c r="AB37"/>
-      <c r="AD37"/>
-      <c r="AF37"/>
-    </row>
-    <row r="38" spans="1:32">
+      <c r="Z37"/>
+      <c r="AC37"/>
+      <c r="AE37"/>
+      <c r="AG37"/>
+    </row>
+    <row r="38" spans="1:33">
       <c r="A38">
         <v>39</v>
       </c>
@@ -4411,31 +3822,31 @@
       <c r="O38">
         <v>1</v>
       </c>
-      <c r="P38"/>
-      <c r="Q38" s="2">
+      <c r="Q38"/>
+      <c r="R38" s="2">
         <v>21</v>
       </c>
-      <c r="R38">
+      <c r="S38">
         <v>4</v>
       </c>
-      <c r="S38" s="3">
+      <c r="T38" s="3">
         <v>5</v>
       </c>
-      <c r="T38" s="2">
-        <v>2</v>
-      </c>
-      <c r="U38">
-        <v>3</v>
-      </c>
-      <c r="V38" s="3">
+      <c r="U38" s="2">
+        <v>2</v>
+      </c>
+      <c r="V38">
+        <v>3</v>
+      </c>
+      <c r="W38" s="3">
         <v>5</v>
       </c>
-      <c r="Y38"/>
-      <c r="AB38"/>
-      <c r="AD38"/>
-      <c r="AF38"/>
-    </row>
-    <row r="39" spans="1:32">
+      <c r="Z38"/>
+      <c r="AC38"/>
+      <c r="AE38"/>
+      <c r="AG38"/>
+    </row>
+    <row r="39" spans="1:33">
       <c r="A39">
         <v>40</v>
       </c>
@@ -4473,31 +3884,31 @@
       <c r="O39">
         <v>1</v>
       </c>
-      <c r="P39"/>
-      <c r="Q39" s="2">
+      <c r="Q39"/>
+      <c r="R39" s="2">
         <v>5</v>
       </c>
-      <c r="R39">
-        <v>1</v>
-      </c>
-      <c r="S39" s="3">
-        <v>2</v>
-      </c>
-      <c r="T39" s="2">
-        <v>2</v>
-      </c>
-      <c r="U39">
+      <c r="S39">
+        <v>1</v>
+      </c>
+      <c r="T39" s="3">
+        <v>2</v>
+      </c>
+      <c r="U39" s="2">
+        <v>2</v>
+      </c>
+      <c r="V39">
         <v>6</v>
       </c>
-      <c r="V39" s="3">
+      <c r="W39" s="3">
         <v>7</v>
       </c>
-      <c r="Y39"/>
-      <c r="AB39"/>
-      <c r="AD39"/>
-      <c r="AF39"/>
-    </row>
-    <row r="40" spans="1:32">
+      <c r="Z39"/>
+      <c r="AC39"/>
+      <c r="AE39"/>
+      <c r="AG39"/>
+    </row>
+    <row r="40" spans="1:33">
       <c r="A40">
         <v>41</v>
       </c>
@@ -4535,31 +3946,31 @@
       <c r="O40">
         <v>1</v>
       </c>
-      <c r="P40"/>
-      <c r="Q40" s="2">
+      <c r="Q40"/>
+      <c r="R40" s="2">
         <v>7</v>
       </c>
-      <c r="R40">
+      <c r="S40">
         <v>4</v>
       </c>
-      <c r="S40" s="3">
+      <c r="T40" s="3">
         <v>5</v>
       </c>
-      <c r="T40" s="2">
+      <c r="U40" s="2">
         <v>38</v>
       </c>
-      <c r="U40">
+      <c r="V40">
         <v>4</v>
       </c>
-      <c r="V40" s="3">
+      <c r="W40" s="3">
         <v>5</v>
       </c>
-      <c r="Y40"/>
-      <c r="AB40"/>
-      <c r="AD40"/>
-      <c r="AF40"/>
-    </row>
-    <row r="41" spans="1:32">
+      <c r="Z40"/>
+      <c r="AC40"/>
+      <c r="AE40"/>
+      <c r="AG40"/>
+    </row>
+    <row r="41" spans="1:33">
       <c r="A41">
         <v>42</v>
       </c>
@@ -4597,31 +4008,31 @@
       <c r="O41">
         <v>0</v>
       </c>
-      <c r="P41"/>
-      <c r="Q41" s="2">
+      <c r="Q41"/>
+      <c r="R41" s="2">
         <v>6</v>
       </c>
-      <c r="R41">
-        <v>3</v>
-      </c>
-      <c r="S41" s="3">
-        <v>3</v>
-      </c>
-      <c r="T41" s="2">
+      <c r="S41">
+        <v>3</v>
+      </c>
+      <c r="T41" s="3">
+        <v>3</v>
+      </c>
+      <c r="U41" s="2">
         <v>39</v>
       </c>
-      <c r="U41">
-        <v>2</v>
-      </c>
-      <c r="V41" s="3">
-        <v>3</v>
-      </c>
-      <c r="Y41"/>
-      <c r="AB41"/>
-      <c r="AD41"/>
-      <c r="AF41"/>
-    </row>
-    <row r="42" spans="1:32">
+      <c r="V41">
+        <v>2</v>
+      </c>
+      <c r="W41" s="3">
+        <v>3</v>
+      </c>
+      <c r="Z41"/>
+      <c r="AC41"/>
+      <c r="AE41"/>
+      <c r="AG41"/>
+    </row>
+    <row r="42" spans="1:33">
       <c r="A42">
         <v>43</v>
       </c>
@@ -4659,31 +4070,31 @@
       <c r="O42">
         <v>1</v>
       </c>
-      <c r="P42"/>
-      <c r="Q42" s="2">
+      <c r="Q42"/>
+      <c r="R42" s="2">
         <v>7</v>
       </c>
-      <c r="R42">
-        <v>1</v>
-      </c>
-      <c r="S42" s="3">
-        <v>3</v>
-      </c>
-      <c r="T42" s="2">
+      <c r="S42">
+        <v>1</v>
+      </c>
+      <c r="T42" s="3">
+        <v>3</v>
+      </c>
+      <c r="U42" s="2">
         <v>41</v>
       </c>
-      <c r="U42">
-        <v>1</v>
-      </c>
-      <c r="V42" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y42"/>
-      <c r="AB42"/>
-      <c r="AD42"/>
-      <c r="AF42"/>
-    </row>
-    <row r="43" spans="1:32">
+      <c r="V42">
+        <v>1</v>
+      </c>
+      <c r="W42" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z42"/>
+      <c r="AC42"/>
+      <c r="AE42"/>
+      <c r="AG42"/>
+    </row>
+    <row r="43" spans="1:33">
       <c r="A43">
         <v>44</v>
       </c>
@@ -4721,39 +4132,39 @@
       <c r="O43">
         <v>1</v>
       </c>
-      <c r="P43"/>
-      <c r="Q43" s="2">
+      <c r="Q43"/>
+      <c r="R43" s="2">
         <v>6</v>
       </c>
-      <c r="R43">
+      <c r="S43">
         <v>5</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5</v>
       </c>
-      <c r="T43" s="2">
+      <c r="U43" s="2">
         <v>14</v>
       </c>
-      <c r="U43">
-        <v>1</v>
-      </c>
-      <c r="V43" s="3">
-        <v>1</v>
-      </c>
-      <c r="W43" s="2">
+      <c r="V43">
+        <v>1</v>
+      </c>
+      <c r="W43" s="3">
+        <v>1</v>
+      </c>
+      <c r="X43" s="2">
         <v>18</v>
       </c>
-      <c r="X43">
+      <c r="Y43">
         <v>0.9</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1.2</v>
       </c>
-      <c r="AB43"/>
-      <c r="AD43"/>
-      <c r="AF43"/>
-    </row>
-    <row r="44" spans="1:22">
+      <c r="AC43"/>
+      <c r="AE43"/>
+      <c r="AG43"/>
+    </row>
+    <row r="44" spans="1:33">
       <c r="A44">
         <v>45</v>
       </c>
@@ -4793,26 +4204,26 @@
       <c r="O44">
         <v>1</v>
       </c>
-      <c r="Q44" s="2">
+      <c r="R44" s="2">
         <v>15</v>
       </c>
-      <c r="R44">
-        <v>2</v>
-      </c>
-      <c r="S44" s="3">
-        <v>2</v>
-      </c>
-      <c r="T44" s="2">
+      <c r="S44">
+        <v>2</v>
+      </c>
+      <c r="T44" s="3">
+        <v>2</v>
+      </c>
+      <c r="U44" s="2">
         <v>42</v>
       </c>
-      <c r="U44">
+      <c r="V44">
         <v>8</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:32">
+    <row r="45" spans="1:33">
       <c r="A45">
         <v>46</v>
       </c>
@@ -4850,39 +4261,39 @@
       <c r="O45">
         <v>1</v>
       </c>
-      <c r="P45"/>
-      <c r="Q45" s="2">
+      <c r="Q45"/>
+      <c r="R45" s="2">
         <v>7</v>
       </c>
-      <c r="R45">
+      <c r="S45">
         <v>7</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>9</v>
       </c>
-      <c r="T45" s="2">
+      <c r="U45" s="2">
         <v>26</v>
       </c>
-      <c r="U45">
-        <v>2</v>
-      </c>
-      <c r="V45" s="3">
-        <v>2</v>
-      </c>
-      <c r="W45" s="2">
-        <v>2</v>
-      </c>
-      <c r="X45">
+      <c r="V45">
+        <v>2</v>
+      </c>
+      <c r="W45" s="3">
+        <v>2</v>
+      </c>
+      <c r="X45" s="2">
+        <v>2</v>
+      </c>
+      <c r="Y45">
         <v>7</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>8</v>
       </c>
-      <c r="AB45"/>
-      <c r="AD45"/>
-      <c r="AF45"/>
-    </row>
-    <row r="46" spans="1:32">
+      <c r="AC45"/>
+      <c r="AE45"/>
+      <c r="AG45"/>
+    </row>
+    <row r="46" spans="1:33">
       <c r="A46">
         <v>47</v>
       </c>
@@ -4920,39 +4331,39 @@
       <c r="O46">
         <v>1</v>
       </c>
-      <c r="P46"/>
-      <c r="Q46" s="2">
+      <c r="Q46"/>
+      <c r="R46" s="2">
         <v>32</v>
       </c>
-      <c r="R46">
+      <c r="S46">
         <v>40</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>40</v>
       </c>
-      <c r="T46" s="2">
+      <c r="U46" s="2">
         <v>33</v>
       </c>
-      <c r="U46">
+      <c r="V46">
         <v>30</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>30</v>
       </c>
-      <c r="W46" s="2">
+      <c r="X46" s="2">
         <v>19</v>
       </c>
-      <c r="X46">
-        <v>1</v>
-      </c>
-      <c r="Y46" s="3">
-        <v>1</v>
-      </c>
-      <c r="AB46"/>
-      <c r="AD46"/>
-      <c r="AF46"/>
-    </row>
-    <row r="47" spans="1:32">
+      <c r="Y46">
+        <v>1</v>
+      </c>
+      <c r="Z46" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC46"/>
+      <c r="AE46"/>
+      <c r="AG46"/>
+    </row>
+    <row r="47" spans="1:33">
       <c r="A47">
         <v>48</v>
       </c>
@@ -4990,23 +4401,23 @@
       <c r="O47">
         <v>0</v>
       </c>
-      <c r="P47"/>
-      <c r="Q47" s="2">
+      <c r="Q47"/>
+      <c r="R47" s="2">
         <v>11</v>
       </c>
-      <c r="R47">
+      <c r="S47">
         <v>10</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>14</v>
       </c>
-      <c r="V47"/>
-      <c r="Y47"/>
-      <c r="AB47"/>
-      <c r="AD47"/>
-      <c r="AF47"/>
-    </row>
-    <row r="48" spans="1:32">
+      <c r="W47"/>
+      <c r="Z47"/>
+      <c r="AC47"/>
+      <c r="AE47"/>
+      <c r="AG47"/>
+    </row>
+    <row r="48" spans="1:33">
       <c r="A48">
         <v>49</v>
       </c>
@@ -5044,31 +4455,31 @@
       <c r="O48">
         <v>0</v>
       </c>
-      <c r="P48"/>
-      <c r="Q48" s="2">
+      <c r="Q48"/>
+      <c r="R48" s="2">
         <v>11</v>
       </c>
-      <c r="R48">
+      <c r="S48">
         <v>8</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>11</v>
       </c>
-      <c r="T48" s="2">
+      <c r="U48" s="2">
         <v>6</v>
       </c>
-      <c r="U48">
-        <v>3</v>
-      </c>
-      <c r="V48" s="3">
-        <v>3</v>
-      </c>
-      <c r="Y48"/>
-      <c r="AB48"/>
-      <c r="AD48"/>
-      <c r="AF48"/>
-    </row>
-    <row r="49" spans="1:22">
+      <c r="V48">
+        <v>3</v>
+      </c>
+      <c r="W48" s="3">
+        <v>3</v>
+      </c>
+      <c r="Z48"/>
+      <c r="AC48"/>
+      <c r="AE48"/>
+      <c r="AG48"/>
+    </row>
+    <row r="49" spans="1:33">
       <c r="A49">
         <v>50</v>
       </c>
@@ -5108,26 +4519,26 @@
       <c r="O49">
         <v>0</v>
       </c>
-      <c r="Q49" s="2">
+      <c r="R49" s="2">
         <v>11</v>
       </c>
-      <c r="R49">
+      <c r="S49">
         <v>7</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>11</v>
       </c>
-      <c r="T49" s="2">
+      <c r="U49" s="2">
         <v>45</v>
       </c>
-      <c r="U49">
-        <v>2</v>
-      </c>
-      <c r="V49" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:32">
+      <c r="V49">
+        <v>2</v>
+      </c>
+      <c r="W49" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:33">
       <c r="A50">
         <v>51</v>
       </c>
@@ -5165,31 +4576,31 @@
       <c r="O50">
         <v>1</v>
       </c>
-      <c r="P50"/>
-      <c r="Q50" s="2">
+      <c r="Q50"/>
+      <c r="R50" s="2">
         <v>6</v>
       </c>
-      <c r="R50">
+      <c r="S50">
         <v>5</v>
       </c>
-      <c r="S50" s="3">
+      <c r="T50" s="3">
         <v>7</v>
       </c>
-      <c r="T50" s="2">
+      <c r="U50" s="2">
         <v>18</v>
       </c>
-      <c r="U50">
-        <v>1.1</v>
-      </c>
-      <c r="V50" s="3">
+      <c r="V50">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="W50" s="3">
         <v>1.7</v>
       </c>
-      <c r="Y50"/>
-      <c r="AB50"/>
-      <c r="AD50"/>
-      <c r="AF50"/>
-    </row>
-    <row r="51" spans="1:32">
+      <c r="Z50"/>
+      <c r="AC50"/>
+      <c r="AE50"/>
+      <c r="AG50"/>
+    </row>
+    <row r="51" spans="1:33">
       <c r="A51">
         <v>52</v>
       </c>
@@ -5227,31 +4638,31 @@
       <c r="O51">
         <v>1</v>
       </c>
-      <c r="P51"/>
-      <c r="Q51" s="2">
+      <c r="Q51"/>
+      <c r="R51" s="2">
         <v>6</v>
       </c>
-      <c r="R51">
-        <v>1</v>
-      </c>
-      <c r="S51" s="3">
-        <v>3</v>
-      </c>
-      <c r="T51" s="2">
+      <c r="S51">
+        <v>1</v>
+      </c>
+      <c r="T51" s="3">
+        <v>3</v>
+      </c>
+      <c r="U51" s="2">
         <v>49</v>
       </c>
-      <c r="U51">
-        <v>1</v>
-      </c>
-      <c r="V51" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y51"/>
-      <c r="AB51"/>
-      <c r="AD51"/>
-      <c r="AF51"/>
-    </row>
-    <row r="52" spans="1:32">
+      <c r="V51">
+        <v>1</v>
+      </c>
+      <c r="W51" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z51"/>
+      <c r="AC51"/>
+      <c r="AE51"/>
+      <c r="AG51"/>
+    </row>
+    <row r="52" spans="1:33">
       <c r="A52">
         <v>53</v>
       </c>
@@ -5289,31 +4700,31 @@
       <c r="O52">
         <v>1</v>
       </c>
-      <c r="P52"/>
-      <c r="Q52" s="2">
+      <c r="Q52"/>
+      <c r="R52" s="2">
         <v>9</v>
       </c>
-      <c r="R52">
-        <v>2</v>
-      </c>
-      <c r="S52" s="3">
-        <v>2</v>
-      </c>
-      <c r="T52" s="2">
+      <c r="S52">
+        <v>2</v>
+      </c>
+      <c r="T52" s="3">
+        <v>2</v>
+      </c>
+      <c r="U52" s="2">
         <v>21</v>
       </c>
-      <c r="U52">
-        <v>2</v>
-      </c>
-      <c r="V52" s="3">
-        <v>2</v>
-      </c>
-      <c r="Y52"/>
-      <c r="AB52"/>
-      <c r="AD52"/>
-      <c r="AF52"/>
-    </row>
-    <row r="53" spans="1:22">
+      <c r="V52">
+        <v>2</v>
+      </c>
+      <c r="W52" s="3">
+        <v>2</v>
+      </c>
+      <c r="Z52"/>
+      <c r="AC52"/>
+      <c r="AE52"/>
+      <c r="AG52"/>
+    </row>
+    <row r="53" spans="1:33">
       <c r="A53">
         <v>54</v>
       </c>
@@ -5353,29 +4764,29 @@
       <c r="O53">
         <v>1</v>
       </c>
-      <c r="P53" s="3">
+      <c r="Q53" s="3">
         <v>6</v>
       </c>
-      <c r="Q53">
+      <c r="R53">
         <v>50</v>
       </c>
-      <c r="R53">
-        <v>3</v>
-      </c>
-      <c r="S53" s="3">
+      <c r="S53">
+        <v>3</v>
+      </c>
+      <c r="T53" s="3">
         <v>4</v>
       </c>
-      <c r="T53">
+      <c r="U53">
         <v>51</v>
       </c>
-      <c r="U53">
+      <c r="V53">
         <v>-0.5</v>
       </c>
-      <c r="V53" s="3">
+      <c r="W53" s="3">
         <v>-0.5</v>
       </c>
     </row>
-    <row r="54" spans="1:25">
+    <row r="54" spans="1:33">
       <c r="A54">
         <v>55</v>
       </c>
@@ -5418,35 +4829,35 @@
       <c r="O54">
         <v>1</v>
       </c>
-      <c r="Q54">
+      <c r="R54">
         <v>15</v>
       </c>
-      <c r="R54">
-        <v>3</v>
-      </c>
-      <c r="S54" s="3">
+      <c r="S54">
+        <v>3</v>
+      </c>
+      <c r="T54" s="3">
         <v>4</v>
       </c>
-      <c r="T54">
+      <c r="U54">
         <v>14</v>
       </c>
-      <c r="U54">
-        <v>1</v>
-      </c>
-      <c r="V54" s="3">
-        <v>1</v>
-      </c>
-      <c r="W54">
+      <c r="V54">
+        <v>1</v>
+      </c>
+      <c r="W54" s="3">
+        <v>1</v>
+      </c>
+      <c r="X54">
         <v>52</v>
       </c>
-      <c r="X54">
-        <v>3</v>
-      </c>
-      <c r="Y54" s="3">
+      <c r="Y54">
+        <v>3</v>
+      </c>
+      <c r="Z54" s="3">
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:31">
+    <row r="55" spans="1:33">
       <c r="A55">
         <v>56</v>
       </c>
@@ -5486,27 +4897,27 @@
       <c r="O55">
         <v>1</v>
       </c>
-      <c r="Q55">
+      <c r="R55">
         <v>15</v>
       </c>
-      <c r="R55">
-        <v>1</v>
-      </c>
-      <c r="S55" s="3">
-        <v>3</v>
-      </c>
-      <c r="T55">
+      <c r="S55">
+        <v>1</v>
+      </c>
+      <c r="T55" s="3">
+        <v>3</v>
+      </c>
+      <c r="U55">
         <v>60</v>
       </c>
-      <c r="U55">
-        <v>1</v>
-      </c>
-      <c r="V55" s="3">
-        <v>1</v>
-      </c>
-      <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="1:31">
+      <c r="V55">
+        <v>1</v>
+      </c>
+      <c r="W55" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="1:33">
       <c r="A56">
         <v>57</v>
       </c>
@@ -5549,36 +4960,36 @@
       <c r="O56">
         <v>1</v>
       </c>
-      <c r="Q56">
+      <c r="R56">
         <v>45</v>
       </c>
-      <c r="R56">
-        <v>3</v>
-      </c>
-      <c r="S56" s="3">
+      <c r="S56">
+        <v>3</v>
+      </c>
+      <c r="T56" s="3">
         <v>4</v>
       </c>
-      <c r="T56">
+      <c r="U56">
         <v>11</v>
       </c>
-      <c r="U56">
+      <c r="V56">
         <v>12</v>
       </c>
-      <c r="V56" s="3">
+      <c r="W56" s="3">
         <v>18</v>
       </c>
-      <c r="W56">
+      <c r="X56">
         <v>14</v>
       </c>
-      <c r="X56">
-        <v>1</v>
-      </c>
-      <c r="Y56" s="3">
-        <v>1</v>
-      </c>
-      <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="1:22">
+      <c r="Y56">
+        <v>1</v>
+      </c>
+      <c r="Z56" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="1:33">
       <c r="A57">
         <v>58</v>
       </c>
@@ -5621,26 +5032,26 @@
       <c r="O57">
         <v>1</v>
       </c>
-      <c r="Q57">
-        <v>2</v>
-      </c>
       <c r="R57">
+        <v>2</v>
+      </c>
+      <c r="S57">
         <v>5</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6</v>
       </c>
-      <c r="T57">
-        <v>2</v>
-      </c>
       <c r="U57">
+        <v>2</v>
+      </c>
+      <c r="V57">
         <v>5</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:15">
+    <row r="58" spans="1:33">
       <c r="A58">
         <v>59</v>
       </c>
@@ -5681,7 +5092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:19">
+    <row r="59" spans="1:33">
       <c r="A59">
         <v>60</v>
       </c>
@@ -5721,17 +5132,17 @@
       <c r="O59">
         <v>0</v>
       </c>
-      <c r="Q59">
-        <v>2</v>
-      </c>
       <c r="R59">
+        <v>2</v>
+      </c>
+      <c r="S59">
         <v>7</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:15">
+    <row r="60" spans="1:33">
       <c r="A60">
         <v>61</v>
       </c>
@@ -5772,7 +5183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:15">
+    <row r="61" spans="1:33">
       <c r="A61">
         <v>62</v>
       </c>
@@ -5818,25 +5229,23 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I67"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.425" customWidth="1"/>
-    <col min="2" max="2" width="27.425" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
     <col min="4" max="4" width="33" customWidth="1"/>
-    <col min="5" max="5" width="19.2833333333333" customWidth="1"/>
-    <col min="6" max="6" width="18.8583333333333" customWidth="1"/>
-    <col min="7" max="8" width="10.2833333333333" customWidth="1"/>
-    <col min="9" max="9" width="15.1416666666667" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" customWidth="1"/>
+    <col min="7" max="8" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7158,7 +6567,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="63" customFormat="1" spans="1:9">
+    <row r="63" spans="1:9">
       <c r="A63">
         <v>61</v>
       </c>
@@ -7218,7 +6627,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="66" customFormat="1" spans="1:9">
+    <row r="66" spans="1:9">
       <c r="A66">
         <v>64</v>
       </c>
@@ -7263,26 +6672,24 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.425" customWidth="1"/>
-    <col min="2" max="2" width="27.425" customWidth="1"/>
-    <col min="3" max="3" width="14.425" customWidth="1"/>
-    <col min="4" max="5" width="16.1416666666667" customWidth="1"/>
-    <col min="6" max="6" width="12.425" customWidth="1"/>
-    <col min="7" max="7" width="14.425" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
+    <col min="4" max="5" width="16.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="10.1416666666667" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7333,7 +6740,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>0</v>
       </c>
@@ -7362,7 +6769,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>1</v>
       </c>
@@ -7385,7 +6792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>2</v>
       </c>
@@ -7402,7 +6809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:15">
       <c r="A5">
         <v>3</v>
       </c>
@@ -7437,7 +6844,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:15">
       <c r="A6">
         <v>4</v>
       </c>
@@ -7460,7 +6867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:15">
       <c r="A7">
         <v>5</v>
       </c>
@@ -7483,7 +6890,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:15">
       <c r="A8">
         <v>6</v>
       </c>
@@ -7506,7 +6913,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:15">
       <c r="A9">
         <v>7</v>
       </c>
@@ -7529,7 +6936,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:15">
       <c r="A10">
         <v>8</v>
       </c>
@@ -7552,7 +6959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:15">
       <c r="A11">
         <v>9</v>
       </c>
@@ -7581,7 +6988,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:15">
       <c r="A12">
         <v>10</v>
       </c>
@@ -7610,7 +7017,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:15">
       <c r="A13">
         <v>11</v>
       </c>
@@ -7633,7 +7040,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:15">
       <c r="A14">
         <v>12</v>
       </c>
@@ -7656,7 +7063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:15">
       <c r="A15">
         <v>13</v>
       </c>
@@ -7679,7 +7086,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:15">
       <c r="A16">
         <v>14</v>
       </c>
@@ -7748,7 +7155,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>17</v>
       </c>
@@ -7765,7 +7172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>18</v>
       </c>
@@ -7782,7 +7189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>19</v>
       </c>
@@ -7868,7 +7275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>23</v>
       </c>
@@ -7885,7 +7292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>24</v>
       </c>
@@ -7902,7 +7309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>25</v>
       </c>
@@ -7919,7 +7326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>26</v>
       </c>
@@ -7936,7 +7343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>27</v>
       </c>
@@ -7953,7 +7360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>28</v>
       </c>
@@ -7970,7 +7377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>29</v>
       </c>
@@ -7987,7 +7394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>30</v>
       </c>
@@ -8040,24 +7447,22 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85833333333333" customWidth="1"/>
-    <col min="2" max="2" width="22.7083333333333" customWidth="1"/>
-    <col min="3" max="3" width="28.5666666666667" customWidth="1"/>
-    <col min="4" max="4" width="15.5666666666667" customWidth="1"/>
-    <col min="5" max="5" width="16.1416666666667" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="11.1416666666667" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -8083,7 +7488,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -8103,7 +7508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="12.95" customHeight="1" spans="1:6">
+    <row r="3" spans="1:7" ht="12.95" customHeight="1">
       <c r="A3">
         <v>1</v>
       </c>
@@ -8120,7 +7525,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" ht="12.95" customHeight="1" spans="1:6">
+    <row r="4" spans="1:7" ht="12.95" customHeight="1">
       <c r="A4">
         <v>2</v>
       </c>
@@ -8137,7 +7542,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>3</v>
       </c>
@@ -8157,7 +7562,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>4</v>
       </c>
@@ -8177,7 +7582,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>5</v>
       </c>
@@ -8197,7 +7602,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>6</v>
       </c>
@@ -8217,7 +7622,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>7</v>
       </c>
@@ -8237,7 +7642,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>8</v>
       </c>
@@ -8257,7 +7662,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>9</v>
       </c>
@@ -8279,7 +7684,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Cards.xlsx
+++ b/Assets/StreamingAssets/Configurations/Cards.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView windowWidth="22190" windowHeight="9040"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,7 @@
     <sheet name="Conditions" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cards!$A$1:$AH$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cards!$G$1:$G$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="339">
   <si>
     <t>ID</t>
   </si>
@@ -143,39 +143,42 @@
     <t>参数+X1</t>
   </si>
   <si>
+    <t>Basic</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Stamina</t>
+  </si>
+  <si>
+    <t>喝水</t>
+  </si>
+  <si>
+    <t>神采+4</t>
+  </si>
+  <si>
+    <t>神采+X1</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>闪耀</t>
+  </si>
+  <si>
+    <t>参数+15，红温大于10层时，参数+9</t>
+  </si>
+  <si>
+    <t>参数+X1，红温大于10层时，参数+X2</t>
+  </si>
+  <si>
     <t>Common</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>Stamina</t>
-  </si>
-  <si>
-    <t>喝水</t>
-  </si>
-  <si>
-    <t>神采+4</t>
-  </si>
-  <si>
-    <t>神采+X1</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>闪耀</t>
-  </si>
-  <si>
-    <t>参数+15，红温大于10层时，参数+9</t>
-  </si>
-  <si>
-    <t>参数+X1，红温大于10层时，参数+X2</t>
-  </si>
-  <si>
     <t>C</t>
   </si>
   <si>
@@ -311,7 +314,7 @@
     <t>舰长+X1，神采+X2，体力消耗减少+X3回合</t>
   </si>
   <si>
-    <t>W</t>
+    <t>revenue</t>
   </si>
   <si>
     <t>攻击弹幕</t>
@@ -389,7 +392,7 @@
     <t>SC</t>
   </si>
   <si>
-    <t>流水+30，神采+3，体力消耗减少+2回合</t>
+    <t>沪币+30，神采+3，体力消耗减少+2回合</t>
   </si>
   <si>
     <t>直播通知</t>
@@ -2286,16 +2289,16 @@
         <v>46</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F4" t="s">
         <v>37</v>
       </c>
       <c r="G4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J4" t="s">
         <v>39</v>
@@ -2337,13 +2340,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>36</v>
@@ -2400,28 +2403,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F6" t="s">
         <v>43</v>
       </c>
       <c r="G6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K6" s="3">
         <v>3</v>
@@ -2466,16 +2469,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F7" t="s">
         <v>43</v>
@@ -2532,25 +2535,25 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F8" t="s">
         <v>43</v>
       </c>
       <c r="G8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -2605,13 +2608,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>36</v>
@@ -2668,13 +2671,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>36</v>
@@ -2683,7 +2686,7 @@
         <v>43</v>
       </c>
       <c r="G10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J10" t="s">
         <v>39</v>
@@ -2731,13 +2734,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>36</v>
@@ -2746,10 +2749,10 @@
         <v>43</v>
       </c>
       <c r="G11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J11" t="s">
         <v>39</v>
@@ -2791,22 +2794,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F12" t="s">
         <v>37</v>
       </c>
       <c r="G12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J12" t="s">
         <v>39</v>
@@ -2849,7 +2852,7 @@
       <c r="AF12"/>
       <c r="AG12" s="5"/>
       <c r="AH12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:33">
@@ -2857,16 +2860,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F13" t="s">
         <v>37</v>
@@ -2920,16 +2923,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F14" t="s">
         <v>43</v>
@@ -2975,16 +2978,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F15" t="s">
         <v>37</v>
@@ -3030,16 +3033,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F16" t="s">
         <v>37</v>
@@ -3093,16 +3096,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F17" t="s">
         <v>43</v>
@@ -3111,7 +3114,7 @@
         <v>38</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J17" t="s">
         <v>39</v>
@@ -3167,25 +3170,25 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D18" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F18" t="s">
         <v>43</v>
       </c>
       <c r="G18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J18" t="s">
         <v>39</v>
@@ -3224,22 +3227,22 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F19" t="s">
         <v>43</v>
       </c>
       <c r="G19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J19" t="s">
         <v>39</v>
@@ -3287,25 +3290,25 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C20" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D20" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s">
         <v>37</v>
       </c>
       <c r="G20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J20" t="s">
         <v>39</v>
@@ -3347,25 +3350,25 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F21" t="s">
         <v>37</v>
       </c>
       <c r="G21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J21" t="s">
         <v>39</v>
@@ -3416,16 +3419,16 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F22" t="s">
         <v>43</v>
@@ -3479,16 +3482,16 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F23" t="s">
         <v>43</v>
@@ -3542,25 +3545,25 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C24" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D24" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F24" t="s">
         <v>37</v>
       </c>
       <c r="G24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J24" t="s">
         <v>39</v>
@@ -3608,22 +3611,22 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C25" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D25" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F25" t="s">
         <v>43</v>
       </c>
       <c r="G25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J25" t="s">
         <v>39</v>
@@ -3663,22 +3666,22 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C26" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D26" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F26" t="s">
         <v>43</v>
       </c>
       <c r="G26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J26" t="s">
         <v>39</v>
@@ -3726,25 +3729,25 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F27" t="s">
         <v>37</v>
       </c>
       <c r="G27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J27" t="s">
         <v>39</v>
@@ -3798,25 +3801,25 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C28" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D28" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F28" t="s">
         <v>43</v>
       </c>
       <c r="G28" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H28" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J28" t="s">
         <v>39</v>
@@ -3855,22 +3858,25 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C29" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D29" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F29" t="s">
         <v>43</v>
       </c>
       <c r="G29" t="s">
         <v>38</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="J29" t="s">
         <v>39</v>
@@ -3926,22 +3932,25 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D30" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F30" t="s">
         <v>43</v>
       </c>
       <c r="G30" t="s">
         <v>38</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="J30" t="s">
         <v>39</v>
@@ -3989,22 +3998,25 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C31" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D31" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F31" t="s">
         <v>43</v>
       </c>
       <c r="G31" t="s">
         <v>38</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="J31" t="s">
         <v>39</v>
@@ -4052,22 +4064,25 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C32" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D32" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F32" t="s">
         <v>43</v>
       </c>
       <c r="G32" t="s">
         <v>38</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="J32" t="s">
         <v>39</v>
@@ -4098,25 +4113,25 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C33" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D33" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F33" t="s">
         <v>37</v>
       </c>
       <c r="G33" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H33" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J33" t="s">
         <v>39</v>
@@ -4154,25 +4169,25 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C34" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D34" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F34" t="s">
         <v>43</v>
       </c>
       <c r="G34" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H34" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J34" t="s">
         <v>39</v>
@@ -4207,25 +4222,25 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C35" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D35" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F35" t="s">
         <v>37</v>
       </c>
       <c r="G35" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J35" t="s">
         <v>39</v>
@@ -4260,22 +4275,22 @@
         <v>144</v>
       </c>
       <c r="C36" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D36" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F36" t="s">
         <v>43</v>
       </c>
       <c r="G36" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H36" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J36" t="s">
         <v>39</v>
@@ -4316,22 +4331,22 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C37" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D37" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F37" t="s">
         <v>43</v>
       </c>
       <c r="G37" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J37" t="s">
         <v>39</v>
@@ -4378,16 +4393,16 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C38" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D38" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F38" t="s">
         <v>43</v>
@@ -4440,16 +4455,16 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C39" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D39" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F39" t="s">
         <v>43</v>
@@ -4502,22 +4517,22 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C40" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D40" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F40" t="s">
         <v>43</v>
       </c>
       <c r="G40" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J40" t="s">
         <v>39</v>
@@ -4564,16 +4579,16 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C41" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D41" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F41" t="s">
         <v>43</v>
@@ -4626,22 +4641,22 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C42" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D42" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F42" t="s">
         <v>43</v>
       </c>
       <c r="G42" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J42" t="s">
         <v>39</v>
@@ -4688,16 +4703,16 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C43" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D43" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F43" t="s">
         <v>37</v>
@@ -4758,25 +4773,25 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C44" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D44" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F44" t="s">
         <v>37</v>
       </c>
       <c r="G44" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H44" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J44" t="s">
         <v>39</v>
@@ -4817,22 +4832,22 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C45" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D45" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F45" t="s">
         <v>43</v>
       </c>
       <c r="G45" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J45" t="s">
         <v>39</v>
@@ -4887,22 +4902,25 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C46" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D46" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F46" t="s">
         <v>43</v>
       </c>
       <c r="G46" t="s">
         <v>38</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="J46" t="s">
         <v>39</v>
@@ -4957,22 +4975,22 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C47" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D47" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F47" t="s">
         <v>37</v>
       </c>
       <c r="G47" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J47" t="s">
         <v>39</v>
@@ -5014,13 +5032,13 @@
         <v>123</v>
       </c>
       <c r="C48" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D48" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F48" t="s">
         <v>37</v>
@@ -5073,25 +5091,25 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C49" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D49" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F49" t="s">
         <v>37</v>
       </c>
       <c r="G49" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H49" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J49" t="s">
         <v>39</v>
@@ -5132,16 +5150,16 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C50" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D50" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F50" t="s">
         <v>37</v>
@@ -5194,16 +5212,16 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C51" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D51" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F51" t="s">
         <v>43</v>
@@ -5256,16 +5274,16 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C52" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D52" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F52" t="s">
         <v>43</v>
@@ -5318,25 +5336,25 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C53" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D53" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F53" t="s">
         <v>37</v>
       </c>
       <c r="G53" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H53" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J53" t="s">
         <v>39</v>
@@ -5380,28 +5398,28 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C54" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D54" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F54" t="s">
         <v>43</v>
       </c>
       <c r="G54" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H54" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J54" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K54" s="3">
         <v>14</v>
@@ -5451,25 +5469,25 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C55" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D55" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F55" t="s">
         <v>43</v>
       </c>
       <c r="G55" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H55" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J55" t="s">
         <v>39</v>
@@ -5511,28 +5529,28 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C56" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D56" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F56" t="s">
         <v>37</v>
       </c>
       <c r="G56" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H56" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J56" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K56" s="3">
         <v>3</v>
@@ -5583,28 +5601,28 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C57" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D57" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F57" t="s">
         <v>37</v>
       </c>
       <c r="G57" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H57" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J57" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K57" s="3">
         <v>3</v>
@@ -5645,25 +5663,25 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C58" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D58" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F58" t="s">
         <v>37</v>
       </c>
       <c r="G58" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H58" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J58" t="s">
         <v>39</v>
@@ -5686,25 +5704,25 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C59" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D59" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F59" t="s">
         <v>37</v>
       </c>
       <c r="G59" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H59" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J59" t="s">
         <v>39</v>
@@ -5736,25 +5754,25 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C60" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D60" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F60" t="s">
         <v>37</v>
       </c>
       <c r="G60" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J60" t="s">
         <v>39</v>
@@ -5777,28 +5795,28 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C61" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D61" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F61" t="s">
         <v>37</v>
       </c>
       <c r="G61" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H61" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J61" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K61" s="3">
         <v>14</v>
@@ -5854,19 +5872,19 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5874,13 +5892,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I2">
         <v>-1</v>
@@ -5891,19 +5909,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -5914,16 +5932,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -5934,16 +5952,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -5954,13 +5972,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -5971,16 +5989,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -5991,13 +6009,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -6011,13 +6029,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C9" t="s">
+        <v>208</v>
+      </c>
+      <c r="D9" t="s">
         <v>207</v>
-      </c>
-      <c r="C9" t="s">
-        <v>207</v>
-      </c>
-      <c r="D9" t="s">
-        <v>206</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -6031,13 +6049,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -6051,13 +6069,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -6068,16 +6086,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D12" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E12" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -6088,16 +6106,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D13" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -6108,19 +6126,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C14" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D14" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -6131,16 +6149,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D15" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E15" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -6151,16 +6169,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C16" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D16" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E16" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -6171,13 +6189,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C17" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D17" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -6191,16 +6209,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C18" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D18" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E18" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -6211,13 +6229,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C19" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D19" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -6231,13 +6249,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C20" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D20" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -6251,16 +6269,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C21" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D21" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E21" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -6271,16 +6289,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C22" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D22" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E22" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -6291,13 +6309,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C23" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D23" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E23">
         <v>5</v>
@@ -6311,19 +6329,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C24" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D24" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -6334,13 +6352,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C25" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D25" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -6354,16 +6372,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C26" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D26" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E26" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -6377,16 +6395,16 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C27" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D27" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E27" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -6397,13 +6415,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C28" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D28" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -6417,19 +6435,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C29" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D29" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -6443,13 +6461,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C30" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D30" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -6463,19 +6481,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C31" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D31" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E31" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F31" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -6486,19 +6504,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C32" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D32" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E32">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -6509,19 +6527,19 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C33" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D33" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E33">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -6532,16 +6550,16 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C34" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D34" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E34" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -6552,16 +6570,16 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C35" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D35" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E35" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -6572,19 +6590,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
+        <v>251</v>
+      </c>
+      <c r="C36" t="s">
+        <v>251</v>
+      </c>
+      <c r="D36" t="s">
+        <v>191</v>
+      </c>
+      <c r="E36" t="s">
         <v>250</v>
       </c>
-      <c r="C36" t="s">
-        <v>250</v>
-      </c>
-      <c r="D36" t="s">
-        <v>190</v>
-      </c>
-      <c r="E36" t="s">
-        <v>249</v>
-      </c>
       <c r="F36" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -6598,13 +6616,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C37" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D37" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E37">
         <v>11</v>
@@ -6618,16 +6636,16 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C38" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D38" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E38" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -6638,13 +6656,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C39" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D39" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -6661,16 +6679,16 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C40" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D40" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E40" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -6681,13 +6699,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C41" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D41" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -6704,19 +6722,19 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D42" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -6730,13 +6748,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C43" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E43">
         <v>12</v>
@@ -6750,13 +6768,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E44">
         <v>13</v>
@@ -6770,19 +6788,19 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C45" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D45" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E45" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F45" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I45">
         <v>-1</v>
@@ -6793,16 +6811,16 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C46" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E46" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I46">
         <v>1</v>
@@ -6813,13 +6831,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C47" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D47" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E47">
         <v>14</v>
@@ -6833,19 +6851,19 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C48" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D48" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I48">
         <v>-1</v>
@@ -6856,13 +6874,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C49" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D49" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E49">
         <v>15</v>
@@ -6876,19 +6894,19 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C50" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D50" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I50">
         <v>-1</v>
@@ -6899,13 +6917,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C51" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D51" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E51">
         <v>16</v>
@@ -6919,13 +6937,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C52" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D52" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -6939,13 +6957,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C53" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D53" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E53">
         <v>3</v>
@@ -6959,13 +6977,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C54" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D54" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E54">
         <v>3</v>
@@ -6982,16 +7000,16 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C55" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D55" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E55" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G55">
         <v>6</v>
@@ -7005,16 +7023,16 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C56" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D56" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E56" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G56">
         <v>7</v>
@@ -7028,16 +7046,16 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C57" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D57" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E57" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G57">
         <v>8</v>
@@ -7051,16 +7069,16 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C58" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D58" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E58" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G58">
         <v>6</v>
@@ -7074,16 +7092,16 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
+        <v>280</v>
+      </c>
+      <c r="C59" t="s">
         <v>279</v>
       </c>
-      <c r="C59" t="s">
-        <v>278</v>
-      </c>
       <c r="D59" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E59" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G59">
         <v>7</v>
@@ -7097,16 +7115,16 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C60" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D60" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E60" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G60">
         <v>8</v>
@@ -7120,19 +7138,19 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C61" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D61" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E61">
         <v>3</v>
       </c>
       <c r="F61" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I61">
         <v>-1</v>
@@ -7143,13 +7161,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C62" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E62">
         <v>20</v>
@@ -7163,16 +7181,16 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C63" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D63" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F63" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I63">
         <v>-1</v>
@@ -7183,13 +7201,13 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C64" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D64" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E64">
         <v>21</v>
@@ -7203,13 +7221,13 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C65" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D65" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E65">
         <v>3</v>
@@ -7223,19 +7241,19 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C66" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D66" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E66">
         <v>14</v>
       </c>
       <c r="F66" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I66">
         <v>-1</v>
@@ -7246,13 +7264,13 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C67" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D67" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E67">
         <v>22</v>
@@ -7294,13 +7312,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F1" t="s">
         <v>16</v>
@@ -7327,10 +7345,10 @@
         <v>26</v>
       </c>
       <c r="N1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -7338,10 +7356,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -7367,10 +7385,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C3" t="s">
         <v>295</v>
-      </c>
-      <c r="C3" t="s">
-        <v>294</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -7390,10 +7408,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -7407,10 +7425,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -7442,10 +7460,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -7465,10 +7483,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -7488,10 +7506,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -7511,10 +7529,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -7534,10 +7552,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -7557,10 +7575,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -7586,10 +7604,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C12" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -7615,10 +7633,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C13" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -7638,10 +7656,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -7661,10 +7679,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C15" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -7684,10 +7702,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C16" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -7707,10 +7725,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C17" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -7730,10 +7748,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C18" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -7753,10 +7771,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C19" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -7770,10 +7788,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C20" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -7787,10 +7805,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C21" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -7804,10 +7822,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C22" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -7827,10 +7845,10 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C23" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -7850,10 +7868,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C24" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -7873,10 +7891,10 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C25" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -7890,10 +7908,10 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C26" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -7907,10 +7925,10 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C27" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -7924,10 +7942,10 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C28" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -7941,10 +7959,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C29" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -7958,10 +7976,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C30" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -7975,10 +7993,10 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C31" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -7992,10 +8010,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -8009,10 +8027,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C33" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -8026,10 +8044,10 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C34" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -8071,16 +8089,16 @@
         <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8088,13 +8106,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -8108,13 +8126,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D3" t="s">
         <v>327</v>
-      </c>
-      <c r="C3" t="s">
-        <v>328</v>
-      </c>
-      <c r="D3" t="s">
-        <v>326</v>
       </c>
       <c r="F3" t="s">
         <v>43</v>
@@ -8125,13 +8143,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>330</v>
+      </c>
+      <c r="C4" t="s">
         <v>329</v>
       </c>
-      <c r="C4" t="s">
-        <v>328</v>
-      </c>
       <c r="D4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F4" t="s">
         <v>37</v>
@@ -8142,13 +8160,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -8162,13 +8180,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -8182,13 +8200,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -8202,13 +8220,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C8" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D8" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -8222,13 +8240,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -8242,13 +8260,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -8262,13 +8280,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E11" t="s">
         <v>43</v>

--- a/Assets/StreamingAssets/Configurations/Cards.xlsx
+++ b/Assets/StreamingAssets/Configurations/Cards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F47183-F6A7-4E70-A44F-2E8DAA5F15B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C73CFC0A-AF50-4F60-A563-A94655455336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="540" windowWidth="38730" windowHeight="20850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>

--- a/Assets/StreamingAssets/Configurations/Cards.xlsx
+++ b/Assets/StreamingAssets/Configurations/Cards.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22190" windowHeight="9040"/>
+    <workbookView windowWidth="24750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="340">
   <si>
     <t>ID</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>NotRepeatable</t>
+  </si>
+  <si>
+    <t>固有牌</t>
   </si>
   <si>
     <t>Condition</t>
@@ -2028,7 +2031,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AH61"/>
+  <dimension ref="A1:AI61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
@@ -2046,25 +2049,26 @@
     <col min="13" max="13" width="14" style="3" customWidth="1"/>
     <col min="14" max="14" width="10.2833333333333" customWidth="1"/>
     <col min="15" max="15" width="13.7083333333333" customWidth="1"/>
-    <col min="16" max="16" width="9.70833333333333" style="3" customWidth="1"/>
-    <col min="17" max="17" width="9.70833333333333" customWidth="1"/>
-    <col min="18" max="18" width="12.1416666666667" customWidth="1"/>
-    <col min="19" max="19" width="17.7083333333333" style="3" customWidth="1"/>
-    <col min="20" max="20" width="11" customWidth="1"/>
-    <col min="21" max="21" width="12.2833333333333" customWidth="1"/>
-    <col min="22" max="22" width="17.1416666666667" style="3" customWidth="1"/>
-    <col min="25" max="25" width="17.7083333333333" style="3" customWidth="1"/>
-    <col min="26" max="26" width="10.7083333333333" customWidth="1"/>
-    <col min="27" max="27" width="11" customWidth="1"/>
-    <col min="28" max="28" width="17.7083333333333" style="3" customWidth="1"/>
-    <col min="29" max="29" width="12.425" customWidth="1"/>
-    <col min="30" max="30" width="12.425" style="3" customWidth="1"/>
-    <col min="31" max="31" width="12.2833333333333" customWidth="1"/>
-    <col min="32" max="32" width="9" style="3"/>
-    <col min="33" max="33" width="4.28333333333333" customWidth="1"/>
+    <col min="16" max="16" width="13.7083333333333" customWidth="1"/>
+    <col min="17" max="17" width="9.70833333333333" style="3" customWidth="1"/>
+    <col min="18" max="18" width="9.70833333333333" customWidth="1"/>
+    <col min="19" max="19" width="12.1416666666667" customWidth="1"/>
+    <col min="20" max="20" width="17.7083333333333" style="3" customWidth="1"/>
+    <col min="21" max="21" width="11" customWidth="1"/>
+    <col min="22" max="22" width="12.2833333333333" customWidth="1"/>
+    <col min="23" max="23" width="17.1416666666667" style="3" customWidth="1"/>
+    <col min="26" max="26" width="17.7083333333333" style="3" customWidth="1"/>
+    <col min="27" max="27" width="10.7083333333333" customWidth="1"/>
+    <col min="28" max="28" width="11" customWidth="1"/>
+    <col min="29" max="29" width="17.7083333333333" style="3" customWidth="1"/>
+    <col min="30" max="30" width="12.425" customWidth="1"/>
+    <col min="31" max="31" width="12.425" style="3" customWidth="1"/>
+    <col min="32" max="32" width="12.2833333333333" customWidth="1"/>
+    <col min="33" max="33" width="9" style="3"/>
+    <col min="34" max="34" width="4.28333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33">
+    <row r="1" spans="1:34">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2110,85 +2114,88 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Y1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AB1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AD1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AE1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AF1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AG1" s="3" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="2" spans="1:33">
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K2"/>
       <c r="L2" s="2">
@@ -2203,47 +2210,47 @@
       <c r="O2">
         <v>0</v>
       </c>
-      <c r="P2"/>
-      <c r="Q2" s="2">
+      <c r="Q2"/>
+      <c r="R2" s="2">
         <v>11</v>
       </c>
-      <c r="R2">
+      <c r="S2">
         <v>7</v>
       </c>
-      <c r="S2" s="3">
+      <c r="T2" s="3">
         <v>7</v>
       </c>
-      <c r="V2"/>
-      <c r="Y2"/>
-      <c r="AB2"/>
-      <c r="AD2"/>
-      <c r="AF2"/>
-      <c r="AG2" s="5"/>
-    </row>
-    <row r="3" spans="1:33">
+      <c r="W2"/>
+      <c r="Z2"/>
+      <c r="AC2"/>
+      <c r="AE2"/>
+      <c r="AG2"/>
+      <c r="AH2" s="5"/>
+    </row>
+    <row r="3" spans="1:34">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" t="s">
         <v>40</v>
-      </c>
-      <c r="C3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G3" t="s">
-        <v>38</v>
-      </c>
-      <c r="J3" t="s">
-        <v>39</v>
       </c>
       <c r="K3"/>
       <c r="L3" s="2">
@@ -2258,50 +2265,50 @@
       <c r="O3">
         <v>0</v>
       </c>
-      <c r="P3"/>
-      <c r="Q3" s="2">
+      <c r="Q3"/>
+      <c r="R3" s="2">
         <v>2</v>
       </c>
-      <c r="R3">
+      <c r="S3">
         <v>4</v>
       </c>
-      <c r="S3" s="3">
+      <c r="T3" s="3">
         <v>4</v>
       </c>
-      <c r="V3"/>
-      <c r="Y3"/>
-      <c r="AB3"/>
-      <c r="AD3"/>
-      <c r="AF3"/>
-      <c r="AG3" s="5"/>
-    </row>
-    <row r="4" spans="1:33">
+      <c r="W3"/>
+      <c r="Z3"/>
+      <c r="AC3"/>
+      <c r="AE3"/>
+      <c r="AG3"/>
+      <c r="AH3" s="5"/>
+    </row>
+    <row r="4" spans="1:34">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L4">
         <v>5</v>
@@ -2315,50 +2322,50 @@
       <c r="O4">
         <v>0</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="R4" s="2">
         <v>11</v>
       </c>
-      <c r="R4">
+      <c r="S4">
         <v>15</v>
       </c>
-      <c r="S4" s="3">
+      <c r="T4" s="3">
         <v>18</v>
       </c>
-      <c r="T4">
+      <c r="U4">
         <v>56</v>
       </c>
-      <c r="U4">
+      <c r="V4">
         <v>9</v>
       </c>
-      <c r="V4" s="3">
+      <c r="W4" s="3">
         <v>12</v>
       </c>
-      <c r="AG4" s="5"/>
-    </row>
-    <row r="5" spans="1:33">
+      <c r="AH4" s="5"/>
+    </row>
+    <row r="5" spans="1:34">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K5"/>
       <c r="L5" s="2">
@@ -2373,58 +2380,58 @@
       <c r="O5">
         <v>0</v>
       </c>
-      <c r="P5"/>
-      <c r="Q5" s="2">
+      <c r="Q5"/>
+      <c r="R5" s="2">
         <v>11</v>
       </c>
-      <c r="R5">
+      <c r="S5">
         <v>5</v>
       </c>
-      <c r="S5" s="3">
+      <c r="T5" s="3">
         <v>5</v>
       </c>
-      <c r="T5" s="2">
+      <c r="U5" s="2">
         <v>2</v>
       </c>
-      <c r="U5">
+      <c r="V5">
         <v>2</v>
       </c>
-      <c r="V5" s="3">
+      <c r="W5" s="3">
         <v>2</v>
       </c>
-      <c r="Y5"/>
-      <c r="AB5"/>
-      <c r="AD5"/>
-      <c r="AF5"/>
-      <c r="AG5" s="5"/>
-    </row>
-    <row r="6" spans="1:33">
+      <c r="Z5"/>
+      <c r="AC5"/>
+      <c r="AE5"/>
+      <c r="AG5"/>
+      <c r="AH5" s="5"/>
+    </row>
+    <row r="6" spans="1:34">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K6" s="3">
         <v>3</v>
@@ -2441,53 +2448,53 @@
       <c r="O6">
         <v>1</v>
       </c>
-      <c r="Q6" s="2">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>2</v>
+      <c r="R6" s="2">
+        <v>0</v>
       </c>
       <c r="U6">
         <v>2</v>
       </c>
-      <c r="V6" s="3">
+      <c r="V6">
+        <v>2</v>
+      </c>
+      <c r="W6" s="3">
         <v>7</v>
       </c>
-      <c r="W6">
+      <c r="X6">
         <v>9</v>
       </c>
-      <c r="X6">
-        <v>1</v>
-      </c>
-      <c r="Y6" s="3">
-        <v>1</v>
-      </c>
-      <c r="AG6" s="5"/>
-    </row>
-    <row r="7" spans="1:33">
+      <c r="Y6">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="3">
+        <v>1</v>
+      </c>
+      <c r="AH6" s="5"/>
+    </row>
+    <row r="7" spans="1:34">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K7"/>
       <c r="L7" s="2">
@@ -2502,58 +2509,58 @@
       <c r="O7">
         <v>1</v>
       </c>
-      <c r="P7"/>
-      <c r="Q7" s="2">
+      <c r="Q7"/>
+      <c r="R7" s="2">
         <v>4</v>
       </c>
-      <c r="S7"/>
-      <c r="T7" s="2">
+      <c r="T7"/>
+      <c r="U7" s="2">
         <v>21</v>
       </c>
-      <c r="U7">
+      <c r="V7">
         <v>2</v>
       </c>
-      <c r="V7" s="3">
+      <c r="W7" s="3">
         <v>2</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>14</v>
       </c>
-      <c r="X7">
-        <v>1</v>
-      </c>
-      <c r="Y7" s="3">
-        <v>1</v>
-      </c>
-      <c r="AB7"/>
-      <c r="AD7"/>
-      <c r="AF7"/>
-      <c r="AG7" s="5"/>
-    </row>
-    <row r="8" spans="1:33">
+      <c r="Y7">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC7"/>
+      <c r="AE7"/>
+      <c r="AG7"/>
+      <c r="AH7" s="5"/>
+    </row>
+    <row r="8" spans="1:34">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -2570,63 +2577,63 @@
       <c r="O8">
         <v>1</v>
       </c>
-      <c r="P8"/>
-      <c r="Q8" s="2">
+      <c r="Q8"/>
+      <c r="R8" s="2">
         <v>2</v>
       </c>
-      <c r="R8">
+      <c r="S8">
         <v>7</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7</v>
       </c>
-      <c r="T8" s="2">
+      <c r="U8" s="2">
         <v>3</v>
       </c>
-      <c r="U8">
-        <v>1</v>
-      </c>
-      <c r="V8" s="3">
-        <v>1</v>
-      </c>
-      <c r="W8" s="2">
+      <c r="V8">
+        <v>1</v>
+      </c>
+      <c r="W8" s="3">
+        <v>1</v>
+      </c>
+      <c r="X8" s="2">
         <v>14</v>
       </c>
-      <c r="X8">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>1</v>
-      </c>
-      <c r="AB8"/>
-      <c r="AD8"/>
-      <c r="AF8"/>
-      <c r="AG8" s="5"/>
-    </row>
-    <row r="9" spans="1:33">
+      <c r="Y8">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC8"/>
+      <c r="AE8"/>
+      <c r="AG8"/>
+      <c r="AH8" s="5"/>
+    </row>
+    <row r="9" spans="1:34">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K9"/>
       <c r="L9" s="2">
@@ -2641,55 +2648,55 @@
       <c r="O9">
         <v>0</v>
       </c>
-      <c r="P9"/>
-      <c r="Q9" s="2">
+      <c r="Q9"/>
+      <c r="R9" s="2">
         <v>6</v>
       </c>
-      <c r="R9">
+      <c r="S9">
         <v>3</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4</v>
       </c>
-      <c r="T9" s="2">
+      <c r="U9" s="2">
         <v>2</v>
       </c>
-      <c r="U9">
+      <c r="V9">
         <v>3</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4</v>
       </c>
-      <c r="Y9"/>
-      <c r="AB9"/>
-      <c r="AD9"/>
-      <c r="AF9"/>
-      <c r="AG9" s="5"/>
-    </row>
-    <row r="10" spans="1:33">
+      <c r="Z9"/>
+      <c r="AC9"/>
+      <c r="AE9"/>
+      <c r="AG9"/>
+      <c r="AH9" s="5"/>
+    </row>
+    <row r="10" spans="1:34">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K10"/>
       <c r="L10" s="2">
@@ -2704,58 +2711,58 @@
       <c r="O10">
         <v>0</v>
       </c>
-      <c r="P10"/>
-      <c r="Q10" s="2">
+      <c r="Q10"/>
+      <c r="R10" s="2">
         <v>7</v>
       </c>
-      <c r="R10">
+      <c r="S10">
         <v>2</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3</v>
       </c>
-      <c r="T10" s="2">
+      <c r="U10" s="2">
         <v>2</v>
       </c>
-      <c r="U10">
+      <c r="V10">
         <v>2</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3</v>
       </c>
-      <c r="Y10"/>
-      <c r="AB10"/>
-      <c r="AD10"/>
-      <c r="AF10"/>
-      <c r="AG10" s="5"/>
-    </row>
-    <row r="11" spans="1:33">
+      <c r="Z10"/>
+      <c r="AC10"/>
+      <c r="AE10"/>
+      <c r="AG10"/>
+      <c r="AH10" s="5"/>
+    </row>
+    <row r="11" spans="1:34">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L11">
         <v>2</v>
@@ -2769,50 +2776,50 @@
       <c r="O11">
         <v>0</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="R11" s="2">
         <v>15</v>
       </c>
-      <c r="R11">
+      <c r="S11">
         <v>2</v>
       </c>
-      <c r="S11" s="3">
+      <c r="T11" s="3">
         <v>3</v>
       </c>
-      <c r="T11" s="2">
+      <c r="U11" s="2">
         <v>2</v>
       </c>
-      <c r="U11">
+      <c r="V11">
         <v>2</v>
       </c>
-      <c r="V11" s="3">
+      <c r="W11" s="3">
         <v>3</v>
       </c>
-      <c r="AG11" s="5"/>
-    </row>
-    <row r="12" spans="1:34">
+      <c r="AH11" s="5"/>
+    </row>
+    <row r="12" spans="1:35">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K12"/>
       <c r="L12" s="2">
@@ -2827,58 +2834,58 @@
       <c r="O12">
         <v>0</v>
       </c>
-      <c r="P12"/>
-      <c r="Q12" s="2">
+      <c r="Q12"/>
+      <c r="R12" s="2">
         <v>11</v>
       </c>
-      <c r="R12">
+      <c r="S12">
         <v>9</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>13</v>
       </c>
-      <c r="T12" s="2">
+      <c r="U12" s="2">
         <v>11</v>
       </c>
-      <c r="U12">
+      <c r="V12">
         <v>9</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>13</v>
       </c>
-      <c r="Y12"/>
-      <c r="AB12"/>
-      <c r="AD12"/>
-      <c r="AF12"/>
-      <c r="AG12" s="5"/>
-      <c r="AH12" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="13" spans="1:33">
+      <c r="Z12"/>
+      <c r="AC12"/>
+      <c r="AE12"/>
+      <c r="AG12"/>
+      <c r="AH12" s="5"/>
+      <c r="AI12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K13"/>
       <c r="L13" s="2">
@@ -2893,55 +2900,55 @@
       <c r="O13">
         <v>0</v>
       </c>
-      <c r="P13"/>
-      <c r="Q13" s="2">
+      <c r="Q13"/>
+      <c r="R13" s="2">
         <v>11</v>
       </c>
-      <c r="R13">
+      <c r="S13">
         <v>11</v>
       </c>
-      <c r="S13" s="3">
+      <c r="T13" s="3">
         <v>15</v>
       </c>
-      <c r="T13" s="2">
+      <c r="U13" s="2">
         <v>2</v>
       </c>
-      <c r="U13">
+      <c r="V13">
         <v>7</v>
       </c>
-      <c r="V13" s="3">
+      <c r="W13" s="3">
         <v>9</v>
       </c>
-      <c r="Y13"/>
-      <c r="AB13"/>
-      <c r="AD13"/>
-      <c r="AF13"/>
-      <c r="AG13" s="5"/>
-    </row>
-    <row r="14" spans="1:33">
+      <c r="Z13"/>
+      <c r="AC13"/>
+      <c r="AE13"/>
+      <c r="AG13"/>
+      <c r="AH13" s="5"/>
+    </row>
+    <row r="14" spans="1:34">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K14"/>
       <c r="L14" s="2">
@@ -2956,47 +2963,47 @@
       <c r="O14">
         <v>0</v>
       </c>
-      <c r="P14"/>
-      <c r="Q14" s="2">
+      <c r="Q14"/>
+      <c r="R14" s="2">
         <v>6</v>
       </c>
-      <c r="R14">
+      <c r="S14">
         <v>6</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>8</v>
       </c>
-      <c r="V14"/>
-      <c r="Y14"/>
-      <c r="AB14"/>
-      <c r="AD14"/>
-      <c r="AF14"/>
-      <c r="AG14" s="5"/>
-    </row>
-    <row r="15" spans="1:33">
+      <c r="W14"/>
+      <c r="Z14"/>
+      <c r="AC14"/>
+      <c r="AE14"/>
+      <c r="AG14"/>
+      <c r="AH14" s="5"/>
+    </row>
+    <row r="15" spans="1:34">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K15"/>
       <c r="L15" s="2">
@@ -3011,47 +3018,47 @@
       <c r="O15">
         <v>0</v>
       </c>
-      <c r="P15"/>
-      <c r="Q15" s="2">
+      <c r="Q15"/>
+      <c r="R15" s="2">
         <v>18</v>
       </c>
-      <c r="R15">
+      <c r="S15">
         <v>1.4</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1.8</v>
       </c>
-      <c r="V15"/>
-      <c r="Y15"/>
-      <c r="AB15"/>
-      <c r="AD15"/>
-      <c r="AF15"/>
-      <c r="AG15" s="5"/>
-    </row>
-    <row r="16" spans="1:33">
+      <c r="W15"/>
+      <c r="Z15"/>
+      <c r="AC15"/>
+      <c r="AE15"/>
+      <c r="AG15"/>
+      <c r="AH15" s="5"/>
+    </row>
+    <row r="16" spans="1:34">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K16"/>
       <c r="L16" s="2">
@@ -3066,58 +3073,58 @@
       <c r="O16">
         <v>0</v>
       </c>
-      <c r="P16"/>
-      <c r="Q16" s="2">
+      <c r="Q16"/>
+      <c r="R16" s="2">
         <v>6</v>
       </c>
-      <c r="R16">
+      <c r="S16">
         <v>4</v>
       </c>
-      <c r="S16" s="3">
+      <c r="T16" s="3">
         <v>5</v>
       </c>
-      <c r="T16" s="2">
+      <c r="U16" s="2">
         <v>18</v>
       </c>
-      <c r="U16">
+      <c r="V16">
         <v>0.8</v>
       </c>
-      <c r="V16" s="3">
+      <c r="W16" s="3">
         <v>1.1</v>
       </c>
-      <c r="Y16"/>
-      <c r="AB16"/>
-      <c r="AD16"/>
-      <c r="AF16"/>
-      <c r="AG16" s="5"/>
-    </row>
-    <row r="17" spans="1:33">
+      <c r="Z16"/>
+      <c r="AC16"/>
+      <c r="AE16"/>
+      <c r="AG16"/>
+      <c r="AH16" s="5"/>
+    </row>
+    <row r="17" spans="1:34">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K17"/>
       <c r="L17" s="2">
@@ -3132,66 +3139,66 @@
       <c r="O17">
         <v>1</v>
       </c>
-      <c r="P17"/>
-      <c r="Q17" s="2">
+      <c r="Q17"/>
+      <c r="R17" s="2">
         <v>19</v>
       </c>
-      <c r="R17">
-        <v>1</v>
-      </c>
-      <c r="S17" s="3">
-        <v>1</v>
-      </c>
-      <c r="T17" s="2">
+      <c r="S17">
+        <v>1</v>
+      </c>
+      <c r="T17" s="3">
+        <v>1</v>
+      </c>
+      <c r="U17" s="2">
         <v>2</v>
       </c>
-      <c r="U17">
+      <c r="V17">
         <v>4</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6</v>
       </c>
-      <c r="W17" s="2">
+      <c r="X17" s="2">
         <v>21</v>
       </c>
-      <c r="X17">
+      <c r="Y17">
         <v>2</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3</v>
       </c>
-      <c r="AB17"/>
-      <c r="AD17"/>
-      <c r="AF17"/>
-      <c r="AG17" s="6"/>
-    </row>
-    <row r="18" spans="1:33">
+      <c r="AC17"/>
+      <c r="AE17"/>
+      <c r="AG17"/>
+      <c r="AH17" s="6"/>
+    </row>
+    <row r="18" spans="1:34">
       <c r="A18">
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L18">
         <v>4</v>
@@ -3205,47 +3212,47 @@
       <c r="O18">
         <v>0</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="R18" s="2">
         <v>15</v>
       </c>
-      <c r="R18">
+      <c r="S18">
         <v>5</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>7</v>
       </c>
-      <c r="AC18">
+      <c r="AD18">
         <v>63</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1.5</v>
       </c>
-      <c r="AG18" s="5"/>
-    </row>
-    <row r="19" spans="1:33">
+      <c r="AH18" s="5"/>
+    </row>
+    <row r="19" spans="1:34">
       <c r="A19">
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D19" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K19"/>
       <c r="L19" s="2">
@@ -3260,58 +3267,58 @@
       <c r="O19">
         <v>1</v>
       </c>
-      <c r="P19"/>
-      <c r="Q19" s="2">
+      <c r="Q19"/>
+      <c r="R19" s="2">
         <v>23</v>
       </c>
-      <c r="R19">
-        <v>1</v>
-      </c>
-      <c r="S19" s="3">
-        <v>1</v>
-      </c>
-      <c r="T19" s="2">
+      <c r="S19">
+        <v>1</v>
+      </c>
+      <c r="T19" s="3">
+        <v>1</v>
+      </c>
+      <c r="U19" s="2">
         <v>7</v>
       </c>
-      <c r="U19">
-        <v>1</v>
-      </c>
-      <c r="V19" s="3">
+      <c r="V19">
+        <v>1</v>
+      </c>
+      <c r="W19" s="3">
         <v>2</v>
       </c>
-      <c r="Y19"/>
-      <c r="AB19"/>
-      <c r="AD19"/>
-      <c r="AF19"/>
-      <c r="AG19" s="5"/>
-    </row>
-    <row r="20" spans="1:33">
+      <c r="Z19"/>
+      <c r="AC19"/>
+      <c r="AE19"/>
+      <c r="AG19"/>
+      <c r="AH19" s="5"/>
+    </row>
+    <row r="20" spans="1:34">
       <c r="A20">
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C20" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D20" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L20">
         <v>6</v>
@@ -3325,53 +3332,53 @@
       <c r="O20">
         <v>0</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="2">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="2">
         <v>11</v>
       </c>
-      <c r="R20">
+      <c r="S20">
         <v>24</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>30</v>
       </c>
-      <c r="AC20">
+      <c r="AD20">
         <v>62</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>7</v>
       </c>
-      <c r="AG20" s="6"/>
-    </row>
-    <row r="21" spans="1:33">
+      <c r="AH20" s="6"/>
+    </row>
+    <row r="21" spans="1:34">
       <c r="A21">
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C21" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D21" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L21">
         <v>5</v>
@@ -3385,59 +3392,59 @@
       <c r="O21">
         <v>1</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="R21" s="2">
         <v>26</v>
       </c>
-      <c r="R21">
+      <c r="S21">
         <v>2</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2</v>
       </c>
-      <c r="T21" s="2">
+      <c r="U21" s="2">
         <v>11</v>
       </c>
-      <c r="U21">
+      <c r="V21">
         <v>30</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>42</v>
       </c>
-      <c r="W21">
+      <c r="X21">
         <v>2</v>
       </c>
-      <c r="X21">
+      <c r="Y21">
         <v>5</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>7</v>
       </c>
-      <c r="AG21" s="5"/>
-    </row>
-    <row r="22" spans="1:33">
+      <c r="AH21" s="5"/>
+    </row>
+    <row r="22" spans="1:34">
       <c r="A22">
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J22" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K22"/>
       <c r="L22" s="2">
@@ -3452,55 +3459,55 @@
       <c r="O22">
         <v>1</v>
       </c>
-      <c r="P22"/>
-      <c r="Q22" s="2">
+      <c r="Q22"/>
+      <c r="R22" s="2">
         <v>6</v>
       </c>
-      <c r="R22">
+      <c r="S22">
         <v>2</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>4</v>
       </c>
-      <c r="T22" s="2">
+      <c r="U22" s="2">
         <v>28</v>
       </c>
-      <c r="U22">
-        <v>1</v>
-      </c>
-      <c r="V22" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y22"/>
-      <c r="AB22"/>
-      <c r="AD22"/>
-      <c r="AF22"/>
-      <c r="AG22" s="5"/>
-    </row>
-    <row r="23" spans="1:33">
+      <c r="V22">
+        <v>1</v>
+      </c>
+      <c r="W22" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z22"/>
+      <c r="AC22"/>
+      <c r="AE22"/>
+      <c r="AG22"/>
+      <c r="AH22" s="5"/>
+    </row>
+    <row r="23" spans="1:34">
       <c r="A23">
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G23" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J23" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K23"/>
       <c r="L23" s="2">
@@ -3515,58 +3522,58 @@
       <c r="O23">
         <v>0</v>
       </c>
-      <c r="P23"/>
-      <c r="Q23" s="2">
+      <c r="Q23"/>
+      <c r="R23" s="2">
         <v>6</v>
       </c>
-      <c r="R23">
+      <c r="S23">
         <v>5</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>7</v>
       </c>
-      <c r="T23" s="2">
+      <c r="U23" s="2">
         <v>2</v>
       </c>
-      <c r="U23">
-        <v>1</v>
-      </c>
-      <c r="V23" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y23"/>
-      <c r="AB23"/>
-      <c r="AD23"/>
-      <c r="AF23"/>
-      <c r="AG23" s="5"/>
-    </row>
-    <row r="24" spans="1:33">
+      <c r="V23">
+        <v>1</v>
+      </c>
+      <c r="W23" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z23"/>
+      <c r="AC23"/>
+      <c r="AE23"/>
+      <c r="AG23"/>
+      <c r="AH23" s="5"/>
+    </row>
+    <row r="24" spans="1:34">
       <c r="A24">
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L24">
         <v>4</v>
@@ -3580,56 +3587,56 @@
       <c r="O24">
         <v>0</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="R24" s="2">
         <v>15</v>
       </c>
-      <c r="R24">
+      <c r="S24">
         <v>3</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>4</v>
       </c>
-      <c r="T24" s="2">
+      <c r="U24" s="2">
         <v>11</v>
       </c>
-      <c r="U24">
+      <c r="V24">
         <v>8</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>11</v>
       </c>
-      <c r="AC24">
+      <c r="AD24">
         <v>63</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3</v>
       </c>
-      <c r="AG24" s="5"/>
-    </row>
-    <row r="25" spans="1:33">
+      <c r="AH24" s="5"/>
+    </row>
+    <row r="25" spans="1:34">
       <c r="A25">
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K25"/>
       <c r="L25" s="2">
@@ -3644,47 +3651,47 @@
       <c r="O25">
         <v>0</v>
       </c>
-      <c r="P25"/>
-      <c r="Q25" s="2">
+      <c r="Q25"/>
+      <c r="R25" s="2">
         <v>7</v>
       </c>
-      <c r="R25">
+      <c r="S25">
         <v>3</v>
       </c>
-      <c r="S25" s="3">
+      <c r="T25" s="3">
         <v>5</v>
       </c>
-      <c r="V25"/>
-      <c r="Y25"/>
-      <c r="AB25"/>
-      <c r="AD25"/>
-      <c r="AF25"/>
-      <c r="AG25" s="5"/>
-    </row>
-    <row r="26" spans="1:33">
+      <c r="W25"/>
+      <c r="Z25"/>
+      <c r="AC25"/>
+      <c r="AE25"/>
+      <c r="AG25"/>
+      <c r="AH25" s="5"/>
+    </row>
+    <row r="26" spans="1:34">
       <c r="A26">
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F26" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J26" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K26"/>
       <c r="L26" s="2">
@@ -3699,58 +3706,58 @@
       <c r="O26">
         <v>0</v>
       </c>
-      <c r="P26"/>
-      <c r="Q26" s="2">
+      <c r="Q26"/>
+      <c r="R26" s="2">
         <v>7</v>
       </c>
-      <c r="R26">
+      <c r="S26">
         <v>3</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4</v>
       </c>
-      <c r="T26" s="2">
+      <c r="U26" s="2">
         <v>2</v>
       </c>
-      <c r="U26">
+      <c r="V26">
         <v>4</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>6</v>
       </c>
-      <c r="Y26"/>
-      <c r="AB26"/>
-      <c r="AD26"/>
-      <c r="AF26"/>
-      <c r="AG26" s="5"/>
-    </row>
-    <row r="27" spans="1:33">
+      <c r="Z26"/>
+      <c r="AC26"/>
+      <c r="AE26"/>
+      <c r="AG26"/>
+      <c r="AH26" s="5"/>
+    </row>
+    <row r="27" spans="1:34">
       <c r="A27">
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C27" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D27" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L27">
         <v>8</v>
@@ -3764,65 +3771,65 @@
       <c r="O27">
         <v>1</v>
       </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="2">
+      <c r="Q27" s="3">
+        <v>0</v>
+      </c>
+      <c r="R27" s="2">
         <v>11</v>
       </c>
-      <c r="R27">
+      <c r="S27">
         <v>12</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>18</v>
       </c>
-      <c r="T27" s="2">
+      <c r="U27" s="2">
         <v>56</v>
       </c>
-      <c r="U27">
+      <c r="V27">
         <v>24</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>30</v>
       </c>
-      <c r="W27">
+      <c r="X27">
         <v>57</v>
       </c>
-      <c r="X27">
+      <c r="Y27">
         <v>36</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>44</v>
       </c>
-      <c r="AG27" s="6"/>
-    </row>
-    <row r="28" spans="1:33">
+      <c r="AH27" s="6"/>
+    </row>
+    <row r="28" spans="1:34">
       <c r="A28">
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C28" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D28" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H28" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L28">
         <v>1</v>
@@ -3836,50 +3843,50 @@
       <c r="O28">
         <v>0</v>
       </c>
-      <c r="Q28" s="2">
+      <c r="R28" s="2">
         <v>2</v>
       </c>
-      <c r="R28">
+      <c r="S28">
         <v>6</v>
       </c>
-      <c r="S28" s="3">
+      <c r="T28" s="3">
         <v>8</v>
       </c>
-      <c r="AC28">
+      <c r="AD28">
         <v>21</v>
       </c>
-      <c r="AD28" s="3">
+      <c r="AE28" s="3">
         <v>12</v>
       </c>
-      <c r="AG28" s="5"/>
-    </row>
-    <row r="29" spans="1:33">
+      <c r="AH28" s="5"/>
+    </row>
+    <row r="29" spans="1:34">
       <c r="A29">
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C29" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D29" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F29" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G29" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J29" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K29"/>
       <c r="L29" s="2">
@@ -3894,66 +3901,66 @@
       <c r="O29">
         <v>1</v>
       </c>
-      <c r="P29"/>
-      <c r="Q29" s="2">
+      <c r="Q29"/>
+      <c r="R29" s="2">
         <v>32</v>
       </c>
-      <c r="R29">
+      <c r="S29">
         <v>30</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>30</v>
       </c>
-      <c r="T29" s="2">
+      <c r="U29" s="2">
         <v>2</v>
       </c>
-      <c r="U29">
+      <c r="V29">
         <v>3</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>5</v>
       </c>
-      <c r="W29" s="2">
+      <c r="X29" s="2">
         <v>21</v>
       </c>
-      <c r="X29">
+      <c r="Y29">
         <v>2</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>3</v>
       </c>
-      <c r="AB29"/>
-      <c r="AD29"/>
-      <c r="AF29"/>
-      <c r="AG29" s="5"/>
-    </row>
-    <row r="30" spans="1:33">
+      <c r="AC29"/>
+      <c r="AE29"/>
+      <c r="AG29"/>
+      <c r="AH29" s="5"/>
+    </row>
+    <row r="30" spans="1:34">
       <c r="A30">
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C30" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D30" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F30" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G30" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K30"/>
       <c r="L30" s="2">
@@ -3968,58 +3975,58 @@
       <c r="O30">
         <v>1</v>
       </c>
-      <c r="P30"/>
-      <c r="Q30" s="2">
+      <c r="Q30"/>
+      <c r="R30" s="2">
         <v>33</v>
       </c>
-      <c r="R30">
+      <c r="S30">
         <v>50</v>
       </c>
-      <c r="S30" s="3">
+      <c r="T30" s="3">
         <v>70</v>
       </c>
-      <c r="T30" s="2">
+      <c r="U30" s="2">
         <v>2</v>
       </c>
-      <c r="U30">
+      <c r="V30">
         <v>2</v>
       </c>
-      <c r="V30" s="3">
+      <c r="W30" s="3">
         <v>4</v>
       </c>
-      <c r="Y30"/>
-      <c r="AB30"/>
-      <c r="AD30"/>
-      <c r="AF30"/>
-      <c r="AG30" s="6"/>
-    </row>
-    <row r="31" spans="1:33">
+      <c r="Z30"/>
+      <c r="AC30"/>
+      <c r="AE30"/>
+      <c r="AG30"/>
+      <c r="AH30" s="6"/>
+    </row>
+    <row r="31" spans="1:34">
       <c r="A31">
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C31" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D31" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F31" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G31" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J31" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K31"/>
       <c r="L31" s="2">
@@ -4034,58 +4041,58 @@
       <c r="O31">
         <v>1</v>
       </c>
-      <c r="P31"/>
-      <c r="Q31" s="2">
+      <c r="Q31"/>
+      <c r="R31" s="2">
         <v>33</v>
       </c>
-      <c r="R31">
+      <c r="S31">
         <v>20</v>
       </c>
-      <c r="S31" s="3">
+      <c r="T31" s="3">
         <v>30</v>
       </c>
-      <c r="T31" s="2">
+      <c r="U31" s="2">
         <v>35</v>
       </c>
-      <c r="U31">
-        <v>1</v>
-      </c>
-      <c r="V31" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y31"/>
-      <c r="AB31"/>
-      <c r="AD31"/>
-      <c r="AF31"/>
-      <c r="AG31" s="6"/>
-    </row>
-    <row r="32" spans="1:32">
+      <c r="V31">
+        <v>1</v>
+      </c>
+      <c r="W31" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z31"/>
+      <c r="AC31"/>
+      <c r="AE31"/>
+      <c r="AG31"/>
+      <c r="AH31" s="6"/>
+    </row>
+    <row r="32" spans="1:33">
       <c r="A32">
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C32" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D32" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F32" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G32" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J32" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K32"/>
       <c r="L32" s="2">
@@ -4100,41 +4107,41 @@
       <c r="O32">
         <v>1</v>
       </c>
-      <c r="P32"/>
-      <c r="S32"/>
-      <c r="V32"/>
-      <c r="Y32"/>
-      <c r="AB32"/>
-      <c r="AD32"/>
-      <c r="AF32"/>
-    </row>
-    <row r="33" spans="1:30">
+      <c r="Q32"/>
+      <c r="T32"/>
+      <c r="W32"/>
+      <c r="Z32"/>
+      <c r="AC32"/>
+      <c r="AE32"/>
+      <c r="AG32"/>
+    </row>
+    <row r="33" spans="1:31">
       <c r="A33">
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C33" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D33" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G33" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H33" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J33" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L33">
         <v>8</v>
@@ -4148,49 +4155,49 @@
       <c r="O33">
         <v>1</v>
       </c>
-      <c r="Q33" s="2">
+      <c r="R33" s="2">
         <v>11</v>
       </c>
-      <c r="R33">
+      <c r="S33">
         <v>38</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>52</v>
       </c>
-      <c r="AC33">
+      <c r="AD33">
         <v>64</v>
       </c>
-      <c r="AD33" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19">
+      <c r="AE33" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20">
       <c r="A34">
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F34" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G34" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H34" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J34" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L34">
         <v>3</v>
@@ -4204,46 +4211,46 @@
       <c r="O34">
         <v>0</v>
       </c>
-      <c r="P34" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="2">
         <v>15</v>
       </c>
-      <c r="R34">
+      <c r="S34">
         <v>3</v>
       </c>
-      <c r="S34" s="3">
+      <c r="T34" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:19">
+    <row r="35" spans="1:20">
       <c r="A35">
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C35" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D35" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F35" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G35" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J35" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L35">
         <v>3</v>
@@ -4257,17 +4264,17 @@
       <c r="O35">
         <v>0</v>
       </c>
-      <c r="Q35" s="2">
+      <c r="R35" s="2">
         <v>11</v>
       </c>
-      <c r="R35">
+      <c r="S35">
         <v>18</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:22">
+    <row r="36" spans="1:23">
       <c r="A36">
         <v>37</v>
       </c>
@@ -4275,25 +4282,25 @@
         <v>144</v>
       </c>
       <c r="C36" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D36" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F36" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G36" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H36" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J36" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L36">
         <v>3</v>
@@ -4307,49 +4314,49 @@
       <c r="O36">
         <v>0</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="R36" s="2">
         <v>15</v>
       </c>
-      <c r="R36">
+      <c r="S36">
         <v>3</v>
       </c>
-      <c r="S36" s="3">
+      <c r="T36" s="3">
         <v>4</v>
       </c>
-      <c r="T36" s="2">
+      <c r="U36" s="2">
         <v>2</v>
       </c>
-      <c r="U36">
+      <c r="V36">
         <v>6</v>
       </c>
-      <c r="V36" s="3">
+      <c r="W36" s="3">
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:32">
+    <row r="37" spans="1:33">
       <c r="A37">
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C37" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D37" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F37" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G37" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J37" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K37"/>
       <c r="L37" s="2">
@@ -4364,54 +4371,54 @@
       <c r="O37">
         <v>0</v>
       </c>
-      <c r="P37"/>
-      <c r="Q37" s="2">
+      <c r="Q37"/>
+      <c r="R37" s="2">
         <v>7</v>
       </c>
-      <c r="R37">
+      <c r="S37">
         <v>3</v>
       </c>
-      <c r="S37" s="3">
+      <c r="T37" s="3">
         <v>4</v>
       </c>
-      <c r="T37" s="2">
+      <c r="U37" s="2">
         <v>2</v>
       </c>
-      <c r="U37">
+      <c r="V37">
         <v>6</v>
       </c>
-      <c r="V37" s="3">
+      <c r="W37" s="3">
         <v>8</v>
       </c>
-      <c r="Y37"/>
-      <c r="AB37"/>
-      <c r="AD37"/>
-      <c r="AF37"/>
-    </row>
-    <row r="38" spans="1:32">
+      <c r="Z37"/>
+      <c r="AC37"/>
+      <c r="AE37"/>
+      <c r="AG37"/>
+    </row>
+    <row r="38" spans="1:33">
       <c r="A38">
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C38" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D38" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G38" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J38" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K38"/>
       <c r="L38" s="2">
@@ -4426,54 +4433,54 @@
       <c r="O38">
         <v>1</v>
       </c>
-      <c r="P38"/>
-      <c r="Q38" s="2">
+      <c r="Q38"/>
+      <c r="R38" s="2">
         <v>21</v>
       </c>
-      <c r="R38">
+      <c r="S38">
         <v>4</v>
       </c>
-      <c r="S38" s="3">
+      <c r="T38" s="3">
         <v>5</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>2</v>
       </c>
-      <c r="U38">
+      <c r="V38">
         <v>3</v>
       </c>
-      <c r="V38" s="3">
+      <c r="W38" s="3">
         <v>5</v>
       </c>
-      <c r="Y38"/>
-      <c r="AB38"/>
-      <c r="AD38"/>
-      <c r="AF38"/>
-    </row>
-    <row r="39" spans="1:32">
+      <c r="Z38"/>
+      <c r="AC38"/>
+      <c r="AE38"/>
+      <c r="AG38"/>
+    </row>
+    <row r="39" spans="1:33">
       <c r="A39">
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C39" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D39" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F39" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G39" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J39" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K39"/>
       <c r="L39" s="2">
@@ -4488,54 +4495,54 @@
       <c r="O39">
         <v>1</v>
       </c>
-      <c r="P39"/>
-      <c r="Q39" s="2">
+      <c r="Q39"/>
+      <c r="R39" s="2">
         <v>5</v>
       </c>
-      <c r="R39">
-        <v>1</v>
-      </c>
-      <c r="S39" s="3">
+      <c r="S39">
+        <v>1</v>
+      </c>
+      <c r="T39" s="3">
         <v>2</v>
       </c>
-      <c r="T39" s="2">
+      <c r="U39" s="2">
         <v>2</v>
       </c>
-      <c r="U39">
+      <c r="V39">
         <v>6</v>
       </c>
-      <c r="V39" s="3">
+      <c r="W39" s="3">
         <v>7</v>
       </c>
-      <c r="Y39"/>
-      <c r="AB39"/>
-      <c r="AD39"/>
-      <c r="AF39"/>
-    </row>
-    <row r="40" spans="1:32">
+      <c r="Z39"/>
+      <c r="AC39"/>
+      <c r="AE39"/>
+      <c r="AG39"/>
+    </row>
+    <row r="40" spans="1:33">
       <c r="A40">
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C40" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D40" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F40" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G40" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J40" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K40"/>
       <c r="L40" s="2">
@@ -4550,54 +4557,54 @@
       <c r="O40">
         <v>1</v>
       </c>
-      <c r="P40"/>
-      <c r="Q40" s="2">
+      <c r="Q40"/>
+      <c r="R40" s="2">
         <v>7</v>
       </c>
-      <c r="R40">
+      <c r="S40">
         <v>4</v>
       </c>
-      <c r="S40" s="3">
+      <c r="T40" s="3">
         <v>5</v>
       </c>
-      <c r="T40" s="2">
+      <c r="U40" s="2">
         <v>38</v>
       </c>
-      <c r="U40">
+      <c r="V40">
         <v>4</v>
       </c>
-      <c r="V40" s="3">
+      <c r="W40" s="3">
         <v>5</v>
       </c>
-      <c r="Y40"/>
-      <c r="AB40"/>
-      <c r="AD40"/>
-      <c r="AF40"/>
-    </row>
-    <row r="41" spans="1:32">
+      <c r="Z40"/>
+      <c r="AC40"/>
+      <c r="AE40"/>
+      <c r="AG40"/>
+    </row>
+    <row r="41" spans="1:33">
       <c r="A41">
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C41" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D41" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F41" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G41" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J41" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K41"/>
       <c r="L41" s="2">
@@ -4612,54 +4619,54 @@
       <c r="O41">
         <v>0</v>
       </c>
-      <c r="P41"/>
-      <c r="Q41" s="2">
+      <c r="Q41"/>
+      <c r="R41" s="2">
         <v>6</v>
       </c>
-      <c r="R41">
+      <c r="S41">
         <v>3</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3</v>
       </c>
-      <c r="T41" s="2">
+      <c r="U41" s="2">
         <v>39</v>
       </c>
-      <c r="U41">
+      <c r="V41">
         <v>2</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3</v>
       </c>
-      <c r="Y41"/>
-      <c r="AB41"/>
-      <c r="AD41"/>
-      <c r="AF41"/>
-    </row>
-    <row r="42" spans="1:32">
+      <c r="Z41"/>
+      <c r="AC41"/>
+      <c r="AE41"/>
+      <c r="AG41"/>
+    </row>
+    <row r="42" spans="1:33">
       <c r="A42">
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C42" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D42" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F42" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G42" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J42" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K42"/>
       <c r="L42" s="2">
@@ -4674,54 +4681,54 @@
       <c r="O42">
         <v>1</v>
       </c>
-      <c r="P42"/>
-      <c r="Q42" s="2">
+      <c r="Q42"/>
+      <c r="R42" s="2">
         <v>7</v>
       </c>
-      <c r="R42">
-        <v>1</v>
-      </c>
-      <c r="S42" s="3">
+      <c r="S42">
+        <v>1</v>
+      </c>
+      <c r="T42" s="3">
         <v>3</v>
       </c>
-      <c r="T42" s="2">
+      <c r="U42" s="2">
         <v>41</v>
       </c>
-      <c r="U42">
-        <v>1</v>
-      </c>
-      <c r="V42" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y42"/>
-      <c r="AB42"/>
-      <c r="AD42"/>
-      <c r="AF42"/>
-    </row>
-    <row r="43" spans="1:32">
+      <c r="V42">
+        <v>1</v>
+      </c>
+      <c r="W42" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z42"/>
+      <c r="AC42"/>
+      <c r="AE42"/>
+      <c r="AG42"/>
+    </row>
+    <row r="43" spans="1:33">
       <c r="A43">
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C43" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D43" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F43" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G43" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J43" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K43"/>
       <c r="L43" s="2">
@@ -4736,65 +4743,65 @@
       <c r="O43">
         <v>1</v>
       </c>
-      <c r="P43"/>
-      <c r="Q43" s="2">
+      <c r="Q43"/>
+      <c r="R43" s="2">
         <v>6</v>
       </c>
-      <c r="R43">
+      <c r="S43">
         <v>5</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5</v>
       </c>
-      <c r="T43" s="2">
+      <c r="U43" s="2">
         <v>14</v>
       </c>
-      <c r="U43">
-        <v>1</v>
-      </c>
-      <c r="V43" s="3">
-        <v>1</v>
-      </c>
-      <c r="W43" s="2">
+      <c r="V43">
+        <v>1</v>
+      </c>
+      <c r="W43" s="3">
+        <v>1</v>
+      </c>
+      <c r="X43" s="2">
         <v>18</v>
       </c>
-      <c r="X43">
+      <c r="Y43">
         <v>0.9</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1.2</v>
       </c>
-      <c r="AB43"/>
-      <c r="AD43"/>
-      <c r="AF43"/>
-    </row>
-    <row r="44" spans="1:22">
+      <c r="AC43"/>
+      <c r="AE43"/>
+      <c r="AG43"/>
+    </row>
+    <row r="44" spans="1:23">
       <c r="A44">
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C44" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D44" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F44" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G44" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H44" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J44" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L44">
         <v>6</v>
@@ -4808,49 +4815,49 @@
       <c r="O44">
         <v>1</v>
       </c>
-      <c r="Q44" s="2">
+      <c r="R44" s="2">
         <v>15</v>
       </c>
-      <c r="R44">
+      <c r="S44">
         <v>2</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2</v>
       </c>
-      <c r="T44" s="2">
+      <c r="U44" s="2">
         <v>42</v>
       </c>
-      <c r="U44">
+      <c r="V44">
         <v>8</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:32">
+    <row r="45" spans="1:33">
       <c r="A45">
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C45" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D45" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F45" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G45" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J45" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K45"/>
       <c r="L45" s="2">
@@ -4865,65 +4872,65 @@
       <c r="O45">
         <v>1</v>
       </c>
-      <c r="P45"/>
-      <c r="Q45" s="2">
+      <c r="Q45"/>
+      <c r="R45" s="2">
         <v>7</v>
       </c>
-      <c r="R45">
+      <c r="S45">
         <v>7</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>9</v>
       </c>
-      <c r="T45" s="2">
+      <c r="U45" s="2">
         <v>26</v>
       </c>
-      <c r="U45">
+      <c r="V45">
         <v>2</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2</v>
       </c>
-      <c r="W45" s="2">
+      <c r="X45" s="2">
         <v>2</v>
       </c>
-      <c r="X45">
+      <c r="Y45">
         <v>7</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>8</v>
       </c>
-      <c r="AB45"/>
-      <c r="AD45"/>
-      <c r="AF45"/>
-    </row>
-    <row r="46" spans="1:32">
+      <c r="AC45"/>
+      <c r="AE45"/>
+      <c r="AG45"/>
+    </row>
+    <row r="46" spans="1:33">
       <c r="A46">
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C46" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D46" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F46" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G46" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J46" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K46"/>
       <c r="L46" s="2">
@@ -4938,62 +4945,62 @@
       <c r="O46">
         <v>1</v>
       </c>
-      <c r="P46"/>
-      <c r="Q46" s="2">
+      <c r="Q46"/>
+      <c r="R46" s="2">
         <v>32</v>
       </c>
-      <c r="R46">
+      <c r="S46">
         <v>40</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>40</v>
       </c>
-      <c r="T46" s="2">
+      <c r="U46" s="2">
         <v>33</v>
       </c>
-      <c r="U46">
+      <c r="V46">
         <v>30</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>30</v>
       </c>
-      <c r="W46" s="2">
+      <c r="X46" s="2">
         <v>19</v>
       </c>
-      <c r="X46">
-        <v>1</v>
-      </c>
-      <c r="Y46" s="3">
-        <v>1</v>
-      </c>
-      <c r="AB46"/>
-      <c r="AD46"/>
-      <c r="AF46"/>
-    </row>
-    <row r="47" spans="1:32">
+      <c r="Y46">
+        <v>1</v>
+      </c>
+      <c r="Z46" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC46"/>
+      <c r="AE46"/>
+      <c r="AG46"/>
+    </row>
+    <row r="47" spans="1:33">
       <c r="A47">
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C47" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D47" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F47" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G47" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J47" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K47"/>
       <c r="L47" s="2">
@@ -5008,23 +5015,23 @@
       <c r="O47">
         <v>0</v>
       </c>
-      <c r="P47"/>
-      <c r="Q47" s="2">
+      <c r="Q47"/>
+      <c r="R47" s="2">
         <v>11</v>
       </c>
-      <c r="R47">
+      <c r="S47">
         <v>10</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>14</v>
       </c>
-      <c r="V47"/>
-      <c r="Y47"/>
-      <c r="AB47"/>
-      <c r="AD47"/>
-      <c r="AF47"/>
-    </row>
-    <row r="48" spans="1:32">
+      <c r="W47"/>
+      <c r="Z47"/>
+      <c r="AC47"/>
+      <c r="AE47"/>
+      <c r="AG47"/>
+    </row>
+    <row r="48" spans="1:33">
       <c r="A48">
         <v>49</v>
       </c>
@@ -5032,22 +5039,22 @@
         <v>123</v>
       </c>
       <c r="C48" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D48" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F48" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G48" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J48" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K48"/>
       <c r="L48" s="2">
@@ -5062,57 +5069,57 @@
       <c r="O48">
         <v>0</v>
       </c>
-      <c r="P48"/>
-      <c r="Q48" s="2">
+      <c r="Q48"/>
+      <c r="R48" s="2">
         <v>11</v>
       </c>
-      <c r="R48">
+      <c r="S48">
         <v>8</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>11</v>
       </c>
-      <c r="T48" s="2">
+      <c r="U48" s="2">
         <v>6</v>
       </c>
-      <c r="U48">
+      <c r="V48">
         <v>3</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3</v>
       </c>
-      <c r="Y48"/>
-      <c r="AB48"/>
-      <c r="AD48"/>
-      <c r="AF48"/>
-    </row>
-    <row r="49" spans="1:22">
+      <c r="Z48"/>
+      <c r="AC48"/>
+      <c r="AE48"/>
+      <c r="AG48"/>
+    </row>
+    <row r="49" spans="1:23">
       <c r="A49">
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C49" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D49" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F49" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G49" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H49" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J49" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L49">
         <v>4</v>
@@ -5126,49 +5133,49 @@
       <c r="O49">
         <v>0</v>
       </c>
-      <c r="Q49" s="2">
+      <c r="R49" s="2">
         <v>11</v>
       </c>
-      <c r="R49">
+      <c r="S49">
         <v>7</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>11</v>
       </c>
-      <c r="T49" s="2">
+      <c r="U49" s="2">
         <v>45</v>
       </c>
-      <c r="U49">
+      <c r="V49">
         <v>2</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:32">
+    <row r="50" spans="1:33">
       <c r="A50">
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C50" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D50" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F50" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G50" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J50" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K50"/>
       <c r="L50" s="2">
@@ -5183,54 +5190,54 @@
       <c r="O50">
         <v>1</v>
       </c>
-      <c r="P50"/>
-      <c r="Q50" s="2">
+      <c r="Q50"/>
+      <c r="R50" s="2">
         <v>6</v>
       </c>
-      <c r="R50">
+      <c r="S50">
         <v>5</v>
       </c>
-      <c r="S50" s="3">
+      <c r="T50" s="3">
         <v>7</v>
       </c>
-      <c r="T50" s="2">
+      <c r="U50" s="2">
         <v>18</v>
       </c>
-      <c r="U50">
+      <c r="V50">
         <v>1.1</v>
       </c>
-      <c r="V50" s="3">
+      <c r="W50" s="3">
         <v>1.7</v>
       </c>
-      <c r="Y50"/>
-      <c r="AB50"/>
-      <c r="AD50"/>
-      <c r="AF50"/>
-    </row>
-    <row r="51" spans="1:32">
+      <c r="Z50"/>
+      <c r="AC50"/>
+      <c r="AE50"/>
+      <c r="AG50"/>
+    </row>
+    <row r="51" spans="1:33">
       <c r="A51">
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C51" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D51" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F51" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G51" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J51" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K51"/>
       <c r="L51" s="2">
@@ -5245,54 +5252,54 @@
       <c r="O51">
         <v>1</v>
       </c>
-      <c r="P51"/>
-      <c r="Q51" s="2">
+      <c r="Q51"/>
+      <c r="R51" s="2">
         <v>6</v>
       </c>
-      <c r="R51">
-        <v>1</v>
-      </c>
-      <c r="S51" s="3">
+      <c r="S51">
+        <v>1</v>
+      </c>
+      <c r="T51" s="3">
         <v>3</v>
       </c>
-      <c r="T51" s="2">
+      <c r="U51" s="2">
         <v>49</v>
       </c>
-      <c r="U51">
-        <v>1</v>
-      </c>
-      <c r="V51" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y51"/>
-      <c r="AB51"/>
-      <c r="AD51"/>
-      <c r="AF51"/>
-    </row>
-    <row r="52" spans="1:32">
+      <c r="V51">
+        <v>1</v>
+      </c>
+      <c r="W51" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z51"/>
+      <c r="AC51"/>
+      <c r="AE51"/>
+      <c r="AG51"/>
+    </row>
+    <row r="52" spans="1:33">
       <c r="A52">
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C52" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D52" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F52" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G52" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J52" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K52"/>
       <c r="L52" s="2">
@@ -5307,57 +5314,57 @@
       <c r="O52">
         <v>1</v>
       </c>
-      <c r="P52"/>
-      <c r="Q52" s="2">
+      <c r="Q52"/>
+      <c r="R52" s="2">
         <v>9</v>
       </c>
-      <c r="R52">
+      <c r="S52">
         <v>2</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2</v>
       </c>
-      <c r="T52" s="2">
+      <c r="U52" s="2">
         <v>21</v>
       </c>
-      <c r="U52">
+      <c r="V52">
         <v>2</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2</v>
       </c>
-      <c r="Y52"/>
-      <c r="AB52"/>
-      <c r="AD52"/>
-      <c r="AF52"/>
-    </row>
-    <row r="53" spans="1:22">
+      <c r="Z52"/>
+      <c r="AC52"/>
+      <c r="AE52"/>
+      <c r="AG52"/>
+    </row>
+    <row r="53" spans="1:23">
       <c r="A53">
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C53" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D53" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F53" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G53" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H53" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J53" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L53">
         <v>5</v>
@@ -5371,55 +5378,55 @@
       <c r="O53">
         <v>1</v>
       </c>
-      <c r="P53" s="3">
+      <c r="Q53" s="3">
         <v>6</v>
       </c>
-      <c r="Q53">
+      <c r="R53">
         <v>50</v>
       </c>
-      <c r="R53">
+      <c r="S53">
         <v>3</v>
       </c>
-      <c r="S53" s="3">
+      <c r="T53" s="3">
         <v>4</v>
       </c>
-      <c r="T53">
+      <c r="U53">
         <v>51</v>
       </c>
-      <c r="U53">
+      <c r="V53">
         <v>-0.5</v>
       </c>
-      <c r="V53" s="3">
+      <c r="W53" s="3">
         <v>-0.5</v>
       </c>
     </row>
-    <row r="54" spans="1:25">
+    <row r="54" spans="1:26">
       <c r="A54">
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C54" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D54" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F54" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G54" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H54" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J54" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K54" s="3">
         <v>14</v>
@@ -5436,61 +5443,61 @@
       <c r="O54">
         <v>1</v>
       </c>
-      <c r="Q54">
+      <c r="R54">
         <v>15</v>
       </c>
-      <c r="R54">
+      <c r="S54">
         <v>3</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4</v>
       </c>
-      <c r="T54">
+      <c r="U54">
         <v>14</v>
       </c>
-      <c r="U54">
-        <v>1</v>
-      </c>
-      <c r="V54" s="3">
-        <v>1</v>
-      </c>
-      <c r="W54">
+      <c r="V54">
+        <v>1</v>
+      </c>
+      <c r="W54" s="3">
+        <v>1</v>
+      </c>
+      <c r="X54">
         <v>52</v>
       </c>
-      <c r="X54">
+      <c r="Y54">
         <v>3</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:31">
+    <row r="55" spans="1:32">
       <c r="A55">
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C55" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D55" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F55" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G55" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H55" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J55" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L55">
         <v>4</v>
@@ -5504,53 +5511,53 @@
       <c r="O55">
         <v>1</v>
       </c>
-      <c r="Q55">
+      <c r="R55">
         <v>15</v>
       </c>
-      <c r="R55">
-        <v>1</v>
-      </c>
-      <c r="S55" s="3">
+      <c r="S55">
+        <v>1</v>
+      </c>
+      <c r="T55" s="3">
         <v>3</v>
       </c>
-      <c r="T55">
+      <c r="U55">
         <v>60</v>
       </c>
-      <c r="U55">
-        <v>1</v>
-      </c>
-      <c r="V55" s="3">
-        <v>1</v>
-      </c>
-      <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="1:31">
+      <c r="V55">
+        <v>1</v>
+      </c>
+      <c r="W55" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="1:32">
       <c r="A56">
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C56" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D56" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F56" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G56" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H56" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J56" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K56" s="3">
         <v>3</v>
@@ -5567,62 +5574,62 @@
       <c r="O56">
         <v>1</v>
       </c>
-      <c r="Q56">
+      <c r="R56">
         <v>45</v>
       </c>
-      <c r="R56">
+      <c r="S56">
         <v>3</v>
       </c>
-      <c r="S56" s="3">
+      <c r="T56" s="3">
         <v>4</v>
       </c>
-      <c r="T56">
+      <c r="U56">
         <v>11</v>
       </c>
-      <c r="U56">
+      <c r="V56">
         <v>12</v>
       </c>
-      <c r="V56" s="3">
+      <c r="W56" s="3">
         <v>18</v>
       </c>
-      <c r="W56">
+      <c r="X56">
         <v>14</v>
       </c>
-      <c r="X56">
-        <v>1</v>
-      </c>
-      <c r="Y56" s="3">
-        <v>1</v>
-      </c>
-      <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="1:22">
+      <c r="Y56">
+        <v>1</v>
+      </c>
+      <c r="Z56" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="1:23">
       <c r="A57">
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C57" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D57" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F57" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G57" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H57" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J57" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K57" s="3">
         <v>3</v>
@@ -5639,22 +5646,22 @@
       <c r="O57">
         <v>1</v>
       </c>
-      <c r="Q57">
+      <c r="R57">
         <v>2</v>
       </c>
-      <c r="R57">
+      <c r="S57">
         <v>5</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6</v>
       </c>
-      <c r="T57">
+      <c r="U57">
         <v>2</v>
       </c>
-      <c r="U57">
+      <c r="V57">
         <v>5</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>6</v>
       </c>
     </row>
@@ -5663,28 +5670,28 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C58" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D58" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F58" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G58" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H58" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J58" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L58">
         <v>3</v>
@@ -5699,33 +5706,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:19">
+    <row r="59" spans="1:20">
       <c r="A59">
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C59" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D59" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F59" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G59" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H59" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J59" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L59">
         <v>4</v>
@@ -5739,13 +5746,13 @@
       <c r="O59">
         <v>0</v>
       </c>
-      <c r="Q59">
+      <c r="R59">
         <v>2</v>
       </c>
-      <c r="R59">
+      <c r="S59">
         <v>7</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9</v>
       </c>
     </row>
@@ -5754,28 +5761,28 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C60" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D60" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F60" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G60" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H60" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J60" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L60">
         <v>2</v>
@@ -5795,28 +5802,28 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C61" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D61" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F61" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G61" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H61" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J61" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K61" s="3">
         <v>14</v>
@@ -5872,19 +5879,19 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5892,13 +5899,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I2">
         <v>-1</v>
@@ -5909,19 +5916,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -5932,16 +5939,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -5952,16 +5959,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -5972,13 +5979,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -5989,16 +5996,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -6009,13 +6016,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -6029,13 +6036,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D9" t="s">
         <v>208</v>
-      </c>
-      <c r="C9" t="s">
-        <v>208</v>
-      </c>
-      <c r="D9" t="s">
-        <v>207</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -6049,13 +6056,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -6069,13 +6076,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -6086,16 +6093,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C12" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D12" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E12" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -6106,16 +6113,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -6126,19 +6133,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -6149,16 +6156,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C15" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D15" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E15" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -6169,16 +6176,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C16" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D16" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E16" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -6189,13 +6196,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C17" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D17" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -6209,16 +6216,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C18" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D18" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E18" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -6229,13 +6236,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C19" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D19" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -6249,13 +6256,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C20" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D20" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -6269,16 +6276,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C21" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D21" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E21" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -6289,16 +6296,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C22" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D22" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E22" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -6309,13 +6316,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C23" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D23" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E23">
         <v>5</v>
@@ -6329,19 +6336,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C24" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D24" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -6352,13 +6359,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C25" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D25" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -6372,16 +6379,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C26" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D26" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E26" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -6395,16 +6402,16 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C27" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D27" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E27" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -6415,13 +6422,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C28" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D28" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -6435,19 +6442,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C29" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D29" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -6461,13 +6468,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C30" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D30" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -6481,19 +6488,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C31" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D31" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E31" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F31" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -6504,19 +6511,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C32" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D32" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E32">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -6527,19 +6534,19 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C33" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D33" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E33">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -6550,16 +6557,16 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C34" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D34" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E34" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -6570,16 +6577,16 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C35" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D35" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E35" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -6590,19 +6597,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
+        <v>252</v>
+      </c>
+      <c r="C36" t="s">
+        <v>252</v>
+      </c>
+      <c r="D36" t="s">
+        <v>192</v>
+      </c>
+      <c r="E36" t="s">
         <v>251</v>
       </c>
-      <c r="C36" t="s">
-        <v>251</v>
-      </c>
-      <c r="D36" t="s">
-        <v>191</v>
-      </c>
-      <c r="E36" t="s">
-        <v>250</v>
-      </c>
       <c r="F36" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -6616,13 +6623,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C37" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D37" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E37">
         <v>11</v>
@@ -6636,16 +6643,16 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C38" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D38" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E38" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -6656,13 +6663,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C39" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D39" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -6679,16 +6686,16 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C40" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D40" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E40" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -6699,13 +6706,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D41" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -6722,19 +6729,19 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -6748,13 +6755,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C43" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D43" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E43">
         <v>12</v>
@@ -6768,13 +6775,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C44" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D44" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E44">
         <v>13</v>
@@ -6788,19 +6795,19 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D45" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E45" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F45" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I45">
         <v>-1</v>
@@ -6811,16 +6818,16 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E46" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I46">
         <v>1</v>
@@ -6831,13 +6838,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C47" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D47" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E47">
         <v>14</v>
@@ -6851,19 +6858,19 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C48" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D48" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I48">
         <v>-1</v>
@@ -6874,13 +6881,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C49" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D49" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E49">
         <v>15</v>
@@ -6894,19 +6901,19 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C50" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D50" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I50">
         <v>-1</v>
@@ -6917,13 +6924,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C51" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D51" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E51">
         <v>16</v>
@@ -6937,13 +6944,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C52" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D52" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -6957,13 +6964,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C53" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D53" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E53">
         <v>3</v>
@@ -6977,13 +6984,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C54" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D54" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E54">
         <v>3</v>
@@ -7000,16 +7007,16 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C55" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D55" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E55" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G55">
         <v>6</v>
@@ -7023,16 +7030,16 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C56" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D56" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E56" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G56">
         <v>7</v>
@@ -7046,16 +7053,16 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C57" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D57" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E57" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G57">
         <v>8</v>
@@ -7069,16 +7076,16 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C58" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D58" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E58" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G58">
         <v>6</v>
@@ -7092,16 +7099,16 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
+        <v>281</v>
+      </c>
+      <c r="C59" t="s">
         <v>280</v>
       </c>
-      <c r="C59" t="s">
-        <v>279</v>
-      </c>
       <c r="D59" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E59" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G59">
         <v>7</v>
@@ -7115,16 +7122,16 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C60" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D60" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E60" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G60">
         <v>8</v>
@@ -7138,19 +7145,19 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C61" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D61" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E61">
         <v>3</v>
       </c>
       <c r="F61" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I61">
         <v>-1</v>
@@ -7161,13 +7168,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C62" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D62" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E62">
         <v>20</v>
@@ -7181,16 +7188,16 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C63" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D63" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F63" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I63">
         <v>-1</v>
@@ -7201,13 +7208,13 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C64" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D64" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E64">
         <v>21</v>
@@ -7221,13 +7228,13 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C65" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D65" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E65">
         <v>3</v>
@@ -7241,19 +7248,19 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C66" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D66" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E66">
         <v>14</v>
       </c>
       <c r="F66" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I66">
         <v>-1</v>
@@ -7264,13 +7271,13 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C67" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D67" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E67">
         <v>22</v>
@@ -7312,43 +7319,43 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -7356,10 +7363,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -7385,10 +7392,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C3" t="s">
         <v>296</v>
-      </c>
-      <c r="C3" t="s">
-        <v>295</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -7408,10 +7415,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -7425,10 +7432,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C5" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -7460,10 +7467,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -7483,10 +7490,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -7506,10 +7513,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -7529,10 +7536,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -7552,10 +7559,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -7575,10 +7582,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -7604,10 +7611,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C12" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -7633,10 +7640,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C13" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -7656,10 +7663,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -7679,10 +7686,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C15" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -7702,10 +7709,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C16" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -7725,10 +7732,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C17" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -7748,10 +7755,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C18" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -7771,10 +7778,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C19" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -7788,10 +7795,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C20" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -7805,10 +7812,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C21" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -7822,10 +7829,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C22" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -7845,10 +7852,10 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C23" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -7868,10 +7875,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C24" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -7891,10 +7898,10 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C25" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -7908,10 +7915,10 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C26" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -7925,10 +7932,10 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C27" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -7942,10 +7949,10 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C28" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -7959,10 +7966,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C29" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -7976,10 +7983,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C30" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -7993,10 +8000,10 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C31" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -8010,10 +8017,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C32" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -8027,10 +8034,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -8044,10 +8051,10 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C34" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -8089,16 +8096,16 @@
         <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8106,13 +8113,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -8126,16 +8133,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C3" t="s">
+        <v>330</v>
+      </c>
+      <c r="D3" t="s">
         <v>328</v>
       </c>
-      <c r="C3" t="s">
-        <v>329</v>
-      </c>
-      <c r="D3" t="s">
-        <v>327</v>
-      </c>
       <c r="F3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" ht="12.95" customHeight="1" spans="1:6">
@@ -8143,16 +8150,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>331</v>
+      </c>
+      <c r="C4" t="s">
         <v>330</v>
       </c>
-      <c r="C4" t="s">
-        <v>329</v>
-      </c>
       <c r="D4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8160,13 +8167,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -8180,13 +8187,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -8200,13 +8207,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -8220,13 +8227,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C8" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -8240,13 +8247,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -8260,13 +8267,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -8280,16 +8287,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C11" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F11">
         <v>2</v>

--- a/Assets/StreamingAssets/Configurations/Cards.xlsx
+++ b/Assets/StreamingAssets/Configurations/Cards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C73CFC0A-AF50-4F60-A563-A94655455336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{620932BE-563C-4629-9CA8-600FCB34636A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>

--- a/Assets/StreamingAssets/Configurations/Cards.xlsx
+++ b/Assets/StreamingAssets/Configurations/Cards.xlsx
@@ -7,13 +7,13 @@
     <workbookView windowWidth="24750" windowHeight="10480"/>
   </bookViews>
   <sheets>
-    <sheet name="Cards" sheetId="1" r:id="rId1"/>
+    <sheet name="Crads" sheetId="1" r:id="rId1"/>
     <sheet name="Effects" sheetId="2" r:id="rId2"/>
     <sheet name="Buffs" sheetId="3" r:id="rId3"/>
     <sheet name="Conditions" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cards!$G$1:$G$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Crads!$G$1:$G$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="381">
   <si>
     <t>ID</t>
   </si>
@@ -143,445 +143,559 @@
     <t>参数+7</t>
   </si>
   <si>
+    <t>参数+X1$1212</t>
+  </si>
+  <si>
+    <t>Basic</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Stamina</t>
+  </si>
+  <si>
+    <t>喝水</t>
+  </si>
+  <si>
+    <t>神采+4</t>
+  </si>
+  <si>
+    <t>神采+X1</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>闪耀</t>
+  </si>
+  <si>
+    <t>参数+15，红温大于10层时，参数+9</t>
+  </si>
+  <si>
+    <t>参数+X1，红温大于10层时，参数+X2</t>
+  </si>
+  <si>
+    <t>Common</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>angry</t>
+  </si>
+  <si>
+    <t>战术喝水</t>
+  </si>
+  <si>
+    <t>参数+5，神采+4</t>
+  </si>
+  <si>
+    <t>参数+X1，神采+X2</t>
+  </si>
+  <si>
+    <t>kale</t>
+  </si>
+  <si>
+    <t>下一张使用的牌会使用两次，抽一张卡,神采+2</t>
+  </si>
+  <si>
+    <t>下一张使用的牌会使用两次，抽X3张卡,神采+X2</t>
+  </si>
+  <si>
+    <t>Epic</t>
+  </si>
+  <si>
+    <t>Buff</t>
+  </si>
+  <si>
+    <t>刷新</t>
+  </si>
+  <si>
+    <t>重抽其他手牌，卡牌使用次数+1，体力消耗减少50%+2回合</t>
+  </si>
+  <si>
+    <t>重抽其他手牌，卡牌使用次数+X3，体力消耗减少50%+X2回合</t>
+  </si>
+  <si>
+    <t>才八点</t>
+  </si>
+  <si>
+    <t>获得一个额外回合，神采+7，出牌次数+1</t>
+  </si>
+  <si>
+    <t>获得一个额外回合，神采+X1，出牌次数+X2</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>wink</t>
+  </si>
+  <si>
+    <t>亲和力+3，神采+2</t>
+  </si>
+  <si>
+    <t>亲和力+X1，神采+X2</t>
+  </si>
+  <si>
+    <t>集中</t>
+  </si>
+  <si>
+    <t>专注+2，神采+2</t>
+  </si>
+  <si>
+    <t>专注+X1，神采+X2</t>
+  </si>
+  <si>
+    <t>生气</t>
+  </si>
+  <si>
+    <t>红温+2，神采+2</t>
+  </si>
+  <si>
+    <t>红温+X1，神采+X2</t>
+  </si>
+  <si>
+    <t>二次推流</t>
+  </si>
+  <si>
+    <t>参数+9/2次</t>
+  </si>
+  <si>
+    <t>参数+X1/2次</t>
+  </si>
+  <si>
+    <t>加分动画显示需改进</t>
+  </si>
+  <si>
+    <t>才艺</t>
+  </si>
+  <si>
+    <t>参数+11，神采+7</t>
+  </si>
+  <si>
+    <t>Rare</t>
+  </si>
+  <si>
+    <t>小花花</t>
+  </si>
+  <si>
+    <t>亲和力+6</t>
+  </si>
+  <si>
+    <t>亲和力+X1</t>
+  </si>
+  <si>
+    <t>饭撒</t>
+  </si>
+  <si>
+    <t>获得亲和力140%的参数</t>
+  </si>
+  <si>
+    <t>获得亲和力X1的参数</t>
+  </si>
+  <si>
+    <t>desuwa</t>
+  </si>
+  <si>
+    <t>亲和力+4，获得亲和力层数80%的参数</t>
+  </si>
+  <si>
+    <t>亲和力+X1，获得亲和力层数X2的参数</t>
+  </si>
+  <si>
+    <t>欢迎上舰</t>
+  </si>
+  <si>
+    <t>舰长+1，神采+4，体力消耗减少+2回合</t>
+  </si>
+  <si>
+    <t>舰长+X1，神采+X2，体力消耗减少+X3回合</t>
+  </si>
+  <si>
+    <t>revenue</t>
+  </si>
+  <si>
+    <t>攻击弹幕</t>
+  </si>
+  <si>
+    <t>红温+5</t>
+  </si>
+  <si>
+    <t>红温+X1</t>
+  </si>
+  <si>
+    <t>神降临</t>
+  </si>
+  <si>
+    <t>专注+1，以后，每回合结束时，专注+2</t>
+  </si>
+  <si>
+    <t>专注+X2，以后，每回合结束时，以后回合结束时专注+X1</t>
+  </si>
+  <si>
+    <t>点名弹幕</t>
+  </si>
+  <si>
+    <t>在有红温的状态下可使用，参数+24</t>
+  </si>
+  <si>
+    <t>在有红温的状态下可使用，参数+X1</t>
+  </si>
+  <si>
+    <t>激怒</t>
+  </si>
+  <si>
+    <t>体力消耗增加50%+2回合，参数+30，神采+5</t>
+  </si>
+  <si>
+    <t>体力消耗增加50%+X1回合，参数+X2，神采+X3</t>
+  </si>
+  <si>
+    <t>美丽动人</t>
+  </si>
+  <si>
+    <t>亲和力+2，以后，每当使用M卡时，亲和力+1</t>
+  </si>
+  <si>
+    <t>亲和力+X1，以后，每当使用M卡时，亲和力+X2</t>
+  </si>
+  <si>
+    <t>小巧思</t>
+  </si>
+  <si>
+    <t>亲和力+5，神采+1</t>
+  </si>
+  <si>
+    <t>冲刺！</t>
+  </si>
+  <si>
+    <t>红温+3，参数+8</t>
+  </si>
+  <si>
+    <t>红温+X1，参数+X2</t>
+  </si>
+  <si>
+    <t>闭眼</t>
+  </si>
+  <si>
+    <t>专注+3</t>
+  </si>
+  <si>
+    <t>专注+X1</t>
+  </si>
+  <si>
+    <t>小憩</t>
+  </si>
+  <si>
+    <t>专注+3，神采+4</t>
+  </si>
+  <si>
+    <t>警告！</t>
+  </si>
+  <si>
+    <t>在红温的状态下可用，参数+12，红温大于10层时，参数+24，红温大于30层时，参数+36</t>
+  </si>
+  <si>
+    <t>在红温的状态下可用，参数+X1，红温大于10层时，参数+X2，红温大于30层时，参数+X3</t>
+  </si>
+  <si>
+    <t>躺</t>
+  </si>
+  <si>
+    <t>神采+6</t>
+  </si>
+  <si>
+    <t>fun</t>
+  </si>
+  <si>
+    <t>SC</t>
+  </si>
+  <si>
+    <t>沪币+30，神采+3，体力消耗减少+2回合</t>
+  </si>
+  <si>
+    <t>流水+X1，神采+X2，体力消耗减少50%+X3回合</t>
+  </si>
+  <si>
+    <t>直播通知</t>
+  </si>
+  <si>
+    <t>同接+50，神采+2</t>
+  </si>
+  <si>
+    <t>同接+X1，神采+X2</t>
+  </si>
+  <si>
+    <t>YLG</t>
+  </si>
+  <si>
+    <t>同接+20，以后，每当打出A卡时，同接+10</t>
+  </si>
+  <si>
+    <t>同接+X1，以后，每当打出A卡时，同接+X2</t>
+  </si>
+  <si>
+    <t>爆米</t>
+  </si>
+  <si>
+    <t>获得同接数20%的流水</t>
+  </si>
+  <si>
+    <t>爆！</t>
+  </si>
+  <si>
+    <t>参数+38，红温大于30层时，卡牌使用次数+1</t>
+  </si>
+  <si>
+    <t>参数+X1，红温大于30层时，卡牌使用次数+1</t>
+  </si>
+  <si>
+    <t>越想越气</t>
+  </si>
+  <si>
+    <t>红温+2，有红温的状态下，红温+2，红温大于30层时，红温+4</t>
+  </si>
+  <si>
+    <t>红温+X1，有红温的状态下，红温+2，红温大于30层时，红温+4</t>
+  </si>
+  <si>
+    <t>为我欢呼</t>
+  </si>
+  <si>
+    <t>幽默+1，以后每当使用M卡时，幽默+1</t>
+  </si>
+  <si>
+    <t>幽默+X1，以后每当使用M卡时，幽默+1</t>
+  </si>
+  <si>
+    <t>红温+3，神采+6</t>
+  </si>
+  <si>
+    <t>观察</t>
+  </si>
+  <si>
+    <t>专注+3，神采+6</t>
+  </si>
+  <si>
+    <t>首页推送</t>
+  </si>
+  <si>
+    <t>体力消耗减少50%+4回合，神采+3</t>
+  </si>
+  <si>
+    <t>体力消耗减少50%+X1回合，神采+X2</t>
+  </si>
+  <si>
+    <t>补充营养</t>
+  </si>
+  <si>
+    <t>体力消耗减少1点，神采+5</t>
+  </si>
+  <si>
+    <t>体力消耗减少X1点，神采+X2</t>
+  </si>
+  <si>
+    <t>距离感</t>
+  </si>
+  <si>
+    <t>专注+4，体力回复4</t>
+  </si>
+  <si>
+    <t>专注+X1，体力回复X2点</t>
+  </si>
+  <si>
+    <t>亲切</t>
+  </si>
+  <si>
+    <t>亲和力+3，亲和力大于三层时，亲和力+2</t>
+  </si>
+  <si>
+    <t>亲和力+X1，亲和力大于三层时，亲和力+X2</t>
+  </si>
+  <si>
+    <t>最初的神降临</t>
+  </si>
+  <si>
+    <t>专注+1，以后每当打出A卡时，专注+1</t>
+  </si>
+  <si>
+    <t>专注+X1，以后每当打出A卡时，专注+1</t>
+  </si>
+  <si>
+    <t>迷人</t>
+  </si>
+  <si>
+    <t>亲和力+5，卡牌使用次数+1，获得亲和力90%的参数</t>
+  </si>
+  <si>
+    <t>亲和力+X1，手牌使用次数+X2，亲和力X3的参数获得</t>
+  </si>
+  <si>
+    <t>申请对线</t>
+  </si>
+  <si>
+    <t>红温+2，之后4回合内，回合结束时，参数+8</t>
+  </si>
+  <si>
+    <t>红温+X1，之后4回合内，回合结束时，参数+X2</t>
+  </si>
+  <si>
+    <t>子弹时间</t>
+  </si>
+  <si>
+    <t>专注+7，体力消耗增加+2回合，神采+7</t>
+  </si>
+  <si>
+    <t>专注+X1，体力消耗增加50%+X2回合，神采+X3</t>
+  </si>
+  <si>
+    <t>哭唧唧</t>
+  </si>
+  <si>
+    <t>流水+40，同接+30，舰长+1</t>
+  </si>
+  <si>
+    <t>流水+X1，同接+X2，舰长+X3</t>
+  </si>
+  <si>
+    <t>耶！</t>
+  </si>
+  <si>
+    <t>参数+10</t>
+  </si>
+  <si>
     <t>参数+X1</t>
   </si>
   <si>
-    <t>Basic</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>Stamina</t>
-  </si>
-  <si>
-    <t>喝水</t>
-  </si>
-  <si>
-    <t>神采+4</t>
-  </si>
-  <si>
-    <t>神采+X1</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>闪耀</t>
-  </si>
-  <si>
-    <t>参数+15，红温大于10层时，参数+9</t>
-  </si>
-  <si>
-    <t>参数+X1，红温大于10层时，参数+X2</t>
-  </si>
-  <si>
-    <t>Common</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>angry</t>
-  </si>
-  <si>
-    <t>战术喝水</t>
-  </si>
-  <si>
-    <t>参数+5，神采+4</t>
-  </si>
-  <si>
-    <t>参数+X1，神采+X2</t>
-  </si>
-  <si>
-    <t>kale</t>
-  </si>
-  <si>
-    <t>下一张使用的牌会使用两次，抽一张卡,神采+2</t>
-  </si>
-  <si>
-    <t>下一张使用的牌会使用两次，抽X3张卡,神采+X2</t>
-  </si>
-  <si>
-    <t>Epic</t>
-  </si>
-  <si>
-    <t>Buff</t>
-  </si>
-  <si>
-    <t>刷新</t>
-  </si>
-  <si>
-    <t>重抽其他手牌，卡牌使用次数+1，体力消耗减少50%+2回合</t>
-  </si>
-  <si>
-    <t>重抽其他手牌，卡牌使用次数+X3，体力消耗减少50%+X2回合</t>
-  </si>
-  <si>
-    <t>才八点</t>
-  </si>
-  <si>
-    <t>获得一个额外回合，神采+7，出牌次数+1</t>
-  </si>
-  <si>
-    <t>获得一个额外回合，神采+X1，出牌次数+X2</t>
-  </si>
-  <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>wink</t>
-  </si>
-  <si>
-    <t>亲和力+3，神采+2</t>
-  </si>
-  <si>
-    <t>亲和力+X1，神采+X2</t>
-  </si>
-  <si>
-    <t>集中</t>
-  </si>
-  <si>
-    <t>专注+2，神采+2</t>
-  </si>
-  <si>
-    <t>专注+X1，神采+X2</t>
-  </si>
-  <si>
-    <t>生气</t>
-  </si>
-  <si>
-    <t>红温+2，神采+2</t>
-  </si>
-  <si>
-    <t>红温+X1，神采+X2</t>
-  </si>
-  <si>
-    <t>二次推流</t>
-  </si>
-  <si>
-    <t>参数+9/2次</t>
-  </si>
-  <si>
-    <t>参数+X1/2次</t>
-  </si>
-  <si>
-    <t>加分动画显示需改进</t>
-  </si>
-  <si>
-    <t>才艺</t>
-  </si>
-  <si>
-    <t>参数+11，神采+7</t>
-  </si>
-  <si>
-    <t>Rare</t>
-  </si>
-  <si>
-    <t>小花花</t>
-  </si>
-  <si>
-    <t>亲和力+6</t>
-  </si>
-  <si>
-    <t>亲和力+X1</t>
-  </si>
-  <si>
-    <t>饭撒</t>
-  </si>
-  <si>
-    <t>获得亲和力140%的参数</t>
-  </si>
-  <si>
-    <t>获得亲和力X1的参数</t>
-  </si>
-  <si>
-    <t>desuwa</t>
-  </si>
-  <si>
-    <t>亲和力+4，获得亲和力层数80%的参数</t>
-  </si>
-  <si>
-    <t>亲和力+X1，获得亲和力层数X2的参数</t>
-  </si>
-  <si>
-    <t>欢迎上舰</t>
-  </si>
-  <si>
-    <t>舰长+1，神采+4，体力消耗减少+2回合</t>
-  </si>
-  <si>
-    <t>舰长+X1，神采+X2，体力消耗减少+X3回合</t>
-  </si>
-  <si>
-    <t>revenue</t>
-  </si>
-  <si>
-    <t>攻击弹幕</t>
-  </si>
-  <si>
-    <t>红温+5</t>
-  </si>
-  <si>
-    <t>红温+X1$红温变为1.5倍</t>
-  </si>
-  <si>
-    <t>神降临</t>
-  </si>
-  <si>
-    <t>专注+1，以后，每回合结束时，专注+2</t>
-  </si>
-  <si>
-    <t>点名弹幕</t>
-  </si>
-  <si>
-    <t>在有红温的状态下可使用，参数+24</t>
-  </si>
-  <si>
-    <t>激怒</t>
-  </si>
-  <si>
-    <t>体力消耗增加50%+2回合，参数+30，神采+5</t>
-  </si>
-  <si>
-    <t>美丽动人</t>
-  </si>
-  <si>
-    <t>亲和力+2，以后，每当使用M卡时，亲和力+1</t>
-  </si>
-  <si>
-    <t>小巧思</t>
-  </si>
-  <si>
-    <t>亲和力+5，神采+1</t>
-  </si>
-  <si>
-    <t>冲刺！</t>
-  </si>
-  <si>
-    <t>红温+3，参数+8</t>
-  </si>
-  <si>
-    <t>闭眼</t>
-  </si>
-  <si>
-    <t>专注+3</t>
-  </si>
-  <si>
-    <t>小憩</t>
-  </si>
-  <si>
-    <t>专注+3，神采+4</t>
-  </si>
-  <si>
-    <t>警告！</t>
-  </si>
-  <si>
-    <t>在红温的状态下可用，参数+12，红温大于10层时，参数+24，红温大于30层时，参数+36</t>
-  </si>
-  <si>
-    <t>躺</t>
-  </si>
-  <si>
-    <t>神采+6</t>
-  </si>
-  <si>
-    <t>fun</t>
-  </si>
-  <si>
-    <t>SC</t>
-  </si>
-  <si>
-    <t>沪币+30，神采+3，体力消耗减少+2回合</t>
-  </si>
-  <si>
-    <t>直播通知</t>
-  </si>
-  <si>
-    <t>同接+50，神采+2</t>
-  </si>
-  <si>
-    <t>YLG</t>
-  </si>
-  <si>
-    <t>同接+20，以后，每当打出A卡时，同接+10</t>
-  </si>
-  <si>
-    <t>爆米</t>
-  </si>
-  <si>
-    <t>获得同接数20%的流水</t>
-  </si>
-  <si>
-    <t>爆！</t>
-  </si>
-  <si>
-    <t>参数+38，红温大于30层时，卡牌使用次数+1</t>
-  </si>
-  <si>
-    <t>越想越气</t>
-  </si>
-  <si>
-    <t>红温+2，有红温的状态下，红温+2，红温大于30层时，红温+4</t>
-  </si>
-  <si>
-    <t>为我欢呼</t>
-  </si>
-  <si>
-    <t>幽默+1，以后每当使用M卡时，幽默+1</t>
-  </si>
-  <si>
-    <t>红温+3，神采+6</t>
-  </si>
-  <si>
-    <t>观察</t>
-  </si>
-  <si>
-    <t>专注+3，神采+6</t>
-  </si>
-  <si>
-    <t>首页推送</t>
-  </si>
-  <si>
-    <t>体力消耗减少50%+4回合，神采+3</t>
-  </si>
-  <si>
-    <t>补充营养</t>
-  </si>
-  <si>
-    <t>体力消耗减少1点，神采+5</t>
-  </si>
-  <si>
-    <t>距离感</t>
-  </si>
-  <si>
-    <t>专注+4，体力回复4</t>
-  </si>
-  <si>
-    <t>亲切</t>
-  </si>
-  <si>
-    <t>亲和力+3，亲和力大于三层时，亲和力+2</t>
-  </si>
-  <si>
-    <t>最初的神降临</t>
-  </si>
-  <si>
-    <t>专注+1，以后每当打出A卡时，专注+1</t>
-  </si>
-  <si>
-    <t>迷人</t>
-  </si>
-  <si>
-    <t>亲和力+5，卡牌使用次数+1，获得亲和力90%的参数</t>
-  </si>
-  <si>
-    <t>申请对线</t>
-  </si>
-  <si>
-    <t>红温+2，之后4回合内，回合结束时，参数+8</t>
-  </si>
-  <si>
-    <t>子弹时间</t>
-  </si>
-  <si>
-    <t>专注+7，体力消耗增加+2回合，神采+7</t>
-  </si>
-  <si>
-    <t>哭唧唧</t>
-  </si>
-  <si>
-    <t>流水+40，同接+30，舰长+1</t>
-  </si>
-  <si>
-    <t>耶！</t>
-  </si>
-  <si>
-    <t>参数+10</t>
-  </si>
-  <si>
     <t>参数+8，亲和力+3</t>
   </si>
   <si>
+    <t>参数+X1，亲和力+X2</t>
+  </si>
+  <si>
     <t>玩梗</t>
   </si>
   <si>
     <t>参数+7，幽默+2</t>
   </si>
   <si>
+    <t>参数+X1，幽默+X2</t>
+  </si>
+  <si>
     <t>盯~</t>
   </si>
   <si>
     <t>亲和力+5，获得亲和力110%的参数</t>
   </si>
   <si>
+    <t>亲和力+X1，获得亲和力X2的参数</t>
+  </si>
+  <si>
     <t>氛围感</t>
   </si>
   <si>
     <t>亲和力+1，以后，回合结束时，亲和力+3</t>
   </si>
   <si>
+    <t>亲和力+X1，以后，回合结束时，亲和力+3</t>
+  </si>
+  <si>
     <t>拿个快递</t>
   </si>
   <si>
     <t>抽两张牌，体力消耗减少+2回合</t>
   </si>
   <si>
+    <t>抽X1张牌，体力消耗减少50%+X2回合</t>
+  </si>
+  <si>
     <t>点炮仗</t>
   </si>
   <si>
     <t>红温&gt;10层时可使用，获得红温300%的参数，红温减少50%</t>
   </si>
   <si>
+    <t>红温&gt;10层时可使用，获得红温X1的参数，红温减少X2</t>
+  </si>
+  <si>
     <t>逼逼赖赖</t>
   </si>
   <si>
     <t>红温+3，卡牌使用次数+1，如果红温大于10层，红温+3</t>
   </si>
   <si>
+    <t>红温+X1，卡牌使用次数+X2，如果红温大于10层，红温+X2</t>
+  </si>
+  <si>
     <t>雷区</t>
   </si>
   <si>
     <t>红温+1，以后每当使用A卡的时候，红温+1</t>
   </si>
   <si>
+    <t>红温+X1，以后每当使用A卡的时候，红温+1</t>
+  </si>
+  <si>
     <t>自洽</t>
   </si>
   <si>
     <t>幽默+3，参数+12，卡牌使用次数+1</t>
   </si>
   <si>
+    <t>幽默+X1，参数+X2，卡牌使用次数+X</t>
+  </si>
+  <si>
     <t>封禁</t>
   </si>
   <si>
     <t>神采+5两次，获得神采70%的参数</t>
   </si>
   <si>
+    <t>神采+X1两次，获得神采X2的参数</t>
+  </si>
+  <si>
     <t>节目效果</t>
   </si>
   <si>
     <t>获得神采120%的参数</t>
   </si>
   <si>
+    <t>获得神采X1%的参数</t>
+  </si>
+  <si>
+    <t>TureStamina</t>
+  </si>
+  <si>
     <t>LLBC</t>
   </si>
   <si>
     <t>神采+7，获得神采90%的参数</t>
   </si>
   <si>
+    <t>神采+X1，获得神采X2%的参数</t>
+  </si>
+  <si>
     <t>大爆特爆</t>
   </si>
   <si>
     <t>消耗所有神采，获得消耗神采300%的参数</t>
   </si>
   <si>
+    <t>消耗所有神采，获得消耗神采X1的参数</t>
+  </si>
+  <si>
     <t>冷笑话</t>
   </si>
   <si>
-    <t>获得神采100%的参数，下一回合抽一张卡牌</t>
+    <t>获得神采120%的参数，下一回合抽一张卡牌</t>
+  </si>
+  <si>
+    <t>获得神采X1%的参数，下一回合抽一张卡牌</t>
   </si>
   <si>
     <t>Parameter</t>
@@ -903,6 +1017,15 @@
   </si>
   <si>
     <t>回合结束时，幽默+1</t>
+  </si>
+  <si>
+    <t>获得神采X%的参数</t>
+  </si>
+  <si>
+    <t>VAddParamAttributePercentageEffect</t>
+  </si>
+  <si>
+    <t>神采变为X%</t>
   </si>
   <si>
     <t>BuffType</t>
@@ -1218,12 +1341,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1566,7 +1695,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1590,16 +1719,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1608,100 +1737,101 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2048,8 +2178,7 @@
     <col min="12" max="12" width="7.14166666666667" customWidth="1"/>
     <col min="13" max="13" width="14" style="3" customWidth="1"/>
     <col min="14" max="14" width="10.2833333333333" customWidth="1"/>
-    <col min="15" max="15" width="13.7083333333333" customWidth="1"/>
-    <col min="16" max="16" width="13.7083333333333" customWidth="1"/>
+    <col min="15" max="16" width="13.7083333333333" customWidth="1"/>
     <col min="17" max="17" width="9.70833333333333" style="3" customWidth="1"/>
     <col min="18" max="18" width="9.70833333333333" customWidth="1"/>
     <col min="19" max="19" width="12.1416666666667" customWidth="1"/>
@@ -2225,7 +2354,7 @@
       <c r="AC2"/>
       <c r="AE2"/>
       <c r="AG2"/>
-      <c r="AH2" s="5"/>
+      <c r="AH2" s="6"/>
     </row>
     <row r="3" spans="1:34">
       <c r="A3">
@@ -2280,7 +2409,7 @@
       <c r="AC3"/>
       <c r="AE3"/>
       <c r="AG3"/>
-      <c r="AH3" s="5"/>
+      <c r="AH3" s="6"/>
     </row>
     <row r="4" spans="1:34">
       <c r="A4">
@@ -2340,7 +2469,7 @@
       <c r="W4" s="3">
         <v>12</v>
       </c>
-      <c r="AH4" s="5"/>
+      <c r="AH4" s="6"/>
     </row>
     <row r="5" spans="1:34">
       <c r="A5">
@@ -2403,7 +2532,7 @@
       <c r="AC5"/>
       <c r="AE5"/>
       <c r="AG5"/>
-      <c r="AH5" s="5"/>
+      <c r="AH5" s="6"/>
     </row>
     <row r="6" spans="1:34">
       <c r="A6">
@@ -2469,7 +2598,7 @@
       <c r="Z6" s="3">
         <v>1</v>
       </c>
-      <c r="AH6" s="5"/>
+      <c r="AH6" s="6"/>
     </row>
     <row r="7" spans="1:34">
       <c r="A7">
@@ -2535,7 +2664,7 @@
       <c r="AC7"/>
       <c r="AE7"/>
       <c r="AG7"/>
-      <c r="AH7" s="5"/>
+      <c r="AH7" s="6"/>
     </row>
     <row r="8" spans="1:34">
       <c r="A8">
@@ -2608,7 +2737,7 @@
       <c r="AC8"/>
       <c r="AE8"/>
       <c r="AG8"/>
-      <c r="AH8" s="5"/>
+      <c r="AH8" s="6"/>
     </row>
     <row r="9" spans="1:34">
       <c r="A9">
@@ -2671,7 +2800,7 @@
       <c r="AC9"/>
       <c r="AE9"/>
       <c r="AG9"/>
-      <c r="AH9" s="5"/>
+      <c r="AH9" s="6"/>
     </row>
     <row r="10" spans="1:34">
       <c r="A10">
@@ -2734,7 +2863,7 @@
       <c r="AC10"/>
       <c r="AE10"/>
       <c r="AG10"/>
-      <c r="AH10" s="5"/>
+      <c r="AH10" s="6"/>
     </row>
     <row r="11" spans="1:34">
       <c r="A11">
@@ -2794,7 +2923,7 @@
       <c r="W11" s="3">
         <v>3</v>
       </c>
-      <c r="AH11" s="5"/>
+      <c r="AH11" s="6"/>
     </row>
     <row r="12" spans="1:35">
       <c r="A12">
@@ -2857,7 +2986,7 @@
       <c r="AC12"/>
       <c r="AE12"/>
       <c r="AG12"/>
-      <c r="AH12" s="5"/>
+      <c r="AH12" s="6"/>
       <c r="AI12" t="s">
         <v>78</v>
       </c>
@@ -2923,7 +3052,7 @@
       <c r="AC13"/>
       <c r="AE13"/>
       <c r="AG13"/>
-      <c r="AH13" s="5"/>
+      <c r="AH13" s="6"/>
     </row>
     <row r="14" spans="1:34">
       <c r="A14">
@@ -2978,7 +3107,7 @@
       <c r="AC14"/>
       <c r="AE14"/>
       <c r="AG14"/>
-      <c r="AH14" s="5"/>
+      <c r="AH14" s="6"/>
     </row>
     <row r="15" spans="1:34">
       <c r="A15">
@@ -3033,7 +3162,7 @@
       <c r="AC15"/>
       <c r="AE15"/>
       <c r="AG15"/>
-      <c r="AH15" s="5"/>
+      <c r="AH15" s="6"/>
     </row>
     <row r="16" spans="1:34">
       <c r="A16">
@@ -3096,7 +3225,7 @@
       <c r="AC16"/>
       <c r="AE16"/>
       <c r="AG16"/>
-      <c r="AH16" s="5"/>
+      <c r="AH16" s="6"/>
     </row>
     <row r="17" spans="1:34">
       <c r="A17">
@@ -3170,7 +3299,7 @@
       <c r="AC17"/>
       <c r="AE17"/>
       <c r="AG17"/>
-      <c r="AH17" s="6"/>
+      <c r="AH17" s="7"/>
     </row>
     <row r="18" spans="1:34">
       <c r="A18">
@@ -3227,7 +3356,7 @@
       <c r="AE18" s="3">
         <v>1.5</v>
       </c>
-      <c r="AH18" s="5"/>
+      <c r="AH18" s="6"/>
     </row>
     <row r="19" spans="1:34">
       <c r="A19">
@@ -3240,7 +3369,7 @@
         <v>99</v>
       </c>
       <c r="D19" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>57</v>
@@ -3290,20 +3419,20 @@
       <c r="AC19"/>
       <c r="AE19"/>
       <c r="AG19"/>
-      <c r="AH19" s="5"/>
+      <c r="AH19" s="6"/>
     </row>
     <row r="20" spans="1:34">
       <c r="A20">
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C20" t="s">
-        <v>101</v>
-      </c>
-      <c r="D20" t="s">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>103</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>48</v>
@@ -3350,20 +3479,20 @@
       <c r="AE20" s="3">
         <v>7</v>
       </c>
-      <c r="AH20" s="6"/>
+      <c r="AH20" s="7"/>
     </row>
     <row r="21" spans="1:34">
       <c r="A21">
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>81</v>
@@ -3419,20 +3548,20 @@
       <c r="Z21" s="3">
         <v>7</v>
       </c>
-      <c r="AH21" s="5"/>
+      <c r="AH21" s="6"/>
     </row>
     <row r="22" spans="1:34">
       <c r="A22">
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D22" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>81</v>
@@ -3482,20 +3611,20 @@
       <c r="AC22"/>
       <c r="AE22"/>
       <c r="AG22"/>
-      <c r="AH22" s="5"/>
+      <c r="AH22" s="6"/>
     </row>
     <row r="23" spans="1:34">
       <c r="A23">
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C23" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D23" t="s">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>81</v>
@@ -3545,20 +3674,20 @@
       <c r="AC23"/>
       <c r="AE23"/>
       <c r="AG23"/>
-      <c r="AH23" s="5"/>
+      <c r="AH23" s="6"/>
     </row>
     <row r="24" spans="1:34">
       <c r="A24">
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C24" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D24" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>48</v>
@@ -3611,20 +3740,20 @@
       <c r="AE24" s="3">
         <v>3</v>
       </c>
-      <c r="AH24" s="5"/>
+      <c r="AH24" s="6"/>
     </row>
     <row r="25" spans="1:34">
       <c r="A25">
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C25" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D25" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>48</v>
@@ -3666,20 +3795,20 @@
       <c r="AC25"/>
       <c r="AE25"/>
       <c r="AG25"/>
-      <c r="AH25" s="5"/>
+      <c r="AH25" s="6"/>
     </row>
     <row r="26" spans="1:34">
       <c r="A26">
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C26" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D26" t="s">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>48</v>
@@ -3729,20 +3858,20 @@
       <c r="AC26"/>
       <c r="AE26"/>
       <c r="AG26"/>
-      <c r="AH26" s="5"/>
+      <c r="AH26" s="6"/>
     </row>
     <row r="27" spans="1:34">
       <c r="A27">
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D27" t="s">
-        <v>115</v>
+        <v>121</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>122</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>57</v>
@@ -3801,20 +3930,20 @@
       <c r="Z27" s="3">
         <v>44</v>
       </c>
-      <c r="AH27" s="6"/>
+      <c r="AH27" s="7"/>
     </row>
     <row r="28" spans="1:34">
       <c r="A28">
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C28" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D28" t="s">
-        <v>117</v>
+        <v>43</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>48</v>
@@ -3826,7 +3955,7 @@
         <v>49</v>
       </c>
       <c r="H28" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="J28" t="s">
         <v>40</v>
@@ -3858,20 +3987,20 @@
       <c r="AE28" s="3">
         <v>12</v>
       </c>
-      <c r="AH28" s="5"/>
+      <c r="AH28" s="6"/>
     </row>
     <row r="29" spans="1:34">
       <c r="A29">
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C29" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="D29" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>81</v>
@@ -3932,20 +4061,20 @@
       <c r="AC29"/>
       <c r="AE29"/>
       <c r="AG29"/>
-      <c r="AH29" s="5"/>
+      <c r="AH29" s="6"/>
     </row>
     <row r="30" spans="1:34">
       <c r="A30">
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="C30" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="D30" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>81</v>
@@ -3998,20 +4127,20 @@
       <c r="AC30"/>
       <c r="AE30"/>
       <c r="AG30"/>
-      <c r="AH30" s="6"/>
+      <c r="AH30" s="7"/>
     </row>
     <row r="31" spans="1:34">
       <c r="A31">
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="C31" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="D31" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>57</v>
@@ -4064,20 +4193,20 @@
       <c r="AC31"/>
       <c r="AE31"/>
       <c r="AG31"/>
-      <c r="AH31" s="6"/>
+      <c r="AH31" s="7"/>
     </row>
     <row r="32" spans="1:33">
       <c r="A32">
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="C32" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="D32" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>57</v>
@@ -4120,13 +4249,13 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="C33" t="s">
-        <v>128</v>
-      </c>
-      <c r="D33" t="s">
-        <v>128</v>
+        <v>138</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>139</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>57</v>
@@ -4176,13 +4305,13 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C34" t="s">
-        <v>130</v>
-      </c>
-      <c r="D34" t="s">
-        <v>130</v>
+        <v>141</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>142</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>81</v>
@@ -4229,13 +4358,13 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C35" t="s">
-        <v>132</v>
-      </c>
-      <c r="D35" t="s">
-        <v>132</v>
+        <v>144</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>81</v>
@@ -4247,7 +4376,7 @@
         <v>49</v>
       </c>
       <c r="H35" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="J35" t="s">
         <v>40</v>
@@ -4278,14 +4407,14 @@
       <c r="A36">
         <v>37</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B36" s="5">
         <v>144</v>
       </c>
       <c r="C36" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="D36" t="s">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>81</v>
@@ -4338,13 +4467,13 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="C37" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="D37" t="s">
-        <v>135</v>
+        <v>71</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>81</v>
@@ -4400,13 +4529,13 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="C38" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D38" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>57</v>
@@ -4462,13 +4591,13 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="C39" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="D39" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>57</v>
@@ -4524,13 +4653,13 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="C40" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="D40" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>57</v>
@@ -4586,13 +4715,13 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="C41" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="D41" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>48</v>
@@ -4648,13 +4777,13 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="C42" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="D42" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>81</v>
@@ -4710,13 +4839,13 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="C43" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="D43" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>81</v>
@@ -4780,13 +4909,13 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="C44" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="D44" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>81</v>
@@ -4839,13 +4968,13 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="C45" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="D45" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>81</v>
@@ -4909,13 +5038,13 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="C46" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="D46" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>57</v>
@@ -4982,13 +5111,13 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="C47" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="D47" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>48</v>
@@ -5039,10 +5168,10 @@
         <v>123</v>
       </c>
       <c r="C48" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="D48" t="s">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>48</v>
@@ -5098,13 +5227,13 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="C49" t="s">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="D49" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>48</v>
@@ -5116,7 +5245,7 @@
         <v>49</v>
       </c>
       <c r="H49" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="J49" t="s">
         <v>40</v>
@@ -5157,13 +5286,13 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="C50" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="D50" t="s">
-        <v>160</v>
+        <v>186</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>57</v>
@@ -5219,13 +5348,13 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>161</v>
+        <v>187</v>
       </c>
       <c r="C51" t="s">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="D51" t="s">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>57</v>
@@ -5281,13 +5410,13 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="C52" t="s">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="D52" t="s">
-        <v>164</v>
+        <v>192</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>81</v>
@@ -5343,13 +5472,13 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>165</v>
+        <v>193</v>
       </c>
       <c r="C53" t="s">
-        <v>166</v>
+        <v>194</v>
       </c>
       <c r="D53" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>57</v>
@@ -5405,13 +5534,13 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>167</v>
+        <v>196</v>
       </c>
       <c r="C54" t="s">
-        <v>168</v>
+        <v>197</v>
       </c>
       <c r="D54" t="s">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>81</v>
@@ -5476,13 +5605,13 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="C55" t="s">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="D55" t="s">
-        <v>170</v>
+        <v>201</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>81</v>
@@ -5536,13 +5665,13 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="C56" t="s">
-        <v>172</v>
+        <v>203</v>
       </c>
       <c r="D56" t="s">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>81</v>
@@ -5554,7 +5683,7 @@
         <v>49</v>
       </c>
       <c r="H56" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="J56" t="s">
         <v>58</v>
@@ -5603,18 +5732,18 @@
       </c>
       <c r="AF56" s="3"/>
     </row>
-    <row r="57" spans="1:23">
+    <row r="57" spans="1:26">
       <c r="A57">
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="C57" t="s">
-        <v>174</v>
-      </c>
-      <c r="D57" t="s">
-        <v>174</v>
+        <v>206</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>207</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>57</v>
@@ -5626,7 +5755,7 @@
         <v>49</v>
       </c>
       <c r="H57" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="J57" t="s">
         <v>58</v>
@@ -5664,19 +5793,28 @@
       <c r="W57" s="3">
         <v>6</v>
       </c>
-    </row>
-    <row r="58" spans="1:15">
+      <c r="X57">
+        <v>66</v>
+      </c>
+      <c r="Y57">
+        <v>0.6</v>
+      </c>
+      <c r="Z57" s="3">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20">
       <c r="A58">
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="C58" t="s">
-        <v>176</v>
-      </c>
-      <c r="D58" t="s">
-        <v>176</v>
+        <v>209</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>210</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>48</v>
@@ -5688,10 +5826,10 @@
         <v>49</v>
       </c>
       <c r="H58" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="J58" t="s">
-        <v>40</v>
+        <v>211</v>
       </c>
       <c r="L58">
         <v>3</v>
@@ -5705,19 +5843,28 @@
       <c r="O58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:20">
+      <c r="R58">
+        <v>66</v>
+      </c>
+      <c r="S58">
+        <v>1.2</v>
+      </c>
+      <c r="T58" s="3">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23">
       <c r="A59">
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="C59" t="s">
-        <v>178</v>
-      </c>
-      <c r="D59" t="s">
-        <v>178</v>
+        <v>213</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>214</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>81</v>
@@ -5729,13 +5876,13 @@
         <v>49</v>
       </c>
       <c r="H59" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="J59" t="s">
-        <v>40</v>
+        <v>211</v>
       </c>
       <c r="L59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M59" s="3">
         <v>3</v>
@@ -5755,19 +5902,28 @@
       <c r="T59" s="3">
         <v>9</v>
       </c>
-    </row>
-    <row r="60" spans="1:15">
+      <c r="U59">
+        <v>66</v>
+      </c>
+      <c r="V59">
+        <v>0.9</v>
+      </c>
+      <c r="W59" s="3">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23">
       <c r="A60">
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>179</v>
+        <v>215</v>
       </c>
       <c r="C60" t="s">
-        <v>180</v>
+        <v>216</v>
       </c>
       <c r="D60" t="s">
-        <v>180</v>
+        <v>217</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>57</v>
@@ -5779,10 +5935,10 @@
         <v>49</v>
       </c>
       <c r="H60" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="J60" t="s">
-        <v>40</v>
+        <v>211</v>
       </c>
       <c r="L60">
         <v>2</v>
@@ -5796,19 +5952,37 @@
       <c r="O60">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:15">
+      <c r="R60">
+        <v>66</v>
+      </c>
+      <c r="S60">
+        <v>3</v>
+      </c>
+      <c r="T60" s="3">
+        <v>4</v>
+      </c>
+      <c r="U60">
+        <v>67</v>
+      </c>
+      <c r="V60">
+        <v>-1</v>
+      </c>
+      <c r="W60" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23">
       <c r="A61">
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="C61" t="s">
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="D61" t="s">
-        <v>182</v>
+        <v>220</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>81</v>
@@ -5820,7 +5994,7 @@
         <v>49</v>
       </c>
       <c r="H61" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="J61" t="s">
         <v>58</v>
@@ -5829,7 +6003,7 @@
         <v>14</v>
       </c>
       <c r="L61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M61" s="3">
         <v>2</v>
@@ -5838,6 +6012,24 @@
         <v>0</v>
       </c>
       <c r="O61">
+        <v>1</v>
+      </c>
+      <c r="R61">
+        <v>66</v>
+      </c>
+      <c r="S61">
+        <v>1.2</v>
+      </c>
+      <c r="T61" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="U61">
+        <v>62</v>
+      </c>
+      <c r="V61">
+        <v>1</v>
+      </c>
+      <c r="W61" s="3">
         <v>1</v>
       </c>
     </row>
@@ -5851,7 +6043,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
@@ -5879,19 +6071,19 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
-        <v>183</v>
+        <v>221</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>184</v>
+        <v>222</v>
       </c>
       <c r="G1" t="s">
-        <v>185</v>
+        <v>223</v>
       </c>
       <c r="H1" t="s">
-        <v>186</v>
+        <v>224</v>
       </c>
       <c r="I1" t="s">
-        <v>187</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5899,13 +6091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>188</v>
+        <v>226</v>
       </c>
       <c r="C2" t="s">
-        <v>188</v>
+        <v>226</v>
       </c>
       <c r="D2" t="s">
-        <v>189</v>
+        <v>227</v>
       </c>
       <c r="I2">
         <v>-1</v>
@@ -5916,19 +6108,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>190</v>
+        <v>228</v>
       </c>
       <c r="C3" t="s">
-        <v>191</v>
+        <v>229</v>
       </c>
       <c r="D3" t="s">
-        <v>192</v>
+        <v>230</v>
       </c>
       <c r="E3" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
       <c r="F3" t="s">
-        <v>194</v>
+        <v>232</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -5939,16 +6131,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>195</v>
+        <v>233</v>
       </c>
       <c r="C4" t="s">
-        <v>196</v>
+        <v>234</v>
       </c>
       <c r="D4" t="s">
-        <v>192</v>
+        <v>230</v>
       </c>
       <c r="E4" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -5959,16 +6151,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="C5" t="s">
-        <v>199</v>
+        <v>237</v>
       </c>
       <c r="D5" t="s">
-        <v>192</v>
+        <v>230</v>
       </c>
       <c r="E5" t="s">
-        <v>200</v>
+        <v>238</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -5979,13 +6171,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>201</v>
+        <v>239</v>
       </c>
       <c r="C6" t="s">
-        <v>202</v>
+        <v>240</v>
       </c>
       <c r="D6" t="s">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -5996,16 +6188,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>204</v>
+        <v>242</v>
       </c>
       <c r="C7" t="s">
-        <v>204</v>
+        <v>242</v>
       </c>
       <c r="D7" t="s">
-        <v>205</v>
+        <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>206</v>
+        <v>244</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -6016,13 +6208,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>207</v>
+        <v>245</v>
       </c>
       <c r="C8" t="s">
-        <v>207</v>
+        <v>245</v>
       </c>
       <c r="D8" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -6036,13 +6228,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>209</v>
+        <v>247</v>
       </c>
       <c r="C9" t="s">
-        <v>209</v>
+        <v>247</v>
       </c>
       <c r="D9" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -6056,13 +6248,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>210</v>
+        <v>248</v>
       </c>
       <c r="C10" t="s">
-        <v>210</v>
+        <v>248</v>
       </c>
       <c r="D10" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -6076,13 +6268,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>211</v>
+        <v>249</v>
       </c>
       <c r="C11" t="s">
-        <v>211</v>
+        <v>249</v>
       </c>
       <c r="D11" t="s">
-        <v>212</v>
+        <v>250</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -6093,16 +6285,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>213</v>
+        <v>251</v>
       </c>
       <c r="C12" t="s">
-        <v>213</v>
+        <v>251</v>
       </c>
       <c r="D12" t="s">
-        <v>214</v>
+        <v>252</v>
       </c>
       <c r="E12" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -6113,16 +6305,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>216</v>
+        <v>254</v>
       </c>
       <c r="C13" t="s">
-        <v>217</v>
+        <v>255</v>
       </c>
       <c r="D13" t="s">
-        <v>192</v>
+        <v>230</v>
       </c>
       <c r="E13" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -6133,19 +6325,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>218</v>
+        <v>256</v>
       </c>
       <c r="C14" t="s">
-        <v>219</v>
+        <v>257</v>
       </c>
       <c r="D14" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>194</v>
+        <v>232</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -6156,16 +6348,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>220</v>
+        <v>258</v>
       </c>
       <c r="C15" t="s">
-        <v>220</v>
+        <v>258</v>
       </c>
       <c r="D15" t="s">
-        <v>221</v>
+        <v>259</v>
       </c>
       <c r="E15" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -6176,16 +6368,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>222</v>
+        <v>260</v>
       </c>
       <c r="C16" t="s">
-        <v>222</v>
+        <v>260</v>
       </c>
       <c r="D16" t="s">
-        <v>192</v>
+        <v>230</v>
       </c>
       <c r="E16" t="s">
-        <v>223</v>
+        <v>261</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -6196,13 +6388,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>224</v>
+        <v>262</v>
       </c>
       <c r="C17" t="s">
-        <v>224</v>
+        <v>262</v>
       </c>
       <c r="D17" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -6216,16 +6408,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>225</v>
+        <v>263</v>
       </c>
       <c r="C18" t="s">
-        <v>225</v>
+        <v>263</v>
       </c>
       <c r="D18" t="s">
-        <v>226</v>
+        <v>264</v>
       </c>
       <c r="E18" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -6236,13 +6428,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>227</v>
+        <v>265</v>
       </c>
       <c r="C19" t="s">
-        <v>227</v>
+        <v>265</v>
       </c>
       <c r="D19" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -6256,13 +6448,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>228</v>
+        <v>266</v>
       </c>
       <c r="C20" t="s">
-        <v>228</v>
+        <v>266</v>
       </c>
       <c r="D20" t="s">
-        <v>229</v>
+        <v>267</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -6276,16 +6468,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
+        <v>268</v>
+      </c>
+      <c r="C21" t="s">
+        <v>268</v>
+      </c>
+      <c r="D21" t="s">
         <v>230</v>
       </c>
-      <c r="C21" t="s">
-        <v>230</v>
-      </c>
-      <c r="D21" t="s">
-        <v>192</v>
-      </c>
       <c r="E21" t="s">
-        <v>231</v>
+        <v>269</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -6296,16 +6488,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="C22" t="s">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="D22" t="s">
-        <v>205</v>
+        <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>233</v>
+        <v>271</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -6316,13 +6508,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>234</v>
+        <v>272</v>
       </c>
       <c r="C23" t="s">
-        <v>234</v>
+        <v>272</v>
       </c>
       <c r="D23" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="E23">
         <v>5</v>
@@ -6336,19 +6528,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>235</v>
+        <v>273</v>
       </c>
       <c r="C24" t="s">
-        <v>235</v>
+        <v>273</v>
       </c>
       <c r="D24" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>194</v>
+        <v>232</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -6359,13 +6551,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>236</v>
+        <v>274</v>
       </c>
       <c r="C25" t="s">
-        <v>236</v>
+        <v>274</v>
       </c>
       <c r="D25" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -6379,16 +6571,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>237</v>
+        <v>275</v>
       </c>
       <c r="C26" t="s">
-        <v>237</v>
+        <v>275</v>
       </c>
       <c r="D26" t="s">
-        <v>192</v>
+        <v>230</v>
       </c>
       <c r="E26" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -6402,16 +6594,16 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>238</v>
+        <v>276</v>
       </c>
       <c r="C27" t="s">
-        <v>238</v>
+        <v>276</v>
       </c>
       <c r="D27" t="s">
-        <v>205</v>
+        <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>233</v>
+        <v>271</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -6422,13 +6614,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>239</v>
+        <v>277</v>
       </c>
       <c r="C28" t="s">
-        <v>239</v>
+        <v>277</v>
       </c>
       <c r="D28" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -6442,19 +6634,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>240</v>
+        <v>278</v>
       </c>
       <c r="C29" t="s">
-        <v>240</v>
+        <v>278</v>
       </c>
       <c r="D29" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>241</v>
+        <v>279</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -6468,13 +6660,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>242</v>
+        <v>280</v>
       </c>
       <c r="C30" t="s">
-        <v>243</v>
+        <v>281</v>
       </c>
       <c r="D30" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -6488,19 +6680,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>244</v>
+        <v>282</v>
       </c>
       <c r="C31" t="s">
-        <v>244</v>
+        <v>282</v>
       </c>
       <c r="D31" t="s">
-        <v>192</v>
+        <v>230</v>
       </c>
       <c r="E31" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
       <c r="F31" t="s">
-        <v>245</v>
+        <v>283</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -6511,19 +6703,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
+        <v>284</v>
+      </c>
+      <c r="C32" t="s">
+        <v>284</v>
+      </c>
+      <c r="D32" t="s">
         <v>246</v>
-      </c>
-      <c r="C32" t="s">
-        <v>246</v>
-      </c>
-      <c r="D32" t="s">
-        <v>208</v>
       </c>
       <c r="E32">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>245</v>
+        <v>283</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -6534,19 +6726,19 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>247</v>
+        <v>285</v>
       </c>
       <c r="C33" t="s">
-        <v>247</v>
+        <v>285</v>
       </c>
       <c r="D33" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="E33">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>245</v>
+        <v>283</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -6557,16 +6749,16 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>248</v>
+        <v>286</v>
       </c>
       <c r="C34" t="s">
-        <v>248</v>
+        <v>286</v>
       </c>
       <c r="D34" t="s">
-        <v>192</v>
+        <v>230</v>
       </c>
       <c r="E34" t="s">
-        <v>249</v>
+        <v>287</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -6577,16 +6769,16 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>250</v>
+        <v>288</v>
       </c>
       <c r="C35" t="s">
-        <v>250</v>
+        <v>288</v>
       </c>
       <c r="D35" t="s">
-        <v>192</v>
+        <v>230</v>
       </c>
       <c r="E35" t="s">
-        <v>251</v>
+        <v>289</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -6597,19 +6789,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>252</v>
+        <v>290</v>
       </c>
       <c r="C36" t="s">
-        <v>252</v>
+        <v>290</v>
       </c>
       <c r="D36" t="s">
-        <v>192</v>
+        <v>230</v>
       </c>
       <c r="E36" t="s">
-        <v>251</v>
+        <v>289</v>
       </c>
       <c r="F36" t="s">
-        <v>241</v>
+        <v>279</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -6623,13 +6815,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>253</v>
+        <v>291</v>
       </c>
       <c r="C37" t="s">
-        <v>254</v>
+        <v>292</v>
       </c>
       <c r="D37" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="E37">
         <v>11</v>
@@ -6643,16 +6835,16 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>255</v>
+        <v>293</v>
       </c>
       <c r="C38" t="s">
-        <v>255</v>
+        <v>293</v>
       </c>
       <c r="D38" t="s">
-        <v>192</v>
+        <v>230</v>
       </c>
       <c r="E38" t="s">
-        <v>249</v>
+        <v>287</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -6663,13 +6855,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>256</v>
+        <v>294</v>
       </c>
       <c r="C39" t="s">
-        <v>256</v>
+        <v>294</v>
       </c>
       <c r="D39" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -6686,16 +6878,16 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>257</v>
+        <v>295</v>
       </c>
       <c r="C40" t="s">
-        <v>258</v>
+        <v>296</v>
       </c>
       <c r="D40" t="s">
-        <v>192</v>
+        <v>230</v>
       </c>
       <c r="E40" t="s">
-        <v>259</v>
+        <v>297</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -6706,13 +6898,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>260</v>
+        <v>298</v>
       </c>
       <c r="C41" t="s">
-        <v>260</v>
+        <v>298</v>
       </c>
       <c r="D41" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -6729,19 +6921,19 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>261</v>
+        <v>299</v>
       </c>
       <c r="C42" t="s">
-        <v>261</v>
+        <v>299</v>
       </c>
       <c r="D42" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>241</v>
+        <v>279</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -6755,13 +6947,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>262</v>
+        <v>300</v>
       </c>
       <c r="C43" t="s">
-        <v>262</v>
+        <v>300</v>
       </c>
       <c r="D43" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="E43">
         <v>12</v>
@@ -6775,13 +6967,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>263</v>
+        <v>301</v>
       </c>
       <c r="C44" t="s">
-        <v>263</v>
+        <v>301</v>
       </c>
       <c r="D44" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="E44">
         <v>13</v>
@@ -6795,19 +6987,19 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>264</v>
+        <v>302</v>
       </c>
       <c r="C45" t="s">
-        <v>190</v>
+        <v>228</v>
       </c>
       <c r="D45" t="s">
-        <v>192</v>
+        <v>230</v>
       </c>
       <c r="E45" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
       <c r="F45" t="s">
-        <v>194</v>
+        <v>232</v>
       </c>
       <c r="I45">
         <v>-1</v>
@@ -6818,16 +7010,16 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>265</v>
+        <v>303</v>
       </c>
       <c r="C46" t="s">
-        <v>265</v>
+        <v>303</v>
       </c>
       <c r="D46" t="s">
-        <v>226</v>
+        <v>264</v>
       </c>
       <c r="E46" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="I46">
         <v>1</v>
@@ -6838,13 +7030,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>266</v>
+        <v>304</v>
       </c>
       <c r="C47" t="s">
-        <v>266</v>
+        <v>304</v>
       </c>
       <c r="D47" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="E47">
         <v>14</v>
@@ -6858,19 +7050,19 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>267</v>
+        <v>305</v>
       </c>
       <c r="C48" t="s">
-        <v>267</v>
+        <v>305</v>
       </c>
       <c r="D48" t="s">
-        <v>268</v>
+        <v>306</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>194</v>
+        <v>232</v>
       </c>
       <c r="I48">
         <v>-1</v>
@@ -6881,13 +7073,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>269</v>
+        <v>307</v>
       </c>
       <c r="C49" t="s">
-        <v>269</v>
+        <v>307</v>
       </c>
       <c r="D49" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="E49">
         <v>15</v>
@@ -6901,19 +7093,19 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>270</v>
+        <v>308</v>
       </c>
       <c r="C50" t="s">
-        <v>270</v>
+        <v>308</v>
       </c>
       <c r="D50" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>194</v>
+        <v>232</v>
       </c>
       <c r="I50">
         <v>-1</v>
@@ -6924,13 +7116,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>271</v>
+        <v>309</v>
       </c>
       <c r="C51" t="s">
-        <v>271</v>
+        <v>309</v>
       </c>
       <c r="D51" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="E51">
         <v>16</v>
@@ -6944,13 +7136,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>272</v>
+        <v>310</v>
       </c>
       <c r="C52" t="s">
-        <v>272</v>
+        <v>310</v>
       </c>
       <c r="D52" t="s">
-        <v>229</v>
+        <v>267</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -6964,13 +7156,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>273</v>
+        <v>311</v>
       </c>
       <c r="C53" t="s">
-        <v>273</v>
+        <v>311</v>
       </c>
       <c r="D53" t="s">
-        <v>268</v>
+        <v>306</v>
       </c>
       <c r="E53">
         <v>3</v>
@@ -6984,13 +7176,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>274</v>
+        <v>312</v>
       </c>
       <c r="C54" t="s">
-        <v>274</v>
+        <v>312</v>
       </c>
       <c r="D54" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="E54">
         <v>3</v>
@@ -7007,16 +7199,16 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>275</v>
+        <v>313</v>
       </c>
       <c r="C55" t="s">
-        <v>275</v>
+        <v>313</v>
       </c>
       <c r="D55" t="s">
-        <v>221</v>
+        <v>259</v>
       </c>
       <c r="E55" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
       <c r="G55">
         <v>6</v>
@@ -7030,16 +7222,16 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>276</v>
+        <v>314</v>
       </c>
       <c r="C56" t="s">
-        <v>276</v>
+        <v>314</v>
       </c>
       <c r="D56" t="s">
-        <v>221</v>
+        <v>259</v>
       </c>
       <c r="E56" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
       <c r="G56">
         <v>7</v>
@@ -7053,16 +7245,16 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>277</v>
+        <v>315</v>
       </c>
       <c r="C57" t="s">
-        <v>278</v>
+        <v>316</v>
       </c>
       <c r="D57" t="s">
-        <v>221</v>
+        <v>259</v>
       </c>
       <c r="E57" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
       <c r="G57">
         <v>8</v>
@@ -7076,16 +7268,16 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>279</v>
+        <v>317</v>
       </c>
       <c r="C58" t="s">
-        <v>280</v>
+        <v>318</v>
       </c>
       <c r="D58" t="s">
-        <v>192</v>
+        <v>230</v>
       </c>
       <c r="E58" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
       <c r="G58">
         <v>6</v>
@@ -7099,16 +7291,16 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>281</v>
+        <v>319</v>
       </c>
       <c r="C59" t="s">
-        <v>280</v>
+        <v>318</v>
       </c>
       <c r="D59" t="s">
-        <v>192</v>
+        <v>230</v>
       </c>
       <c r="E59" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
       <c r="G59">
         <v>7</v>
@@ -7122,16 +7314,16 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>282</v>
+        <v>320</v>
       </c>
       <c r="C60" t="s">
-        <v>280</v>
+        <v>318</v>
       </c>
       <c r="D60" t="s">
-        <v>192</v>
+        <v>230</v>
       </c>
       <c r="E60" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
       <c r="G60">
         <v>8</v>
@@ -7145,19 +7337,19 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>283</v>
+        <v>321</v>
       </c>
       <c r="C61" t="s">
-        <v>283</v>
+        <v>321</v>
       </c>
       <c r="D61" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="E61">
         <v>3</v>
       </c>
       <c r="F61" t="s">
-        <v>241</v>
+        <v>279</v>
       </c>
       <c r="I61">
         <v>-1</v>
@@ -7168,13 +7360,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>284</v>
+        <v>322</v>
       </c>
       <c r="C62" t="s">
-        <v>284</v>
+        <v>322</v>
       </c>
       <c r="D62" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="E62">
         <v>20</v>
@@ -7188,16 +7380,16 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>285</v>
+        <v>323</v>
       </c>
       <c r="C63" t="s">
-        <v>285</v>
+        <v>323</v>
       </c>
       <c r="D63" t="s">
-        <v>212</v>
+        <v>250</v>
       </c>
       <c r="F63" t="s">
-        <v>245</v>
+        <v>283</v>
       </c>
       <c r="I63">
         <v>-1</v>
@@ -7208,13 +7400,13 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>286</v>
+        <v>324</v>
       </c>
       <c r="C64" t="s">
-        <v>286</v>
+        <v>324</v>
       </c>
       <c r="D64" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="E64">
         <v>21</v>
@@ -7228,13 +7420,13 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>287</v>
+        <v>325</v>
       </c>
       <c r="C65" t="s">
-        <v>287</v>
+        <v>325</v>
       </c>
       <c r="D65" t="s">
-        <v>268</v>
+        <v>306</v>
       </c>
       <c r="E65">
         <v>3</v>
@@ -7248,19 +7440,19 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="C66" t="s">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="D66" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="E66">
         <v>14</v>
       </c>
       <c r="F66" t="s">
-        <v>194</v>
+        <v>232</v>
       </c>
       <c r="I66">
         <v>-1</v>
@@ -7271,19 +7463,50 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>289</v>
+        <v>327</v>
       </c>
       <c r="C67" t="s">
-        <v>289</v>
+        <v>327</v>
       </c>
       <c r="D67" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="E67">
         <v>22</v>
       </c>
       <c r="I67">
         <v>-1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68">
+        <v>66</v>
+      </c>
+      <c r="B68" t="s">
+        <v>328</v>
+      </c>
+      <c r="D68" t="s">
+        <v>329</v>
+      </c>
+      <c r="E68" t="s">
+        <v>235</v>
+      </c>
+      <c r="I68">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69">
+        <v>67</v>
+      </c>
+      <c r="B69" t="s">
+        <v>330</v>
+      </c>
+      <c r="D69" t="s">
+        <v>329</v>
+      </c>
+      <c r="E69" t="s">
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -7319,13 +7542,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>290</v>
+        <v>331</v>
       </c>
       <c r="D1" t="s">
-        <v>291</v>
+        <v>332</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>292</v>
+        <v>333</v>
       </c>
       <c r="F1" t="s">
         <v>17</v>
@@ -7352,10 +7575,10 @@
         <v>27</v>
       </c>
       <c r="N1" t="s">
-        <v>293</v>
+        <v>334</v>
       </c>
       <c r="O1" t="s">
-        <v>294</v>
+        <v>335</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -7363,10 +7586,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>295</v>
+        <v>336</v>
       </c>
       <c r="C2" t="s">
-        <v>296</v>
+        <v>337</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -7392,10 +7615,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>297</v>
+        <v>338</v>
       </c>
       <c r="C3" t="s">
-        <v>296</v>
+        <v>337</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -7415,10 +7638,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>298</v>
+        <v>339</v>
       </c>
       <c r="C4" t="s">
-        <v>296</v>
+        <v>337</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -7432,10 +7655,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>299</v>
+        <v>340</v>
       </c>
       <c r="C5" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -7467,10 +7690,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>301</v>
+        <v>342</v>
       </c>
       <c r="C6" t="s">
-        <v>296</v>
+        <v>337</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -7490,10 +7713,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>302</v>
+        <v>343</v>
       </c>
       <c r="C7" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -7513,10 +7736,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>303</v>
+        <v>344</v>
       </c>
       <c r="C8" t="s">
-        <v>296</v>
+        <v>337</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -7536,10 +7759,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>304</v>
+        <v>345</v>
       </c>
       <c r="C9" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -7559,10 +7782,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>243</v>
+        <v>281</v>
       </c>
       <c r="C10" t="s">
-        <v>296</v>
+        <v>337</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -7582,10 +7805,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>246</v>
+        <v>284</v>
       </c>
       <c r="C11" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -7611,10 +7834,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>247</v>
+        <v>285</v>
       </c>
       <c r="C12" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -7640,10 +7863,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>254</v>
+        <v>292</v>
       </c>
       <c r="C13" t="s">
-        <v>296</v>
+        <v>337</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -7663,10 +7886,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>262</v>
+        <v>300</v>
       </c>
       <c r="C14" t="s">
-        <v>296</v>
+        <v>337</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -7686,10 +7909,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>305</v>
+        <v>346</v>
       </c>
       <c r="C15" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -7709,10 +7932,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>306</v>
+        <v>347</v>
       </c>
       <c r="C16" t="s">
-        <v>296</v>
+        <v>337</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -7732,10 +7955,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>269</v>
+        <v>307</v>
       </c>
       <c r="C17" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -7755,10 +7978,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>271</v>
+        <v>309</v>
       </c>
       <c r="C18" t="s">
-        <v>296</v>
+        <v>337</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -7778,10 +8001,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>307</v>
+        <v>348</v>
       </c>
       <c r="C19" t="s">
-        <v>296</v>
+        <v>337</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -7795,10 +8018,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>308</v>
+        <v>349</v>
       </c>
       <c r="C20" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -7812,10 +8035,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>309</v>
+        <v>350</v>
       </c>
       <c r="C21" t="s">
-        <v>296</v>
+        <v>337</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -7829,10 +8052,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>310</v>
+        <v>351</v>
       </c>
       <c r="C22" t="s">
-        <v>296</v>
+        <v>337</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -7852,10 +8075,10 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>311</v>
+        <v>352</v>
       </c>
       <c r="C23" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -7875,10 +8098,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>289</v>
+        <v>327</v>
       </c>
       <c r="C24" t="s">
-        <v>296</v>
+        <v>337</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -7893,15 +8116,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>312</v>
+        <v>353</v>
       </c>
       <c r="C25" t="s">
-        <v>296</v>
+        <v>337</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -7909,16 +8132,22 @@
       <c r="E25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="F25">
+        <v>13</v>
+      </c>
+      <c r="G25">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>313</v>
+        <v>354</v>
       </c>
       <c r="C26" t="s">
-        <v>296</v>
+        <v>337</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -7926,16 +8155,22 @@
       <c r="E26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:5">
+      <c r="F26">
+        <v>13</v>
+      </c>
+      <c r="G26">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>314</v>
+        <v>355</v>
       </c>
       <c r="C27" t="s">
-        <v>296</v>
+        <v>337</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -7943,16 +8178,22 @@
       <c r="E27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:5">
+      <c r="F27">
+        <v>13</v>
+      </c>
+      <c r="G27">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="C28" t="s">
-        <v>296</v>
+        <v>337</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -7960,16 +8201,22 @@
       <c r="E28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:5">
+      <c r="F28">
+        <v>13</v>
+      </c>
+      <c r="G28">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>316</v>
+        <v>357</v>
       </c>
       <c r="C29" t="s">
-        <v>296</v>
+        <v>337</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -7977,16 +8224,22 @@
       <c r="E29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:5">
+      <c r="F29">
+        <v>13</v>
+      </c>
+      <c r="G29">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>317</v>
+        <v>358</v>
       </c>
       <c r="C30" t="s">
-        <v>296</v>
+        <v>337</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -7994,16 +8247,22 @@
       <c r="E30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:5">
+      <c r="F30">
+        <v>13</v>
+      </c>
+      <c r="G30">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
       <c r="C31" t="s">
-        <v>296</v>
+        <v>337</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -8011,16 +8270,22 @@
       <c r="E31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:5">
+      <c r="F31">
+        <v>13</v>
+      </c>
+      <c r="G31">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>319</v>
+        <v>360</v>
       </c>
       <c r="C32" t="s">
-        <v>296</v>
+        <v>337</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -8028,16 +8293,22 @@
       <c r="E32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:5">
+      <c r="F32">
+        <v>13</v>
+      </c>
+      <c r="G32">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>320</v>
+        <v>361</v>
       </c>
       <c r="C33" t="s">
-        <v>296</v>
+        <v>337</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -8045,22 +8316,34 @@
       <c r="E33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:5">
+      <c r="F33">
+        <v>13</v>
+      </c>
+      <c r="G33">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>321</v>
+        <v>362</v>
       </c>
       <c r="C34" t="s">
-        <v>296</v>
+        <v>337</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34">
         <v>0</v>
+      </c>
+      <c r="F34">
+        <v>13</v>
+      </c>
+      <c r="G34">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -8096,16 +8379,16 @@
         <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>322</v>
+        <v>363</v>
       </c>
       <c r="E1" t="s">
-        <v>323</v>
+        <v>364</v>
       </c>
       <c r="F1" t="s">
-        <v>324</v>
+        <v>365</v>
       </c>
       <c r="G1" t="s">
-        <v>325</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8113,13 +8396,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>326</v>
+        <v>367</v>
       </c>
       <c r="C2" t="s">
-        <v>327</v>
+        <v>368</v>
       </c>
       <c r="D2" t="s">
-        <v>328</v>
+        <v>369</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -8133,13 +8416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>329</v>
+        <v>370</v>
       </c>
       <c r="C3" t="s">
-        <v>330</v>
+        <v>371</v>
       </c>
       <c r="D3" t="s">
-        <v>328</v>
+        <v>369</v>
       </c>
       <c r="F3" t="s">
         <v>44</v>
@@ -8150,13 +8433,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>331</v>
+        <v>372</v>
       </c>
       <c r="C4" t="s">
-        <v>330</v>
+        <v>371</v>
       </c>
       <c r="D4" t="s">
-        <v>328</v>
+        <v>369</v>
       </c>
       <c r="F4" t="s">
         <v>38</v>
@@ -8167,13 +8450,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>332</v>
+        <v>373</v>
       </c>
       <c r="C5" t="s">
-        <v>327</v>
+        <v>368</v>
       </c>
       <c r="D5" t="s">
-        <v>328</v>
+        <v>369</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -8187,13 +8470,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>333</v>
+        <v>374</v>
       </c>
       <c r="C6" t="s">
-        <v>327</v>
+        <v>368</v>
       </c>
       <c r="D6" t="s">
-        <v>328</v>
+        <v>369</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -8207,13 +8490,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>334</v>
+        <v>375</v>
       </c>
       <c r="C7" t="s">
-        <v>327</v>
+        <v>368</v>
       </c>
       <c r="D7" t="s">
-        <v>328</v>
+        <v>369</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -8227,13 +8510,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>335</v>
+        <v>376</v>
       </c>
       <c r="C8" t="s">
-        <v>327</v>
+        <v>368</v>
       </c>
       <c r="D8" t="s">
-        <v>328</v>
+        <v>369</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -8247,13 +8530,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>336</v>
+        <v>377</v>
       </c>
       <c r="C9" t="s">
-        <v>327</v>
+        <v>368</v>
       </c>
       <c r="D9" t="s">
-        <v>328</v>
+        <v>369</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -8267,13 +8550,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>337</v>
+        <v>378</v>
       </c>
       <c r="C10" t="s">
-        <v>327</v>
+        <v>368</v>
       </c>
       <c r="D10" t="s">
-        <v>328</v>
+        <v>369</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -8287,13 +8570,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>338</v>
+        <v>379</v>
       </c>
       <c r="C11" t="s">
-        <v>339</v>
+        <v>380</v>
       </c>
       <c r="D11" t="s">
-        <v>328</v>
+        <v>369</v>
       </c>
       <c r="E11" t="s">
         <v>44</v>

--- a/Assets/StreamingAssets/Configurations/Cards.xlsx
+++ b/Assets/StreamingAssets/Configurations/Cards.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA0FBF0A-7FAD-4F89-97EF-B2A0B61F6812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -24,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1058,167 +1062,17 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1237,188 +1091,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1444,251 +1118,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1703,71 +1135,27 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="00FFFFFF"/>
-      <color rgb="00AB0580"/>
-      <color rgb="0000B050"/>
-      <color rgb="00FFB200"/>
-      <color rgb="004B58FF"/>
-      <color rgb="00FF2160"/>
+      <color rgb="FFFFFFFF"/>
+      <color rgb="FFAB0580"/>
+      <color rgb="FF00B050"/>
+      <color rgb="FFFFB200"/>
+      <color rgb="FF4B58FF"/>
+      <color rgb="FFFF2160"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2025,50 +1413,49 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AI61"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.425" customWidth="1"/>
-    <col min="2" max="2" width="12.7083333333333" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
-    <col min="4" max="4" width="57.7083333333333" customWidth="1"/>
-    <col min="5" max="5" width="10.425" style="2" customWidth="1"/>
-    <col min="6" max="6" width="4.85833333333333" customWidth="1"/>
-    <col min="7" max="7" width="7.85833333333333" customWidth="1"/>
+    <col min="4" max="4" width="57.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="4.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.85546875" customWidth="1"/>
     <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="9" max="9" width="5.56666666666667" style="3" customWidth="1"/>
-    <col min="10" max="10" width="10.5666666666667" customWidth="1"/>
-    <col min="11" max="11" width="9.70833333333333" style="3" customWidth="1"/>
-    <col min="12" max="12" width="7.14166666666667" customWidth="1"/>
+    <col min="9" max="9" width="5.5703125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" style="3" customWidth="1"/>
+    <col min="12" max="12" width="7.140625" customWidth="1"/>
     <col min="13" max="13" width="14" style="3" customWidth="1"/>
-    <col min="14" max="14" width="10.2833333333333" customWidth="1"/>
-    <col min="15" max="15" width="13.7083333333333" customWidth="1"/>
-    <col min="16" max="16" width="13.7083333333333" customWidth="1"/>
-    <col min="17" max="17" width="9.70833333333333" style="3" customWidth="1"/>
-    <col min="18" max="18" width="9.70833333333333" customWidth="1"/>
-    <col min="19" max="19" width="12.1416666666667" customWidth="1"/>
-    <col min="20" max="20" width="17.7083333333333" style="3" customWidth="1"/>
+    <col min="14" max="14" width="10.28515625" customWidth="1"/>
+    <col min="15" max="16" width="13.7109375" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="3" customWidth="1"/>
+    <col min="18" max="18" width="9.7109375" customWidth="1"/>
+    <col min="19" max="19" width="12.140625" customWidth="1"/>
+    <col min="20" max="20" width="17.7109375" style="3" customWidth="1"/>
     <col min="21" max="21" width="11" customWidth="1"/>
-    <col min="22" max="22" width="12.2833333333333" customWidth="1"/>
-    <col min="23" max="23" width="17.1416666666667" style="3" customWidth="1"/>
-    <col min="26" max="26" width="17.7083333333333" style="3" customWidth="1"/>
-    <col min="27" max="27" width="10.7083333333333" customWidth="1"/>
+    <col min="22" max="22" width="12.28515625" customWidth="1"/>
+    <col min="23" max="23" width="17.140625" style="3" customWidth="1"/>
+    <col min="26" max="26" width="17.7109375" style="3" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" customWidth="1"/>
     <col min="28" max="28" width="11" customWidth="1"/>
-    <col min="29" max="29" width="17.7083333333333" style="3" customWidth="1"/>
-    <col min="30" max="30" width="12.425" customWidth="1"/>
-    <col min="31" max="31" width="12.425" style="3" customWidth="1"/>
-    <col min="32" max="32" width="12.2833333333333" customWidth="1"/>
+    <col min="29" max="29" width="17.7109375" style="3" customWidth="1"/>
+    <col min="30" max="30" width="12.42578125" customWidth="1"/>
+    <col min="31" max="31" width="12.42578125" style="3" customWidth="1"/>
+    <col min="32" max="32" width="12.28515625" customWidth="1"/>
     <col min="33" max="33" width="9" style="3"/>
-    <col min="34" max="34" width="4.28333333333333" customWidth="1"/>
+    <col min="34" max="34" width="4.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2172,7 +1559,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:34">
+    <row r="2" spans="1:35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2227,7 +1614,7 @@
       <c r="AG2"/>
       <c r="AH2" s="5"/>
     </row>
-    <row r="3" spans="1:34">
+    <row r="3" spans="1:35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2282,7 +1669,7 @@
       <c r="AG3"/>
       <c r="AH3" s="5"/>
     </row>
-    <row r="4" spans="1:34">
+    <row r="4" spans="1:35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2342,7 +1729,7 @@
       </c>
       <c r="AH4" s="5"/>
     </row>
-    <row r="5" spans="1:34">
+    <row r="5" spans="1:35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2405,7 +1792,7 @@
       <c r="AG5"/>
       <c r="AH5" s="5"/>
     </row>
-    <row r="6" spans="1:34">
+    <row r="6" spans="1:35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2471,7 +1858,7 @@
       </c>
       <c r="AH6" s="5"/>
     </row>
-    <row r="7" spans="1:34">
+    <row r="7" spans="1:35">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2537,7 +1924,7 @@
       <c r="AG7"/>
       <c r="AH7" s="5"/>
     </row>
-    <row r="8" spans="1:34">
+    <row r="8" spans="1:35">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2610,7 +1997,7 @@
       <c r="AG8"/>
       <c r="AH8" s="5"/>
     </row>
-    <row r="9" spans="1:34">
+    <row r="9" spans="1:35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2673,7 +2060,7 @@
       <c r="AG9"/>
       <c r="AH9" s="5"/>
     </row>
-    <row r="10" spans="1:34">
+    <row r="10" spans="1:35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2736,7 +2123,7 @@
       <c r="AG10"/>
       <c r="AH10" s="5"/>
     </row>
-    <row r="11" spans="1:34">
+    <row r="11" spans="1:35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2862,7 +2249,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="1:34">
+    <row r="13" spans="1:35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2925,7 +2312,7 @@
       <c r="AG13"/>
       <c r="AH13" s="5"/>
     </row>
-    <row r="14" spans="1:34">
+    <row r="14" spans="1:35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2980,7 +2367,7 @@
       <c r="AG14"/>
       <c r="AH14" s="5"/>
     </row>
-    <row r="15" spans="1:34">
+    <row r="15" spans="1:35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3035,7 +2422,7 @@
       <c r="AG15"/>
       <c r="AH15" s="5"/>
     </row>
-    <row r="16" spans="1:34">
+    <row r="16" spans="1:35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3090,7 +2477,7 @@
         <v>0.8</v>
       </c>
       <c r="W16" s="3">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="Z16"/>
       <c r="AC16"/>
@@ -4066,7 +3453,7 @@
       <c r="AG31"/>
       <c r="AH31" s="6"/>
     </row>
-    <row r="32" spans="1:33">
+    <row r="32" spans="1:34">
       <c r="A32">
         <v>33</v>
       </c>
@@ -4115,7 +3502,7 @@
       <c r="AE32"/>
       <c r="AG32"/>
     </row>
-    <row r="33" spans="1:31">
+    <row r="33" spans="1:33">
       <c r="A33">
         <v>34</v>
       </c>
@@ -4171,7 +3558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:20">
+    <row r="34" spans="1:33">
       <c r="A34">
         <v>35</v>
       </c>
@@ -4224,7 +3611,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:20">
+    <row r="35" spans="1:33">
       <c r="A35">
         <v>36</v>
       </c>
@@ -4274,7 +3661,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:23">
+    <row r="36" spans="1:33">
       <c r="A36">
         <v>37</v>
       </c>
@@ -4775,7 +4162,7 @@
       <c r="AE43"/>
       <c r="AG43"/>
     </row>
-    <row r="44" spans="1:23">
+    <row r="44" spans="1:33">
       <c r="A44">
         <v>45</v>
       </c>
@@ -5093,7 +4480,7 @@
       <c r="AE48"/>
       <c r="AG48"/>
     </row>
-    <row r="49" spans="1:23">
+    <row r="49" spans="1:33">
       <c r="A49">
         <v>50</v>
       </c>
@@ -5204,7 +4591,7 @@
         <v>18</v>
       </c>
       <c r="V50">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="W50" s="3">
         <v>1.7</v>
@@ -5338,7 +4725,7 @@
       <c r="AE52"/>
       <c r="AG52"/>
     </row>
-    <row r="53" spans="1:23">
+    <row r="53" spans="1:33">
       <c r="A53">
         <v>54</v>
       </c>
@@ -5400,7 +4787,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="54" spans="1:26">
+    <row r="54" spans="1:33">
       <c r="A54">
         <v>55</v>
       </c>
@@ -5471,7 +4858,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:32">
+    <row r="55" spans="1:33">
       <c r="A55">
         <v>56</v>
       </c>
@@ -5531,7 +4918,7 @@
       </c>
       <c r="AF55" s="3"/>
     </row>
-    <row r="56" spans="1:32">
+    <row r="56" spans="1:33">
       <c r="A56">
         <v>57</v>
       </c>
@@ -5603,7 +4990,7 @@
       </c>
       <c r="AF56" s="3"/>
     </row>
-    <row r="57" spans="1:23">
+    <row r="57" spans="1:33">
       <c r="A57">
         <v>58</v>
       </c>
@@ -5665,7 +5052,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:15">
+    <row r="58" spans="1:33">
       <c r="A58">
         <v>59</v>
       </c>
@@ -5706,7 +5093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:20">
+    <row r="59" spans="1:33">
       <c r="A59">
         <v>60</v>
       </c>
@@ -5756,7 +5143,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:15">
+    <row r="60" spans="1:33">
       <c r="A60">
         <v>61</v>
       </c>
@@ -5797,7 +5184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:15">
+    <row r="61" spans="1:33">
       <c r="A61">
         <v>62</v>
       </c>
@@ -5843,25 +5230,23 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I67"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.425" customWidth="1"/>
-    <col min="2" max="2" width="27.425" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
     <col min="4" max="4" width="33" customWidth="1"/>
-    <col min="5" max="5" width="19.2833333333333" customWidth="1"/>
-    <col min="6" max="6" width="18.8583333333333" customWidth="1"/>
-    <col min="7" max="8" width="10.2833333333333" customWidth="1"/>
-    <col min="9" max="9" width="15.1416666666667" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" customWidth="1"/>
+    <col min="7" max="8" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7183,7 +6568,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="63" customFormat="1" spans="1:9">
+    <row r="63" spans="1:9">
       <c r="A63">
         <v>61</v>
       </c>
@@ -7243,7 +6628,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="66" customFormat="1" spans="1:9">
+    <row r="66" spans="1:9">
       <c r="A66">
         <v>64</v>
       </c>
@@ -7288,26 +6673,24 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.425" customWidth="1"/>
-    <col min="2" max="2" width="27.425" customWidth="1"/>
-    <col min="3" max="3" width="14.425" customWidth="1"/>
-    <col min="4" max="5" width="16.1416666666667" customWidth="1"/>
-    <col min="6" max="6" width="12.425" customWidth="1"/>
-    <col min="7" max="7" width="14.425" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
+    <col min="4" max="5" width="16.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="10.1416666666667" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7358,7 +6741,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>0</v>
       </c>
@@ -7387,7 +6770,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>1</v>
       </c>
@@ -7410,7 +6793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>2</v>
       </c>
@@ -7427,7 +6810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:15">
       <c r="A5">
         <v>3</v>
       </c>
@@ -7462,7 +6845,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:15">
       <c r="A6">
         <v>4</v>
       </c>
@@ -7485,7 +6868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:15">
       <c r="A7">
         <v>5</v>
       </c>
@@ -7508,7 +6891,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:15">
       <c r="A8">
         <v>6</v>
       </c>
@@ -7531,7 +6914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:15">
       <c r="A9">
         <v>7</v>
       </c>
@@ -7554,7 +6937,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:15">
       <c r="A10">
         <v>8</v>
       </c>
@@ -7577,7 +6960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:15">
       <c r="A11">
         <v>9</v>
       </c>
@@ -7606,7 +6989,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:15">
       <c r="A12">
         <v>10</v>
       </c>
@@ -7635,7 +7018,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:15">
       <c r="A13">
         <v>11</v>
       </c>
@@ -7658,7 +7041,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:15">
       <c r="A14">
         <v>12</v>
       </c>
@@ -7681,7 +7064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:15">
       <c r="A15">
         <v>13</v>
       </c>
@@ -7704,7 +7087,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:15">
       <c r="A16">
         <v>14</v>
       </c>
@@ -7773,7 +7156,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>17</v>
       </c>
@@ -7790,7 +7173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>18</v>
       </c>
@@ -7807,7 +7190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>19</v>
       </c>
@@ -7893,7 +7276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>23</v>
       </c>
@@ -7910,7 +7293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>24</v>
       </c>
@@ -7927,7 +7310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>25</v>
       </c>
@@ -7944,7 +7327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>26</v>
       </c>
@@ -7961,7 +7344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>27</v>
       </c>
@@ -7978,7 +7361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>28</v>
       </c>
@@ -7995,7 +7378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>29</v>
       </c>
@@ -8012,7 +7395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>30</v>
       </c>
@@ -8065,24 +7448,22 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85833333333333" customWidth="1"/>
-    <col min="2" max="2" width="22.7083333333333" customWidth="1"/>
-    <col min="3" max="3" width="28.5666666666667" customWidth="1"/>
-    <col min="4" max="4" width="15.5666666666667" customWidth="1"/>
-    <col min="5" max="5" width="16.1416666666667" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="11.1416666666667" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -8108,7 +7489,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -8128,7 +7509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="12.95" customHeight="1" spans="1:6">
+    <row r="3" spans="1:7" ht="12.95" customHeight="1">
       <c r="A3">
         <v>1</v>
       </c>
@@ -8145,7 +7526,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" ht="12.95" customHeight="1" spans="1:6">
+    <row r="4" spans="1:7" ht="12.95" customHeight="1">
       <c r="A4">
         <v>2</v>
       </c>
@@ -8162,7 +7543,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>3</v>
       </c>
@@ -8182,7 +7563,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>4</v>
       </c>
@@ -8202,7 +7583,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>5</v>
       </c>
@@ -8222,7 +7603,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>6</v>
       </c>
@@ -8242,7 +7623,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>7</v>
       </c>
@@ -8262,7 +7643,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>8</v>
       </c>
@@ -8282,7 +7663,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>9</v>
       </c>
@@ -8304,7 +7685,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Cards.xlsx
+++ b/Assets/StreamingAssets/Configurations/Cards.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView windowWidth="22190" windowHeight="9040" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Crads" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="394">
   <si>
     <t>ID</t>
   </si>
@@ -698,6 +698,36 @@
     <t>获得神采X1%的参数，下一回合抽一张卡牌</t>
   </si>
   <si>
+    <t>好娇娇</t>
+  </si>
+  <si>
+    <t>红温+6，幽默+6</t>
+  </si>
+  <si>
+    <t>红温+X1，幽默+X2</t>
+  </si>
+  <si>
+    <t>窝里横</t>
+  </si>
+  <si>
+    <t>同接-30，参数+32，神采+15，获得神采150%的参数</t>
+  </si>
+  <si>
+    <t>同接-30，参数+X2，神采+X3，获得神采X4%的参数</t>
+  </si>
+  <si>
+    <t>养</t>
+  </si>
+  <si>
+    <t>同接+50，获得同接10%的神采</t>
+  </si>
+  <si>
+    <t>gachi距离</t>
+  </si>
+  <si>
+    <t>舰长+1，获得舰长数100%的参数</t>
+  </si>
+  <si>
     <t>Parameter</t>
   </si>
   <si>
@@ -1028,6 +1058,18 @@
     <t>神采变为X%</t>
   </si>
   <si>
+    <t>获得等同于同接X%的神采</t>
+  </si>
+  <si>
+    <t>VAddPercentageFromAttributeEffect</t>
+  </si>
+  <si>
+    <t>BAViewerCount,BAShield</t>
+  </si>
+  <si>
+    <t>获得舰长数X%的参数</t>
+  </si>
+  <si>
     <t>BuffType</t>
   </si>
   <si>
@@ -1083,9 +1125,6 @@
   </si>
   <si>
     <t>盐应对</t>
-  </si>
-  <si>
-    <t>好娇娇</t>
   </si>
   <si>
     <t>每当使用A卡时，红温+1</t>
@@ -2161,7 +2200,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AI61"/>
+  <dimension ref="A1:AI65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
@@ -6033,6 +6072,254 @@
         <v>1</v>
       </c>
     </row>
+    <row r="62" spans="1:23">
+      <c r="A62">
+        <v>63</v>
+      </c>
+      <c r="B62" t="s">
+        <v>221</v>
+      </c>
+      <c r="C62" t="s">
+        <v>222</v>
+      </c>
+      <c r="D62" t="s">
+        <v>223</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F62" t="s">
+        <v>44</v>
+      </c>
+      <c r="G62" t="s">
+        <v>49</v>
+      </c>
+      <c r="H62" t="s">
+        <v>50</v>
+      </c>
+      <c r="I62" t="s">
+        <v>125</v>
+      </c>
+      <c r="J62" t="s">
+        <v>40</v>
+      </c>
+      <c r="L62">
+        <v>5</v>
+      </c>
+      <c r="M62" s="3">
+        <v>4</v>
+      </c>
+      <c r="N62">
+        <v>1</v>
+      </c>
+      <c r="O62">
+        <v>1</v>
+      </c>
+      <c r="R62">
+        <v>15</v>
+      </c>
+      <c r="S62">
+        <v>6</v>
+      </c>
+      <c r="T62" s="3">
+        <v>8</v>
+      </c>
+      <c r="U62">
+        <v>45</v>
+      </c>
+      <c r="V62">
+        <v>6</v>
+      </c>
+      <c r="W62" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:29">
+      <c r="A63">
+        <v>64</v>
+      </c>
+      <c r="B63" t="s">
+        <v>224</v>
+      </c>
+      <c r="C63" t="s">
+        <v>225</v>
+      </c>
+      <c r="D63" t="s">
+        <v>226</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F63" t="s">
+        <v>38</v>
+      </c>
+      <c r="G63" t="s">
+        <v>49</v>
+      </c>
+      <c r="H63" t="s">
+        <v>50</v>
+      </c>
+      <c r="I63" t="s">
+        <v>125</v>
+      </c>
+      <c r="J63" t="s">
+        <v>211</v>
+      </c>
+      <c r="L63">
+        <v>6</v>
+      </c>
+      <c r="M63" s="3">
+        <v>5</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>1</v>
+      </c>
+      <c r="R63">
+        <v>33</v>
+      </c>
+      <c r="S63">
+        <v>-30</v>
+      </c>
+      <c r="T63" s="3">
+        <v>-30</v>
+      </c>
+      <c r="U63">
+        <v>11</v>
+      </c>
+      <c r="V63">
+        <v>32</v>
+      </c>
+      <c r="W63" s="3">
+        <v>40</v>
+      </c>
+      <c r="X63">
+        <v>2</v>
+      </c>
+      <c r="Y63">
+        <v>15</v>
+      </c>
+      <c r="Z63" s="3">
+        <v>18</v>
+      </c>
+      <c r="AA63">
+        <v>66</v>
+      </c>
+      <c r="AB63">
+        <v>1.5</v>
+      </c>
+      <c r="AC63" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23">
+      <c r="A64">
+        <v>65</v>
+      </c>
+      <c r="B64" t="s">
+        <v>227</v>
+      </c>
+      <c r="C64" t="s">
+        <v>228</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F64" t="s">
+        <v>38</v>
+      </c>
+      <c r="G64" t="s">
+        <v>39</v>
+      </c>
+      <c r="J64" t="s">
+        <v>40</v>
+      </c>
+      <c r="L64">
+        <v>4</v>
+      </c>
+      <c r="M64" s="3">
+        <v>4</v>
+      </c>
+      <c r="N64">
+        <v>1</v>
+      </c>
+      <c r="O64">
+        <v>1</v>
+      </c>
+      <c r="R64">
+        <v>33</v>
+      </c>
+      <c r="S64">
+        <v>50</v>
+      </c>
+      <c r="T64" s="3">
+        <v>50</v>
+      </c>
+      <c r="U64">
+        <v>68</v>
+      </c>
+      <c r="V64">
+        <v>0.1</v>
+      </c>
+      <c r="W64" s="3">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23">
+      <c r="A65">
+        <v>66</v>
+      </c>
+      <c r="B65" t="s">
+        <v>229</v>
+      </c>
+      <c r="C65" t="s">
+        <v>230</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F65" t="s">
+        <v>38</v>
+      </c>
+      <c r="G65" t="s">
+        <v>39</v>
+      </c>
+      <c r="J65" t="s">
+        <v>40</v>
+      </c>
+      <c r="L65">
+        <v>5</v>
+      </c>
+      <c r="M65" s="3">
+        <v>5</v>
+      </c>
+      <c r="N65">
+        <v>1</v>
+      </c>
+      <c r="O65">
+        <v>1</v>
+      </c>
+      <c r="R65">
+        <v>19</v>
+      </c>
+      <c r="S65">
+        <v>1</v>
+      </c>
+      <c r="T65" s="3">
+        <v>1</v>
+      </c>
+      <c r="U65">
+        <v>69</v>
+      </c>
+      <c r="V65">
+        <v>1</v>
+      </c>
+      <c r="W65" s="3">
+        <v>1.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
@@ -6043,7 +6330,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
@@ -6071,19 +6358,19 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="G1" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="H1" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="I1" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6091,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="C2" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="D2" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="I2">
         <v>-1</v>
@@ -6108,19 +6395,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="C3" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="D3" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="E3" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="F3" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -6131,16 +6418,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="C4" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="D4" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="E4" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -6151,16 +6438,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C5" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="D5" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="E5" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -6171,13 +6458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C6" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="D6" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -6188,16 +6475,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="C7" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="D7" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="E7" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -6208,13 +6495,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="C8" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="D8" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -6228,13 +6515,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="C9" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="D9" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -6248,13 +6535,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="C10" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="D10" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -6268,13 +6555,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C11" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -6285,16 +6572,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="C12" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="D12" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="E12" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -6305,16 +6592,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="C13" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="D13" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="E13" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -6325,19 +6612,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
+        <v>266</v>
+      </c>
+      <c r="C14" t="s">
+        <v>267</v>
+      </c>
+      <c r="D14" t="s">
         <v>256</v>
       </c>
-      <c r="C14" t="s">
-        <v>257</v>
-      </c>
-      <c r="D14" t="s">
-        <v>246</v>
-      </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -6348,16 +6635,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="C15" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="D15" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="E15" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -6368,16 +6655,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="C16" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="D16" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="E16" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -6388,13 +6675,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="C17" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="D17" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -6408,16 +6695,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="C18" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="D18" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="E18" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -6428,13 +6715,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="C19" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="D19" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -6448,13 +6735,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="C20" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="D20" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -6468,16 +6755,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="C21" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="D21" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="E21" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -6488,16 +6775,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="C22" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="D22" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="E22" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -6508,13 +6795,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="C23" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="D23" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E23">
         <v>5</v>
@@ -6528,19 +6815,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="C24" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="D24" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -6551,13 +6838,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="C25" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="D25" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -6571,16 +6858,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="C26" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="D26" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="E26" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -6594,16 +6881,16 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="C27" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="D27" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="E27" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -6614,13 +6901,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="C28" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="D28" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -6634,19 +6921,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="C29" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="D29" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -6660,13 +6947,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="C30" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="D30" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -6680,19 +6967,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="C31" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="D31" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="E31" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="F31" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -6703,19 +6990,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="C32" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="D32" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E32">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -6726,19 +7013,19 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="C33" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="D33" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E33">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -6749,16 +7036,16 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="C34" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="D34" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="E34" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -6769,16 +7056,16 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="C35" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="D35" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="E35" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -6789,19 +7076,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="C36" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="D36" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="E36" t="s">
+        <v>299</v>
+      </c>
+      <c r="F36" t="s">
         <v>289</v>
-      </c>
-      <c r="F36" t="s">
-        <v>279</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -6815,13 +7102,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="C37" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="D37" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E37">
         <v>11</v>
@@ -6835,16 +7122,16 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="C38" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="D38" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="E38" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -6855,13 +7142,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="C39" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="D39" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -6878,16 +7165,16 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="C40" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="D40" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="E40" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -6898,13 +7185,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="C41" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="D41" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -6921,19 +7208,19 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="C42" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="D42" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -6947,13 +7234,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="C43" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="D43" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E43">
         <v>12</v>
@@ -6967,13 +7254,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="C44" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="D44" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E44">
         <v>13</v>
@@ -6987,19 +7274,19 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="C45" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="D45" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="E45" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="F45" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="I45">
         <v>-1</v>
@@ -7010,16 +7297,16 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="C46" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="D46" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="E46" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="I46">
         <v>1</v>
@@ -7030,13 +7317,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="C47" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="D47" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E47">
         <v>14</v>
@@ -7050,19 +7337,19 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="C48" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="D48" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="I48">
         <v>-1</v>
@@ -7073,13 +7360,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="C49" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="D49" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E49">
         <v>15</v>
@@ -7093,19 +7380,19 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="C50" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="D50" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="I50">
         <v>-1</v>
@@ -7116,13 +7403,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="C51" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="D51" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E51">
         <v>16</v>
@@ -7136,13 +7423,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="C52" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="D52" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -7156,13 +7443,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="C53" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="D53" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="E53">
         <v>3</v>
@@ -7176,13 +7463,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="C54" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="D54" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E54">
         <v>3</v>
@@ -7199,16 +7486,16 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="C55" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="D55" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="E55" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="G55">
         <v>6</v>
@@ -7222,16 +7509,16 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="C56" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="D56" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="E56" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="G56">
         <v>7</v>
@@ -7245,16 +7532,16 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="C57" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="D57" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="E57" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="G57">
         <v>8</v>
@@ -7268,16 +7555,16 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="C58" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="D58" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="E58" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="G58">
         <v>6</v>
@@ -7291,16 +7578,16 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="C59" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="D59" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="E59" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="G59">
         <v>7</v>
@@ -7314,16 +7601,16 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="C60" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="D60" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="E60" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="G60">
         <v>8</v>
@@ -7337,19 +7624,19 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="C61" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="D61" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E61">
         <v>3</v>
       </c>
       <c r="F61" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="I61">
         <v>-1</v>
@@ -7360,13 +7647,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="C62" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="D62" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E62">
         <v>20</v>
@@ -7380,16 +7667,16 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="C63" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="D63" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F63" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="I63">
         <v>-1</v>
@@ -7400,13 +7687,13 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="C64" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="D64" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E64">
         <v>21</v>
@@ -7420,13 +7707,13 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="C65" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="D65" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="E65">
         <v>3</v>
@@ -7440,19 +7727,19 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="C66" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="D66" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E66">
         <v>14</v>
       </c>
       <c r="F66" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="I66">
         <v>-1</v>
@@ -7463,13 +7750,13 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="C67" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="D67" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E67">
         <v>22</v>
@@ -7483,30 +7770,67 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="D68" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="E68" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="I68">
         <v>-1</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:9">
       <c r="A69">
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="D69" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="E69" t="s">
-        <v>235</v>
+        <v>245</v>
+      </c>
+      <c r="I69">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
+      <c r="A70">
+        <v>68</v>
+      </c>
+      <c r="B70" t="s">
+        <v>341</v>
+      </c>
+      <c r="D70" t="s">
+        <v>342</v>
+      </c>
+      <c r="E70" t="s">
+        <v>343</v>
+      </c>
+      <c r="I70">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71">
+        <v>69</v>
+      </c>
+      <c r="B71" t="s">
+        <v>344</v>
+      </c>
+      <c r="D71" t="s">
+        <v>339</v>
+      </c>
+      <c r="E71" t="s">
+        <v>279</v>
+      </c>
+      <c r="I71">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
@@ -7542,13 +7866,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="D1" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="F1" t="s">
         <v>17</v>
@@ -7575,10 +7899,10 @@
         <v>27</v>
       </c>
       <c r="N1" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="O1" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -7586,10 +7910,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="C2" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -7615,10 +7939,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="C3" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -7638,10 +7962,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="C4" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -7655,10 +7979,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="C5" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -7690,10 +8014,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="C6" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -7713,10 +8037,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="C7" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -7736,10 +8060,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="C8" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -7759,10 +8083,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="C9" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -7782,10 +8106,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="C10" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -7805,10 +8129,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="C11" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -7834,10 +8158,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="C12" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -7863,10 +8187,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="C13" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -7886,10 +8210,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="C14" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -7909,10 +8233,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="C15" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -7932,10 +8256,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="C16" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -7955,10 +8279,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="C17" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -7978,10 +8302,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="C18" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -8001,10 +8325,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="C19" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -8018,10 +8342,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="C20" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -8035,10 +8359,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>350</v>
+        <v>221</v>
       </c>
       <c r="C21" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -8052,10 +8376,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
+        <v>364</v>
+      </c>
+      <c r="C22" t="s">
         <v>351</v>
-      </c>
-      <c r="C22" t="s">
-        <v>337</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -8075,10 +8399,10 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="C23" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -8098,10 +8422,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="C24" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -8121,10 +8445,10 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="C25" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -8144,10 +8468,10 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="C26" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -8167,10 +8491,10 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="C27" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -8190,10 +8514,10 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="C28" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -8213,10 +8537,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="C29" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -8236,10 +8560,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>358</v>
+        <v>371</v>
       </c>
       <c r="C30" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -8259,10 +8583,10 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="C31" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -8282,10 +8606,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="C32" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -8305,10 +8629,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="C33" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -8328,10 +8652,10 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="C34" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -8379,16 +8703,16 @@
         <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="E1" t="s">
-        <v>364</v>
+        <v>377</v>
       </c>
       <c r="F1" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="G1" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8396,13 +8720,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="C2" t="s">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="D2" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -8416,13 +8740,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="C3" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="D3" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="F3" t="s">
         <v>44</v>
@@ -8433,13 +8757,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="C4" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="D4" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="F4" t="s">
         <v>38</v>
@@ -8450,13 +8774,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="C5" t="s">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="D5" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -8470,13 +8794,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="C6" t="s">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="D6" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -8490,13 +8814,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="C7" t="s">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="D7" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -8510,13 +8834,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="C8" t="s">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="D8" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -8530,13 +8854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="C9" t="s">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="D9" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -8550,13 +8874,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="C10" t="s">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="D10" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -8570,13 +8894,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="C11" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="D11" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="E11" t="s">
         <v>44</v>

--- a/Assets/StreamingAssets/Configurations/Cards.xlsx
+++ b/Assets/StreamingAssets/Configurations/Cards.xlsx
@@ -1,19 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10DE11E-A0D9-4062-90B4-175373358093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="22190" windowHeight="9040" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Crads" sheetId="1" r:id="rId1"/>
+    <sheet name="Cards" sheetId="1" r:id="rId1"/>
     <sheet name="Effects" sheetId="2" r:id="rId2"/>
     <sheet name="Buffs" sheetId="3" r:id="rId3"/>
     <sheet name="Conditions" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Crads!$G$1:$G$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cards!$G$1:$G$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -24,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -668,9 +672,6 @@
     <t>获得神采X1%的参数</t>
   </si>
   <si>
-    <t>TureStamina</t>
-  </si>
-  <si>
     <t>LLBC</t>
   </si>
   <si>
@@ -1215,172 +1216,25 @@
   </si>
   <si>
     <t>VCardTypeUsedCountCondition</t>
+  </si>
+  <si>
+    <t>TrueStamina</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1405,188 +1259,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1612,251 +1286,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1872,71 +1304,27 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="00FFFFFF"/>
-      <color rgb="00AB0580"/>
-      <color rgb="0000B050"/>
-      <color rgb="00FFB200"/>
-      <color rgb="004B58FF"/>
-      <color rgb="00FF2160"/>
+      <color rgb="FFFFFFFF"/>
+      <color rgb="FFAB0580"/>
+      <color rgb="FF00B050"/>
+      <color rgb="FFFFB200"/>
+      <color rgb="FF4B58FF"/>
+      <color rgb="FFFF2160"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2194,49 +1582,49 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AI65"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.425" customWidth="1"/>
-    <col min="2" max="2" width="12.7083333333333" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
-    <col min="4" max="4" width="57.7083333333333" customWidth="1"/>
-    <col min="5" max="5" width="10.425" style="2" customWidth="1"/>
-    <col min="6" max="6" width="4.85833333333333" customWidth="1"/>
-    <col min="7" max="7" width="7.85833333333333" customWidth="1"/>
+    <col min="4" max="4" width="57.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="4.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.85546875" customWidth="1"/>
     <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="9" max="9" width="5.56666666666667" style="3" customWidth="1"/>
-    <col min="10" max="10" width="10.5666666666667" customWidth="1"/>
-    <col min="11" max="11" width="9.70833333333333" style="3" customWidth="1"/>
-    <col min="12" max="12" width="7.14166666666667" customWidth="1"/>
+    <col min="9" max="9" width="5.5703125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" style="3" customWidth="1"/>
+    <col min="12" max="12" width="7.140625" customWidth="1"/>
     <col min="13" max="13" width="14" style="3" customWidth="1"/>
-    <col min="14" max="14" width="10.2833333333333" customWidth="1"/>
-    <col min="15" max="16" width="13.7083333333333" customWidth="1"/>
-    <col min="17" max="17" width="9.70833333333333" style="3" customWidth="1"/>
-    <col min="18" max="18" width="9.70833333333333" customWidth="1"/>
-    <col min="19" max="19" width="12.1416666666667" customWidth="1"/>
-    <col min="20" max="20" width="17.7083333333333" style="3" customWidth="1"/>
+    <col min="14" max="14" width="10.28515625" customWidth="1"/>
+    <col min="15" max="16" width="13.7109375" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="3" customWidth="1"/>
+    <col min="18" max="18" width="9.7109375" customWidth="1"/>
+    <col min="19" max="19" width="12.140625" customWidth="1"/>
+    <col min="20" max="20" width="17.7109375" style="3" customWidth="1"/>
     <col min="21" max="21" width="11" customWidth="1"/>
-    <col min="22" max="22" width="12.2833333333333" customWidth="1"/>
-    <col min="23" max="23" width="17.1416666666667" style="3" customWidth="1"/>
-    <col min="26" max="26" width="17.7083333333333" style="3" customWidth="1"/>
-    <col min="27" max="27" width="10.7083333333333" customWidth="1"/>
+    <col min="22" max="22" width="12.28515625" customWidth="1"/>
+    <col min="23" max="23" width="17.140625" style="3" customWidth="1"/>
+    <col min="26" max="26" width="17.7109375" style="3" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" customWidth="1"/>
     <col min="28" max="28" width="11" customWidth="1"/>
-    <col min="29" max="29" width="17.7083333333333" style="3" customWidth="1"/>
-    <col min="30" max="30" width="12.425" customWidth="1"/>
-    <col min="31" max="31" width="12.425" style="3" customWidth="1"/>
-    <col min="32" max="32" width="12.2833333333333" customWidth="1"/>
+    <col min="29" max="29" width="17.7109375" style="3" customWidth="1"/>
+    <col min="30" max="30" width="12.42578125" customWidth="1"/>
+    <col min="31" max="31" width="12.42578125" style="3" customWidth="1"/>
+    <col min="32" max="32" width="12.28515625" customWidth="1"/>
     <col min="33" max="33" width="9" style="3"/>
-    <col min="34" max="34" width="4.28333333333333" customWidth="1"/>
+    <col min="34" max="34" width="4.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2340,7 +1728,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:34">
+    <row r="2" spans="1:35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2395,7 +1783,7 @@
       <c r="AG2"/>
       <c r="AH2" s="6"/>
     </row>
-    <row r="3" spans="1:34">
+    <row r="3" spans="1:35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2450,7 +1838,7 @@
       <c r="AG3"/>
       <c r="AH3" s="6"/>
     </row>
-    <row r="4" spans="1:34">
+    <row r="4" spans="1:35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2510,7 +1898,7 @@
       </c>
       <c r="AH4" s="6"/>
     </row>
-    <row r="5" spans="1:34">
+    <row r="5" spans="1:35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2573,7 +1961,7 @@
       <c r="AG5"/>
       <c r="AH5" s="6"/>
     </row>
-    <row r="6" spans="1:34">
+    <row r="6" spans="1:35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2639,7 +2027,7 @@
       </c>
       <c r="AH6" s="6"/>
     </row>
-    <row r="7" spans="1:34">
+    <row r="7" spans="1:35">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2705,7 +2093,7 @@
       <c r="AG7"/>
       <c r="AH7" s="6"/>
     </row>
-    <row r="8" spans="1:34">
+    <row r="8" spans="1:35">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2778,7 +2166,7 @@
       <c r="AG8"/>
       <c r="AH8" s="6"/>
     </row>
-    <row r="9" spans="1:34">
+    <row r="9" spans="1:35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2841,7 +2229,7 @@
       <c r="AG9"/>
       <c r="AH9" s="6"/>
     </row>
-    <row r="10" spans="1:34">
+    <row r="10" spans="1:35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2904,7 +2292,7 @@
       <c r="AG10"/>
       <c r="AH10" s="6"/>
     </row>
-    <row r="11" spans="1:34">
+    <row r="11" spans="1:35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3030,7 +2418,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="1:34">
+    <row r="13" spans="1:35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3093,7 +2481,7 @@
       <c r="AG13"/>
       <c r="AH13" s="6"/>
     </row>
-    <row r="14" spans="1:34">
+    <row r="14" spans="1:35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3148,7 +2536,7 @@
       <c r="AG14"/>
       <c r="AH14" s="6"/>
     </row>
-    <row r="15" spans="1:34">
+    <row r="15" spans="1:35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3203,7 +2591,7 @@
       <c r="AG15"/>
       <c r="AH15" s="6"/>
     </row>
-    <row r="16" spans="1:34">
+    <row r="16" spans="1:35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3258,7 +2646,7 @@
         <v>0.8</v>
       </c>
       <c r="W16" s="3">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="Z16"/>
       <c r="AC16"/>
@@ -4234,7 +3622,7 @@
       <c r="AG31"/>
       <c r="AH31" s="7"/>
     </row>
-    <row r="32" spans="1:33">
+    <row r="32" spans="1:34">
       <c r="A32">
         <v>33</v>
       </c>
@@ -4283,7 +3671,7 @@
       <c r="AE32"/>
       <c r="AG32"/>
     </row>
-    <row r="33" spans="1:31">
+    <row r="33" spans="1:33">
       <c r="A33">
         <v>34</v>
       </c>
@@ -4339,7 +3727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:20">
+    <row r="34" spans="1:33">
       <c r="A34">
         <v>35</v>
       </c>
@@ -4392,7 +3780,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:20">
+    <row r="35" spans="1:33">
       <c r="A35">
         <v>36</v>
       </c>
@@ -4442,7 +3830,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:23">
+    <row r="36" spans="1:33">
       <c r="A36">
         <v>37</v>
       </c>
@@ -4943,7 +4331,7 @@
       <c r="AE43"/>
       <c r="AG43"/>
     </row>
-    <row r="44" spans="1:23">
+    <row r="44" spans="1:33">
       <c r="A44">
         <v>45</v>
       </c>
@@ -5261,7 +4649,7 @@
       <c r="AE48"/>
       <c r="AG48"/>
     </row>
-    <row r="49" spans="1:23">
+    <row r="49" spans="1:33">
       <c r="A49">
         <v>50</v>
       </c>
@@ -5372,7 +4760,7 @@
         <v>18</v>
       </c>
       <c r="V50">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="W50" s="3">
         <v>1.7</v>
@@ -5506,7 +4894,7 @@
       <c r="AE52"/>
       <c r="AG52"/>
     </row>
-    <row r="53" spans="1:23">
+    <row r="53" spans="1:33">
       <c r="A53">
         <v>54</v>
       </c>
@@ -5568,7 +4956,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="54" spans="1:26">
+    <row r="54" spans="1:33">
       <c r="A54">
         <v>55</v>
       </c>
@@ -5639,7 +5027,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:32">
+    <row r="55" spans="1:33">
       <c r="A55">
         <v>56</v>
       </c>
@@ -5699,7 +5087,7 @@
       </c>
       <c r="AF55" s="3"/>
     </row>
-    <row r="56" spans="1:32">
+    <row r="56" spans="1:33">
       <c r="A56">
         <v>57</v>
       </c>
@@ -5771,7 +5159,7 @@
       </c>
       <c r="AF56" s="3"/>
     </row>
-    <row r="57" spans="1:26">
+    <row r="57" spans="1:33">
       <c r="A57">
         <v>58</v>
       </c>
@@ -5842,7 +5230,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="58" spans="1:20">
+    <row r="58" spans="1:33">
       <c r="A58">
         <v>59</v>
       </c>
@@ -5868,7 +5256,7 @@
         <v>125</v>
       </c>
       <c r="J58" t="s">
-        <v>211</v>
+        <v>393</v>
       </c>
       <c r="L58">
         <v>3</v>
@@ -5892,18 +5280,18 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="59" spans="1:23">
+    <row r="59" spans="1:33">
       <c r="A59">
         <v>60</v>
       </c>
       <c r="B59" t="s">
+        <v>211</v>
+      </c>
+      <c r="C59" t="s">
         <v>212</v>
       </c>
-      <c r="C59" t="s">
+      <c r="D59" s="4" t="s">
         <v>213</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>214</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>81</v>
@@ -5918,7 +5306,7 @@
         <v>125</v>
       </c>
       <c r="J59" t="s">
-        <v>211</v>
+        <v>393</v>
       </c>
       <c r="L59">
         <v>3</v>
@@ -5951,18 +5339,18 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="60" spans="1:23">
+    <row r="60" spans="1:33">
       <c r="A60">
         <v>61</v>
       </c>
       <c r="B60" t="s">
+        <v>214</v>
+      </c>
+      <c r="C60" t="s">
         <v>215</v>
       </c>
-      <c r="C60" t="s">
+      <c r="D60" t="s">
         <v>216</v>
-      </c>
-      <c r="D60" t="s">
-        <v>217</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>57</v>
@@ -5977,7 +5365,7 @@
         <v>125</v>
       </c>
       <c r="J60" t="s">
-        <v>211</v>
+        <v>393</v>
       </c>
       <c r="L60">
         <v>2</v>
@@ -6010,18 +5398,18 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="61" spans="1:23">
+    <row r="61" spans="1:33">
       <c r="A61">
         <v>62</v>
       </c>
       <c r="B61" t="s">
+        <v>217</v>
+      </c>
+      <c r="C61" t="s">
         <v>218</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
         <v>219</v>
-      </c>
-      <c r="D61" t="s">
-        <v>220</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>81</v>
@@ -6072,18 +5460,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:23">
+    <row r="62" spans="1:33">
       <c r="A62">
         <v>63</v>
       </c>
       <c r="B62" t="s">
+        <v>220</v>
+      </c>
+      <c r="C62" t="s">
         <v>221</v>
       </c>
-      <c r="C62" t="s">
+      <c r="D62" t="s">
         <v>222</v>
-      </c>
-      <c r="D62" t="s">
-        <v>223</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>57</v>
@@ -6134,18 +5522,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="1:29">
+    <row r="63" spans="1:33">
       <c r="A63">
         <v>64</v>
       </c>
       <c r="B63" t="s">
+        <v>223</v>
+      </c>
+      <c r="C63" t="s">
         <v>224</v>
       </c>
-      <c r="C63" t="s">
+      <c r="D63" t="s">
         <v>225</v>
-      </c>
-      <c r="D63" t="s">
-        <v>226</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>57</v>
@@ -6163,7 +5551,7 @@
         <v>125</v>
       </c>
       <c r="J63" t="s">
-        <v>211</v>
+        <v>393</v>
       </c>
       <c r="L63">
         <v>6</v>
@@ -6214,15 +5602,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:23">
+    <row r="64" spans="1:33">
       <c r="A64">
         <v>65</v>
       </c>
       <c r="B64" t="s">
+        <v>226</v>
+      </c>
+      <c r="C64" t="s">
         <v>227</v>
-      </c>
-      <c r="C64" t="s">
-        <v>228</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>57</v>
@@ -6272,10 +5660,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
+        <v>228</v>
+      </c>
+      <c r="C65" t="s">
         <v>229</v>
-      </c>
-      <c r="C65" t="s">
-        <v>230</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>57</v>
@@ -6322,25 +5710,23 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I71"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.425" customWidth="1"/>
-    <col min="2" max="2" width="27.425" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
     <col min="4" max="4" width="33" customWidth="1"/>
-    <col min="5" max="5" width="19.2833333333333" customWidth="1"/>
-    <col min="6" max="6" width="18.8583333333333" customWidth="1"/>
-    <col min="7" max="8" width="10.2833333333333" customWidth="1"/>
-    <col min="9" max="9" width="15.1416666666667" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" customWidth="1"/>
+    <col min="7" max="8" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6358,19 +5744,19 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" t="s">
         <v>232</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>233</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>234</v>
-      </c>
-      <c r="I1" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6378,13 +5764,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D2" t="s">
         <v>236</v>
-      </c>
-      <c r="C2" t="s">
-        <v>236</v>
-      </c>
-      <c r="D2" t="s">
-        <v>237</v>
       </c>
       <c r="I2">
         <v>-1</v>
@@ -6395,19 +5781,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C3" t="s">
         <v>238</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>239</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>240</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>241</v>
-      </c>
-      <c r="F3" t="s">
-        <v>242</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -6418,16 +5804,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C4" t="s">
         <v>243</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>239</v>
+      </c>
+      <c r="E4" t="s">
         <v>244</v>
-      </c>
-      <c r="D4" t="s">
-        <v>240</v>
-      </c>
-      <c r="E4" t="s">
-        <v>245</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -6438,16 +5824,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>245</v>
+      </c>
+      <c r="C5" t="s">
         <v>246</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>239</v>
+      </c>
+      <c r="E5" t="s">
         <v>247</v>
-      </c>
-      <c r="D5" t="s">
-        <v>240</v>
-      </c>
-      <c r="E5" t="s">
-        <v>248</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -6458,13 +5844,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>248</v>
+      </c>
+      <c r="C6" t="s">
         <v>249</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>250</v>
-      </c>
-      <c r="D6" t="s">
-        <v>251</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -6475,16 +5861,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>251</v>
+      </c>
+      <c r="C7" t="s">
+        <v>251</v>
+      </c>
+      <c r="D7" t="s">
         <v>252</v>
       </c>
-      <c r="C7" t="s">
-        <v>252</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>253</v>
-      </c>
-      <c r="E7" t="s">
-        <v>254</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -6495,13 +5881,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>254</v>
+      </c>
+      <c r="C8" t="s">
+        <v>254</v>
+      </c>
+      <c r="D8" t="s">
         <v>255</v>
-      </c>
-      <c r="C8" t="s">
-        <v>255</v>
-      </c>
-      <c r="D8" t="s">
-        <v>256</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -6515,13 +5901,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -6535,13 +5921,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -6555,13 +5941,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
+        <v>258</v>
+      </c>
+      <c r="C11" t="s">
+        <v>258</v>
+      </c>
+      <c r="D11" t="s">
         <v>259</v>
-      </c>
-      <c r="C11" t="s">
-        <v>259</v>
-      </c>
-      <c r="D11" t="s">
-        <v>260</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -6572,16 +5958,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C12" t="s">
+        <v>260</v>
+      </c>
+      <c r="D12" t="s">
         <v>261</v>
       </c>
-      <c r="C12" t="s">
-        <v>261</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>262</v>
-      </c>
-      <c r="E12" t="s">
-        <v>263</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -6592,16 +5978,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
+        <v>263</v>
+      </c>
+      <c r="C13" t="s">
         <v>264</v>
       </c>
-      <c r="C13" t="s">
-        <v>265</v>
-      </c>
       <c r="D13" t="s">
+        <v>239</v>
+      </c>
+      <c r="E13" t="s">
         <v>240</v>
-      </c>
-      <c r="E13" t="s">
-        <v>241</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -6612,19 +5998,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
+        <v>265</v>
+      </c>
+      <c r="C14" t="s">
         <v>266</v>
       </c>
-      <c r="C14" t="s">
-        <v>267</v>
-      </c>
       <c r="D14" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -6635,16 +6021,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
+        <v>267</v>
+      </c>
+      <c r="C15" t="s">
+        <v>267</v>
+      </c>
+      <c r="D15" t="s">
         <v>268</v>
       </c>
-      <c r="C15" t="s">
-        <v>268</v>
-      </c>
-      <c r="D15" t="s">
-        <v>269</v>
-      </c>
       <c r="E15" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -6655,16 +6041,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
+        <v>269</v>
+      </c>
+      <c r="C16" t="s">
+        <v>269</v>
+      </c>
+      <c r="D16" t="s">
+        <v>239</v>
+      </c>
+      <c r="E16" t="s">
         <v>270</v>
-      </c>
-      <c r="C16" t="s">
-        <v>270</v>
-      </c>
-      <c r="D16" t="s">
-        <v>240</v>
-      </c>
-      <c r="E16" t="s">
-        <v>271</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -6675,13 +6061,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C17" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -6695,16 +6081,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
+        <v>272</v>
+      </c>
+      <c r="C18" t="s">
+        <v>272</v>
+      </c>
+      <c r="D18" t="s">
         <v>273</v>
       </c>
-      <c r="C18" t="s">
-        <v>273</v>
-      </c>
-      <c r="D18" t="s">
-        <v>274</v>
-      </c>
       <c r="E18" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -6715,13 +6101,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C19" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D19" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -6735,13 +6121,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
+        <v>275</v>
+      </c>
+      <c r="C20" t="s">
+        <v>275</v>
+      </c>
+      <c r="D20" t="s">
         <v>276</v>
-      </c>
-      <c r="C20" t="s">
-        <v>276</v>
-      </c>
-      <c r="D20" t="s">
-        <v>277</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -6755,16 +6141,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
+        <v>277</v>
+      </c>
+      <c r="C21" t="s">
+        <v>277</v>
+      </c>
+      <c r="D21" t="s">
+        <v>239</v>
+      </c>
+      <c r="E21" t="s">
         <v>278</v>
-      </c>
-      <c r="C21" t="s">
-        <v>278</v>
-      </c>
-      <c r="D21" t="s">
-        <v>240</v>
-      </c>
-      <c r="E21" t="s">
-        <v>279</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -6775,16 +6161,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
+        <v>279</v>
+      </c>
+      <c r="C22" t="s">
+        <v>279</v>
+      </c>
+      <c r="D22" t="s">
+        <v>252</v>
+      </c>
+      <c r="E22" t="s">
         <v>280</v>
-      </c>
-      <c r="C22" t="s">
-        <v>280</v>
-      </c>
-      <c r="D22" t="s">
-        <v>253</v>
-      </c>
-      <c r="E22" t="s">
-        <v>281</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -6795,13 +6181,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C23" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D23" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E23">
         <v>5</v>
@@ -6815,19 +6201,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C24" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D24" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -6838,13 +6224,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C25" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D25" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -6858,16 +6244,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C26" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D26" t="s">
+        <v>239</v>
+      </c>
+      <c r="E26" t="s">
         <v>240</v>
-      </c>
-      <c r="E26" t="s">
-        <v>241</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -6881,16 +6267,16 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C27" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D27" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E27" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -6901,13 +6287,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C28" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D28" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -6921,19 +6307,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
+        <v>287</v>
+      </c>
+      <c r="C29" t="s">
+        <v>287</v>
+      </c>
+      <c r="D29" t="s">
+        <v>255</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29" t="s">
         <v>288</v>
-      </c>
-      <c r="C29" t="s">
-        <v>288</v>
-      </c>
-      <c r="D29" t="s">
-        <v>256</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29" t="s">
-        <v>289</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -6947,13 +6333,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
+        <v>289</v>
+      </c>
+      <c r="C30" t="s">
         <v>290</v>
       </c>
-      <c r="C30" t="s">
-        <v>291</v>
-      </c>
       <c r="D30" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -6967,19 +6353,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
+        <v>291</v>
+      </c>
+      <c r="C31" t="s">
+        <v>291</v>
+      </c>
+      <c r="D31" t="s">
+        <v>239</v>
+      </c>
+      <c r="E31" t="s">
+        <v>240</v>
+      </c>
+      <c r="F31" t="s">
         <v>292</v>
-      </c>
-      <c r="C31" t="s">
-        <v>292</v>
-      </c>
-      <c r="D31" t="s">
-        <v>240</v>
-      </c>
-      <c r="E31" t="s">
-        <v>241</v>
-      </c>
-      <c r="F31" t="s">
-        <v>293</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -6990,19 +6376,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C32" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D32" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E32">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -7013,19 +6399,19 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C33" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D33" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E33">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -7036,16 +6422,16 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
+        <v>295</v>
+      </c>
+      <c r="C34" t="s">
+        <v>295</v>
+      </c>
+      <c r="D34" t="s">
+        <v>239</v>
+      </c>
+      <c r="E34" t="s">
         <v>296</v>
-      </c>
-      <c r="C34" t="s">
-        <v>296</v>
-      </c>
-      <c r="D34" t="s">
-        <v>240</v>
-      </c>
-      <c r="E34" t="s">
-        <v>297</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -7056,16 +6442,16 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
+        <v>297</v>
+      </c>
+      <c r="C35" t="s">
+        <v>297</v>
+      </c>
+      <c r="D35" t="s">
+        <v>239</v>
+      </c>
+      <c r="E35" t="s">
         <v>298</v>
-      </c>
-      <c r="C35" t="s">
-        <v>298</v>
-      </c>
-      <c r="D35" t="s">
-        <v>240</v>
-      </c>
-      <c r="E35" t="s">
-        <v>299</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -7076,19 +6462,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C36" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D36" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E36" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F36" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -7102,13 +6488,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
+        <v>300</v>
+      </c>
+      <c r="C37" t="s">
         <v>301</v>
       </c>
-      <c r="C37" t="s">
-        <v>302</v>
-      </c>
       <c r="D37" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E37">
         <v>11</v>
@@ -7122,16 +6508,16 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C38" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D38" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E38" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -7142,13 +6528,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C39" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D39" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -7165,16 +6551,16 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
+        <v>304</v>
+      </c>
+      <c r="C40" t="s">
         <v>305</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
+        <v>239</v>
+      </c>
+      <c r="E40" t="s">
         <v>306</v>
-      </c>
-      <c r="D40" t="s">
-        <v>240</v>
-      </c>
-      <c r="E40" t="s">
-        <v>307</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -7185,13 +6571,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C41" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D41" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -7208,19 +6594,19 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C42" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D42" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -7234,13 +6620,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C43" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D43" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E43">
         <v>12</v>
@@ -7254,13 +6640,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C44" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D44" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E44">
         <v>13</v>
@@ -7274,19 +6660,19 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C45" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D45" t="s">
+        <v>239</v>
+      </c>
+      <c r="E45" t="s">
         <v>240</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>241</v>
-      </c>
-      <c r="F45" t="s">
-        <v>242</v>
       </c>
       <c r="I45">
         <v>-1</v>
@@ -7297,16 +6683,16 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D46" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E46" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I46">
         <v>1</v>
@@ -7317,13 +6703,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C47" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D47" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E47">
         <v>14</v>
@@ -7337,19 +6723,19 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
+        <v>314</v>
+      </c>
+      <c r="C48" t="s">
+        <v>314</v>
+      </c>
+      <c r="D48" t="s">
         <v>315</v>
       </c>
-      <c r="C48" t="s">
-        <v>315</v>
-      </c>
-      <c r="D48" t="s">
-        <v>316</v>
-      </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I48">
         <v>-1</v>
@@ -7360,13 +6746,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C49" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D49" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E49">
         <v>15</v>
@@ -7380,19 +6766,19 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C50" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D50" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I50">
         <v>-1</v>
@@ -7403,13 +6789,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C51" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D51" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E51">
         <v>16</v>
@@ -7423,13 +6809,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C52" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D52" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -7443,13 +6829,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C53" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E53">
         <v>3</v>
@@ -7463,13 +6849,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C54" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D54" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E54">
         <v>3</v>
@@ -7486,16 +6872,16 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C55" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D55" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E55" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G55">
         <v>6</v>
@@ -7509,16 +6895,16 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C56" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D56" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G56">
         <v>7</v>
@@ -7532,16 +6918,16 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
+        <v>324</v>
+      </c>
+      <c r="C57" t="s">
         <v>325</v>
       </c>
-      <c r="C57" t="s">
-        <v>326</v>
-      </c>
       <c r="D57" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E57" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G57">
         <v>8</v>
@@ -7555,16 +6941,16 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
+        <v>326</v>
+      </c>
+      <c r="C58" t="s">
         <v>327</v>
       </c>
-      <c r="C58" t="s">
-        <v>328</v>
-      </c>
       <c r="D58" t="s">
+        <v>239</v>
+      </c>
+      <c r="E58" t="s">
         <v>240</v>
-      </c>
-      <c r="E58" t="s">
-        <v>241</v>
       </c>
       <c r="G58">
         <v>6</v>
@@ -7578,16 +6964,16 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C59" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D59" t="s">
+        <v>239</v>
+      </c>
+      <c r="E59" t="s">
         <v>240</v>
-      </c>
-      <c r="E59" t="s">
-        <v>241</v>
       </c>
       <c r="G59">
         <v>7</v>
@@ -7601,16 +6987,16 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C60" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D60" t="s">
+        <v>239</v>
+      </c>
+      <c r="E60" t="s">
         <v>240</v>
-      </c>
-      <c r="E60" t="s">
-        <v>241</v>
       </c>
       <c r="G60">
         <v>8</v>
@@ -7624,19 +7010,19 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C61" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D61" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E61">
         <v>3</v>
       </c>
       <c r="F61" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I61">
         <v>-1</v>
@@ -7647,13 +7033,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C62" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D62" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E62">
         <v>20</v>
@@ -7662,21 +7048,21 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="63" customFormat="1" spans="1:9">
+    <row r="63" spans="1:9">
       <c r="A63">
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C63" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D63" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F63" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I63">
         <v>-1</v>
@@ -7687,13 +7073,13 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C64" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D64" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E64">
         <v>21</v>
@@ -7707,13 +7093,13 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C65" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D65" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E65">
         <v>3</v>
@@ -7722,24 +7108,24 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="66" customFormat="1" spans="1:9">
+    <row r="66" spans="1:9">
       <c r="A66">
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C66" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D66" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E66">
         <v>14</v>
       </c>
       <c r="F66" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I66">
         <v>-1</v>
@@ -7750,13 +7136,13 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C67" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D67" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E67">
         <v>22</v>
@@ -7770,13 +7156,13 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
+        <v>337</v>
+      </c>
+      <c r="D68" t="s">
         <v>338</v>
       </c>
-      <c r="D68" t="s">
-        <v>339</v>
-      </c>
       <c r="E68" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I68">
         <v>-1</v>
@@ -7787,13 +7173,13 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D69" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E69" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I69">
         <v>-1</v>
@@ -7804,13 +7190,13 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
+        <v>340</v>
+      </c>
+      <c r="D70" t="s">
         <v>341</v>
       </c>
-      <c r="D70" t="s">
+      <c r="E70" t="s">
         <v>342</v>
-      </c>
-      <c r="E70" t="s">
-        <v>343</v>
       </c>
       <c r="I70">
         <v>-1</v>
@@ -7821,13 +7207,13 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D71" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E71" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I71">
         <v>-1</v>
@@ -7835,26 +7221,24 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.425" customWidth="1"/>
-    <col min="2" max="2" width="27.425" customWidth="1"/>
-    <col min="3" max="3" width="14.425" customWidth="1"/>
-    <col min="4" max="5" width="16.1416666666667" customWidth="1"/>
-    <col min="6" max="6" width="12.425" customWidth="1"/>
-    <col min="7" max="7" width="14.425" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
+    <col min="4" max="5" width="16.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="10.1416666666667" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7866,13 +7250,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D1" t="s">
         <v>345</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>347</v>
       </c>
       <c r="F1" t="s">
         <v>17</v>
@@ -7899,21 +7283,21 @@
         <v>27</v>
       </c>
       <c r="N1" t="s">
+        <v>347</v>
+      </c>
+      <c r="O1" t="s">
         <v>348</v>
       </c>
-      <c r="O1" t="s">
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>350</v>
-      </c>
-      <c r="C2" t="s">
-        <v>351</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -7934,15 +7318,15 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -7957,15 +7341,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -7974,15 +7358,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:15">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>353</v>
+      </c>
+      <c r="C5" t="s">
         <v>354</v>
-      </c>
-      <c r="C5" t="s">
-        <v>355</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -8009,15 +7393,15 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:15">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -8032,15 +7416,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:15">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -8055,15 +7439,15 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:15">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -8078,15 +7462,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:15">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -8101,15 +7485,15 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:15">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -8124,15 +7508,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:15">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C11" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -8153,15 +7537,15 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:15">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C12" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -8182,15 +7566,15 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:15">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C13" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -8205,15 +7589,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:15">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C14" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -8228,15 +7612,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:15">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C15" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -8251,15 +7635,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:15">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C16" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -8279,10 +7663,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C17" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -8302,10 +7686,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C18" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -8320,15 +7704,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -8337,15 +7721,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C20" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -8354,15 +7738,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C21" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -8376,10 +7760,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C22" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -8399,10 +7783,10 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C23" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -8422,10 +7806,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C24" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -8445,10 +7829,10 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C25" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -8468,10 +7852,10 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C26" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -8491,10 +7875,10 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C27" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -8514,10 +7898,10 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C28" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -8537,10 +7921,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C29" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -8560,10 +7944,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C30" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -8583,10 +7967,10 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C31" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -8606,10 +7990,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C32" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -8629,10 +8013,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C33" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -8652,10 +8036,10 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C34" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -8672,24 +8056,22 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85833333333333" customWidth="1"/>
-    <col min="2" max="2" width="22.7083333333333" customWidth="1"/>
-    <col min="3" max="3" width="28.5666666666667" customWidth="1"/>
-    <col min="4" max="4" width="15.5666666666667" customWidth="1"/>
-    <col min="5" max="5" width="16.1416666666667" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="11.1416666666667" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -8703,30 +8085,30 @@
         <v>5</v>
       </c>
       <c r="D1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E1" t="s">
         <v>376</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>377</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>378</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>380</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>381</v>
-      </c>
-      <c r="D2" t="s">
-        <v>382</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -8735,52 +8117,52 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="12.95" customHeight="1" spans="1:6">
+    <row r="3" spans="1:7" ht="12.95" customHeight="1">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>382</v>
+      </c>
+      <c r="C3" t="s">
         <v>383</v>
       </c>
-      <c r="C3" t="s">
-        <v>384</v>
-      </c>
       <c r="D3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" ht="12.95" customHeight="1" spans="1:6">
+    <row r="4" spans="1:7" ht="12.95" customHeight="1">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C5" t="s">
+        <v>380</v>
+      </c>
+      <c r="D5" t="s">
         <v>381</v>
-      </c>
-      <c r="D5" t="s">
-        <v>382</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -8789,18 +8171,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C6" t="s">
+        <v>380</v>
+      </c>
+      <c r="D6" t="s">
         <v>381</v>
-      </c>
-      <c r="D6" t="s">
-        <v>382</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -8809,18 +8191,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C7" t="s">
+        <v>380</v>
+      </c>
+      <c r="D7" t="s">
         <v>381</v>
-      </c>
-      <c r="D7" t="s">
-        <v>382</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -8829,18 +8211,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C8" t="s">
+        <v>380</v>
+      </c>
+      <c r="D8" t="s">
         <v>381</v>
-      </c>
-      <c r="D8" t="s">
-        <v>382</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -8849,18 +8231,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C9" t="s">
+        <v>380</v>
+      </c>
+      <c r="D9" t="s">
         <v>381</v>
-      </c>
-      <c r="D9" t="s">
-        <v>382</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -8869,18 +8251,18 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C10" t="s">
+        <v>380</v>
+      </c>
+      <c r="D10" t="s">
         <v>381</v>
-      </c>
-      <c r="D10" t="s">
-        <v>382</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -8889,18 +8271,18 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
+        <v>391</v>
+      </c>
+      <c r="C11" t="s">
         <v>392</v>
       </c>
-      <c r="C11" t="s">
-        <v>393</v>
-      </c>
       <c r="D11" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E11" t="s">
         <v>44</v>
@@ -8911,7 +8293,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Cards.xlsx
+++ b/Assets/StreamingAssets/Configurations/Cards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA0FBF0A-7FAD-4F89-97EF-B2A0B61F6812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10DE11E-A0D9-4062-90B4-175373358093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="394">
   <si>
     <t>ID</t>
   </si>
@@ -147,445 +147,586 @@
     <t>参数+7</t>
   </si>
   <si>
+    <t>参数+X1$1212</t>
+  </si>
+  <si>
+    <t>Basic</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Stamina</t>
+  </si>
+  <si>
+    <t>喝水</t>
+  </si>
+  <si>
+    <t>神采+4</t>
+  </si>
+  <si>
+    <t>神采+X1</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>闪耀</t>
+  </si>
+  <si>
+    <t>参数+15，红温大于10层时，参数+9</t>
+  </si>
+  <si>
+    <t>参数+X1，红温大于10层时，参数+X2</t>
+  </si>
+  <si>
+    <t>Common</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>angry</t>
+  </si>
+  <si>
+    <t>战术喝水</t>
+  </si>
+  <si>
+    <t>参数+5，神采+4</t>
+  </si>
+  <si>
+    <t>参数+X1，神采+X2</t>
+  </si>
+  <si>
+    <t>kale</t>
+  </si>
+  <si>
+    <t>下一张使用的牌会使用两次，抽一张卡,神采+2</t>
+  </si>
+  <si>
+    <t>下一张使用的牌会使用两次，抽X3张卡,神采+X2</t>
+  </si>
+  <si>
+    <t>Epic</t>
+  </si>
+  <si>
+    <t>Buff</t>
+  </si>
+  <si>
+    <t>刷新</t>
+  </si>
+  <si>
+    <t>重抽其他手牌，卡牌使用次数+1，体力消耗减少50%+2回合</t>
+  </si>
+  <si>
+    <t>重抽其他手牌，卡牌使用次数+X3，体力消耗减少50%+X2回合</t>
+  </si>
+  <si>
+    <t>才八点</t>
+  </si>
+  <si>
+    <t>获得一个额外回合，神采+7，出牌次数+1</t>
+  </si>
+  <si>
+    <t>获得一个额外回合，神采+X1，出牌次数+X2</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>wink</t>
+  </si>
+  <si>
+    <t>亲和力+3，神采+2</t>
+  </si>
+  <si>
+    <t>亲和力+X1，神采+X2</t>
+  </si>
+  <si>
+    <t>集中</t>
+  </si>
+  <si>
+    <t>专注+2，神采+2</t>
+  </si>
+  <si>
+    <t>专注+X1，神采+X2</t>
+  </si>
+  <si>
+    <t>生气</t>
+  </si>
+  <si>
+    <t>红温+2，神采+2</t>
+  </si>
+  <si>
+    <t>红温+X1，神采+X2</t>
+  </si>
+  <si>
+    <t>二次推流</t>
+  </si>
+  <si>
+    <t>参数+9/2次</t>
+  </si>
+  <si>
+    <t>参数+X1/2次</t>
+  </si>
+  <si>
+    <t>加分动画显示需改进</t>
+  </si>
+  <si>
+    <t>才艺</t>
+  </si>
+  <si>
+    <t>参数+11，神采+7</t>
+  </si>
+  <si>
+    <t>Rare</t>
+  </si>
+  <si>
+    <t>小花花</t>
+  </si>
+  <si>
+    <t>亲和力+6</t>
+  </si>
+  <si>
+    <t>亲和力+X1</t>
+  </si>
+  <si>
+    <t>饭撒</t>
+  </si>
+  <si>
+    <t>获得亲和力140%的参数</t>
+  </si>
+  <si>
+    <t>获得亲和力X1的参数</t>
+  </si>
+  <si>
+    <t>desuwa</t>
+  </si>
+  <si>
+    <t>亲和力+4，获得亲和力层数80%的参数</t>
+  </si>
+  <si>
+    <t>亲和力+X1，获得亲和力层数X2的参数</t>
+  </si>
+  <si>
+    <t>欢迎上舰</t>
+  </si>
+  <si>
+    <t>舰长+1，神采+4，体力消耗减少+2回合</t>
+  </si>
+  <si>
+    <t>舰长+X1，神采+X2，体力消耗减少+X3回合</t>
+  </si>
+  <si>
+    <t>revenue</t>
+  </si>
+  <si>
+    <t>攻击弹幕</t>
+  </si>
+  <si>
+    <t>红温+5</t>
+  </si>
+  <si>
+    <t>红温+X1</t>
+  </si>
+  <si>
+    <t>神降临</t>
+  </si>
+  <si>
+    <t>专注+1，以后，每回合结束时，专注+2</t>
+  </si>
+  <si>
+    <t>专注+X2，以后，每回合结束时，以后回合结束时专注+X1</t>
+  </si>
+  <si>
+    <t>点名弹幕</t>
+  </si>
+  <si>
+    <t>在有红温的状态下可使用，参数+24</t>
+  </si>
+  <si>
+    <t>在有红温的状态下可使用，参数+X1</t>
+  </si>
+  <si>
+    <t>激怒</t>
+  </si>
+  <si>
+    <t>体力消耗增加50%+2回合，参数+30，神采+5</t>
+  </si>
+  <si>
+    <t>体力消耗增加50%+X1回合，参数+X2，神采+X3</t>
+  </si>
+  <si>
+    <t>美丽动人</t>
+  </si>
+  <si>
+    <t>亲和力+2，以后，每当使用M卡时，亲和力+1</t>
+  </si>
+  <si>
+    <t>亲和力+X1，以后，每当使用M卡时，亲和力+X2</t>
+  </si>
+  <si>
+    <t>小巧思</t>
+  </si>
+  <si>
+    <t>亲和力+5，神采+1</t>
+  </si>
+  <si>
+    <t>冲刺！</t>
+  </si>
+  <si>
+    <t>红温+3，参数+8</t>
+  </si>
+  <si>
+    <t>红温+X1，参数+X2</t>
+  </si>
+  <si>
+    <t>闭眼</t>
+  </si>
+  <si>
+    <t>专注+3</t>
+  </si>
+  <si>
+    <t>专注+X1</t>
+  </si>
+  <si>
+    <t>小憩</t>
+  </si>
+  <si>
+    <t>专注+3，神采+4</t>
+  </si>
+  <si>
+    <t>警告！</t>
+  </si>
+  <si>
+    <t>在红温的状态下可用，参数+12，红温大于10层时，参数+24，红温大于30层时，参数+36</t>
+  </si>
+  <si>
+    <t>在红温的状态下可用，参数+X1，红温大于10层时，参数+X2，红温大于30层时，参数+X3</t>
+  </si>
+  <si>
+    <t>躺</t>
+  </si>
+  <si>
+    <t>神采+6</t>
+  </si>
+  <si>
+    <t>fun</t>
+  </si>
+  <si>
+    <t>SC</t>
+  </si>
+  <si>
+    <t>沪币+30，神采+3，体力消耗减少+2回合</t>
+  </si>
+  <si>
+    <t>流水+X1，神采+X2，体力消耗减少50%+X3回合</t>
+  </si>
+  <si>
+    <t>直播通知</t>
+  </si>
+  <si>
+    <t>同接+50，神采+2</t>
+  </si>
+  <si>
+    <t>同接+X1，神采+X2</t>
+  </si>
+  <si>
+    <t>YLG</t>
+  </si>
+  <si>
+    <t>同接+20，以后，每当打出A卡时，同接+10</t>
+  </si>
+  <si>
+    <t>同接+X1，以后，每当打出A卡时，同接+X2</t>
+  </si>
+  <si>
+    <t>爆米</t>
+  </si>
+  <si>
+    <t>获得同接数20%的流水</t>
+  </si>
+  <si>
+    <t>爆！</t>
+  </si>
+  <si>
+    <t>参数+38，红温大于30层时，卡牌使用次数+1</t>
+  </si>
+  <si>
+    <t>参数+X1，红温大于30层时，卡牌使用次数+1</t>
+  </si>
+  <si>
+    <t>越想越气</t>
+  </si>
+  <si>
+    <t>红温+2，有红温的状态下，红温+2，红温大于30层时，红温+4</t>
+  </si>
+  <si>
+    <t>红温+X1，有红温的状态下，红温+2，红温大于30层时，红温+4</t>
+  </si>
+  <si>
+    <t>为我欢呼</t>
+  </si>
+  <si>
+    <t>幽默+1，以后每当使用M卡时，幽默+1</t>
+  </si>
+  <si>
+    <t>幽默+X1，以后每当使用M卡时，幽默+1</t>
+  </si>
+  <si>
+    <t>红温+3，神采+6</t>
+  </si>
+  <si>
+    <t>观察</t>
+  </si>
+  <si>
+    <t>专注+3，神采+6</t>
+  </si>
+  <si>
+    <t>首页推送</t>
+  </si>
+  <si>
+    <t>体力消耗减少50%+4回合，神采+3</t>
+  </si>
+  <si>
+    <t>体力消耗减少50%+X1回合，神采+X2</t>
+  </si>
+  <si>
+    <t>补充营养</t>
+  </si>
+  <si>
+    <t>体力消耗减少1点，神采+5</t>
+  </si>
+  <si>
+    <t>体力消耗减少X1点，神采+X2</t>
+  </si>
+  <si>
+    <t>距离感</t>
+  </si>
+  <si>
+    <t>专注+4，体力回复4</t>
+  </si>
+  <si>
+    <t>专注+X1，体力回复X2点</t>
+  </si>
+  <si>
+    <t>亲切</t>
+  </si>
+  <si>
+    <t>亲和力+3，亲和力大于三层时，亲和力+2</t>
+  </si>
+  <si>
+    <t>亲和力+X1，亲和力大于三层时，亲和力+X2</t>
+  </si>
+  <si>
+    <t>最初的神降临</t>
+  </si>
+  <si>
+    <t>专注+1，以后每当打出A卡时，专注+1</t>
+  </si>
+  <si>
+    <t>专注+X1，以后每当打出A卡时，专注+1</t>
+  </si>
+  <si>
+    <t>迷人</t>
+  </si>
+  <si>
+    <t>亲和力+5，卡牌使用次数+1，获得亲和力90%的参数</t>
+  </si>
+  <si>
+    <t>亲和力+X1，手牌使用次数+X2，亲和力X3的参数获得</t>
+  </si>
+  <si>
+    <t>申请对线</t>
+  </si>
+  <si>
+    <t>红温+2，之后4回合内，回合结束时，参数+8</t>
+  </si>
+  <si>
+    <t>红温+X1，之后4回合内，回合结束时，参数+X2</t>
+  </si>
+  <si>
+    <t>子弹时间</t>
+  </si>
+  <si>
+    <t>专注+7，体力消耗增加+2回合，神采+7</t>
+  </si>
+  <si>
+    <t>专注+X1，体力消耗增加50%+X2回合，神采+X3</t>
+  </si>
+  <si>
+    <t>哭唧唧</t>
+  </si>
+  <si>
+    <t>流水+40，同接+30，舰长+1</t>
+  </si>
+  <si>
+    <t>流水+X1，同接+X2，舰长+X3</t>
+  </si>
+  <si>
+    <t>耶！</t>
+  </si>
+  <si>
+    <t>参数+10</t>
+  </si>
+  <si>
     <t>参数+X1</t>
   </si>
   <si>
-    <t>Basic</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>Stamina</t>
-  </si>
-  <si>
-    <t>喝水</t>
-  </si>
-  <si>
-    <t>神采+4</t>
-  </si>
-  <si>
-    <t>神采+X1</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>闪耀</t>
-  </si>
-  <si>
-    <t>参数+15，红温大于10层时，参数+9</t>
-  </si>
-  <si>
-    <t>参数+X1，红温大于10层时，参数+X2</t>
-  </si>
-  <si>
-    <t>Common</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>angry</t>
-  </si>
-  <si>
-    <t>战术喝水</t>
-  </si>
-  <si>
-    <t>参数+5，神采+4</t>
-  </si>
-  <si>
-    <t>参数+X1，神采+X2</t>
-  </si>
-  <si>
-    <t>kale</t>
-  </si>
-  <si>
-    <t>下一张使用的牌会使用两次，抽一张卡,神采+2</t>
-  </si>
-  <si>
-    <t>下一张使用的牌会使用两次，抽X3张卡,神采+X2</t>
-  </si>
-  <si>
-    <t>Epic</t>
-  </si>
-  <si>
-    <t>Buff</t>
-  </si>
-  <si>
-    <t>刷新</t>
-  </si>
-  <si>
-    <t>重抽其他手牌，卡牌使用次数+1，体力消耗减少50%+2回合</t>
-  </si>
-  <si>
-    <t>重抽其他手牌，卡牌使用次数+X3，体力消耗减少50%+X2回合</t>
-  </si>
-  <si>
-    <t>才八点</t>
-  </si>
-  <si>
-    <t>获得一个额外回合，神采+7，出牌次数+1</t>
-  </si>
-  <si>
-    <t>获得一个额外回合，神采+X1，出牌次数+X2</t>
-  </si>
-  <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>wink</t>
-  </si>
-  <si>
-    <t>亲和力+3，神采+2</t>
-  </si>
-  <si>
-    <t>亲和力+X1，神采+X2</t>
-  </si>
-  <si>
-    <t>集中</t>
-  </si>
-  <si>
-    <t>专注+2，神采+2</t>
-  </si>
-  <si>
-    <t>专注+X1，神采+X2</t>
-  </si>
-  <si>
-    <t>生气</t>
-  </si>
-  <si>
-    <t>红温+2，神采+2</t>
-  </si>
-  <si>
-    <t>红温+X1，神采+X2</t>
-  </si>
-  <si>
-    <t>二次推流</t>
-  </si>
-  <si>
-    <t>参数+9/2次</t>
-  </si>
-  <si>
-    <t>参数+X1/2次</t>
-  </si>
-  <si>
-    <t>加分动画显示需改进</t>
-  </si>
-  <si>
-    <t>才艺</t>
-  </si>
-  <si>
-    <t>参数+11，神采+7</t>
-  </si>
-  <si>
-    <t>Rare</t>
-  </si>
-  <si>
-    <t>小花花</t>
-  </si>
-  <si>
-    <t>亲和力+6</t>
-  </si>
-  <si>
-    <t>亲和力+X1</t>
-  </si>
-  <si>
-    <t>饭撒</t>
-  </si>
-  <si>
-    <t>获得亲和力140%的参数</t>
-  </si>
-  <si>
-    <t>获得亲和力X1的参数</t>
-  </si>
-  <si>
-    <t>desuwa</t>
-  </si>
-  <si>
-    <t>亲和力+4，获得亲和力层数80%的参数</t>
-  </si>
-  <si>
-    <t>亲和力+X1，获得亲和力层数X2的参数</t>
-  </si>
-  <si>
-    <t>欢迎上舰</t>
-  </si>
-  <si>
-    <t>舰长+1，神采+4，体力消耗减少+2回合</t>
-  </si>
-  <si>
-    <t>舰长+X1，神采+X2，体力消耗减少+X3回合</t>
-  </si>
-  <si>
-    <t>revenue</t>
-  </si>
-  <si>
-    <t>攻击弹幕</t>
-  </si>
-  <si>
-    <t>红温+5</t>
-  </si>
-  <si>
-    <t>红温+X1$红温变为1.5倍</t>
-  </si>
-  <si>
-    <t>神降临</t>
-  </si>
-  <si>
-    <t>专注+1，以后，每回合结束时，专注+2</t>
-  </si>
-  <si>
-    <t>点名弹幕</t>
-  </si>
-  <si>
-    <t>在有红温的状态下可使用，参数+24</t>
-  </si>
-  <si>
-    <t>激怒</t>
-  </si>
-  <si>
-    <t>体力消耗增加50%+2回合，参数+30，神采+5</t>
-  </si>
-  <si>
-    <t>美丽动人</t>
-  </si>
-  <si>
-    <t>亲和力+2，以后，每当使用M卡时，亲和力+1</t>
-  </si>
-  <si>
-    <t>小巧思</t>
-  </si>
-  <si>
-    <t>亲和力+5，神采+1</t>
-  </si>
-  <si>
-    <t>冲刺！</t>
-  </si>
-  <si>
-    <t>红温+3，参数+8</t>
-  </si>
-  <si>
-    <t>闭眼</t>
-  </si>
-  <si>
-    <t>专注+3</t>
-  </si>
-  <si>
-    <t>小憩</t>
-  </si>
-  <si>
-    <t>专注+3，神采+4</t>
-  </si>
-  <si>
-    <t>警告！</t>
-  </si>
-  <si>
-    <t>在红温的状态下可用，参数+12，红温大于10层时，参数+24，红温大于30层时，参数+36</t>
-  </si>
-  <si>
-    <t>躺</t>
-  </si>
-  <si>
-    <t>神采+6</t>
-  </si>
-  <si>
-    <t>fun</t>
-  </si>
-  <si>
-    <t>SC</t>
-  </si>
-  <si>
-    <t>沪币+30，神采+3，体力消耗减少+2回合</t>
-  </si>
-  <si>
-    <t>直播通知</t>
-  </si>
-  <si>
-    <t>同接+50，神采+2</t>
-  </si>
-  <si>
-    <t>YLG</t>
-  </si>
-  <si>
-    <t>同接+20，以后，每当打出A卡时，同接+10</t>
-  </si>
-  <si>
-    <t>爆米</t>
-  </si>
-  <si>
-    <t>获得同接数20%的流水</t>
-  </si>
-  <si>
-    <t>爆！</t>
-  </si>
-  <si>
-    <t>参数+38，红温大于30层时，卡牌使用次数+1</t>
-  </si>
-  <si>
-    <t>越想越气</t>
-  </si>
-  <si>
-    <t>红温+2，有红温的状态下，红温+2，红温大于30层时，红温+4</t>
-  </si>
-  <si>
-    <t>为我欢呼</t>
-  </si>
-  <si>
-    <t>幽默+1，以后每当使用M卡时，幽默+1</t>
-  </si>
-  <si>
-    <t>红温+3，神采+6</t>
-  </si>
-  <si>
-    <t>观察</t>
-  </si>
-  <si>
-    <t>专注+3，神采+6</t>
-  </si>
-  <si>
-    <t>首页推送</t>
-  </si>
-  <si>
-    <t>体力消耗减少50%+4回合，神采+3</t>
-  </si>
-  <si>
-    <t>补充营养</t>
-  </si>
-  <si>
-    <t>体力消耗减少1点，神采+5</t>
-  </si>
-  <si>
-    <t>距离感</t>
-  </si>
-  <si>
-    <t>专注+4，体力回复4</t>
-  </si>
-  <si>
-    <t>亲切</t>
-  </si>
-  <si>
-    <t>亲和力+3，亲和力大于三层时，亲和力+2</t>
-  </si>
-  <si>
-    <t>最初的神降临</t>
-  </si>
-  <si>
-    <t>专注+1，以后每当打出A卡时，专注+1</t>
-  </si>
-  <si>
-    <t>迷人</t>
-  </si>
-  <si>
-    <t>亲和力+5，卡牌使用次数+1，获得亲和力90%的参数</t>
-  </si>
-  <si>
-    <t>申请对线</t>
-  </si>
-  <si>
-    <t>红温+2，之后4回合内，回合结束时，参数+8</t>
-  </si>
-  <si>
-    <t>子弹时间</t>
-  </si>
-  <si>
-    <t>专注+7，体力消耗增加+2回合，神采+7</t>
-  </si>
-  <si>
-    <t>哭唧唧</t>
-  </si>
-  <si>
-    <t>流水+40，同接+30，舰长+1</t>
-  </si>
-  <si>
-    <t>耶！</t>
-  </si>
-  <si>
-    <t>参数+10</t>
-  </si>
-  <si>
     <t>参数+8，亲和力+3</t>
   </si>
   <si>
+    <t>参数+X1，亲和力+X2</t>
+  </si>
+  <si>
     <t>玩梗</t>
   </si>
   <si>
     <t>参数+7，幽默+2</t>
   </si>
   <si>
+    <t>参数+X1，幽默+X2</t>
+  </si>
+  <si>
     <t>盯~</t>
   </si>
   <si>
     <t>亲和力+5，获得亲和力110%的参数</t>
   </si>
   <si>
+    <t>亲和力+X1，获得亲和力X2的参数</t>
+  </si>
+  <si>
     <t>氛围感</t>
   </si>
   <si>
     <t>亲和力+1，以后，回合结束时，亲和力+3</t>
   </si>
   <si>
+    <t>亲和力+X1，以后，回合结束时，亲和力+3</t>
+  </si>
+  <si>
     <t>拿个快递</t>
   </si>
   <si>
     <t>抽两张牌，体力消耗减少+2回合</t>
   </si>
   <si>
+    <t>抽X1张牌，体力消耗减少50%+X2回合</t>
+  </si>
+  <si>
     <t>点炮仗</t>
   </si>
   <si>
     <t>红温&gt;10层时可使用，获得红温300%的参数，红温减少50%</t>
   </si>
   <si>
+    <t>红温&gt;10层时可使用，获得红温X1的参数，红温减少X2</t>
+  </si>
+  <si>
     <t>逼逼赖赖</t>
   </si>
   <si>
     <t>红温+3，卡牌使用次数+1，如果红温大于10层，红温+3</t>
   </si>
   <si>
+    <t>红温+X1，卡牌使用次数+X2，如果红温大于10层，红温+X2</t>
+  </si>
+  <si>
     <t>雷区</t>
   </si>
   <si>
     <t>红温+1，以后每当使用A卡的时候，红温+1</t>
   </si>
   <si>
+    <t>红温+X1，以后每当使用A卡的时候，红温+1</t>
+  </si>
+  <si>
     <t>自洽</t>
   </si>
   <si>
     <t>幽默+3，参数+12，卡牌使用次数+1</t>
   </si>
   <si>
+    <t>幽默+X1，参数+X2，卡牌使用次数+X</t>
+  </si>
+  <si>
     <t>封禁</t>
   </si>
   <si>
     <t>神采+5两次，获得神采70%的参数</t>
   </si>
   <si>
+    <t>神采+X1两次，获得神采X2的参数</t>
+  </si>
+  <si>
     <t>节目效果</t>
   </si>
   <si>
     <t>获得神采120%的参数</t>
   </si>
   <si>
+    <t>获得神采X1%的参数</t>
+  </si>
+  <si>
     <t>LLBC</t>
   </si>
   <si>
     <t>神采+7，获得神采90%的参数</t>
   </si>
   <si>
+    <t>神采+X1，获得神采X2%的参数</t>
+  </si>
+  <si>
     <t>大爆特爆</t>
   </si>
   <si>
     <t>消耗所有神采，获得消耗神采300%的参数</t>
   </si>
   <si>
+    <t>消耗所有神采，获得消耗神采X1的参数</t>
+  </si>
+  <si>
     <t>冷笑话</t>
   </si>
   <si>
-    <t>获得神采100%的参数，下一回合抽一张卡牌</t>
+    <t>获得神采120%的参数，下一回合抽一张卡牌</t>
+  </si>
+  <si>
+    <t>获得神采X1%的参数，下一回合抽一张卡牌</t>
+  </si>
+  <si>
+    <t>好娇娇</t>
+  </si>
+  <si>
+    <t>红温+6，幽默+6</t>
+  </si>
+  <si>
+    <t>红温+X1，幽默+X2</t>
+  </si>
+  <si>
+    <t>窝里横</t>
+  </si>
+  <si>
+    <t>同接-30，参数+32，神采+15，获得神采150%的参数</t>
+  </si>
+  <si>
+    <t>同接-30，参数+X2，神采+X3，获得神采X4%的参数</t>
+  </si>
+  <si>
+    <t>养</t>
+  </si>
+  <si>
+    <t>同接+50，获得同接10%的神采</t>
+  </si>
+  <si>
+    <t>gachi距离</t>
+  </si>
+  <si>
+    <t>舰长+1，获得舰长数100%的参数</t>
   </si>
   <si>
     <t>Parameter</t>
@@ -909,6 +1050,27 @@
     <t>回合结束时，幽默+1</t>
   </si>
   <si>
+    <t>获得神采X%的参数</t>
+  </si>
+  <si>
+    <t>VAddParamAttributePercentageEffect</t>
+  </si>
+  <si>
+    <t>神采变为X%</t>
+  </si>
+  <si>
+    <t>获得等同于同接X%的神采</t>
+  </si>
+  <si>
+    <t>VAddPercentageFromAttributeEffect</t>
+  </si>
+  <si>
+    <t>BAViewerCount,BAShield</t>
+  </si>
+  <si>
+    <t>获得舰长数X%的参数</t>
+  </si>
+  <si>
     <t>BuffType</t>
   </si>
   <si>
@@ -966,9 +1128,6 @@
     <t>盐应对</t>
   </si>
   <si>
-    <t>好娇娇</t>
-  </si>
-  <si>
     <t>每当使用A卡时，红温+1</t>
   </si>
   <si>
@@ -1057,6 +1216,9 @@
   </si>
   <si>
     <t>VCardTypeUsedCountCondition</t>
+  </si>
+  <si>
+    <t>TrueStamina</t>
   </si>
 </sst>
 </file>
@@ -1072,12 +1234,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1122,18 +1290,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1419,7 +1588,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI61"/>
+  <dimension ref="A1:AI65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.42578125" customWidth="1"/>
@@ -1612,7 +1781,7 @@
       <c r="AC2"/>
       <c r="AE2"/>
       <c r="AG2"/>
-      <c r="AH2" s="5"/>
+      <c r="AH2" s="6"/>
     </row>
     <row r="3" spans="1:35">
       <c r="A3">
@@ -1667,7 +1836,7 @@
       <c r="AC3"/>
       <c r="AE3"/>
       <c r="AG3"/>
-      <c r="AH3" s="5"/>
+      <c r="AH3" s="6"/>
     </row>
     <row r="4" spans="1:35">
       <c r="A4">
@@ -1727,7 +1896,7 @@
       <c r="W4" s="3">
         <v>12</v>
       </c>
-      <c r="AH4" s="5"/>
+      <c r="AH4" s="6"/>
     </row>
     <row r="5" spans="1:35">
       <c r="A5">
@@ -1790,7 +1959,7 @@
       <c r="AC5"/>
       <c r="AE5"/>
       <c r="AG5"/>
-      <c r="AH5" s="5"/>
+      <c r="AH5" s="6"/>
     </row>
     <row r="6" spans="1:35">
       <c r="A6">
@@ -1856,7 +2025,7 @@
       <c r="Z6" s="3">
         <v>1</v>
       </c>
-      <c r="AH6" s="5"/>
+      <c r="AH6" s="6"/>
     </row>
     <row r="7" spans="1:35">
       <c r="A7">
@@ -1922,7 +2091,7 @@
       <c r="AC7"/>
       <c r="AE7"/>
       <c r="AG7"/>
-      <c r="AH7" s="5"/>
+      <c r="AH7" s="6"/>
     </row>
     <row r="8" spans="1:35">
       <c r="A8">
@@ -1995,7 +2164,7 @@
       <c r="AC8"/>
       <c r="AE8"/>
       <c r="AG8"/>
-      <c r="AH8" s="5"/>
+      <c r="AH8" s="6"/>
     </row>
     <row r="9" spans="1:35">
       <c r="A9">
@@ -2058,7 +2227,7 @@
       <c r="AC9"/>
       <c r="AE9"/>
       <c r="AG9"/>
-      <c r="AH9" s="5"/>
+      <c r="AH9" s="6"/>
     </row>
     <row r="10" spans="1:35">
       <c r="A10">
@@ -2121,7 +2290,7 @@
       <c r="AC10"/>
       <c r="AE10"/>
       <c r="AG10"/>
-      <c r="AH10" s="5"/>
+      <c r="AH10" s="6"/>
     </row>
     <row r="11" spans="1:35">
       <c r="A11">
@@ -2181,7 +2350,7 @@
       <c r="W11" s="3">
         <v>3</v>
       </c>
-      <c r="AH11" s="5"/>
+      <c r="AH11" s="6"/>
     </row>
     <row r="12" spans="1:35">
       <c r="A12">
@@ -2244,7 +2413,7 @@
       <c r="AC12"/>
       <c r="AE12"/>
       <c r="AG12"/>
-      <c r="AH12" s="5"/>
+      <c r="AH12" s="6"/>
       <c r="AI12" t="s">
         <v>78</v>
       </c>
@@ -2310,7 +2479,7 @@
       <c r="AC13"/>
       <c r="AE13"/>
       <c r="AG13"/>
-      <c r="AH13" s="5"/>
+      <c r="AH13" s="6"/>
     </row>
     <row r="14" spans="1:35">
       <c r="A14">
@@ -2365,7 +2534,7 @@
       <c r="AC14"/>
       <c r="AE14"/>
       <c r="AG14"/>
-      <c r="AH14" s="5"/>
+      <c r="AH14" s="6"/>
     </row>
     <row r="15" spans="1:35">
       <c r="A15">
@@ -2420,7 +2589,7 @@
       <c r="AC15"/>
       <c r="AE15"/>
       <c r="AG15"/>
-      <c r="AH15" s="5"/>
+      <c r="AH15" s="6"/>
     </row>
     <row r="16" spans="1:35">
       <c r="A16">
@@ -2483,7 +2652,7 @@
       <c r="AC16"/>
       <c r="AE16"/>
       <c r="AG16"/>
-      <c r="AH16" s="5"/>
+      <c r="AH16" s="6"/>
     </row>
     <row r="17" spans="1:34">
       <c r="A17">
@@ -2557,7 +2726,7 @@
       <c r="AC17"/>
       <c r="AE17"/>
       <c r="AG17"/>
-      <c r="AH17" s="6"/>
+      <c r="AH17" s="7"/>
     </row>
     <row r="18" spans="1:34">
       <c r="A18">
@@ -2614,7 +2783,7 @@
       <c r="AE18" s="3">
         <v>1.5</v>
       </c>
-      <c r="AH18" s="5"/>
+      <c r="AH18" s="6"/>
     </row>
     <row r="19" spans="1:34">
       <c r="A19">
@@ -2627,7 +2796,7 @@
         <v>99</v>
       </c>
       <c r="D19" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>57</v>
@@ -2677,20 +2846,20 @@
       <c r="AC19"/>
       <c r="AE19"/>
       <c r="AG19"/>
-      <c r="AH19" s="5"/>
+      <c r="AH19" s="6"/>
     </row>
     <row r="20" spans="1:34">
       <c r="A20">
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C20" t="s">
-        <v>101</v>
-      </c>
-      <c r="D20" t="s">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>103</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>48</v>
@@ -2737,20 +2906,20 @@
       <c r="AE20" s="3">
         <v>7</v>
       </c>
-      <c r="AH20" s="6"/>
+      <c r="AH20" s="7"/>
     </row>
     <row r="21" spans="1:34">
       <c r="A21">
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>81</v>
@@ -2806,20 +2975,20 @@
       <c r="Z21" s="3">
         <v>7</v>
       </c>
-      <c r="AH21" s="5"/>
+      <c r="AH21" s="6"/>
     </row>
     <row r="22" spans="1:34">
       <c r="A22">
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D22" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>81</v>
@@ -2869,20 +3038,20 @@
       <c r="AC22"/>
       <c r="AE22"/>
       <c r="AG22"/>
-      <c r="AH22" s="5"/>
+      <c r="AH22" s="6"/>
     </row>
     <row r="23" spans="1:34">
       <c r="A23">
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C23" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D23" t="s">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>81</v>
@@ -2932,20 +3101,20 @@
       <c r="AC23"/>
       <c r="AE23"/>
       <c r="AG23"/>
-      <c r="AH23" s="5"/>
+      <c r="AH23" s="6"/>
     </row>
     <row r="24" spans="1:34">
       <c r="A24">
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C24" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D24" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>48</v>
@@ -2998,20 +3167,20 @@
       <c r="AE24" s="3">
         <v>3</v>
       </c>
-      <c r="AH24" s="5"/>
+      <c r="AH24" s="6"/>
     </row>
     <row r="25" spans="1:34">
       <c r="A25">
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C25" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D25" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>48</v>
@@ -3053,20 +3222,20 @@
       <c r="AC25"/>
       <c r="AE25"/>
       <c r="AG25"/>
-      <c r="AH25" s="5"/>
+      <c r="AH25" s="6"/>
     </row>
     <row r="26" spans="1:34">
       <c r="A26">
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C26" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D26" t="s">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>48</v>
@@ -3116,20 +3285,20 @@
       <c r="AC26"/>
       <c r="AE26"/>
       <c r="AG26"/>
-      <c r="AH26" s="5"/>
+      <c r="AH26" s="6"/>
     </row>
     <row r="27" spans="1:34">
       <c r="A27">
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D27" t="s">
-        <v>115</v>
+        <v>121</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>122</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>57</v>
@@ -3188,20 +3357,20 @@
       <c r="Z27" s="3">
         <v>44</v>
       </c>
-      <c r="AH27" s="6"/>
+      <c r="AH27" s="7"/>
     </row>
     <row r="28" spans="1:34">
       <c r="A28">
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C28" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D28" t="s">
-        <v>117</v>
+        <v>43</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>48</v>
@@ -3213,7 +3382,7 @@
         <v>49</v>
       </c>
       <c r="H28" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="J28" t="s">
         <v>40</v>
@@ -3245,20 +3414,20 @@
       <c r="AE28" s="3">
         <v>12</v>
       </c>
-      <c r="AH28" s="5"/>
+      <c r="AH28" s="6"/>
     </row>
     <row r="29" spans="1:34">
       <c r="A29">
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C29" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="D29" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>81</v>
@@ -3319,20 +3488,20 @@
       <c r="AC29"/>
       <c r="AE29"/>
       <c r="AG29"/>
-      <c r="AH29" s="5"/>
+      <c r="AH29" s="6"/>
     </row>
     <row r="30" spans="1:34">
       <c r="A30">
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="C30" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="D30" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>81</v>
@@ -3385,20 +3554,20 @@
       <c r="AC30"/>
       <c r="AE30"/>
       <c r="AG30"/>
-      <c r="AH30" s="6"/>
+      <c r="AH30" s="7"/>
     </row>
     <row r="31" spans="1:34">
       <c r="A31">
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="C31" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="D31" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>57</v>
@@ -3451,20 +3620,20 @@
       <c r="AC31"/>
       <c r="AE31"/>
       <c r="AG31"/>
-      <c r="AH31" s="6"/>
+      <c r="AH31" s="7"/>
     </row>
     <row r="32" spans="1:34">
       <c r="A32">
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="C32" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="D32" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>57</v>
@@ -3507,13 +3676,13 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="C33" t="s">
-        <v>128</v>
-      </c>
-      <c r="D33" t="s">
-        <v>128</v>
+        <v>138</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>139</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>57</v>
@@ -3563,13 +3732,13 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C34" t="s">
-        <v>130</v>
-      </c>
-      <c r="D34" t="s">
-        <v>130</v>
+        <v>141</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>142</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>81</v>
@@ -3616,13 +3785,13 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C35" t="s">
-        <v>132</v>
-      </c>
-      <c r="D35" t="s">
-        <v>132</v>
+        <v>144</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>81</v>
@@ -3634,7 +3803,7 @@
         <v>49</v>
       </c>
       <c r="H35" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="J35" t="s">
         <v>40</v>
@@ -3665,14 +3834,14 @@
       <c r="A36">
         <v>37</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B36" s="5">
         <v>144</v>
       </c>
       <c r="C36" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="D36" t="s">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>81</v>
@@ -3725,13 +3894,13 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="C37" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="D37" t="s">
-        <v>135</v>
+        <v>71</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>81</v>
@@ -3787,13 +3956,13 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="C38" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D38" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>57</v>
@@ -3849,13 +4018,13 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="C39" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="D39" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>57</v>
@@ -3911,13 +4080,13 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="C40" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="D40" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>57</v>
@@ -3973,13 +4142,13 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="C41" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="D41" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>48</v>
@@ -4035,13 +4204,13 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="C42" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="D42" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>81</v>
@@ -4097,13 +4266,13 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="C43" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="D43" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>81</v>
@@ -4167,13 +4336,13 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="C44" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="D44" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>81</v>
@@ -4226,13 +4395,13 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="C45" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="D45" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>81</v>
@@ -4296,13 +4465,13 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="C46" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="D46" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>57</v>
@@ -4369,13 +4538,13 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="C47" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="D47" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>48</v>
@@ -4426,10 +4595,10 @@
         <v>123</v>
       </c>
       <c r="C48" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="D48" t="s">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>48</v>
@@ -4485,13 +4654,13 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="C49" t="s">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="D49" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>48</v>
@@ -4503,7 +4672,7 @@
         <v>49</v>
       </c>
       <c r="H49" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="J49" t="s">
         <v>40</v>
@@ -4544,13 +4713,13 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="C50" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="D50" t="s">
-        <v>160</v>
+        <v>186</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>57</v>
@@ -4606,13 +4775,13 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>161</v>
+        <v>187</v>
       </c>
       <c r="C51" t="s">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="D51" t="s">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>57</v>
@@ -4668,13 +4837,13 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="C52" t="s">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="D52" t="s">
-        <v>164</v>
+        <v>192</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>81</v>
@@ -4730,13 +4899,13 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>165</v>
+        <v>193</v>
       </c>
       <c r="C53" t="s">
-        <v>166</v>
+        <v>194</v>
       </c>
       <c r="D53" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>57</v>
@@ -4792,13 +4961,13 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>167</v>
+        <v>196</v>
       </c>
       <c r="C54" t="s">
-        <v>168</v>
+        <v>197</v>
       </c>
       <c r="D54" t="s">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>81</v>
@@ -4863,13 +5032,13 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="C55" t="s">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="D55" t="s">
-        <v>170</v>
+        <v>201</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>81</v>
@@ -4923,13 +5092,13 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="C56" t="s">
-        <v>172</v>
+        <v>203</v>
       </c>
       <c r="D56" t="s">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>81</v>
@@ -4941,7 +5110,7 @@
         <v>49</v>
       </c>
       <c r="H56" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="J56" t="s">
         <v>58</v>
@@ -4995,13 +5164,13 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="C57" t="s">
-        <v>174</v>
-      </c>
-      <c r="D57" t="s">
-        <v>174</v>
+        <v>206</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>207</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>57</v>
@@ -5013,7 +5182,7 @@
         <v>49</v>
       </c>
       <c r="H57" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="J57" t="s">
         <v>58</v>
@@ -5050,6 +5219,15 @@
       </c>
       <c r="W57" s="3">
         <v>6</v>
+      </c>
+      <c r="X57">
+        <v>66</v>
+      </c>
+      <c r="Y57">
+        <v>0.6</v>
+      </c>
+      <c r="Z57" s="3">
+        <v>1.2</v>
       </c>
     </row>
     <row r="58" spans="1:33">
@@ -5057,13 +5235,13 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="C58" t="s">
-        <v>176</v>
-      </c>
-      <c r="D58" t="s">
-        <v>176</v>
+        <v>209</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>210</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>48</v>
@@ -5075,10 +5253,10 @@
         <v>49</v>
       </c>
       <c r="H58" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="J58" t="s">
-        <v>40</v>
+        <v>393</v>
       </c>
       <c r="L58">
         <v>3</v>
@@ -5091,6 +5269,15 @@
       </c>
       <c r="O58">
         <v>0</v>
+      </c>
+      <c r="R58">
+        <v>66</v>
+      </c>
+      <c r="S58">
+        <v>1.2</v>
+      </c>
+      <c r="T58" s="3">
+        <v>1.7</v>
       </c>
     </row>
     <row r="59" spans="1:33">
@@ -5098,13 +5285,13 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>177</v>
+        <v>211</v>
       </c>
       <c r="C59" t="s">
-        <v>178</v>
-      </c>
-      <c r="D59" t="s">
-        <v>178</v>
+        <v>212</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>213</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>81</v>
@@ -5116,13 +5303,13 @@
         <v>49</v>
       </c>
       <c r="H59" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="J59" t="s">
-        <v>40</v>
+        <v>393</v>
       </c>
       <c r="L59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M59" s="3">
         <v>3</v>
@@ -5141,6 +5328,15 @@
       </c>
       <c r="T59" s="3">
         <v>9</v>
+      </c>
+      <c r="U59">
+        <v>66</v>
+      </c>
+      <c r="V59">
+        <v>0.9</v>
+      </c>
+      <c r="W59" s="3">
+        <v>1.4</v>
       </c>
     </row>
     <row r="60" spans="1:33">
@@ -5148,13 +5344,13 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>179</v>
+        <v>214</v>
       </c>
       <c r="C60" t="s">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="D60" t="s">
-        <v>180</v>
+        <v>216</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>57</v>
@@ -5166,10 +5362,10 @@
         <v>49</v>
       </c>
       <c r="H60" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="J60" t="s">
-        <v>40</v>
+        <v>393</v>
       </c>
       <c r="L60">
         <v>2</v>
@@ -5182,6 +5378,24 @@
       </c>
       <c r="O60">
         <v>1</v>
+      </c>
+      <c r="R60">
+        <v>66</v>
+      </c>
+      <c r="S60">
+        <v>3</v>
+      </c>
+      <c r="T60" s="3">
+        <v>4</v>
+      </c>
+      <c r="U60">
+        <v>67</v>
+      </c>
+      <c r="V60">
+        <v>-1</v>
+      </c>
+      <c r="W60" s="3">
+        <v>-1</v>
       </c>
     </row>
     <row r="61" spans="1:33">
@@ -5189,13 +5403,13 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>181</v>
+        <v>217</v>
       </c>
       <c r="C61" t="s">
-        <v>182</v>
+        <v>218</v>
       </c>
       <c r="D61" t="s">
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>81</v>
@@ -5207,7 +5421,7 @@
         <v>49</v>
       </c>
       <c r="H61" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="J61" t="s">
         <v>58</v>
@@ -5216,7 +5430,7 @@
         <v>14</v>
       </c>
       <c r="L61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M61" s="3">
         <v>2</v>
@@ -5226,6 +5440,272 @@
       </c>
       <c r="O61">
         <v>1</v>
+      </c>
+      <c r="R61">
+        <v>66</v>
+      </c>
+      <c r="S61">
+        <v>1.2</v>
+      </c>
+      <c r="T61" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="U61">
+        <v>62</v>
+      </c>
+      <c r="V61">
+        <v>1</v>
+      </c>
+      <c r="W61" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:33">
+      <c r="A62">
+        <v>63</v>
+      </c>
+      <c r="B62" t="s">
+        <v>220</v>
+      </c>
+      <c r="C62" t="s">
+        <v>221</v>
+      </c>
+      <c r="D62" t="s">
+        <v>222</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F62" t="s">
+        <v>44</v>
+      </c>
+      <c r="G62" t="s">
+        <v>49</v>
+      </c>
+      <c r="H62" t="s">
+        <v>50</v>
+      </c>
+      <c r="I62" t="s">
+        <v>125</v>
+      </c>
+      <c r="J62" t="s">
+        <v>40</v>
+      </c>
+      <c r="L62">
+        <v>5</v>
+      </c>
+      <c r="M62" s="3">
+        <v>4</v>
+      </c>
+      <c r="N62">
+        <v>1</v>
+      </c>
+      <c r="O62">
+        <v>1</v>
+      </c>
+      <c r="R62">
+        <v>15</v>
+      </c>
+      <c r="S62">
+        <v>6</v>
+      </c>
+      <c r="T62" s="3">
+        <v>8</v>
+      </c>
+      <c r="U62">
+        <v>45</v>
+      </c>
+      <c r="V62">
+        <v>6</v>
+      </c>
+      <c r="W62" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:33">
+      <c r="A63">
+        <v>64</v>
+      </c>
+      <c r="B63" t="s">
+        <v>223</v>
+      </c>
+      <c r="C63" t="s">
+        <v>224</v>
+      </c>
+      <c r="D63" t="s">
+        <v>225</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F63" t="s">
+        <v>38</v>
+      </c>
+      <c r="G63" t="s">
+        <v>49</v>
+      </c>
+      <c r="H63" t="s">
+        <v>50</v>
+      </c>
+      <c r="I63" t="s">
+        <v>125</v>
+      </c>
+      <c r="J63" t="s">
+        <v>393</v>
+      </c>
+      <c r="L63">
+        <v>6</v>
+      </c>
+      <c r="M63" s="3">
+        <v>5</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>1</v>
+      </c>
+      <c r="R63">
+        <v>33</v>
+      </c>
+      <c r="S63">
+        <v>-30</v>
+      </c>
+      <c r="T63" s="3">
+        <v>-30</v>
+      </c>
+      <c r="U63">
+        <v>11</v>
+      </c>
+      <c r="V63">
+        <v>32</v>
+      </c>
+      <c r="W63" s="3">
+        <v>40</v>
+      </c>
+      <c r="X63">
+        <v>2</v>
+      </c>
+      <c r="Y63">
+        <v>15</v>
+      </c>
+      <c r="Z63" s="3">
+        <v>18</v>
+      </c>
+      <c r="AA63">
+        <v>66</v>
+      </c>
+      <c r="AB63">
+        <v>1.5</v>
+      </c>
+      <c r="AC63" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:33">
+      <c r="A64">
+        <v>65</v>
+      </c>
+      <c r="B64" t="s">
+        <v>226</v>
+      </c>
+      <c r="C64" t="s">
+        <v>227</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F64" t="s">
+        <v>38</v>
+      </c>
+      <c r="G64" t="s">
+        <v>39</v>
+      </c>
+      <c r="J64" t="s">
+        <v>40</v>
+      </c>
+      <c r="L64">
+        <v>4</v>
+      </c>
+      <c r="M64" s="3">
+        <v>4</v>
+      </c>
+      <c r="N64">
+        <v>1</v>
+      </c>
+      <c r="O64">
+        <v>1</v>
+      </c>
+      <c r="R64">
+        <v>33</v>
+      </c>
+      <c r="S64">
+        <v>50</v>
+      </c>
+      <c r="T64" s="3">
+        <v>50</v>
+      </c>
+      <c r="U64">
+        <v>68</v>
+      </c>
+      <c r="V64">
+        <v>0.1</v>
+      </c>
+      <c r="W64" s="3">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23">
+      <c r="A65">
+        <v>66</v>
+      </c>
+      <c r="B65" t="s">
+        <v>228</v>
+      </c>
+      <c r="C65" t="s">
+        <v>229</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F65" t="s">
+        <v>38</v>
+      </c>
+      <c r="G65" t="s">
+        <v>39</v>
+      </c>
+      <c r="J65" t="s">
+        <v>40</v>
+      </c>
+      <c r="L65">
+        <v>5</v>
+      </c>
+      <c r="M65" s="3">
+        <v>5</v>
+      </c>
+      <c r="N65">
+        <v>1</v>
+      </c>
+      <c r="O65">
+        <v>1</v>
+      </c>
+      <c r="R65">
+        <v>19</v>
+      </c>
+      <c r="S65">
+        <v>1</v>
+      </c>
+      <c r="T65" s="3">
+        <v>1</v>
+      </c>
+      <c r="U65">
+        <v>69</v>
+      </c>
+      <c r="V65">
+        <v>1</v>
+      </c>
+      <c r="W65" s="3">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
@@ -5236,7 +5716,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.42578125" customWidth="1"/>
@@ -5264,19 +5744,19 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
-        <v>183</v>
+        <v>230</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>184</v>
+        <v>231</v>
       </c>
       <c r="G1" t="s">
-        <v>185</v>
+        <v>232</v>
       </c>
       <c r="H1" t="s">
-        <v>186</v>
+        <v>233</v>
       </c>
       <c r="I1" t="s">
-        <v>187</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5284,13 +5764,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>188</v>
+        <v>235</v>
       </c>
       <c r="C2" t="s">
-        <v>188</v>
+        <v>235</v>
       </c>
       <c r="D2" t="s">
-        <v>189</v>
+        <v>236</v>
       </c>
       <c r="I2">
         <v>-1</v>
@@ -5301,19 +5781,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>190</v>
+        <v>237</v>
       </c>
       <c r="C3" t="s">
-        <v>191</v>
+        <v>238</v>
       </c>
       <c r="D3" t="s">
-        <v>192</v>
+        <v>239</v>
       </c>
       <c r="E3" t="s">
-        <v>193</v>
+        <v>240</v>
       </c>
       <c r="F3" t="s">
-        <v>194</v>
+        <v>241</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -5324,16 +5804,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>195</v>
+        <v>242</v>
       </c>
       <c r="C4" t="s">
-        <v>196</v>
+        <v>243</v>
       </c>
       <c r="D4" t="s">
-        <v>192</v>
+        <v>239</v>
       </c>
       <c r="E4" t="s">
-        <v>197</v>
+        <v>244</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -5344,16 +5824,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>198</v>
+        <v>245</v>
       </c>
       <c r="C5" t="s">
-        <v>199</v>
+        <v>246</v>
       </c>
       <c r="D5" t="s">
-        <v>192</v>
+        <v>239</v>
       </c>
       <c r="E5" t="s">
-        <v>200</v>
+        <v>247</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -5364,13 +5844,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>201</v>
+        <v>248</v>
       </c>
       <c r="C6" t="s">
-        <v>202</v>
+        <v>249</v>
       </c>
       <c r="D6" t="s">
-        <v>203</v>
+        <v>250</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -5381,16 +5861,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>204</v>
+        <v>251</v>
       </c>
       <c r="C7" t="s">
-        <v>204</v>
+        <v>251</v>
       </c>
       <c r="D7" t="s">
-        <v>205</v>
+        <v>252</v>
       </c>
       <c r="E7" t="s">
-        <v>206</v>
+        <v>253</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -5401,13 +5881,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>207</v>
+        <v>254</v>
       </c>
       <c r="C8" t="s">
-        <v>207</v>
+        <v>254</v>
       </c>
       <c r="D8" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -5421,13 +5901,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>209</v>
+        <v>256</v>
       </c>
       <c r="C9" t="s">
-        <v>209</v>
+        <v>256</v>
       </c>
       <c r="D9" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -5441,13 +5921,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>210</v>
+        <v>257</v>
       </c>
       <c r="C10" t="s">
-        <v>210</v>
+        <v>257</v>
       </c>
       <c r="D10" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -5461,13 +5941,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>211</v>
+        <v>258</v>
       </c>
       <c r="C11" t="s">
-        <v>211</v>
+        <v>258</v>
       </c>
       <c r="D11" t="s">
-        <v>212</v>
+        <v>259</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -5478,16 +5958,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>213</v>
+        <v>260</v>
       </c>
       <c r="C12" t="s">
-        <v>213</v>
+        <v>260</v>
       </c>
       <c r="D12" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
       <c r="E12" t="s">
-        <v>215</v>
+        <v>262</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -5498,16 +5978,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>216</v>
+        <v>263</v>
       </c>
       <c r="C13" t="s">
-        <v>217</v>
+        <v>264</v>
       </c>
       <c r="D13" t="s">
-        <v>192</v>
+        <v>239</v>
       </c>
       <c r="E13" t="s">
-        <v>193</v>
+        <v>240</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -5518,19 +5998,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>218</v>
+        <v>265</v>
       </c>
       <c r="C14" t="s">
-        <v>219</v>
+        <v>266</v>
       </c>
       <c r="D14" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>194</v>
+        <v>241</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -5541,16 +6021,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>220</v>
+        <v>267</v>
       </c>
       <c r="C15" t="s">
-        <v>220</v>
+        <v>267</v>
       </c>
       <c r="D15" t="s">
-        <v>221</v>
+        <v>268</v>
       </c>
       <c r="E15" t="s">
-        <v>193</v>
+        <v>240</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -5561,16 +6041,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>222</v>
+        <v>269</v>
       </c>
       <c r="C16" t="s">
-        <v>222</v>
+        <v>269</v>
       </c>
       <c r="D16" t="s">
-        <v>192</v>
+        <v>239</v>
       </c>
       <c r="E16" t="s">
-        <v>223</v>
+        <v>270</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -5581,13 +6061,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>224</v>
+        <v>271</v>
       </c>
       <c r="C17" t="s">
-        <v>224</v>
+        <v>271</v>
       </c>
       <c r="D17" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -5601,16 +6081,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>225</v>
+        <v>272</v>
       </c>
       <c r="C18" t="s">
-        <v>225</v>
+        <v>272</v>
       </c>
       <c r="D18" t="s">
-        <v>226</v>
+        <v>273</v>
       </c>
       <c r="E18" t="s">
-        <v>193</v>
+        <v>240</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -5621,13 +6101,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>227</v>
+        <v>274</v>
       </c>
       <c r="C19" t="s">
-        <v>227</v>
+        <v>274</v>
       </c>
       <c r="D19" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -5641,13 +6121,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>228</v>
+        <v>275</v>
       </c>
       <c r="C20" t="s">
-        <v>228</v>
+        <v>275</v>
       </c>
       <c r="D20" t="s">
-        <v>229</v>
+        <v>276</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -5661,16 +6141,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>230</v>
+        <v>277</v>
       </c>
       <c r="C21" t="s">
-        <v>230</v>
+        <v>277</v>
       </c>
       <c r="D21" t="s">
-        <v>192</v>
+        <v>239</v>
       </c>
       <c r="E21" t="s">
-        <v>231</v>
+        <v>278</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -5681,16 +6161,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>232</v>
+        <v>279</v>
       </c>
       <c r="C22" t="s">
-        <v>232</v>
+        <v>279</v>
       </c>
       <c r="D22" t="s">
-        <v>205</v>
+        <v>252</v>
       </c>
       <c r="E22" t="s">
-        <v>233</v>
+        <v>280</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -5701,13 +6181,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>234</v>
+        <v>281</v>
       </c>
       <c r="C23" t="s">
-        <v>234</v>
+        <v>281</v>
       </c>
       <c r="D23" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="E23">
         <v>5</v>
@@ -5721,19 +6201,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>235</v>
+        <v>282</v>
       </c>
       <c r="C24" t="s">
-        <v>235</v>
+        <v>282</v>
       </c>
       <c r="D24" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>194</v>
+        <v>241</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -5744,13 +6224,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>236</v>
+        <v>283</v>
       </c>
       <c r="C25" t="s">
-        <v>236</v>
+        <v>283</v>
       </c>
       <c r="D25" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -5764,16 +6244,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>237</v>
+        <v>284</v>
       </c>
       <c r="C26" t="s">
-        <v>237</v>
+        <v>284</v>
       </c>
       <c r="D26" t="s">
-        <v>192</v>
+        <v>239</v>
       </c>
       <c r="E26" t="s">
-        <v>193</v>
+        <v>240</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -5787,16 +6267,16 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>238</v>
+        <v>285</v>
       </c>
       <c r="C27" t="s">
-        <v>238</v>
+        <v>285</v>
       </c>
       <c r="D27" t="s">
-        <v>205</v>
+        <v>252</v>
       </c>
       <c r="E27" t="s">
-        <v>233</v>
+        <v>280</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -5807,13 +6287,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>239</v>
+        <v>286</v>
       </c>
       <c r="C28" t="s">
-        <v>239</v>
+        <v>286</v>
       </c>
       <c r="D28" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -5827,19 +6307,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>240</v>
+        <v>287</v>
       </c>
       <c r="C29" t="s">
-        <v>240</v>
+        <v>287</v>
       </c>
       <c r="D29" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>241</v>
+        <v>288</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -5853,13 +6333,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>242</v>
+        <v>289</v>
       </c>
       <c r="C30" t="s">
-        <v>243</v>
+        <v>290</v>
       </c>
       <c r="D30" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -5873,19 +6353,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>244</v>
+        <v>291</v>
       </c>
       <c r="C31" t="s">
-        <v>244</v>
+        <v>291</v>
       </c>
       <c r="D31" t="s">
-        <v>192</v>
+        <v>239</v>
       </c>
       <c r="E31" t="s">
-        <v>193</v>
+        <v>240</v>
       </c>
       <c r="F31" t="s">
-        <v>245</v>
+        <v>292</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -5896,19 +6376,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>246</v>
+        <v>293</v>
       </c>
       <c r="C32" t="s">
-        <v>246</v>
+        <v>293</v>
       </c>
       <c r="D32" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="E32">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>245</v>
+        <v>292</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -5919,19 +6399,19 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>247</v>
+        <v>294</v>
       </c>
       <c r="C33" t="s">
-        <v>247</v>
+        <v>294</v>
       </c>
       <c r="D33" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="E33">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>245</v>
+        <v>292</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -5942,16 +6422,16 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>248</v>
+        <v>295</v>
       </c>
       <c r="C34" t="s">
-        <v>248</v>
+        <v>295</v>
       </c>
       <c r="D34" t="s">
-        <v>192</v>
+        <v>239</v>
       </c>
       <c r="E34" t="s">
-        <v>249</v>
+        <v>296</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -5962,16 +6442,16 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>250</v>
+        <v>297</v>
       </c>
       <c r="C35" t="s">
-        <v>250</v>
+        <v>297</v>
       </c>
       <c r="D35" t="s">
-        <v>192</v>
+        <v>239</v>
       </c>
       <c r="E35" t="s">
-        <v>251</v>
+        <v>298</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -5982,19 +6462,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>252</v>
+        <v>299</v>
       </c>
       <c r="C36" t="s">
-        <v>252</v>
+        <v>299</v>
       </c>
       <c r="D36" t="s">
-        <v>192</v>
+        <v>239</v>
       </c>
       <c r="E36" t="s">
-        <v>251</v>
+        <v>298</v>
       </c>
       <c r="F36" t="s">
-        <v>241</v>
+        <v>288</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -6008,13 +6488,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>253</v>
+        <v>300</v>
       </c>
       <c r="C37" t="s">
-        <v>254</v>
+        <v>301</v>
       </c>
       <c r="D37" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="E37">
         <v>11</v>
@@ -6028,16 +6508,16 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>255</v>
+        <v>302</v>
       </c>
       <c r="C38" t="s">
-        <v>255</v>
+        <v>302</v>
       </c>
       <c r="D38" t="s">
-        <v>192</v>
+        <v>239</v>
       </c>
       <c r="E38" t="s">
-        <v>249</v>
+        <v>296</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -6048,13 +6528,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>256</v>
+        <v>303</v>
       </c>
       <c r="C39" t="s">
-        <v>256</v>
+        <v>303</v>
       </c>
       <c r="D39" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -6071,16 +6551,16 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>257</v>
+        <v>304</v>
       </c>
       <c r="C40" t="s">
-        <v>258</v>
+        <v>305</v>
       </c>
       <c r="D40" t="s">
-        <v>192</v>
+        <v>239</v>
       </c>
       <c r="E40" t="s">
-        <v>259</v>
+        <v>306</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -6091,13 +6571,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>260</v>
+        <v>307</v>
       </c>
       <c r="C41" t="s">
-        <v>260</v>
+        <v>307</v>
       </c>
       <c r="D41" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -6114,19 +6594,19 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>261</v>
+        <v>308</v>
       </c>
       <c r="C42" t="s">
-        <v>261</v>
+        <v>308</v>
       </c>
       <c r="D42" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>241</v>
+        <v>288</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -6140,13 +6620,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>262</v>
+        <v>309</v>
       </c>
       <c r="C43" t="s">
-        <v>262</v>
+        <v>309</v>
       </c>
       <c r="D43" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="E43">
         <v>12</v>
@@ -6160,13 +6640,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>263</v>
+        <v>310</v>
       </c>
       <c r="C44" t="s">
-        <v>263</v>
+        <v>310</v>
       </c>
       <c r="D44" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="E44">
         <v>13</v>
@@ -6180,19 +6660,19 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>264</v>
+        <v>311</v>
       </c>
       <c r="C45" t="s">
-        <v>190</v>
+        <v>237</v>
       </c>
       <c r="D45" t="s">
-        <v>192</v>
+        <v>239</v>
       </c>
       <c r="E45" t="s">
-        <v>193</v>
+        <v>240</v>
       </c>
       <c r="F45" t="s">
-        <v>194</v>
+        <v>241</v>
       </c>
       <c r="I45">
         <v>-1</v>
@@ -6203,16 +6683,16 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>265</v>
+        <v>312</v>
       </c>
       <c r="C46" t="s">
-        <v>265</v>
+        <v>312</v>
       </c>
       <c r="D46" t="s">
-        <v>226</v>
+        <v>273</v>
       </c>
       <c r="E46" t="s">
-        <v>197</v>
+        <v>244</v>
       </c>
       <c r="I46">
         <v>1</v>
@@ -6223,13 +6703,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>266</v>
+        <v>313</v>
       </c>
       <c r="C47" t="s">
-        <v>266</v>
+        <v>313</v>
       </c>
       <c r="D47" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="E47">
         <v>14</v>
@@ -6243,19 +6723,19 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>267</v>
+        <v>314</v>
       </c>
       <c r="C48" t="s">
-        <v>267</v>
+        <v>314</v>
       </c>
       <c r="D48" t="s">
-        <v>268</v>
+        <v>315</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>194</v>
+        <v>241</v>
       </c>
       <c r="I48">
         <v>-1</v>
@@ -6266,13 +6746,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>269</v>
+        <v>316</v>
       </c>
       <c r="C49" t="s">
-        <v>269</v>
+        <v>316</v>
       </c>
       <c r="D49" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="E49">
         <v>15</v>
@@ -6286,19 +6766,19 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>270</v>
+        <v>317</v>
       </c>
       <c r="C50" t="s">
-        <v>270</v>
+        <v>317</v>
       </c>
       <c r="D50" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>194</v>
+        <v>241</v>
       </c>
       <c r="I50">
         <v>-1</v>
@@ -6309,13 +6789,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>271</v>
+        <v>318</v>
       </c>
       <c r="C51" t="s">
-        <v>271</v>
+        <v>318</v>
       </c>
       <c r="D51" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="E51">
         <v>16</v>
@@ -6329,13 +6809,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>272</v>
+        <v>319</v>
       </c>
       <c r="C52" t="s">
-        <v>272</v>
+        <v>319</v>
       </c>
       <c r="D52" t="s">
-        <v>229</v>
+        <v>276</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -6349,13 +6829,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>273</v>
+        <v>320</v>
       </c>
       <c r="C53" t="s">
-        <v>273</v>
+        <v>320</v>
       </c>
       <c r="D53" t="s">
-        <v>268</v>
+        <v>315</v>
       </c>
       <c r="E53">
         <v>3</v>
@@ -6369,13 +6849,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>274</v>
+        <v>321</v>
       </c>
       <c r="C54" t="s">
-        <v>274</v>
+        <v>321</v>
       </c>
       <c r="D54" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="E54">
         <v>3</v>
@@ -6392,16 +6872,16 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>275</v>
+        <v>322</v>
       </c>
       <c r="C55" t="s">
-        <v>275</v>
+        <v>322</v>
       </c>
       <c r="D55" t="s">
-        <v>221</v>
+        <v>268</v>
       </c>
       <c r="E55" t="s">
-        <v>193</v>
+        <v>240</v>
       </c>
       <c r="G55">
         <v>6</v>
@@ -6415,16 +6895,16 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="C56" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="D56" t="s">
-        <v>221</v>
+        <v>268</v>
       </c>
       <c r="E56" t="s">
-        <v>193</v>
+        <v>240</v>
       </c>
       <c r="G56">
         <v>7</v>
@@ -6438,16 +6918,16 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>277</v>
+        <v>324</v>
       </c>
       <c r="C57" t="s">
-        <v>278</v>
+        <v>325</v>
       </c>
       <c r="D57" t="s">
-        <v>221</v>
+        <v>268</v>
       </c>
       <c r="E57" t="s">
-        <v>193</v>
+        <v>240</v>
       </c>
       <c r="G57">
         <v>8</v>
@@ -6461,16 +6941,16 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>279</v>
+        <v>326</v>
       </c>
       <c r="C58" t="s">
-        <v>280</v>
+        <v>327</v>
       </c>
       <c r="D58" t="s">
-        <v>192</v>
+        <v>239</v>
       </c>
       <c r="E58" t="s">
-        <v>193</v>
+        <v>240</v>
       </c>
       <c r="G58">
         <v>6</v>
@@ -6484,16 +6964,16 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>281</v>
+        <v>328</v>
       </c>
       <c r="C59" t="s">
-        <v>280</v>
+        <v>327</v>
       </c>
       <c r="D59" t="s">
-        <v>192</v>
+        <v>239</v>
       </c>
       <c r="E59" t="s">
-        <v>193</v>
+        <v>240</v>
       </c>
       <c r="G59">
         <v>7</v>
@@ -6507,16 +6987,16 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>282</v>
+        <v>329</v>
       </c>
       <c r="C60" t="s">
-        <v>280</v>
+        <v>327</v>
       </c>
       <c r="D60" t="s">
-        <v>192</v>
+        <v>239</v>
       </c>
       <c r="E60" t="s">
-        <v>193</v>
+        <v>240</v>
       </c>
       <c r="G60">
         <v>8</v>
@@ -6530,19 +7010,19 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>283</v>
+        <v>330</v>
       </c>
       <c r="C61" t="s">
-        <v>283</v>
+        <v>330</v>
       </c>
       <c r="D61" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="E61">
         <v>3</v>
       </c>
       <c r="F61" t="s">
-        <v>241</v>
+        <v>288</v>
       </c>
       <c r="I61">
         <v>-1</v>
@@ -6553,13 +7033,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>284</v>
+        <v>331</v>
       </c>
       <c r="C62" t="s">
-        <v>284</v>
+        <v>331</v>
       </c>
       <c r="D62" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="E62">
         <v>20</v>
@@ -6573,16 +7053,16 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>285</v>
+        <v>332</v>
       </c>
       <c r="C63" t="s">
-        <v>285</v>
+        <v>332</v>
       </c>
       <c r="D63" t="s">
-        <v>212</v>
+        <v>259</v>
       </c>
       <c r="F63" t="s">
-        <v>245</v>
+        <v>292</v>
       </c>
       <c r="I63">
         <v>-1</v>
@@ -6593,13 +7073,13 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>286</v>
+        <v>333</v>
       </c>
       <c r="C64" t="s">
-        <v>286</v>
+        <v>333</v>
       </c>
       <c r="D64" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="E64">
         <v>21</v>
@@ -6613,13 +7093,13 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>287</v>
+        <v>334</v>
       </c>
       <c r="C65" t="s">
-        <v>287</v>
+        <v>334</v>
       </c>
       <c r="D65" t="s">
-        <v>268</v>
+        <v>315</v>
       </c>
       <c r="E65">
         <v>3</v>
@@ -6633,19 +7113,19 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>288</v>
+        <v>335</v>
       </c>
       <c r="C66" t="s">
-        <v>288</v>
+        <v>335</v>
       </c>
       <c r="D66" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="E66">
         <v>14</v>
       </c>
       <c r="F66" t="s">
-        <v>194</v>
+        <v>241</v>
       </c>
       <c r="I66">
         <v>-1</v>
@@ -6656,18 +7136,86 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>289</v>
+        <v>336</v>
       </c>
       <c r="C67" t="s">
-        <v>289</v>
+        <v>336</v>
       </c>
       <c r="D67" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="E67">
         <v>22</v>
       </c>
       <c r="I67">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68">
+        <v>66</v>
+      </c>
+      <c r="B68" t="s">
+        <v>337</v>
+      </c>
+      <c r="D68" t="s">
+        <v>338</v>
+      </c>
+      <c r="E68" t="s">
+        <v>244</v>
+      </c>
+      <c r="I68">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="A69">
+        <v>67</v>
+      </c>
+      <c r="B69" t="s">
+        <v>339</v>
+      </c>
+      <c r="D69" t="s">
+        <v>338</v>
+      </c>
+      <c r="E69" t="s">
+        <v>244</v>
+      </c>
+      <c r="I69">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
+      <c r="A70">
+        <v>68</v>
+      </c>
+      <c r="B70" t="s">
+        <v>340</v>
+      </c>
+      <c r="D70" t="s">
+        <v>341</v>
+      </c>
+      <c r="E70" t="s">
+        <v>342</v>
+      </c>
+      <c r="I70">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71">
+        <v>69</v>
+      </c>
+      <c r="B71" t="s">
+        <v>343</v>
+      </c>
+      <c r="D71" t="s">
+        <v>338</v>
+      </c>
+      <c r="E71" t="s">
+        <v>278</v>
+      </c>
+      <c r="I71">
         <v>-1</v>
       </c>
     </row>
@@ -6702,13 +7250,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>290</v>
+        <v>344</v>
       </c>
       <c r="D1" t="s">
-        <v>291</v>
+        <v>345</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>292</v>
+        <v>346</v>
       </c>
       <c r="F1" t="s">
         <v>17</v>
@@ -6735,10 +7283,10 @@
         <v>27</v>
       </c>
       <c r="N1" t="s">
-        <v>293</v>
+        <v>347</v>
       </c>
       <c r="O1" t="s">
-        <v>294</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -6746,10 +7294,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>295</v>
+        <v>349</v>
       </c>
       <c r="C2" t="s">
-        <v>296</v>
+        <v>350</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -6775,10 +7323,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>297</v>
+        <v>351</v>
       </c>
       <c r="C3" t="s">
-        <v>296</v>
+        <v>350</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -6798,10 +7346,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>298</v>
+        <v>352</v>
       </c>
       <c r="C4" t="s">
-        <v>296</v>
+        <v>350</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -6815,10 +7363,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>299</v>
+        <v>353</v>
       </c>
       <c r="C5" t="s">
-        <v>300</v>
+        <v>354</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -6850,10 +7398,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>301</v>
+        <v>355</v>
       </c>
       <c r="C6" t="s">
-        <v>296</v>
+        <v>350</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -6873,10 +7421,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>302</v>
+        <v>356</v>
       </c>
       <c r="C7" t="s">
-        <v>300</v>
+        <v>354</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -6896,10 +7444,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>303</v>
+        <v>357</v>
       </c>
       <c r="C8" t="s">
-        <v>296</v>
+        <v>350</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -6919,10 +7467,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>304</v>
+        <v>358</v>
       </c>
       <c r="C9" t="s">
-        <v>300</v>
+        <v>354</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -6942,10 +7490,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>243</v>
+        <v>290</v>
       </c>
       <c r="C10" t="s">
-        <v>296</v>
+        <v>350</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -6965,10 +7513,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>246</v>
+        <v>293</v>
       </c>
       <c r="C11" t="s">
-        <v>300</v>
+        <v>354</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -6994,10 +7542,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>247</v>
+        <v>294</v>
       </c>
       <c r="C12" t="s">
-        <v>300</v>
+        <v>354</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -7023,10 +7571,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>254</v>
+        <v>301</v>
       </c>
       <c r="C13" t="s">
-        <v>296</v>
+        <v>350</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -7046,10 +7594,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>262</v>
+        <v>309</v>
       </c>
       <c r="C14" t="s">
-        <v>296</v>
+        <v>350</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -7069,10 +7617,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>305</v>
+        <v>359</v>
       </c>
       <c r="C15" t="s">
-        <v>300</v>
+        <v>354</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -7092,10 +7640,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>306</v>
+        <v>360</v>
       </c>
       <c r="C16" t="s">
-        <v>296</v>
+        <v>350</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -7115,10 +7663,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>269</v>
+        <v>316</v>
       </c>
       <c r="C17" t="s">
-        <v>300</v>
+        <v>354</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -7138,10 +7686,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>271</v>
+        <v>318</v>
       </c>
       <c r="C18" t="s">
-        <v>296</v>
+        <v>350</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -7161,10 +7709,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>307</v>
+        <v>361</v>
       </c>
       <c r="C19" t="s">
-        <v>296</v>
+        <v>350</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -7178,10 +7726,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>308</v>
+        <v>362</v>
       </c>
       <c r="C20" t="s">
-        <v>300</v>
+        <v>354</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -7195,10 +7743,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>309</v>
+        <v>220</v>
       </c>
       <c r="C21" t="s">
-        <v>296</v>
+        <v>350</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -7212,10 +7760,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>310</v>
+        <v>363</v>
       </c>
       <c r="C22" t="s">
-        <v>296</v>
+        <v>350</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -7235,10 +7783,10 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="C23" t="s">
-        <v>300</v>
+        <v>354</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -7258,10 +7806,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>289</v>
+        <v>336</v>
       </c>
       <c r="C24" t="s">
-        <v>296</v>
+        <v>350</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -7281,16 +7829,22 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>312</v>
+        <v>365</v>
       </c>
       <c r="C25" t="s">
-        <v>296</v>
+        <v>350</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
         <v>0</v>
+      </c>
+      <c r="F25">
+        <v>13</v>
+      </c>
+      <c r="G25">
+        <v>0.05</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -7298,16 +7852,22 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>313</v>
+        <v>366</v>
       </c>
       <c r="C26" t="s">
-        <v>296</v>
+        <v>350</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
       <c r="E26">
         <v>0</v>
+      </c>
+      <c r="F26">
+        <v>13</v>
+      </c>
+      <c r="G26">
+        <v>0.1</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -7315,16 +7875,22 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>314</v>
+        <v>367</v>
       </c>
       <c r="C27" t="s">
-        <v>296</v>
+        <v>350</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
         <v>0</v>
+      </c>
+      <c r="F27">
+        <v>13</v>
+      </c>
+      <c r="G27">
+        <v>0.15</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -7332,16 +7898,22 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>315</v>
+        <v>368</v>
       </c>
       <c r="C28" t="s">
-        <v>296</v>
+        <v>350</v>
       </c>
       <c r="D28">
         <v>0</v>
       </c>
       <c r="E28">
         <v>0</v>
+      </c>
+      <c r="F28">
+        <v>13</v>
+      </c>
+      <c r="G28">
+        <v>0.2</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -7349,16 +7921,22 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>316</v>
+        <v>369</v>
       </c>
       <c r="C29" t="s">
-        <v>296</v>
+        <v>350</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29">
         <v>0</v>
+      </c>
+      <c r="F29">
+        <v>13</v>
+      </c>
+      <c r="G29">
+        <v>0.25</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -7366,16 +7944,22 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>317</v>
+        <v>370</v>
       </c>
       <c r="C30" t="s">
-        <v>296</v>
+        <v>350</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30">
         <v>0</v>
+      </c>
+      <c r="F30">
+        <v>13</v>
+      </c>
+      <c r="G30">
+        <v>0.3</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -7383,16 +7967,22 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>318</v>
+        <v>371</v>
       </c>
       <c r="C31" t="s">
-        <v>296</v>
+        <v>350</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
       <c r="E31">
         <v>0</v>
+      </c>
+      <c r="F31">
+        <v>13</v>
+      </c>
+      <c r="G31">
+        <v>0.35</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -7400,10 +7990,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="C32" t="s">
-        <v>296</v>
+        <v>350</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -7411,16 +8001,22 @@
       <c r="E32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:5">
+      <c r="F32">
+        <v>13</v>
+      </c>
+      <c r="G32">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="C33" t="s">
-        <v>296</v>
+        <v>350</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -7428,22 +8024,34 @@
       <c r="E33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:5">
+      <c r="F33">
+        <v>13</v>
+      </c>
+      <c r="G33">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>321</v>
+        <v>374</v>
       </c>
       <c r="C34" t="s">
-        <v>296</v>
+        <v>350</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34">
         <v>0</v>
+      </c>
+      <c r="F34">
+        <v>13</v>
+      </c>
+      <c r="G34">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -7477,16 +8085,16 @@
         <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>322</v>
+        <v>375</v>
       </c>
       <c r="E1" t="s">
-        <v>323</v>
+        <v>376</v>
       </c>
       <c r="F1" t="s">
-        <v>324</v>
+        <v>377</v>
       </c>
       <c r="G1" t="s">
-        <v>325</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -7494,13 +8102,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>326</v>
+        <v>379</v>
       </c>
       <c r="C2" t="s">
-        <v>327</v>
+        <v>380</v>
       </c>
       <c r="D2" t="s">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -7514,13 +8122,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>329</v>
+        <v>382</v>
       </c>
       <c r="C3" t="s">
-        <v>330</v>
+        <v>383</v>
       </c>
       <c r="D3" t="s">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="F3" t="s">
         <v>44</v>
@@ -7531,13 +8139,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>331</v>
+        <v>384</v>
       </c>
       <c r="C4" t="s">
-        <v>330</v>
+        <v>383</v>
       </c>
       <c r="D4" t="s">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="F4" t="s">
         <v>38</v>
@@ -7548,13 +8156,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>332</v>
+        <v>385</v>
       </c>
       <c r="C5" t="s">
-        <v>327</v>
+        <v>380</v>
       </c>
       <c r="D5" t="s">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -7568,13 +8176,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>333</v>
+        <v>386</v>
       </c>
       <c r="C6" t="s">
-        <v>327</v>
+        <v>380</v>
       </c>
       <c r="D6" t="s">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -7588,13 +8196,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>334</v>
+        <v>387</v>
       </c>
       <c r="C7" t="s">
-        <v>327</v>
+        <v>380</v>
       </c>
       <c r="D7" t="s">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -7608,13 +8216,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>335</v>
+        <v>388</v>
       </c>
       <c r="C8" t="s">
-        <v>327</v>
+        <v>380</v>
       </c>
       <c r="D8" t="s">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -7628,13 +8236,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>336</v>
+        <v>389</v>
       </c>
       <c r="C9" t="s">
-        <v>327</v>
+        <v>380</v>
       </c>
       <c r="D9" t="s">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -7648,13 +8256,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>337</v>
+        <v>390</v>
       </c>
       <c r="C10" t="s">
-        <v>327</v>
+        <v>380</v>
       </c>
       <c r="D10" t="s">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -7668,13 +8276,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>338</v>
+        <v>391</v>
       </c>
       <c r="C11" t="s">
-        <v>339</v>
+        <v>392</v>
       </c>
       <c r="D11" t="s">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="E11" t="s">
         <v>44</v>

--- a/Assets/StreamingAssets/Configurations/Cards.xlsx
+++ b/Assets/StreamingAssets/Configurations/Cards.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10DE11E-A0D9-4062-90B4-175373358093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="22190" windowHeight="9040"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -30,6 +24,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="397">
   <si>
     <t>ID</t>
   </si>
@@ -672,6 +668,9 @@
     <t>获得神采X1%的参数</t>
   </si>
   <si>
+    <t>TrueStamina</t>
+  </si>
+  <si>
     <t>LLBC</t>
   </si>
   <si>
@@ -729,6 +728,15 @@
     <t>舰长+1，获得舰长数100%的参数</t>
   </si>
   <si>
+    <t>下头</t>
+  </si>
+  <si>
+    <t>参数+12，神采+5，抽一张卡，卡牌使用次数+1</t>
+  </si>
+  <si>
+    <t>参数+X1，神采+X4，抽一张卡，卡牌使用次数+1</t>
+  </si>
+  <si>
     <t>Parameter</t>
   </si>
   <si>
@@ -1216,25 +1224,172 @@
   </si>
   <si>
     <t>VCardTypeUsedCountCondition</t>
-  </si>
-  <si>
-    <t>TrueStamina</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1259,8 +1414,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1286,9 +1627,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1304,27 +1887,71 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFFFFFFF"/>
-      <color rgb="FFAB0580"/>
-      <color rgb="FF00B050"/>
-      <color rgb="FFFFB200"/>
-      <color rgb="FF4B58FF"/>
-      <color rgb="FFFF2160"/>
+      <color rgb="00FFFFFF"/>
+      <color rgb="00AB0580"/>
+      <color rgb="0000B050"/>
+      <color rgb="00FFB200"/>
+      <color rgb="004B58FF"/>
+      <color rgb="00FF2160"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1582,49 +2209,49 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI65"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:AI66"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="3.425" customWidth="1"/>
+    <col min="2" max="2" width="12.7083333333333" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
-    <col min="4" max="4" width="57.7109375" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="4.85546875" customWidth="1"/>
-    <col min="7" max="7" width="7.85546875" customWidth="1"/>
+    <col min="4" max="4" width="57.7083333333333" customWidth="1"/>
+    <col min="5" max="5" width="10.425" style="2" customWidth="1"/>
+    <col min="6" max="6" width="4.85833333333333" customWidth="1"/>
+    <col min="7" max="7" width="7.85833333333333" customWidth="1"/>
     <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="9" max="9" width="5.5703125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" customWidth="1"/>
-    <col min="11" max="11" width="9.7109375" style="3" customWidth="1"/>
-    <col min="12" max="12" width="7.140625" customWidth="1"/>
+    <col min="9" max="9" width="5.56666666666667" style="3" customWidth="1"/>
+    <col min="10" max="10" width="10.5666666666667" customWidth="1"/>
+    <col min="11" max="11" width="9.70833333333333" style="3" customWidth="1"/>
+    <col min="12" max="12" width="7.14166666666667" customWidth="1"/>
     <col min="13" max="13" width="14" style="3" customWidth="1"/>
-    <col min="14" max="14" width="10.28515625" customWidth="1"/>
-    <col min="15" max="16" width="13.7109375" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="3" customWidth="1"/>
-    <col min="18" max="18" width="9.7109375" customWidth="1"/>
-    <col min="19" max="19" width="12.140625" customWidth="1"/>
-    <col min="20" max="20" width="17.7109375" style="3" customWidth="1"/>
+    <col min="14" max="14" width="10.2833333333333" customWidth="1"/>
+    <col min="15" max="16" width="13.7083333333333" customWidth="1"/>
+    <col min="17" max="17" width="9.70833333333333" style="3" customWidth="1"/>
+    <col min="18" max="18" width="9.70833333333333" customWidth="1"/>
+    <col min="19" max="19" width="12.1416666666667" customWidth="1"/>
+    <col min="20" max="20" width="17.7083333333333" style="3" customWidth="1"/>
     <col min="21" max="21" width="11" customWidth="1"/>
-    <col min="22" max="22" width="12.28515625" customWidth="1"/>
-    <col min="23" max="23" width="17.140625" style="3" customWidth="1"/>
-    <col min="26" max="26" width="17.7109375" style="3" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" customWidth="1"/>
+    <col min="22" max="22" width="12.2833333333333" customWidth="1"/>
+    <col min="23" max="23" width="17.1416666666667" style="3" customWidth="1"/>
+    <col min="26" max="26" width="17.7083333333333" style="3" customWidth="1"/>
+    <col min="27" max="27" width="10.7083333333333" customWidth="1"/>
     <col min="28" max="28" width="11" customWidth="1"/>
-    <col min="29" max="29" width="17.7109375" style="3" customWidth="1"/>
-    <col min="30" max="30" width="12.42578125" customWidth="1"/>
-    <col min="31" max="31" width="12.42578125" style="3" customWidth="1"/>
-    <col min="32" max="32" width="12.28515625" customWidth="1"/>
+    <col min="29" max="29" width="17.7083333333333" style="3" customWidth="1"/>
+    <col min="30" max="30" width="12.425" customWidth="1"/>
+    <col min="31" max="31" width="12.425" style="3" customWidth="1"/>
+    <col min="32" max="32" width="12.2833333333333" customWidth="1"/>
     <col min="33" max="33" width="9" style="3"/>
-    <col min="34" max="34" width="4.28515625" customWidth="1"/>
+    <col min="34" max="34" width="4.28333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:34">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1728,7 +2355,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:34">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1783,7 +2410,7 @@
       <c r="AG2"/>
       <c r="AH2" s="6"/>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:34">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1838,7 +2465,7 @@
       <c r="AG3"/>
       <c r="AH3" s="6"/>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:34">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1898,7 +2525,7 @@
       </c>
       <c r="AH4" s="6"/>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:34">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1961,7 +2588,7 @@
       <c r="AG5"/>
       <c r="AH5" s="6"/>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:34">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2027,7 +2654,7 @@
       </c>
       <c r="AH6" s="6"/>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:34">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2093,7 +2720,7 @@
       <c r="AG7"/>
       <c r="AH7" s="6"/>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:34">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2166,7 +2793,7 @@
       <c r="AG8"/>
       <c r="AH8" s="6"/>
     </row>
-    <row r="9" spans="1:35">
+    <row r="9" spans="1:34">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2229,7 +2856,7 @@
       <c r="AG9"/>
       <c r="AH9" s="6"/>
     </row>
-    <row r="10" spans="1:35">
+    <row r="10" spans="1:34">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2292,7 +2919,7 @@
       <c r="AG10"/>
       <c r="AH10" s="6"/>
     </row>
-    <row r="11" spans="1:35">
+    <row r="11" spans="1:34">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2418,7 +3045,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="1:35">
+    <row r="13" spans="1:34">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2481,7 +3108,7 @@
       <c r="AG13"/>
       <c r="AH13" s="6"/>
     </row>
-    <row r="14" spans="1:35">
+    <row r="14" spans="1:34">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2536,7 +3163,7 @@
       <c r="AG14"/>
       <c r="AH14" s="6"/>
     </row>
-    <row r="15" spans="1:35">
+    <row r="15" spans="1:34">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2591,7 +3218,7 @@
       <c r="AG15"/>
       <c r="AH15" s="6"/>
     </row>
-    <row r="16" spans="1:35">
+    <row r="16" spans="1:34">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2646,7 +3273,7 @@
         <v>0.8</v>
       </c>
       <c r="W16" s="3">
-        <v>1.1000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="Z16"/>
       <c r="AC16"/>
@@ -3622,7 +4249,7 @@
       <c r="AG31"/>
       <c r="AH31" s="7"/>
     </row>
-    <row r="32" spans="1:34">
+    <row r="32" spans="1:33">
       <c r="A32">
         <v>33</v>
       </c>
@@ -3671,7 +4298,7 @@
       <c r="AE32"/>
       <c r="AG32"/>
     </row>
-    <row r="33" spans="1:33">
+    <row r="33" spans="1:31">
       <c r="A33">
         <v>34</v>
       </c>
@@ -3727,7 +4354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:33">
+    <row r="34" spans="1:20">
       <c r="A34">
         <v>35</v>
       </c>
@@ -3780,7 +4407,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:33">
+    <row r="35" spans="1:20">
       <c r="A35">
         <v>36</v>
       </c>
@@ -3830,7 +4457,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:33">
+    <row r="36" spans="1:23">
       <c r="A36">
         <v>37</v>
       </c>
@@ -4331,7 +4958,7 @@
       <c r="AE43"/>
       <c r="AG43"/>
     </row>
-    <row r="44" spans="1:33">
+    <row r="44" spans="1:23">
       <c r="A44">
         <v>45</v>
       </c>
@@ -4649,7 +5276,7 @@
       <c r="AE48"/>
       <c r="AG48"/>
     </row>
-    <row r="49" spans="1:33">
+    <row r="49" spans="1:23">
       <c r="A49">
         <v>50</v>
       </c>
@@ -4760,7 +5387,7 @@
         <v>18</v>
       </c>
       <c r="V50">
-        <v>1.1000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="W50" s="3">
         <v>1.7</v>
@@ -4894,7 +5521,7 @@
       <c r="AE52"/>
       <c r="AG52"/>
     </row>
-    <row r="53" spans="1:33">
+    <row r="53" spans="1:23">
       <c r="A53">
         <v>54</v>
       </c>
@@ -4956,7 +5583,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="54" spans="1:33">
+    <row r="54" spans="1:26">
       <c r="A54">
         <v>55</v>
       </c>
@@ -5027,7 +5654,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:33">
+    <row r="55" spans="1:32">
       <c r="A55">
         <v>56</v>
       </c>
@@ -5087,7 +5714,7 @@
       </c>
       <c r="AF55" s="3"/>
     </row>
-    <row r="56" spans="1:33">
+    <row r="56" spans="1:32">
       <c r="A56">
         <v>57</v>
       </c>
@@ -5159,7 +5786,7 @@
       </c>
       <c r="AF56" s="3"/>
     </row>
-    <row r="57" spans="1:33">
+    <row r="57" spans="1:26">
       <c r="A57">
         <v>58</v>
       </c>
@@ -5230,7 +5857,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="58" spans="1:33">
+    <row r="58" spans="1:20">
       <c r="A58">
         <v>59</v>
       </c>
@@ -5256,7 +5883,7 @@
         <v>125</v>
       </c>
       <c r="J58" t="s">
-        <v>393</v>
+        <v>211</v>
       </c>
       <c r="L58">
         <v>3</v>
@@ -5280,18 +5907,18 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="59" spans="1:33">
+    <row r="59" spans="1:23">
       <c r="A59">
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C59" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>81</v>
@@ -5306,7 +5933,7 @@
         <v>125</v>
       </c>
       <c r="J59" t="s">
-        <v>393</v>
+        <v>211</v>
       </c>
       <c r="L59">
         <v>3</v>
@@ -5339,18 +5966,18 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="60" spans="1:33">
+    <row r="60" spans="1:23">
       <c r="A60">
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C60" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D60" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>57</v>
@@ -5365,7 +5992,7 @@
         <v>125</v>
       </c>
       <c r="J60" t="s">
-        <v>393</v>
+        <v>211</v>
       </c>
       <c r="L60">
         <v>2</v>
@@ -5398,18 +6025,18 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="61" spans="1:33">
+    <row r="61" spans="1:23">
       <c r="A61">
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C61" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D61" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>81</v>
@@ -5460,18 +6087,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:33">
+    <row r="62" spans="1:23">
       <c r="A62">
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C62" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D62" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>57</v>
@@ -5522,18 +6149,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="1:33">
+    <row r="63" spans="1:29">
       <c r="A63">
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C63" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D63" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>57</v>
@@ -5551,7 +6178,7 @@
         <v>125</v>
       </c>
       <c r="J63" t="s">
-        <v>393</v>
+        <v>211</v>
       </c>
       <c r="L63">
         <v>6</v>
@@ -5602,15 +6229,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:33">
+    <row r="64" spans="1:23">
       <c r="A64">
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C64" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>57</v>
@@ -5660,10 +6287,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C65" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>57</v>
@@ -5708,25 +6335,102 @@
         <v>1.5</v>
       </c>
     </row>
+    <row r="66" spans="1:29">
+      <c r="A66">
+        <v>67</v>
+      </c>
+      <c r="B66" t="s">
+        <v>231</v>
+      </c>
+      <c r="C66" t="s">
+        <v>232</v>
+      </c>
+      <c r="D66" t="s">
+        <v>233</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F66" t="s">
+        <v>38</v>
+      </c>
+      <c r="G66" t="s">
+        <v>39</v>
+      </c>
+      <c r="J66" t="s">
+        <v>40</v>
+      </c>
+      <c r="K66" s="3"/>
+      <c r="L66">
+        <v>4</v>
+      </c>
+      <c r="M66" s="3">
+        <v>4</v>
+      </c>
+      <c r="N66">
+        <v>1</v>
+      </c>
+      <c r="O66">
+        <v>1</v>
+      </c>
+      <c r="R66">
+        <v>11</v>
+      </c>
+      <c r="S66">
+        <v>12</v>
+      </c>
+      <c r="T66" s="3">
+        <v>15</v>
+      </c>
+      <c r="U66">
+        <v>9</v>
+      </c>
+      <c r="V66">
+        <v>1</v>
+      </c>
+      <c r="W66" s="3">
+        <v>1</v>
+      </c>
+      <c r="X66">
+        <v>14</v>
+      </c>
+      <c r="Y66">
+        <v>1</v>
+      </c>
+      <c r="Z66" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA66">
+        <v>2</v>
+      </c>
+      <c r="AB66">
+        <v>5</v>
+      </c>
+      <c r="AC66" s="3">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I71"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.42578125" customWidth="1"/>
+    <col min="1" max="1" width="3.425" customWidth="1"/>
+    <col min="2" max="2" width="27.425" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
     <col min="4" max="4" width="33" customWidth="1"/>
-    <col min="5" max="5" width="19.28515625" customWidth="1"/>
-    <col min="6" max="6" width="18.85546875" customWidth="1"/>
-    <col min="7" max="8" width="10.28515625" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" customWidth="1"/>
+    <col min="5" max="5" width="19.2833333333333" customWidth="1"/>
+    <col min="6" max="6" width="18.8583333333333" customWidth="1"/>
+    <col min="7" max="8" width="10.2833333333333" customWidth="1"/>
+    <col min="9" max="9" width="15.1416666666667" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5744,19 +6448,19 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="G1" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="H1" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="I1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5764,13 +6468,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="I2">
         <v>-1</v>
@@ -5781,19 +6485,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="D3" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F3" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -5804,16 +6508,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C4" t="s">
+        <v>247</v>
+      </c>
+      <c r="D4" t="s">
         <v>243</v>
       </c>
-      <c r="D4" t="s">
-        <v>239</v>
-      </c>
       <c r="E4" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -5824,16 +6528,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D5" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -5844,13 +6548,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C6" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D6" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -5861,16 +6565,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C7" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D7" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E7" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -5881,13 +6585,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C8" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D8" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -5901,13 +6605,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C9" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D9" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -5921,13 +6625,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C10" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D10" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -5941,13 +6645,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C11" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D11" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -5958,16 +6662,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C12" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D12" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E12" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -5978,16 +6682,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C13" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D13" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -5998,19 +6702,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C14" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D14" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -6021,16 +6725,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C15" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D15" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="E15" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -6041,16 +6745,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C16" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D16" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -6061,13 +6765,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C17" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D17" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -6081,16 +6785,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C18" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D18" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="E18" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -6101,13 +6805,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C19" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D19" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -6121,13 +6825,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C20" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D20" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -6141,16 +6845,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C21" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D21" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -6161,16 +6865,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C22" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D22" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E22" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -6181,13 +6885,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C23" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D23" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E23">
         <v>5</v>
@@ -6201,19 +6905,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C24" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D24" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -6224,13 +6928,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C25" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D25" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -6244,16 +6948,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C26" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D26" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -6267,16 +6971,16 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C27" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D27" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E27" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -6287,13 +6991,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C28" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D28" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -6307,19 +7011,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C29" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D29" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -6333,13 +7037,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C30" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D30" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -6353,19 +7057,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C31" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D31" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F31" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -6376,19 +7080,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C32" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D32" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E32">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -6399,19 +7103,19 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C33" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D33" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E33">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -6422,16 +7126,16 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C34" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D34" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -6442,16 +7146,16 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C35" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="D35" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -6462,19 +7166,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C36" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="D36" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="F36" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -6488,13 +7192,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C37" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D37" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E37">
         <v>11</v>
@@ -6508,16 +7212,16 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C38" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D38" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -6528,13 +7232,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C39" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D39" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -6551,16 +7255,16 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C40" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="D40" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -6571,13 +7275,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C41" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D41" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -6594,19 +7298,19 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C42" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D42" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -6620,13 +7324,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C43" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D43" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E43">
         <v>12</v>
@@ -6640,13 +7344,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C44" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D44" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E44">
         <v>13</v>
@@ -6660,19 +7364,19 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C45" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D45" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F45" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="I45">
         <v>-1</v>
@@ -6683,16 +7387,16 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C46" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D46" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="E46" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I46">
         <v>1</v>
@@ -6703,13 +7407,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C47" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D47" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E47">
         <v>14</v>
@@ -6723,19 +7427,19 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="C48" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="D48" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="I48">
         <v>-1</v>
@@ -6746,13 +7450,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C49" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D49" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E49">
         <v>15</v>
@@ -6766,19 +7470,19 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C50" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="D50" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="I50">
         <v>-1</v>
@@ -6789,13 +7493,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C51" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="D51" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E51">
         <v>16</v>
@@ -6809,13 +7513,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="C52" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D52" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -6829,13 +7533,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C53" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="E53">
         <v>3</v>
@@ -6849,13 +7553,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C54" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D54" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E54">
         <v>3</v>
@@ -6872,16 +7576,16 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C55" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="D55" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="E55" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="G55">
         <v>6</v>
@@ -6895,16 +7599,16 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C56" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D56" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="E56" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="G56">
         <v>7</v>
@@ -6918,16 +7622,16 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C57" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="D57" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="E57" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="G57">
         <v>8</v>
@@ -6941,16 +7645,16 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C58" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D58" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E58" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="G58">
         <v>6</v>
@@ -6964,16 +7668,16 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C59" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D59" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E59" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="G59">
         <v>7</v>
@@ -6987,16 +7691,16 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C60" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D60" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E60" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="G60">
         <v>8</v>
@@ -7010,19 +7714,19 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C61" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D61" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E61">
         <v>3</v>
       </c>
       <c r="F61" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="I61">
         <v>-1</v>
@@ -7033,13 +7737,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C62" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D62" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E62">
         <v>20</v>
@@ -7053,16 +7757,16 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C63" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="D63" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F63" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="I63">
         <v>-1</v>
@@ -7073,13 +7777,13 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C64" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="D64" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E64">
         <v>21</v>
@@ -7093,13 +7797,13 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C65" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="D65" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="E65">
         <v>3</v>
@@ -7113,19 +7817,19 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C66" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D66" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E66">
         <v>14</v>
       </c>
       <c r="F66" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="I66">
         <v>-1</v>
@@ -7136,13 +7840,13 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C67" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="D67" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E67">
         <v>22</v>
@@ -7156,13 +7860,13 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="D68" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E68" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I68">
         <v>-1</v>
@@ -7173,13 +7877,13 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="D69" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E69" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I69">
         <v>-1</v>
@@ -7190,13 +7894,13 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D70" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="E70" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="I70">
         <v>-1</v>
@@ -7207,13 +7911,13 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="D71" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E71" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="I71">
         <v>-1</v>
@@ -7221,24 +7925,26 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:O34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.42578125" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" customWidth="1"/>
-    <col min="4" max="5" width="16.140625" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" customWidth="1"/>
+    <col min="1" max="1" width="9.425" customWidth="1"/>
+    <col min="2" max="2" width="27.425" customWidth="1"/>
+    <col min="3" max="3" width="14.425" customWidth="1"/>
+    <col min="4" max="5" width="16.1416666666667" customWidth="1"/>
+    <col min="6" max="6" width="12.425" customWidth="1"/>
+    <col min="7" max="7" width="14.425" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="10.140625" customWidth="1"/>
+    <col min="10" max="10" width="10.1416666666667" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7250,13 +7956,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="D1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="F1" t="s">
         <v>17</v>
@@ -7283,21 +7989,21 @@
         <v>27</v>
       </c>
       <c r="N1" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="O1" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -7318,15 +8024,15 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C3" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -7341,15 +8047,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C4" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -7358,15 +8064,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C5" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -7393,15 +8099,15 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C6" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -7416,15 +8122,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C7" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -7439,15 +8145,15 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C8" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -7462,15 +8168,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>362</v>
+      </c>
+      <c r="C9" t="s">
         <v>358</v>
-      </c>
-      <c r="C9" t="s">
-        <v>354</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -7485,15 +8191,15 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C10" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -7508,15 +8214,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:9">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C11" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -7537,15 +8243,15 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:9">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C12" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -7566,15 +8272,15 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C13" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -7589,15 +8295,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C14" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -7612,15 +8318,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="C15" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -7635,15 +8341,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C16" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -7663,10 +8369,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C17" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -7686,10 +8392,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C18" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -7704,15 +8410,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C19" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -7721,15 +8427,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C20" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -7738,15 +8444,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C21" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -7760,10 +8466,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C22" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -7783,10 +8489,10 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C23" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -7806,10 +8512,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C24" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -7829,10 +8535,10 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C25" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -7852,10 +8558,10 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C26" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -7875,10 +8581,10 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C27" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -7898,10 +8604,10 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C28" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -7921,10 +8627,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="C29" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -7944,10 +8650,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C30" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -7967,10 +8673,10 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="C31" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -7990,10 +8696,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C32" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -8013,10 +8719,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="C33" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -8036,10 +8742,10 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C34" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -8056,22 +8762,24 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.85833333333333" customWidth="1"/>
+    <col min="2" max="2" width="22.7083333333333" customWidth="1"/>
+    <col min="3" max="3" width="28.5666666666667" customWidth="1"/>
+    <col min="4" max="4" width="15.5666666666667" customWidth="1"/>
+    <col min="5" max="5" width="16.1416666666667" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" customWidth="1"/>
+    <col min="7" max="7" width="11.1416666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -8085,30 +8793,30 @@
         <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E1" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F1" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="G1" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C2" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D2" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -8117,52 +8825,52 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="12.95" customHeight="1">
+    <row r="3" ht="12.95" customHeight="1" spans="1:6">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C3" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="D3" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="F3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="12.95" customHeight="1">
+    <row r="4" ht="12.95" customHeight="1" spans="1:6">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C4" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="D4" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="F4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>389</v>
+      </c>
+      <c r="C5" t="s">
+        <v>384</v>
+      </c>
+      <c r="D5" t="s">
         <v>385</v>
-      </c>
-      <c r="C5" t="s">
-        <v>380</v>
-      </c>
-      <c r="D5" t="s">
-        <v>381</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -8171,18 +8879,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C6" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D6" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -8191,18 +8899,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C7" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D7" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -8211,18 +8919,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C8" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D8" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -8231,18 +8939,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C9" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D9" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -8251,18 +8959,18 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C10" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D10" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -8271,18 +8979,18 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C11" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="D11" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E11" t="s">
         <v>44</v>
@@ -8293,6 +9001,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Cards.xlsx
+++ b/Assets/StreamingAssets/Configurations/Cards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10DE11E-A0D9-4062-90B4-175373358093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8446EA0-88BA-4AC0-A287-A93BD8BD414F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="395">
   <si>
     <t>ID</t>
   </si>
@@ -1219,6 +1219,9 @@
   </si>
   <si>
     <t>TrueStamina</t>
+  </si>
+  <si>
+    <t>Icon</t>
   </si>
 </sst>
 </file>
@@ -1290,7 +1293,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1303,6 +1306,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1588,43 +1593,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI65"/>
+  <dimension ref="A1:AJ65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.42578125" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
-    <col min="4" max="4" width="57.7109375" customWidth="1"/>
+    <col min="4" max="4" width="58" customWidth="1"/>
     <col min="5" max="5" width="10.42578125" style="2" customWidth="1"/>
     <col min="6" max="6" width="4.85546875" customWidth="1"/>
     <col min="7" max="7" width="7.85546875" customWidth="1"/>
     <col min="8" max="8" width="5" customWidth="1"/>
     <col min="9" max="9" width="5.5703125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" customWidth="1"/>
-    <col min="11" max="11" width="9.7109375" style="3" customWidth="1"/>
-    <col min="12" max="12" width="7.140625" customWidth="1"/>
-    <col min="13" max="13" width="14" style="3" customWidth="1"/>
-    <col min="14" max="14" width="10.28515625" customWidth="1"/>
-    <col min="15" max="16" width="13.7109375" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="3" customWidth="1"/>
-    <col min="18" max="18" width="9.7109375" customWidth="1"/>
-    <col min="19" max="19" width="12.140625" customWidth="1"/>
-    <col min="20" max="20" width="17.7109375" style="3" customWidth="1"/>
-    <col min="21" max="21" width="11" customWidth="1"/>
-    <col min="22" max="22" width="12.28515625" customWidth="1"/>
-    <col min="23" max="23" width="17.140625" style="3" customWidth="1"/>
-    <col min="26" max="26" width="17.7109375" style="3" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" customWidth="1"/>
-    <col min="28" max="28" width="11" customWidth="1"/>
-    <col min="29" max="29" width="17.7109375" style="3" customWidth="1"/>
-    <col min="30" max="30" width="12.42578125" customWidth="1"/>
-    <col min="31" max="31" width="12.42578125" style="3" customWidth="1"/>
-    <col min="32" max="32" width="12.28515625" customWidth="1"/>
-    <col min="33" max="33" width="9" style="3"/>
-    <col min="34" max="34" width="4.28515625" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="8" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" customWidth="1"/>
+    <col min="12" max="12" width="9.7109375" style="3" customWidth="1"/>
+    <col min="13" max="13" width="7.140625" customWidth="1"/>
+    <col min="14" max="14" width="14" style="3" customWidth="1"/>
+    <col min="15" max="15" width="10.28515625" customWidth="1"/>
+    <col min="16" max="17" width="13.7109375" customWidth="1"/>
+    <col min="18" max="18" width="9.7109375" style="3" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="20" max="20" width="12.140625" customWidth="1"/>
+    <col min="21" max="21" width="17.7109375" style="3" customWidth="1"/>
+    <col min="22" max="22" width="11" customWidth="1"/>
+    <col min="23" max="23" width="12.28515625" customWidth="1"/>
+    <col min="24" max="24" width="17.140625" style="3" customWidth="1"/>
+    <col min="27" max="27" width="17.7109375" style="3" customWidth="1"/>
+    <col min="28" max="28" width="10.7109375" customWidth="1"/>
+    <col min="29" max="29" width="11" customWidth="1"/>
+    <col min="30" max="30" width="17.7109375" style="3" customWidth="1"/>
+    <col min="31" max="31" width="12.42578125" customWidth="1"/>
+    <col min="32" max="32" width="12.42578125" style="3" customWidth="1"/>
+    <col min="33" max="33" width="12.28515625" customWidth="1"/>
+    <col min="34" max="34" width="9" style="3"/>
+    <col min="35" max="35" width="4.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:36">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1652,83 +1658,86 @@
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AE1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:36">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1750,40 +1759,43 @@
       <c r="G2" t="s">
         <v>39</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="K2" t="s">
         <v>40</v>
       </c>
-      <c r="K2"/>
-      <c r="L2" s="2">
+      <c r="L2"/>
+      <c r="M2" s="2">
         <v>4</v>
       </c>
-      <c r="M2" s="3">
+      <c r="N2" s="3">
         <v>3</v>
       </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
       <c r="O2">
         <v>0</v>
       </c>
-      <c r="Q2"/>
-      <c r="R2" s="2">
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="R2"/>
+      <c r="S2" s="2">
         <v>11</v>
       </c>
-      <c r="S2">
+      <c r="T2">
         <v>7</v>
       </c>
-      <c r="T2" s="3">
+      <c r="U2" s="3">
         <v>7</v>
       </c>
-      <c r="W2"/>
-      <c r="Z2"/>
-      <c r="AC2"/>
-      <c r="AE2"/>
-      <c r="AG2"/>
-      <c r="AH2" s="6"/>
-    </row>
-    <row r="3" spans="1:35">
+      <c r="X2"/>
+      <c r="AA2"/>
+      <c r="AD2"/>
+      <c r="AF2"/>
+      <c r="AH2"/>
+      <c r="AI2" s="6"/>
+    </row>
+    <row r="3" spans="1:36">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1805,40 +1817,43 @@
       <c r="G3" t="s">
         <v>39</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="K3" t="s">
         <v>40</v>
       </c>
-      <c r="K3"/>
-      <c r="L3" s="2">
-        <v>0</v>
-      </c>
-      <c r="M3" s="3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>1</v>
+      <c r="L3"/>
+      <c r="M3" s="2">
+        <v>0</v>
+      </c>
+      <c r="N3" s="3">
+        <v>0</v>
       </c>
       <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="Q3"/>
-      <c r="R3" s="2">
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="R3"/>
+      <c r="S3" s="2">
         <v>2</v>
       </c>
-      <c r="S3">
+      <c r="T3">
         <v>4</v>
       </c>
-      <c r="T3" s="3">
+      <c r="U3" s="3">
         <v>4</v>
       </c>
-      <c r="W3"/>
-      <c r="Z3"/>
-      <c r="AC3"/>
-      <c r="AE3"/>
-      <c r="AG3"/>
-      <c r="AH3" s="6"/>
-    </row>
-    <row r="4" spans="1:35">
+      <c r="X3"/>
+      <c r="AA3"/>
+      <c r="AD3"/>
+      <c r="AF3"/>
+      <c r="AH3"/>
+      <c r="AI3" s="6"/>
+    </row>
+    <row r="4" spans="1:36">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1863,42 +1878,45 @@
       <c r="H4" t="s">
         <v>50</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="K4" t="s">
         <v>40</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>5</v>
       </c>
-      <c r="M4" s="3">
+      <c r="N4" s="3">
         <v>4</v>
       </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
       <c r="O4">
         <v>0</v>
       </c>
-      <c r="R4" s="2">
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2">
         <v>11</v>
       </c>
-      <c r="S4">
+      <c r="T4">
         <v>15</v>
       </c>
-      <c r="T4" s="3">
+      <c r="U4" s="3">
         <v>18</v>
       </c>
-      <c r="U4">
+      <c r="V4">
         <v>56</v>
       </c>
-      <c r="V4">
+      <c r="W4">
         <v>9</v>
       </c>
-      <c r="W4" s="3">
+      <c r="X4" s="3">
         <v>12</v>
       </c>
-      <c r="AH4" s="6"/>
-    </row>
-    <row r="5" spans="1:35">
+      <c r="AI4" s="6"/>
+    </row>
+    <row r="5" spans="1:36">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1920,48 +1938,48 @@
       <c r="G5" t="s">
         <v>39</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>40</v>
       </c>
-      <c r="K5"/>
-      <c r="L5" s="2">
+      <c r="L5"/>
+      <c r="M5" s="2">
         <v>3</v>
       </c>
-      <c r="M5" s="3">
+      <c r="N5" s="3">
         <v>3</v>
       </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
       <c r="O5">
         <v>0</v>
       </c>
-      <c r="Q5"/>
-      <c r="R5" s="2">
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="R5"/>
+      <c r="S5" s="2">
         <v>11</v>
       </c>
-      <c r="S5">
+      <c r="T5">
         <v>5</v>
       </c>
-      <c r="T5" s="3">
+      <c r="U5" s="3">
         <v>5</v>
       </c>
-      <c r="U5" s="2">
+      <c r="V5" s="2">
         <v>2</v>
       </c>
-      <c r="V5">
+      <c r="W5">
         <v>2</v>
       </c>
-      <c r="W5" s="3">
+      <c r="X5" s="3">
         <v>2</v>
       </c>
-      <c r="Z5"/>
-      <c r="AC5"/>
-      <c r="AE5"/>
-      <c r="AG5"/>
-      <c r="AH5" s="6"/>
-    </row>
-    <row r="6" spans="1:35">
+      <c r="AA5"/>
+      <c r="AD5"/>
+      <c r="AF5"/>
+      <c r="AH5"/>
+      <c r="AI5" s="6"/>
+    </row>
+    <row r="6" spans="1:36">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1986,48 +2004,48 @@
       <c r="H6" t="s">
         <v>50</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>58</v>
       </c>
-      <c r="K6" s="3">
+      <c r="L6" s="3">
         <v>3</v>
       </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6" s="3">
-        <v>1</v>
-      </c>
-      <c r="N6">
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6" s="3">
         <v>1</v>
       </c>
       <c r="O6">
         <v>1</v>
       </c>
-      <c r="R6" s="2">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>2</v>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="S6" s="2">
+        <v>0</v>
       </c>
       <c r="V6">
         <v>2</v>
       </c>
-      <c r="W6" s="3">
+      <c r="W6">
+        <v>2</v>
+      </c>
+      <c r="X6" s="3">
         <v>7</v>
       </c>
-      <c r="X6">
+      <c r="Y6">
         <v>9</v>
       </c>
-      <c r="Y6">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="3">
-        <v>1</v>
-      </c>
-      <c r="AH6" s="6"/>
-    </row>
-    <row r="7" spans="1:35">
+      <c r="Z6">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="3">
+        <v>1</v>
+      </c>
+      <c r="AI6" s="6"/>
+    </row>
+    <row r="7" spans="1:36">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2049,51 +2067,51 @@
       <c r="G7" t="s">
         <v>39</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>40</v>
       </c>
-      <c r="K7"/>
-      <c r="L7" s="2">
+      <c r="L7"/>
+      <c r="M7" s="2">
         <v>5</v>
       </c>
-      <c r="M7" s="3">
+      <c r="N7" s="3">
         <v>4</v>
       </c>
-      <c r="N7">
-        <v>1</v>
-      </c>
       <c r="O7">
         <v>1</v>
       </c>
-      <c r="Q7"/>
-      <c r="R7" s="2">
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="R7"/>
+      <c r="S7" s="2">
         <v>4</v>
       </c>
-      <c r="T7"/>
-      <c r="U7" s="2">
+      <c r="U7"/>
+      <c r="V7" s="2">
         <v>21</v>
       </c>
-      <c r="V7">
+      <c r="W7">
         <v>2</v>
       </c>
-      <c r="W7" s="3">
+      <c r="X7" s="3">
         <v>2</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>14</v>
       </c>
-      <c r="Y7">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="3">
-        <v>1</v>
-      </c>
-      <c r="AC7"/>
-      <c r="AE7"/>
-      <c r="AG7"/>
-      <c r="AH7" s="6"/>
-    </row>
-    <row r="8" spans="1:35">
+      <c r="Z7">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AD7"/>
+      <c r="AF7"/>
+      <c r="AH7"/>
+      <c r="AI7" s="6"/>
+    </row>
+    <row r="8" spans="1:36">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2115,58 +2133,58 @@
       <c r="G8" t="s">
         <v>65</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>58</v>
       </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8" s="2">
-        <v>1</v>
-      </c>
-      <c r="M8" s="3">
-        <v>1</v>
-      </c>
-      <c r="N8">
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2">
+        <v>1</v>
+      </c>
+      <c r="N8" s="3">
         <v>1</v>
       </c>
       <c r="O8">
         <v>1</v>
       </c>
-      <c r="Q8"/>
-      <c r="R8" s="2">
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="R8"/>
+      <c r="S8" s="2">
         <v>2</v>
       </c>
-      <c r="S8">
+      <c r="T8">
         <v>7</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>7</v>
       </c>
-      <c r="U8" s="2">
+      <c r="V8" s="2">
         <v>3</v>
       </c>
-      <c r="V8">
-        <v>1</v>
-      </c>
-      <c r="W8" s="3">
-        <v>1</v>
-      </c>
-      <c r="X8" s="2">
+      <c r="W8">
+        <v>1</v>
+      </c>
+      <c r="X8" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="2">
         <v>14</v>
       </c>
-      <c r="Y8">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>1</v>
-      </c>
-      <c r="AC8"/>
-      <c r="AE8"/>
-      <c r="AG8"/>
-      <c r="AH8" s="6"/>
-    </row>
-    <row r="9" spans="1:35">
+      <c r="Z8">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AD8"/>
+      <c r="AF8"/>
+      <c r="AH8"/>
+      <c r="AI8" s="6"/>
+    </row>
+    <row r="9" spans="1:36">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2188,48 +2206,48 @@
       <c r="G9" t="s">
         <v>38</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>40</v>
       </c>
-      <c r="K9"/>
-      <c r="L9" s="2">
+      <c r="L9"/>
+      <c r="M9" s="2">
         <v>2</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2</v>
       </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
       <c r="O9">
         <v>0</v>
       </c>
-      <c r="Q9"/>
-      <c r="R9" s="2">
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="R9"/>
+      <c r="S9" s="2">
         <v>6</v>
       </c>
-      <c r="S9">
+      <c r="T9">
         <v>3</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4</v>
       </c>
-      <c r="U9" s="2">
+      <c r="V9" s="2">
         <v>2</v>
       </c>
-      <c r="V9">
+      <c r="W9">
         <v>3</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4</v>
       </c>
-      <c r="Z9"/>
-      <c r="AC9"/>
-      <c r="AE9"/>
-      <c r="AG9"/>
-      <c r="AH9" s="6"/>
-    </row>
-    <row r="10" spans="1:35">
+      <c r="AA9"/>
+      <c r="AD9"/>
+      <c r="AF9"/>
+      <c r="AH9"/>
+      <c r="AI9" s="6"/>
+    </row>
+    <row r="10" spans="1:36">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2251,48 +2269,48 @@
       <c r="G10" t="s">
         <v>65</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>40</v>
       </c>
-      <c r="K10"/>
-      <c r="L10" s="2">
+      <c r="L10"/>
+      <c r="M10" s="2">
         <v>2</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2</v>
       </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
       <c r="O10">
         <v>0</v>
       </c>
-      <c r="Q10"/>
-      <c r="R10" s="2">
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="R10"/>
+      <c r="S10" s="2">
         <v>7</v>
       </c>
-      <c r="S10">
+      <c r="T10">
         <v>2</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3</v>
       </c>
-      <c r="U10" s="2">
+      <c r="V10" s="2">
         <v>2</v>
       </c>
-      <c r="V10">
+      <c r="W10">
         <v>2</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3</v>
       </c>
-      <c r="Z10"/>
-      <c r="AC10"/>
-      <c r="AE10"/>
-      <c r="AG10"/>
-      <c r="AH10" s="6"/>
-    </row>
-    <row r="11" spans="1:35">
+      <c r="AA10"/>
+      <c r="AD10"/>
+      <c r="AF10"/>
+      <c r="AH10"/>
+      <c r="AI10" s="6"/>
+    </row>
+    <row r="11" spans="1:36">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2317,42 +2335,42 @@
       <c r="H11" t="s">
         <v>50</v>
       </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
         <v>40</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>2</v>
       </c>
-      <c r="M11" s="3">
+      <c r="N11" s="3">
         <v>2</v>
       </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
       <c r="O11">
         <v>0</v>
       </c>
-      <c r="R11" s="2">
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="S11" s="2">
         <v>15</v>
       </c>
-      <c r="S11">
+      <c r="T11">
         <v>2</v>
       </c>
-      <c r="T11" s="3">
+      <c r="U11" s="3">
         <v>3</v>
       </c>
-      <c r="U11" s="2">
+      <c r="V11" s="2">
         <v>2</v>
       </c>
-      <c r="V11">
+      <c r="W11">
         <v>2</v>
       </c>
-      <c r="W11" s="3">
+      <c r="X11" s="3">
         <v>3</v>
       </c>
-      <c r="AH11" s="6"/>
-    </row>
-    <row r="12" spans="1:35">
+      <c r="AI11" s="6"/>
+    </row>
+    <row r="12" spans="1:36">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2374,51 +2392,51 @@
       <c r="G12" t="s">
         <v>65</v>
       </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
         <v>40</v>
       </c>
-      <c r="K12"/>
-      <c r="L12" s="2">
+      <c r="L12"/>
+      <c r="M12" s="2">
         <v>6</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>6</v>
       </c>
-      <c r="N12">
-        <v>1</v>
-      </c>
       <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="Q12"/>
-      <c r="R12" s="2">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="R12"/>
+      <c r="S12" s="2">
         <v>11</v>
       </c>
-      <c r="S12">
+      <c r="T12">
         <v>9</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>13</v>
       </c>
-      <c r="U12" s="2">
+      <c r="V12" s="2">
         <v>11</v>
       </c>
-      <c r="V12">
+      <c r="W12">
         <v>9</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>13</v>
       </c>
-      <c r="Z12"/>
-      <c r="AC12"/>
-      <c r="AE12"/>
-      <c r="AG12"/>
-      <c r="AH12" s="6"/>
-      <c r="AI12" t="s">
+      <c r="AA12"/>
+      <c r="AD12"/>
+      <c r="AF12"/>
+      <c r="AH12"/>
+      <c r="AI12" s="6"/>
+      <c r="AJ12" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="1:35">
+    <row r="13" spans="1:36">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2440,48 +2458,48 @@
       <c r="G13" t="s">
         <v>39</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
         <v>40</v>
       </c>
-      <c r="K13"/>
-      <c r="L13" s="2">
+      <c r="L13"/>
+      <c r="M13" s="2">
         <v>5</v>
       </c>
-      <c r="M13" s="3">
+      <c r="N13" s="3">
         <v>5</v>
       </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
       <c r="O13">
         <v>0</v>
       </c>
-      <c r="Q13"/>
-      <c r="R13" s="2">
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="R13"/>
+      <c r="S13" s="2">
         <v>11</v>
       </c>
-      <c r="S13">
+      <c r="T13">
         <v>11</v>
       </c>
-      <c r="T13" s="3">
+      <c r="U13" s="3">
         <v>15</v>
       </c>
-      <c r="U13" s="2">
+      <c r="V13" s="2">
         <v>2</v>
       </c>
-      <c r="V13">
+      <c r="W13">
         <v>7</v>
       </c>
-      <c r="W13" s="3">
+      <c r="X13" s="3">
         <v>9</v>
       </c>
-      <c r="Z13"/>
-      <c r="AC13"/>
-      <c r="AE13"/>
-      <c r="AG13"/>
-      <c r="AH13" s="6"/>
-    </row>
-    <row r="14" spans="1:35">
+      <c r="AA13"/>
+      <c r="AD13"/>
+      <c r="AF13"/>
+      <c r="AH13"/>
+      <c r="AI13" s="6"/>
+    </row>
+    <row r="14" spans="1:36">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2503,40 +2521,40 @@
       <c r="G14" t="s">
         <v>38</v>
       </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
         <v>40</v>
       </c>
-      <c r="K14"/>
-      <c r="L14" s="2">
+      <c r="L14"/>
+      <c r="M14" s="2">
         <v>5</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>4</v>
       </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
       <c r="O14">
         <v>0</v>
       </c>
-      <c r="Q14"/>
-      <c r="R14" s="2">
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="R14"/>
+      <c r="S14" s="2">
         <v>6</v>
       </c>
-      <c r="S14">
+      <c r="T14">
         <v>6</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>8</v>
       </c>
-      <c r="W14"/>
-      <c r="Z14"/>
-      <c r="AC14"/>
-      <c r="AE14"/>
-      <c r="AG14"/>
-      <c r="AH14" s="6"/>
-    </row>
-    <row r="15" spans="1:35">
+      <c r="X14"/>
+      <c r="AA14"/>
+      <c r="AD14"/>
+      <c r="AF14"/>
+      <c r="AH14"/>
+      <c r="AI14" s="6"/>
+    </row>
+    <row r="15" spans="1:36">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2558,40 +2576,40 @@
       <c r="G15" t="s">
         <v>38</v>
       </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>40</v>
       </c>
-      <c r="K15"/>
-      <c r="L15" s="2">
+      <c r="L15"/>
+      <c r="M15" s="2">
         <v>4</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4</v>
       </c>
-      <c r="N15">
-        <v>1</v>
-      </c>
       <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="Q15"/>
-      <c r="R15" s="2">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="R15"/>
+      <c r="S15" s="2">
         <v>18</v>
       </c>
-      <c r="S15">
+      <c r="T15">
         <v>1.4</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1.8</v>
       </c>
-      <c r="W15"/>
-      <c r="Z15"/>
-      <c r="AC15"/>
-      <c r="AE15"/>
-      <c r="AG15"/>
-      <c r="AH15" s="6"/>
-    </row>
-    <row r="16" spans="1:35">
+      <c r="X15"/>
+      <c r="AA15"/>
+      <c r="AD15"/>
+      <c r="AF15"/>
+      <c r="AH15"/>
+      <c r="AI15" s="6"/>
+    </row>
+    <row r="16" spans="1:36">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2613,48 +2631,48 @@
       <c r="G16" t="s">
         <v>38</v>
       </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
         <v>40</v>
       </c>
-      <c r="K16"/>
-      <c r="L16" s="2">
+      <c r="L16"/>
+      <c r="M16" s="2">
         <v>6</v>
       </c>
-      <c r="M16" s="3">
+      <c r="N16" s="3">
         <v>5</v>
       </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
       <c r="O16">
         <v>0</v>
       </c>
-      <c r="Q16"/>
-      <c r="R16" s="2">
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="R16"/>
+      <c r="S16" s="2">
         <v>6</v>
       </c>
-      <c r="S16">
+      <c r="T16">
         <v>4</v>
       </c>
-      <c r="T16" s="3">
+      <c r="U16" s="3">
         <v>5</v>
       </c>
-      <c r="U16" s="2">
+      <c r="V16" s="2">
         <v>18</v>
       </c>
-      <c r="V16">
+      <c r="W16">
         <v>0.8</v>
       </c>
-      <c r="W16" s="3">
+      <c r="X16" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Z16"/>
-      <c r="AC16"/>
-      <c r="AE16"/>
-      <c r="AG16"/>
-      <c r="AH16" s="6"/>
-    </row>
-    <row r="17" spans="1:34">
+      <c r="AA16"/>
+      <c r="AD16"/>
+      <c r="AF16"/>
+      <c r="AH16"/>
+      <c r="AI16" s="6"/>
+    </row>
+    <row r="17" spans="1:35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2679,56 +2697,56 @@
       <c r="I17" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
         <v>40</v>
       </c>
-      <c r="K17"/>
-      <c r="L17" s="2">
+      <c r="L17"/>
+      <c r="M17" s="2">
         <v>3</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3</v>
       </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
       <c r="O17">
-        <v>1</v>
-      </c>
-      <c r="Q17"/>
-      <c r="R17" s="2">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>1</v>
+      </c>
+      <c r="R17"/>
+      <c r="S17" s="2">
         <v>19</v>
       </c>
-      <c r="S17">
-        <v>1</v>
-      </c>
-      <c r="T17" s="3">
-        <v>1</v>
-      </c>
-      <c r="U17" s="2">
+      <c r="T17">
+        <v>1</v>
+      </c>
+      <c r="U17" s="3">
+        <v>1</v>
+      </c>
+      <c r="V17" s="2">
         <v>2</v>
       </c>
-      <c r="V17">
+      <c r="W17">
         <v>4</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6</v>
       </c>
-      <c r="X17" s="2">
+      <c r="Y17" s="2">
         <v>21</v>
       </c>
-      <c r="Y17">
+      <c r="Z17">
         <v>2</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3</v>
       </c>
-      <c r="AC17"/>
-      <c r="AE17"/>
-      <c r="AG17"/>
-      <c r="AH17" s="7"/>
-    </row>
-    <row r="18" spans="1:34">
+      <c r="AD17"/>
+      <c r="AF17"/>
+      <c r="AH17"/>
+      <c r="AI17" s="7"/>
+    </row>
+    <row r="18" spans="1:35">
       <c r="A18">
         <v>18</v>
       </c>
@@ -2753,39 +2771,39 @@
       <c r="H18" t="s">
         <v>50</v>
       </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
         <v>40</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>4</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3</v>
       </c>
-      <c r="N18">
-        <v>1</v>
-      </c>
       <c r="O18">
-        <v>0</v>
-      </c>
-      <c r="R18" s="2">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="S18" s="2">
         <v>15</v>
       </c>
-      <c r="S18">
+      <c r="T18">
         <v>5</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>7</v>
       </c>
-      <c r="AD18">
+      <c r="AE18">
         <v>63</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1.5</v>
       </c>
-      <c r="AH18" s="6"/>
-    </row>
-    <row r="19" spans="1:34">
+      <c r="AI18" s="6"/>
+    </row>
+    <row r="19" spans="1:35">
       <c r="A19">
         <v>19</v>
       </c>
@@ -2807,48 +2825,48 @@
       <c r="G19" t="s">
         <v>65</v>
       </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
         <v>40</v>
       </c>
-      <c r="K19"/>
-      <c r="L19" s="2">
+      <c r="L19"/>
+      <c r="M19" s="2">
         <v>5</v>
       </c>
-      <c r="M19" s="3">
+      <c r="N19" s="3">
         <v>4</v>
       </c>
-      <c r="N19">
-        <v>1</v>
-      </c>
       <c r="O19">
         <v>1</v>
       </c>
-      <c r="Q19"/>
-      <c r="R19" s="2">
+      <c r="P19">
+        <v>1</v>
+      </c>
+      <c r="R19"/>
+      <c r="S19" s="2">
         <v>23</v>
       </c>
-      <c r="S19">
-        <v>1</v>
-      </c>
-      <c r="T19" s="3">
-        <v>1</v>
-      </c>
-      <c r="U19" s="2">
+      <c r="T19">
+        <v>1</v>
+      </c>
+      <c r="U19" s="3">
+        <v>1</v>
+      </c>
+      <c r="V19" s="2">
         <v>7</v>
       </c>
-      <c r="V19">
-        <v>1</v>
-      </c>
-      <c r="W19" s="3">
+      <c r="W19">
+        <v>1</v>
+      </c>
+      <c r="X19" s="3">
         <v>2</v>
       </c>
-      <c r="Z19"/>
-      <c r="AC19"/>
-      <c r="AE19"/>
-      <c r="AG19"/>
-      <c r="AH19" s="6"/>
-    </row>
-    <row r="20" spans="1:34">
+      <c r="AA19"/>
+      <c r="AD19"/>
+      <c r="AF19"/>
+      <c r="AH19"/>
+      <c r="AI19" s="6"/>
+    </row>
+    <row r="20" spans="1:35">
       <c r="A20">
         <v>20</v>
       </c>
@@ -2873,42 +2891,42 @@
       <c r="H20" t="s">
         <v>50</v>
       </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>40</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>6</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>6</v>
       </c>
-      <c r="N20">
-        <v>1</v>
-      </c>
       <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="2">
+        <v>1</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="2">
         <v>11</v>
       </c>
-      <c r="S20">
+      <c r="T20">
         <v>24</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>30</v>
       </c>
-      <c r="AD20">
+      <c r="AE20">
         <v>62</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>7</v>
       </c>
-      <c r="AH20" s="7"/>
-    </row>
-    <row r="21" spans="1:34">
+      <c r="AI20" s="7"/>
+    </row>
+    <row r="21" spans="1:35">
       <c r="A21">
         <v>21</v>
       </c>
@@ -2933,51 +2951,51 @@
       <c r="H21" t="s">
         <v>50</v>
       </c>
-      <c r="J21" t="s">
+      <c r="K21" t="s">
         <v>40</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>5</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4</v>
       </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
       <c r="O21">
-        <v>1</v>
-      </c>
-      <c r="R21" s="2">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>1</v>
+      </c>
+      <c r="S21" s="2">
         <v>26</v>
       </c>
-      <c r="S21">
+      <c r="T21">
         <v>2</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2</v>
       </c>
-      <c r="U21" s="2">
+      <c r="V21" s="2">
         <v>11</v>
       </c>
-      <c r="V21">
+      <c r="W21">
         <v>30</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>42</v>
       </c>
-      <c r="X21">
+      <c r="Y21">
         <v>2</v>
       </c>
-      <c r="Y21">
+      <c r="Z21">
         <v>5</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>7</v>
       </c>
-      <c r="AH21" s="6"/>
-    </row>
-    <row r="22" spans="1:34">
+      <c r="AI21" s="6"/>
+    </row>
+    <row r="22" spans="1:35">
       <c r="A22">
         <v>22</v>
       </c>
@@ -2999,48 +3017,48 @@
       <c r="G22" t="s">
         <v>38</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>40</v>
       </c>
-      <c r="K22"/>
-      <c r="L22" s="2">
+      <c r="L22"/>
+      <c r="M22" s="2">
         <v>4</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>4</v>
       </c>
-      <c r="N22">
-        <v>1</v>
-      </c>
       <c r="O22">
         <v>1</v>
       </c>
-      <c r="Q22"/>
-      <c r="R22" s="2">
+      <c r="P22">
+        <v>1</v>
+      </c>
+      <c r="R22"/>
+      <c r="S22" s="2">
         <v>6</v>
       </c>
-      <c r="S22">
+      <c r="T22">
         <v>2</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>4</v>
       </c>
-      <c r="U22" s="2">
+      <c r="V22" s="2">
         <v>28</v>
       </c>
-      <c r="V22">
-        <v>1</v>
-      </c>
-      <c r="W22" s="3">
-        <v>1</v>
-      </c>
-      <c r="Z22"/>
-      <c r="AC22"/>
-      <c r="AE22"/>
-      <c r="AG22"/>
-      <c r="AH22" s="6"/>
-    </row>
-    <row r="23" spans="1:34">
+      <c r="W22">
+        <v>1</v>
+      </c>
+      <c r="X22" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA22"/>
+      <c r="AD22"/>
+      <c r="AF22"/>
+      <c r="AH22"/>
+      <c r="AI22" s="6"/>
+    </row>
+    <row r="23" spans="1:35">
       <c r="A23">
         <v>23</v>
       </c>
@@ -3062,48 +3080,48 @@
       <c r="G23" t="s">
         <v>38</v>
       </c>
-      <c r="J23" t="s">
+      <c r="K23" t="s">
         <v>40</v>
       </c>
-      <c r="K23"/>
-      <c r="L23" s="2">
-        <v>1</v>
-      </c>
-      <c r="M23" s="3">
-        <v>1</v>
-      </c>
-      <c r="N23">
+      <c r="L23"/>
+      <c r="M23" s="2">
+        <v>1</v>
+      </c>
+      <c r="N23" s="3">
         <v>1</v>
       </c>
       <c r="O23">
-        <v>0</v>
-      </c>
-      <c r="Q23"/>
-      <c r="R23" s="2">
+        <v>1</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="R23"/>
+      <c r="S23" s="2">
         <v>6</v>
       </c>
-      <c r="S23">
+      <c r="T23">
         <v>5</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>7</v>
       </c>
-      <c r="U23" s="2">
+      <c r="V23" s="2">
         <v>2</v>
       </c>
-      <c r="V23">
-        <v>1</v>
-      </c>
-      <c r="W23" s="3">
-        <v>1</v>
-      </c>
-      <c r="Z23"/>
-      <c r="AC23"/>
-      <c r="AE23"/>
-      <c r="AG23"/>
-      <c r="AH23" s="6"/>
-    </row>
-    <row r="24" spans="1:34">
+      <c r="W23">
+        <v>1</v>
+      </c>
+      <c r="X23" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA23"/>
+      <c r="AD23"/>
+      <c r="AF23"/>
+      <c r="AH23"/>
+      <c r="AI23" s="6"/>
+    </row>
+    <row r="24" spans="1:35">
       <c r="A24">
         <v>24</v>
       </c>
@@ -3128,48 +3146,48 @@
       <c r="H24" t="s">
         <v>50</v>
       </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
         <v>40</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>4</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4</v>
       </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
       <c r="O24">
         <v>0</v>
       </c>
-      <c r="R24" s="2">
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="S24" s="2">
         <v>15</v>
       </c>
-      <c r="S24">
+      <c r="T24">
         <v>3</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>4</v>
       </c>
-      <c r="U24" s="2">
+      <c r="V24" s="2">
         <v>11</v>
       </c>
-      <c r="V24">
+      <c r="W24">
         <v>8</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>11</v>
       </c>
-      <c r="AD24">
+      <c r="AE24">
         <v>63</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>3</v>
       </c>
-      <c r="AH24" s="6"/>
-    </row>
-    <row r="25" spans="1:34">
+      <c r="AI24" s="6"/>
+    </row>
+    <row r="25" spans="1:35">
       <c r="A25">
         <v>25</v>
       </c>
@@ -3191,40 +3209,40 @@
       <c r="G25" t="s">
         <v>65</v>
       </c>
-      <c r="J25" t="s">
+      <c r="K25" t="s">
         <v>40</v>
       </c>
-      <c r="K25"/>
-      <c r="L25" s="2">
+      <c r="L25"/>
+      <c r="M25" s="2">
         <v>3</v>
       </c>
-      <c r="M25" s="3">
+      <c r="N25" s="3">
         <v>2</v>
       </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
       <c r="O25">
         <v>0</v>
       </c>
-      <c r="Q25"/>
-      <c r="R25" s="2">
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="R25"/>
+      <c r="S25" s="2">
         <v>7</v>
       </c>
-      <c r="S25">
+      <c r="T25">
         <v>3</v>
       </c>
-      <c r="T25" s="3">
+      <c r="U25" s="3">
         <v>5</v>
       </c>
-      <c r="W25"/>
-      <c r="Z25"/>
-      <c r="AC25"/>
-      <c r="AE25"/>
-      <c r="AG25"/>
-      <c r="AH25" s="6"/>
-    </row>
-    <row r="26" spans="1:34">
+      <c r="X25"/>
+      <c r="AA25"/>
+      <c r="AD25"/>
+      <c r="AF25"/>
+      <c r="AH25"/>
+      <c r="AI25" s="6"/>
+    </row>
+    <row r="26" spans="1:35">
       <c r="A26">
         <v>26</v>
       </c>
@@ -3246,48 +3264,48 @@
       <c r="G26" t="s">
         <v>65</v>
       </c>
-      <c r="J26" t="s">
+      <c r="K26" t="s">
         <v>40</v>
       </c>
-      <c r="K26"/>
-      <c r="L26" s="2">
+      <c r="L26"/>
+      <c r="M26" s="2">
         <v>3</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2</v>
       </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
       <c r="O26">
         <v>0</v>
       </c>
-      <c r="Q26"/>
-      <c r="R26" s="2">
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="R26"/>
+      <c r="S26" s="2">
         <v>7</v>
       </c>
-      <c r="S26">
+      <c r="T26">
         <v>3</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4</v>
       </c>
-      <c r="U26" s="2">
+      <c r="V26" s="2">
         <v>2</v>
       </c>
-      <c r="V26">
+      <c r="W26">
         <v>4</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>6</v>
       </c>
-      <c r="Z26"/>
-      <c r="AC26"/>
-      <c r="AE26"/>
-      <c r="AG26"/>
-      <c r="AH26" s="6"/>
-    </row>
-    <row r="27" spans="1:34">
+      <c r="AA26"/>
+      <c r="AD26"/>
+      <c r="AF26"/>
+      <c r="AH26"/>
+      <c r="AI26" s="6"/>
+    </row>
+    <row r="27" spans="1:35">
       <c r="A27">
         <v>27</v>
       </c>
@@ -3312,54 +3330,54 @@
       <c r="H27" t="s">
         <v>50</v>
       </c>
-      <c r="J27" t="s">
+      <c r="K27" t="s">
         <v>40</v>
       </c>
-      <c r="L27">
+      <c r="M27">
         <v>8</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6</v>
       </c>
-      <c r="N27">
-        <v>1</v>
-      </c>
       <c r="O27">
         <v>1</v>
       </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
-      <c r="R27" s="2">
+      <c r="P27">
+        <v>1</v>
+      </c>
+      <c r="R27" s="3">
+        <v>0</v>
+      </c>
+      <c r="S27" s="2">
         <v>11</v>
       </c>
-      <c r="S27">
+      <c r="T27">
         <v>12</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>18</v>
       </c>
-      <c r="U27" s="2">
+      <c r="V27" s="2">
         <v>56</v>
       </c>
-      <c r="V27">
+      <c r="W27">
         <v>24</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>30</v>
       </c>
-      <c r="X27">
+      <c r="Y27">
         <v>57</v>
       </c>
-      <c r="Y27">
+      <c r="Z27">
         <v>36</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>44</v>
       </c>
-      <c r="AH27" s="7"/>
-    </row>
-    <row r="28" spans="1:34">
+      <c r="AI27" s="7"/>
+    </row>
+    <row r="28" spans="1:35">
       <c r="A28">
         <v>28</v>
       </c>
@@ -3384,39 +3402,39 @@
       <c r="H28" t="s">
         <v>125</v>
       </c>
-      <c r="J28" t="s">
+      <c r="K28" t="s">
         <v>40</v>
       </c>
-      <c r="L28">
-        <v>1</v>
-      </c>
-      <c r="M28" s="3">
-        <v>0</v>
-      </c>
-      <c r="N28">
-        <v>1</v>
+      <c r="M28">
+        <v>1</v>
+      </c>
+      <c r="N28" s="3">
+        <v>0</v>
       </c>
       <c r="O28">
-        <v>0</v>
-      </c>
-      <c r="R28" s="2">
+        <v>1</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="S28" s="2">
         <v>2</v>
       </c>
-      <c r="S28">
+      <c r="T28">
         <v>6</v>
       </c>
-      <c r="T28" s="3">
+      <c r="U28" s="3">
         <v>8</v>
       </c>
-      <c r="AD28">
+      <c r="AE28">
         <v>21</v>
       </c>
-      <c r="AE28" s="3">
+      <c r="AF28" s="3">
         <v>12</v>
       </c>
-      <c r="AH28" s="6"/>
-    </row>
-    <row r="29" spans="1:34">
+      <c r="AI28" s="6"/>
+    </row>
+    <row r="29" spans="1:35">
       <c r="A29">
         <v>30</v>
       </c>
@@ -3441,56 +3459,56 @@
       <c r="I29" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J29" t="s">
+      <c r="K29" t="s">
         <v>40</v>
       </c>
-      <c r="K29"/>
-      <c r="L29" s="2">
+      <c r="L29"/>
+      <c r="M29" s="2">
         <v>5</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>5</v>
       </c>
-      <c r="N29">
-        <v>1</v>
-      </c>
       <c r="O29">
         <v>1</v>
       </c>
-      <c r="Q29"/>
-      <c r="R29" s="2">
+      <c r="P29">
+        <v>1</v>
+      </c>
+      <c r="R29"/>
+      <c r="S29" s="2">
         <v>32</v>
       </c>
-      <c r="S29">
+      <c r="T29">
         <v>30</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>30</v>
       </c>
-      <c r="U29" s="2">
+      <c r="V29" s="2">
         <v>2</v>
       </c>
-      <c r="V29">
+      <c r="W29">
         <v>3</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>5</v>
       </c>
-      <c r="X29" s="2">
+      <c r="Y29" s="2">
         <v>21</v>
       </c>
-      <c r="Y29">
+      <c r="Z29">
         <v>2</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>3</v>
       </c>
-      <c r="AC29"/>
-      <c r="AE29"/>
-      <c r="AG29"/>
-      <c r="AH29" s="6"/>
-    </row>
-    <row r="30" spans="1:34">
+      <c r="AD29"/>
+      <c r="AF29"/>
+      <c r="AH29"/>
+      <c r="AI29" s="6"/>
+    </row>
+    <row r="30" spans="1:35">
       <c r="A30">
         <v>31</v>
       </c>
@@ -3515,48 +3533,48 @@
       <c r="I30" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J30" t="s">
+      <c r="K30" t="s">
         <v>40</v>
       </c>
-      <c r="K30"/>
-      <c r="L30" s="2">
+      <c r="L30"/>
+      <c r="M30" s="2">
         <v>4</v>
       </c>
-      <c r="M30" s="3">
+      <c r="N30" s="3">
         <v>4</v>
       </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
       <c r="O30">
-        <v>1</v>
-      </c>
-      <c r="Q30"/>
-      <c r="R30" s="2">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>1</v>
+      </c>
+      <c r="R30"/>
+      <c r="S30" s="2">
         <v>33</v>
       </c>
-      <c r="S30">
+      <c r="T30">
         <v>50</v>
       </c>
-      <c r="T30" s="3">
+      <c r="U30" s="3">
         <v>70</v>
       </c>
-      <c r="U30" s="2">
+      <c r="V30" s="2">
         <v>2</v>
       </c>
-      <c r="V30">
+      <c r="W30">
         <v>2</v>
       </c>
-      <c r="W30" s="3">
+      <c r="X30" s="3">
         <v>4</v>
       </c>
-      <c r="Z30"/>
-      <c r="AC30"/>
-      <c r="AE30"/>
-      <c r="AG30"/>
-      <c r="AH30" s="7"/>
-    </row>
-    <row r="31" spans="1:34">
+      <c r="AA30"/>
+      <c r="AD30"/>
+      <c r="AF30"/>
+      <c r="AH30"/>
+      <c r="AI30" s="7"/>
+    </row>
+    <row r="31" spans="1:35">
       <c r="A31">
         <v>32</v>
       </c>
@@ -3581,48 +3599,48 @@
       <c r="I31" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J31" t="s">
+      <c r="K31" t="s">
         <v>40</v>
       </c>
-      <c r="K31"/>
-      <c r="L31" s="2">
+      <c r="L31"/>
+      <c r="M31" s="2">
         <v>4</v>
       </c>
-      <c r="M31" s="3">
+      <c r="N31" s="3">
         <v>3</v>
       </c>
-      <c r="N31">
-        <v>1</v>
-      </c>
       <c r="O31">
         <v>1</v>
       </c>
-      <c r="Q31"/>
-      <c r="R31" s="2">
+      <c r="P31">
+        <v>1</v>
+      </c>
+      <c r="R31"/>
+      <c r="S31" s="2">
         <v>33</v>
       </c>
-      <c r="S31">
+      <c r="T31">
         <v>20</v>
       </c>
-      <c r="T31" s="3">
+      <c r="U31" s="3">
         <v>30</v>
       </c>
-      <c r="U31" s="2">
+      <c r="V31" s="2">
         <v>35</v>
       </c>
-      <c r="V31">
-        <v>1</v>
-      </c>
-      <c r="W31" s="3">
-        <v>1</v>
-      </c>
-      <c r="Z31"/>
-      <c r="AC31"/>
-      <c r="AE31"/>
-      <c r="AG31"/>
-      <c r="AH31" s="7"/>
-    </row>
-    <row r="32" spans="1:34">
+      <c r="W31">
+        <v>1</v>
+      </c>
+      <c r="X31" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA31"/>
+      <c r="AD31"/>
+      <c r="AF31"/>
+      <c r="AH31"/>
+      <c r="AI31" s="7"/>
+    </row>
+    <row r="32" spans="1:35">
       <c r="A32">
         <v>33</v>
       </c>
@@ -3647,31 +3665,31 @@
       <c r="I32" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J32" t="s">
+      <c r="K32" t="s">
         <v>40</v>
       </c>
-      <c r="K32"/>
-      <c r="L32" s="2">
+      <c r="L32"/>
+      <c r="M32" s="2">
         <v>7</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>6</v>
       </c>
-      <c r="N32">
-        <v>1</v>
-      </c>
       <c r="O32">
         <v>1</v>
       </c>
-      <c r="Q32"/>
-      <c r="T32"/>
-      <c r="W32"/>
-      <c r="Z32"/>
-      <c r="AC32"/>
-      <c r="AE32"/>
-      <c r="AG32"/>
-    </row>
-    <row r="33" spans="1:33">
+      <c r="P32">
+        <v>1</v>
+      </c>
+      <c r="R32"/>
+      <c r="U32"/>
+      <c r="X32"/>
+      <c r="AA32"/>
+      <c r="AD32"/>
+      <c r="AF32"/>
+      <c r="AH32"/>
+    </row>
+    <row r="33" spans="1:34">
       <c r="A33">
         <v>34</v>
       </c>
@@ -3696,38 +3714,38 @@
       <c r="H33" t="s">
         <v>50</v>
       </c>
-      <c r="J33" t="s">
+      <c r="K33" t="s">
         <v>40</v>
       </c>
-      <c r="L33">
+      <c r="M33">
         <v>8</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>7</v>
       </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
       <c r="O33">
-        <v>1</v>
-      </c>
-      <c r="R33" s="2">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>1</v>
+      </c>
+      <c r="S33" s="2">
         <v>11</v>
       </c>
-      <c r="S33">
+      <c r="T33">
         <v>38</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>52</v>
       </c>
-      <c r="AD33">
+      <c r="AE33">
         <v>64</v>
       </c>
-      <c r="AE33" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:33">
+      <c r="AF33" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:34">
       <c r="A34">
         <v>35</v>
       </c>
@@ -3752,35 +3770,35 @@
       <c r="H34" t="s">
         <v>50</v>
       </c>
-      <c r="J34" t="s">
+      <c r="K34" t="s">
         <v>40</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>3</v>
       </c>
-      <c r="M34" s="3">
+      <c r="N34" s="3">
         <v>3</v>
       </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
       <c r="O34">
         <v>0</v>
       </c>
-      <c r="Q34" s="3">
-        <v>0</v>
-      </c>
-      <c r="R34" s="2">
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="2">
         <v>15</v>
       </c>
-      <c r="S34">
+      <c r="T34">
         <v>3</v>
       </c>
-      <c r="T34" s="3">
+      <c r="U34" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:33">
+    <row r="35" spans="1:34">
       <c r="A35">
         <v>36</v>
       </c>
@@ -3805,32 +3823,32 @@
       <c r="H35" t="s">
         <v>125</v>
       </c>
-      <c r="J35" t="s">
+      <c r="K35" t="s">
         <v>40</v>
       </c>
-      <c r="L35">
+      <c r="M35">
         <v>3</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3</v>
       </c>
-      <c r="N35">
-        <v>1</v>
-      </c>
       <c r="O35">
-        <v>0</v>
-      </c>
-      <c r="R35" s="2">
+        <v>1</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="S35" s="2">
         <v>11</v>
       </c>
-      <c r="S35">
+      <c r="T35">
         <v>18</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:33">
+    <row r="36" spans="1:34">
       <c r="A36">
         <v>37</v>
       </c>
@@ -3855,41 +3873,41 @@
       <c r="H36" t="s">
         <v>50</v>
       </c>
-      <c r="J36" t="s">
+      <c r="K36" t="s">
         <v>40</v>
       </c>
-      <c r="L36">
+      <c r="M36">
         <v>3</v>
       </c>
-      <c r="M36" s="3">
+      <c r="N36" s="3">
         <v>3</v>
       </c>
-      <c r="N36">
-        <v>1</v>
-      </c>
       <c r="O36">
-        <v>0</v>
-      </c>
-      <c r="R36" s="2">
+        <v>1</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="S36" s="2">
         <v>15</v>
       </c>
-      <c r="S36">
+      <c r="T36">
         <v>3</v>
       </c>
-      <c r="T36" s="3">
+      <c r="U36" s="3">
         <v>4</v>
       </c>
-      <c r="U36" s="2">
+      <c r="V36" s="2">
         <v>2</v>
       </c>
-      <c r="V36">
+      <c r="W36">
         <v>6</v>
       </c>
-      <c r="W36" s="3">
+      <c r="X36" s="3">
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:33">
+    <row r="37" spans="1:34">
       <c r="A37">
         <v>38</v>
       </c>
@@ -3911,47 +3929,47 @@
       <c r="G37" t="s">
         <v>65</v>
       </c>
-      <c r="J37" t="s">
+      <c r="K37" t="s">
         <v>40</v>
       </c>
-      <c r="K37"/>
-      <c r="L37" s="2">
+      <c r="L37"/>
+      <c r="M37" s="2">
         <v>3</v>
       </c>
-      <c r="M37" s="3">
+      <c r="N37" s="3">
         <v>3</v>
       </c>
-      <c r="N37">
-        <v>1</v>
-      </c>
       <c r="O37">
-        <v>0</v>
-      </c>
-      <c r="Q37"/>
-      <c r="R37" s="2">
+        <v>1</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="R37"/>
+      <c r="S37" s="2">
         <v>7</v>
       </c>
-      <c r="S37">
+      <c r="T37">
         <v>3</v>
       </c>
-      <c r="T37" s="3">
+      <c r="U37" s="3">
         <v>4</v>
       </c>
-      <c r="U37" s="2">
+      <c r="V37" s="2">
         <v>2</v>
       </c>
-      <c r="V37">
+      <c r="W37">
         <v>6</v>
       </c>
-      <c r="W37" s="3">
+      <c r="X37" s="3">
         <v>8</v>
       </c>
-      <c r="Z37"/>
-      <c r="AC37"/>
-      <c r="AE37"/>
-      <c r="AG37"/>
-    </row>
-    <row r="38" spans="1:33">
+      <c r="AA37"/>
+      <c r="AD37"/>
+      <c r="AF37"/>
+      <c r="AH37"/>
+    </row>
+    <row r="38" spans="1:34">
       <c r="A38">
         <v>39</v>
       </c>
@@ -3973,47 +3991,47 @@
       <c r="G38" t="s">
         <v>39</v>
       </c>
-      <c r="J38" t="s">
+      <c r="K38" t="s">
         <v>40</v>
       </c>
-      <c r="K38"/>
-      <c r="L38" s="2">
-        <v>1</v>
-      </c>
-      <c r="M38" s="3">
-        <v>1</v>
-      </c>
-      <c r="N38">
+      <c r="L38"/>
+      <c r="M38" s="2">
+        <v>1</v>
+      </c>
+      <c r="N38" s="3">
         <v>1</v>
       </c>
       <c r="O38">
         <v>1</v>
       </c>
-      <c r="Q38"/>
-      <c r="R38" s="2">
+      <c r="P38">
+        <v>1</v>
+      </c>
+      <c r="R38"/>
+      <c r="S38" s="2">
         <v>21</v>
       </c>
-      <c r="S38">
+      <c r="T38">
         <v>4</v>
       </c>
-      <c r="T38" s="3">
+      <c r="U38" s="3">
         <v>5</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>2</v>
       </c>
-      <c r="V38">
+      <c r="W38">
         <v>3</v>
       </c>
-      <c r="W38" s="3">
+      <c r="X38" s="3">
         <v>5</v>
       </c>
-      <c r="Z38"/>
-      <c r="AC38"/>
-      <c r="AE38"/>
-      <c r="AG38"/>
-    </row>
-    <row r="39" spans="1:33">
+      <c r="AA38"/>
+      <c r="AD38"/>
+      <c r="AF38"/>
+      <c r="AH38"/>
+    </row>
+    <row r="39" spans="1:34">
       <c r="A39">
         <v>40</v>
       </c>
@@ -4035,47 +4053,47 @@
       <c r="G39" t="s">
         <v>39</v>
       </c>
-      <c r="J39" t="s">
+      <c r="K39" t="s">
         <v>40</v>
       </c>
-      <c r="K39"/>
-      <c r="L39" s="2">
-        <v>1</v>
-      </c>
-      <c r="M39" s="3">
-        <v>1</v>
-      </c>
-      <c r="N39">
+      <c r="L39"/>
+      <c r="M39" s="2">
+        <v>1</v>
+      </c>
+      <c r="N39" s="3">
         <v>1</v>
       </c>
       <c r="O39">
         <v>1</v>
       </c>
-      <c r="Q39"/>
-      <c r="R39" s="2">
+      <c r="P39">
+        <v>1</v>
+      </c>
+      <c r="R39"/>
+      <c r="S39" s="2">
         <v>5</v>
       </c>
-      <c r="S39">
-        <v>1</v>
-      </c>
-      <c r="T39" s="3">
+      <c r="T39">
+        <v>1</v>
+      </c>
+      <c r="U39" s="3">
         <v>2</v>
       </c>
-      <c r="U39" s="2">
+      <c r="V39" s="2">
         <v>2</v>
       </c>
-      <c r="V39">
+      <c r="W39">
         <v>6</v>
       </c>
-      <c r="W39" s="3">
+      <c r="X39" s="3">
         <v>7</v>
       </c>
-      <c r="Z39"/>
-      <c r="AC39"/>
-      <c r="AE39"/>
-      <c r="AG39"/>
-    </row>
-    <row r="40" spans="1:33">
+      <c r="AA39"/>
+      <c r="AD39"/>
+      <c r="AF39"/>
+      <c r="AH39"/>
+    </row>
+    <row r="40" spans="1:34">
       <c r="A40">
         <v>41</v>
       </c>
@@ -4097,47 +4115,47 @@
       <c r="G40" t="s">
         <v>65</v>
       </c>
-      <c r="J40" t="s">
+      <c r="K40" t="s">
         <v>40</v>
       </c>
-      <c r="K40"/>
-      <c r="L40" s="2">
+      <c r="L40"/>
+      <c r="M40" s="2">
         <v>4</v>
       </c>
-      <c r="M40" s="3">
+      <c r="N40" s="3">
         <v>3</v>
       </c>
-      <c r="N40">
-        <v>1</v>
-      </c>
       <c r="O40">
         <v>1</v>
       </c>
-      <c r="Q40"/>
-      <c r="R40" s="2">
+      <c r="P40">
+        <v>1</v>
+      </c>
+      <c r="R40"/>
+      <c r="S40" s="2">
         <v>7</v>
       </c>
-      <c r="S40">
+      <c r="T40">
         <v>4</v>
       </c>
-      <c r="T40" s="3">
+      <c r="U40" s="3">
         <v>5</v>
       </c>
-      <c r="U40" s="2">
+      <c r="V40" s="2">
         <v>38</v>
       </c>
-      <c r="V40">
+      <c r="W40">
         <v>4</v>
       </c>
-      <c r="W40" s="3">
+      <c r="X40" s="3">
         <v>5</v>
       </c>
-      <c r="Z40"/>
-      <c r="AC40"/>
-      <c r="AE40"/>
-      <c r="AG40"/>
-    </row>
-    <row r="41" spans="1:33">
+      <c r="AA40"/>
+      <c r="AD40"/>
+      <c r="AF40"/>
+      <c r="AH40"/>
+    </row>
+    <row r="41" spans="1:34">
       <c r="A41">
         <v>42</v>
       </c>
@@ -4159,47 +4177,47 @@
       <c r="G41" t="s">
         <v>38</v>
       </c>
-      <c r="J41" t="s">
+      <c r="K41" t="s">
         <v>40</v>
       </c>
-      <c r="K41"/>
-      <c r="L41" s="2">
+      <c r="L41"/>
+      <c r="M41" s="2">
         <v>2</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2</v>
       </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
       <c r="O41">
         <v>0</v>
       </c>
-      <c r="Q41"/>
-      <c r="R41" s="2">
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="R41"/>
+      <c r="S41" s="2">
         <v>6</v>
       </c>
-      <c r="S41">
+      <c r="T41">
         <v>3</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3</v>
       </c>
-      <c r="U41" s="2">
+      <c r="V41" s="2">
         <v>39</v>
       </c>
-      <c r="V41">
+      <c r="W41">
         <v>2</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3</v>
       </c>
-      <c r="Z41"/>
-      <c r="AC41"/>
-      <c r="AE41"/>
-      <c r="AG41"/>
-    </row>
-    <row r="42" spans="1:33">
+      <c r="AA41"/>
+      <c r="AD41"/>
+      <c r="AF41"/>
+      <c r="AH41"/>
+    </row>
+    <row r="42" spans="1:34">
       <c r="A42">
         <v>43</v>
       </c>
@@ -4221,47 +4239,47 @@
       <c r="G42" t="s">
         <v>65</v>
       </c>
-      <c r="J42" t="s">
+      <c r="K42" t="s">
         <v>40</v>
       </c>
-      <c r="K42"/>
-      <c r="L42" s="2">
+      <c r="L42"/>
+      <c r="M42" s="2">
         <v>4</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>3</v>
       </c>
-      <c r="N42">
-        <v>1</v>
-      </c>
       <c r="O42">
         <v>1</v>
       </c>
-      <c r="Q42"/>
-      <c r="R42" s="2">
+      <c r="P42">
+        <v>1</v>
+      </c>
+      <c r="R42"/>
+      <c r="S42" s="2">
         <v>7</v>
       </c>
-      <c r="S42">
-        <v>1</v>
-      </c>
-      <c r="T42" s="3">
+      <c r="T42">
+        <v>1</v>
+      </c>
+      <c r="U42" s="3">
         <v>3</v>
       </c>
-      <c r="U42" s="2">
+      <c r="V42" s="2">
         <v>41</v>
       </c>
-      <c r="V42">
-        <v>1</v>
-      </c>
-      <c r="W42" s="3">
-        <v>1</v>
-      </c>
-      <c r="Z42"/>
-      <c r="AC42"/>
-      <c r="AE42"/>
-      <c r="AG42"/>
-    </row>
-    <row r="43" spans="1:33">
+      <c r="W42">
+        <v>1</v>
+      </c>
+      <c r="X42" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA42"/>
+      <c r="AD42"/>
+      <c r="AF42"/>
+      <c r="AH42"/>
+    </row>
+    <row r="43" spans="1:34">
       <c r="A43">
         <v>44</v>
       </c>
@@ -4283,55 +4301,55 @@
       <c r="G43" t="s">
         <v>38</v>
       </c>
-      <c r="J43" t="s">
+      <c r="K43" t="s">
         <v>40</v>
       </c>
-      <c r="K43"/>
-      <c r="L43" s="2">
+      <c r="L43"/>
+      <c r="M43" s="2">
         <v>7</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4</v>
       </c>
-      <c r="N43">
-        <v>0</v>
-      </c>
       <c r="O43">
-        <v>1</v>
-      </c>
-      <c r="Q43"/>
-      <c r="R43" s="2">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>1</v>
+      </c>
+      <c r="R43"/>
+      <c r="S43" s="2">
         <v>6</v>
       </c>
-      <c r="S43">
+      <c r="T43">
         <v>5</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5</v>
       </c>
-      <c r="U43" s="2">
+      <c r="V43" s="2">
         <v>14</v>
       </c>
-      <c r="V43">
-        <v>1</v>
-      </c>
-      <c r="W43" s="3">
-        <v>1</v>
-      </c>
-      <c r="X43" s="2">
+      <c r="W43">
+        <v>1</v>
+      </c>
+      <c r="X43" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y43" s="2">
         <v>18</v>
       </c>
-      <c r="Y43">
+      <c r="Z43">
         <v>0.9</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1.2</v>
       </c>
-      <c r="AC43"/>
-      <c r="AE43"/>
-      <c r="AG43"/>
-    </row>
-    <row r="44" spans="1:33">
+      <c r="AD43"/>
+      <c r="AF43"/>
+      <c r="AH43"/>
+    </row>
+    <row r="44" spans="1:34">
       <c r="A44">
         <v>45</v>
       </c>
@@ -4356,41 +4374,41 @@
       <c r="H44" t="s">
         <v>50</v>
       </c>
-      <c r="J44" t="s">
+      <c r="K44" t="s">
         <v>40</v>
       </c>
-      <c r="L44">
+      <c r="M44">
         <v>6</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4</v>
       </c>
-      <c r="N44">
-        <v>1</v>
-      </c>
       <c r="O44">
         <v>1</v>
       </c>
-      <c r="R44" s="2">
+      <c r="P44">
+        <v>1</v>
+      </c>
+      <c r="S44" s="2">
         <v>15</v>
       </c>
-      <c r="S44">
+      <c r="T44">
         <v>2</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2</v>
       </c>
-      <c r="U44" s="2">
+      <c r="V44" s="2">
         <v>42</v>
       </c>
-      <c r="V44">
+      <c r="W44">
         <v>8</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:33">
+    <row r="45" spans="1:34">
       <c r="A45">
         <v>46</v>
       </c>
@@ -4412,55 +4430,55 @@
       <c r="G45" t="s">
         <v>65</v>
       </c>
-      <c r="J45" t="s">
+      <c r="K45" t="s">
         <v>40</v>
       </c>
-      <c r="K45"/>
-      <c r="L45" s="2">
+      <c r="L45"/>
+      <c r="M45" s="2">
         <v>5</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4</v>
       </c>
-      <c r="N45">
-        <v>0</v>
-      </c>
       <c r="O45">
-        <v>1</v>
-      </c>
-      <c r="Q45"/>
-      <c r="R45" s="2">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>1</v>
+      </c>
+      <c r="R45"/>
+      <c r="S45" s="2">
         <v>7</v>
       </c>
-      <c r="S45">
+      <c r="T45">
         <v>7</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>9</v>
       </c>
-      <c r="U45" s="2">
+      <c r="V45" s="2">
         <v>26</v>
       </c>
-      <c r="V45">
+      <c r="W45">
         <v>2</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2</v>
       </c>
-      <c r="X45" s="2">
+      <c r="Y45" s="2">
         <v>2</v>
       </c>
-      <c r="Y45">
+      <c r="Z45">
         <v>7</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>8</v>
       </c>
-      <c r="AC45"/>
-      <c r="AE45"/>
-      <c r="AG45"/>
-    </row>
-    <row r="46" spans="1:33">
+      <c r="AD45"/>
+      <c r="AF45"/>
+      <c r="AH45"/>
+    </row>
+    <row r="46" spans="1:34">
       <c r="A46">
         <v>47</v>
       </c>
@@ -4485,55 +4503,55 @@
       <c r="I46" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J46" t="s">
+      <c r="K46" t="s">
         <v>40</v>
       </c>
-      <c r="K46"/>
-      <c r="L46" s="2">
+      <c r="L46"/>
+      <c r="M46" s="2">
         <v>10</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6</v>
       </c>
-      <c r="N46">
-        <v>1</v>
-      </c>
       <c r="O46">
         <v>1</v>
       </c>
-      <c r="Q46"/>
-      <c r="R46" s="2">
+      <c r="P46">
+        <v>1</v>
+      </c>
+      <c r="R46"/>
+      <c r="S46" s="2">
         <v>32</v>
       </c>
-      <c r="S46">
+      <c r="T46">
         <v>40</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>40</v>
       </c>
-      <c r="U46" s="2">
+      <c r="V46" s="2">
         <v>33</v>
       </c>
-      <c r="V46">
+      <c r="W46">
         <v>30</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>30</v>
       </c>
-      <c r="X46" s="2">
+      <c r="Y46" s="2">
         <v>19</v>
       </c>
-      <c r="Y46">
-        <v>1</v>
-      </c>
-      <c r="Z46" s="3">
-        <v>1</v>
-      </c>
-      <c r="AC46"/>
-      <c r="AE46"/>
-      <c r="AG46"/>
-    </row>
-    <row r="47" spans="1:33">
+      <c r="Z46">
+        <v>1</v>
+      </c>
+      <c r="AA46" s="3">
+        <v>1</v>
+      </c>
+      <c r="AD46"/>
+      <c r="AF46"/>
+      <c r="AH46"/>
+    </row>
+    <row r="47" spans="1:34">
       <c r="A47">
         <v>48</v>
       </c>
@@ -4555,39 +4573,39 @@
       <c r="G47" t="s">
         <v>65</v>
       </c>
-      <c r="J47" t="s">
+      <c r="K47" t="s">
         <v>40</v>
       </c>
-      <c r="K47"/>
-      <c r="L47" s="2">
+      <c r="L47"/>
+      <c r="M47" s="2">
         <v>2</v>
       </c>
-      <c r="M47" s="3">
-        <v>1</v>
-      </c>
-      <c r="N47">
-        <v>0</v>
+      <c r="N47" s="3">
+        <v>1</v>
       </c>
       <c r="O47">
         <v>0</v>
       </c>
-      <c r="Q47"/>
-      <c r="R47" s="2">
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="R47"/>
+      <c r="S47" s="2">
         <v>11</v>
       </c>
-      <c r="S47">
+      <c r="T47">
         <v>10</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>14</v>
       </c>
-      <c r="W47"/>
-      <c r="Z47"/>
-      <c r="AC47"/>
-      <c r="AE47"/>
-      <c r="AG47"/>
-    </row>
-    <row r="48" spans="1:33">
+      <c r="X47"/>
+      <c r="AA47"/>
+      <c r="AD47"/>
+      <c r="AF47"/>
+      <c r="AH47"/>
+    </row>
+    <row r="48" spans="1:34">
       <c r="A48">
         <v>49</v>
       </c>
@@ -4609,47 +4627,47 @@
       <c r="G48" t="s">
         <v>38</v>
       </c>
-      <c r="J48" t="s">
+      <c r="K48" t="s">
         <v>40</v>
       </c>
-      <c r="K48"/>
-      <c r="L48" s="2">
+      <c r="L48"/>
+      <c r="M48" s="2">
         <v>4</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3</v>
       </c>
-      <c r="N48">
-        <v>0</v>
-      </c>
       <c r="O48">
         <v>0</v>
       </c>
-      <c r="Q48"/>
-      <c r="R48" s="2">
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="R48"/>
+      <c r="S48" s="2">
         <v>11</v>
       </c>
-      <c r="S48">
+      <c r="T48">
         <v>8</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>11</v>
       </c>
-      <c r="U48" s="2">
+      <c r="V48" s="2">
         <v>6</v>
       </c>
-      <c r="V48">
+      <c r="W48">
         <v>3</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3</v>
       </c>
-      <c r="Z48"/>
-      <c r="AC48"/>
-      <c r="AE48"/>
-      <c r="AG48"/>
-    </row>
-    <row r="49" spans="1:33">
+      <c r="AA48"/>
+      <c r="AD48"/>
+      <c r="AF48"/>
+      <c r="AH48"/>
+    </row>
+    <row r="49" spans="1:34">
       <c r="A49">
         <v>50</v>
       </c>
@@ -4674,41 +4692,41 @@
       <c r="H49" t="s">
         <v>125</v>
       </c>
-      <c r="J49" t="s">
+      <c r="K49" t="s">
         <v>40</v>
       </c>
-      <c r="L49">
+      <c r="M49">
         <v>4</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3</v>
       </c>
-      <c r="N49">
-        <v>0</v>
-      </c>
       <c r="O49">
         <v>0</v>
       </c>
-      <c r="R49" s="2">
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="S49" s="2">
         <v>11</v>
       </c>
-      <c r="S49">
+      <c r="T49">
         <v>7</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>11</v>
       </c>
-      <c r="U49" s="2">
+      <c r="V49" s="2">
         <v>45</v>
       </c>
-      <c r="V49">
+      <c r="W49">
         <v>2</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:33">
+    <row r="50" spans="1:34">
       <c r="A50">
         <v>51</v>
       </c>
@@ -4730,47 +4748,47 @@
       <c r="G50" t="s">
         <v>38</v>
       </c>
-      <c r="J50" t="s">
+      <c r="K50" t="s">
         <v>40</v>
       </c>
-      <c r="K50"/>
-      <c r="L50" s="2">
+      <c r="L50"/>
+      <c r="M50" s="2">
         <v>5</v>
       </c>
-      <c r="M50" s="3">
+      <c r="N50" s="3">
         <v>4</v>
       </c>
-      <c r="N50">
-        <v>1</v>
-      </c>
       <c r="O50">
         <v>1</v>
       </c>
-      <c r="Q50"/>
-      <c r="R50" s="2">
+      <c r="P50">
+        <v>1</v>
+      </c>
+      <c r="R50"/>
+      <c r="S50" s="2">
         <v>6</v>
       </c>
-      <c r="S50">
+      <c r="T50">
         <v>5</v>
       </c>
-      <c r="T50" s="3">
+      <c r="U50" s="3">
         <v>7</v>
       </c>
-      <c r="U50" s="2">
+      <c r="V50" s="2">
         <v>18</v>
       </c>
-      <c r="V50">
+      <c r="W50">
         <v>1.1000000000000001</v>
       </c>
-      <c r="W50" s="3">
+      <c r="X50" s="3">
         <v>1.7</v>
       </c>
-      <c r="Z50"/>
-      <c r="AC50"/>
-      <c r="AE50"/>
-      <c r="AG50"/>
-    </row>
-    <row r="51" spans="1:33">
+      <c r="AA50"/>
+      <c r="AD50"/>
+      <c r="AF50"/>
+      <c r="AH50"/>
+    </row>
+    <row r="51" spans="1:34">
       <c r="A51">
         <v>52</v>
       </c>
@@ -4792,47 +4810,47 @@
       <c r="G51" t="s">
         <v>38</v>
       </c>
-      <c r="J51" t="s">
+      <c r="K51" t="s">
         <v>40</v>
       </c>
-      <c r="K51"/>
-      <c r="L51" s="2">
+      <c r="L51"/>
+      <c r="M51" s="2">
         <v>9</v>
       </c>
-      <c r="M51" s="3">
+      <c r="N51" s="3">
         <v>6</v>
       </c>
-      <c r="N51">
-        <v>1</v>
-      </c>
       <c r="O51">
         <v>1</v>
       </c>
-      <c r="Q51"/>
-      <c r="R51" s="2">
+      <c r="P51">
+        <v>1</v>
+      </c>
+      <c r="R51"/>
+      <c r="S51" s="2">
         <v>6</v>
       </c>
-      <c r="S51">
-        <v>1</v>
-      </c>
-      <c r="T51" s="3">
+      <c r="T51">
+        <v>1</v>
+      </c>
+      <c r="U51" s="3">
         <v>3</v>
       </c>
-      <c r="U51" s="2">
+      <c r="V51" s="2">
         <v>49</v>
       </c>
-      <c r="V51">
-        <v>1</v>
-      </c>
-      <c r="W51" s="3">
-        <v>1</v>
-      </c>
-      <c r="Z51"/>
-      <c r="AC51"/>
-      <c r="AE51"/>
-      <c r="AG51"/>
-    </row>
-    <row r="52" spans="1:33">
+      <c r="W51">
+        <v>1</v>
+      </c>
+      <c r="X51" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA51"/>
+      <c r="AD51"/>
+      <c r="AF51"/>
+      <c r="AH51"/>
+    </row>
+    <row r="52" spans="1:34">
       <c r="A52">
         <v>53</v>
       </c>
@@ -4854,47 +4872,47 @@
       <c r="G52" t="s">
         <v>39</v>
       </c>
-      <c r="J52" t="s">
+      <c r="K52" t="s">
         <v>40</v>
       </c>
-      <c r="K52"/>
-      <c r="L52" s="2">
-        <v>1</v>
-      </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
-      <c r="N52">
-        <v>1</v>
+      <c r="L52"/>
+      <c r="M52" s="2">
+        <v>1</v>
+      </c>
+      <c r="N52" s="3">
+        <v>0</v>
       </c>
       <c r="O52">
         <v>1</v>
       </c>
-      <c r="Q52"/>
-      <c r="R52" s="2">
+      <c r="P52">
+        <v>1</v>
+      </c>
+      <c r="R52"/>
+      <c r="S52" s="2">
         <v>9</v>
       </c>
-      <c r="S52">
+      <c r="T52">
         <v>2</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2</v>
       </c>
-      <c r="U52" s="2">
+      <c r="V52" s="2">
         <v>21</v>
       </c>
-      <c r="V52">
+      <c r="W52">
         <v>2</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2</v>
       </c>
-      <c r="Z52"/>
-      <c r="AC52"/>
-      <c r="AE52"/>
-      <c r="AG52"/>
-    </row>
-    <row r="53" spans="1:33">
+      <c r="AA52"/>
+      <c r="AD52"/>
+      <c r="AF52"/>
+      <c r="AH52"/>
+    </row>
+    <row r="53" spans="1:34">
       <c r="A53">
         <v>54</v>
       </c>
@@ -4919,44 +4937,44 @@
       <c r="H53" t="s">
         <v>50</v>
       </c>
-      <c r="J53" t="s">
+      <c r="K53" t="s">
         <v>40</v>
       </c>
-      <c r="L53">
+      <c r="M53">
         <v>5</v>
       </c>
-      <c r="M53" s="3">
+      <c r="N53" s="3">
         <v>5</v>
       </c>
-      <c r="N53">
-        <v>0</v>
-      </c>
       <c r="O53">
-        <v>1</v>
-      </c>
-      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>1</v>
+      </c>
+      <c r="R53" s="3">
         <v>6</v>
       </c>
-      <c r="R53">
+      <c r="S53">
         <v>50</v>
       </c>
-      <c r="S53">
+      <c r="T53">
         <v>3</v>
       </c>
-      <c r="T53" s="3">
+      <c r="U53" s="3">
         <v>4</v>
       </c>
-      <c r="U53">
+      <c r="V53">
         <v>51</v>
       </c>
-      <c r="V53">
+      <c r="W53">
         <v>-0.5</v>
       </c>
-      <c r="W53" s="3">
+      <c r="X53" s="3">
         <v>-0.5</v>
       </c>
     </row>
-    <row r="54" spans="1:33">
+    <row r="54" spans="1:34">
       <c r="A54">
         <v>55</v>
       </c>
@@ -4981,53 +4999,53 @@
       <c r="H54" t="s">
         <v>50</v>
       </c>
-      <c r="J54" t="s">
+      <c r="K54" t="s">
         <v>58</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>14</v>
       </c>
-      <c r="L54">
+      <c r="M54">
         <v>2</v>
       </c>
-      <c r="M54" s="3">
-        <v>1</v>
-      </c>
-      <c r="N54">
-        <v>0</v>
+      <c r="N54" s="3">
+        <v>1</v>
       </c>
       <c r="O54">
-        <v>1</v>
-      </c>
-      <c r="R54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>1</v>
+      </c>
+      <c r="S54">
         <v>15</v>
       </c>
-      <c r="S54">
+      <c r="T54">
         <v>3</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4</v>
       </c>
-      <c r="U54">
+      <c r="V54">
         <v>14</v>
       </c>
-      <c r="V54">
-        <v>1</v>
-      </c>
-      <c r="W54" s="3">
-        <v>1</v>
-      </c>
-      <c r="X54">
+      <c r="W54">
+        <v>1</v>
+      </c>
+      <c r="X54" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y54">
         <v>52</v>
       </c>
-      <c r="Y54">
+      <c r="Z54">
         <v>3</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:33">
+    <row r="55" spans="1:34">
       <c r="A55">
         <v>56</v>
       </c>
@@ -5052,42 +5070,42 @@
       <c r="H55" t="s">
         <v>50</v>
       </c>
-      <c r="J55" t="s">
+      <c r="K55" t="s">
         <v>40</v>
       </c>
-      <c r="L55">
+      <c r="M55">
         <v>4</v>
       </c>
-      <c r="M55" s="3">
+      <c r="N55" s="3">
         <v>3</v>
       </c>
-      <c r="N55">
-        <v>1</v>
-      </c>
       <c r="O55">
         <v>1</v>
       </c>
-      <c r="R55">
+      <c r="P55">
+        <v>1</v>
+      </c>
+      <c r="S55">
         <v>15</v>
       </c>
-      <c r="S55">
-        <v>1</v>
-      </c>
-      <c r="T55" s="3">
+      <c r="T55">
+        <v>1</v>
+      </c>
+      <c r="U55" s="3">
         <v>3</v>
       </c>
-      <c r="U55">
+      <c r="V55">
         <v>60</v>
       </c>
-      <c r="V55">
-        <v>1</v>
-      </c>
-      <c r="W55" s="3">
-        <v>1</v>
-      </c>
-      <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="1:33">
+      <c r="W55">
+        <v>1</v>
+      </c>
+      <c r="X55" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="1:34">
       <c r="A56">
         <v>57</v>
       </c>
@@ -5112,54 +5130,54 @@
       <c r="H56" t="s">
         <v>125</v>
       </c>
-      <c r="J56" t="s">
+      <c r="K56" t="s">
         <v>58</v>
       </c>
-      <c r="K56" s="3">
+      <c r="L56" s="3">
         <v>3</v>
       </c>
-      <c r="L56">
+      <c r="M56">
         <v>2</v>
       </c>
-      <c r="M56" s="3">
-        <v>1</v>
-      </c>
-      <c r="N56">
-        <v>0</v>
+      <c r="N56" s="3">
+        <v>1</v>
       </c>
       <c r="O56">
-        <v>1</v>
-      </c>
-      <c r="R56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>1</v>
+      </c>
+      <c r="S56">
         <v>45</v>
       </c>
-      <c r="S56">
+      <c r="T56">
         <v>3</v>
       </c>
-      <c r="T56" s="3">
+      <c r="U56" s="3">
         <v>4</v>
       </c>
-      <c r="U56">
+      <c r="V56">
         <v>11</v>
       </c>
-      <c r="V56">
+      <c r="W56">
         <v>12</v>
       </c>
-      <c r="W56" s="3">
+      <c r="X56" s="3">
         <v>18</v>
       </c>
-      <c r="X56">
+      <c r="Y56">
         <v>14</v>
       </c>
-      <c r="Y56">
-        <v>1</v>
-      </c>
-      <c r="Z56" s="3">
-        <v>1</v>
-      </c>
-      <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="1:33">
+      <c r="Z56">
+        <v>1</v>
+      </c>
+      <c r="AA56" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="1:34">
       <c r="A57">
         <v>58</v>
       </c>
@@ -5184,53 +5202,53 @@
       <c r="H57" t="s">
         <v>125</v>
       </c>
-      <c r="J57" t="s">
+      <c r="K57" t="s">
         <v>58</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3</v>
       </c>
-      <c r="L57">
+      <c r="M57">
         <v>2</v>
       </c>
-      <c r="M57" s="3">
-        <v>1</v>
-      </c>
-      <c r="N57">
+      <c r="N57" s="3">
         <v>1</v>
       </c>
       <c r="O57">
         <v>1</v>
       </c>
-      <c r="R57">
+      <c r="P57">
+        <v>1</v>
+      </c>
+      <c r="S57">
         <v>2</v>
       </c>
-      <c r="S57">
+      <c r="T57">
         <v>5</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6</v>
       </c>
-      <c r="U57">
+      <c r="V57">
         <v>2</v>
       </c>
-      <c r="V57">
+      <c r="W57">
         <v>5</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>6</v>
       </c>
-      <c r="X57">
+      <c r="Y57">
         <v>66</v>
       </c>
-      <c r="Y57">
+      <c r="Z57">
         <v>0.6</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1.2</v>
       </c>
     </row>
-    <row r="58" spans="1:33">
+    <row r="58" spans="1:34">
       <c r="A58">
         <v>59</v>
       </c>
@@ -5255,32 +5273,32 @@
       <c r="H58" t="s">
         <v>125</v>
       </c>
-      <c r="J58" t="s">
+      <c r="K58" t="s">
         <v>393</v>
       </c>
-      <c r="L58">
+      <c r="M58">
         <v>3</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2</v>
       </c>
-      <c r="N58">
-        <v>1</v>
-      </c>
       <c r="O58">
-        <v>0</v>
-      </c>
-      <c r="R58">
+        <v>1</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="S58">
         <v>66</v>
       </c>
-      <c r="S58">
+      <c r="T58">
         <v>1.2</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1.7</v>
       </c>
     </row>
-    <row r="59" spans="1:33">
+    <row r="59" spans="1:34">
       <c r="A59">
         <v>60</v>
       </c>
@@ -5305,41 +5323,41 @@
       <c r="H59" t="s">
         <v>125</v>
       </c>
-      <c r="J59" t="s">
+      <c r="K59" t="s">
         <v>393</v>
       </c>
-      <c r="L59">
+      <c r="M59">
         <v>3</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3</v>
       </c>
-      <c r="N59">
-        <v>1</v>
-      </c>
       <c r="O59">
-        <v>0</v>
-      </c>
-      <c r="R59">
+        <v>1</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="S59">
         <v>2</v>
       </c>
-      <c r="S59">
+      <c r="T59">
         <v>7</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9</v>
       </c>
-      <c r="U59">
+      <c r="V59">
         <v>66</v>
       </c>
-      <c r="V59">
+      <c r="W59">
         <v>0.9</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1.4</v>
       </c>
     </row>
-    <row r="60" spans="1:33">
+    <row r="60" spans="1:34">
       <c r="A60">
         <v>61</v>
       </c>
@@ -5364,41 +5382,41 @@
       <c r="H60" t="s">
         <v>125</v>
       </c>
-      <c r="J60" t="s">
+      <c r="K60" t="s">
         <v>393</v>
       </c>
-      <c r="L60">
+      <c r="M60">
         <v>2</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2</v>
       </c>
-      <c r="N60">
-        <v>1</v>
-      </c>
       <c r="O60">
         <v>1</v>
       </c>
-      <c r="R60">
+      <c r="P60">
+        <v>1</v>
+      </c>
+      <c r="S60">
         <v>66</v>
       </c>
-      <c r="S60">
+      <c r="T60">
         <v>3</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4</v>
       </c>
-      <c r="U60">
+      <c r="V60">
         <v>67</v>
       </c>
-      <c r="V60">
+      <c r="W60">
         <v>-1</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>-1</v>
       </c>
     </row>
-    <row r="61" spans="1:33">
+    <row r="61" spans="1:34">
       <c r="A61">
         <v>62</v>
       </c>
@@ -5423,44 +5441,44 @@
       <c r="H61" t="s">
         <v>125</v>
       </c>
-      <c r="J61" t="s">
+      <c r="K61" t="s">
         <v>58</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>14</v>
       </c>
-      <c r="L61">
+      <c r="M61">
         <v>2</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2</v>
       </c>
-      <c r="N61">
-        <v>0</v>
-      </c>
       <c r="O61">
-        <v>1</v>
-      </c>
-      <c r="R61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>1</v>
+      </c>
+      <c r="S61">
         <v>66</v>
       </c>
-      <c r="S61">
+      <c r="T61">
         <v>1.2</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1.5</v>
       </c>
-      <c r="U61">
+      <c r="V61">
         <v>62</v>
       </c>
-      <c r="V61">
-        <v>1</v>
-      </c>
-      <c r="W61" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:33">
+      <c r="W61">
+        <v>1</v>
+      </c>
+      <c r="X61" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:34">
       <c r="A62">
         <v>63</v>
       </c>
@@ -5488,41 +5506,42 @@
       <c r="I62" t="s">
         <v>125</v>
       </c>
-      <c r="J62" t="s">
+      <c r="J62"/>
+      <c r="K62" t="s">
         <v>40</v>
       </c>
-      <c r="L62">
+      <c r="M62">
         <v>5</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4</v>
       </c>
-      <c r="N62">
-        <v>1</v>
-      </c>
       <c r="O62">
         <v>1</v>
       </c>
-      <c r="R62">
+      <c r="P62">
+        <v>1</v>
+      </c>
+      <c r="S62">
         <v>15</v>
       </c>
-      <c r="S62">
+      <c r="T62">
         <v>6</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>8</v>
       </c>
-      <c r="U62">
+      <c r="V62">
         <v>45</v>
       </c>
-      <c r="V62">
+      <c r="W62">
         <v>6</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="1:33">
+    <row r="63" spans="1:34">
       <c r="A63">
         <v>64</v>
       </c>
@@ -5550,59 +5569,60 @@
       <c r="I63" t="s">
         <v>125</v>
       </c>
-      <c r="J63" t="s">
+      <c r="J63"/>
+      <c r="K63" t="s">
         <v>393</v>
       </c>
-      <c r="L63">
+      <c r="M63">
         <v>6</v>
       </c>
-      <c r="M63" s="3">
+      <c r="N63" s="3">
         <v>5</v>
       </c>
-      <c r="N63">
-        <v>0</v>
-      </c>
       <c r="O63">
-        <v>1</v>
-      </c>
-      <c r="R63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>1</v>
+      </c>
+      <c r="S63">
         <v>33</v>
       </c>
-      <c r="S63">
+      <c r="T63">
         <v>-30</v>
       </c>
-      <c r="T63" s="3">
+      <c r="U63" s="3">
         <v>-30</v>
       </c>
-      <c r="U63">
+      <c r="V63">
         <v>11</v>
       </c>
-      <c r="V63">
+      <c r="W63">
         <v>32</v>
       </c>
-      <c r="W63" s="3">
+      <c r="X63" s="3">
         <v>40</v>
       </c>
-      <c r="X63">
+      <c r="Y63">
         <v>2</v>
       </c>
-      <c r="Y63">
+      <c r="Z63">
         <v>15</v>
       </c>
-      <c r="Z63" s="3">
+      <c r="AA63" s="3">
         <v>18</v>
       </c>
-      <c r="AA63">
+      <c r="AB63">
         <v>66</v>
       </c>
-      <c r="AB63">
+      <c r="AC63">
         <v>1.5</v>
       </c>
-      <c r="AC63" s="3">
+      <c r="AD63" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:33">
+    <row r="64" spans="1:34">
       <c r="A64">
         <v>65</v>
       </c>
@@ -5621,41 +5641,41 @@
       <c r="G64" t="s">
         <v>39</v>
       </c>
-      <c r="J64" t="s">
+      <c r="K64" t="s">
         <v>40</v>
       </c>
-      <c r="L64">
+      <c r="M64">
         <v>4</v>
       </c>
-      <c r="M64" s="3">
+      <c r="N64" s="3">
         <v>4</v>
       </c>
-      <c r="N64">
-        <v>1</v>
-      </c>
       <c r="O64">
         <v>1</v>
       </c>
-      <c r="R64">
+      <c r="P64">
+        <v>1</v>
+      </c>
+      <c r="S64">
         <v>33</v>
       </c>
-      <c r="S64">
+      <c r="T64">
         <v>50</v>
       </c>
-      <c r="T64" s="3">
+      <c r="U64" s="3">
         <v>50</v>
       </c>
-      <c r="U64">
+      <c r="V64">
         <v>68</v>
       </c>
-      <c r="V64">
+      <c r="W64">
         <v>0.1</v>
       </c>
-      <c r="W64" s="3">
+      <c r="X64" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="65" spans="1:23">
+    <row r="65" spans="1:24">
       <c r="A65">
         <v>66</v>
       </c>
@@ -5674,43 +5694,43 @@
       <c r="G65" t="s">
         <v>39</v>
       </c>
-      <c r="J65" t="s">
+      <c r="K65" t="s">
         <v>40</v>
       </c>
-      <c r="L65">
+      <c r="M65">
         <v>5</v>
       </c>
-      <c r="M65" s="3">
+      <c r="N65" s="3">
         <v>5</v>
       </c>
-      <c r="N65">
-        <v>1</v>
-      </c>
       <c r="O65">
         <v>1</v>
       </c>
-      <c r="R65">
+      <c r="P65">
+        <v>1</v>
+      </c>
+      <c r="S65">
         <v>19</v>
       </c>
-      <c r="S65">
-        <v>1</v>
-      </c>
-      <c r="T65" s="3">
-        <v>1</v>
-      </c>
-      <c r="U65">
+      <c r="T65">
+        <v>1</v>
+      </c>
+      <c r="U65" s="3">
+        <v>1</v>
+      </c>
+      <c r="V65">
         <v>69</v>
       </c>
-      <c r="V65">
-        <v>1</v>
-      </c>
-      <c r="W65" s="3">
+      <c r="W65">
+        <v>1</v>
+      </c>
+      <c r="X65" s="3">
         <v>1.5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7227,22 +7247,23 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
     <col min="2" max="2" width="27.42578125" customWidth="1"/>
     <col min="3" max="3" width="14.42578125" customWidth="1"/>
-    <col min="4" max="5" width="16.140625" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="10.140625" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" customWidth="1"/>
+    <col min="5" max="6" width="11.42578125" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="10.140625" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7258,38 +7279,41 @@
       <c r="E1" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="G1" t="s">
         <v>17</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>18</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>20</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>21</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>23</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>24</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>26</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>27</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>347</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:16">
       <c r="A2">
         <v>0</v>
       </c>
@@ -7305,20 +7329,20 @@
       <c r="E2">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
         <v>12</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>-1</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:16">
       <c r="A3">
         <v>1</v>
       </c>
@@ -7334,14 +7358,14 @@
       <c r="E3">
         <v>0</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>16</v>
       </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4">
         <v>2</v>
       </c>
@@ -7358,7 +7382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:16">
       <c r="A5">
         <v>3</v>
       </c>
@@ -7374,26 +7398,26 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>13</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>0.5</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>53</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>0.5</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>54</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:16">
       <c r="A6">
         <v>4</v>
       </c>
@@ -7409,14 +7433,14 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>5</v>
       </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="H6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7">
         <v>5</v>
       </c>
@@ -7432,14 +7456,14 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>20</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:16">
       <c r="A8">
         <v>6</v>
       </c>
@@ -7455,14 +7479,14 @@
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>22</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:16">
       <c r="A9">
         <v>7</v>
       </c>
@@ -7478,14 +7502,14 @@
       <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>25</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>-0.5</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:16">
       <c r="A10">
         <v>8</v>
       </c>
@@ -7501,14 +7525,14 @@
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>27</v>
       </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="H10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11">
         <v>9</v>
       </c>
@@ -7524,20 +7548,20 @@
       <c r="E11">
         <v>1</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>29</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>18</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>30</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>-1</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:16">
       <c r="A12">
         <v>10</v>
       </c>
@@ -7553,20 +7577,20 @@
       <c r="E12">
         <v>2</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>29</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>24</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>31</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>-1</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:16">
       <c r="A13">
         <v>11</v>
       </c>
@@ -7582,14 +7606,14 @@
       <c r="E13">
         <v>0</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>33</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:16">
       <c r="A14">
         <v>12</v>
       </c>
@@ -7605,14 +7629,14 @@
       <c r="E14">
         <v>0</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>40</v>
       </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+      <c r="H14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15">
         <v>13</v>
       </c>
@@ -7628,14 +7652,14 @@
       <c r="E15">
         <v>0</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>43</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:16">
       <c r="A16">
         <v>14</v>
       </c>
@@ -7651,14 +7675,14 @@
       <c r="E16">
         <v>0</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>44</v>
       </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="H16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17">
         <v>15</v>
       </c>
@@ -7674,14 +7698,14 @@
       <c r="E17">
         <v>0</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>46</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>0.1</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:8">
       <c r="A18">
         <v>16</v>
       </c>
@@ -7697,14 +7721,14 @@
       <c r="E18">
         <v>0</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>48</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:8">
       <c r="A19">
         <v>17</v>
       </c>
@@ -7721,7 +7745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:8">
       <c r="A20">
         <v>18</v>
       </c>
@@ -7738,7 +7762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:8">
       <c r="A21">
         <v>19</v>
       </c>
@@ -7755,7 +7779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:8">
       <c r="A22">
         <v>20</v>
       </c>
@@ -7771,14 +7795,14 @@
       <c r="E22">
         <v>0</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>59</v>
       </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+      <c r="H22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23">
         <v>21</v>
       </c>
@@ -7794,14 +7818,14 @@
       <c r="E23">
         <v>0</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>61</v>
       </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+      <c r="H23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24">
         <v>22</v>
       </c>
@@ -7817,14 +7841,14 @@
       <c r="E24">
         <v>0</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>64</v>
       </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+      <c r="H24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25">
         <v>23</v>
       </c>
@@ -7840,14 +7864,14 @@
       <c r="E25">
         <v>0</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>13</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>0.05</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:8">
       <c r="A26">
         <v>24</v>
       </c>
@@ -7863,14 +7887,14 @@
       <c r="E26">
         <v>0</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>13</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>0.1</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:8">
       <c r="A27">
         <v>25</v>
       </c>
@@ -7886,14 +7910,14 @@
       <c r="E27">
         <v>0</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <v>13</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <v>0.15</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:8">
       <c r="A28">
         <v>26</v>
       </c>
@@ -7909,14 +7933,14 @@
       <c r="E28">
         <v>0</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>13</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>0.2</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:8">
       <c r="A29">
         <v>27</v>
       </c>
@@ -7932,14 +7956,14 @@
       <c r="E29">
         <v>0</v>
       </c>
-      <c r="F29">
+      <c r="G29">
         <v>13</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>0.25</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:8">
       <c r="A30">
         <v>28</v>
       </c>
@@ -7955,14 +7979,14 @@
       <c r="E30">
         <v>0</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>13</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>0.3</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:8">
       <c r="A31">
         <v>29</v>
       </c>
@@ -7978,14 +8002,14 @@
       <c r="E31">
         <v>0</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <v>13</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>0.35</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:8">
       <c r="A32">
         <v>30</v>
       </c>
@@ -8001,14 +8025,14 @@
       <c r="E32">
         <v>0</v>
       </c>
-      <c r="F32">
+      <c r="G32">
         <v>13</v>
       </c>
-      <c r="G32">
+      <c r="H32">
         <v>0.4</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:8">
       <c r="A33">
         <v>31</v>
       </c>
@@ -8024,14 +8048,14 @@
       <c r="E33">
         <v>0</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>13</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>0.45</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:8">
       <c r="A34">
         <v>32</v>
       </c>
@@ -8047,16 +8071,16 @@
       <c r="E34">
         <v>0</v>
       </c>
-      <c r="F34">
+      <c r="G34">
         <v>13</v>
       </c>
-      <c r="G34">
+      <c r="H34">
         <v>0.5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Assets/StreamingAssets/Configurations/Cards.xlsx
+++ b/Assets/StreamingAssets/Configurations/Cards.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22190" windowHeight="9040"/>
+    <workbookView windowWidth="24750" windowHeight="10480" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="398">
   <si>
     <t>ID</t>
   </si>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t>TAG2</t>
+  </si>
+  <si>
+    <t>icon</t>
   </si>
   <si>
     <t>CostType</t>
@@ -1389,7 +1392,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1573,12 +1576,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1860,16 +1857,16 @@
     <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2215,7 +2212,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AI66"/>
+  <dimension ref="A1:AJ66"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
@@ -2228,30 +2225,31 @@
     <col min="8" max="8" width="5" customWidth="1"/>
     <col min="9" max="9" width="5.56666666666667" style="3" customWidth="1"/>
     <col min="10" max="10" width="10.5666666666667" customWidth="1"/>
-    <col min="11" max="11" width="9.70833333333333" style="3" customWidth="1"/>
-    <col min="12" max="12" width="7.14166666666667" customWidth="1"/>
-    <col min="13" max="13" width="14" style="3" customWidth="1"/>
-    <col min="14" max="14" width="10.2833333333333" customWidth="1"/>
-    <col min="15" max="16" width="13.7083333333333" customWidth="1"/>
-    <col min="17" max="17" width="9.70833333333333" style="3" customWidth="1"/>
-    <col min="18" max="18" width="9.70833333333333" customWidth="1"/>
-    <col min="19" max="19" width="12.1416666666667" customWidth="1"/>
-    <col min="20" max="20" width="17.7083333333333" style="3" customWidth="1"/>
-    <col min="21" max="21" width="11" customWidth="1"/>
-    <col min="22" max="22" width="12.2833333333333" customWidth="1"/>
-    <col min="23" max="23" width="17.1416666666667" style="3" customWidth="1"/>
-    <col min="26" max="26" width="17.7083333333333" style="3" customWidth="1"/>
-    <col min="27" max="27" width="10.7083333333333" customWidth="1"/>
-    <col min="28" max="28" width="11" customWidth="1"/>
-    <col min="29" max="29" width="17.7083333333333" style="3" customWidth="1"/>
-    <col min="30" max="30" width="12.425" customWidth="1"/>
-    <col min="31" max="31" width="12.425" style="3" customWidth="1"/>
-    <col min="32" max="32" width="12.2833333333333" customWidth="1"/>
-    <col min="33" max="33" width="9" style="3"/>
-    <col min="34" max="34" width="4.28333333333333" customWidth="1"/>
+    <col min="11" max="11" width="10.5666666666667" customWidth="1"/>
+    <col min="12" max="12" width="9.70833333333333" style="3" customWidth="1"/>
+    <col min="13" max="13" width="7.14166666666667" customWidth="1"/>
+    <col min="14" max="14" width="14" style="3" customWidth="1"/>
+    <col min="15" max="15" width="10.2833333333333" customWidth="1"/>
+    <col min="16" max="17" width="13.7083333333333" customWidth="1"/>
+    <col min="18" max="18" width="9.70833333333333" style="3" customWidth="1"/>
+    <col min="19" max="19" width="9.70833333333333" customWidth="1"/>
+    <col min="20" max="20" width="12.1416666666667" customWidth="1"/>
+    <col min="21" max="21" width="17.7083333333333" style="3" customWidth="1"/>
+    <col min="22" max="22" width="11" customWidth="1"/>
+    <col min="23" max="23" width="12.2833333333333" customWidth="1"/>
+    <col min="24" max="24" width="17.1416666666667" style="3" customWidth="1"/>
+    <col min="27" max="27" width="17.7083333333333" style="3" customWidth="1"/>
+    <col min="28" max="28" width="10.7083333333333" customWidth="1"/>
+    <col min="29" max="29" width="11" customWidth="1"/>
+    <col min="30" max="30" width="17.7083333333333" style="3" customWidth="1"/>
+    <col min="31" max="31" width="12.425" customWidth="1"/>
+    <col min="32" max="32" width="12.425" style="3" customWidth="1"/>
+    <col min="33" max="33" width="12.2833333333333" customWidth="1"/>
+    <col min="34" max="34" width="9" style="3"/>
+    <col min="35" max="35" width="4.28333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2282,16 +2280,16 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
       <c r="O1" t="s">
@@ -2300,2164 +2298,2167 @@
       <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="Z1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AC1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AE1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AF1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AG1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AH1" s="3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="2" spans="1:34">
+      <c r="AI1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:35">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L2"/>
+      <c r="M2" s="2">
+        <v>4</v>
+      </c>
+      <c r="N2" s="3">
+        <v>3</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="R2"/>
+      <c r="S2" s="2">
+        <v>11</v>
+      </c>
+      <c r="T2">
+        <v>7</v>
+      </c>
+      <c r="U2" s="3">
+        <v>7</v>
+      </c>
+      <c r="X2"/>
+      <c r="AA2"/>
+      <c r="AD2"/>
+      <c r="AF2"/>
+      <c r="AH2"/>
+      <c r="AI2" s="6"/>
+    </row>
+    <row r="3" spans="1:35">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="F3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G3" t="s">
         <v>40</v>
       </c>
-      <c r="K2"/>
-      <c r="L2" s="2">
+      <c r="K3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L3"/>
+      <c r="M3" s="2">
+        <v>0</v>
+      </c>
+      <c r="N3" s="3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="R3"/>
+      <c r="S3" s="2">
+        <v>2</v>
+      </c>
+      <c r="T3">
         <v>4</v>
       </c>
-      <c r="M2" s="3">
-        <v>3</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="Q2"/>
-      <c r="R2" s="2">
-        <v>11</v>
-      </c>
-      <c r="S2">
-        <v>7</v>
-      </c>
-      <c r="T2" s="3">
-        <v>7</v>
-      </c>
-      <c r="W2"/>
-      <c r="Z2"/>
-      <c r="AC2"/>
-      <c r="AE2"/>
-      <c r="AG2"/>
-      <c r="AH2" s="6"/>
-    </row>
-    <row r="3" spans="1:34">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K3"/>
-      <c r="L3" s="2">
-        <v>0</v>
-      </c>
-      <c r="M3" s="3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>1</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="Q3"/>
-      <c r="R3" s="2">
-        <v>2</v>
-      </c>
-      <c r="S3">
+      <c r="U3" s="3">
         <v>4</v>
       </c>
-      <c r="T3" s="3">
-        <v>4</v>
-      </c>
-      <c r="W3"/>
-      <c r="Z3"/>
-      <c r="AC3"/>
-      <c r="AE3"/>
-      <c r="AG3"/>
-      <c r="AH3" s="6"/>
-    </row>
-    <row r="4" spans="1:34">
+      <c r="X3"/>
+      <c r="AA3"/>
+      <c r="AD3"/>
+      <c r="AF3"/>
+      <c r="AH3"/>
+      <c r="AI3" s="6"/>
+    </row>
+    <row r="4" spans="1:35">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J4" t="s">
-        <v>40</v>
-      </c>
-      <c r="L4">
+        <v>51</v>
+      </c>
+      <c r="K4" t="s">
+        <v>41</v>
+      </c>
+      <c r="M4">
         <v>5</v>
       </c>
-      <c r="M4" s="3">
+      <c r="N4" s="3">
         <v>4</v>
       </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
       <c r="O4">
         <v>0</v>
       </c>
-      <c r="R4" s="2">
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2">
         <v>11</v>
       </c>
-      <c r="S4">
+      <c r="T4">
         <v>15</v>
       </c>
-      <c r="T4" s="3">
+      <c r="U4" s="3">
         <v>18</v>
       </c>
-      <c r="U4">
+      <c r="V4">
         <v>56</v>
       </c>
-      <c r="V4">
+      <c r="W4">
         <v>9</v>
       </c>
-      <c r="W4" s="3">
+      <c r="X4" s="3">
         <v>12</v>
       </c>
-      <c r="AH4" s="6"/>
-    </row>
-    <row r="5" spans="1:34">
+      <c r="AI4" s="6"/>
+    </row>
+    <row r="5" spans="1:35">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5" t="s">
         <v>40</v>
       </c>
-      <c r="K5"/>
-      <c r="L5" s="2">
+      <c r="K5" t="s">
+        <v>41</v>
+      </c>
+      <c r="L5"/>
+      <c r="M5" s="2">
         <v>3</v>
       </c>
-      <c r="M5" s="3">
+      <c r="N5" s="3">
         <v>3</v>
       </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
       <c r="O5">
         <v>0</v>
       </c>
-      <c r="Q5"/>
-      <c r="R5" s="2">
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="R5"/>
+      <c r="S5" s="2">
         <v>11</v>
       </c>
-      <c r="S5">
+      <c r="T5">
         <v>5</v>
       </c>
-      <c r="T5" s="3">
+      <c r="U5" s="3">
         <v>5</v>
       </c>
-      <c r="U5" s="2">
+      <c r="V5" s="2">
         <v>2</v>
       </c>
-      <c r="V5">
+      <c r="W5">
         <v>2</v>
       </c>
-      <c r="W5" s="3">
+      <c r="X5" s="3">
         <v>2</v>
       </c>
-      <c r="Z5"/>
-      <c r="AC5"/>
-      <c r="AE5"/>
-      <c r="AG5"/>
-      <c r="AH5" s="6"/>
-    </row>
-    <row r="6" spans="1:34">
+      <c r="AA5"/>
+      <c r="AD5"/>
+      <c r="AF5"/>
+      <c r="AH5"/>
+      <c r="AI5" s="6"/>
+    </row>
+    <row r="6" spans="1:35">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H6" t="s">
-        <v>50</v>
-      </c>
-      <c r="J6" t="s">
-        <v>58</v>
-      </c>
-      <c r="K6" s="3">
+        <v>51</v>
+      </c>
+      <c r="K6" t="s">
+        <v>59</v>
+      </c>
+      <c r="L6" s="3">
         <v>3</v>
       </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6" s="3">
-        <v>1</v>
-      </c>
-      <c r="N6">
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6" s="3">
         <v>1</v>
       </c>
       <c r="O6">
         <v>1</v>
       </c>
-      <c r="R6" s="2">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>2</v>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="S6" s="2">
+        <v>0</v>
       </c>
       <c r="V6">
         <v>2</v>
       </c>
-      <c r="W6" s="3">
+      <c r="W6">
+        <v>2</v>
+      </c>
+      <c r="X6" s="3">
         <v>7</v>
       </c>
-      <c r="X6">
+      <c r="Y6">
         <v>9</v>
       </c>
-      <c r="Y6">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="3">
-        <v>1</v>
-      </c>
-      <c r="AH6" s="6"/>
-    </row>
-    <row r="7" spans="1:34">
+      <c r="Z6">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="3">
+        <v>1</v>
+      </c>
+      <c r="AI6" s="6"/>
+    </row>
+    <row r="7" spans="1:35">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J7" t="s">
         <v>40</v>
       </c>
-      <c r="K7"/>
-      <c r="L7" s="2">
+      <c r="K7" t="s">
+        <v>41</v>
+      </c>
+      <c r="L7"/>
+      <c r="M7" s="2">
         <v>5</v>
       </c>
-      <c r="M7" s="3">
+      <c r="N7" s="3">
         <v>4</v>
       </c>
-      <c r="N7">
-        <v>1</v>
-      </c>
       <c r="O7">
         <v>1</v>
       </c>
-      <c r="Q7"/>
-      <c r="R7" s="2">
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="R7"/>
+      <c r="S7" s="2">
         <v>4</v>
       </c>
-      <c r="T7"/>
-      <c r="U7" s="2">
+      <c r="U7"/>
+      <c r="V7" s="2">
         <v>21</v>
       </c>
-      <c r="V7">
+      <c r="W7">
         <v>2</v>
       </c>
-      <c r="W7" s="3">
+      <c r="X7" s="3">
         <v>2</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>14</v>
       </c>
-      <c r="Y7">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="3">
-        <v>1</v>
-      </c>
-      <c r="AC7"/>
-      <c r="AE7"/>
-      <c r="AG7"/>
-      <c r="AH7" s="6"/>
-    </row>
-    <row r="8" spans="1:34">
+      <c r="Z7">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AD7"/>
+      <c r="AF7"/>
+      <c r="AH7"/>
+      <c r="AI7" s="6"/>
+    </row>
+    <row r="8" spans="1:35">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G8" t="s">
-        <v>65</v>
-      </c>
-      <c r="J8" t="s">
-        <v>58</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8" s="2">
-        <v>1</v>
-      </c>
-      <c r="M8" s="3">
-        <v>1</v>
-      </c>
-      <c r="N8">
+        <v>66</v>
+      </c>
+      <c r="K8" t="s">
+        <v>59</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2">
+        <v>1</v>
+      </c>
+      <c r="N8" s="3">
         <v>1</v>
       </c>
       <c r="O8">
         <v>1</v>
       </c>
-      <c r="Q8"/>
-      <c r="R8" s="2">
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="R8"/>
+      <c r="S8" s="2">
         <v>2</v>
       </c>
-      <c r="S8">
+      <c r="T8">
         <v>7</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>7</v>
       </c>
-      <c r="U8" s="2">
+      <c r="V8" s="2">
         <v>3</v>
       </c>
-      <c r="V8">
-        <v>1</v>
-      </c>
-      <c r="W8" s="3">
-        <v>1</v>
-      </c>
-      <c r="X8" s="2">
+      <c r="W8">
+        <v>1</v>
+      </c>
+      <c r="X8" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="2">
         <v>14</v>
       </c>
-      <c r="Y8">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>1</v>
-      </c>
-      <c r="AC8"/>
-      <c r="AE8"/>
-      <c r="AG8"/>
-      <c r="AH8" s="6"/>
-    </row>
-    <row r="9" spans="1:34">
+      <c r="Z8">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AD8"/>
+      <c r="AF8"/>
+      <c r="AH8"/>
+      <c r="AI8" s="6"/>
+    </row>
+    <row r="9" spans="1:35">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G9" t="s">
-        <v>38</v>
-      </c>
-      <c r="J9" t="s">
-        <v>40</v>
-      </c>
-      <c r="K9"/>
-      <c r="L9" s="2">
+        <v>39</v>
+      </c>
+      <c r="K9" t="s">
+        <v>41</v>
+      </c>
+      <c r="L9"/>
+      <c r="M9" s="2">
         <v>2</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2</v>
       </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
       <c r="O9">
         <v>0</v>
       </c>
-      <c r="Q9"/>
-      <c r="R9" s="2">
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="R9"/>
+      <c r="S9" s="2">
         <v>6</v>
       </c>
-      <c r="S9">
+      <c r="T9">
         <v>3</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4</v>
       </c>
-      <c r="U9" s="2">
+      <c r="V9" s="2">
         <v>2</v>
       </c>
-      <c r="V9">
+      <c r="W9">
         <v>3</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4</v>
       </c>
-      <c r="Z9"/>
-      <c r="AC9"/>
-      <c r="AE9"/>
-      <c r="AG9"/>
-      <c r="AH9" s="6"/>
-    </row>
-    <row r="10" spans="1:34">
+      <c r="AA9"/>
+      <c r="AD9"/>
+      <c r="AF9"/>
+      <c r="AH9"/>
+      <c r="AI9" s="6"/>
+    </row>
+    <row r="10" spans="1:35">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G10" t="s">
-        <v>65</v>
-      </c>
-      <c r="J10" t="s">
-        <v>40</v>
-      </c>
-      <c r="K10"/>
-      <c r="L10" s="2">
+        <v>66</v>
+      </c>
+      <c r="K10" t="s">
+        <v>41</v>
+      </c>
+      <c r="L10"/>
+      <c r="M10" s="2">
         <v>2</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2</v>
       </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
       <c r="O10">
         <v>0</v>
       </c>
-      <c r="Q10"/>
-      <c r="R10" s="2">
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="R10"/>
+      <c r="S10" s="2">
         <v>7</v>
       </c>
-      <c r="S10">
+      <c r="T10">
         <v>2</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3</v>
       </c>
-      <c r="U10" s="2">
+      <c r="V10" s="2">
         <v>2</v>
       </c>
-      <c r="V10">
+      <c r="W10">
         <v>2</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3</v>
       </c>
-      <c r="Z10"/>
-      <c r="AC10"/>
-      <c r="AE10"/>
-      <c r="AG10"/>
-      <c r="AH10" s="6"/>
-    </row>
-    <row r="11" spans="1:34">
+      <c r="AA10"/>
+      <c r="AD10"/>
+      <c r="AF10"/>
+      <c r="AH10"/>
+      <c r="AI10" s="6"/>
+    </row>
+    <row r="11" spans="1:35">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H11" t="s">
-        <v>50</v>
-      </c>
-      <c r="J11" t="s">
-        <v>40</v>
-      </c>
-      <c r="L11">
+        <v>51</v>
+      </c>
+      <c r="K11" t="s">
+        <v>41</v>
+      </c>
+      <c r="M11">
         <v>2</v>
       </c>
-      <c r="M11" s="3">
+      <c r="N11" s="3">
         <v>2</v>
       </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
       <c r="O11">
         <v>0</v>
       </c>
-      <c r="R11" s="2">
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="S11" s="2">
         <v>15</v>
       </c>
-      <c r="S11">
+      <c r="T11">
         <v>2</v>
       </c>
-      <c r="T11" s="3">
+      <c r="U11" s="3">
         <v>3</v>
       </c>
-      <c r="U11" s="2">
+      <c r="V11" s="2">
         <v>2</v>
       </c>
-      <c r="V11">
+      <c r="W11">
         <v>2</v>
       </c>
-      <c r="W11" s="3">
+      <c r="X11" s="3">
         <v>3</v>
       </c>
-      <c r="AH11" s="6"/>
-    </row>
-    <row r="12" spans="1:35">
+      <c r="AI11" s="6"/>
+    </row>
+    <row r="12" spans="1:36">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>65</v>
-      </c>
-      <c r="J12" t="s">
-        <v>40</v>
-      </c>
-      <c r="K12"/>
-      <c r="L12" s="2">
+        <v>66</v>
+      </c>
+      <c r="K12" t="s">
+        <v>41</v>
+      </c>
+      <c r="L12"/>
+      <c r="M12" s="2">
         <v>6</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>6</v>
       </c>
-      <c r="N12">
-        <v>1</v>
-      </c>
       <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="Q12"/>
-      <c r="R12" s="2">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="R12"/>
+      <c r="S12" s="2">
         <v>11</v>
       </c>
-      <c r="S12">
+      <c r="T12">
         <v>9</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>13</v>
       </c>
-      <c r="U12" s="2">
+      <c r="V12" s="2">
         <v>11</v>
       </c>
-      <c r="V12">
+      <c r="W12">
         <v>9</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>13</v>
       </c>
-      <c r="Z12"/>
-      <c r="AC12"/>
-      <c r="AE12"/>
-      <c r="AG12"/>
-      <c r="AH12" s="6"/>
-      <c r="AI12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="13" spans="1:34">
+      <c r="AA12"/>
+      <c r="AD12"/>
+      <c r="AF12"/>
+      <c r="AH12"/>
+      <c r="AI12" s="6"/>
+      <c r="AJ12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
-      </c>
-      <c r="J13" t="s">
         <v>40</v>
       </c>
-      <c r="K13"/>
-      <c r="L13" s="2">
+      <c r="K13" t="s">
+        <v>41</v>
+      </c>
+      <c r="L13"/>
+      <c r="M13" s="2">
         <v>5</v>
       </c>
-      <c r="M13" s="3">
+      <c r="N13" s="3">
         <v>5</v>
       </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
       <c r="O13">
         <v>0</v>
       </c>
-      <c r="Q13"/>
-      <c r="R13" s="2">
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="R13"/>
+      <c r="S13" s="2">
         <v>11</v>
       </c>
-      <c r="S13">
+      <c r="T13">
         <v>11</v>
       </c>
-      <c r="T13" s="3">
+      <c r="U13" s="3">
         <v>15</v>
       </c>
-      <c r="U13" s="2">
+      <c r="V13" s="2">
         <v>2</v>
       </c>
-      <c r="V13">
+      <c r="W13">
         <v>7</v>
       </c>
-      <c r="W13" s="3">
+      <c r="X13" s="3">
         <v>9</v>
       </c>
-      <c r="Z13"/>
-      <c r="AC13"/>
-      <c r="AE13"/>
-      <c r="AG13"/>
-      <c r="AH13" s="6"/>
-    </row>
-    <row r="14" spans="1:34">
+      <c r="AA13"/>
+      <c r="AD13"/>
+      <c r="AF13"/>
+      <c r="AH13"/>
+      <c r="AI13" s="6"/>
+    </row>
+    <row r="14" spans="1:35">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G14" t="s">
-        <v>38</v>
-      </c>
-      <c r="J14" t="s">
-        <v>40</v>
-      </c>
-      <c r="K14"/>
-      <c r="L14" s="2">
+        <v>39</v>
+      </c>
+      <c r="K14" t="s">
+        <v>41</v>
+      </c>
+      <c r="L14"/>
+      <c r="M14" s="2">
         <v>5</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>4</v>
       </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
       <c r="O14">
         <v>0</v>
       </c>
-      <c r="Q14"/>
-      <c r="R14" s="2">
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="R14"/>
+      <c r="S14" s="2">
         <v>6</v>
       </c>
-      <c r="S14">
+      <c r="T14">
         <v>6</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>8</v>
       </c>
-      <c r="W14"/>
-      <c r="Z14"/>
-      <c r="AC14"/>
-      <c r="AE14"/>
-      <c r="AG14"/>
-      <c r="AH14" s="6"/>
-    </row>
-    <row r="15" spans="1:34">
+      <c r="X14"/>
+      <c r="AA14"/>
+      <c r="AD14"/>
+      <c r="AF14"/>
+      <c r="AH14"/>
+      <c r="AI14" s="6"/>
+    </row>
+    <row r="15" spans="1:35">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G15" t="s">
-        <v>38</v>
-      </c>
-      <c r="J15" t="s">
-        <v>40</v>
-      </c>
-      <c r="K15"/>
-      <c r="L15" s="2">
+        <v>39</v>
+      </c>
+      <c r="K15" t="s">
+        <v>41</v>
+      </c>
+      <c r="L15"/>
+      <c r="M15" s="2">
         <v>4</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4</v>
       </c>
-      <c r="N15">
-        <v>1</v>
-      </c>
       <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="Q15"/>
-      <c r="R15" s="2">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="R15"/>
+      <c r="S15" s="2">
         <v>18</v>
       </c>
-      <c r="S15">
+      <c r="T15">
         <v>1.4</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1.8</v>
       </c>
-      <c r="W15"/>
-      <c r="Z15"/>
-      <c r="AC15"/>
-      <c r="AE15"/>
-      <c r="AG15"/>
-      <c r="AH15" s="6"/>
-    </row>
-    <row r="16" spans="1:34">
+      <c r="X15"/>
+      <c r="AA15"/>
+      <c r="AD15"/>
+      <c r="AF15"/>
+      <c r="AH15"/>
+      <c r="AI15" s="6"/>
+    </row>
+    <row r="16" spans="1:35">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G16" t="s">
-        <v>38</v>
-      </c>
-      <c r="J16" t="s">
-        <v>40</v>
-      </c>
-      <c r="K16"/>
-      <c r="L16" s="2">
+        <v>39</v>
+      </c>
+      <c r="K16" t="s">
+        <v>41</v>
+      </c>
+      <c r="L16"/>
+      <c r="M16" s="2">
         <v>6</v>
       </c>
-      <c r="M16" s="3">
+      <c r="N16" s="3">
         <v>5</v>
       </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
       <c r="O16">
         <v>0</v>
       </c>
-      <c r="Q16"/>
-      <c r="R16" s="2">
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="R16"/>
+      <c r="S16" s="2">
         <v>6</v>
       </c>
-      <c r="S16">
+      <c r="T16">
         <v>4</v>
       </c>
-      <c r="T16" s="3">
+      <c r="U16" s="3">
         <v>5</v>
       </c>
-      <c r="U16" s="2">
+      <c r="V16" s="2">
         <v>18</v>
       </c>
-      <c r="V16">
+      <c r="W16">
         <v>0.8</v>
       </c>
-      <c r="W16" s="3">
+      <c r="X16" s="3">
         <v>1.1</v>
       </c>
-      <c r="Z16"/>
-      <c r="AC16"/>
-      <c r="AE16"/>
-      <c r="AG16"/>
-      <c r="AH16" s="6"/>
-    </row>
-    <row r="17" spans="1:34">
+      <c r="AA16"/>
+      <c r="AD16"/>
+      <c r="AF16"/>
+      <c r="AH16"/>
+      <c r="AI16" s="6"/>
+    </row>
+    <row r="17" spans="1:35">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="J17" t="s">
-        <v>40</v>
-      </c>
-      <c r="K17"/>
-      <c r="L17" s="2">
+        <v>95</v>
+      </c>
+      <c r="K17" t="s">
+        <v>41</v>
+      </c>
+      <c r="L17"/>
+      <c r="M17" s="2">
         <v>3</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3</v>
       </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
       <c r="O17">
-        <v>1</v>
-      </c>
-      <c r="Q17"/>
-      <c r="R17" s="2">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>1</v>
+      </c>
+      <c r="R17"/>
+      <c r="S17" s="2">
         <v>19</v>
       </c>
-      <c r="S17">
-        <v>1</v>
-      </c>
-      <c r="T17" s="3">
-        <v>1</v>
-      </c>
-      <c r="U17" s="2">
+      <c r="T17">
+        <v>1</v>
+      </c>
+      <c r="U17" s="3">
+        <v>1</v>
+      </c>
+      <c r="V17" s="2">
         <v>2</v>
       </c>
-      <c r="V17">
+      <c r="W17">
         <v>4</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6</v>
       </c>
-      <c r="X17" s="2">
+      <c r="Y17" s="2">
         <v>21</v>
       </c>
-      <c r="Y17">
+      <c r="Z17">
         <v>2</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3</v>
       </c>
-      <c r="AC17"/>
-      <c r="AE17"/>
-      <c r="AG17"/>
-      <c r="AH17" s="7"/>
-    </row>
-    <row r="18" spans="1:34">
+      <c r="AD17"/>
+      <c r="AF17"/>
+      <c r="AH17"/>
+      <c r="AI17" s="7"/>
+    </row>
+    <row r="18" spans="1:35">
       <c r="A18">
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H18" t="s">
-        <v>50</v>
-      </c>
-      <c r="J18" t="s">
-        <v>40</v>
-      </c>
-      <c r="L18">
+        <v>51</v>
+      </c>
+      <c r="K18" t="s">
+        <v>41</v>
+      </c>
+      <c r="M18">
         <v>4</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3</v>
       </c>
-      <c r="N18">
-        <v>1</v>
-      </c>
       <c r="O18">
-        <v>0</v>
-      </c>
-      <c r="R18" s="2">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="S18" s="2">
         <v>15</v>
       </c>
-      <c r="S18">
+      <c r="T18">
         <v>5</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>7</v>
       </c>
-      <c r="AD18">
+      <c r="AE18">
         <v>63</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1.5</v>
       </c>
-      <c r="AH18" s="6"/>
-    </row>
-    <row r="19" spans="1:34">
+      <c r="AI18" s="6"/>
+    </row>
+    <row r="19" spans="1:35">
       <c r="A19">
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G19" t="s">
-        <v>65</v>
-      </c>
-      <c r="J19" t="s">
-        <v>40</v>
-      </c>
-      <c r="K19"/>
-      <c r="L19" s="2">
+        <v>66</v>
+      </c>
+      <c r="K19" t="s">
+        <v>41</v>
+      </c>
+      <c r="L19"/>
+      <c r="M19" s="2">
         <v>5</v>
       </c>
-      <c r="M19" s="3">
+      <c r="N19" s="3">
         <v>4</v>
       </c>
-      <c r="N19">
-        <v>1</v>
-      </c>
       <c r="O19">
         <v>1</v>
       </c>
-      <c r="Q19"/>
-      <c r="R19" s="2">
+      <c r="P19">
+        <v>1</v>
+      </c>
+      <c r="R19"/>
+      <c r="S19" s="2">
         <v>23</v>
       </c>
-      <c r="S19">
-        <v>1</v>
-      </c>
-      <c r="T19" s="3">
-        <v>1</v>
-      </c>
-      <c r="U19" s="2">
+      <c r="T19">
+        <v>1</v>
+      </c>
+      <c r="U19" s="3">
+        <v>1</v>
+      </c>
+      <c r="V19" s="2">
         <v>7</v>
       </c>
-      <c r="V19">
-        <v>1</v>
-      </c>
-      <c r="W19" s="3">
+      <c r="W19">
+        <v>1</v>
+      </c>
+      <c r="X19" s="3">
         <v>2</v>
       </c>
-      <c r="Z19"/>
-      <c r="AC19"/>
-      <c r="AE19"/>
-      <c r="AG19"/>
-      <c r="AH19" s="6"/>
-    </row>
-    <row r="20" spans="1:34">
+      <c r="AA19"/>
+      <c r="AD19"/>
+      <c r="AF19"/>
+      <c r="AH19"/>
+      <c r="AI19" s="6"/>
+    </row>
+    <row r="20" spans="1:35">
       <c r="A20">
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C20" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H20" t="s">
-        <v>50</v>
-      </c>
-      <c r="J20" t="s">
-        <v>40</v>
-      </c>
-      <c r="L20">
+        <v>51</v>
+      </c>
+      <c r="K20" t="s">
+        <v>41</v>
+      </c>
+      <c r="M20">
         <v>6</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>6</v>
       </c>
-      <c r="N20">
-        <v>1</v>
-      </c>
       <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="2">
+        <v>1</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="2">
         <v>11</v>
       </c>
-      <c r="S20">
+      <c r="T20">
         <v>24</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>30</v>
       </c>
-      <c r="AD20">
+      <c r="AE20">
         <v>62</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>7</v>
       </c>
-      <c r="AH20" s="7"/>
-    </row>
-    <row r="21" spans="1:34">
+      <c r="AI20" s="7"/>
+    </row>
+    <row r="21" spans="1:35">
       <c r="A21">
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H21" t="s">
-        <v>50</v>
-      </c>
-      <c r="J21" t="s">
-        <v>40</v>
-      </c>
-      <c r="L21">
+        <v>51</v>
+      </c>
+      <c r="K21" t="s">
+        <v>41</v>
+      </c>
+      <c r="M21">
         <v>5</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4</v>
       </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
       <c r="O21">
-        <v>1</v>
-      </c>
-      <c r="R21" s="2">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>1</v>
+      </c>
+      <c r="S21" s="2">
         <v>26</v>
       </c>
-      <c r="S21">
+      <c r="T21">
         <v>2</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2</v>
       </c>
-      <c r="U21" s="2">
+      <c r="V21" s="2">
         <v>11</v>
       </c>
-      <c r="V21">
+      <c r="W21">
         <v>30</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>42</v>
       </c>
-      <c r="X21">
+      <c r="Y21">
         <v>2</v>
       </c>
-      <c r="Y21">
+      <c r="Z21">
         <v>5</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>7</v>
       </c>
-      <c r="AH21" s="6"/>
-    </row>
-    <row r="22" spans="1:34">
+      <c r="AI21" s="6"/>
+    </row>
+    <row r="22" spans="1:35">
       <c r="A22">
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D22" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G22" t="s">
-        <v>38</v>
-      </c>
-      <c r="J22" t="s">
-        <v>40</v>
-      </c>
-      <c r="K22"/>
-      <c r="L22" s="2">
+        <v>39</v>
+      </c>
+      <c r="K22" t="s">
+        <v>41</v>
+      </c>
+      <c r="L22"/>
+      <c r="M22" s="2">
         <v>4</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>4</v>
       </c>
-      <c r="N22">
-        <v>1</v>
-      </c>
       <c r="O22">
         <v>1</v>
       </c>
-      <c r="Q22"/>
-      <c r="R22" s="2">
+      <c r="P22">
+        <v>1</v>
+      </c>
+      <c r="R22"/>
+      <c r="S22" s="2">
         <v>6</v>
       </c>
-      <c r="S22">
+      <c r="T22">
         <v>2</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>4</v>
       </c>
-      <c r="U22" s="2">
+      <c r="V22" s="2">
         <v>28</v>
       </c>
-      <c r="V22">
-        <v>1</v>
-      </c>
-      <c r="W22" s="3">
-        <v>1</v>
-      </c>
-      <c r="Z22"/>
-      <c r="AC22"/>
-      <c r="AE22"/>
-      <c r="AG22"/>
-      <c r="AH22" s="6"/>
-    </row>
-    <row r="23" spans="1:34">
+      <c r="W22">
+        <v>1</v>
+      </c>
+      <c r="X22" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA22"/>
+      <c r="AD22"/>
+      <c r="AF22"/>
+      <c r="AH22"/>
+      <c r="AI22" s="6"/>
+    </row>
+    <row r="23" spans="1:35">
       <c r="A23">
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D23" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G23" t="s">
-        <v>38</v>
-      </c>
-      <c r="J23" t="s">
-        <v>40</v>
-      </c>
-      <c r="K23"/>
-      <c r="L23" s="2">
-        <v>1</v>
-      </c>
-      <c r="M23" s="3">
-        <v>1</v>
-      </c>
-      <c r="N23">
+        <v>39</v>
+      </c>
+      <c r="K23" t="s">
+        <v>41</v>
+      </c>
+      <c r="L23"/>
+      <c r="M23" s="2">
+        <v>1</v>
+      </c>
+      <c r="N23" s="3">
         <v>1</v>
       </c>
       <c r="O23">
-        <v>0</v>
-      </c>
-      <c r="Q23"/>
-      <c r="R23" s="2">
+        <v>1</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="R23"/>
+      <c r="S23" s="2">
         <v>6</v>
       </c>
-      <c r="S23">
+      <c r="T23">
         <v>5</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>7</v>
       </c>
-      <c r="U23" s="2">
+      <c r="V23" s="2">
         <v>2</v>
       </c>
-      <c r="V23">
-        <v>1</v>
-      </c>
-      <c r="W23" s="3">
-        <v>1</v>
-      </c>
-      <c r="Z23"/>
-      <c r="AC23"/>
-      <c r="AE23"/>
-      <c r="AG23"/>
-      <c r="AH23" s="6"/>
-    </row>
-    <row r="24" spans="1:34">
+      <c r="W23">
+        <v>1</v>
+      </c>
+      <c r="X23" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA23"/>
+      <c r="AD23"/>
+      <c r="AF23"/>
+      <c r="AH23"/>
+      <c r="AI23" s="6"/>
+    </row>
+    <row r="24" spans="1:35">
       <c r="A24">
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H24" t="s">
-        <v>50</v>
-      </c>
-      <c r="J24" t="s">
-        <v>40</v>
-      </c>
-      <c r="L24">
+        <v>51</v>
+      </c>
+      <c r="K24" t="s">
+        <v>41</v>
+      </c>
+      <c r="M24">
         <v>4</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4</v>
       </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
       <c r="O24">
         <v>0</v>
       </c>
-      <c r="R24" s="2">
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="S24" s="2">
         <v>15</v>
       </c>
-      <c r="S24">
+      <c r="T24">
         <v>3</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>4</v>
       </c>
-      <c r="U24" s="2">
+      <c r="V24" s="2">
         <v>11</v>
       </c>
-      <c r="V24">
+      <c r="W24">
         <v>8</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>11</v>
       </c>
-      <c r="AD24">
+      <c r="AE24">
         <v>63</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>3</v>
       </c>
-      <c r="AH24" s="6"/>
-    </row>
-    <row r="25" spans="1:34">
+      <c r="AI24" s="6"/>
+    </row>
+    <row r="25" spans="1:35">
       <c r="A25">
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C25" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D25" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G25" t="s">
-        <v>65</v>
-      </c>
-      <c r="J25" t="s">
-        <v>40</v>
-      </c>
-      <c r="K25"/>
-      <c r="L25" s="2">
+        <v>66</v>
+      </c>
+      <c r="K25" t="s">
+        <v>41</v>
+      </c>
+      <c r="L25"/>
+      <c r="M25" s="2">
         <v>3</v>
       </c>
-      <c r="M25" s="3">
+      <c r="N25" s="3">
         <v>2</v>
       </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
       <c r="O25">
         <v>0</v>
       </c>
-      <c r="Q25"/>
-      <c r="R25" s="2">
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="R25"/>
+      <c r="S25" s="2">
         <v>7</v>
       </c>
-      <c r="S25">
+      <c r="T25">
         <v>3</v>
       </c>
-      <c r="T25" s="3">
+      <c r="U25" s="3">
         <v>5</v>
       </c>
-      <c r="W25"/>
-      <c r="Z25"/>
-      <c r="AC25"/>
-      <c r="AE25"/>
-      <c r="AG25"/>
-      <c r="AH25" s="6"/>
-    </row>
-    <row r="26" spans="1:34">
+      <c r="X25"/>
+      <c r="AA25"/>
+      <c r="AD25"/>
+      <c r="AF25"/>
+      <c r="AH25"/>
+      <c r="AI25" s="6"/>
+    </row>
+    <row r="26" spans="1:35">
       <c r="A26">
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C26" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D26" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G26" t="s">
-        <v>65</v>
-      </c>
-      <c r="J26" t="s">
-        <v>40</v>
-      </c>
-      <c r="K26"/>
-      <c r="L26" s="2">
+        <v>66</v>
+      </c>
+      <c r="K26" t="s">
+        <v>41</v>
+      </c>
+      <c r="L26"/>
+      <c r="M26" s="2">
         <v>3</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2</v>
       </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
       <c r="O26">
         <v>0</v>
       </c>
-      <c r="Q26"/>
-      <c r="R26" s="2">
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="R26"/>
+      <c r="S26" s="2">
         <v>7</v>
       </c>
-      <c r="S26">
+      <c r="T26">
         <v>3</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4</v>
       </c>
-      <c r="U26" s="2">
+      <c r="V26" s="2">
         <v>2</v>
       </c>
-      <c r="V26">
+      <c r="W26">
         <v>4</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>6</v>
       </c>
-      <c r="Z26"/>
-      <c r="AC26"/>
-      <c r="AE26"/>
-      <c r="AG26"/>
-      <c r="AH26" s="6"/>
-    </row>
-    <row r="27" spans="1:34">
+      <c r="AA26"/>
+      <c r="AD26"/>
+      <c r="AF26"/>
+      <c r="AH26"/>
+      <c r="AI26" s="6"/>
+    </row>
+    <row r="27" spans="1:35">
       <c r="A27">
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C27" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E27" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G27" t="s">
+        <v>50</v>
+      </c>
+      <c r="H27" t="s">
+        <v>51</v>
+      </c>
+      <c r="K27" t="s">
+        <v>41</v>
+      </c>
+      <c r="M27">
+        <v>8</v>
+      </c>
+      <c r="N27" s="3">
+        <v>6</v>
+      </c>
+      <c r="O27">
+        <v>1</v>
+      </c>
+      <c r="P27">
+        <v>1</v>
+      </c>
+      <c r="R27" s="3">
+        <v>0</v>
+      </c>
+      <c r="S27" s="2">
+        <v>11</v>
+      </c>
+      <c r="T27">
+        <v>12</v>
+      </c>
+      <c r="U27" s="3">
+        <v>18</v>
+      </c>
+      <c r="V27" s="2">
+        <v>56</v>
+      </c>
+      <c r="W27">
+        <v>24</v>
+      </c>
+      <c r="X27" s="3">
+        <v>30</v>
+      </c>
+      <c r="Y27">
         <v>57</v>
       </c>
-      <c r="F27" t="s">
-        <v>38</v>
-      </c>
-      <c r="G27" t="s">
-        <v>49</v>
-      </c>
-      <c r="H27" t="s">
-        <v>50</v>
-      </c>
-      <c r="J27" t="s">
-        <v>40</v>
-      </c>
-      <c r="L27">
-        <v>8</v>
-      </c>
-      <c r="M27" s="3">
-        <v>6</v>
-      </c>
-      <c r="N27">
-        <v>1</v>
-      </c>
-      <c r="O27">
-        <v>1</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
-      <c r="R27" s="2">
-        <v>11</v>
-      </c>
-      <c r="S27">
-        <v>12</v>
-      </c>
-      <c r="T27" s="3">
-        <v>18</v>
-      </c>
-      <c r="U27" s="2">
-        <v>56</v>
-      </c>
-      <c r="V27">
-        <v>24</v>
-      </c>
-      <c r="W27" s="3">
-        <v>30</v>
-      </c>
-      <c r="X27">
-        <v>57</v>
-      </c>
-      <c r="Y27">
+      <c r="Z27">
         <v>36</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>44</v>
       </c>
-      <c r="AH27" s="7"/>
-    </row>
-    <row r="28" spans="1:34">
+      <c r="AI27" s="7"/>
+    </row>
+    <row r="28" spans="1:35">
       <c r="A28">
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C28" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H28" t="s">
-        <v>125</v>
-      </c>
-      <c r="J28" t="s">
-        <v>40</v>
-      </c>
-      <c r="L28">
-        <v>1</v>
-      </c>
-      <c r="M28" s="3">
-        <v>0</v>
-      </c>
-      <c r="N28">
-        <v>1</v>
+        <v>126</v>
+      </c>
+      <c r="K28" t="s">
+        <v>41</v>
+      </c>
+      <c r="M28">
+        <v>1</v>
+      </c>
+      <c r="N28" s="3">
+        <v>0</v>
       </c>
       <c r="O28">
-        <v>0</v>
-      </c>
-      <c r="R28" s="2">
+        <v>1</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="S28" s="2">
         <v>2</v>
       </c>
-      <c r="S28">
+      <c r="T28">
         <v>6</v>
       </c>
-      <c r="T28" s="3">
+      <c r="U28" s="3">
         <v>8</v>
       </c>
-      <c r="AD28">
+      <c r="AE28">
         <v>21</v>
       </c>
-      <c r="AE28" s="3">
+      <c r="AF28" s="3">
         <v>12</v>
       </c>
-      <c r="AH28" s="6"/>
-    </row>
-    <row r="29" spans="1:34">
+      <c r="AI28" s="6"/>
+    </row>
+    <row r="29" spans="1:35">
       <c r="A29">
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G29" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="J29" t="s">
-        <v>40</v>
-      </c>
-      <c r="K29"/>
-      <c r="L29" s="2">
+        <v>95</v>
+      </c>
+      <c r="K29" t="s">
+        <v>41</v>
+      </c>
+      <c r="L29"/>
+      <c r="M29" s="2">
         <v>5</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>5</v>
       </c>
-      <c r="N29">
-        <v>1</v>
-      </c>
       <c r="O29">
         <v>1</v>
       </c>
-      <c r="Q29"/>
-      <c r="R29" s="2">
+      <c r="P29">
+        <v>1</v>
+      </c>
+      <c r="R29"/>
+      <c r="S29" s="2">
         <v>32</v>
       </c>
-      <c r="S29">
+      <c r="T29">
         <v>30</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>30</v>
       </c>
-      <c r="U29" s="2">
+      <c r="V29" s="2">
         <v>2</v>
       </c>
-      <c r="V29">
+      <c r="W29">
         <v>3</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>5</v>
       </c>
-      <c r="X29" s="2">
+      <c r="Y29" s="2">
         <v>21</v>
       </c>
-      <c r="Y29">
+      <c r="Z29">
         <v>2</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>3</v>
       </c>
-      <c r="AC29"/>
-      <c r="AE29"/>
-      <c r="AG29"/>
-      <c r="AH29" s="6"/>
-    </row>
-    <row r="30" spans="1:34">
+      <c r="AD29"/>
+      <c r="AF29"/>
+      <c r="AH29"/>
+      <c r="AI29" s="6"/>
+    </row>
+    <row r="30" spans="1:35">
       <c r="A30">
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C30" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D30" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="J30" t="s">
-        <v>40</v>
-      </c>
-      <c r="K30"/>
-      <c r="L30" s="2">
+        <v>95</v>
+      </c>
+      <c r="K30" t="s">
+        <v>41</v>
+      </c>
+      <c r="L30"/>
+      <c r="M30" s="2">
         <v>4</v>
       </c>
-      <c r="M30" s="3">
+      <c r="N30" s="3">
         <v>4</v>
       </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
       <c r="O30">
-        <v>1</v>
-      </c>
-      <c r="Q30"/>
-      <c r="R30" s="2">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>1</v>
+      </c>
+      <c r="R30"/>
+      <c r="S30" s="2">
         <v>33</v>
       </c>
-      <c r="S30">
+      <c r="T30">
         <v>50</v>
       </c>
-      <c r="T30" s="3">
+      <c r="U30" s="3">
         <v>70</v>
       </c>
-      <c r="U30" s="2">
+      <c r="V30" s="2">
         <v>2</v>
       </c>
-      <c r="V30">
+      <c r="W30">
         <v>2</v>
       </c>
-      <c r="W30" s="3">
+      <c r="X30" s="3">
         <v>4</v>
       </c>
-      <c r="Z30"/>
-      <c r="AC30"/>
-      <c r="AE30"/>
-      <c r="AG30"/>
-      <c r="AH30" s="7"/>
-    </row>
-    <row r="31" spans="1:34">
+      <c r="AA30"/>
+      <c r="AD30"/>
+      <c r="AF30"/>
+      <c r="AH30"/>
+      <c r="AI30" s="7"/>
+    </row>
+    <row r="31" spans="1:35">
       <c r="A31">
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C31" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D31" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G31" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="J31" t="s">
-        <v>40</v>
-      </c>
-      <c r="K31"/>
-      <c r="L31" s="2">
+        <v>95</v>
+      </c>
+      <c r="K31" t="s">
+        <v>41</v>
+      </c>
+      <c r="L31"/>
+      <c r="M31" s="2">
         <v>4</v>
       </c>
-      <c r="M31" s="3">
+      <c r="N31" s="3">
         <v>3</v>
       </c>
-      <c r="N31">
-        <v>1</v>
-      </c>
       <c r="O31">
         <v>1</v>
       </c>
-      <c r="Q31"/>
-      <c r="R31" s="2">
+      <c r="P31">
+        <v>1</v>
+      </c>
+      <c r="R31"/>
+      <c r="S31" s="2">
         <v>33</v>
       </c>
-      <c r="S31">
+      <c r="T31">
         <v>20</v>
       </c>
-      <c r="T31" s="3">
+      <c r="U31" s="3">
         <v>30</v>
       </c>
-      <c r="U31" s="2">
+      <c r="V31" s="2">
         <v>35</v>
       </c>
-      <c r="V31">
-        <v>1</v>
-      </c>
-      <c r="W31" s="3">
-        <v>1</v>
-      </c>
-      <c r="Z31"/>
-      <c r="AC31"/>
-      <c r="AE31"/>
-      <c r="AG31"/>
-      <c r="AH31" s="7"/>
-    </row>
-    <row r="32" spans="1:33">
+      <c r="W31">
+        <v>1</v>
+      </c>
+      <c r="X31" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA31"/>
+      <c r="AD31"/>
+      <c r="AF31"/>
+      <c r="AH31"/>
+      <c r="AI31" s="7"/>
+    </row>
+    <row r="32" spans="1:34">
       <c r="A32">
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C32" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D32" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G32" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="J32" t="s">
-        <v>40</v>
-      </c>
-      <c r="K32"/>
-      <c r="L32" s="2">
+        <v>95</v>
+      </c>
+      <c r="K32" t="s">
+        <v>41</v>
+      </c>
+      <c r="L32"/>
+      <c r="M32" s="2">
         <v>7</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>6</v>
       </c>
-      <c r="N32">
-        <v>1</v>
-      </c>
       <c r="O32">
         <v>1</v>
       </c>
-      <c r="Q32"/>
-      <c r="T32"/>
-      <c r="W32"/>
-      <c r="Z32"/>
-      <c r="AC32"/>
-      <c r="AE32"/>
-      <c r="AG32"/>
-    </row>
-    <row r="33" spans="1:31">
+      <c r="P32">
+        <v>1</v>
+      </c>
+      <c r="R32"/>
+      <c r="U32"/>
+      <c r="X32"/>
+      <c r="AA32"/>
+      <c r="AD32"/>
+      <c r="AF32"/>
+      <c r="AH32"/>
+    </row>
+    <row r="33" spans="1:32">
       <c r="A33">
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C33" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F33" t="s">
+        <v>39</v>
+      </c>
+      <c r="G33" t="s">
+        <v>50</v>
+      </c>
+      <c r="H33" t="s">
+        <v>51</v>
+      </c>
+      <c r="K33" t="s">
+        <v>41</v>
+      </c>
+      <c r="M33">
+        <v>8</v>
+      </c>
+      <c r="N33" s="3">
+        <v>7</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>1</v>
+      </c>
+      <c r="S33" s="2">
+        <v>11</v>
+      </c>
+      <c r="T33">
         <v>38</v>
       </c>
-      <c r="G33" t="s">
-        <v>49</v>
-      </c>
-      <c r="H33" t="s">
-        <v>50</v>
-      </c>
-      <c r="J33" t="s">
-        <v>40</v>
-      </c>
-      <c r="L33">
-        <v>8</v>
-      </c>
-      <c r="M33" s="3">
-        <v>7</v>
-      </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33">
-        <v>1</v>
-      </c>
-      <c r="R33" s="2">
-        <v>11</v>
-      </c>
-      <c r="S33">
-        <v>38</v>
-      </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>52</v>
       </c>
-      <c r="AD33">
+      <c r="AE33">
         <v>64</v>
       </c>
-      <c r="AE33" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20">
+      <c r="AF33" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21">
       <c r="A34">
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C34" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G34" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H34" t="s">
-        <v>50</v>
-      </c>
-      <c r="J34" t="s">
-        <v>40</v>
-      </c>
-      <c r="L34">
+        <v>51</v>
+      </c>
+      <c r="K34" t="s">
+        <v>41</v>
+      </c>
+      <c r="M34">
         <v>3</v>
       </c>
-      <c r="M34" s="3">
+      <c r="N34" s="3">
         <v>3</v>
       </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
       <c r="O34">
         <v>0</v>
       </c>
-      <c r="Q34" s="3">
-        <v>0</v>
-      </c>
-      <c r="R34" s="2">
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="2">
         <v>15</v>
       </c>
-      <c r="S34">
+      <c r="T34">
         <v>3</v>
       </c>
-      <c r="T34" s="3">
+      <c r="U34" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:20">
+    <row r="35" spans="1:21">
       <c r="A35">
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C35" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F35" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G35" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H35" t="s">
-        <v>125</v>
-      </c>
-      <c r="J35" t="s">
-        <v>40</v>
-      </c>
-      <c r="L35">
+        <v>126</v>
+      </c>
+      <c r="K35" t="s">
+        <v>41</v>
+      </c>
+      <c r="M35">
         <v>3</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3</v>
       </c>
-      <c r="N35">
-        <v>1</v>
-      </c>
       <c r="O35">
-        <v>0</v>
-      </c>
-      <c r="R35" s="2">
+        <v>1</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="S35" s="2">
         <v>11</v>
       </c>
-      <c r="S35">
+      <c r="T35">
         <v>18</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:23">
+    <row r="36" spans="1:24">
       <c r="A36">
         <v>37</v>
       </c>
@@ -4465,756 +4466,756 @@
         <v>144</v>
       </c>
       <c r="C36" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D36" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F36" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G36" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H36" t="s">
-        <v>50</v>
-      </c>
-      <c r="J36" t="s">
-        <v>40</v>
-      </c>
-      <c r="L36">
+        <v>51</v>
+      </c>
+      <c r="K36" t="s">
+        <v>41</v>
+      </c>
+      <c r="M36">
         <v>3</v>
       </c>
-      <c r="M36" s="3">
+      <c r="N36" s="3">
         <v>3</v>
       </c>
-      <c r="N36">
-        <v>1</v>
-      </c>
       <c r="O36">
-        <v>0</v>
-      </c>
-      <c r="R36" s="2">
+        <v>1</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="S36" s="2">
         <v>15</v>
       </c>
-      <c r="S36">
+      <c r="T36">
         <v>3</v>
       </c>
-      <c r="T36" s="3">
+      <c r="U36" s="3">
         <v>4</v>
       </c>
-      <c r="U36" s="2">
+      <c r="V36" s="2">
         <v>2</v>
       </c>
-      <c r="V36">
+      <c r="W36">
         <v>6</v>
       </c>
-      <c r="W36" s="3">
+      <c r="X36" s="3">
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:33">
+    <row r="37" spans="1:34">
       <c r="A37">
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C37" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D37" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F37" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G37" t="s">
-        <v>65</v>
-      </c>
-      <c r="J37" t="s">
-        <v>40</v>
-      </c>
-      <c r="K37"/>
-      <c r="L37" s="2">
+        <v>66</v>
+      </c>
+      <c r="K37" t="s">
+        <v>41</v>
+      </c>
+      <c r="L37"/>
+      <c r="M37" s="2">
         <v>3</v>
       </c>
-      <c r="M37" s="3">
+      <c r="N37" s="3">
         <v>3</v>
       </c>
-      <c r="N37">
-        <v>1</v>
-      </c>
       <c r="O37">
-        <v>0</v>
-      </c>
-      <c r="Q37"/>
-      <c r="R37" s="2">
+        <v>1</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="R37"/>
+      <c r="S37" s="2">
         <v>7</v>
       </c>
-      <c r="S37">
+      <c r="T37">
         <v>3</v>
       </c>
-      <c r="T37" s="3">
+      <c r="U37" s="3">
         <v>4</v>
       </c>
-      <c r="U37" s="2">
+      <c r="V37" s="2">
         <v>2</v>
       </c>
-      <c r="V37">
+      <c r="W37">
         <v>6</v>
       </c>
-      <c r="W37" s="3">
+      <c r="X37" s="3">
         <v>8</v>
       </c>
-      <c r="Z37"/>
-      <c r="AC37"/>
-      <c r="AE37"/>
-      <c r="AG37"/>
-    </row>
-    <row r="38" spans="1:33">
+      <c r="AA37"/>
+      <c r="AD37"/>
+      <c r="AF37"/>
+      <c r="AH37"/>
+    </row>
+    <row r="38" spans="1:34">
       <c r="A38">
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C38" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D38" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F38" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G38" t="s">
-        <v>39</v>
-      </c>
-      <c r="J38" t="s">
         <v>40</v>
       </c>
-      <c r="K38"/>
-      <c r="L38" s="2">
-        <v>1</v>
-      </c>
-      <c r="M38" s="3">
-        <v>1</v>
-      </c>
-      <c r="N38">
+      <c r="K38" t="s">
+        <v>41</v>
+      </c>
+      <c r="L38"/>
+      <c r="M38" s="2">
+        <v>1</v>
+      </c>
+      <c r="N38" s="3">
         <v>1</v>
       </c>
       <c r="O38">
         <v>1</v>
       </c>
-      <c r="Q38"/>
-      <c r="R38" s="2">
+      <c r="P38">
+        <v>1</v>
+      </c>
+      <c r="R38"/>
+      <c r="S38" s="2">
         <v>21</v>
       </c>
-      <c r="S38">
+      <c r="T38">
         <v>4</v>
       </c>
-      <c r="T38" s="3">
+      <c r="U38" s="3">
         <v>5</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>2</v>
       </c>
-      <c r="V38">
+      <c r="W38">
         <v>3</v>
       </c>
-      <c r="W38" s="3">
+      <c r="X38" s="3">
         <v>5</v>
       </c>
-      <c r="Z38"/>
-      <c r="AC38"/>
-      <c r="AE38"/>
-      <c r="AG38"/>
-    </row>
-    <row r="39" spans="1:33">
+      <c r="AA38"/>
+      <c r="AD38"/>
+      <c r="AF38"/>
+      <c r="AH38"/>
+    </row>
+    <row r="39" spans="1:34">
       <c r="A39">
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C39" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D39" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F39" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G39" t="s">
-        <v>39</v>
-      </c>
-      <c r="J39" t="s">
         <v>40</v>
       </c>
-      <c r="K39"/>
-      <c r="L39" s="2">
-        <v>1</v>
-      </c>
-      <c r="M39" s="3">
-        <v>1</v>
-      </c>
-      <c r="N39">
+      <c r="K39" t="s">
+        <v>41</v>
+      </c>
+      <c r="L39"/>
+      <c r="M39" s="2">
+        <v>1</v>
+      </c>
+      <c r="N39" s="3">
         <v>1</v>
       </c>
       <c r="O39">
         <v>1</v>
       </c>
-      <c r="Q39"/>
-      <c r="R39" s="2">
+      <c r="P39">
+        <v>1</v>
+      </c>
+      <c r="R39"/>
+      <c r="S39" s="2">
         <v>5</v>
       </c>
-      <c r="S39">
-        <v>1</v>
-      </c>
-      <c r="T39" s="3">
+      <c r="T39">
+        <v>1</v>
+      </c>
+      <c r="U39" s="3">
         <v>2</v>
       </c>
-      <c r="U39" s="2">
+      <c r="V39" s="2">
         <v>2</v>
       </c>
-      <c r="V39">
+      <c r="W39">
         <v>6</v>
       </c>
-      <c r="W39" s="3">
+      <c r="X39" s="3">
         <v>7</v>
       </c>
-      <c r="Z39"/>
-      <c r="AC39"/>
-      <c r="AE39"/>
-      <c r="AG39"/>
-    </row>
-    <row r="40" spans="1:33">
+      <c r="AA39"/>
+      <c r="AD39"/>
+      <c r="AF39"/>
+      <c r="AH39"/>
+    </row>
+    <row r="40" spans="1:34">
       <c r="A40">
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C40" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D40" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F40" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G40" t="s">
-        <v>65</v>
-      </c>
-      <c r="J40" t="s">
-        <v>40</v>
-      </c>
-      <c r="K40"/>
-      <c r="L40" s="2">
+        <v>66</v>
+      </c>
+      <c r="K40" t="s">
+        <v>41</v>
+      </c>
+      <c r="L40"/>
+      <c r="M40" s="2">
         <v>4</v>
       </c>
-      <c r="M40" s="3">
+      <c r="N40" s="3">
         <v>3</v>
       </c>
-      <c r="N40">
-        <v>1</v>
-      </c>
       <c r="O40">
         <v>1</v>
       </c>
-      <c r="Q40"/>
-      <c r="R40" s="2">
+      <c r="P40">
+        <v>1</v>
+      </c>
+      <c r="R40"/>
+      <c r="S40" s="2">
         <v>7</v>
       </c>
-      <c r="S40">
+      <c r="T40">
         <v>4</v>
       </c>
-      <c r="T40" s="3">
+      <c r="U40" s="3">
         <v>5</v>
       </c>
-      <c r="U40" s="2">
+      <c r="V40" s="2">
         <v>38</v>
       </c>
-      <c r="V40">
+      <c r="W40">
         <v>4</v>
       </c>
-      <c r="W40" s="3">
+      <c r="X40" s="3">
         <v>5</v>
       </c>
-      <c r="Z40"/>
-      <c r="AC40"/>
-      <c r="AE40"/>
-      <c r="AG40"/>
-    </row>
-    <row r="41" spans="1:33">
+      <c r="AA40"/>
+      <c r="AD40"/>
+      <c r="AF40"/>
+      <c r="AH40"/>
+    </row>
+    <row r="41" spans="1:34">
       <c r="A41">
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C41" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D41" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F41" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G41" t="s">
-        <v>38</v>
-      </c>
-      <c r="J41" t="s">
-        <v>40</v>
-      </c>
-      <c r="K41"/>
-      <c r="L41" s="2">
+        <v>39</v>
+      </c>
+      <c r="K41" t="s">
+        <v>41</v>
+      </c>
+      <c r="L41"/>
+      <c r="M41" s="2">
         <v>2</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2</v>
       </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
       <c r="O41">
         <v>0</v>
       </c>
-      <c r="Q41"/>
-      <c r="R41" s="2">
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="R41"/>
+      <c r="S41" s="2">
         <v>6</v>
       </c>
-      <c r="S41">
+      <c r="T41">
         <v>3</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3</v>
       </c>
-      <c r="U41" s="2">
+      <c r="V41" s="2">
         <v>39</v>
       </c>
-      <c r="V41">
+      <c r="W41">
         <v>2</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3</v>
       </c>
-      <c r="Z41"/>
-      <c r="AC41"/>
-      <c r="AE41"/>
-      <c r="AG41"/>
-    </row>
-    <row r="42" spans="1:33">
+      <c r="AA41"/>
+      <c r="AD41"/>
+      <c r="AF41"/>
+      <c r="AH41"/>
+    </row>
+    <row r="42" spans="1:34">
       <c r="A42">
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C42" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D42" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F42" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G42" t="s">
-        <v>65</v>
-      </c>
-      <c r="J42" t="s">
-        <v>40</v>
-      </c>
-      <c r="K42"/>
-      <c r="L42" s="2">
+        <v>66</v>
+      </c>
+      <c r="K42" t="s">
+        <v>41</v>
+      </c>
+      <c r="L42"/>
+      <c r="M42" s="2">
         <v>4</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>3</v>
       </c>
-      <c r="N42">
-        <v>1</v>
-      </c>
       <c r="O42">
         <v>1</v>
       </c>
-      <c r="Q42"/>
-      <c r="R42" s="2">
+      <c r="P42">
+        <v>1</v>
+      </c>
+      <c r="R42"/>
+      <c r="S42" s="2">
         <v>7</v>
       </c>
-      <c r="S42">
-        <v>1</v>
-      </c>
-      <c r="T42" s="3">
+      <c r="T42">
+        <v>1</v>
+      </c>
+      <c r="U42" s="3">
         <v>3</v>
       </c>
-      <c r="U42" s="2">
+      <c r="V42" s="2">
         <v>41</v>
       </c>
-      <c r="V42">
-        <v>1</v>
-      </c>
-      <c r="W42" s="3">
-        <v>1</v>
-      </c>
-      <c r="Z42"/>
-      <c r="AC42"/>
-      <c r="AE42"/>
-      <c r="AG42"/>
-    </row>
-    <row r="43" spans="1:33">
+      <c r="W42">
+        <v>1</v>
+      </c>
+      <c r="X42" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA42"/>
+      <c r="AD42"/>
+      <c r="AF42"/>
+      <c r="AH42"/>
+    </row>
+    <row r="43" spans="1:34">
       <c r="A43">
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C43" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D43" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F43" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G43" t="s">
-        <v>38</v>
-      </c>
-      <c r="J43" t="s">
-        <v>40</v>
-      </c>
-      <c r="K43"/>
-      <c r="L43" s="2">
+        <v>39</v>
+      </c>
+      <c r="K43" t="s">
+        <v>41</v>
+      </c>
+      <c r="L43"/>
+      <c r="M43" s="2">
         <v>7</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4</v>
       </c>
-      <c r="N43">
-        <v>0</v>
-      </c>
       <c r="O43">
-        <v>1</v>
-      </c>
-      <c r="Q43"/>
-      <c r="R43" s="2">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>1</v>
+      </c>
+      <c r="R43"/>
+      <c r="S43" s="2">
         <v>6</v>
       </c>
-      <c r="S43">
+      <c r="T43">
         <v>5</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5</v>
       </c>
-      <c r="U43" s="2">
+      <c r="V43" s="2">
         <v>14</v>
       </c>
-      <c r="V43">
-        <v>1</v>
-      </c>
-      <c r="W43" s="3">
-        <v>1</v>
-      </c>
-      <c r="X43" s="2">
+      <c r="W43">
+        <v>1</v>
+      </c>
+      <c r="X43" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y43" s="2">
         <v>18</v>
       </c>
-      <c r="Y43">
+      <c r="Z43">
         <v>0.9</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1.2</v>
       </c>
-      <c r="AC43"/>
-      <c r="AE43"/>
-      <c r="AG43"/>
-    </row>
-    <row r="44" spans="1:23">
+      <c r="AD43"/>
+      <c r="AF43"/>
+      <c r="AH43"/>
+    </row>
+    <row r="44" spans="1:24">
       <c r="A44">
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C44" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D44" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F44" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G44" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H44" t="s">
-        <v>50</v>
-      </c>
-      <c r="J44" t="s">
-        <v>40</v>
-      </c>
-      <c r="L44">
+        <v>51</v>
+      </c>
+      <c r="K44" t="s">
+        <v>41</v>
+      </c>
+      <c r="M44">
         <v>6</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4</v>
       </c>
-      <c r="N44">
-        <v>1</v>
-      </c>
       <c r="O44">
         <v>1</v>
       </c>
-      <c r="R44" s="2">
+      <c r="P44">
+        <v>1</v>
+      </c>
+      <c r="S44" s="2">
         <v>15</v>
       </c>
-      <c r="S44">
+      <c r="T44">
         <v>2</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2</v>
       </c>
-      <c r="U44" s="2">
+      <c r="V44" s="2">
         <v>42</v>
       </c>
-      <c r="V44">
+      <c r="W44">
         <v>8</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:33">
+    <row r="45" spans="1:34">
       <c r="A45">
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C45" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D45" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F45" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G45" t="s">
-        <v>65</v>
-      </c>
-      <c r="J45" t="s">
-        <v>40</v>
-      </c>
-      <c r="K45"/>
-      <c r="L45" s="2">
+        <v>66</v>
+      </c>
+      <c r="K45" t="s">
+        <v>41</v>
+      </c>
+      <c r="L45"/>
+      <c r="M45" s="2">
         <v>5</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4</v>
       </c>
-      <c r="N45">
-        <v>0</v>
-      </c>
       <c r="O45">
-        <v>1</v>
-      </c>
-      <c r="Q45"/>
-      <c r="R45" s="2">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>1</v>
+      </c>
+      <c r="R45"/>
+      <c r="S45" s="2">
         <v>7</v>
       </c>
-      <c r="S45">
+      <c r="T45">
         <v>7</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>9</v>
       </c>
-      <c r="U45" s="2">
+      <c r="V45" s="2">
         <v>26</v>
       </c>
-      <c r="V45">
+      <c r="W45">
         <v>2</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2</v>
       </c>
-      <c r="X45" s="2">
+      <c r="Y45" s="2">
         <v>2</v>
       </c>
-      <c r="Y45">
+      <c r="Z45">
         <v>7</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>8</v>
       </c>
-      <c r="AC45"/>
-      <c r="AE45"/>
-      <c r="AG45"/>
-    </row>
-    <row r="46" spans="1:33">
+      <c r="AD45"/>
+      <c r="AF45"/>
+      <c r="AH45"/>
+    </row>
+    <row r="46" spans="1:34">
       <c r="A46">
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C46" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D46" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F46" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G46" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="J46" t="s">
+        <v>95</v>
+      </c>
+      <c r="K46" t="s">
+        <v>41</v>
+      </c>
+      <c r="L46"/>
+      <c r="M46" s="2">
+        <v>10</v>
+      </c>
+      <c r="N46" s="3">
+        <v>6</v>
+      </c>
+      <c r="O46">
+        <v>1</v>
+      </c>
+      <c r="P46">
+        <v>1</v>
+      </c>
+      <c r="R46"/>
+      <c r="S46" s="2">
+        <v>32</v>
+      </c>
+      <c r="T46">
         <v>40</v>
       </c>
-      <c r="K46"/>
-      <c r="L46" s="2">
-        <v>10</v>
-      </c>
-      <c r="M46" s="3">
-        <v>6</v>
-      </c>
-      <c r="N46">
-        <v>1</v>
-      </c>
-      <c r="O46">
-        <v>1</v>
-      </c>
-      <c r="Q46"/>
-      <c r="R46" s="2">
-        <v>32</v>
-      </c>
-      <c r="S46">
+      <c r="U46" s="3">
         <v>40</v>
       </c>
-      <c r="T46" s="3">
-        <v>40</v>
-      </c>
-      <c r="U46" s="2">
+      <c r="V46" s="2">
         <v>33</v>
       </c>
-      <c r="V46">
+      <c r="W46">
         <v>30</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>30</v>
       </c>
-      <c r="X46" s="2">
+      <c r="Y46" s="2">
         <v>19</v>
       </c>
-      <c r="Y46">
-        <v>1</v>
-      </c>
-      <c r="Z46" s="3">
-        <v>1</v>
-      </c>
-      <c r="AC46"/>
-      <c r="AE46"/>
-      <c r="AG46"/>
-    </row>
-    <row r="47" spans="1:33">
+      <c r="Z46">
+        <v>1</v>
+      </c>
+      <c r="AA46" s="3">
+        <v>1</v>
+      </c>
+      <c r="AD46"/>
+      <c r="AF46"/>
+      <c r="AH46"/>
+    </row>
+    <row r="47" spans="1:34">
       <c r="A47">
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C47" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D47" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F47" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G47" t="s">
-        <v>65</v>
-      </c>
-      <c r="J47" t="s">
-        <v>40</v>
-      </c>
-      <c r="K47"/>
-      <c r="L47" s="2">
+        <v>66</v>
+      </c>
+      <c r="K47" t="s">
+        <v>41</v>
+      </c>
+      <c r="L47"/>
+      <c r="M47" s="2">
         <v>2</v>
       </c>
-      <c r="M47" s="3">
-        <v>1</v>
-      </c>
-      <c r="N47">
-        <v>0</v>
+      <c r="N47" s="3">
+        <v>1</v>
       </c>
       <c r="O47">
         <v>0</v>
       </c>
-      <c r="Q47"/>
-      <c r="R47" s="2">
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="R47"/>
+      <c r="S47" s="2">
         <v>11</v>
       </c>
-      <c r="S47">
+      <c r="T47">
         <v>10</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>14</v>
       </c>
-      <c r="W47"/>
-      <c r="Z47"/>
-      <c r="AC47"/>
-      <c r="AE47"/>
-      <c r="AG47"/>
-    </row>
-    <row r="48" spans="1:33">
+      <c r="X47"/>
+      <c r="AA47"/>
+      <c r="AD47"/>
+      <c r="AF47"/>
+      <c r="AH47"/>
+    </row>
+    <row r="48" spans="1:34">
       <c r="A48">
         <v>49</v>
       </c>
@@ -5222,1191 +5223,1190 @@
         <v>123</v>
       </c>
       <c r="C48" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D48" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F48" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G48" t="s">
-        <v>38</v>
-      </c>
-      <c r="J48" t="s">
-        <v>40</v>
-      </c>
-      <c r="K48"/>
-      <c r="L48" s="2">
+        <v>39</v>
+      </c>
+      <c r="K48" t="s">
+        <v>41</v>
+      </c>
+      <c r="L48"/>
+      <c r="M48" s="2">
         <v>4</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3</v>
       </c>
-      <c r="N48">
-        <v>0</v>
-      </c>
       <c r="O48">
         <v>0</v>
       </c>
-      <c r="Q48"/>
-      <c r="R48" s="2">
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="R48"/>
+      <c r="S48" s="2">
         <v>11</v>
       </c>
-      <c r="S48">
+      <c r="T48">
         <v>8</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>11</v>
       </c>
-      <c r="U48" s="2">
+      <c r="V48" s="2">
         <v>6</v>
       </c>
-      <c r="V48">
+      <c r="W48">
         <v>3</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3</v>
       </c>
-      <c r="Z48"/>
-      <c r="AC48"/>
-      <c r="AE48"/>
-      <c r="AG48"/>
-    </row>
-    <row r="49" spans="1:23">
+      <c r="AA48"/>
+      <c r="AD48"/>
+      <c r="AF48"/>
+      <c r="AH48"/>
+    </row>
+    <row r="49" spans="1:24">
       <c r="A49">
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C49" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D49" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F49" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G49" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H49" t="s">
-        <v>125</v>
-      </c>
-      <c r="J49" t="s">
-        <v>40</v>
-      </c>
-      <c r="L49">
+        <v>126</v>
+      </c>
+      <c r="K49" t="s">
+        <v>41</v>
+      </c>
+      <c r="M49">
         <v>4</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3</v>
       </c>
-      <c r="N49">
-        <v>0</v>
-      </c>
       <c r="O49">
         <v>0</v>
       </c>
-      <c r="R49" s="2">
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="S49" s="2">
         <v>11</v>
       </c>
-      <c r="S49">
+      <c r="T49">
         <v>7</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>11</v>
       </c>
-      <c r="U49" s="2">
+      <c r="V49" s="2">
         <v>45</v>
       </c>
-      <c r="V49">
+      <c r="W49">
         <v>2</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:33">
+    <row r="50" spans="1:34">
       <c r="A50">
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C50" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D50" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F50" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G50" t="s">
-        <v>38</v>
-      </c>
-      <c r="J50" t="s">
-        <v>40</v>
-      </c>
-      <c r="K50"/>
-      <c r="L50" s="2">
+        <v>39</v>
+      </c>
+      <c r="K50" t="s">
+        <v>41</v>
+      </c>
+      <c r="L50"/>
+      <c r="M50" s="2">
         <v>5</v>
       </c>
-      <c r="M50" s="3">
+      <c r="N50" s="3">
         <v>4</v>
       </c>
-      <c r="N50">
-        <v>1</v>
-      </c>
       <c r="O50">
         <v>1</v>
       </c>
-      <c r="Q50"/>
-      <c r="R50" s="2">
+      <c r="P50">
+        <v>1</v>
+      </c>
+      <c r="R50"/>
+      <c r="S50" s="2">
         <v>6</v>
       </c>
-      <c r="S50">
+      <c r="T50">
         <v>5</v>
       </c>
-      <c r="T50" s="3">
+      <c r="U50" s="3">
         <v>7</v>
       </c>
-      <c r="U50" s="2">
+      <c r="V50" s="2">
         <v>18</v>
       </c>
-      <c r="V50">
+      <c r="W50">
         <v>1.1</v>
       </c>
-      <c r="W50" s="3">
+      <c r="X50" s="3">
         <v>1.7</v>
       </c>
-      <c r="Z50"/>
-      <c r="AC50"/>
-      <c r="AE50"/>
-      <c r="AG50"/>
-    </row>
-    <row r="51" spans="1:33">
+      <c r="AA50"/>
+      <c r="AD50"/>
+      <c r="AF50"/>
+      <c r="AH50"/>
+    </row>
+    <row r="51" spans="1:34">
       <c r="A51">
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C51" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D51" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F51" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G51" t="s">
-        <v>38</v>
-      </c>
-      <c r="J51" t="s">
-        <v>40</v>
-      </c>
-      <c r="K51"/>
-      <c r="L51" s="2">
+        <v>39</v>
+      </c>
+      <c r="K51" t="s">
+        <v>41</v>
+      </c>
+      <c r="L51"/>
+      <c r="M51" s="2">
         <v>9</v>
       </c>
-      <c r="M51" s="3">
+      <c r="N51" s="3">
         <v>6</v>
       </c>
-      <c r="N51">
-        <v>1</v>
-      </c>
       <c r="O51">
         <v>1</v>
       </c>
-      <c r="Q51"/>
-      <c r="R51" s="2">
+      <c r="P51">
+        <v>1</v>
+      </c>
+      <c r="R51"/>
+      <c r="S51" s="2">
         <v>6</v>
       </c>
-      <c r="S51">
-        <v>1</v>
-      </c>
-      <c r="T51" s="3">
+      <c r="T51">
+        <v>1</v>
+      </c>
+      <c r="U51" s="3">
         <v>3</v>
       </c>
-      <c r="U51" s="2">
+      <c r="V51" s="2">
         <v>49</v>
       </c>
-      <c r="V51">
-        <v>1</v>
-      </c>
-      <c r="W51" s="3">
-        <v>1</v>
-      </c>
-      <c r="Z51"/>
-      <c r="AC51"/>
-      <c r="AE51"/>
-      <c r="AG51"/>
-    </row>
-    <row r="52" spans="1:33">
+      <c r="W51">
+        <v>1</v>
+      </c>
+      <c r="X51" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA51"/>
+      <c r="AD51"/>
+      <c r="AF51"/>
+      <c r="AH51"/>
+    </row>
+    <row r="52" spans="1:34">
       <c r="A52">
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C52" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D52" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F52" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G52" t="s">
-        <v>39</v>
-      </c>
-      <c r="J52" t="s">
         <v>40</v>
       </c>
-      <c r="K52"/>
-      <c r="L52" s="2">
-        <v>1</v>
-      </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
-      <c r="N52">
-        <v>1</v>
+      <c r="K52" t="s">
+        <v>41</v>
+      </c>
+      <c r="L52"/>
+      <c r="M52" s="2">
+        <v>1</v>
+      </c>
+      <c r="N52" s="3">
+        <v>0</v>
       </c>
       <c r="O52">
         <v>1</v>
       </c>
-      <c r="Q52"/>
-      <c r="R52" s="2">
+      <c r="P52">
+        <v>1</v>
+      </c>
+      <c r="R52"/>
+      <c r="S52" s="2">
         <v>9</v>
       </c>
-      <c r="S52">
+      <c r="T52">
         <v>2</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2</v>
       </c>
-      <c r="U52" s="2">
+      <c r="V52" s="2">
         <v>21</v>
       </c>
-      <c r="V52">
+      <c r="W52">
         <v>2</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2</v>
       </c>
-      <c r="Z52"/>
-      <c r="AC52"/>
-      <c r="AE52"/>
-      <c r="AG52"/>
-    </row>
-    <row r="53" spans="1:23">
+      <c r="AA52"/>
+      <c r="AD52"/>
+      <c r="AF52"/>
+      <c r="AH52"/>
+    </row>
+    <row r="53" spans="1:24">
       <c r="A53">
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C53" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D53" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F53" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G53" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H53" t="s">
+        <v>51</v>
+      </c>
+      <c r="K53" t="s">
+        <v>41</v>
+      </c>
+      <c r="M53">
+        <v>5</v>
+      </c>
+      <c r="N53" s="3">
+        <v>5</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>1</v>
+      </c>
+      <c r="R53" s="3">
+        <v>6</v>
+      </c>
+      <c r="S53">
         <v>50</v>
       </c>
-      <c r="J53" t="s">
-        <v>40</v>
-      </c>
-      <c r="L53">
-        <v>5</v>
-      </c>
-      <c r="M53" s="3">
-        <v>5</v>
-      </c>
-      <c r="N53">
-        <v>0</v>
-      </c>
-      <c r="O53">
-        <v>1</v>
-      </c>
-      <c r="Q53" s="3">
-        <v>6</v>
-      </c>
-      <c r="R53">
-        <v>50</v>
-      </c>
-      <c r="S53">
+      <c r="T53">
         <v>3</v>
       </c>
-      <c r="T53" s="3">
+      <c r="U53" s="3">
         <v>4</v>
       </c>
-      <c r="U53">
+      <c r="V53">
         <v>51</v>
       </c>
-      <c r="V53">
+      <c r="W53">
         <v>-0.5</v>
       </c>
-      <c r="W53" s="3">
+      <c r="X53" s="3">
         <v>-0.5</v>
       </c>
     </row>
-    <row r="54" spans="1:26">
+    <row r="54" spans="1:27">
       <c r="A54">
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C54" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F54" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G54" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H54" t="s">
-        <v>50</v>
-      </c>
-      <c r="J54" t="s">
-        <v>58</v>
-      </c>
-      <c r="K54" s="3">
+        <v>51</v>
+      </c>
+      <c r="K54" t="s">
+        <v>59</v>
+      </c>
+      <c r="L54" s="3">
         <v>14</v>
       </c>
-      <c r="L54">
+      <c r="M54">
         <v>2</v>
       </c>
-      <c r="M54" s="3">
-        <v>1</v>
-      </c>
-      <c r="N54">
-        <v>0</v>
+      <c r="N54" s="3">
+        <v>1</v>
       </c>
       <c r="O54">
-        <v>1</v>
-      </c>
-      <c r="R54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>1</v>
+      </c>
+      <c r="S54">
         <v>15</v>
       </c>
-      <c r="S54">
+      <c r="T54">
         <v>3</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4</v>
       </c>
-      <c r="U54">
+      <c r="V54">
         <v>14</v>
       </c>
-      <c r="V54">
-        <v>1</v>
-      </c>
-      <c r="W54" s="3">
-        <v>1</v>
-      </c>
-      <c r="X54">
+      <c r="W54">
+        <v>1</v>
+      </c>
+      <c r="X54" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y54">
         <v>52</v>
       </c>
-      <c r="Y54">
+      <c r="Z54">
         <v>3</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:32">
+    <row r="55" spans="1:33">
       <c r="A55">
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C55" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D55" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F55" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G55" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H55" t="s">
-        <v>50</v>
-      </c>
-      <c r="J55" t="s">
-        <v>40</v>
-      </c>
-      <c r="L55">
+        <v>51</v>
+      </c>
+      <c r="K55" t="s">
+        <v>41</v>
+      </c>
+      <c r="M55">
         <v>4</v>
       </c>
-      <c r="M55" s="3">
+      <c r="N55" s="3">
         <v>3</v>
       </c>
-      <c r="N55">
-        <v>1</v>
-      </c>
       <c r="O55">
         <v>1</v>
       </c>
-      <c r="R55">
+      <c r="P55">
+        <v>1</v>
+      </c>
+      <c r="S55">
         <v>15</v>
       </c>
-      <c r="S55">
-        <v>1</v>
-      </c>
-      <c r="T55" s="3">
+      <c r="T55">
+        <v>1</v>
+      </c>
+      <c r="U55" s="3">
         <v>3</v>
       </c>
-      <c r="U55">
+      <c r="V55">
         <v>60</v>
       </c>
-      <c r="V55">
-        <v>1</v>
-      </c>
-      <c r="W55" s="3">
-        <v>1</v>
-      </c>
-      <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="1:32">
+      <c r="W55">
+        <v>1</v>
+      </c>
+      <c r="X55" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="1:33">
       <c r="A56">
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C56" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D56" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F56" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G56" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H56" t="s">
-        <v>125</v>
-      </c>
-      <c r="J56" t="s">
-        <v>58</v>
-      </c>
-      <c r="K56" s="3">
+        <v>126</v>
+      </c>
+      <c r="K56" t="s">
+        <v>59</v>
+      </c>
+      <c r="L56" s="3">
         <v>3</v>
       </c>
-      <c r="L56">
+      <c r="M56">
         <v>2</v>
       </c>
-      <c r="M56" s="3">
-        <v>1</v>
-      </c>
-      <c r="N56">
-        <v>0</v>
+      <c r="N56" s="3">
+        <v>1</v>
       </c>
       <c r="O56">
-        <v>1</v>
-      </c>
-      <c r="R56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>1</v>
+      </c>
+      <c r="S56">
         <v>45</v>
       </c>
-      <c r="S56">
+      <c r="T56">
         <v>3</v>
       </c>
-      <c r="T56" s="3">
+      <c r="U56" s="3">
         <v>4</v>
       </c>
-      <c r="U56">
+      <c r="V56">
         <v>11</v>
       </c>
-      <c r="V56">
+      <c r="W56">
         <v>12</v>
       </c>
-      <c r="W56" s="3">
+      <c r="X56" s="3">
         <v>18</v>
       </c>
-      <c r="X56">
+      <c r="Y56">
         <v>14</v>
       </c>
-      <c r="Y56">
-        <v>1</v>
-      </c>
-      <c r="Z56" s="3">
-        <v>1</v>
-      </c>
-      <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="1:26">
+      <c r="Z56">
+        <v>1</v>
+      </c>
+      <c r="AA56" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="1:27">
       <c r="A57">
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C57" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F57" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G57" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H57" t="s">
-        <v>125</v>
-      </c>
-      <c r="J57" t="s">
-        <v>58</v>
-      </c>
-      <c r="K57" s="3">
+        <v>126</v>
+      </c>
+      <c r="K57" t="s">
+        <v>59</v>
+      </c>
+      <c r="L57" s="3">
         <v>3</v>
       </c>
-      <c r="L57">
+      <c r="M57">
         <v>2</v>
       </c>
-      <c r="M57" s="3">
-        <v>1</v>
-      </c>
-      <c r="N57">
+      <c r="N57" s="3">
         <v>1</v>
       </c>
       <c r="O57">
         <v>1</v>
       </c>
-      <c r="R57">
+      <c r="P57">
+        <v>1</v>
+      </c>
+      <c r="S57">
         <v>2</v>
       </c>
-      <c r="S57">
+      <c r="T57">
         <v>5</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6</v>
       </c>
-      <c r="U57">
+      <c r="V57">
         <v>2</v>
       </c>
-      <c r="V57">
+      <c r="W57">
         <v>5</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>6</v>
       </c>
-      <c r="X57">
+      <c r="Y57">
         <v>66</v>
       </c>
-      <c r="Y57">
+      <c r="Z57">
         <v>0.6</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1.2</v>
       </c>
     </row>
-    <row r="58" spans="1:20">
+    <row r="58" spans="1:21">
       <c r="A58">
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C58" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F58" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G58" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H58" t="s">
-        <v>125</v>
-      </c>
-      <c r="J58" t="s">
-        <v>211</v>
-      </c>
-      <c r="L58">
+        <v>126</v>
+      </c>
+      <c r="K58" t="s">
+        <v>212</v>
+      </c>
+      <c r="M58">
         <v>3</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2</v>
       </c>
-      <c r="N58">
-        <v>1</v>
-      </c>
       <c r="O58">
-        <v>0</v>
-      </c>
-      <c r="R58">
+        <v>1</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="S58">
         <v>66</v>
       </c>
-      <c r="S58">
+      <c r="T58">
         <v>1.2</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1.7</v>
       </c>
     </row>
-    <row r="59" spans="1:23">
+    <row r="59" spans="1:24">
       <c r="A59">
         <v>60</v>
       </c>
       <c r="B59" t="s">
+        <v>213</v>
+      </c>
+      <c r="C59" t="s">
+        <v>214</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F59" t="s">
+        <v>39</v>
+      </c>
+      <c r="G59" t="s">
+        <v>50</v>
+      </c>
+      <c r="H59" t="s">
+        <v>126</v>
+      </c>
+      <c r="K59" t="s">
         <v>212</v>
       </c>
-      <c r="C59" t="s">
-        <v>213</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F59" t="s">
-        <v>38</v>
-      </c>
-      <c r="G59" t="s">
-        <v>49</v>
-      </c>
-      <c r="H59" t="s">
-        <v>125</v>
-      </c>
-      <c r="J59" t="s">
-        <v>211</v>
-      </c>
-      <c r="L59">
+      <c r="M59">
         <v>3</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3</v>
       </c>
-      <c r="N59">
-        <v>1</v>
-      </c>
       <c r="O59">
-        <v>0</v>
-      </c>
-      <c r="R59">
+        <v>1</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="S59">
         <v>2</v>
       </c>
-      <c r="S59">
+      <c r="T59">
         <v>7</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9</v>
       </c>
-      <c r="U59">
+      <c r="V59">
         <v>66</v>
       </c>
-      <c r="V59">
+      <c r="W59">
         <v>0.9</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1.4</v>
       </c>
     </row>
-    <row r="60" spans="1:23">
+    <row r="60" spans="1:24">
       <c r="A60">
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C60" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D60" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F60" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G60" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H60" t="s">
-        <v>125</v>
-      </c>
-      <c r="J60" t="s">
-        <v>211</v>
-      </c>
-      <c r="L60">
+        <v>126</v>
+      </c>
+      <c r="K60" t="s">
+        <v>212</v>
+      </c>
+      <c r="M60">
         <v>2</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2</v>
       </c>
-      <c r="N60">
-        <v>1</v>
-      </c>
       <c r="O60">
         <v>1</v>
       </c>
-      <c r="R60">
+      <c r="P60">
+        <v>1</v>
+      </c>
+      <c r="S60">
         <v>66</v>
       </c>
-      <c r="S60">
+      <c r="T60">
         <v>3</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4</v>
       </c>
-      <c r="U60">
+      <c r="V60">
         <v>67</v>
       </c>
-      <c r="V60">
+      <c r="W60">
         <v>-1</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>-1</v>
       </c>
     </row>
-    <row r="61" spans="1:23">
+    <row r="61" spans="1:24">
       <c r="A61">
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C61" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D61" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F61" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G61" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H61" t="s">
-        <v>125</v>
-      </c>
-      <c r="J61" t="s">
-        <v>58</v>
-      </c>
-      <c r="K61" s="3">
+        <v>126</v>
+      </c>
+      <c r="K61" t="s">
+        <v>59</v>
+      </c>
+      <c r="L61" s="3">
         <v>14</v>
       </c>
-      <c r="L61">
+      <c r="M61">
         <v>2</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2</v>
       </c>
-      <c r="N61">
-        <v>0</v>
-      </c>
       <c r="O61">
-        <v>1</v>
-      </c>
-      <c r="R61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>1</v>
+      </c>
+      <c r="S61">
         <v>66</v>
       </c>
-      <c r="S61">
+      <c r="T61">
         <v>1.2</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1.5</v>
       </c>
-      <c r="U61">
+      <c r="V61">
         <v>62</v>
       </c>
-      <c r="V61">
-        <v>1</v>
-      </c>
-      <c r="W61" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:23">
+      <c r="W61">
+        <v>1</v>
+      </c>
+      <c r="X61" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:24">
       <c r="A62">
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C62" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D62" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F62" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G62" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H62" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I62" t="s">
-        <v>125</v>
-      </c>
-      <c r="J62" t="s">
-        <v>40</v>
-      </c>
-      <c r="L62">
+        <v>126</v>
+      </c>
+      <c r="K62" t="s">
+        <v>41</v>
+      </c>
+      <c r="M62">
         <v>5</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4</v>
       </c>
-      <c r="N62">
-        <v>1</v>
-      </c>
       <c r="O62">
         <v>1</v>
       </c>
-      <c r="R62">
+      <c r="P62">
+        <v>1</v>
+      </c>
+      <c r="S62">
         <v>15</v>
       </c>
-      <c r="S62">
+      <c r="T62">
         <v>6</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>8</v>
       </c>
-      <c r="U62">
+      <c r="V62">
         <v>45</v>
       </c>
-      <c r="V62">
+      <c r="W62">
         <v>6</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="1:29">
+    <row r="63" spans="1:30">
       <c r="A63">
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C63" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D63" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F63" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G63" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H63" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I63" t="s">
-        <v>125</v>
-      </c>
-      <c r="J63" t="s">
-        <v>211</v>
-      </c>
-      <c r="L63">
+        <v>126</v>
+      </c>
+      <c r="K63" t="s">
+        <v>212</v>
+      </c>
+      <c r="M63">
         <v>6</v>
       </c>
-      <c r="M63" s="3">
+      <c r="N63" s="3">
         <v>5</v>
       </c>
-      <c r="N63">
-        <v>0</v>
-      </c>
       <c r="O63">
-        <v>1</v>
-      </c>
-      <c r="R63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>1</v>
+      </c>
+      <c r="S63">
         <v>33</v>
       </c>
-      <c r="S63">
+      <c r="T63">
         <v>-30</v>
       </c>
-      <c r="T63" s="3">
+      <c r="U63" s="3">
         <v>-30</v>
       </c>
-      <c r="U63">
+      <c r="V63">
         <v>11</v>
       </c>
-      <c r="V63">
+      <c r="W63">
         <v>32</v>
       </c>
-      <c r="W63" s="3">
+      <c r="X63" s="3">
         <v>40</v>
       </c>
-      <c r="X63">
+      <c r="Y63">
         <v>2</v>
       </c>
-      <c r="Y63">
+      <c r="Z63">
         <v>15</v>
       </c>
-      <c r="Z63" s="3">
+      <c r="AA63" s="3">
         <v>18</v>
       </c>
-      <c r="AA63">
+      <c r="AB63">
         <v>66</v>
       </c>
-      <c r="AB63">
+      <c r="AC63">
         <v>1.5</v>
       </c>
-      <c r="AC63" s="3">
+      <c r="AD63" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:23">
+    <row r="64" spans="1:24">
       <c r="A64">
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C64" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F64" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G64" t="s">
-        <v>39</v>
-      </c>
-      <c r="J64" t="s">
         <v>40</v>
       </c>
-      <c r="L64">
+      <c r="K64" t="s">
+        <v>41</v>
+      </c>
+      <c r="M64">
         <v>4</v>
       </c>
-      <c r="M64" s="3">
+      <c r="N64" s="3">
         <v>4</v>
       </c>
-      <c r="N64">
-        <v>1</v>
-      </c>
       <c r="O64">
         <v>1</v>
       </c>
-      <c r="R64">
+      <c r="P64">
+        <v>1</v>
+      </c>
+      <c r="S64">
         <v>33</v>
       </c>
-      <c r="S64">
+      <c r="T64">
         <v>50</v>
       </c>
-      <c r="T64" s="3">
+      <c r="U64" s="3">
         <v>50</v>
       </c>
-      <c r="U64">
+      <c r="V64">
         <v>68</v>
       </c>
-      <c r="V64">
+      <c r="W64">
         <v>0.1</v>
       </c>
-      <c r="W64" s="3">
+      <c r="X64" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="65" spans="1:23">
+    <row r="65" spans="1:24">
       <c r="A65">
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C65" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F65" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G65" t="s">
-        <v>39</v>
-      </c>
-      <c r="J65" t="s">
         <v>40</v>
       </c>
-      <c r="L65">
+      <c r="K65" t="s">
+        <v>41</v>
+      </c>
+      <c r="M65">
         <v>5</v>
       </c>
-      <c r="M65" s="3">
+      <c r="N65" s="3">
         <v>5</v>
       </c>
-      <c r="N65">
-        <v>1</v>
-      </c>
       <c r="O65">
         <v>1</v>
       </c>
-      <c r="R65">
+      <c r="P65">
+        <v>1</v>
+      </c>
+      <c r="S65">
         <v>19</v>
       </c>
-      <c r="S65">
-        <v>1</v>
-      </c>
-      <c r="T65" s="3">
-        <v>1</v>
-      </c>
-      <c r="U65">
+      <c r="T65">
+        <v>1</v>
+      </c>
+      <c r="U65" s="3">
+        <v>1</v>
+      </c>
+      <c r="V65">
         <v>69</v>
       </c>
-      <c r="V65">
-        <v>1</v>
-      </c>
-      <c r="W65" s="3">
+      <c r="W65">
+        <v>1</v>
+      </c>
+      <c r="X65" s="3">
         <v>1.5</v>
       </c>
     </row>
-    <row r="66" spans="1:29">
+    <row r="66" spans="1:30">
       <c r="A66">
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C66" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D66" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F66" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G66" t="s">
-        <v>39</v>
-      </c>
-      <c r="J66" t="s">
         <v>40</v>
       </c>
-      <c r="K66" s="3"/>
-      <c r="L66">
+      <c r="K66" t="s">
+        <v>41</v>
+      </c>
+      <c r="M66">
         <v>4</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4</v>
       </c>
-      <c r="N66">
-        <v>1</v>
-      </c>
       <c r="O66">
         <v>1</v>
       </c>
-      <c r="R66">
+      <c r="P66">
+        <v>1</v>
+      </c>
+      <c r="S66">
         <v>11</v>
       </c>
-      <c r="S66">
+      <c r="T66">
         <v>12</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>15</v>
       </c>
-      <c r="U66">
+      <c r="V66">
         <v>9</v>
       </c>
-      <c r="V66">
-        <v>1</v>
-      </c>
-      <c r="W66" s="3">
-        <v>1</v>
-      </c>
-      <c r="X66">
+      <c r="W66">
+        <v>1</v>
+      </c>
+      <c r="X66" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y66">
         <v>14</v>
       </c>
-      <c r="Y66">
-        <v>1</v>
-      </c>
-      <c r="Z66" s="3">
-        <v>1</v>
-      </c>
-      <c r="AA66">
+      <c r="Z66">
+        <v>1</v>
+      </c>
+      <c r="AA66" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB66">
         <v>2</v>
       </c>
-      <c r="AB66">
+      <c r="AC66">
         <v>5</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>7</v>
       </c>
     </row>
@@ -6448,19 +6448,19 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6468,13 +6468,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I2">
         <v>-1</v>
@@ -6485,19 +6485,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -6508,16 +6508,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -6528,16 +6528,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -6548,13 +6548,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -6565,16 +6565,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -6585,13 +6585,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -6605,13 +6605,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>261</v>
+      </c>
+      <c r="C9" t="s">
+        <v>261</v>
+      </c>
+      <c r="D9" t="s">
         <v>260</v>
-      </c>
-      <c r="C9" t="s">
-        <v>260</v>
-      </c>
-      <c r="D9" t="s">
-        <v>259</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -6625,13 +6625,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -6645,13 +6645,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D11" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -6662,16 +6662,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C12" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D12" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E12" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -6682,16 +6682,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C13" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D13" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -6702,19 +6702,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -6725,16 +6725,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C15" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D15" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -6745,16 +6745,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C16" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D16" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E16" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -6765,13 +6765,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C17" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -6785,16 +6785,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C18" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D18" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -6805,13 +6805,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C19" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D19" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -6825,13 +6825,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C20" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -6845,16 +6845,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C21" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D21" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E21" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -6865,16 +6865,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C22" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D22" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -6885,13 +6885,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D23" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E23">
         <v>5</v>
@@ -6905,19 +6905,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D24" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -6928,13 +6928,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D25" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -6948,16 +6948,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D26" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E26" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -6971,16 +6971,16 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D27" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E27" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -6991,13 +6991,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D28" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -7011,19 +7011,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D29" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -7037,13 +7037,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C30" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D30" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -7057,19 +7057,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C31" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D31" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E31" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F31" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -7080,19 +7080,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C32" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D32" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E32">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -7103,19 +7103,19 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C33" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D33" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E33">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -7126,16 +7126,16 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C34" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D34" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E34" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -7146,16 +7146,16 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C35" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D35" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E35" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -7166,19 +7166,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
+        <v>304</v>
+      </c>
+      <c r="C36" t="s">
+        <v>304</v>
+      </c>
+      <c r="D36" t="s">
+        <v>244</v>
+      </c>
+      <c r="E36" t="s">
         <v>303</v>
       </c>
-      <c r="C36" t="s">
-        <v>303</v>
-      </c>
-      <c r="D36" t="s">
-        <v>243</v>
-      </c>
-      <c r="E36" t="s">
-        <v>302</v>
-      </c>
       <c r="F36" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -7192,13 +7192,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C37" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D37" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E37">
         <v>11</v>
@@ -7212,16 +7212,16 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C38" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D38" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -7232,13 +7232,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C39" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D39" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -7255,16 +7255,16 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C40" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D40" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E40" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -7275,13 +7275,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C41" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D41" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -7298,19 +7298,19 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C42" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D42" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -7324,13 +7324,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C43" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D43" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E43">
         <v>12</v>
@@ -7344,13 +7344,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C44" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D44" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E44">
         <v>13</v>
@@ -7364,19 +7364,19 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C45" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D45" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E45" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F45" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I45">
         <v>-1</v>
@@ -7387,16 +7387,16 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C46" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D46" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E46" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I46">
         <v>1</v>
@@ -7407,13 +7407,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C47" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D47" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E47">
         <v>14</v>
@@ -7427,19 +7427,19 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C48" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D48" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I48">
         <v>-1</v>
@@ -7450,13 +7450,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C49" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D49" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E49">
         <v>15</v>
@@ -7470,19 +7470,19 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C50" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D50" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I50">
         <v>-1</v>
@@ -7493,13 +7493,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C51" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D51" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E51">
         <v>16</v>
@@ -7513,13 +7513,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C52" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D52" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -7533,13 +7533,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C53" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D53" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E53">
         <v>3</v>
@@ -7553,13 +7553,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C54" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D54" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E54">
         <v>3</v>
@@ -7576,16 +7576,16 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C55" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D55" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E55" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G55">
         <v>6</v>
@@ -7599,16 +7599,16 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C56" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D56" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E56" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G56">
         <v>7</v>
@@ -7622,16 +7622,16 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C57" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D57" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E57" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G57">
         <v>8</v>
@@ -7645,16 +7645,16 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C58" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D58" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E58" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G58">
         <v>6</v>
@@ -7668,16 +7668,16 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
+        <v>333</v>
+      </c>
+      <c r="C59" t="s">
         <v>332</v>
       </c>
-      <c r="C59" t="s">
-        <v>331</v>
-      </c>
       <c r="D59" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E59" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G59">
         <v>7</v>
@@ -7691,16 +7691,16 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C60" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D60" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E60" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G60">
         <v>8</v>
@@ -7714,19 +7714,19 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C61" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D61" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E61">
         <v>3</v>
       </c>
       <c r="F61" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I61">
         <v>-1</v>
@@ -7737,13 +7737,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C62" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D62" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E62">
         <v>20</v>
@@ -7757,16 +7757,16 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C63" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D63" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F63" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="I63">
         <v>-1</v>
@@ -7777,13 +7777,13 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C64" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D64" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E64">
         <v>21</v>
@@ -7797,13 +7797,13 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C65" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D65" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E65">
         <v>3</v>
@@ -7817,19 +7817,19 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C66" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D66" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E66">
         <v>14</v>
       </c>
       <c r="F66" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I66">
         <v>-1</v>
@@ -7840,13 +7840,13 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C67" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D67" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E67">
         <v>22</v>
@@ -7860,13 +7860,13 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D68" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E68" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I68">
         <v>-1</v>
@@ -7877,13 +7877,13 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
+        <v>344</v>
+      </c>
+      <c r="D69" t="s">
         <v>343</v>
       </c>
-      <c r="D69" t="s">
-        <v>342</v>
-      </c>
       <c r="E69" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I69">
         <v>-1</v>
@@ -7894,13 +7894,13 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D70" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E70" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I70">
         <v>-1</v>
@@ -7911,13 +7911,13 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D71" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E71" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I71">
         <v>-1</v>
@@ -7933,22 +7933,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9.425" customWidth="1"/>
     <col min="2" max="2" width="27.425" customWidth="1"/>
     <col min="3" max="3" width="14.425" customWidth="1"/>
-    <col min="4" max="5" width="16.1416666666667" customWidth="1"/>
-    <col min="6" max="6" width="12.425" customWidth="1"/>
-    <col min="7" max="7" width="14.425" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="10.1416666666667" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="4" max="6" width="16.1416666666667" customWidth="1"/>
+    <col min="7" max="7" width="12.425" customWidth="1"/>
+    <col min="8" max="8" width="14.425" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="10.1416666666667" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7956,54 +7956,57 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="F1" t="s">
-        <v>17</v>
+        <v>351</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="G1" t="s">
         <v>18</v>
       </c>
       <c r="H1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I1" t="s">
         <v>21</v>
       </c>
       <c r="J1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K1" t="s">
         <v>24</v>
       </c>
       <c r="L1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M1" t="s">
         <v>27</v>
       </c>
       <c r="N1" t="s">
-        <v>351</v>
+        <v>28</v>
       </c>
       <c r="O1" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="P1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -8011,39 +8014,39 @@
       <c r="E2">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
         <v>12</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>-1</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C3" t="s">
         <v>355</v>
       </c>
-      <c r="C3" t="s">
-        <v>354</v>
-      </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>16</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>1</v>
       </c>
     </row>
@@ -8052,10 +8055,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -8064,15 +8067,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:12">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C5" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -8080,34 +8083,34 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>13</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>0.5</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>53</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>0.5</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>54</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -8115,22 +8118,22 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>5</v>
       </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="H6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -8138,22 +8141,22 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>20</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:8">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C8" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -8161,22 +8164,22 @@
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>22</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:8">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -8184,22 +8187,22 @@
       <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>25</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>-0.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:8">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C10" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -8207,22 +8210,22 @@
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>27</v>
       </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="H10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -8230,28 +8233,28 @@
       <c r="E11">
         <v>1</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>29</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>18</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>30</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>-1</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:10">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C12" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -8259,28 +8262,28 @@
       <c r="E12">
         <v>2</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>29</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>24</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>31</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>-1</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:8">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C13" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -8288,22 +8291,22 @@
       <c r="E13">
         <v>0</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>33</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:8">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -8311,22 +8314,22 @@
       <c r="E14">
         <v>0</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>40</v>
       </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="H14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C15" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -8334,22 +8337,22 @@
       <c r="E15">
         <v>0</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>43</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:8">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C16" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -8357,22 +8360,22 @@
       <c r="E16">
         <v>0</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>44</v>
       </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="H16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -8380,22 +8383,22 @@
       <c r="E17">
         <v>0</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>46</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>0.1</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:8">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C18" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -8403,10 +8406,10 @@
       <c r="E18">
         <v>0</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>48</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>3</v>
       </c>
     </row>
@@ -8415,10 +8418,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C19" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -8432,10 +8435,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C20" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -8449,10 +8452,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C21" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -8461,15 +8464,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:8">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C22" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -8477,22 +8480,22 @@
       <c r="E22">
         <v>0</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>59</v>
       </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+      <c r="H22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23">
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C23" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -8500,22 +8503,22 @@
       <c r="E23">
         <v>0</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>61</v>
       </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+      <c r="H23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24">
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C24" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -8523,22 +8526,22 @@
       <c r="E24">
         <v>0</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>64</v>
       </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+      <c r="H24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25">
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C25" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -8546,22 +8549,22 @@
       <c r="E25">
         <v>0</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>13</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>0.05</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:8">
       <c r="A26">
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C26" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -8569,22 +8572,22 @@
       <c r="E26">
         <v>0</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>13</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>0.1</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:8">
       <c r="A27">
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C27" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -8592,22 +8595,22 @@
       <c r="E27">
         <v>0</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <v>13</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <v>0.15</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:8">
       <c r="A28">
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C28" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -8615,22 +8618,22 @@
       <c r="E28">
         <v>0</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>13</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>0.2</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:8">
       <c r="A29">
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C29" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -8638,22 +8641,22 @@
       <c r="E29">
         <v>0</v>
       </c>
-      <c r="F29">
+      <c r="G29">
         <v>13</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>0.25</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:8">
       <c r="A30">
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C30" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -8661,22 +8664,22 @@
       <c r="E30">
         <v>0</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>13</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>0.3</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:8">
       <c r="A31">
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C31" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -8684,22 +8687,22 @@
       <c r="E31">
         <v>0</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <v>13</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>0.35</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:8">
       <c r="A32">
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C32" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -8707,22 +8710,22 @@
       <c r="E32">
         <v>0</v>
       </c>
-      <c r="F32">
+      <c r="G32">
         <v>13</v>
       </c>
-      <c r="G32">
+      <c r="H32">
         <v>0.4</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:8">
       <c r="A33">
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C33" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -8730,22 +8733,22 @@
       <c r="E33">
         <v>0</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>13</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>0.45</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:8">
       <c r="A34">
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C34" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -8753,10 +8756,10 @@
       <c r="E34">
         <v>0</v>
       </c>
-      <c r="F34">
+      <c r="G34">
         <v>13</v>
       </c>
-      <c r="G34">
+      <c r="H34">
         <v>0.5</v>
       </c>
     </row>
@@ -8793,16 +8796,16 @@
         <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8810,13 +8813,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -8830,16 +8833,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>387</v>
+      </c>
+      <c r="C3" t="s">
+        <v>388</v>
+      </c>
+      <c r="D3" t="s">
         <v>386</v>
       </c>
-      <c r="C3" t="s">
-        <v>387</v>
-      </c>
-      <c r="D3" t="s">
-        <v>385</v>
-      </c>
       <c r="F3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" ht="12.95" customHeight="1" spans="1:6">
@@ -8847,16 +8850,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>389</v>
+      </c>
+      <c r="C4" t="s">
         <v>388</v>
       </c>
-      <c r="C4" t="s">
-        <v>387</v>
-      </c>
       <c r="D4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8864,13 +8867,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C5" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D5" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -8884,13 +8887,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -8904,13 +8907,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C7" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D7" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -8924,13 +8927,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C8" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D8" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -8944,13 +8947,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D9" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -8964,13 +8967,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C10" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D10" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -8984,16 +8987,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D11" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F11">
         <v>2</v>

--- a/Assets/StreamingAssets/Configurations/Cards.xlsx
+++ b/Assets/StreamingAssets/Configurations/Cards.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" activeTab="2"/>
+    <workbookView windowWidth="22190" windowHeight="9040"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="407">
   <si>
     <t>ID</t>
   </si>
@@ -740,6 +740,21 @@
     <t>参数+X1，神采+X4，抽一张卡，卡牌使用次数+1</t>
   </si>
   <si>
+    <t>战略规划</t>
+  </si>
+  <si>
+    <t>抽两张牌，下一回合开始时，再抽两张牌，卡牌使用次数+1</t>
+  </si>
+  <si>
+    <t>抽两张牌，卡牌使用次数+1。下一回合开始时，抽两张牌，卡牌使用次数+1</t>
+  </si>
+  <si>
+    <t>专注模式</t>
+  </si>
+  <si>
+    <t>获得一个额外回合，以后，每当使用M卡时，神采+2</t>
+  </si>
+  <si>
     <t>Parameter</t>
   </si>
   <si>
@@ -1082,6 +1097,12 @@
     <t>获得舰长数X%的参数</t>
   </si>
   <si>
+    <t>每当使用M卡时，神采+X</t>
+  </si>
+  <si>
+    <t>每当使用M卡时，神采+2</t>
+  </si>
+  <si>
     <t>BuffType</t>
   </si>
   <si>
@@ -1173,6 +1194,12 @@
   </si>
   <si>
     <t>舰长BUFF10</t>
+  </si>
+  <si>
+    <t>回合开始时，抽两张牌，卡牌使用次数+1</t>
+  </si>
+  <si>
+    <t>以后，每当使用M卡时，神采+2</t>
   </si>
   <si>
     <t>OperatorType</t>
@@ -1607,19 +1634,19 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left/>
+      <right style="thin">
         <color rgb="FFFF0000"/>
-      </left>
-      <right/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
+      <left style="thin">
         <color rgb="FFFF0000"/>
-      </right>
+      </left>
+      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -2212,40 +2239,39 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AJ66"/>
+  <dimension ref="A1:AJ68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
     <col min="2" max="2" width="12.7083333333333" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
     <col min="4" max="4" width="57.7083333333333" customWidth="1"/>
-    <col min="5" max="5" width="10.425" style="2" customWidth="1"/>
+    <col min="5" max="5" width="10.425" style="3" customWidth="1"/>
     <col min="6" max="6" width="4.85833333333333" customWidth="1"/>
     <col min="7" max="7" width="7.85833333333333" customWidth="1"/>
     <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="9" max="9" width="5.56666666666667" style="3" customWidth="1"/>
-    <col min="10" max="10" width="10.5666666666667" customWidth="1"/>
-    <col min="11" max="11" width="10.5666666666667" customWidth="1"/>
-    <col min="12" max="12" width="9.70833333333333" style="3" customWidth="1"/>
+    <col min="9" max="9" width="5.56666666666667" style="2" customWidth="1"/>
+    <col min="10" max="11" width="10.5666666666667" customWidth="1"/>
+    <col min="12" max="12" width="9.70833333333333" style="2" customWidth="1"/>
     <col min="13" max="13" width="7.14166666666667" customWidth="1"/>
-    <col min="14" max="14" width="14" style="3" customWidth="1"/>
+    <col min="14" max="14" width="14" style="2" customWidth="1"/>
     <col min="15" max="15" width="10.2833333333333" customWidth="1"/>
     <col min="16" max="17" width="13.7083333333333" customWidth="1"/>
-    <col min="18" max="18" width="9.70833333333333" style="3" customWidth="1"/>
+    <col min="18" max="18" width="9.70833333333333" style="2" customWidth="1"/>
     <col min="19" max="19" width="9.70833333333333" customWidth="1"/>
     <col min="20" max="20" width="12.1416666666667" customWidth="1"/>
-    <col min="21" max="21" width="17.7083333333333" style="3" customWidth="1"/>
+    <col min="21" max="21" width="17.7083333333333" style="2" customWidth="1"/>
     <col min="22" max="22" width="11" customWidth="1"/>
     <col min="23" max="23" width="12.2833333333333" customWidth="1"/>
-    <col min="24" max="24" width="17.1416666666667" style="3" customWidth="1"/>
-    <col min="27" max="27" width="17.7083333333333" style="3" customWidth="1"/>
+    <col min="24" max="24" width="17.1416666666667" style="2" customWidth="1"/>
+    <col min="27" max="27" width="17.7083333333333" style="2" customWidth="1"/>
     <col min="28" max="28" width="10.7083333333333" customWidth="1"/>
     <col min="29" max="29" width="11" customWidth="1"/>
-    <col min="30" max="30" width="17.7083333333333" style="3" customWidth="1"/>
+    <col min="30" max="30" width="17.7083333333333" style="2" customWidth="1"/>
     <col min="31" max="31" width="12.425" customWidth="1"/>
-    <col min="32" max="32" width="12.425" style="3" customWidth="1"/>
+    <col min="32" max="32" width="12.425" style="2" customWidth="1"/>
     <col min="33" max="33" width="12.2833333333333" customWidth="1"/>
-    <col min="34" max="34" width="9" style="3"/>
+    <col min="34" max="34" width="9" style="2"/>
     <col min="35" max="35" width="4.28333333333333" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2262,7 +2288,7 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -2274,7 +2300,7 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
@@ -2283,13 +2309,13 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
       <c r="O1" t="s">
@@ -2301,55 +2327,55 @@
       <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
       <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="3" t="s">
         <v>21</v>
       </c>
       <c r="W1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="3" t="s">
         <v>24</v>
       </c>
       <c r="Z1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AA1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="3" t="s">
         <v>27</v>
       </c>
       <c r="AC1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AD1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AF1" s="2" t="s">
         <v>31</v>
       </c>
       <c r="AG1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AH1" s="2" t="s">
         <v>33</v>
       </c>
       <c r="AI1" t="s">
@@ -2369,7 +2395,7 @@
       <c r="D2" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F2" t="s">
@@ -2382,10 +2408,10 @@
         <v>41</v>
       </c>
       <c r="L2"/>
-      <c r="M2" s="2">
+      <c r="M2" s="3">
         <v>4</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2" s="2">
         <v>3</v>
       </c>
       <c r="O2">
@@ -2395,13 +2421,13 @@
         <v>0</v>
       </c>
       <c r="R2"/>
-      <c r="S2" s="2">
+      <c r="S2" s="3">
         <v>11</v>
       </c>
       <c r="T2">
         <v>7</v>
       </c>
-      <c r="U2" s="3">
+      <c r="U2" s="2">
         <v>7</v>
       </c>
       <c r="X2"/>
@@ -2424,7 +2450,7 @@
       <c r="D3" t="s">
         <v>44</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F3" t="s">
@@ -2437,10 +2463,10 @@
         <v>41</v>
       </c>
       <c r="L3"/>
-      <c r="M3" s="2">
-        <v>0</v>
-      </c>
-      <c r="N3" s="3">
+      <c r="M3" s="3">
+        <v>0</v>
+      </c>
+      <c r="N3" s="2">
         <v>0</v>
       </c>
       <c r="O3">
@@ -2450,13 +2476,13 @@
         <v>0</v>
       </c>
       <c r="R3"/>
-      <c r="S3" s="2">
+      <c r="S3" s="3">
         <v>2</v>
       </c>
       <c r="T3">
         <v>4</v>
       </c>
-      <c r="U3" s="3">
+      <c r="U3" s="2">
         <v>4</v>
       </c>
       <c r="X3"/>
@@ -2479,7 +2505,7 @@
       <c r="D4" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>49</v>
       </c>
       <c r="F4" t="s">
@@ -2497,7 +2523,7 @@
       <c r="M4">
         <v>5</v>
       </c>
-      <c r="N4" s="3">
+      <c r="N4" s="2">
         <v>4</v>
       </c>
       <c r="O4">
@@ -2506,13 +2532,13 @@
       <c r="P4">
         <v>0</v>
       </c>
-      <c r="S4" s="2">
+      <c r="S4" s="3">
         <v>11</v>
       </c>
       <c r="T4">
         <v>15</v>
       </c>
-      <c r="U4" s="3">
+      <c r="U4" s="2">
         <v>18</v>
       </c>
       <c r="V4">
@@ -2521,7 +2547,7 @@
       <c r="W4">
         <v>9</v>
       </c>
-      <c r="X4" s="3">
+      <c r="X4" s="2">
         <v>12</v>
       </c>
       <c r="AI4" s="6"/>
@@ -2539,7 +2565,7 @@
       <c r="D5" t="s">
         <v>54</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F5" t="s">
@@ -2552,10 +2578,10 @@
         <v>41</v>
       </c>
       <c r="L5"/>
-      <c r="M5" s="2">
+      <c r="M5" s="3">
         <v>3</v>
       </c>
-      <c r="N5" s="3">
+      <c r="N5" s="2">
         <v>3</v>
       </c>
       <c r="O5">
@@ -2565,22 +2591,22 @@
         <v>0</v>
       </c>
       <c r="R5"/>
-      <c r="S5" s="2">
+      <c r="S5" s="3">
         <v>11</v>
       </c>
       <c r="T5">
         <v>5</v>
       </c>
-      <c r="U5" s="3">
+      <c r="U5" s="2">
         <v>5</v>
       </c>
-      <c r="V5" s="2">
+      <c r="V5" s="3">
         <v>2</v>
       </c>
       <c r="W5">
         <v>2</v>
       </c>
-      <c r="X5" s="3">
+      <c r="X5" s="2">
         <v>2</v>
       </c>
       <c r="AA5"/>
@@ -2602,7 +2628,7 @@
       <c r="D6" t="s">
         <v>57</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F6" t="s">
@@ -2617,13 +2643,13 @@
       <c r="K6" t="s">
         <v>59</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="2">
         <v>3</v>
       </c>
       <c r="M6">
         <v>1</v>
       </c>
-      <c r="N6" s="3">
+      <c r="N6" s="2">
         <v>1</v>
       </c>
       <c r="O6">
@@ -2632,7 +2658,7 @@
       <c r="P6">
         <v>1</v>
       </c>
-      <c r="S6" s="2">
+      <c r="S6" s="3">
         <v>0</v>
       </c>
       <c r="V6">
@@ -2641,7 +2667,7 @@
       <c r="W6">
         <v>2</v>
       </c>
-      <c r="X6" s="3">
+      <c r="X6" s="2">
         <v>7</v>
       </c>
       <c r="Y6">
@@ -2650,7 +2676,7 @@
       <c r="Z6">
         <v>1</v>
       </c>
-      <c r="AA6" s="3">
+      <c r="AA6" s="2">
         <v>1</v>
       </c>
       <c r="AI6" s="6"/>
@@ -2668,7 +2694,7 @@
       <c r="D7" t="s">
         <v>62</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F7" t="s">
@@ -2681,10 +2707,10 @@
         <v>41</v>
       </c>
       <c r="L7"/>
-      <c r="M7" s="2">
+      <c r="M7" s="3">
         <v>5</v>
       </c>
-      <c r="N7" s="3">
+      <c r="N7" s="2">
         <v>4</v>
       </c>
       <c r="O7">
@@ -2694,26 +2720,26 @@
         <v>1</v>
       </c>
       <c r="R7"/>
-      <c r="S7" s="2">
+      <c r="S7" s="3">
         <v>4</v>
       </c>
       <c r="U7"/>
-      <c r="V7" s="2">
+      <c r="V7" s="3">
         <v>21</v>
       </c>
       <c r="W7">
         <v>2</v>
       </c>
-      <c r="X7" s="3">
+      <c r="X7" s="2">
         <v>2</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Y7" s="3">
         <v>14</v>
       </c>
       <c r="Z7">
         <v>1</v>
       </c>
-      <c r="AA7" s="3">
+      <c r="AA7" s="2">
         <v>1</v>
       </c>
       <c r="AD7"/>
@@ -2734,7 +2760,7 @@
       <c r="D8" t="s">
         <v>65</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F8" t="s">
@@ -2749,10 +2775,10 @@
       <c r="L8">
         <v>0</v>
       </c>
-      <c r="M8" s="2">
-        <v>1</v>
-      </c>
-      <c r="N8" s="3">
+      <c r="M8" s="3">
+        <v>1</v>
+      </c>
+      <c r="N8" s="2">
         <v>1</v>
       </c>
       <c r="O8">
@@ -2762,31 +2788,31 @@
         <v>1</v>
       </c>
       <c r="R8"/>
-      <c r="S8" s="2">
+      <c r="S8" s="3">
         <v>2</v>
       </c>
       <c r="T8">
         <v>7</v>
       </c>
-      <c r="U8" s="3">
+      <c r="U8" s="2">
         <v>7</v>
       </c>
-      <c r="V8" s="2">
+      <c r="V8" s="3">
         <v>3</v>
       </c>
       <c r="W8">
         <v>1</v>
       </c>
-      <c r="X8" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="2">
+      <c r="X8" s="2">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="3">
         <v>14</v>
       </c>
       <c r="Z8">
         <v>1</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AA8" s="2">
         <v>1</v>
       </c>
       <c r="AD8"/>
@@ -2807,7 +2833,7 @@
       <c r="D9" t="s">
         <v>69</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F9" t="s">
@@ -2820,10 +2846,10 @@
         <v>41</v>
       </c>
       <c r="L9"/>
-      <c r="M9" s="2">
+      <c r="M9" s="3">
         <v>2</v>
       </c>
-      <c r="N9" s="3">
+      <c r="N9" s="2">
         <v>2</v>
       </c>
       <c r="O9">
@@ -2833,22 +2859,22 @@
         <v>0</v>
       </c>
       <c r="R9"/>
-      <c r="S9" s="2">
+      <c r="S9" s="3">
         <v>6</v>
       </c>
       <c r="T9">
         <v>3</v>
       </c>
-      <c r="U9" s="3">
+      <c r="U9" s="2">
         <v>4</v>
       </c>
-      <c r="V9" s="2">
+      <c r="V9" s="3">
         <v>2</v>
       </c>
       <c r="W9">
         <v>3</v>
       </c>
-      <c r="X9" s="3">
+      <c r="X9" s="2">
         <v>4</v>
       </c>
       <c r="AA9"/>
@@ -2870,7 +2896,7 @@
       <c r="D10" t="s">
         <v>72</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F10" t="s">
@@ -2883,10 +2909,10 @@
         <v>41</v>
       </c>
       <c r="L10"/>
-      <c r="M10" s="2">
+      <c r="M10" s="3">
         <v>2</v>
       </c>
-      <c r="N10" s="3">
+      <c r="N10" s="2">
         <v>2</v>
       </c>
       <c r="O10">
@@ -2896,22 +2922,22 @@
         <v>0</v>
       </c>
       <c r="R10"/>
-      <c r="S10" s="2">
+      <c r="S10" s="3">
         <v>7</v>
       </c>
       <c r="T10">
         <v>2</v>
       </c>
-      <c r="U10" s="3">
+      <c r="U10" s="2">
         <v>3</v>
       </c>
-      <c r="V10" s="2">
+      <c r="V10" s="3">
         <v>2</v>
       </c>
       <c r="W10">
         <v>2</v>
       </c>
-      <c r="X10" s="3">
+      <c r="X10" s="2">
         <v>3</v>
       </c>
       <c r="AA10"/>
@@ -2933,7 +2959,7 @@
       <c r="D11" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F11" t="s">
@@ -2951,7 +2977,7 @@
       <c r="M11">
         <v>2</v>
       </c>
-      <c r="N11" s="3">
+      <c r="N11" s="2">
         <v>2</v>
       </c>
       <c r="O11">
@@ -2960,22 +2986,22 @@
       <c r="P11">
         <v>0</v>
       </c>
-      <c r="S11" s="2">
+      <c r="S11" s="3">
         <v>15</v>
       </c>
       <c r="T11">
         <v>2</v>
       </c>
-      <c r="U11" s="3">
+      <c r="U11" s="2">
         <v>3</v>
       </c>
-      <c r="V11" s="2">
+      <c r="V11" s="3">
         <v>2</v>
       </c>
       <c r="W11">
         <v>2</v>
       </c>
-      <c r="X11" s="3">
+      <c r="X11" s="2">
         <v>3</v>
       </c>
       <c r="AI11" s="6"/>
@@ -2993,7 +3019,7 @@
       <c r="D12" t="s">
         <v>78</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="3" t="s">
         <v>49</v>
       </c>
       <c r="F12" t="s">
@@ -3006,10 +3032,10 @@
         <v>41</v>
       </c>
       <c r="L12"/>
-      <c r="M12" s="2">
+      <c r="M12" s="3">
         <v>6</v>
       </c>
-      <c r="N12" s="3">
+      <c r="N12" s="2">
         <v>6</v>
       </c>
       <c r="O12">
@@ -3019,22 +3045,22 @@
         <v>0</v>
       </c>
       <c r="R12"/>
-      <c r="S12" s="2">
+      <c r="S12" s="3">
         <v>11</v>
       </c>
       <c r="T12">
         <v>9</v>
       </c>
-      <c r="U12" s="3">
+      <c r="U12" s="2">
         <v>13</v>
       </c>
-      <c r="V12" s="2">
+      <c r="V12" s="3">
         <v>11</v>
       </c>
       <c r="W12">
         <v>9</v>
       </c>
-      <c r="X12" s="3">
+      <c r="X12" s="2">
         <v>13</v>
       </c>
       <c r="AA12"/>
@@ -3059,7 +3085,7 @@
       <c r="D13" t="s">
         <v>54</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F13" t="s">
@@ -3072,10 +3098,10 @@
         <v>41</v>
       </c>
       <c r="L13"/>
-      <c r="M13" s="2">
+      <c r="M13" s="3">
         <v>5</v>
       </c>
-      <c r="N13" s="3">
+      <c r="N13" s="2">
         <v>5</v>
       </c>
       <c r="O13">
@@ -3085,22 +3111,22 @@
         <v>0</v>
       </c>
       <c r="R13"/>
-      <c r="S13" s="2">
+      <c r="S13" s="3">
         <v>11</v>
       </c>
       <c r="T13">
         <v>11</v>
       </c>
-      <c r="U13" s="3">
+      <c r="U13" s="2">
         <v>15</v>
       </c>
-      <c r="V13" s="2">
+      <c r="V13" s="3">
         <v>2</v>
       </c>
       <c r="W13">
         <v>7</v>
       </c>
-      <c r="X13" s="3">
+      <c r="X13" s="2">
         <v>9</v>
       </c>
       <c r="AA13"/>
@@ -3122,7 +3148,7 @@
       <c r="D14" t="s">
         <v>85</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="3" t="s">
         <v>49</v>
       </c>
       <c r="F14" t="s">
@@ -3135,10 +3161,10 @@
         <v>41</v>
       </c>
       <c r="L14"/>
-      <c r="M14" s="2">
+      <c r="M14" s="3">
         <v>5</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="2">
         <v>4</v>
       </c>
       <c r="O14">
@@ -3148,13 +3174,13 @@
         <v>0</v>
       </c>
       <c r="R14"/>
-      <c r="S14" s="2">
+      <c r="S14" s="3">
         <v>6</v>
       </c>
       <c r="T14">
         <v>6</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="2">
         <v>8</v>
       </c>
       <c r="X14"/>
@@ -3177,7 +3203,7 @@
       <c r="D15" t="s">
         <v>88</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F15" t="s">
@@ -3190,10 +3216,10 @@
         <v>41</v>
       </c>
       <c r="L15"/>
-      <c r="M15" s="2">
+      <c r="M15" s="3">
         <v>4</v>
       </c>
-      <c r="N15" s="3">
+      <c r="N15" s="2">
         <v>4</v>
       </c>
       <c r="O15">
@@ -3203,13 +3229,13 @@
         <v>0</v>
       </c>
       <c r="R15"/>
-      <c r="S15" s="2">
+      <c r="S15" s="3">
         <v>18</v>
       </c>
       <c r="T15">
         <v>1.4</v>
       </c>
-      <c r="U15" s="3">
+      <c r="U15" s="2">
         <v>1.8</v>
       </c>
       <c r="X15"/>
@@ -3232,7 +3258,7 @@
       <c r="D16" t="s">
         <v>91</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F16" t="s">
@@ -3245,10 +3271,10 @@
         <v>41</v>
       </c>
       <c r="L16"/>
-      <c r="M16" s="2">
+      <c r="M16" s="3">
         <v>6</v>
       </c>
-      <c r="N16" s="3">
+      <c r="N16" s="2">
         <v>5</v>
       </c>
       <c r="O16">
@@ -3258,22 +3284,22 @@
         <v>0</v>
       </c>
       <c r="R16"/>
-      <c r="S16" s="2">
+      <c r="S16" s="3">
         <v>6</v>
       </c>
       <c r="T16">
         <v>4</v>
       </c>
-      <c r="U16" s="3">
+      <c r="U16" s="2">
         <v>5</v>
       </c>
-      <c r="V16" s="2">
+      <c r="V16" s="3">
         <v>18</v>
       </c>
       <c r="W16">
         <v>0.8</v>
       </c>
-      <c r="X16" s="3">
+      <c r="X16" s="2">
         <v>1.1</v>
       </c>
       <c r="AA16"/>
@@ -3295,7 +3321,7 @@
       <c r="D17" t="s">
         <v>94</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F17" t="s">
@@ -3304,17 +3330,17 @@
       <c r="G17" t="s">
         <v>40</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="I17" s="2" t="s">
         <v>95</v>
       </c>
       <c r="K17" t="s">
         <v>41</v>
       </c>
       <c r="L17"/>
-      <c r="M17" s="2">
+      <c r="M17" s="3">
         <v>3</v>
       </c>
-      <c r="N17" s="3">
+      <c r="N17" s="2">
         <v>3</v>
       </c>
       <c r="O17">
@@ -3324,31 +3350,31 @@
         <v>1</v>
       </c>
       <c r="R17"/>
-      <c r="S17" s="2">
+      <c r="S17" s="3">
         <v>19</v>
       </c>
       <c r="T17">
         <v>1</v>
       </c>
-      <c r="U17" s="3">
-        <v>1</v>
-      </c>
-      <c r="V17" s="2">
+      <c r="U17" s="2">
+        <v>1</v>
+      </c>
+      <c r="V17" s="3">
         <v>2</v>
       </c>
       <c r="W17">
         <v>4</v>
       </c>
-      <c r="X17" s="3">
+      <c r="X17" s="2">
         <v>6</v>
       </c>
-      <c r="Y17" s="2">
+      <c r="Y17" s="3">
         <v>21</v>
       </c>
       <c r="Z17">
         <v>2</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AA17" s="2">
         <v>3</v>
       </c>
       <c r="AD17"/>
@@ -3369,7 +3395,7 @@
       <c r="D18" t="s">
         <v>98</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F18" t="s">
@@ -3387,7 +3413,7 @@
       <c r="M18">
         <v>4</v>
       </c>
-      <c r="N18" s="3">
+      <c r="N18" s="2">
         <v>3</v>
       </c>
       <c r="O18">
@@ -3396,19 +3422,19 @@
       <c r="P18">
         <v>0</v>
       </c>
-      <c r="S18" s="2">
+      <c r="S18" s="3">
         <v>15</v>
       </c>
       <c r="T18">
         <v>5</v>
       </c>
-      <c r="U18" s="3">
+      <c r="U18" s="2">
         <v>7</v>
       </c>
       <c r="AE18">
         <v>63</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AF18" s="2">
         <v>1.5</v>
       </c>
       <c r="AI18" s="6"/>
@@ -3426,7 +3452,7 @@
       <c r="D19" t="s">
         <v>101</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F19" t="s">
@@ -3439,10 +3465,10 @@
         <v>41</v>
       </c>
       <c r="L19"/>
-      <c r="M19" s="2">
+      <c r="M19" s="3">
         <v>5</v>
       </c>
-      <c r="N19" s="3">
+      <c r="N19" s="2">
         <v>4</v>
       </c>
       <c r="O19">
@@ -3452,22 +3478,22 @@
         <v>1</v>
       </c>
       <c r="R19"/>
-      <c r="S19" s="2">
+      <c r="S19" s="3">
         <v>23</v>
       </c>
       <c r="T19">
         <v>1</v>
       </c>
-      <c r="U19" s="3">
-        <v>1</v>
-      </c>
-      <c r="V19" s="2">
+      <c r="U19" s="2">
+        <v>1</v>
+      </c>
+      <c r="V19" s="3">
         <v>7</v>
       </c>
       <c r="W19">
         <v>1</v>
       </c>
-      <c r="X19" s="3">
+      <c r="X19" s="2">
         <v>2</v>
       </c>
       <c r="AA19"/>
@@ -3489,7 +3515,7 @@
       <c r="D20" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="3" t="s">
         <v>49</v>
       </c>
       <c r="F20" t="s">
@@ -3507,7 +3533,7 @@
       <c r="M20">
         <v>6</v>
       </c>
-      <c r="N20" s="3">
+      <c r="N20" s="2">
         <v>6</v>
       </c>
       <c r="O20">
@@ -3516,22 +3542,22 @@
       <c r="P20">
         <v>0</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="2">
+      <c r="R20" s="2">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>11</v>
       </c>
       <c r="T20">
         <v>24</v>
       </c>
-      <c r="U20" s="3">
+      <c r="U20" s="2">
         <v>30</v>
       </c>
       <c r="AE20">
         <v>62</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AF20" s="2">
         <v>7</v>
       </c>
       <c r="AI20" s="7"/>
@@ -3549,7 +3575,7 @@
       <c r="D21" t="s">
         <v>107</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F21" t="s">
@@ -3567,7 +3593,7 @@
       <c r="M21">
         <v>5</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="2">
         <v>4</v>
       </c>
       <c r="O21">
@@ -3576,22 +3602,22 @@
       <c r="P21">
         <v>1</v>
       </c>
-      <c r="S21" s="2">
+      <c r="S21" s="3">
         <v>26</v>
       </c>
       <c r="T21">
         <v>2</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="2">
         <v>2</v>
       </c>
-      <c r="V21" s="2">
+      <c r="V21" s="3">
         <v>11</v>
       </c>
       <c r="W21">
         <v>30</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="2">
         <v>42</v>
       </c>
       <c r="Y21">
@@ -3600,7 +3626,7 @@
       <c r="Z21">
         <v>5</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="2">
         <v>7</v>
       </c>
       <c r="AI21" s="6"/>
@@ -3618,7 +3644,7 @@
       <c r="D22" t="s">
         <v>110</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F22" t="s">
@@ -3631,10 +3657,10 @@
         <v>41</v>
       </c>
       <c r="L22"/>
-      <c r="M22" s="2">
+      <c r="M22" s="3">
         <v>4</v>
       </c>
-      <c r="N22" s="3">
+      <c r="N22" s="2">
         <v>4</v>
       </c>
       <c r="O22">
@@ -3644,22 +3670,22 @@
         <v>1</v>
       </c>
       <c r="R22"/>
-      <c r="S22" s="2">
+      <c r="S22" s="3">
         <v>6</v>
       </c>
       <c r="T22">
         <v>2</v>
       </c>
-      <c r="U22" s="3">
+      <c r="U22" s="2">
         <v>4</v>
       </c>
-      <c r="V22" s="2">
+      <c r="V22" s="3">
         <v>28</v>
       </c>
       <c r="W22">
         <v>1</v>
       </c>
-      <c r="X22" s="3">
+      <c r="X22" s="2">
         <v>1</v>
       </c>
       <c r="AA22"/>
@@ -3681,7 +3707,7 @@
       <c r="D23" t="s">
         <v>69</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F23" t="s">
@@ -3694,10 +3720,10 @@
         <v>41</v>
       </c>
       <c r="L23"/>
-      <c r="M23" s="2">
-        <v>1</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="M23" s="3">
+        <v>1</v>
+      </c>
+      <c r="N23" s="2">
         <v>1</v>
       </c>
       <c r="O23">
@@ -3707,22 +3733,22 @@
         <v>0</v>
       </c>
       <c r="R23"/>
-      <c r="S23" s="2">
+      <c r="S23" s="3">
         <v>6</v>
       </c>
       <c r="T23">
         <v>5</v>
       </c>
-      <c r="U23" s="3">
+      <c r="U23" s="2">
         <v>7</v>
       </c>
-      <c r="V23" s="2">
+      <c r="V23" s="3">
         <v>2</v>
       </c>
       <c r="W23">
         <v>1</v>
       </c>
-      <c r="X23" s="3">
+      <c r="X23" s="2">
         <v>1</v>
       </c>
       <c r="AA23"/>
@@ -3744,7 +3770,7 @@
       <c r="D24" t="s">
         <v>115</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="3" t="s">
         <v>49</v>
       </c>
       <c r="F24" t="s">
@@ -3762,7 +3788,7 @@
       <c r="M24">
         <v>4</v>
       </c>
-      <c r="N24" s="3">
+      <c r="N24" s="2">
         <v>4</v>
       </c>
       <c r="O24">
@@ -3771,28 +3797,28 @@
       <c r="P24">
         <v>0</v>
       </c>
-      <c r="S24" s="2">
+      <c r="S24" s="3">
         <v>15</v>
       </c>
       <c r="T24">
         <v>3</v>
       </c>
-      <c r="U24" s="3">
+      <c r="U24" s="2">
         <v>4</v>
       </c>
-      <c r="V24" s="2">
+      <c r="V24" s="3">
         <v>11</v>
       </c>
       <c r="W24">
         <v>8</v>
       </c>
-      <c r="X24" s="3">
+      <c r="X24" s="2">
         <v>11</v>
       </c>
       <c r="AE24">
         <v>63</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AF24" s="2">
         <v>3</v>
       </c>
       <c r="AI24" s="6"/>
@@ -3810,7 +3836,7 @@
       <c r="D25" t="s">
         <v>118</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="3" t="s">
         <v>49</v>
       </c>
       <c r="F25" t="s">
@@ -3823,10 +3849,10 @@
         <v>41</v>
       </c>
       <c r="L25"/>
-      <c r="M25" s="2">
+      <c r="M25" s="3">
         <v>3</v>
       </c>
-      <c r="N25" s="3">
+      <c r="N25" s="2">
         <v>2</v>
       </c>
       <c r="O25">
@@ -3836,13 +3862,13 @@
         <v>0</v>
       </c>
       <c r="R25"/>
-      <c r="S25" s="2">
+      <c r="S25" s="3">
         <v>7</v>
       </c>
       <c r="T25">
         <v>3</v>
       </c>
-      <c r="U25" s="3">
+      <c r="U25" s="2">
         <v>5</v>
       </c>
       <c r="X25"/>
@@ -3865,7 +3891,7 @@
       <c r="D26" t="s">
         <v>72</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="3" t="s">
         <v>49</v>
       </c>
       <c r="F26" t="s">
@@ -3878,10 +3904,10 @@
         <v>41</v>
       </c>
       <c r="L26"/>
-      <c r="M26" s="2">
+      <c r="M26" s="3">
         <v>3</v>
       </c>
-      <c r="N26" s="3">
+      <c r="N26" s="2">
         <v>2</v>
       </c>
       <c r="O26">
@@ -3891,22 +3917,22 @@
         <v>0</v>
       </c>
       <c r="R26"/>
-      <c r="S26" s="2">
+      <c r="S26" s="3">
         <v>7</v>
       </c>
       <c r="T26">
         <v>3</v>
       </c>
-      <c r="U26" s="3">
+      <c r="U26" s="2">
         <v>4</v>
       </c>
-      <c r="V26" s="2">
+      <c r="V26" s="3">
         <v>2</v>
       </c>
       <c r="W26">
         <v>4</v>
       </c>
-      <c r="X26" s="3">
+      <c r="X26" s="2">
         <v>6</v>
       </c>
       <c r="AA26"/>
@@ -3928,7 +3954,7 @@
       <c r="D27" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F27" t="s">
@@ -3946,7 +3972,7 @@
       <c r="M27">
         <v>8</v>
       </c>
-      <c r="N27" s="3">
+      <c r="N27" s="2">
         <v>6</v>
       </c>
       <c r="O27">
@@ -3955,25 +3981,25 @@
       <c r="P27">
         <v>1</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
-      <c r="S27" s="2">
+      <c r="R27" s="2">
+        <v>0</v>
+      </c>
+      <c r="S27" s="3">
         <v>11</v>
       </c>
       <c r="T27">
         <v>12</v>
       </c>
-      <c r="U27" s="3">
+      <c r="U27" s="2">
         <v>18</v>
       </c>
-      <c r="V27" s="2">
+      <c r="V27" s="3">
         <v>56</v>
       </c>
       <c r="W27">
         <v>24</v>
       </c>
-      <c r="X27" s="3">
+      <c r="X27" s="2">
         <v>30</v>
       </c>
       <c r="Y27">
@@ -3982,7 +4008,7 @@
       <c r="Z27">
         <v>36</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AA27" s="2">
         <v>44</v>
       </c>
       <c r="AI27" s="7"/>
@@ -4000,7 +4026,7 @@
       <c r="D28" t="s">
         <v>44</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="3" t="s">
         <v>49</v>
       </c>
       <c r="F28" t="s">
@@ -4018,7 +4044,7 @@
       <c r="M28">
         <v>1</v>
       </c>
-      <c r="N28" s="3">
+      <c r="N28" s="2">
         <v>0</v>
       </c>
       <c r="O28">
@@ -4027,19 +4053,19 @@
       <c r="P28">
         <v>0</v>
       </c>
-      <c r="S28" s="2">
+      <c r="S28" s="3">
         <v>2</v>
       </c>
       <c r="T28">
         <v>6</v>
       </c>
-      <c r="U28" s="3">
+      <c r="U28" s="2">
         <v>8</v>
       </c>
       <c r="AE28">
         <v>21</v>
       </c>
-      <c r="AF28" s="3">
+      <c r="AF28" s="2">
         <v>12</v>
       </c>
       <c r="AI28" s="6"/>
@@ -4057,7 +4083,7 @@
       <c r="D29" t="s">
         <v>129</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F29" t="s">
@@ -4066,17 +4092,17 @@
       <c r="G29" t="s">
         <v>40</v>
       </c>
-      <c r="I29" s="3" t="s">
+      <c r="I29" s="2" t="s">
         <v>95</v>
       </c>
       <c r="K29" t="s">
         <v>41</v>
       </c>
       <c r="L29"/>
-      <c r="M29" s="2">
+      <c r="M29" s="3">
         <v>5</v>
       </c>
-      <c r="N29" s="3">
+      <c r="N29" s="2">
         <v>5</v>
       </c>
       <c r="O29">
@@ -4086,31 +4112,31 @@
         <v>1</v>
       </c>
       <c r="R29"/>
-      <c r="S29" s="2">
+      <c r="S29" s="3">
         <v>32</v>
       </c>
       <c r="T29">
         <v>30</v>
       </c>
-      <c r="U29" s="3">
+      <c r="U29" s="2">
         <v>30</v>
       </c>
-      <c r="V29" s="2">
+      <c r="V29" s="3">
         <v>2</v>
       </c>
       <c r="W29">
         <v>3</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="2">
         <v>5</v>
       </c>
-      <c r="Y29" s="2">
+      <c r="Y29" s="3">
         <v>21</v>
       </c>
       <c r="Z29">
         <v>2</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="2">
         <v>3</v>
       </c>
       <c r="AD29"/>
@@ -4131,7 +4157,7 @@
       <c r="D30" t="s">
         <v>132</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F30" t="s">
@@ -4140,17 +4166,17 @@
       <c r="G30" t="s">
         <v>40</v>
       </c>
-      <c r="I30" s="3" t="s">
+      <c r="I30" s="2" t="s">
         <v>95</v>
       </c>
       <c r="K30" t="s">
         <v>41</v>
       </c>
       <c r="L30"/>
-      <c r="M30" s="2">
+      <c r="M30" s="3">
         <v>4</v>
       </c>
-      <c r="N30" s="3">
+      <c r="N30" s="2">
         <v>4</v>
       </c>
       <c r="O30">
@@ -4160,22 +4186,22 @@
         <v>1</v>
       </c>
       <c r="R30"/>
-      <c r="S30" s="2">
+      <c r="S30" s="3">
         <v>33</v>
       </c>
       <c r="T30">
         <v>50</v>
       </c>
-      <c r="U30" s="3">
+      <c r="U30" s="2">
         <v>70</v>
       </c>
-      <c r="V30" s="2">
+      <c r="V30" s="3">
         <v>2</v>
       </c>
       <c r="W30">
         <v>2</v>
       </c>
-      <c r="X30" s="3">
+      <c r="X30" s="2">
         <v>4</v>
       </c>
       <c r="AA30"/>
@@ -4197,7 +4223,7 @@
       <c r="D31" t="s">
         <v>135</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F31" t="s">
@@ -4206,17 +4232,17 @@
       <c r="G31" t="s">
         <v>40</v>
       </c>
-      <c r="I31" s="3" t="s">
+      <c r="I31" s="2" t="s">
         <v>95</v>
       </c>
       <c r="K31" t="s">
         <v>41</v>
       </c>
       <c r="L31"/>
-      <c r="M31" s="2">
+      <c r="M31" s="3">
         <v>4</v>
       </c>
-      <c r="N31" s="3">
+      <c r="N31" s="2">
         <v>3</v>
       </c>
       <c r="O31">
@@ -4226,22 +4252,22 @@
         <v>1</v>
       </c>
       <c r="R31"/>
-      <c r="S31" s="2">
+      <c r="S31" s="3">
         <v>33</v>
       </c>
       <c r="T31">
         <v>20</v>
       </c>
-      <c r="U31" s="3">
+      <c r="U31" s="2">
         <v>30</v>
       </c>
-      <c r="V31" s="2">
+      <c r="V31" s="3">
         <v>35</v>
       </c>
       <c r="W31">
         <v>1</v>
       </c>
-      <c r="X31" s="3">
+      <c r="X31" s="2">
         <v>1</v>
       </c>
       <c r="AA31"/>
@@ -4263,7 +4289,7 @@
       <c r="D32" t="s">
         <v>137</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F32" t="s">
@@ -4272,17 +4298,17 @@
       <c r="G32" t="s">
         <v>40</v>
       </c>
-      <c r="I32" s="3" t="s">
+      <c r="I32" s="2" t="s">
         <v>95</v>
       </c>
       <c r="K32" t="s">
         <v>41</v>
       </c>
       <c r="L32"/>
-      <c r="M32" s="2">
+      <c r="M32" s="3">
         <v>7</v>
       </c>
-      <c r="N32" s="3">
+      <c r="N32" s="2">
         <v>6</v>
       </c>
       <c r="O32">
@@ -4312,7 +4338,7 @@
       <c r="D33" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F33" t="s">
@@ -4330,7 +4356,7 @@
       <c r="M33">
         <v>8</v>
       </c>
-      <c r="N33" s="3">
+      <c r="N33" s="2">
         <v>7</v>
       </c>
       <c r="O33">
@@ -4339,19 +4365,19 @@
       <c r="P33">
         <v>1</v>
       </c>
-      <c r="S33" s="2">
+      <c r="S33" s="3">
         <v>11</v>
       </c>
       <c r="T33">
         <v>38</v>
       </c>
-      <c r="U33" s="3">
+      <c r="U33" s="2">
         <v>52</v>
       </c>
       <c r="AE33">
         <v>64</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AF33" s="2">
         <v>1</v>
       </c>
     </row>
@@ -4368,7 +4394,7 @@
       <c r="D34" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E34" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F34" t="s">
@@ -4386,7 +4412,7 @@
       <c r="M34">
         <v>3</v>
       </c>
-      <c r="N34" s="3">
+      <c r="N34" s="2">
         <v>3</v>
       </c>
       <c r="O34">
@@ -4395,16 +4421,16 @@
       <c r="P34">
         <v>0</v>
       </c>
-      <c r="R34" s="3">
-        <v>0</v>
-      </c>
-      <c r="S34" s="2">
+      <c r="R34" s="2">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
         <v>15</v>
       </c>
       <c r="T34">
         <v>3</v>
       </c>
-      <c r="U34" s="3">
+      <c r="U34" s="2">
         <v>4</v>
       </c>
     </row>
@@ -4421,7 +4447,7 @@
       <c r="D35" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E35" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F35" t="s">
@@ -4439,7 +4465,7 @@
       <c r="M35">
         <v>3</v>
       </c>
-      <c r="N35" s="3">
+      <c r="N35" s="2">
         <v>3</v>
       </c>
       <c r="O35">
@@ -4448,13 +4474,13 @@
       <c r="P35">
         <v>0</v>
       </c>
-      <c r="S35" s="2">
+      <c r="S35" s="3">
         <v>11</v>
       </c>
       <c r="T35">
         <v>18</v>
       </c>
-      <c r="U35" s="3">
+      <c r="U35" s="2">
         <v>22</v>
       </c>
     </row>
@@ -4471,7 +4497,7 @@
       <c r="D36" t="s">
         <v>75</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E36" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F36" t="s">
@@ -4489,7 +4515,7 @@
       <c r="M36">
         <v>3</v>
       </c>
-      <c r="N36" s="3">
+      <c r="N36" s="2">
         <v>3</v>
       </c>
       <c r="O36">
@@ -4498,22 +4524,22 @@
       <c r="P36">
         <v>0</v>
       </c>
-      <c r="S36" s="2">
+      <c r="S36" s="3">
         <v>15</v>
       </c>
       <c r="T36">
         <v>3</v>
       </c>
-      <c r="U36" s="3">
+      <c r="U36" s="2">
         <v>4</v>
       </c>
-      <c r="V36" s="2">
+      <c r="V36" s="3">
         <v>2</v>
       </c>
       <c r="W36">
         <v>6</v>
       </c>
-      <c r="X36" s="3">
+      <c r="X36" s="2">
         <v>8</v>
       </c>
     </row>
@@ -4530,7 +4556,7 @@
       <c r="D37" t="s">
         <v>72</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E37" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F37" t="s">
@@ -4543,10 +4569,10 @@
         <v>41</v>
       </c>
       <c r="L37"/>
-      <c r="M37" s="2">
+      <c r="M37" s="3">
         <v>3</v>
       </c>
-      <c r="N37" s="3">
+      <c r="N37" s="2">
         <v>3</v>
       </c>
       <c r="O37">
@@ -4556,22 +4582,22 @@
         <v>0</v>
       </c>
       <c r="R37"/>
-      <c r="S37" s="2">
+      <c r="S37" s="3">
         <v>7</v>
       </c>
       <c r="T37">
         <v>3</v>
       </c>
-      <c r="U37" s="3">
+      <c r="U37" s="2">
         <v>4</v>
       </c>
-      <c r="V37" s="2">
+      <c r="V37" s="3">
         <v>2</v>
       </c>
       <c r="W37">
         <v>6</v>
       </c>
-      <c r="X37" s="3">
+      <c r="X37" s="2">
         <v>8</v>
       </c>
       <c r="AA37"/>
@@ -4592,7 +4618,7 @@
       <c r="D38" t="s">
         <v>152</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E38" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F38" t="s">
@@ -4605,10 +4631,10 @@
         <v>41</v>
       </c>
       <c r="L38"/>
-      <c r="M38" s="2">
-        <v>1</v>
-      </c>
-      <c r="N38" s="3">
+      <c r="M38" s="3">
+        <v>1</v>
+      </c>
+      <c r="N38" s="2">
         <v>1</v>
       </c>
       <c r="O38">
@@ -4618,22 +4644,22 @@
         <v>1</v>
       </c>
       <c r="R38"/>
-      <c r="S38" s="2">
+      <c r="S38" s="3">
         <v>21</v>
       </c>
       <c r="T38">
         <v>4</v>
       </c>
-      <c r="U38" s="3">
+      <c r="U38" s="2">
         <v>5</v>
       </c>
-      <c r="V38" s="2">
+      <c r="V38" s="3">
         <v>2</v>
       </c>
       <c r="W38">
         <v>3</v>
       </c>
-      <c r="X38" s="3">
+      <c r="X38" s="2">
         <v>5</v>
       </c>
       <c r="AA38"/>
@@ -4654,7 +4680,7 @@
       <c r="D39" t="s">
         <v>155</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="E39" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F39" t="s">
@@ -4667,10 +4693,10 @@
         <v>41</v>
       </c>
       <c r="L39"/>
-      <c r="M39" s="2">
-        <v>1</v>
-      </c>
-      <c r="N39" s="3">
+      <c r="M39" s="3">
+        <v>1</v>
+      </c>
+      <c r="N39" s="2">
         <v>1</v>
       </c>
       <c r="O39">
@@ -4680,22 +4706,22 @@
         <v>1</v>
       </c>
       <c r="R39"/>
-      <c r="S39" s="2">
+      <c r="S39" s="3">
         <v>5</v>
       </c>
       <c r="T39">
         <v>1</v>
       </c>
-      <c r="U39" s="3">
+      <c r="U39" s="2">
         <v>2</v>
       </c>
-      <c r="V39" s="2">
+      <c r="V39" s="3">
         <v>2</v>
       </c>
       <c r="W39">
         <v>6</v>
       </c>
-      <c r="X39" s="3">
+      <c r="X39" s="2">
         <v>7</v>
       </c>
       <c r="AA39"/>
@@ -4716,7 +4742,7 @@
       <c r="D40" t="s">
         <v>158</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="E40" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F40" t="s">
@@ -4729,10 +4755,10 @@
         <v>41</v>
       </c>
       <c r="L40"/>
-      <c r="M40" s="2">
+      <c r="M40" s="3">
         <v>4</v>
       </c>
-      <c r="N40" s="3">
+      <c r="N40" s="2">
         <v>3</v>
       </c>
       <c r="O40">
@@ -4742,22 +4768,22 @@
         <v>1</v>
       </c>
       <c r="R40"/>
-      <c r="S40" s="2">
+      <c r="S40" s="3">
         <v>7</v>
       </c>
       <c r="T40">
         <v>4</v>
       </c>
-      <c r="U40" s="3">
+      <c r="U40" s="2">
         <v>5</v>
       </c>
-      <c r="V40" s="2">
+      <c r="V40" s="3">
         <v>38</v>
       </c>
       <c r="W40">
         <v>4</v>
       </c>
-      <c r="X40" s="3">
+      <c r="X40" s="2">
         <v>5</v>
       </c>
       <c r="AA40"/>
@@ -4778,7 +4804,7 @@
       <c r="D41" t="s">
         <v>161</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="E41" s="3" t="s">
         <v>49</v>
       </c>
       <c r="F41" t="s">
@@ -4791,10 +4817,10 @@
         <v>41</v>
       </c>
       <c r="L41"/>
-      <c r="M41" s="2">
+      <c r="M41" s="3">
         <v>2</v>
       </c>
-      <c r="N41" s="3">
+      <c r="N41" s="2">
         <v>2</v>
       </c>
       <c r="O41">
@@ -4804,22 +4830,22 @@
         <v>0</v>
       </c>
       <c r="R41"/>
-      <c r="S41" s="2">
+      <c r="S41" s="3">
         <v>6</v>
       </c>
       <c r="T41">
         <v>3</v>
       </c>
-      <c r="U41" s="3">
+      <c r="U41" s="2">
         <v>3</v>
       </c>
-      <c r="V41" s="2">
+      <c r="V41" s="3">
         <v>39</v>
       </c>
       <c r="W41">
         <v>2</v>
       </c>
-      <c r="X41" s="3">
+      <c r="X41" s="2">
         <v>3</v>
       </c>
       <c r="AA41"/>
@@ -4840,7 +4866,7 @@
       <c r="D42" t="s">
         <v>164</v>
       </c>
-      <c r="E42" s="2" t="s">
+      <c r="E42" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F42" t="s">
@@ -4853,10 +4879,10 @@
         <v>41</v>
       </c>
       <c r="L42"/>
-      <c r="M42" s="2">
+      <c r="M42" s="3">
         <v>4</v>
       </c>
-      <c r="N42" s="3">
+      <c r="N42" s="2">
         <v>3</v>
       </c>
       <c r="O42">
@@ -4866,22 +4892,22 @@
         <v>1</v>
       </c>
       <c r="R42"/>
-      <c r="S42" s="2">
+      <c r="S42" s="3">
         <v>7</v>
       </c>
       <c r="T42">
         <v>1</v>
       </c>
-      <c r="U42" s="3">
+      <c r="U42" s="2">
         <v>3</v>
       </c>
-      <c r="V42" s="2">
+      <c r="V42" s="3">
         <v>41</v>
       </c>
       <c r="W42">
         <v>1</v>
       </c>
-      <c r="X42" s="3">
+      <c r="X42" s="2">
         <v>1</v>
       </c>
       <c r="AA42"/>
@@ -4902,7 +4928,7 @@
       <c r="D43" t="s">
         <v>167</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="E43" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F43" t="s">
@@ -4915,10 +4941,10 @@
         <v>41</v>
       </c>
       <c r="L43"/>
-      <c r="M43" s="2">
+      <c r="M43" s="3">
         <v>7</v>
       </c>
-      <c r="N43" s="3">
+      <c r="N43" s="2">
         <v>4</v>
       </c>
       <c r="O43">
@@ -4928,31 +4954,31 @@
         <v>1</v>
       </c>
       <c r="R43"/>
-      <c r="S43" s="2">
+      <c r="S43" s="3">
         <v>6</v>
       </c>
       <c r="T43">
         <v>5</v>
       </c>
-      <c r="U43" s="3">
+      <c r="U43" s="2">
         <v>5</v>
       </c>
-      <c r="V43" s="2">
+      <c r="V43" s="3">
         <v>14</v>
       </c>
       <c r="W43">
         <v>1</v>
       </c>
-      <c r="X43" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y43" s="2">
+      <c r="X43" s="2">
+        <v>1</v>
+      </c>
+      <c r="Y43" s="3">
         <v>18</v>
       </c>
       <c r="Z43">
         <v>0.9</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AA43" s="2">
         <v>1.2</v>
       </c>
       <c r="AD43"/>
@@ -4972,7 +4998,7 @@
       <c r="D44" t="s">
         <v>170</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="E44" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F44" t="s">
@@ -4990,7 +5016,7 @@
       <c r="M44">
         <v>6</v>
       </c>
-      <c r="N44" s="3">
+      <c r="N44" s="2">
         <v>4</v>
       </c>
       <c r="O44">
@@ -4999,22 +5025,22 @@
       <c r="P44">
         <v>1</v>
       </c>
-      <c r="S44" s="2">
+      <c r="S44" s="3">
         <v>15</v>
       </c>
       <c r="T44">
         <v>2</v>
       </c>
-      <c r="U44" s="3">
+      <c r="U44" s="2">
         <v>2</v>
       </c>
-      <c r="V44" s="2">
+      <c r="V44" s="3">
         <v>42</v>
       </c>
       <c r="W44">
         <v>8</v>
       </c>
-      <c r="X44" s="3">
+      <c r="X44" s="2">
         <v>12</v>
       </c>
     </row>
@@ -5031,7 +5057,7 @@
       <c r="D45" t="s">
         <v>173</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="E45" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F45" t="s">
@@ -5044,10 +5070,10 @@
         <v>41</v>
       </c>
       <c r="L45"/>
-      <c r="M45" s="2">
+      <c r="M45" s="3">
         <v>5</v>
       </c>
-      <c r="N45" s="3">
+      <c r="N45" s="2">
         <v>4</v>
       </c>
       <c r="O45">
@@ -5057,31 +5083,31 @@
         <v>1</v>
       </c>
       <c r="R45"/>
-      <c r="S45" s="2">
+      <c r="S45" s="3">
         <v>7</v>
       </c>
       <c r="T45">
         <v>7</v>
       </c>
-      <c r="U45" s="3">
+      <c r="U45" s="2">
         <v>9</v>
       </c>
-      <c r="V45" s="2">
+      <c r="V45" s="3">
         <v>26</v>
       </c>
       <c r="W45">
         <v>2</v>
       </c>
-      <c r="X45" s="3">
+      <c r="X45" s="2">
         <v>2</v>
       </c>
-      <c r="Y45" s="2">
+      <c r="Y45" s="3">
         <v>2</v>
       </c>
       <c r="Z45">
         <v>7</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AA45" s="2">
         <v>8</v>
       </c>
       <c r="AD45"/>
@@ -5101,7 +5127,7 @@
       <c r="D46" t="s">
         <v>176</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="E46" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F46" t="s">
@@ -5110,17 +5136,17 @@
       <c r="G46" t="s">
         <v>40</v>
       </c>
-      <c r="I46" s="3" t="s">
+      <c r="I46" s="2" t="s">
         <v>95</v>
       </c>
       <c r="K46" t="s">
         <v>41</v>
       </c>
       <c r="L46"/>
-      <c r="M46" s="2">
+      <c r="M46" s="3">
         <v>10</v>
       </c>
-      <c r="N46" s="3">
+      <c r="N46" s="2">
         <v>6</v>
       </c>
       <c r="O46">
@@ -5130,31 +5156,31 @@
         <v>1</v>
       </c>
       <c r="R46"/>
-      <c r="S46" s="2">
+      <c r="S46" s="3">
         <v>32</v>
       </c>
       <c r="T46">
         <v>40</v>
       </c>
-      <c r="U46" s="3">
+      <c r="U46" s="2">
         <v>40</v>
       </c>
-      <c r="V46" s="2">
+      <c r="V46" s="3">
         <v>33</v>
       </c>
       <c r="W46">
         <v>30</v>
       </c>
-      <c r="X46" s="3">
+      <c r="X46" s="2">
         <v>30</v>
       </c>
-      <c r="Y46" s="2">
+      <c r="Y46" s="3">
         <v>19</v>
       </c>
       <c r="Z46">
         <v>1</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AA46" s="2">
         <v>1</v>
       </c>
       <c r="AD46"/>
@@ -5174,7 +5200,7 @@
       <c r="D47" t="s">
         <v>179</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="E47" s="3" t="s">
         <v>49</v>
       </c>
       <c r="F47" t="s">
@@ -5187,10 +5213,10 @@
         <v>41</v>
       </c>
       <c r="L47"/>
-      <c r="M47" s="2">
+      <c r="M47" s="3">
         <v>2</v>
       </c>
-      <c r="N47" s="3">
+      <c r="N47" s="2">
         <v>1</v>
       </c>
       <c r="O47">
@@ -5200,13 +5226,13 @@
         <v>0</v>
       </c>
       <c r="R47"/>
-      <c r="S47" s="2">
+      <c r="S47" s="3">
         <v>11</v>
       </c>
       <c r="T47">
         <v>10</v>
       </c>
-      <c r="U47" s="3">
+      <c r="U47" s="2">
         <v>14</v>
       </c>
       <c r="X47"/>
@@ -5228,7 +5254,7 @@
       <c r="D48" t="s">
         <v>181</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="E48" s="3" t="s">
         <v>49</v>
       </c>
       <c r="F48" t="s">
@@ -5241,10 +5267,10 @@
         <v>41</v>
       </c>
       <c r="L48"/>
-      <c r="M48" s="2">
+      <c r="M48" s="3">
         <v>4</v>
       </c>
-      <c r="N48" s="3">
+      <c r="N48" s="2">
         <v>3</v>
       </c>
       <c r="O48">
@@ -5254,22 +5280,22 @@
         <v>0</v>
       </c>
       <c r="R48"/>
-      <c r="S48" s="2">
+      <c r="S48" s="3">
         <v>11</v>
       </c>
       <c r="T48">
         <v>8</v>
       </c>
-      <c r="U48" s="3">
+      <c r="U48" s="2">
         <v>11</v>
       </c>
-      <c r="V48" s="2">
+      <c r="V48" s="3">
         <v>6</v>
       </c>
       <c r="W48">
         <v>3</v>
       </c>
-      <c r="X48" s="3">
+      <c r="X48" s="2">
         <v>3</v>
       </c>
       <c r="AA48"/>
@@ -5290,7 +5316,7 @@
       <c r="D49" t="s">
         <v>184</v>
       </c>
-      <c r="E49" s="2" t="s">
+      <c r="E49" s="3" t="s">
         <v>49</v>
       </c>
       <c r="F49" t="s">
@@ -5308,7 +5334,7 @@
       <c r="M49">
         <v>4</v>
       </c>
-      <c r="N49" s="3">
+      <c r="N49" s="2">
         <v>3</v>
       </c>
       <c r="O49">
@@ -5317,22 +5343,22 @@
       <c r="P49">
         <v>0</v>
       </c>
-      <c r="S49" s="2">
+      <c r="S49" s="3">
         <v>11</v>
       </c>
       <c r="T49">
         <v>7</v>
       </c>
-      <c r="U49" s="3">
+      <c r="U49" s="2">
         <v>11</v>
       </c>
-      <c r="V49" s="2">
+      <c r="V49" s="3">
         <v>45</v>
       </c>
       <c r="W49">
         <v>2</v>
       </c>
-      <c r="X49" s="3">
+      <c r="X49" s="2">
         <v>3</v>
       </c>
     </row>
@@ -5349,7 +5375,7 @@
       <c r="D50" t="s">
         <v>187</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="E50" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F50" t="s">
@@ -5362,10 +5388,10 @@
         <v>41</v>
       </c>
       <c r="L50"/>
-      <c r="M50" s="2">
+      <c r="M50" s="3">
         <v>5</v>
       </c>
-      <c r="N50" s="3">
+      <c r="N50" s="2">
         <v>4</v>
       </c>
       <c r="O50">
@@ -5375,22 +5401,22 @@
         <v>1</v>
       </c>
       <c r="R50"/>
-      <c r="S50" s="2">
+      <c r="S50" s="3">
         <v>6</v>
       </c>
       <c r="T50">
         <v>5</v>
       </c>
-      <c r="U50" s="3">
+      <c r="U50" s="2">
         <v>7</v>
       </c>
-      <c r="V50" s="2">
+      <c r="V50" s="3">
         <v>18</v>
       </c>
       <c r="W50">
         <v>1.1</v>
       </c>
-      <c r="X50" s="3">
+      <c r="X50" s="2">
         <v>1.7</v>
       </c>
       <c r="AA50"/>
@@ -5411,7 +5437,7 @@
       <c r="D51" t="s">
         <v>190</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="E51" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F51" t="s">
@@ -5424,10 +5450,10 @@
         <v>41</v>
       </c>
       <c r="L51"/>
-      <c r="M51" s="2">
+      <c r="M51" s="3">
         <v>9</v>
       </c>
-      <c r="N51" s="3">
+      <c r="N51" s="2">
         <v>6</v>
       </c>
       <c r="O51">
@@ -5437,22 +5463,22 @@
         <v>1</v>
       </c>
       <c r="R51"/>
-      <c r="S51" s="2">
+      <c r="S51" s="3">
         <v>6</v>
       </c>
       <c r="T51">
         <v>1</v>
       </c>
-      <c r="U51" s="3">
+      <c r="U51" s="2">
         <v>3</v>
       </c>
-      <c r="V51" s="2">
+      <c r="V51" s="3">
         <v>49</v>
       </c>
       <c r="W51">
         <v>1</v>
       </c>
-      <c r="X51" s="3">
+      <c r="X51" s="2">
         <v>1</v>
       </c>
       <c r="AA51"/>
@@ -5473,7 +5499,7 @@
       <c r="D52" t="s">
         <v>193</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="E52" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F52" t="s">
@@ -5486,10 +5512,10 @@
         <v>41</v>
       </c>
       <c r="L52"/>
-      <c r="M52" s="2">
-        <v>1</v>
-      </c>
-      <c r="N52" s="3">
+      <c r="M52" s="3">
+        <v>1</v>
+      </c>
+      <c r="N52" s="2">
         <v>0</v>
       </c>
       <c r="O52">
@@ -5499,22 +5525,22 @@
         <v>1</v>
       </c>
       <c r="R52"/>
-      <c r="S52" s="2">
+      <c r="S52" s="3">
         <v>9</v>
       </c>
       <c r="T52">
         <v>2</v>
       </c>
-      <c r="U52" s="3">
+      <c r="U52" s="2">
         <v>2</v>
       </c>
-      <c r="V52" s="2">
+      <c r="V52" s="3">
         <v>21</v>
       </c>
       <c r="W52">
         <v>2</v>
       </c>
-      <c r="X52" s="3">
+      <c r="X52" s="2">
         <v>2</v>
       </c>
       <c r="AA52"/>
@@ -5535,7 +5561,7 @@
       <c r="D53" t="s">
         <v>196</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="E53" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F53" t="s">
@@ -5553,7 +5579,7 @@
       <c r="M53">
         <v>5</v>
       </c>
-      <c r="N53" s="3">
+      <c r="N53" s="2">
         <v>5</v>
       </c>
       <c r="O53">
@@ -5562,7 +5588,7 @@
       <c r="P53">
         <v>1</v>
       </c>
-      <c r="R53" s="3">
+      <c r="R53" s="2">
         <v>6</v>
       </c>
       <c r="S53">
@@ -5571,7 +5597,7 @@
       <c r="T53">
         <v>3</v>
       </c>
-      <c r="U53" s="3">
+      <c r="U53" s="2">
         <v>4</v>
       </c>
       <c r="V53">
@@ -5580,7 +5606,7 @@
       <c r="W53">
         <v>-0.5</v>
       </c>
-      <c r="X53" s="3">
+      <c r="X53" s="2">
         <v>-0.5</v>
       </c>
     </row>
@@ -5597,7 +5623,7 @@
       <c r="D54" t="s">
         <v>199</v>
       </c>
-      <c r="E54" s="2" t="s">
+      <c r="E54" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F54" t="s">
@@ -5612,13 +5638,13 @@
       <c r="K54" t="s">
         <v>59</v>
       </c>
-      <c r="L54" s="3">
+      <c r="L54" s="2">
         <v>14</v>
       </c>
       <c r="M54">
         <v>2</v>
       </c>
-      <c r="N54" s="3">
+      <c r="N54" s="2">
         <v>1</v>
       </c>
       <c r="O54">
@@ -5633,7 +5659,7 @@
       <c r="T54">
         <v>3</v>
       </c>
-      <c r="U54" s="3">
+      <c r="U54" s="2">
         <v>4</v>
       </c>
       <c r="V54">
@@ -5642,7 +5668,7 @@
       <c r="W54">
         <v>1</v>
       </c>
-      <c r="X54" s="3">
+      <c r="X54" s="2">
         <v>1</v>
       </c>
       <c r="Y54">
@@ -5651,7 +5677,7 @@
       <c r="Z54">
         <v>3</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AA54" s="2">
         <v>5</v>
       </c>
     </row>
@@ -5668,7 +5694,7 @@
       <c r="D55" t="s">
         <v>202</v>
       </c>
-      <c r="E55" s="2" t="s">
+      <c r="E55" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F55" t="s">
@@ -5686,7 +5712,7 @@
       <c r="M55">
         <v>4</v>
       </c>
-      <c r="N55" s="3">
+      <c r="N55" s="2">
         <v>3</v>
       </c>
       <c r="O55">
@@ -5701,7 +5727,7 @@
       <c r="T55">
         <v>1</v>
       </c>
-      <c r="U55" s="3">
+      <c r="U55" s="2">
         <v>3</v>
       </c>
       <c r="V55">
@@ -5710,10 +5736,10 @@
       <c r="W55">
         <v>1</v>
       </c>
-      <c r="X55" s="3">
-        <v>1</v>
-      </c>
-      <c r="AG55" s="3"/>
+      <c r="X55" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG55" s="2"/>
     </row>
     <row r="56" spans="1:33">
       <c r="A56">
@@ -5728,7 +5754,7 @@
       <c r="D56" t="s">
         <v>205</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="E56" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F56" t="s">
@@ -5743,13 +5769,13 @@
       <c r="K56" t="s">
         <v>59</v>
       </c>
-      <c r="L56" s="3">
+      <c r="L56" s="2">
         <v>3</v>
       </c>
       <c r="M56">
         <v>2</v>
       </c>
-      <c r="N56" s="3">
+      <c r="N56" s="2">
         <v>1</v>
       </c>
       <c r="O56">
@@ -5764,7 +5790,7 @@
       <c r="T56">
         <v>3</v>
       </c>
-      <c r="U56" s="3">
+      <c r="U56" s="2">
         <v>4</v>
       </c>
       <c r="V56">
@@ -5773,7 +5799,7 @@
       <c r="W56">
         <v>12</v>
       </c>
-      <c r="X56" s="3">
+      <c r="X56" s="2">
         <v>18</v>
       </c>
       <c r="Y56">
@@ -5782,10 +5808,10 @@
       <c r="Z56">
         <v>1</v>
       </c>
-      <c r="AA56" s="3">
-        <v>1</v>
-      </c>
-      <c r="AG56" s="3"/>
+      <c r="AA56" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG56" s="2"/>
     </row>
     <row r="57" spans="1:27">
       <c r="A57">
@@ -5800,7 +5826,7 @@
       <c r="D57" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="E57" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F57" t="s">
@@ -5815,13 +5841,13 @@
       <c r="K57" t="s">
         <v>59</v>
       </c>
-      <c r="L57" s="3">
+      <c r="L57" s="2">
         <v>3</v>
       </c>
       <c r="M57">
         <v>2</v>
       </c>
-      <c r="N57" s="3">
+      <c r="N57" s="2">
         <v>1</v>
       </c>
       <c r="O57">
@@ -5836,7 +5862,7 @@
       <c r="T57">
         <v>5</v>
       </c>
-      <c r="U57" s="3">
+      <c r="U57" s="2">
         <v>6</v>
       </c>
       <c r="V57">
@@ -5845,7 +5871,7 @@
       <c r="W57">
         <v>5</v>
       </c>
-      <c r="X57" s="3">
+      <c r="X57" s="2">
         <v>6</v>
       </c>
       <c r="Y57">
@@ -5854,7 +5880,7 @@
       <c r="Z57">
         <v>0.6</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AA57" s="2">
         <v>1.2</v>
       </c>
     </row>
@@ -5871,7 +5897,7 @@
       <c r="D58" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="E58" s="2" t="s">
+      <c r="E58" s="3" t="s">
         <v>49</v>
       </c>
       <c r="F58" t="s">
@@ -5889,7 +5915,7 @@
       <c r="M58">
         <v>3</v>
       </c>
-      <c r="N58" s="3">
+      <c r="N58" s="2">
         <v>2</v>
       </c>
       <c r="O58">
@@ -5904,7 +5930,7 @@
       <c r="T58">
         <v>1.2</v>
       </c>
-      <c r="U58" s="3">
+      <c r="U58" s="2">
         <v>1.7</v>
       </c>
     </row>
@@ -5921,7 +5947,7 @@
       <c r="D59" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E59" s="2" t="s">
+      <c r="E59" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F59" t="s">
@@ -5939,7 +5965,7 @@
       <c r="M59">
         <v>3</v>
       </c>
-      <c r="N59" s="3">
+      <c r="N59" s="2">
         <v>3</v>
       </c>
       <c r="O59">
@@ -5954,7 +5980,7 @@
       <c r="T59">
         <v>7</v>
       </c>
-      <c r="U59" s="3">
+      <c r="U59" s="2">
         <v>9</v>
       </c>
       <c r="V59">
@@ -5963,7 +5989,7 @@
       <c r="W59">
         <v>0.9</v>
       </c>
-      <c r="X59" s="3">
+      <c r="X59" s="2">
         <v>1.4</v>
       </c>
     </row>
@@ -5980,7 +6006,7 @@
       <c r="D60" t="s">
         <v>218</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="E60" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F60" t="s">
@@ -5998,7 +6024,7 @@
       <c r="M60">
         <v>2</v>
       </c>
-      <c r="N60" s="3">
+      <c r="N60" s="2">
         <v>2</v>
       </c>
       <c r="O60">
@@ -6013,7 +6039,7 @@
       <c r="T60">
         <v>3</v>
       </c>
-      <c r="U60" s="3">
+      <c r="U60" s="2">
         <v>4</v>
       </c>
       <c r="V60">
@@ -6022,7 +6048,7 @@
       <c r="W60">
         <v>-1</v>
       </c>
-      <c r="X60" s="3">
+      <c r="X60" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -6039,7 +6065,7 @@
       <c r="D61" t="s">
         <v>221</v>
       </c>
-      <c r="E61" s="2" t="s">
+      <c r="E61" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F61" t="s">
@@ -6054,13 +6080,13 @@
       <c r="K61" t="s">
         <v>59</v>
       </c>
-      <c r="L61" s="3">
+      <c r="L61" s="2">
         <v>14</v>
       </c>
       <c r="M61">
         <v>2</v>
       </c>
-      <c r="N61" s="3">
+      <c r="N61" s="2">
         <v>2</v>
       </c>
       <c r="O61">
@@ -6075,7 +6101,7 @@
       <c r="T61">
         <v>1.2</v>
       </c>
-      <c r="U61" s="3">
+      <c r="U61" s="2">
         <v>1.5</v>
       </c>
       <c r="V61">
@@ -6084,7 +6110,7 @@
       <c r="W61">
         <v>1</v>
       </c>
-      <c r="X61" s="3">
+      <c r="X61" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6101,7 +6127,7 @@
       <c r="D62" t="s">
         <v>224</v>
       </c>
-      <c r="E62" s="2" t="s">
+      <c r="E62" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F62" t="s">
@@ -6122,7 +6148,7 @@
       <c r="M62">
         <v>5</v>
       </c>
-      <c r="N62" s="3">
+      <c r="N62" s="2">
         <v>4</v>
       </c>
       <c r="O62">
@@ -6137,7 +6163,7 @@
       <c r="T62">
         <v>6</v>
       </c>
-      <c r="U62" s="3">
+      <c r="U62" s="2">
         <v>8</v>
       </c>
       <c r="V62">
@@ -6146,7 +6172,7 @@
       <c r="W62">
         <v>6</v>
       </c>
-      <c r="X62" s="3">
+      <c r="X62" s="2">
         <v>8</v>
       </c>
     </row>
@@ -6163,7 +6189,7 @@
       <c r="D63" t="s">
         <v>227</v>
       </c>
-      <c r="E63" s="2" t="s">
+      <c r="E63" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F63" t="s">
@@ -6184,7 +6210,7 @@
       <c r="M63">
         <v>6</v>
       </c>
-      <c r="N63" s="3">
+      <c r="N63" s="2">
         <v>5</v>
       </c>
       <c r="O63">
@@ -6199,7 +6225,7 @@
       <c r="T63">
         <v>-30</v>
       </c>
-      <c r="U63" s="3">
+      <c r="U63" s="2">
         <v>-30</v>
       </c>
       <c r="V63">
@@ -6208,7 +6234,7 @@
       <c r="W63">
         <v>32</v>
       </c>
-      <c r="X63" s="3">
+      <c r="X63" s="2">
         <v>40</v>
       </c>
       <c r="Y63">
@@ -6217,7 +6243,7 @@
       <c r="Z63">
         <v>15</v>
       </c>
-      <c r="AA63" s="3">
+      <c r="AA63" s="2">
         <v>18</v>
       </c>
       <c r="AB63">
@@ -6226,7 +6252,7 @@
       <c r="AC63">
         <v>1.5</v>
       </c>
-      <c r="AD63" s="3">
+      <c r="AD63" s="2">
         <v>2</v>
       </c>
     </row>
@@ -6240,7 +6266,7 @@
       <c r="C64" t="s">
         <v>229</v>
       </c>
-      <c r="E64" s="2" t="s">
+      <c r="E64" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F64" t="s">
@@ -6255,7 +6281,7 @@
       <c r="M64">
         <v>4</v>
       </c>
-      <c r="N64" s="3">
+      <c r="N64" s="2">
         <v>4</v>
       </c>
       <c r="O64">
@@ -6270,7 +6296,7 @@
       <c r="T64">
         <v>50</v>
       </c>
-      <c r="U64" s="3">
+      <c r="U64" s="2">
         <v>50</v>
       </c>
       <c r="V64">
@@ -6279,7 +6305,7 @@
       <c r="W64">
         <v>0.1</v>
       </c>
-      <c r="X64" s="3">
+      <c r="X64" s="2">
         <v>0.15</v>
       </c>
     </row>
@@ -6293,7 +6319,7 @@
       <c r="C65" t="s">
         <v>231</v>
       </c>
-      <c r="E65" s="2" t="s">
+      <c r="E65" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F65" t="s">
@@ -6308,7 +6334,7 @@
       <c r="M65">
         <v>5</v>
       </c>
-      <c r="N65" s="3">
+      <c r="N65" s="2">
         <v>5</v>
       </c>
       <c r="O65">
@@ -6323,7 +6349,7 @@
       <c r="T65">
         <v>1</v>
       </c>
-      <c r="U65" s="3">
+      <c r="U65" s="2">
         <v>1</v>
       </c>
       <c r="V65">
@@ -6332,7 +6358,7 @@
       <c r="W65">
         <v>1</v>
       </c>
-      <c r="X65" s="3">
+      <c r="X65" s="2">
         <v>1.5</v>
       </c>
     </row>
@@ -6349,7 +6375,7 @@
       <c r="D66" t="s">
         <v>234</v>
       </c>
-      <c r="E66" s="2" t="s">
+      <c r="E66" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F66" t="s">
@@ -6364,7 +6390,7 @@
       <c r="M66">
         <v>4</v>
       </c>
-      <c r="N66" s="3">
+      <c r="N66" s="2">
         <v>4</v>
       </c>
       <c r="O66">
@@ -6379,7 +6405,7 @@
       <c r="T66">
         <v>12</v>
       </c>
-      <c r="U66" s="3">
+      <c r="U66" s="2">
         <v>15</v>
       </c>
       <c r="V66">
@@ -6388,7 +6414,7 @@
       <c r="W66">
         <v>1</v>
       </c>
-      <c r="X66" s="3">
+      <c r="X66" s="2">
         <v>1</v>
       </c>
       <c r="Y66">
@@ -6397,7 +6423,7 @@
       <c r="Z66">
         <v>1</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AA66" s="2">
         <v>1</v>
       </c>
       <c r="AB66">
@@ -6406,8 +6432,133 @@
       <c r="AC66">
         <v>5</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AD66" s="2">
         <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:27">
+      <c r="A67">
+        <v>68</v>
+      </c>
+      <c r="B67" t="s">
+        <v>235</v>
+      </c>
+      <c r="C67" t="s">
+        <v>236</v>
+      </c>
+      <c r="D67" t="s">
+        <v>237</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F67" t="s">
+        <v>45</v>
+      </c>
+      <c r="G67" t="s">
+        <v>40</v>
+      </c>
+      <c r="K67" t="s">
+        <v>59</v>
+      </c>
+      <c r="L67" s="2">
+        <v>14</v>
+      </c>
+      <c r="M67">
+        <v>2</v>
+      </c>
+      <c r="N67" s="2">
+        <v>1</v>
+      </c>
+      <c r="O67">
+        <v>1</v>
+      </c>
+      <c r="P67">
+        <v>1</v>
+      </c>
+      <c r="S67">
+        <v>9</v>
+      </c>
+      <c r="T67">
+        <v>2</v>
+      </c>
+      <c r="U67" s="2">
+        <v>2</v>
+      </c>
+      <c r="V67">
+        <v>14</v>
+      </c>
+      <c r="W67">
+        <v>1</v>
+      </c>
+      <c r="X67" s="2">
+        <v>1</v>
+      </c>
+      <c r="Y67">
+        <v>70</v>
+      </c>
+      <c r="Z67">
+        <v>1</v>
+      </c>
+      <c r="AA67" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:24">
+      <c r="A68">
+        <v>69</v>
+      </c>
+      <c r="B68" t="s">
+        <v>238</v>
+      </c>
+      <c r="C68" t="s">
+        <v>239</v>
+      </c>
+      <c r="D68" t="s">
+        <v>239</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F68" t="s">
+        <v>45</v>
+      </c>
+      <c r="G68" t="s">
+        <v>40</v>
+      </c>
+      <c r="K68" t="s">
+        <v>41</v>
+      </c>
+      <c r="L68" s="2"/>
+      <c r="M68">
+        <v>5</v>
+      </c>
+      <c r="N68" s="2">
+        <v>3</v>
+      </c>
+      <c r="O68">
+        <v>1</v>
+      </c>
+      <c r="P68">
+        <v>1</v>
+      </c>
+      <c r="S68">
+        <v>3</v>
+      </c>
+      <c r="T68">
+        <v>1</v>
+      </c>
+      <c r="U68" s="2">
+        <v>1</v>
+      </c>
+      <c r="V68">
+        <v>72</v>
+      </c>
+      <c r="W68">
+        <v>1</v>
+      </c>
+      <c r="X68" s="2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6420,7 +6571,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
@@ -6448,19 +6599,19 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="G1" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="H1" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="I1" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6468,13 +6619,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C2" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="I2">
         <v>-1</v>
@@ -6485,19 +6636,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C3" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D3" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E3" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="F3" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -6508,16 +6659,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C4" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D4" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E4" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -6528,16 +6679,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="C5" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="D5" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E5" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -6548,13 +6699,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="C6" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -6565,16 +6716,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="C7" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="D7" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="E7" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -6585,13 +6736,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="C8" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D8" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -6605,13 +6756,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C9" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D9" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -6625,13 +6776,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C10" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D10" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -6645,13 +6796,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C11" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="D11" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -6662,16 +6813,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C12" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D12" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E12" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -6682,16 +6833,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C13" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="D13" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E13" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -6702,19 +6853,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C14" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="D14" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -6725,16 +6876,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C15" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="D15" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="E15" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -6745,16 +6896,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C16" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D16" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E16" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -6765,13 +6916,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C17" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="D17" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -6785,16 +6936,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C18" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="D18" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="E18" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -6805,13 +6956,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C19" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D19" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -6825,13 +6976,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C20" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -6845,16 +6996,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C21" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="D21" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E21" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -6865,16 +7016,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="C22" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="D22" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="E22" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -6885,13 +7036,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C23" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="D23" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E23">
         <v>5</v>
@@ -6905,19 +7056,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C24" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="D24" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -6928,13 +7079,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C25" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="D25" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -6948,16 +7099,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="C26" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="D26" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E26" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -6971,16 +7122,16 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
+        <v>295</v>
+      </c>
+      <c r="C27" t="s">
+        <v>295</v>
+      </c>
+      <c r="D27" t="s">
+        <v>262</v>
+      </c>
+      <c r="E27" t="s">
         <v>290</v>
-      </c>
-      <c r="C27" t="s">
-        <v>290</v>
-      </c>
-      <c r="D27" t="s">
-        <v>257</v>
-      </c>
-      <c r="E27" t="s">
-        <v>285</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -6991,13 +7142,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C28" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="D28" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -7011,19 +7162,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C29" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="D29" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -7037,13 +7188,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="C30" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="D30" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -7057,19 +7208,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="C31" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="D31" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E31" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="F31" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -7080,19 +7231,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="C32" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="D32" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E32">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -7103,19 +7254,19 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C33" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="D33" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E33">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -7126,16 +7277,16 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C34" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="D34" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E34" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -7146,16 +7297,16 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C35" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="D35" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E35" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -7166,19 +7317,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="C36" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="D36" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E36" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="F36" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -7192,13 +7343,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C37" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="D37" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E37">
         <v>11</v>
@@ -7212,16 +7363,16 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="C38" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="D38" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E38" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -7232,13 +7383,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C39" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="D39" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -7255,16 +7406,16 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="C40" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="D40" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E40" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -7275,13 +7426,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C41" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="D41" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -7298,19 +7449,19 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C42" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="D42" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -7324,13 +7475,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C43" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="D43" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E43">
         <v>12</v>
@@ -7344,13 +7495,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C44" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="D44" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E44">
         <v>13</v>
@@ -7364,19 +7515,19 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C45" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="D45" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E45" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="F45" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="I45">
         <v>-1</v>
@@ -7387,16 +7538,16 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C46" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="D46" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="E46" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="I46">
         <v>1</v>
@@ -7407,13 +7558,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="C47" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="D47" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E47">
         <v>14</v>
@@ -7427,19 +7578,19 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C48" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="D48" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="I48">
         <v>-1</v>
@@ -7450,13 +7601,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C49" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="D49" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E49">
         <v>15</v>
@@ -7470,19 +7621,19 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C50" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="D50" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="I50">
         <v>-1</v>
@@ -7493,13 +7644,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="C51" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="D51" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E51">
         <v>16</v>
@@ -7513,13 +7664,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C52" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="D52" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -7533,13 +7684,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
+        <v>330</v>
+      </c>
+      <c r="C53" t="s">
+        <v>330</v>
+      </c>
+      <c r="D53" t="s">
         <v>325</v>
-      </c>
-      <c r="C53" t="s">
-        <v>325</v>
-      </c>
-      <c r="D53" t="s">
-        <v>320</v>
       </c>
       <c r="E53">
         <v>3</v>
@@ -7553,13 +7704,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C54" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="D54" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E54">
         <v>3</v>
@@ -7576,16 +7727,16 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C55" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="D55" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="E55" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="G55">
         <v>6</v>
@@ -7599,16 +7750,16 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C56" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="D56" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="E56" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="G56">
         <v>7</v>
@@ -7622,16 +7773,16 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="C57" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="D57" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="E57" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="G57">
         <v>8</v>
@@ -7645,16 +7796,16 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C58" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="D58" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E58" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="G58">
         <v>6</v>
@@ -7668,16 +7819,16 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C59" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="D59" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E59" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="G59">
         <v>7</v>
@@ -7691,16 +7842,16 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C60" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="D60" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E60" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="G60">
         <v>8</v>
@@ -7714,19 +7865,19 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C61" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="D61" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E61">
         <v>3</v>
       </c>
       <c r="F61" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="I61">
         <v>-1</v>
@@ -7737,13 +7888,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C62" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="D62" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E62">
         <v>20</v>
@@ -7757,16 +7908,16 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C63" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="D63" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="F63" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="I63">
         <v>-1</v>
@@ -7777,13 +7928,13 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C64" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="D64" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E64">
         <v>21</v>
@@ -7797,13 +7948,13 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C65" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="D65" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="E65">
         <v>3</v>
@@ -7817,19 +7968,19 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C66" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="D66" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E66">
         <v>14</v>
       </c>
       <c r="F66" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="I66">
         <v>-1</v>
@@ -7840,13 +7991,13 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="C67" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="D67" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E67">
         <v>22</v>
@@ -7860,13 +8011,13 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="D68" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E68" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="I68">
         <v>-1</v>
@@ -7877,13 +8028,13 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="D69" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E69" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="I69">
         <v>-1</v>
@@ -7894,13 +8045,13 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="D70" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="E70" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="I70">
         <v>-1</v>
@@ -7911,15 +8062,75 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
+        <v>353</v>
+      </c>
+      <c r="D71" t="s">
         <v>348</v>
       </c>
-      <c r="D71" t="s">
-        <v>343</v>
-      </c>
       <c r="E71" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="I71">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72">
+        <v>70</v>
+      </c>
+      <c r="B72" t="s">
+        <v>235</v>
+      </c>
+      <c r="D72" t="s">
+        <v>265</v>
+      </c>
+      <c r="E72">
+        <v>33</v>
+      </c>
+      <c r="F72" t="s">
+        <v>302</v>
+      </c>
+      <c r="I72">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
+      <c r="A73">
+        <v>71</v>
+      </c>
+      <c r="B73" t="s">
+        <v>354</v>
+      </c>
+      <c r="D73" t="s">
+        <v>249</v>
+      </c>
+      <c r="E73" t="s">
+        <v>254</v>
+      </c>
+      <c r="F73" t="s">
+        <v>298</v>
+      </c>
+      <c r="G73">
+        <v>1</v>
+      </c>
+      <c r="I73">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="A74">
+        <v>72</v>
+      </c>
+      <c r="B74" t="s">
+        <v>355</v>
+      </c>
+      <c r="D74" t="s">
+        <v>265</v>
+      </c>
+      <c r="E74">
+        <v>34</v>
+      </c>
+      <c r="I74">
         <v>-1</v>
       </c>
     </row>
@@ -7933,7 +8144,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:P36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9.425" customWidth="1"/>
@@ -7956,13 +8167,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="D1" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>9</v>
@@ -7992,10 +8203,10 @@
         <v>28</v>
       </c>
       <c r="O1" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="P1" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -8003,10 +8214,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="C2" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -8032,10 +8243,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="C3" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -8055,10 +8266,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="C4" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -8072,10 +8283,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="C5" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -8107,10 +8318,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="C6" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -8130,10 +8341,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="C7" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -8153,10 +8364,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>369</v>
+      </c>
+      <c r="C8" t="s">
         <v>362</v>
-      </c>
-      <c r="C8" t="s">
-        <v>355</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -8176,10 +8387,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C9" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -8199,10 +8410,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="C10" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -8222,10 +8433,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="C11" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -8251,10 +8462,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C12" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -8280,10 +8491,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="C13" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -8303,10 +8514,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C14" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -8326,10 +8537,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="C15" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -8349,10 +8560,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="C16" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -8372,10 +8583,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C17" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -8395,10 +8606,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="C18" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -8418,10 +8629,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="C19" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -8435,10 +8646,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C20" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -8455,7 +8666,7 @@
         <v>222</v>
       </c>
       <c r="C21" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -8469,10 +8680,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="C22" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -8492,10 +8703,10 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="C23" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -8515,10 +8726,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="C24" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -8538,10 +8749,10 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="C25" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -8561,10 +8772,10 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="C26" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -8584,10 +8795,10 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="C27" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -8607,10 +8818,10 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="C28" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -8630,10 +8841,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="C29" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -8653,10 +8864,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="C30" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -8676,10 +8887,10 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="C31" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -8699,10 +8910,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="C32" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -8722,10 +8933,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="C33" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -8745,10 +8956,10 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="C34" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -8761,6 +8972,64 @@
       </c>
       <c r="H34">
         <v>0.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35" t="s">
+        <v>387</v>
+      </c>
+      <c r="C35" t="s">
+        <v>366</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>9</v>
+      </c>
+      <c r="H35">
+        <v>2</v>
+      </c>
+      <c r="I35" s="2">
+        <v>2</v>
+      </c>
+      <c r="J35">
+        <v>14</v>
+      </c>
+      <c r="K35">
+        <v>1</v>
+      </c>
+      <c r="L35" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36" t="s">
+        <v>388</v>
+      </c>
+      <c r="C36" t="s">
+        <v>362</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>71</v>
+      </c>
+      <c r="H36">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -8796,16 +9065,16 @@
         <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="E1" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="F1" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="G1" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8813,13 +9082,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="C2" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="D2" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -8833,13 +9102,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="C3" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="D3" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="F3" t="s">
         <v>45</v>
@@ -8850,13 +9119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="C4" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="D4" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="F4" t="s">
         <v>39</v>
@@ -8867,13 +9136,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="C5" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="D5" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -8887,13 +9156,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="C6" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="D6" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -8907,13 +9176,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="C7" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="D7" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -8927,13 +9196,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="C8" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="D8" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -8947,13 +9216,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>403</v>
+      </c>
+      <c r="C9" t="s">
         <v>394</v>
       </c>
-      <c r="C9" t="s">
-        <v>385</v>
-      </c>
       <c r="D9" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -8967,13 +9236,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>404</v>
+      </c>
+      <c r="C10" t="s">
+        <v>394</v>
+      </c>
+      <c r="D10" t="s">
         <v>395</v>
-      </c>
-      <c r="C10" t="s">
-        <v>385</v>
-      </c>
-      <c r="D10" t="s">
-        <v>386</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -8987,13 +9256,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="C11" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="D11" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="E11" t="s">
         <v>45</v>

--- a/Assets/StreamingAssets/Configurations/Cards.xlsx
+++ b/Assets/StreamingAssets/Configurations/Cards.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F2C36A-6F33-499C-B9F9-1B8A589D979D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" activeTab="2"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -24,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1232,167 +1236,17 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1417,188 +1271,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1624,251 +1298,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color 